--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260629</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5510</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2469</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2933</v>
+      </c>
+      <c r="E2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35393.41</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4027.2648</v>
+        <v>4073.9017</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.26</v>
+        <v>1.16</v>
       </c>
       <c r="F2" t="n">
-        <v>16211.96</v>
+        <v>16662.2</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15782.2229</v>
+        <v>15812.8707</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.44</v>
+        <v>0.19</v>
       </c>
       <c r="F3" t="n">
-        <v>19312</v>
+        <v>18515.24</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4194.2089</v>
+        <v>4216.6985</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.07</v>
+        <v>0.54</v>
       </c>
       <c r="F4" t="n">
-        <v>9324.83</v>
+        <v>9163.6</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4868.2205</v>
+        <v>4926.921</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.03</v>
+        <v>1.21</v>
       </c>
       <c r="F5" t="n">
-        <v>10680.83</v>
+        <v>10537.24</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2032.2842</v>
+        <v>2126.0105</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.65</v>
+        <v>4.61</v>
       </c>
       <c r="F6" t="n">
-        <v>2017.28</v>
+        <v>2300.72</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8601.407499999999</v>
+        <v>8597.8932</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.54</v>
+        <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>7554.64</v>
+        <v>7500.59</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6506 @@
           <t>20260629</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>35393.41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.77</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>211.6517</v>
+      </c>
+      <c r="J2" t="n">
+        <v>128277.82</v>
+      </c>
+      <c r="K2" t="n">
+        <v>638487.95323</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920367.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" t="n">
+        <v>108653.56</v>
+      </c>
+      <c r="K3" t="n">
+        <v>208994.03686</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>688548.SH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20.0052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>652667.88</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2722803.786</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688796.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="D5" t="n">
+        <v>110.56</v>
+      </c>
+      <c r="E5" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>110.56</v>
+      </c>
+      <c r="G5" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.0043</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38158.12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>402549.101</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688233.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>184.14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>194.33</v>
+      </c>
+      <c r="E6" t="n">
+        <v>179.17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>194.33</v>
+      </c>
+      <c r="G6" t="n">
+        <v>161.94</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0012</v>
+      </c>
+      <c r="J6" t="n">
+        <v>223184.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4201717.12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688120.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>264.93</v>
+      </c>
+      <c r="D7" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>264.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>183248.82</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5260505.401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="D8" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24287.84</v>
+      </c>
+      <c r="K8" t="n">
+        <v>68247.67380999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301528.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="D9" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>61.21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>62</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>61002.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>423014.74525</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301307.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="F10" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>210967.63</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1416644.13731</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>944735.79</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3294047.431</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300553.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D2" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="E2" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-14.69</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-19.9973</v>
+      </c>
+      <c r="J2" t="n">
+        <v>70372.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>447124.17662</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="D3" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="F3" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-17.4762</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1720206.26</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6208002.34467</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301502.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-14.72</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-17.1802</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25721.59</v>
+      </c>
+      <c r="K4" t="n">
+        <v>190476.55522</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301051.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17.0802</v>
+      </c>
+      <c r="J5" t="n">
+        <v>487200.81</v>
+      </c>
+      <c r="K5" t="n">
+        <v>908360.11209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688143.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>212</v>
+      </c>
+      <c r="D6" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>172</v>
+      </c>
+      <c r="F6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>215</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-16.2791</v>
+      </c>
+      <c r="J6" t="n">
+        <v>125799.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2303342.136</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>920083.BJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>56</v>
+      </c>
+      <c r="D7" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-15.9624</v>
+      </c>
+      <c r="J7" t="n">
+        <v>73786.00999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>382278.87881</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300264.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-15.2508</v>
+      </c>
+      <c r="J8" t="n">
+        <v>727867.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>638918.9349399999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301319.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>170</v>
+      </c>
+      <c r="F9" t="n">
+        <v>177.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>207</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-29.99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-14.4879</v>
+      </c>
+      <c r="J9" t="n">
+        <v>154731.44</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2834268.51031</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300057.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-13.1343</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1529883.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1395328.0818</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>920725.BJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>107</v>
+      </c>
+      <c r="D11" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="E11" t="n">
+        <v>93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-13.95</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-13.0435</v>
+      </c>
+      <c r="J11" t="n">
+        <v>77648.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>770569.9383799999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.7143</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2794103</v>
+      </c>
+      <c r="H2" t="n">
+        <v>896799</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1350856</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2247655</v>
+      </c>
+      <c r="K2" t="n">
+        <v>454057</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39149611.08</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000021.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.998100000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13770298102</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1650209506.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1927024746.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3577234253.14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>276815239.44</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="N3" t="n">
+        <v>92653826248.8</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000551.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>创元科技</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.0274</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2425263548</v>
+      </c>
+      <c r="H4" t="n">
+        <v>385459696</v>
+      </c>
+      <c r="I4" t="n">
+        <v>294511065.65</v>
+      </c>
+      <c r="J4" t="n">
+        <v>679970761.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-90948630.34999999</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9729707816.16</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000636.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.2548</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="G5" t="n">
+        <v>277035883679.11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>277035883679.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>277035883679.11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>554071767358.22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>200</v>
+      </c>
+      <c r="N5" t="n">
+        <v>92873442419.97</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>严重异常期间日收盘价格涨幅偏离值累计达到200%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-8.8545</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4315858599</v>
+      </c>
+      <c r="H6" t="n">
+        <v>748459054.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>727374289.87</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1475833344.82</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-21084765.08</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15432540411.98</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000859.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>国风新材</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-9.9704</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2373033929</v>
+      </c>
+      <c r="H7" t="n">
+        <v>178689903</v>
+      </c>
+      <c r="I7" t="n">
+        <v>179118322.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>357808225.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>428419.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8170838471.52</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000920.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>沃顿科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.021</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>778272145</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82089721</v>
+      </c>
+      <c r="I8" t="n">
+        <v>106447634.34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>188537355.34</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24357913.34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7419798302.6</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000962.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>东方钽业</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.8708</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11437589797</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1901961470.22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1835274884.52</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3737236354.74</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-66686585.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="N9" t="n">
+        <v>47238326231.2</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000967.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>盈峰环境</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-9.9718</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2397813592</v>
+      </c>
+      <c r="H10" t="n">
+        <v>627326485.49</v>
+      </c>
+      <c r="I10" t="n">
+        <v>461734641.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1089061126.79</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-165591844.19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32132885410.89</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000988.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>177.03</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9975</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19961381256</v>
+      </c>
+      <c r="H11" t="n">
+        <v>832463339.5599999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2215275126.59</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3047738466.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1382811787.03</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="N11" t="n">
+        <v>177912610858.71</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001270.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>铖昌科技</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>153.31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.954800000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4821942379</v>
+      </c>
+      <c r="H12" t="n">
+        <v>619771916.42</v>
+      </c>
+      <c r="I12" t="n">
+        <v>784786547.37</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1404558463.79</v>
+      </c>
+      <c r="K12" t="n">
+        <v>165014630.95</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>31398387177.36</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001331.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>胜通能源</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.5932</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1136792257</v>
+      </c>
+      <c r="H13" t="n">
+        <v>181932769.09</v>
+      </c>
+      <c r="I13" t="n">
+        <v>191157412.55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>373090181.64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9224643.460000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14649000187.5</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.9719</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33.23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4474761050</v>
+      </c>
+      <c r="H14" t="n">
+        <v>721741418.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>466481700.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1188223118.32</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-255259718.28</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13619056360</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002180.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>奔图科技</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0344</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1655544574</v>
+      </c>
+      <c r="H15" t="n">
+        <v>257068917.82</v>
+      </c>
+      <c r="I15" t="n">
+        <v>314535748.16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>571604665.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>57466830.34</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M15" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="N15" t="n">
+        <v>21778202842.98</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002208.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>合肥城建</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2092085939</v>
+      </c>
+      <c r="H16" t="n">
+        <v>274340260.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>315868788.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>590209049.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>41528527.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14760468267.46</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002208.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>合肥城建</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3855676647</v>
+      </c>
+      <c r="H17" t="n">
+        <v>449786472.18</v>
+      </c>
+      <c r="I17" t="n">
+        <v>474175566.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>923962038.38</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24389094.02</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M17" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14760468267.46</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002273.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>水晶光电</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-9.9916</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3736855057</v>
+      </c>
+      <c r="H18" t="n">
+        <v>844609916.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>616101222.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1460711138.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-228508694.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>43927027722.75</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002323.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>*ST雅博</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.3846</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>210617376</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20965991.68</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27697289.84</v>
+      </c>
+      <c r="J19" t="n">
+        <v>48663281.52</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6731298.16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2905072590.54</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.171</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5963464944</v>
+      </c>
+      <c r="H20" t="n">
+        <v>788975259.45</v>
+      </c>
+      <c r="I20" t="n">
+        <v>752377448.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1541352708.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-36597810.75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="N20" t="n">
+        <v>14810070326.69</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002409.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>雅克科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>207.46</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8436285956</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1246702649.41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>806680193.97</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2053382843.38</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-440022455.44</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="N21" t="n">
+        <v>66080729092.62</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002485.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST雪发</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.0193</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G22" t="n">
+        <v>88784302</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21701946.35</v>
+      </c>
+      <c r="I22" t="n">
+        <v>17696509.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>39398455.95</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-4005436.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-4.51</v>
+      </c>
+      <c r="M22" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2959360000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002559.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>亚威股份</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.6052</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2139614560</v>
+      </c>
+      <c r="H23" t="n">
+        <v>281590942.98</v>
+      </c>
+      <c r="I23" t="n">
+        <v>236952399.85</v>
+      </c>
+      <c r="J23" t="n">
+        <v>518543342.83</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-44638543.13</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6552065117</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002559.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>亚威股份</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.6052</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4331576967</v>
+      </c>
+      <c r="H24" t="n">
+        <v>437526949.86</v>
+      </c>
+      <c r="I24" t="n">
+        <v>540619994.83</v>
+      </c>
+      <c r="J24" t="n">
+        <v>978146944.6900001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>103093044.97</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6552065117</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002568.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>百润股份</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.9809</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G25" t="n">
+        <v>882388795</v>
+      </c>
+      <c r="H25" t="n">
+        <v>184738118.05</v>
+      </c>
+      <c r="I25" t="n">
+        <v>230088293.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>414826411.95</v>
+      </c>
+      <c r="K25" t="n">
+        <v>45350175.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13201306853.3</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-10.0088</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2666219473</v>
+      </c>
+      <c r="H26" t="n">
+        <v>380618630.55</v>
+      </c>
+      <c r="I26" t="n">
+        <v>276264906.97</v>
+      </c>
+      <c r="J26" t="n">
+        <v>656883537.52</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-104353723.58</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="N26" t="n">
+        <v>11959943827</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002655.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>共达电声</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-9.9941</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1521581863</v>
+      </c>
+      <c r="H27" t="n">
+        <v>400320510.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>237527489</v>
+      </c>
+      <c r="J27" t="n">
+        <v>637847999.97</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-162793021.97</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="N27" t="n">
+        <v>16741289058</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002735.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>王子新材</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-4.759</v>
+      </c>
+      <c r="F28" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1003310531</v>
+      </c>
+      <c r="H28" t="n">
+        <v>206190679.39</v>
+      </c>
+      <c r="I28" t="n">
+        <v>137989261.74</v>
+      </c>
+      <c r="J28" t="n">
+        <v>344179941.13</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-68201417.65000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4506788181.21</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002741.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>光华科技</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-9.997400000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1937302346</v>
+      </c>
+      <c r="H29" t="n">
+        <v>241948704.96</v>
+      </c>
+      <c r="I29" t="n">
+        <v>226876792.75</v>
+      </c>
+      <c r="J29" t="n">
+        <v>468825497.71</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-15071912.21</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M29" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>15007809168</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11.7647</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2983355</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1490948</v>
+      </c>
+      <c r="I30" t="n">
+        <v>975243</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2466191</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-515705</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-17.29</v>
+      </c>
+      <c r="M30" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="N30" t="n">
+        <v>35503600.64</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002859.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>洁美科技</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.0029</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4460491709</v>
+      </c>
+      <c r="H31" t="n">
+        <v>652098099.47</v>
+      </c>
+      <c r="I31" t="n">
+        <v>846521234.23</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1498619333.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>194423134.76</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M31" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>46333417080.75</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002859.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>洁美科技</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10.0029</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7830977683</v>
+      </c>
+      <c r="H32" t="n">
+        <v>909794704.64</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1038419112.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1948213817.14</v>
+      </c>
+      <c r="K32" t="n">
+        <v>128624407.86</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M32" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="N32" t="n">
+        <v>46333417080.75</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-8.571400000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2581787</v>
+      </c>
+      <c r="H33" t="n">
+        <v>950328.72</v>
+      </c>
+      <c r="I33" t="n">
+        <v>922845</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1873173.72</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-27483.72</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="M33" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32403984.32</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002943.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>宇晶股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-4.9453</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1258840139</v>
+      </c>
+      <c r="H34" t="n">
+        <v>402448928.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>228860505.88</v>
+      </c>
+      <c r="J34" t="n">
+        <v>631309434.28</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-173588422.52</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-13.79</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9183883458.6</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002962.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>五方光电</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.3764</v>
+      </c>
+      <c r="F35" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1414565937</v>
+      </c>
+      <c r="H35" t="n">
+        <v>155093559.51</v>
+      </c>
+      <c r="I35" t="n">
+        <v>122628466.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>277722026.11</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-32465092.91</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4384496744.8</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>002962.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>五方光电</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.3764</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2431355370</v>
+      </c>
+      <c r="H36" t="n">
+        <v>163290640.51</v>
+      </c>
+      <c r="I36" t="n">
+        <v>235927741.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>399218381.91</v>
+      </c>
+      <c r="K36" t="n">
+        <v>72637100.89</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M36" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4384496744.8</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>002971.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.1906</v>
+      </c>
+      <c r="F37" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2129458112</v>
+      </c>
+      <c r="H37" t="n">
+        <v>264620998.65</v>
+      </c>
+      <c r="I37" t="n">
+        <v>158679809.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>423300808.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-105941189.05</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M37" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10771360974.5</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>111012.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>福新转债</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>266.53</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-16.7866</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>512100870</v>
+      </c>
+      <c r="H38" t="n">
+        <v>134056280</v>
+      </c>
+      <c r="I38" t="n">
+        <v>127489370</v>
+      </c>
+      <c r="J38" t="n">
+        <v>261545650</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-6566910</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M38" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价跌幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>118011.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>银微转债</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>178.129</v>
+      </c>
+      <c r="E39" t="n">
+        <v>19.9999</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>125978170</v>
+      </c>
+      <c r="H39" t="n">
+        <v>86969700</v>
+      </c>
+      <c r="I39" t="n">
+        <v>91914560</v>
+      </c>
+      <c r="J39" t="n">
+        <v>178884260</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4944860</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M39" t="n">
+        <v>142</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>123245.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>集智转债</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>337.764</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>827996761</v>
+      </c>
+      <c r="H40" t="n">
+        <v>269858712.64</v>
+      </c>
+      <c r="I40" t="n">
+        <v>254243257.72</v>
+      </c>
+      <c r="J40" t="n">
+        <v>524101970.36</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-15615454.92</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="M40" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>127079.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>华亚转债</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>314</v>
+      </c>
+      <c r="E41" t="n">
+        <v>17.3832</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>2788822760</v>
+      </c>
+      <c r="H41" t="n">
+        <v>781982441.96</v>
+      </c>
+      <c r="I41" t="n">
+        <v>790392605.52</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1572375047.48</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8410163.560000001</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>200017.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>深中华B</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7.8125</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G42" t="n">
+        <v>994692</v>
+      </c>
+      <c r="H42" t="n">
+        <v>368064.03</v>
+      </c>
+      <c r="I42" t="n">
+        <v>388251.68</v>
+      </c>
+      <c r="J42" t="n">
+        <v>756315.71</v>
+      </c>
+      <c r="K42" t="n">
+        <v>20187.65</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M42" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2793710962.72</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1219415</v>
+      </c>
+      <c r="H43" t="n">
+        <v>835977</v>
+      </c>
+      <c r="I43" t="n">
+        <v>354674</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1190651</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-481303</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-39.47</v>
+      </c>
+      <c r="M43" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="N43" t="n">
+        <v>30054037.5</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>300162.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>雷曼光电</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.6381</v>
+      </c>
+      <c r="F44" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1630415793</v>
+      </c>
+      <c r="H44" t="n">
+        <v>236649056.06</v>
+      </c>
+      <c r="I44" t="n">
+        <v>194244715.03</v>
+      </c>
+      <c r="J44" t="n">
+        <v>430893771.09</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-42404341.03</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4259914161</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>300204.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>舒泰神</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1212504348</v>
+      </c>
+      <c r="H45" t="n">
+        <v>113318166.96</v>
+      </c>
+      <c r="I45" t="n">
+        <v>323765101.72</v>
+      </c>
+      <c r="J45" t="n">
+        <v>437083268.68</v>
+      </c>
+      <c r="K45" t="n">
+        <v>210446934.76</v>
+      </c>
+      <c r="L45" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="M45" t="n">
+        <v>36.05</v>
+      </c>
+      <c r="N45" t="n">
+        <v>10561309583.28</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>300260.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>新莱应材</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>11.5178</v>
+      </c>
+      <c r="F46" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="G46" t="n">
+        <v>9719949359</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1701627564.04</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1696328992.18</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3397956556.22</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-5298571.86</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="N46" t="n">
+        <v>29799187502</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>300264.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>佳创视讯</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-15.2508</v>
+      </c>
+      <c r="F47" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="G47" t="n">
+        <v>638918935</v>
+      </c>
+      <c r="H47" t="n">
+        <v>113620679.64</v>
+      </c>
+      <c r="I47" t="n">
+        <v>64591500</v>
+      </c>
+      <c r="J47" t="n">
+        <v>178212179.64</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-49029179.64</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-7.67</v>
+      </c>
+      <c r="M47" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3066799830.84</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>300434.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>金石亚药</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.9778</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="G48" t="n">
+        <v>390684404</v>
+      </c>
+      <c r="H48" t="n">
+        <v>57465012</v>
+      </c>
+      <c r="I48" t="n">
+        <v>110921687.15</v>
+      </c>
+      <c r="J48" t="n">
+        <v>168386699.15</v>
+      </c>
+      <c r="K48" t="n">
+        <v>53456675.15</v>
+      </c>
+      <c r="L48" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="M48" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3698264349.91</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>300436.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>广生堂</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1363483493</v>
+      </c>
+      <c r="H49" t="n">
+        <v>118409523.35</v>
+      </c>
+      <c r="I49" t="n">
+        <v>375240289.41</v>
+      </c>
+      <c r="J49" t="n">
+        <v>493649812.76</v>
+      </c>
+      <c r="K49" t="n">
+        <v>256830766.06</v>
+      </c>
+      <c r="L49" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="M49" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="N49" t="n">
+        <v>14569093016.64</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>300489.SZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>光智科技</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>309.67</v>
+      </c>
+      <c r="E50" t="n">
+        <v>9.331300000000001</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4768276707</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1238212151.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1129793320.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2368005472.4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-108418831</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="M50" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="N50" t="n">
+        <v>42935275111.27</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>日振幅值达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>300553.SZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>集智股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-19.9973</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="G51" t="n">
+        <v>447124177</v>
+      </c>
+      <c r="H51" t="n">
+        <v>99924542.19</v>
+      </c>
+      <c r="I51" t="n">
+        <v>116203056.8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>216127598.99</v>
+      </c>
+      <c r="K51" t="n">
+        <v>16278514.61</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="M51" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4989302951.85</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>300706.SZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>阿石创</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>91.88</v>
+      </c>
+      <c r="E52" t="n">
+        <v>19.0618</v>
+      </c>
+      <c r="F52" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2818792516</v>
+      </c>
+      <c r="H52" t="n">
+        <v>107965812.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>127346698</v>
+      </c>
+      <c r="J52" t="n">
+        <v>235312510.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>19380885.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M52" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="N52" t="n">
+        <v>10458750842.12</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>300721.SZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>怡达股份</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="E53" t="n">
+        <v>11.7154</v>
+      </c>
+      <c r="F53" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1833329835</v>
+      </c>
+      <c r="H53" t="n">
+        <v>250083743.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>146148903.71</v>
+      </c>
+      <c r="J53" t="n">
+        <v>396232647.11</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-103934839.69</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="M53" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5712540413.01</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>301051.SZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>信濠光电</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-17.0802</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="G54" t="n">
+        <v>908360112</v>
+      </c>
+      <c r="H54" t="n">
+        <v>152514662.62</v>
+      </c>
+      <c r="I54" t="n">
+        <v>149474934.55</v>
+      </c>
+      <c r="J54" t="n">
+        <v>301989597.17</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-3039728.07</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M54" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3925049076.08</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>301307.SZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>美利信</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1416644137</v>
+      </c>
+      <c r="H55" t="n">
+        <v>276341533.66</v>
+      </c>
+      <c r="I55" t="n">
+        <v>299972860.39</v>
+      </c>
+      <c r="J55" t="n">
+        <v>576314394.05</v>
+      </c>
+      <c r="K55" t="n">
+        <v>23631326.73</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M55" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7558127503.2</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>301392.SZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>汇成真空</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>261.12</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7.1042</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6944759265</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1125866455.08</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1329503051.42</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2455369506.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>203636596.34</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M56" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="N56" t="n">
+        <v>10652628280.32</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>301502.SZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>华阳智能</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-17.1802</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190476555</v>
+      </c>
+      <c r="H57" t="n">
+        <v>47513960.84</v>
+      </c>
+      <c r="I57" t="n">
+        <v>46555353.49</v>
+      </c>
+      <c r="J57" t="n">
+        <v>94069314.33</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-958607.35</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1673733520</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>301528.SZ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>多浦乐</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="G58" t="n">
+        <v>423014745</v>
+      </c>
+      <c r="H58" t="n">
+        <v>87970633.29000001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>118086489.61</v>
+      </c>
+      <c r="J58" t="n">
+        <v>206057122.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>30115856.32</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M58" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3441471175.2</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>600129.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>太极集团</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.0337</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G59" t="n">
+        <v>216100043</v>
+      </c>
+      <c r="H59" t="n">
+        <v>29353259</v>
+      </c>
+      <c r="I59" t="n">
+        <v>52047847.17</v>
+      </c>
+      <c r="J59" t="n">
+        <v>81401106.17</v>
+      </c>
+      <c r="K59" t="n">
+        <v>22694588.17</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7196007314.25</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>600162.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>香江控股</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-6.962</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2858776684</v>
+      </c>
+      <c r="H60" t="n">
+        <v>348039147.15</v>
+      </c>
+      <c r="I60" t="n">
+        <v>308978255.88</v>
+      </c>
+      <c r="J60" t="n">
+        <v>657017403.03</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-39060891.27</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="M60" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="N60" t="n">
+        <v>9609208078.68</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>600193.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>退市创兴</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3485348</v>
+      </c>
+      <c r="H61" t="n">
+        <v>996306</v>
+      </c>
+      <c r="I61" t="n">
+        <v>863370.4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1859676.4</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-132935.6</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="M61" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="N61" t="n">
+        <v>68059680</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>退市整理的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>600228.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>返利科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-5.5607</v>
+      </c>
+      <c r="F62" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1040408505</v>
+      </c>
+      <c r="H62" t="n">
+        <v>177693799.15</v>
+      </c>
+      <c r="I62" t="n">
+        <v>198733378.72</v>
+      </c>
+      <c r="J62" t="n">
+        <v>376427177.87</v>
+      </c>
+      <c r="K62" t="n">
+        <v>21039579.57</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M62" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4239418833.63</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>600246.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>万通发展</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-7.5113</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3744775888</v>
+      </c>
+      <c r="H63" t="n">
+        <v>533751456.99</v>
+      </c>
+      <c r="I63" t="n">
+        <v>300874884.87</v>
+      </c>
+      <c r="J63" t="n">
+        <v>834626341.86</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-232876572.12</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M63" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="N63" t="n">
+        <v>34915918431.72</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>600353.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>旭光电子</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-10.0042</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1918890113</v>
+      </c>
+      <c r="H64" t="n">
+        <v>195584377.42</v>
+      </c>
+      <c r="I64" t="n">
+        <v>126888397.92</v>
+      </c>
+      <c r="J64" t="n">
+        <v>322472775.34</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-68695979.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="M64" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="N64" t="n">
+        <v>35788065845.62</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>600491.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ST龙元</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-4.902</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G65" t="n">
+        <v>188805553</v>
+      </c>
+      <c r="H65" t="n">
+        <v>18848796</v>
+      </c>
+      <c r="I65" t="n">
+        <v>16768177</v>
+      </c>
+      <c r="J65" t="n">
+        <v>35616973</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-2080619</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1483865216.35</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格跌幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>600552.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>凯盛科技</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6.3514</v>
+      </c>
+      <c r="F66" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="G66" t="n">
+        <v>7603429625</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1191651621.71</v>
+      </c>
+      <c r="I66" t="n">
+        <v>876347554.8099999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2067999176.52</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-315304066.9</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="M66" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>29736225023.12</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>600576.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>祥源文旅</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10.0372</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="G67" t="n">
+        <v>159508268</v>
+      </c>
+      <c r="H67" t="n">
+        <v>30956082</v>
+      </c>
+      <c r="I67" t="n">
+        <v>30408351.02</v>
+      </c>
+      <c r="J67" t="n">
+        <v>61364433.02</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-547730.98</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="M67" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3909509291.36</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>600608.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>退市沪科</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2896492</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1493700.88</v>
+      </c>
+      <c r="I68" t="n">
+        <v>877119</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2370819.88</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-616581.88</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-21.29</v>
+      </c>
+      <c r="M68" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="N68" t="n">
+        <v>54123144.97</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>退市整理的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>600667.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>太极实业</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>29</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7.8869</v>
+      </c>
+      <c r="F69" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="G69" t="n">
+        <v>14260078746</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2122668874.89</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1311407165.14</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3434076040.03</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-811261709.75</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="M69" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="N69" t="n">
+        <v>60654723162</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>600734.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>*ST实达</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-4.9689</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G70" t="n">
+        <v>273150201</v>
+      </c>
+      <c r="H70" t="n">
+        <v>15632934</v>
+      </c>
+      <c r="I70" t="n">
+        <v>16311070.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>31944004.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>678136.5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3332115252.18</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格跌幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>600745.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>*ST闻泰</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4.9793</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2883810513</v>
+      </c>
+      <c r="H71" t="n">
+        <v>263984712.25</v>
+      </c>
+      <c r="I71" t="n">
+        <v>241609136.16</v>
+      </c>
+      <c r="J71" t="n">
+        <v>505593848.41</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-22375576.09</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M71" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="N71" t="n">
+        <v>22043108923.22</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>601636.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>旗滨集团</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E72" t="n">
+        <v>9.9664</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6381959545</v>
+      </c>
+      <c r="H72" t="n">
+        <v>704298840.28</v>
+      </c>
+      <c r="I72" t="n">
+        <v>819811593.67</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1524110433.95</v>
+      </c>
+      <c r="K72" t="n">
+        <v>115512753.39</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M72" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="N72" t="n">
+        <v>29053979608.96</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>603010.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>万盛股份</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="E73" t="n">
+        <v>5.9001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2111009479</v>
+      </c>
+      <c r="H73" t="n">
+        <v>312933276.2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>395194100.72</v>
+      </c>
+      <c r="J73" t="n">
+        <v>708127376.92</v>
+      </c>
+      <c r="K73" t="n">
+        <v>82260824.52</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M73" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="N73" t="n">
+        <v>10039990173.87</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>603078.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>江化微</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-6.2982</v>
+      </c>
+      <c r="F74" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3188482576</v>
+      </c>
+      <c r="H74" t="n">
+        <v>528515565.18</v>
+      </c>
+      <c r="I74" t="n">
+        <v>325092566.47</v>
+      </c>
+      <c r="J74" t="n">
+        <v>853608131.65</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-203422998.71</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="M74" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="N74" t="n">
+        <v>17326681552.64</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>603201.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>常润股份</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-10.0193</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>151342574</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32176109.12</v>
+      </c>
+      <c r="I75" t="n">
+        <v>11059651</v>
+      </c>
+      <c r="J75" t="n">
+        <v>43235760.12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-21116458.12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-13.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2638849935.42</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>603261.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>立航科技</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-8.0245</v>
+      </c>
+      <c r="F76" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G76" t="n">
+        <v>316472443</v>
+      </c>
+      <c r="H76" t="n">
+        <v>80458145.34999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>56286229</v>
+      </c>
+      <c r="J76" t="n">
+        <v>136744374.35</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-24171916.35</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="M76" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4077539207.42</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>603313.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>梦百合</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>6.1433</v>
+      </c>
+      <c r="F77" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="G77" t="n">
+        <v>649857108</v>
+      </c>
+      <c r="H77" t="n">
+        <v>65913219.43</v>
+      </c>
+      <c r="I77" t="n">
+        <v>44462524.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>110375743.63</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-21450695.23</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M77" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3549050424.7</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>603327.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>福蓉科技</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-9.9589</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1487014400</v>
+      </c>
+      <c r="H78" t="n">
+        <v>126677552.58</v>
+      </c>
+      <c r="I78" t="n">
+        <v>97644026.45999999</v>
+      </c>
+      <c r="J78" t="n">
+        <v>224321579.04</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-29033526.12</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="M78" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="N78" t="n">
+        <v>9168678587.200001</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>603336.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>宏辉果蔬</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E79" t="n">
+        <v>10.0671</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G79" t="n">
+        <v>268746899</v>
+      </c>
+      <c r="H79" t="n">
+        <v>59117720.08</v>
+      </c>
+      <c r="I79" t="n">
+        <v>62780638</v>
+      </c>
+      <c r="J79" t="n">
+        <v>121898358.08</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3662917.92</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M79" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4991495349</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="E80" t="n">
+        <v>6.2793</v>
+      </c>
+      <c r="F80" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1126356696</v>
+      </c>
+      <c r="H80" t="n">
+        <v>206068398.75</v>
+      </c>
+      <c r="I80" t="n">
+        <v>174247471.98</v>
+      </c>
+      <c r="J80" t="n">
+        <v>380315870.73</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-31820926.77</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="M80" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3501060100.08</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>603459.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>红板科技</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>102.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9.995699999999999</v>
+      </c>
+      <c r="F81" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2603458278</v>
+      </c>
+      <c r="H81" t="n">
+        <v>181989306.9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>463316731</v>
+      </c>
+      <c r="J81" t="n">
+        <v>645306037.9</v>
+      </c>
+      <c r="K81" t="n">
+        <v>281327424.1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M81" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8064080034.58</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>603637.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>镇海股份</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-10.0054</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G82" t="n">
+        <v>78045777</v>
+      </c>
+      <c r="H82" t="n">
+        <v>26320188</v>
+      </c>
+      <c r="I82" t="n">
+        <v>9301935</v>
+      </c>
+      <c r="J82" t="n">
+        <v>35622123</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-17018253</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-21.81</v>
+      </c>
+      <c r="M82" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3971732993.28</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>603687.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="E83" t="n">
+        <v>8.187099999999999</v>
+      </c>
+      <c r="F83" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3151812970</v>
+      </c>
+      <c r="H83" t="n">
+        <v>257967926</v>
+      </c>
+      <c r="I83" t="n">
+        <v>518745744.16</v>
+      </c>
+      <c r="J83" t="n">
+        <v>776713670.16</v>
+      </c>
+      <c r="K83" t="n">
+        <v>260777818.16</v>
+      </c>
+      <c r="L83" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="M83" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="N83" t="n">
+        <v>11193148432.4</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>603848.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>好太太</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-10.0068</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>76821417</v>
+      </c>
+      <c r="H84" t="n">
+        <v>21613155</v>
+      </c>
+      <c r="I84" t="n">
+        <v>10016102</v>
+      </c>
+      <c r="J84" t="n">
+        <v>31629257</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-11597053</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5356030661.41</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>603928.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>兴业股份</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9.9755</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>364018939</v>
+      </c>
+      <c r="H85" t="n">
+        <v>36669673.75</v>
+      </c>
+      <c r="I85" t="n">
+        <v>82344976.59999999</v>
+      </c>
+      <c r="J85" t="n">
+        <v>119014650.35</v>
+      </c>
+      <c r="K85" t="n">
+        <v>45675302.85</v>
+      </c>
+      <c r="L85" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="M85" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4582468800</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>605058.SH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-10.0026</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G86" t="n">
+        <v>189747390</v>
+      </c>
+      <c r="H86" t="n">
+        <v>27648351</v>
+      </c>
+      <c r="I86" t="n">
+        <v>25648887</v>
+      </c>
+      <c r="J86" t="n">
+        <v>53297238</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-1999464</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="M86" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4925199635.2</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>605081.SH</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>退市太和</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11.1111</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2015644</v>
+      </c>
+      <c r="H87" t="n">
+        <v>757168</v>
+      </c>
+      <c r="I87" t="n">
+        <v>849792.36</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1606960.36</v>
+      </c>
+      <c r="K87" t="n">
+        <v>92624.36</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M87" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="N87" t="n">
+        <v>45298828.8</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>退市整理的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>605178.SH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>时空科技</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="E88" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2217135402</v>
+      </c>
+      <c r="H88" t="n">
+        <v>387613027.8</v>
+      </c>
+      <c r="I88" t="n">
+        <v>565217009.7</v>
+      </c>
+      <c r="J88" t="n">
+        <v>952830037.5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>177603981.9</v>
+      </c>
+      <c r="L88" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="M88" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="N88" t="n">
+        <v>9645438000</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>605300.SH</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>佳禾食品</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="E89" t="n">
+        <v>9.9894</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G89" t="n">
+        <v>277871150</v>
+      </c>
+      <c r="H89" t="n">
+        <v>49060894.53</v>
+      </c>
+      <c r="I89" t="n">
+        <v>64448475.75</v>
+      </c>
+      <c r="J89" t="n">
+        <v>113509370.28</v>
+      </c>
+      <c r="K89" t="n">
+        <v>15387581.22</v>
+      </c>
+      <c r="L89" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="M89" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4703025478.95</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>605376.SH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>博迁新材</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5.8712</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G90" t="n">
+        <v>12072250182</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2368146859.35</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2859691821.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5227838680.85</v>
+      </c>
+      <c r="K90" t="n">
+        <v>491544962.15</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M90" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="N90" t="n">
+        <v>73117200000</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>605377.SH</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>华旺科技</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="E91" t="n">
+        <v>10.0578</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G91" t="n">
+        <v>143431332</v>
+      </c>
+      <c r="H91" t="n">
+        <v>35043829.54</v>
+      </c>
+      <c r="I91" t="n">
+        <v>42221279.8</v>
+      </c>
+      <c r="J91" t="n">
+        <v>77265109.34</v>
+      </c>
+      <c r="K91" t="n">
+        <v>7177450.26</v>
+      </c>
+      <c r="L91" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5299500951.36</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>688051.SH</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>佳华科技</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-0.7953</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2166581500</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2166581500</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2166581500</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4333163000</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>200</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1832815800</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续30个交易日内收盘价格跌幅偏离值累计达到-70%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>688120.SH</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>华海清科</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>316.32</v>
+      </c>
+      <c r="E93" t="n">
+        <v>20</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5260505400</v>
+      </c>
+      <c r="H93" t="n">
+        <v>949436781.11</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1109184584.94</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2058621366.05</v>
+      </c>
+      <c r="K93" t="n">
+        <v>159747803.83</v>
+      </c>
+      <c r="L93" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M93" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="N93" t="n">
+        <v>156493350092.64</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>688143.SH</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>长盈通</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>180</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-16.2791</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2303342100</v>
+      </c>
+      <c r="H94" t="n">
+        <v>458126099.58</v>
+      </c>
+      <c r="I94" t="n">
+        <v>214797308.39</v>
+      </c>
+      <c r="J94" t="n">
+        <v>672923407.97</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-243328791.19</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="M94" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="N94" t="n">
+        <v>22027396680</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>688143.SH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>长盈通</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>180</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-16.2791</v>
+      </c>
+      <c r="F95" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5659043300</v>
+      </c>
+      <c r="H95" t="n">
+        <v>512240860.72</v>
+      </c>
+      <c r="I95" t="n">
+        <v>427638587.68</v>
+      </c>
+      <c r="J95" t="n">
+        <v>939879448.4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-84602273.04000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="M95" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="N95" t="n">
+        <v>22027396680</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格跌幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>688233.SH</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>神工股份</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>194.33</v>
+      </c>
+      <c r="E96" t="n">
+        <v>20.0012</v>
+      </c>
+      <c r="F96" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4201717100</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1288024514.61</v>
+      </c>
+      <c r="I96" t="n">
+        <v>874431939.86</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2162456454.47</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-413592574.75</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-9.84</v>
+      </c>
+      <c r="M96" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="N96" t="n">
+        <v>33095513676.88</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>688233.SH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>神工股份</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>194.33</v>
+      </c>
+      <c r="E97" t="n">
+        <v>20.0012</v>
+      </c>
+      <c r="F97" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="G97" t="n">
+        <v>8378551300</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2155191721.21</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1500480461.03</v>
+      </c>
+      <c r="J97" t="n">
+        <v>3655672182.24</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-654711260.1799999</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="M97" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="N97" t="n">
+        <v>33095513676.88</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>688336.SH</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>三生国健</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="E98" t="n">
+        <v>19.9952</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G98" t="n">
+        <v>935576100</v>
+      </c>
+      <c r="H98" t="n">
+        <v>77562745.59999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>260436517.38</v>
+      </c>
+      <c r="J98" t="n">
+        <v>337999262.98</v>
+      </c>
+      <c r="K98" t="n">
+        <v>182873771.78</v>
+      </c>
+      <c r="L98" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="M98" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="N98" t="n">
+        <v>44493385150</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>688376.SH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>美埃科技</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="E99" t="n">
+        <v>13.0914</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3330188900</v>
+      </c>
+      <c r="H99" t="n">
+        <v>727868270.48</v>
+      </c>
+      <c r="I99" t="n">
+        <v>207178655.13</v>
+      </c>
+      <c r="J99" t="n">
+        <v>935046925.61</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-520689615.35</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-15.64</v>
+      </c>
+      <c r="M99" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="N99" t="n">
+        <v>16228880760.56</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="E100" t="n">
+        <v>20</v>
+      </c>
+      <c r="F100" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3294047400</v>
+      </c>
+      <c r="H100" t="n">
+        <v>415520362.62</v>
+      </c>
+      <c r="I100" t="n">
+        <v>378317890.3</v>
+      </c>
+      <c r="J100" t="n">
+        <v>793838252.92</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-37202472.32</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="M100" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N100" t="n">
+        <v>46361192894.64</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="E101" t="n">
+        <v>20</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5389164400</v>
+      </c>
+      <c r="H101" t="n">
+        <v>563536267.08</v>
+      </c>
+      <c r="I101" t="n">
+        <v>558447947.65</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1121984214.73</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-5088319.43</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M101" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="N101" t="n">
+        <v>46361192894.64</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260630</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5508</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2364</v>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32938.2</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4073.9017</v>
+        <v>4094.3972</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>16662.2</v>
+        <v>15303.26</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15812.8707</v>
+        <v>16205.5565</v>
       </c>
       <c r="E3" t="n">
-        <v>0.19</v>
+        <v>2.48</v>
       </c>
       <c r="F3" t="n">
-        <v>18515.24</v>
+        <v>17434.19</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4216.6985</v>
+        <v>4342.7123</v>
       </c>
       <c r="E4" t="n">
-        <v>0.54</v>
+        <v>2.99</v>
       </c>
       <c r="F4" t="n">
-        <v>9163.6</v>
+        <v>8598.26</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4926.921</v>
+        <v>4979.4328</v>
       </c>
       <c r="E5" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="F5" t="n">
-        <v>10537.24</v>
+        <v>9857.950000000001</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2126.0105</v>
+        <v>2207.8648</v>
       </c>
       <c r="E6" t="n">
-        <v>4.61</v>
+        <v>3.85</v>
       </c>
       <c r="F6" t="n">
-        <v>2300.72</v>
+        <v>2193.5</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8597.8932</v>
+        <v>8809.785900000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04</v>
+        <v>2.46</v>
       </c>
       <c r="F7" t="n">
-        <v>7500.59</v>
+        <v>6853.82</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6498 @@
           <t>20260630</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>32938.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920222.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D2" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="H2" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="I2" t="n">
+        <v>258.4737</v>
+      </c>
+      <c r="J2" t="n">
+        <v>99383.23</v>
+      </c>
+      <c r="K2" t="n">
+        <v>418136.01836</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300044.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20.0935</v>
+      </c>
+      <c r="J3" t="n">
+        <v>427079.85</v>
+      </c>
+      <c r="K3" t="n">
+        <v>199825.16004</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300269.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20.0436</v>
+      </c>
+      <c r="J4" t="n">
+        <v>326060</v>
+      </c>
+      <c r="K4" t="n">
+        <v>172607.046</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688728.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.0228</v>
+      </c>
+      <c r="J5" t="n">
+        <v>868276.49</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1765970.409</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300270.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0185</v>
+      </c>
+      <c r="J6" t="n">
+        <v>239018.83</v>
+      </c>
+      <c r="K6" t="n">
+        <v>298594.70983</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300540.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.0127</v>
+      </c>
+      <c r="J7" t="n">
+        <v>360976.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1271793.37561</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688355.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.0125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50143.67</v>
+      </c>
+      <c r="K8" t="n">
+        <v>89205.466</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300518.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.0073</v>
+      </c>
+      <c r="J9" t="n">
+        <v>242516.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>765496.00833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300873.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.0071</v>
+      </c>
+      <c r="J10" t="n">
+        <v>331286.06</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1066283.59744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>301045.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="F11" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20.0054</v>
+      </c>
+      <c r="J11" t="n">
+        <v>92372.88</v>
+      </c>
+      <c r="K11" t="n">
+        <v>765950.31986</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-10.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-22.2473</v>
+      </c>
+      <c r="J2" t="n">
+        <v>87867.44</v>
+      </c>
+      <c r="K2" t="n">
+        <v>336710.00636</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300087.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-20.0594</v>
+      </c>
+      <c r="J3" t="n">
+        <v>395012.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>213798.99167</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-19.9759</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16705</v>
+      </c>
+      <c r="K4" t="n">
+        <v>11108.825</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300997.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-10.3836</v>
+      </c>
+      <c r="J5" t="n">
+        <v>166899.74</v>
+      </c>
+      <c r="K5" t="n">
+        <v>229587.54691</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>000766.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-10.0186</v>
+      </c>
+      <c r="J6" t="n">
+        <v>194987.73</v>
+      </c>
+      <c r="K6" t="n">
+        <v>383072.01508</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>603262.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-10.0146</v>
+      </c>
+      <c r="J7" t="n">
+        <v>72870.13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>185406.897</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>000636.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-10.0037</v>
+      </c>
+      <c r="J8" t="n">
+        <v>447226</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3230760.624</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>605318.SH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>126.98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>112.86</v>
+      </c>
+      <c r="F9" t="n">
+        <v>112.86</v>
+      </c>
+      <c r="G9" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-12.54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>67423.73</v>
+      </c>
+      <c r="K9" t="n">
+        <v>782384.972</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>68350</v>
+      </c>
+      <c r="K10" t="n">
+        <v>195007.2488</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>600791.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-9.989699999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>267446.78</v>
+      </c>
+      <c r="K11" t="n">
+        <v>244456.471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.6774</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G2" t="n">
+        <v>815800</v>
+      </c>
+      <c r="H2" t="n">
+        <v>353376</v>
+      </c>
+      <c r="I2" t="n">
+        <v>638369.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>991745.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>284993.4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="M2" t="n">
+        <v>121.57</v>
+      </c>
+      <c r="N2" t="n">
+        <v>42938283.12</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000017.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>深中华A</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.0719</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G3" t="n">
+        <v>344167601</v>
+      </c>
+      <c r="H3" t="n">
+        <v>48713615.52</v>
+      </c>
+      <c r="I3" t="n">
+        <v>75092344.84</v>
+      </c>
+      <c r="J3" t="n">
+        <v>123805960.36</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26378729.32</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="M3" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3052989404.38</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000021.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.1913</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>42606092821</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5060772009.87</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4320066438.76</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9380838448.629999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-740705571.11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="N4" t="n">
+        <v>101169918671.6</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000048.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>京基智农</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.149</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="G5" t="n">
+        <v>683672242</v>
+      </c>
+      <c r="H5" t="n">
+        <v>132584748.72</v>
+      </c>
+      <c r="I5" t="n">
+        <v>191468408.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>324053157.12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>58883659.68</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11692297747.5</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000100.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TCL科技</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.0189</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6656399856</v>
+      </c>
+      <c r="H6" t="n">
+        <v>550204096.47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1391634421.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1941838517.76</v>
+      </c>
+      <c r="K6" t="n">
+        <v>841430324.8200001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>111348439637.64</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000636.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.0037</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3230760624</v>
+      </c>
+      <c r="H7" t="n">
+        <v>171129119.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>654725568</v>
+      </c>
+      <c r="J7" t="n">
+        <v>825854687.28</v>
+      </c>
+      <c r="K7" t="n">
+        <v>483596448.72</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M7" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="N7" t="n">
+        <v>83582627138.64</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000703.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>恒逸石化</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.533300000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2361257979</v>
+      </c>
+      <c r="H8" t="n">
+        <v>304952944.35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>295111475.99</v>
+      </c>
+      <c r="J8" t="n">
+        <v>600064420.34</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-9841468.359999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="N8" t="n">
+        <v>51591981420.54</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000703.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>恒逸石化</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-9.533300000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3523015145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>305099060.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>372301153.61</v>
+      </c>
+      <c r="J9" t="n">
+        <v>677400213.65</v>
+      </c>
+      <c r="K9" t="n">
+        <v>67202093.56999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="N9" t="n">
+        <v>51591981420.54</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000766.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>通化金马</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10.0186</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>383072015</v>
+      </c>
+      <c r="H10" t="n">
+        <v>54352377.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>59744389</v>
+      </c>
+      <c r="J10" t="n">
+        <v>114096766.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5392011.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="N10" t="n">
+        <v>18740549011.4</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000766.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>通化金马</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-10.0186</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1133032443</v>
+      </c>
+      <c r="H11" t="n">
+        <v>142679868.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>164267128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>306946996.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21587259.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18740549011.4</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000938.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>紫光股份</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.9848</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4698481943</v>
+      </c>
+      <c r="H12" t="n">
+        <v>332282572.37</v>
+      </c>
+      <c r="I12" t="n">
+        <v>721659573.16</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1053942145.53</v>
+      </c>
+      <c r="K12" t="n">
+        <v>389377000.79</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="N12" t="n">
+        <v>82541697371.64</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001229.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>魅视科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.9939</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>630076058</v>
+      </c>
+      <c r="H13" t="n">
+        <v>98517255.52</v>
+      </c>
+      <c r="I13" t="n">
+        <v>176731218.11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>275248473.63</v>
+      </c>
+      <c r="K13" t="n">
+        <v>78213962.59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2678643765.6</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>001237.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>惠康科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>740809447</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74164629.59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>163632834.92</v>
+      </c>
+      <c r="J14" t="n">
+        <v>237797464.51</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89468205.33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="M14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2499874328.16</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002106.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>莱宝高科</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.981199999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3252878061</v>
+      </c>
+      <c r="H15" t="n">
+        <v>256525938.87</v>
+      </c>
+      <c r="I15" t="n">
+        <v>451002825.82</v>
+      </c>
+      <c r="J15" t="n">
+        <v>707528764.6900001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>194476886.95</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M15" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12349891204.32</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002119.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>康强电子</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0028</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3526363787</v>
+      </c>
+      <c r="H16" t="n">
+        <v>468800534.22</v>
+      </c>
+      <c r="I16" t="n">
+        <v>701990571.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1170791105.95</v>
+      </c>
+      <c r="K16" t="n">
+        <v>233190037.51</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M16" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14981337280</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002167.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>东方锆业</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0199</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3077236010</v>
+      </c>
+      <c r="H17" t="n">
+        <v>313842017.76</v>
+      </c>
+      <c r="I17" t="n">
+        <v>462161589</v>
+      </c>
+      <c r="J17" t="n">
+        <v>776003606.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>148319571.24</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M17" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16744795093.41</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002182.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>宝武镁业</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.0353</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2475876753</v>
+      </c>
+      <c r="H18" t="n">
+        <v>437389603.52</v>
+      </c>
+      <c r="I18" t="n">
+        <v>549954190.87</v>
+      </c>
+      <c r="J18" t="n">
+        <v>987343794.39</v>
+      </c>
+      <c r="K18" t="n">
+        <v>112564587.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M18" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13475917754.55</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002202.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>金风科技</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.9862</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4875022659</v>
+      </c>
+      <c r="H19" t="n">
+        <v>299758784.54</v>
+      </c>
+      <c r="I19" t="n">
+        <v>738232871.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1037991655.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>438474086.82</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>80387771435.89999</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002217.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST合力泰</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-5.102</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>48327694</v>
+      </c>
+      <c r="H20" t="n">
+        <v>14055052</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4978156</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19033208</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9076896</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-18.78</v>
+      </c>
+      <c r="M20" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13539539647.26</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.0856</v>
+      </c>
+      <c r="F21" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4999174005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>686545568.08</v>
+      </c>
+      <c r="I21" t="n">
+        <v>451606078.62</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1138151646.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-234939489.46</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15118952144.7</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002407.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>多氟多</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.0088</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9392668642</v>
+      </c>
+      <c r="H22" t="n">
+        <v>724500183.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1779750385.78</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2504250568.88</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1055250202.68</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="N22" t="n">
+        <v>54186483739.35</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>61</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.4637</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1036602367</v>
+      </c>
+      <c r="H23" t="n">
+        <v>129431900.29</v>
+      </c>
+      <c r="I23" t="n">
+        <v>116177781.02</v>
+      </c>
+      <c r="J23" t="n">
+        <v>245609681.31</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-13254119.27</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N23" t="n">
+        <v>22478700629</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002600.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>领益智造</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10.0254</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5108548477</v>
+      </c>
+      <c r="H24" t="n">
+        <v>598312159.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>855751239.77</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1454063398.85</v>
+      </c>
+      <c r="K24" t="n">
+        <v>257439080.69</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="M24" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="N24" t="n">
+        <v>124842881197.32</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002628.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>成都路桥</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.0823</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G25" t="n">
+        <v>537016697</v>
+      </c>
+      <c r="H25" t="n">
+        <v>67681223</v>
+      </c>
+      <c r="I25" t="n">
+        <v>73962260</v>
+      </c>
+      <c r="J25" t="n">
+        <v>141643483</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6281037</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M25" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4032748690.7</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>兴业科技</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>195007249</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29560019</v>
+      </c>
+      <c r="I26" t="n">
+        <v>19117963</v>
+      </c>
+      <c r="J26" t="n">
+        <v>48677982</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-10442056</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-5.35</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24.96</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8346840991.56</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.5263</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4943827</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1371741.72</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2833728</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4205469.72</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1461986.28</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="N27" t="n">
+        <v>39240821.76</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002816.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>*ST和科</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.993</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="G28" t="n">
+        <v>350866728</v>
+      </c>
+      <c r="H28" t="n">
+        <v>46086436.15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>105336103.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>151422540.05</v>
+      </c>
+      <c r="K28" t="n">
+        <v>59249667.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="M28" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3007000000</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.375</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5241643</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2337247.62</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1668633.42</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4005881.04</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-668614.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-12.76</v>
+      </c>
+      <c r="M29" t="n">
+        <v>76.42</v>
+      </c>
+      <c r="N29" t="n">
+        <v>35441857.85</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002910.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>庄园牧场</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>540667887</v>
+      </c>
+      <c r="H30" t="n">
+        <v>86043276</v>
+      </c>
+      <c r="I30" t="n">
+        <v>89201561</v>
+      </c>
+      <c r="J30" t="n">
+        <v>175244837</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3158285</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M30" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1895366406</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002943.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>宇晶股份</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-9.0479</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1264453526</v>
+      </c>
+      <c r="H31" t="n">
+        <v>265673374.34</v>
+      </c>
+      <c r="I31" t="n">
+        <v>212424529.88</v>
+      </c>
+      <c r="J31" t="n">
+        <v>478097904.22</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-53248844.46</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="M31" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8352933690.6</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002962.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>五方光电</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.8664</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1388440043</v>
+      </c>
+      <c r="H32" t="n">
+        <v>135524374.44</v>
+      </c>
+      <c r="I32" t="n">
+        <v>133444607.12</v>
+      </c>
+      <c r="J32" t="n">
+        <v>268968981.56</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-2079767.32</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4597864429.9</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002971.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>62</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-9.975300000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1842786819</v>
+      </c>
+      <c r="H33" t="n">
+        <v>219646741.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>128324277.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>347971019.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-91322463.90000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M33" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9696883700</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>003004.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>声迅股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>81.55</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6.3927</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1126018117</v>
+      </c>
+      <c r="H34" t="n">
+        <v>240297121.77</v>
+      </c>
+      <c r="I34" t="n">
+        <v>254814129.37</v>
+      </c>
+      <c r="J34" t="n">
+        <v>495111251.14</v>
+      </c>
+      <c r="K34" t="n">
+        <v>14517007.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M34" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5605923474.2</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>113702.SH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>斯达转债</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>268.318</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.9356</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>2134051300</v>
+      </c>
+      <c r="H35" t="n">
+        <v>414386160</v>
+      </c>
+      <c r="I35" t="n">
+        <v>415499240</v>
+      </c>
+      <c r="J35" t="n">
+        <v>829885400</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1113080</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M35" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>118011.SH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>银微转债</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>199.68</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12.0985</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>5179457450</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1166952690</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1160677620</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2327630310</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-6275070</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M36" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>118059.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>颀中转债</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>256.528</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.0002</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>1456624430</v>
+      </c>
+      <c r="H37" t="n">
+        <v>386153280</v>
+      </c>
+      <c r="I37" t="n">
+        <v>295505270</v>
+      </c>
+      <c r="J37" t="n">
+        <v>681658550</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-90648010</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M37" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>118061.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>茂莱转债</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>263.852</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18.9873</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>2983774330</v>
+      </c>
+      <c r="H38" t="n">
+        <v>652315650</v>
+      </c>
+      <c r="I38" t="n">
+        <v>656869400</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1309185050</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4553750</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M38" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>118068.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N迪威转</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>93100330</v>
+      </c>
+      <c r="H39" t="n">
+        <v>22159790</v>
+      </c>
+      <c r="I39" t="n">
+        <v>36234090</v>
+      </c>
+      <c r="J39" t="n">
+        <v>58393880</v>
+      </c>
+      <c r="K39" t="n">
+        <v>14074300</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="M39" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>123272.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>中汽转债</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>159119688</v>
+      </c>
+      <c r="H40" t="n">
+        <v>57396378</v>
+      </c>
+      <c r="I40" t="n">
+        <v>96242159</v>
+      </c>
+      <c r="J40" t="n">
+        <v>153638537</v>
+      </c>
+      <c r="K40" t="n">
+        <v>38845781</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="M40" t="n">
+        <v>96.56</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>200468.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>宁通信B</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-9.8462</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2242378</v>
+      </c>
+      <c r="H41" t="n">
+        <v>961043.83</v>
+      </c>
+      <c r="I41" t="n">
+        <v>968815.5699999999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1929859.4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7771.74</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="N41" t="n">
+        <v>293000000</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>200725.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>京东方B</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7.7758</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G42" t="n">
+        <v>58931379</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9266623.199999999</v>
+      </c>
+      <c r="I42" t="n">
+        <v>12364008.62</v>
+      </c>
+      <c r="J42" t="n">
+        <v>21630631.82</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3097385.42</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M42" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="N42" t="n">
+        <v>311116313532.48</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2149380</v>
+      </c>
+      <c r="H43" t="n">
+        <v>795734</v>
+      </c>
+      <c r="I43" t="n">
+        <v>863320</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1659054</v>
+      </c>
+      <c r="K43" t="n">
+        <v>67586</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="N43" t="n">
+        <v>30054037.5</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>300087.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ST荃银</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-20.0594</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G44" t="n">
+        <v>213798992</v>
+      </c>
+      <c r="H44" t="n">
+        <v>33880489.29</v>
+      </c>
+      <c r="I44" t="n">
+        <v>19732548.65</v>
+      </c>
+      <c r="J44" t="n">
+        <v>53613037.94</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-14147940.64</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="M44" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4854351942</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>300162.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>雷曼光电</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.9237</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1480998230</v>
+      </c>
+      <c r="H45" t="n">
+        <v>189023455.63</v>
+      </c>
+      <c r="I45" t="n">
+        <v>135505382</v>
+      </c>
+      <c r="J45" t="n">
+        <v>324528837.63</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-53518073.63</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="M45" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4725254181.8</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>300162.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>雷曼光电</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10.9237</v>
+      </c>
+      <c r="F46" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4328367997</v>
+      </c>
+      <c r="H46" t="n">
+        <v>455017912.22</v>
+      </c>
+      <c r="I46" t="n">
+        <v>540614302.09</v>
+      </c>
+      <c r="J46" t="n">
+        <v>995632214.3099999</v>
+      </c>
+      <c r="K46" t="n">
+        <v>85596389.87</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M46" t="n">
+        <v>23</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4725254181.8</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ST荣科</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-19.9759</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G47" t="n">
+        <v>11108825</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3227910</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2747780</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5975690</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-480130</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="M47" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4252957252.6</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>300503.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>昊志机电</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.9948</v>
+      </c>
+      <c r="F48" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3576224981</v>
+      </c>
+      <c r="H48" t="n">
+        <v>313924717.96</v>
+      </c>
+      <c r="I48" t="n">
+        <v>739018237.21</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1052942955.17</v>
+      </c>
+      <c r="K48" t="n">
+        <v>425093519.25</v>
+      </c>
+      <c r="L48" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="M48" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="N48" t="n">
+        <v>22242001637.7</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>300540.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>蜀道装备</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20.0127</v>
+      </c>
+      <c r="F49" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1271793376</v>
+      </c>
+      <c r="H49" t="n">
+        <v>162617186.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>214638363.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>377255550.1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>52021176.3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M49" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7834961107.4</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>300540.SZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>蜀道装备</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20.0127</v>
+      </c>
+      <c r="F50" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3469929050</v>
+      </c>
+      <c r="H50" t="n">
+        <v>424852402.04</v>
+      </c>
+      <c r="I50" t="n">
+        <v>549238916.22</v>
+      </c>
+      <c r="J50" t="n">
+        <v>974091318.26</v>
+      </c>
+      <c r="K50" t="n">
+        <v>124386514.18</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M50" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7834961107.4</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>300671.SZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>富满微</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>20</v>
+      </c>
+      <c r="F51" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3304636255</v>
+      </c>
+      <c r="H51" t="n">
+        <v>686794678.0700001</v>
+      </c>
+      <c r="I51" t="n">
+        <v>637596842.86</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1324391520.93</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-49197835.21</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="M51" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="N51" t="n">
+        <v>19019240401.68</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>301045.SZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>天禄科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20.0054</v>
+      </c>
+      <c r="F52" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1620116936</v>
+      </c>
+      <c r="H52" t="n">
+        <v>272973537.98</v>
+      </c>
+      <c r="I52" t="n">
+        <v>295760170.08</v>
+      </c>
+      <c r="J52" t="n">
+        <v>568733708.0599999</v>
+      </c>
+      <c r="K52" t="n">
+        <v>22786632.1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M52" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6210304130.56</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>301165.SZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>锐捷网络</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20.003</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1725891761</v>
+      </c>
+      <c r="H53" t="n">
+        <v>134718573.81</v>
+      </c>
+      <c r="I53" t="n">
+        <v>449277944.86</v>
+      </c>
+      <c r="J53" t="n">
+        <v>583996518.67</v>
+      </c>
+      <c r="K53" t="n">
+        <v>314559371.05</v>
+      </c>
+      <c r="L53" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="M53" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="N53" t="n">
+        <v>89592045403.35001</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>301307.SZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>美利信</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>75.29000000000001</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.3621</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3618628869</v>
+      </c>
+      <c r="H54" t="n">
+        <v>659759752.13</v>
+      </c>
+      <c r="I54" t="n">
+        <v>711791992.9299999</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1371551745.06</v>
+      </c>
+      <c r="K54" t="n">
+        <v>52032240.8</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M54" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="N54" t="n">
+        <v>8190147088.6</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>15.0035</v>
+      </c>
+      <c r="F55" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="G55" t="n">
+        <v>473424568</v>
+      </c>
+      <c r="H55" t="n">
+        <v>102960000.16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>69646269.69</v>
+      </c>
+      <c r="J55" t="n">
+        <v>172606269.85</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-33313730.47</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="M55" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1062699397.5</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>15.0035</v>
+      </c>
+      <c r="F56" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="G56" t="n">
+        <v>541672242</v>
+      </c>
+      <c r="H56" t="n">
+        <v>117223225.76</v>
+      </c>
+      <c r="I56" t="n">
+        <v>98588197.69</v>
+      </c>
+      <c r="J56" t="n">
+        <v>215811423.45</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-18635028.07</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="M56" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1062699397.5</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>301607.SZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>富特科技</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20.0046</v>
+      </c>
+      <c r="F57" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1230888793</v>
+      </c>
+      <c r="H57" t="n">
+        <v>160982978.58</v>
+      </c>
+      <c r="I57" t="n">
+        <v>289449379.39</v>
+      </c>
+      <c r="J57" t="n">
+        <v>450432357.97</v>
+      </c>
+      <c r="K57" t="n">
+        <v>128466400.81</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="M57" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="N57" t="n">
+        <v>7931094223.25</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>600180.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>*ST瑞茂</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5.042</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>11084102</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1807561</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5175298</v>
+      </c>
+      <c r="J58" t="n">
+        <v>6982859</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3367737</v>
+      </c>
+      <c r="L58" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="M58" t="n">
+        <v>63</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1358284330</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>600206.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>有研新材</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="F59" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="G59" t="n">
+        <v>9298783418</v>
+      </c>
+      <c r="H59" t="n">
+        <v>564795592.5700001</v>
+      </c>
+      <c r="I59" t="n">
+        <v>453724063.72</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1018519656.29</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-111071528.85</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M59" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="N59" t="n">
+        <v>56380451911.2</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>600353.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>旭光电子</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5.6044</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3070193132</v>
+      </c>
+      <c r="H60" t="n">
+        <v>314543758.56</v>
+      </c>
+      <c r="I60" t="n">
+        <v>440548090.31</v>
+      </c>
+      <c r="J60" t="n">
+        <v>755091848.87</v>
+      </c>
+      <c r="K60" t="n">
+        <v>126004331.75</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="N60" t="n">
+        <v>37793788850.4</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>600539.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>狮头股份</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8.013199999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1001846218</v>
+      </c>
+      <c r="H61" t="n">
+        <v>145491393</v>
+      </c>
+      <c r="I61" t="n">
+        <v>173842397.25</v>
+      </c>
+      <c r="J61" t="n">
+        <v>319333790.25</v>
+      </c>
+      <c r="K61" t="n">
+        <v>28351004.25</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M61" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3751300000</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>600545.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>卓郎智能</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7.4766</v>
+      </c>
+      <c r="F62" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5260735161</v>
+      </c>
+      <c r="H62" t="n">
+        <v>533352702.35</v>
+      </c>
+      <c r="I62" t="n">
+        <v>815080090.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1348432792.95</v>
+      </c>
+      <c r="K62" t="n">
+        <v>281727388.25</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="N62" t="n">
+        <v>14392693387.1</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>600552.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>凯盛科技</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.4943</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6547453963</v>
+      </c>
+      <c r="H63" t="n">
+        <v>980443438.58</v>
+      </c>
+      <c r="I63" t="n">
+        <v>771753624.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1752197062.87</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-208689814.29</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="M63" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="N63" t="n">
+        <v>30775292606.52</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>600552.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>凯盛科技</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.4943</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="G64" t="n">
+        <v>18619390080</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2214414576.19</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2301921306.67</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4516335882.86</v>
+      </c>
+      <c r="K64" t="n">
+        <v>87506730.48</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M64" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="N64" t="n">
+        <v>30775292606.52</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>600566.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>济川药业</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-9.979699999999999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G65" t="n">
+        <v>347685384</v>
+      </c>
+      <c r="H65" t="n">
+        <v>88074095.36</v>
+      </c>
+      <c r="I65" t="n">
+        <v>30459225</v>
+      </c>
+      <c r="J65" t="n">
+        <v>118533320.36</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-57614870.36</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-16.57</v>
+      </c>
+      <c r="M65" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="N65" t="n">
+        <v>20384207978.4</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>600568.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ST中珠</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4.8889</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G66" t="n">
+        <v>119207054</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16555925</v>
+      </c>
+      <c r="I66" t="n">
+        <v>13746353</v>
+      </c>
+      <c r="J66" t="n">
+        <v>30302278</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-2809572</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="M66" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3938998778.44</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>600707.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>彩虹股份</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10.0326</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3422619101</v>
+      </c>
+      <c r="H67" t="n">
+        <v>296313885.19</v>
+      </c>
+      <c r="I67" t="n">
+        <v>637045405.08</v>
+      </c>
+      <c r="J67" t="n">
+        <v>933359290.27</v>
+      </c>
+      <c r="K67" t="n">
+        <v>340731519.89</v>
+      </c>
+      <c r="L67" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="M67" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="N67" t="n">
+        <v>60595741773.48</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>600707.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>彩虹股份</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10.0326</v>
+      </c>
+      <c r="F68" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G68" t="n">
+        <v>13644782357</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1201927392.34</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1630389040.09</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2832316432.43</v>
+      </c>
+      <c r="K68" t="n">
+        <v>428461647.75</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M68" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="N68" t="n">
+        <v>60595741773.48</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>600735.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ST新华锦</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G69" t="n">
+        <v>97355566</v>
+      </c>
+      <c r="H69" t="n">
+        <v>19657291</v>
+      </c>
+      <c r="I69" t="n">
+        <v>23268769</v>
+      </c>
+      <c r="J69" t="n">
+        <v>42926060</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3611478</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M69" t="n">
+        <v>44.09</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2680346510.1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>600791.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>京能置业</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-9.989699999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="G70" t="n">
+        <v>244456471</v>
+      </c>
+      <c r="H70" t="n">
+        <v>45139917.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>63597642.07</v>
+      </c>
+      <c r="J70" t="n">
+        <v>108737559.57</v>
+      </c>
+      <c r="K70" t="n">
+        <v>18457724.57</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="M70" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3953221703.04</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>600996.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>贵广网络</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-8.3223</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="G71" t="n">
+        <v>914557292</v>
+      </c>
+      <c r="H71" t="n">
+        <v>72823464.2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>95334756.87</v>
+      </c>
+      <c r="J71" t="n">
+        <v>168158221.07</v>
+      </c>
+      <c r="K71" t="n">
+        <v>22511292.67</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M71" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8652790986.76</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>603061.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>金海通</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>502.22</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10.0009</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4953687274</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1070097958.63</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1204523792.51</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2274621751.14</v>
+      </c>
+      <c r="K72" t="n">
+        <v>134425833.88</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M72" t="n">
+        <v>45.92</v>
+      </c>
+      <c r="N72" t="n">
+        <v>43693140000</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>603155.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>新亚强</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.5475</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="G73" t="n">
+        <v>994267977</v>
+      </c>
+      <c r="H73" t="n">
+        <v>94470406.84</v>
+      </c>
+      <c r="I73" t="n">
+        <v>116705237.05</v>
+      </c>
+      <c r="J73" t="n">
+        <v>211175643.89</v>
+      </c>
+      <c r="K73" t="n">
+        <v>22234830.21</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M73" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="N73" t="n">
+        <v>9025186744</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>603222.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>济民健康</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.026</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G74" t="n">
+        <v>80712170</v>
+      </c>
+      <c r="H74" t="n">
+        <v>14293870</v>
+      </c>
+      <c r="I74" t="n">
+        <v>45941785</v>
+      </c>
+      <c r="J74" t="n">
+        <v>60235655</v>
+      </c>
+      <c r="K74" t="n">
+        <v>31647915</v>
+      </c>
+      <c r="L74" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="M74" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4437015696.75</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>603261.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>立航科技</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-5.0561</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G75" t="n">
+        <v>271111993</v>
+      </c>
+      <c r="H75" t="n">
+        <v>68703113</v>
+      </c>
+      <c r="I75" t="n">
+        <v>35152732</v>
+      </c>
+      <c r="J75" t="n">
+        <v>103855845</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-33550381</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-12.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3871375848.9</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>603262.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>技源集团</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-10.0146</v>
+      </c>
+      <c r="F76" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="G76" t="n">
+        <v>185406897</v>
+      </c>
+      <c r="H76" t="n">
+        <v>72910547.47</v>
+      </c>
+      <c r="I76" t="n">
+        <v>52945443</v>
+      </c>
+      <c r="J76" t="n">
+        <v>125855990.47</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-19965104.47</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="M76" t="n">
+        <v>67.88</v>
+      </c>
+      <c r="N76" t="n">
+        <v>984996960</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>603262.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>技源集团</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-10.0146</v>
+      </c>
+      <c r="F77" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="G77" t="n">
+        <v>331602132</v>
+      </c>
+      <c r="H77" t="n">
+        <v>127436125.07</v>
+      </c>
+      <c r="I77" t="n">
+        <v>86758911.55</v>
+      </c>
+      <c r="J77" t="n">
+        <v>214195036.62</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-40677213.52</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-12.27</v>
+      </c>
+      <c r="M77" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="N77" t="n">
+        <v>984996960</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>603399.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>永杉锂业</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="E78" t="n">
+        <v>5.2927</v>
+      </c>
+      <c r="F78" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2383277178</v>
+      </c>
+      <c r="H78" t="n">
+        <v>252978541.93</v>
+      </c>
+      <c r="I78" t="n">
+        <v>311718127.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>564696669.13</v>
+      </c>
+      <c r="K78" t="n">
+        <v>58739585.27</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M78" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="N78" t="n">
+        <v>11516293789.52</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>106.02</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8.749599999999999</v>
+      </c>
+      <c r="F79" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1138869297</v>
+      </c>
+      <c r="H79" t="n">
+        <v>202574808.63</v>
+      </c>
+      <c r="I79" t="n">
+        <v>236686205.67</v>
+      </c>
+      <c r="J79" t="n">
+        <v>439261014.3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>34111397.04</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3807389391.84</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>603429.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>*ST集友</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-4.9941</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G80" t="n">
+        <v>107545281</v>
+      </c>
+      <c r="H80" t="n">
+        <v>22204938.8</v>
+      </c>
+      <c r="I80" t="n">
+        <v>23441162</v>
+      </c>
+      <c r="J80" t="n">
+        <v>45646100.8</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1236223.2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M80" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4190638865.35</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格跌幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>603435.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>嘉德利</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4.597</v>
+      </c>
+      <c r="F81" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>549794942</v>
+      </c>
+      <c r="H81" t="n">
+        <v>94309225.48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>54258608.89</v>
+      </c>
+      <c r="J81" t="n">
+        <v>148567834.37</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-40050616.59</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="M81" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2436031616.92</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>603459.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>红板科技</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="E82" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="F82" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3337481357</v>
+      </c>
+      <c r="H82" t="n">
+        <v>438237930.56</v>
+      </c>
+      <c r="I82" t="n">
+        <v>546362826.24</v>
+      </c>
+      <c r="J82" t="n">
+        <v>984600756.8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>108124895.68</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M82" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8870408986.18</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>603577.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>汇金通</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="E83" t="n">
+        <v>10.0467</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G83" t="n">
+        <v>78898360</v>
+      </c>
+      <c r="H83" t="n">
+        <v>15201447</v>
+      </c>
+      <c r="I83" t="n">
+        <v>20587986.2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>35789433.2</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5386539.2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="M83" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3194690322</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>603637.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>镇海股份</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-8.2933</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="G84" t="n">
+        <v>638271736</v>
+      </c>
+      <c r="H84" t="n">
+        <v>99301865.72</v>
+      </c>
+      <c r="I84" t="n">
+        <v>102535530.79</v>
+      </c>
+      <c r="J84" t="n">
+        <v>201837396.51</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3233665.07</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M84" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3642346483.02</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>603657.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>春光科技</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10.0202</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G85" t="n">
+        <v>612059524</v>
+      </c>
+      <c r="H85" t="n">
+        <v>105543231</v>
+      </c>
+      <c r="I85" t="n">
+        <v>154164752.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>259707983.6</v>
+      </c>
+      <c r="K85" t="n">
+        <v>48621521.6</v>
+      </c>
+      <c r="L85" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="M85" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3681225061.5</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>603823.SH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9.997999999999999</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1113667864</v>
+      </c>
+      <c r="H86" t="n">
+        <v>130481757</v>
+      </c>
+      <c r="I86" t="n">
+        <v>225424546.38</v>
+      </c>
+      <c r="J86" t="n">
+        <v>355906303.38</v>
+      </c>
+      <c r="K86" t="n">
+        <v>94942789.38</v>
+      </c>
+      <c r="L86" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="M86" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="N86" t="n">
+        <v>22721185607.28</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>603928.SH</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>兴业股份</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10.0372</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G87" t="n">
+        <v>189331877</v>
+      </c>
+      <c r="H87" t="n">
+        <v>24717608.95</v>
+      </c>
+      <c r="I87" t="n">
+        <v>49325665.6</v>
+      </c>
+      <c r="J87" t="n">
+        <v>74043274.55</v>
+      </c>
+      <c r="K87" t="n">
+        <v>24608056.65</v>
+      </c>
+      <c r="L87" t="n">
+        <v>13</v>
+      </c>
+      <c r="M87" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5042419200</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>603983.SH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>丸美生物</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="E88" t="n">
+        <v>10.0078</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G88" t="n">
+        <v>703453382</v>
+      </c>
+      <c r="H88" t="n">
+        <v>101035462.96</v>
+      </c>
+      <c r="I88" t="n">
+        <v>164868351.47</v>
+      </c>
+      <c r="J88" t="n">
+        <v>265903814.43</v>
+      </c>
+      <c r="K88" t="n">
+        <v>63832888.51</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="M88" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="N88" t="n">
+        <v>11284140000</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>605018.SH</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>长华集团</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="E89" t="n">
+        <v>10.0369</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G89" t="n">
+        <v>190350454</v>
+      </c>
+      <c r="H89" t="n">
+        <v>37803939</v>
+      </c>
+      <c r="I89" t="n">
+        <v>37361152</v>
+      </c>
+      <c r="J89" t="n">
+        <v>75165091</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-442787</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M89" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7008680973.63</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>605098.SH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>行动教育</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-9.2645</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G90" t="n">
+        <v>170425743</v>
+      </c>
+      <c r="H90" t="n">
+        <v>64284557</v>
+      </c>
+      <c r="I90" t="n">
+        <v>23962060</v>
+      </c>
+      <c r="J90" t="n">
+        <v>88246617</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-40322497</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-23.66</v>
+      </c>
+      <c r="M90" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="N90" t="n">
+        <v>6458639576</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>605111.SH</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>新洁能</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9.996700000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G91" t="n">
+        <v>9762343418</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1762817873.94</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1979374270.95</v>
+      </c>
+      <c r="J91" t="n">
+        <v>3742192144.89</v>
+      </c>
+      <c r="K91" t="n">
+        <v>216556397.01</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M91" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="N91" t="n">
+        <v>41176070692.38</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>605255.SH</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>天普股份</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-3.6891</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G92" t="n">
+        <v>419527280</v>
+      </c>
+      <c r="H92" t="n">
+        <v>44446267.85</v>
+      </c>
+      <c r="I92" t="n">
+        <v>43761392.2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>88207660.05</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-684875.65</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M92" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="N92" t="n">
+        <v>8821123200</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>605318.SH</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>法狮龙</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>112.86</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G93" t="n">
+        <v>782384972</v>
+      </c>
+      <c r="H93" t="n">
+        <v>317639975.69</v>
+      </c>
+      <c r="I93" t="n">
+        <v>153539709</v>
+      </c>
+      <c r="J93" t="n">
+        <v>471179684.69</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-164100266.69</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-20.97</v>
+      </c>
+      <c r="M93" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="N93" t="n">
+        <v>14189778100.08</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>605336.SH</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>*ST帅电</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-5.0209</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>51962650</v>
+      </c>
+      <c r="H94" t="n">
+        <v>21405443</v>
+      </c>
+      <c r="I94" t="n">
+        <v>26355219</v>
+      </c>
+      <c r="J94" t="n">
+        <v>47760662</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4949776</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="M94" t="n">
+        <v>91.91</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2498077569</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格跌幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>688048.SH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>长光华芯</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>502</v>
+      </c>
+      <c r="E95" t="n">
+        <v>20.001</v>
+      </c>
+      <c r="F95" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="G95" t="n">
+        <v>9750808500</v>
+      </c>
+      <c r="H95" t="n">
+        <v>448379823.21</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1854427703.45</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2302807526.66</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1406047880.24</v>
+      </c>
+      <c r="L95" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="M95" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="N95" t="n">
+        <v>88492531386</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>688166.SH</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>博瑞医药</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-2.6418</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>17292447300</v>
+      </c>
+      <c r="H96" t="n">
+        <v>17292447200</v>
+      </c>
+      <c r="I96" t="n">
+        <v>17292447300</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34584894500</v>
+      </c>
+      <c r="K96" t="n">
+        <v>100</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>200</v>
+      </c>
+      <c r="N96" t="n">
+        <v>15257182634.91</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续30个交易日内收盘价格跌幅偏离值累计达到-70%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>688220.SH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>翱捷科技</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>124.32</v>
+      </c>
+      <c r="E97" t="n">
+        <v>20</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3029830600</v>
+      </c>
+      <c r="H97" t="n">
+        <v>789739377.03</v>
+      </c>
+      <c r="I97" t="n">
+        <v>522908905.96</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1312648282.99</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-266830471.07</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="M97" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="N97" t="n">
+        <v>45891401754.24</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>688355.SH</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>明志科技</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20.0125</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G98" t="n">
+        <v>89205500</v>
+      </c>
+      <c r="H98" t="n">
+        <v>22061387.72</v>
+      </c>
+      <c r="I98" t="n">
+        <v>28929751.16</v>
+      </c>
+      <c r="J98" t="n">
+        <v>50991138.88</v>
+      </c>
+      <c r="K98" t="n">
+        <v>6868363.44</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M98" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2386154386</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>688502.SH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>茂莱光学</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="E99" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2064145000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>214213580.6</v>
+      </c>
+      <c r="I99" t="n">
+        <v>517787365.93</v>
+      </c>
+      <c r="J99" t="n">
+        <v>732000946.53</v>
+      </c>
+      <c r="K99" t="n">
+        <v>303573785.33</v>
+      </c>
+      <c r="L99" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="M99" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="N99" t="n">
+        <v>36622476045.6</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>688503.SH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>聚和材料</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="E100" t="n">
+        <v>19.8735</v>
+      </c>
+      <c r="F100" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="G100" t="n">
+        <v>7827973900</v>
+      </c>
+      <c r="H100" t="n">
+        <v>776824221.8099999</v>
+      </c>
+      <c r="I100" t="n">
+        <v>986409891.92</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1763234113.73</v>
+      </c>
+      <c r="K100" t="n">
+        <v>209585670.11</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M100" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="N100" t="n">
+        <v>32117864426.1</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>688639.SH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>华恒生物</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-2.9465</v>
+      </c>
+      <c r="F101" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1861578700</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1861578600</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1861578600</v>
+      </c>
+      <c r="J101" t="n">
+        <v>3723157200</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>200</v>
+      </c>
+      <c r="N101" t="n">
+        <v>4036867285.02</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续10个交易日内收盘价格跌幅偏离值累计达到-50%的证券</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260701</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5511</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4329</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2" t="n">
+        <v>36827.97</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4094.3972</v>
+        <v>4112.4453</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="F2" t="n">
-        <v>15303.26</v>
+        <v>16984.88</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16205.5565</v>
+        <v>16119.1683</v>
       </c>
       <c r="E3" t="n">
-        <v>2.48</v>
+        <v>-0.53</v>
       </c>
       <c r="F3" t="n">
-        <v>17434.19</v>
+        <v>19615.04</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4342.7123</v>
+        <v>4260.7208</v>
       </c>
       <c r="E4" t="n">
-        <v>2.99</v>
+        <v>-1.89</v>
       </c>
       <c r="F4" t="n">
-        <v>8598.26</v>
+        <v>9815.209999999999</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4979.4328</v>
+        <v>4958.9773</v>
       </c>
       <c r="E5" t="n">
-        <v>1.07</v>
+        <v>-0.41</v>
       </c>
       <c r="F5" t="n">
-        <v>9857.950000000001</v>
+        <v>11017.18</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2207.8648</v>
+        <v>2153.0431</v>
       </c>
       <c r="E6" t="n">
-        <v>3.85</v>
+        <v>-2.48</v>
       </c>
       <c r="F6" t="n">
-        <v>2193.5</v>
+        <v>2323.28</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8809.785900000001</v>
+        <v>8876.630300000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.46</v>
+        <v>0.76</v>
       </c>
       <c r="F7" t="n">
-        <v>6853.82</v>
+        <v>7828</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6494 @@
           <t>20260701</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>36827.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920699.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>92.93000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29.9902</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36836.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>309655.32287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920090.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.8246</v>
+      </c>
+      <c r="J3" t="n">
+        <v>135455.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46822.78673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>920970.BJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26.8293</v>
+      </c>
+      <c r="J4" t="n">
+        <v>187262.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>121109.49618</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="F5" t="n">
+        <v>46.28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.2153</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2198231.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9252312.953919999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300175.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0864</v>
+      </c>
+      <c r="J6" t="n">
+        <v>225146.53</v>
+      </c>
+      <c r="K6" t="n">
+        <v>117640.49768</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300385.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.0397</v>
+      </c>
+      <c r="J7" t="n">
+        <v>113142.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>129043.29775</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688553.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.0376</v>
+      </c>
+      <c r="J8" t="n">
+        <v>379157.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>455217.325</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300345.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.0342</v>
+      </c>
+      <c r="J9" t="n">
+        <v>988216.13</v>
+      </c>
+      <c r="K9" t="n">
+        <v>656244.77125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301279.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.0184</v>
+      </c>
+      <c r="J10" t="n">
+        <v>46305.28</v>
+      </c>
+      <c r="K10" t="n">
+        <v>113967.52542</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300873.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20.0167</v>
+      </c>
+      <c r="J11" t="n">
+        <v>549642.73</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1523997.13954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42250</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22477</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300863.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="E3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="G3" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-13.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-17.8129</v>
+      </c>
+      <c r="J3" t="n">
+        <v>248101.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1720853.74867</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300274.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>151.07</v>
+      </c>
+      <c r="D4" t="n">
+        <v>151.09</v>
+      </c>
+      <c r="E4" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>136.92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>159.02</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-13.8976</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1652069.77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22413748.6257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688319.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="D5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-12.2328</v>
+      </c>
+      <c r="J5" t="n">
+        <v>284020.61</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1133604.54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688785.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>478</v>
+      </c>
+      <c r="D6" t="n">
+        <v>482.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>408</v>
+      </c>
+      <c r="F6" t="n">
+        <v>432</v>
+      </c>
+      <c r="G6" t="n">
+        <v>484.03</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-52.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-10.7493</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16754.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>743422.389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301626.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="D7" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>330.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>383.96</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-40.46</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-10.5376</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44768</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1589921.79172</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688662.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>159.08</v>
+      </c>
+      <c r="D8" t="n">
+        <v>162.56</v>
+      </c>
+      <c r="E8" t="n">
+        <v>148.21</v>
+      </c>
+      <c r="F8" t="n">
+        <v>150.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>168</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-17.34</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-10.3214</v>
+      </c>
+      <c r="J8" t="n">
+        <v>104507.08</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1627124.268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>002522.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-10.0376</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1285583.26</v>
+      </c>
+      <c r="K9" t="n">
+        <v>954703.45262</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>603203.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>75.16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>77.77</v>
+      </c>
+      <c r="E10" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-10.0026</v>
+      </c>
+      <c r="J10" t="n">
+        <v>243160.37</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1773542.164</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>600228.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>751250.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>647264.278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.823499999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4161907</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1857867</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1635690</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3493557</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-222177</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="M2" t="n">
+        <v>83.94</v>
+      </c>
+      <c r="N2" t="n">
+        <v>46726955.16</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000566.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>海南海药</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1076585693</v>
+      </c>
+      <c r="H3" t="n">
+        <v>80021668.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>121129003.46</v>
+      </c>
+      <c r="J3" t="n">
+        <v>201150671.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>41107334.96</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7119078625.17</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000566.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>海南海药</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2392407566</v>
+      </c>
+      <c r="H4" t="n">
+        <v>197458450.65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>234847133.36</v>
+      </c>
+      <c r="J4" t="n">
+        <v>432305584.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>37388682.71</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7119078625.17</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000620.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>盈新发展</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3141476127</v>
+      </c>
+      <c r="H5" t="n">
+        <v>311795188.24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>355961530.52</v>
+      </c>
+      <c r="J5" t="n">
+        <v>667756718.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>44166342.28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17986232937.75</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000823.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超声电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.3645</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4440731957</v>
+      </c>
+      <c r="H6" t="n">
+        <v>563683486.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>602193302.34</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1165876788.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>38509816.19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="M6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15468236342</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>001223.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>欧克科技</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-9.9567</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G7" t="n">
+        <v>277816514</v>
+      </c>
+      <c r="H7" t="n">
+        <v>51692108.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16816543.97</v>
+      </c>
+      <c r="J7" t="n">
+        <v>68508652.59999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-34875564.66</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-12.55</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3340896832</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001237.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>惠康科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.0218</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>899714102</v>
+      </c>
+      <c r="H8" t="n">
+        <v>155173884.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>73034987.53</v>
+      </c>
+      <c r="J8" t="n">
+        <v>228208872.42</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-82138897.36</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2550415568.76</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001237.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>惠康科技</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>73.17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.0218</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2047347520</v>
+      </c>
+      <c r="H9" t="n">
+        <v>203057772.55</v>
+      </c>
+      <c r="I9" t="n">
+        <v>271752469.24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>474810241.79</v>
+      </c>
+      <c r="K9" t="n">
+        <v>68694696.69</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2550415568.76</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001257.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>盛龙股份</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.9584</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1032571361</v>
+      </c>
+      <c r="H10" t="n">
+        <v>129528983.08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>145345530.36</v>
+      </c>
+      <c r="J10" t="n">
+        <v>274874513.44</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15816547.28</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M10" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3971491652</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001331.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>胜通能源</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0035</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3067182925</v>
+      </c>
+      <c r="H11" t="n">
+        <v>606875562.22</v>
+      </c>
+      <c r="I11" t="n">
+        <v>491861506.29</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1098737068.51</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-115014055.93</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="N11" t="n">
+        <v>17727433983</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001388.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>信通电子</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.9359</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>124917441</v>
+      </c>
+      <c r="H12" t="n">
+        <v>47005375.67</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20126913.12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>67132288.79000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-26878462.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-21.52</v>
+      </c>
+      <c r="M12" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2506682841.95</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001389.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>广合科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-8.746</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3648275177</v>
+      </c>
+      <c r="H13" t="n">
+        <v>597030138.1900001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>515899929.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1112930067.67</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-81130208.70999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32954004951</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002038.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>双鹭药业</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.9022</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1164077571</v>
+      </c>
+      <c r="H14" t="n">
+        <v>148480437.51</v>
+      </c>
+      <c r="I14" t="n">
+        <v>136748392.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>285228830.11</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-11732044.91</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5350003064.48</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002053.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>云南能投</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.9695</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>524664929</v>
+      </c>
+      <c r="H15" t="n">
+        <v>84723356.84999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>129892808.17</v>
+      </c>
+      <c r="J15" t="n">
+        <v>214616165.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>45169451.32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9953014970.59</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002150.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>正泰电源</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.5983</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="G16" t="n">
+        <v>641618430</v>
+      </c>
+      <c r="H16" t="n">
+        <v>128475027</v>
+      </c>
+      <c r="I16" t="n">
+        <v>132644998.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>261120025.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4169971.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9393878423.6</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002167.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>东方锆业</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0136</v>
+      </c>
+      <c r="F17" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3966088328</v>
+      </c>
+      <c r="H17" t="n">
+        <v>346312217.32</v>
+      </c>
+      <c r="I17" t="n">
+        <v>716027299.77</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1062339517.09</v>
+      </c>
+      <c r="K17" t="n">
+        <v>369715082.45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="N17" t="n">
+        <v>18421550741.64</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.0753</v>
+      </c>
+      <c r="F18" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4962384392</v>
+      </c>
+      <c r="H18" t="n">
+        <v>549779887.65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>483595707.05</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1033375594.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-66184180.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15281521522.6</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002407.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>多氟多</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3893123432</v>
+      </c>
+      <c r="H19" t="n">
+        <v>256253853.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>574866891.9299999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>831120745.1900001</v>
+      </c>
+      <c r="K19" t="n">
+        <v>318613038.67</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="M19" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="N19" t="n">
+        <v>59601895811.25</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002407.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>多氟多</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15008142888</v>
+      </c>
+      <c r="H20" t="n">
+        <v>888501887.8200001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2674755016.05</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3563256903.87</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1786253128.23</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="N20" t="n">
+        <v>59601895811.25</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002409.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>雅克科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>236.09</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.1626</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>28779763201</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2728957415.33</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2937616079.04</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5666573494.37</v>
+      </c>
+      <c r="K21" t="n">
+        <v>208658663.71</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M21" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="N21" t="n">
+        <v>75200035339.23</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002491.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-8.672800000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5459576512</v>
+      </c>
+      <c r="H22" t="n">
+        <v>805923929.33</v>
+      </c>
+      <c r="I22" t="n">
+        <v>652710227.99</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1458634157.32</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-153213701.34</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="N22" t="n">
+        <v>34811713892.89</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002491.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>通鼎互联</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>29.59</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-8.672800000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16373335922</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2082527771.17</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1875841682.56</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3958369453.73</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-206686088.61</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34811713892.89</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002522.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>浙江众成</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-10.0376</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="G24" t="n">
+        <v>954703453</v>
+      </c>
+      <c r="H24" t="n">
+        <v>112675577.51</v>
+      </c>
+      <c r="I24" t="n">
+        <v>61301109.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>173976687.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-51374468.01</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="M24" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6488992532.43</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002653.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>海思科</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.978899999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1496298568</v>
+      </c>
+      <c r="H25" t="n">
+        <v>182366865.43</v>
+      </c>
+      <c r="I25" t="n">
+        <v>181320652.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>363687518.23</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1046212.63</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="N25" t="n">
+        <v>39163916263.68</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002653.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>海思科</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.978899999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3336347969</v>
+      </c>
+      <c r="H26" t="n">
+        <v>395684231.98</v>
+      </c>
+      <c r="I26" t="n">
+        <v>365224428.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>760908660.78</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-30459803.18</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="N26" t="n">
+        <v>39163916263.68</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>兴业科技</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-9.9895</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1100753640</v>
+      </c>
+      <c r="H27" t="n">
+        <v>102441550</v>
+      </c>
+      <c r="I27" t="n">
+        <v>102109363</v>
+      </c>
+      <c r="J27" t="n">
+        <v>204550913</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-332187</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M27" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7513034583.36</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>兴业科技</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-9.9895</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1295760888</v>
+      </c>
+      <c r="H28" t="n">
+        <v>103366008</v>
+      </c>
+      <c r="I28" t="n">
+        <v>111675482</v>
+      </c>
+      <c r="J28" t="n">
+        <v>215041490</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8309474</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M28" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7513034583.36</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002733.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>雄韬股份</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-8.0052</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2792166553</v>
+      </c>
+      <c r="H29" t="n">
+        <v>458841618.03</v>
+      </c>
+      <c r="I29" t="n">
+        <v>450764040.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>909605658.63</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-8077577.43</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10512588631.5</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002747.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>埃斯顿</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.992000000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2197218339</v>
+      </c>
+      <c r="H30" t="n">
+        <v>213431190.01</v>
+      </c>
+      <c r="I30" t="n">
+        <v>413406819</v>
+      </c>
+      <c r="J30" t="n">
+        <v>626838009.01</v>
+      </c>
+      <c r="K30" t="n">
+        <v>199975628.99</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="N30" t="n">
+        <v>32125534025.68</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.5238</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1966895</v>
+      </c>
+      <c r="H31" t="n">
+        <v>902494</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1379547</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2282041</v>
+      </c>
+      <c r="K31" t="n">
+        <v>477053</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="N31" t="n">
+        <v>42978042.88</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002822.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ST中装</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>196011379</v>
+      </c>
+      <c r="H32" t="n">
+        <v>21649389.76</v>
+      </c>
+      <c r="I32" t="n">
+        <v>26221242.88</v>
+      </c>
+      <c r="J32" t="n">
+        <v>47870632.64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4571853.12</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M32" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3591660216.48</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002856.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>*ST美芝</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.0233</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G33" t="n">
+        <v>345491033</v>
+      </c>
+      <c r="H33" t="n">
+        <v>57662351.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>84227256.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>141889608.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>26564905</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M33" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2512782104.04</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3791054</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1451152.42</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1326228</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2777380.42</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-124924.42</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="N34" t="n">
+        <v>35441857.85</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002910.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>庄园牧场</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.5271</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="G35" t="n">
+        <v>484704068</v>
+      </c>
+      <c r="H35" t="n">
+        <v>94969193.62</v>
+      </c>
+      <c r="I35" t="n">
+        <v>89827959</v>
+      </c>
+      <c r="J35" t="n">
+        <v>184797152.62</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-5141234.62</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="M35" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1943263752</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>002929.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>润建股份</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10.003</v>
+      </c>
+      <c r="F36" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2919174554</v>
+      </c>
+      <c r="H36" t="n">
+        <v>224456077.08</v>
+      </c>
+      <c r="I36" t="n">
+        <v>511780620.81</v>
+      </c>
+      <c r="J36" t="n">
+        <v>736236697.89</v>
+      </c>
+      <c r="K36" t="n">
+        <v>287324543.73</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="N36" t="n">
+        <v>15929572979.04</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>003026.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>中晶科技</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>44</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3.5299</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1488738436</v>
+      </c>
+      <c r="H37" t="n">
+        <v>80925393.09999999</v>
+      </c>
+      <c r="I37" t="n">
+        <v>72250668.89</v>
+      </c>
+      <c r="J37" t="n">
+        <v>153176061.99</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-8674724.210000001</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6360678676</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>003043.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>华亚智能</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>106</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.6506</v>
+      </c>
+      <c r="F38" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2644172309</v>
+      </c>
+      <c r="H38" t="n">
+        <v>489893404.26</v>
+      </c>
+      <c r="I38" t="n">
+        <v>405469056.59</v>
+      </c>
+      <c r="J38" t="n">
+        <v>895362460.85</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-84424347.67</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="M38" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9430298904</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>111012.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>福新转债</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>343.711</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.9308</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>2253749130</v>
+      </c>
+      <c r="H39" t="n">
+        <v>463817860</v>
+      </c>
+      <c r="I39" t="n">
+        <v>472851700</v>
+      </c>
+      <c r="J39" t="n">
+        <v>936669560</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9033840</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>118011.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>银微转债</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>239.487</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19.9354</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>5920143600</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1544110570</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1551937710</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3096048280</v>
+      </c>
+      <c r="K40" t="n">
+        <v>7827140</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M40" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>123195.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>蓝晓转02</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>181.98</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>1355776034</v>
+      </c>
+      <c r="H41" t="n">
+        <v>363830495.01</v>
+      </c>
+      <c r="I41" t="n">
+        <v>367591206.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>731421701.51</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3760711.49</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M41" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>123272.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>中汽转债</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>188.74</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19.9873</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>2985407628</v>
+      </c>
+      <c r="H42" t="n">
+        <v>921793779.28</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1015930810.74</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1937724590.02</v>
+      </c>
+      <c r="K42" t="n">
+        <v>94137031.45999999</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M42" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2448543</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1165665</v>
+      </c>
+      <c r="I43" t="n">
+        <v>913510.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2079175.35</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-252154.65</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="N43" t="n">
+        <v>30054037.5</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>300121.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>阳谷华泰</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="E44" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1486079907</v>
+      </c>
+      <c r="H44" t="n">
+        <v>120357641.38</v>
+      </c>
+      <c r="I44" t="n">
+        <v>300669887.36</v>
+      </c>
+      <c r="J44" t="n">
+        <v>421027528.74</v>
+      </c>
+      <c r="K44" t="n">
+        <v>180312245.98</v>
+      </c>
+      <c r="L44" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="M44" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6492632146.56</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>300269.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>联建光电</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11.9782</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="G45" t="n">
+        <v>919315630</v>
+      </c>
+      <c r="H45" t="n">
+        <v>104003465.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>79116985</v>
+      </c>
+      <c r="J45" t="n">
+        <v>183120450.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-24886480.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="M45" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3243433432.76</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>300270.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>中威电子</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9.761699999999999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1354937618</v>
+      </c>
+      <c r="H46" t="n">
+        <v>240897239.19</v>
+      </c>
+      <c r="I46" t="n">
+        <v>341801844.53</v>
+      </c>
+      <c r="J46" t="n">
+        <v>582699083.72</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100904605.34</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M46" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3726083941.44</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ST荣科</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G47" t="n">
+        <v>22477000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3680402.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4536364</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8216766.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>855961.4</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="M47" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3402365802.08</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>300290.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ST荣科</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33585825</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4450871.6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5356974</v>
+      </c>
+      <c r="J48" t="n">
+        <v>9807845.6</v>
+      </c>
+      <c r="K48" t="n">
+        <v>906102.4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M48" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3402365802.08</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>300487.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>蓝晓科技</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1340227084</v>
+      </c>
+      <c r="H49" t="n">
+        <v>144873523</v>
+      </c>
+      <c r="I49" t="n">
+        <v>257941142.67</v>
+      </c>
+      <c r="J49" t="n">
+        <v>402814665.67</v>
+      </c>
+      <c r="K49" t="n">
+        <v>113067619.67</v>
+      </c>
+      <c r="L49" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="M49" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="N49" t="n">
+        <v>21752331511.02</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>300518.SZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>新迅达</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1292215681</v>
+      </c>
+      <c r="H50" t="n">
+        <v>237999312.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>245774439.35</v>
+      </c>
+      <c r="J50" t="n">
+        <v>483773751.36</v>
+      </c>
+      <c r="K50" t="n">
+        <v>7775127.34</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M50" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7907113389.66</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>300545.SZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>联得装备</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-6.5584</v>
+      </c>
+      <c r="F51" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1829922655</v>
+      </c>
+      <c r="H51" t="n">
+        <v>378005797</v>
+      </c>
+      <c r="I51" t="n">
+        <v>176824139.99</v>
+      </c>
+      <c r="J51" t="n">
+        <v>554829936.99</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-201181657.01</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-10.99</v>
+      </c>
+      <c r="M51" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5161359223.95</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>300566.SZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>激智科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="E52" t="n">
+        <v>14.3166</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4865733717</v>
+      </c>
+      <c r="H52" t="n">
+        <v>663804275.0599999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>691438879.83</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1355243154.89</v>
+      </c>
+      <c r="K52" t="n">
+        <v>27634604.77</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M52" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="N52" t="n">
+        <v>9574981405.440001</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>300607.SZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>拓斯达</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20.0097</v>
+      </c>
+      <c r="F53" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2454412950</v>
+      </c>
+      <c r="H53" t="n">
+        <v>215811070.32</v>
+      </c>
+      <c r="I53" t="n">
+        <v>411770153.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>627581223.61</v>
+      </c>
+      <c r="K53" t="n">
+        <v>195959082.97</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="N53" t="n">
+        <v>16699468332.8</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>300852.SZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>四会富仕</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20.0029</v>
+      </c>
+      <c r="F54" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1640902466</v>
+      </c>
+      <c r="H54" t="n">
+        <v>171671623.62</v>
+      </c>
+      <c r="I54" t="n">
+        <v>391396863.19</v>
+      </c>
+      <c r="J54" t="n">
+        <v>563068486.8099999</v>
+      </c>
+      <c r="K54" t="n">
+        <v>219725239.57</v>
+      </c>
+      <c r="L54" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="M54" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="N54" t="n">
+        <v>12875319880.99</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>300852.SZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>四会富仕</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>83.09</v>
+      </c>
+      <c r="E55" t="n">
+        <v>20.0029</v>
+      </c>
+      <c r="F55" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2808962814</v>
+      </c>
+      <c r="H55" t="n">
+        <v>374669383.66</v>
+      </c>
+      <c r="I55" t="n">
+        <v>515877951.15</v>
+      </c>
+      <c r="J55" t="n">
+        <v>890547334.8099999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>141208567.49</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M55" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="N55" t="n">
+        <v>12875319880.99</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>300863.SZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>卡倍亿</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-17.8129</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1720853749</v>
+      </c>
+      <c r="H56" t="n">
+        <v>292226203.27</v>
+      </c>
+      <c r="I56" t="n">
+        <v>152533365.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>444759568.47</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-139692838.07</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="N56" t="n">
+        <v>15815557123.8</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>300873.SZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>海晨股份</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20.0167</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1523997140</v>
+      </c>
+      <c r="H57" t="n">
+        <v>263040671.84</v>
+      </c>
+      <c r="I57" t="n">
+        <v>178738419.88</v>
+      </c>
+      <c r="J57" t="n">
+        <v>441779091.72</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-84302251.95999999</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="M57" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6718412131.28</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>300873.SZ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>海晨股份</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="E58" t="n">
+        <v>20.0167</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2590280737</v>
+      </c>
+      <c r="H58" t="n">
+        <v>475444092.77</v>
+      </c>
+      <c r="I58" t="n">
+        <v>360512248.85</v>
+      </c>
+      <c r="J58" t="n">
+        <v>835956341.62</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-114931843.92</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="M58" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6718412131.28</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>301165.SZ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>锐捷网络</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6.7993</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6146197383</v>
+      </c>
+      <c r="H59" t="n">
+        <v>752744164.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1113003859.45</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1865748023.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>360259694.95</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M59" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="N59" t="n">
+        <v>95683636308.96001</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>301328.SZ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>维峰电子</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E60" t="n">
+        <v>13.2022</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1941637205</v>
+      </c>
+      <c r="H60" t="n">
+        <v>395733102.53</v>
+      </c>
+      <c r="I60" t="n">
+        <v>365724193.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>761457295.8200001</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-30008909.24</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="M60" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="N60" t="n">
+        <v>9282223477.799999</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>301421.SZ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>波长光电</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>121</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.8518</v>
+      </c>
+      <c r="F61" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2277865353</v>
+      </c>
+      <c r="H61" t="n">
+        <v>179146602.25</v>
+      </c>
+      <c r="I61" t="n">
+        <v>441385818</v>
+      </c>
+      <c r="J61" t="n">
+        <v>620532420.25</v>
+      </c>
+      <c r="K61" t="n">
+        <v>262239215.75</v>
+      </c>
+      <c r="L61" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="M61" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5603326685</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>301421.SZ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>波长光电</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>121</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.8518</v>
+      </c>
+      <c r="F62" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3500956896</v>
+      </c>
+      <c r="H62" t="n">
+        <v>308933415.74</v>
+      </c>
+      <c r="I62" t="n">
+        <v>643968209.91</v>
+      </c>
+      <c r="J62" t="n">
+        <v>952901625.65</v>
+      </c>
+      <c r="K62" t="n">
+        <v>335034794.17</v>
+      </c>
+      <c r="L62" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="M62" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5603326685</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>31</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-4.6154</v>
+      </c>
+      <c r="F63" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="G63" t="n">
+        <v>362191446</v>
+      </c>
+      <c r="H63" t="n">
+        <v>68436171.61</v>
+      </c>
+      <c r="I63" t="n">
+        <v>33105684.03</v>
+      </c>
+      <c r="J63" t="n">
+        <v>101541855.64</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-35330487.58</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1013651733</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>301528.SZ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>多浦乐</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4.2002</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1480543606</v>
+      </c>
+      <c r="H64" t="n">
+        <v>240422104.89</v>
+      </c>
+      <c r="I64" t="n">
+        <v>287253526.78</v>
+      </c>
+      <c r="J64" t="n">
+        <v>527675631.67</v>
+      </c>
+      <c r="K64" t="n">
+        <v>46831421.89</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M64" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3947515458.22</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>301669.SZ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>高特电子</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.0666</v>
+      </c>
+      <c r="F65" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1152081455</v>
+      </c>
+      <c r="H65" t="n">
+        <v>108538338.78</v>
+      </c>
+      <c r="I65" t="n">
+        <v>116222051.66</v>
+      </c>
+      <c r="J65" t="n">
+        <v>224760390.44</v>
+      </c>
+      <c r="K65" t="n">
+        <v>7683712.88</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M65" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3437639139.1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>600113.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>浙江东日</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10.006</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>835459518</v>
+      </c>
+      <c r="H66" t="n">
+        <v>162861608</v>
+      </c>
+      <c r="I66" t="n">
+        <v>150018615.2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>312880223.2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-12842992.8</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="M66" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="N66" t="n">
+        <v>15017237340</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>600206.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>有研新材</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F67" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G67" t="n">
+        <v>9258574105</v>
+      </c>
+      <c r="H67" t="n">
+        <v>390710894.44</v>
+      </c>
+      <c r="I67" t="n">
+        <v>385769570.59</v>
+      </c>
+      <c r="J67" t="n">
+        <v>776480465.03</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-4941323.85</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M67" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="N67" t="n">
+        <v>50742406720.08</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>600228.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>返利科技</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F68" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="G68" t="n">
+        <v>647264278</v>
+      </c>
+      <c r="H68" t="n">
+        <v>160565925</v>
+      </c>
+      <c r="I68" t="n">
+        <v>122360557</v>
+      </c>
+      <c r="J68" t="n">
+        <v>282926482</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-38205368</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="M68" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3482231171.49</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>600228.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>返利科技</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F69" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2458211505</v>
+      </c>
+      <c r="H69" t="n">
+        <v>406020410.15</v>
+      </c>
+      <c r="I69" t="n">
+        <v>381783872</v>
+      </c>
+      <c r="J69" t="n">
+        <v>787804282.15</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-24236538.15</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="M69" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3482231171.49</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>600233.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>圆通速递</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="E70" t="n">
+        <v>10.0317</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G70" t="n">
+        <v>205475554</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="J70" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="K70" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="L70" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="M70" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="N70" t="n">
+        <v>59319552591.54</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>600233.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>圆通速递</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.0317</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G71" t="n">
+        <v>205475554</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="J71" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="K71" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="L71" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="M71" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="N71" t="n">
+        <v>59319552591.54</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>600233.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>圆通速递</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10.0317</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G72" t="n">
+        <v>205475554</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="J72" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="K72" t="n">
+        <v>103662861</v>
+      </c>
+      <c r="L72" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="M72" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="N72" t="n">
+        <v>59319552591.54</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>600363.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>联创光电</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3.5495</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3490852687</v>
+      </c>
+      <c r="H73" t="n">
+        <v>420667671.04</v>
+      </c>
+      <c r="I73" t="n">
+        <v>358737316.33</v>
+      </c>
+      <c r="J73" t="n">
+        <v>779404987.37</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-61930354.71</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="M73" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="N73" t="n">
+        <v>16705417072.5</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>600378.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>昊华科技</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>81</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7.4556</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="G74" t="n">
+        <v>24450154939</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1898932358.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2658208161.52</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4557140520.02</v>
+      </c>
+      <c r="K74" t="n">
+        <v>759275803.02</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M74" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="N74" t="n">
+        <v>86877794403</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>600509.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>天富能源</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10.0592</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>142815450</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="J75" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="K75" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="L75" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12781895885.1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>600509.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>天富能源</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E76" t="n">
+        <v>10.0592</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G76" t="n">
+        <v>142815450</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="J76" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="K76" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="L76" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="M76" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="N76" t="n">
+        <v>12781895885.1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>600509.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>天富能源</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E77" t="n">
+        <v>10.0592</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G77" t="n">
+        <v>142815450</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="J77" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="K77" t="n">
+        <v>101724330</v>
+      </c>
+      <c r="L77" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="M77" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="N77" t="n">
+        <v>12781895885.1</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>600509.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>天富能源</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>10.0592</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G78" t="n">
+        <v>142815450</v>
+      </c>
+      <c r="H78" t="n">
+        <v>13122300</v>
+      </c>
+      <c r="I78" t="n">
+        <v>116899140</v>
+      </c>
+      <c r="J78" t="n">
+        <v>130021440</v>
+      </c>
+      <c r="K78" t="n">
+        <v>103776840</v>
+      </c>
+      <c r="L78" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="M78" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="N78" t="n">
+        <v>12781895885.1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>600552.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>凯盛科技</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-8.9932</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5862684109</v>
+      </c>
+      <c r="H79" t="n">
+        <v>564551595.5599999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>518241697.95</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1082793293.51</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-46309897.61</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="M79" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="N79" t="n">
+        <v>28007594407.1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>600641.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>先导基电</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="E80" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8381032080</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1051890303.38</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1760680673.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2812570976.58</v>
+      </c>
+      <c r="K80" t="n">
+        <v>708790369.8200001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M80" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="N80" t="n">
+        <v>40808121992</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>600724.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>宁波富达</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="E81" t="n">
+        <v>10.0592</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G81" t="n">
+        <v>83593665</v>
+      </c>
+      <c r="H81" t="n">
+        <v>11525264</v>
+      </c>
+      <c r="I81" t="n">
+        <v>29209485.42</v>
+      </c>
+      <c r="J81" t="n">
+        <v>40734749.42</v>
+      </c>
+      <c r="K81" t="n">
+        <v>17684221.42</v>
+      </c>
+      <c r="L81" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="M81" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8062780065.12</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>600737.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>中粮糖业</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4.5418</v>
+      </c>
+      <c r="F82" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2249797420</v>
+      </c>
+      <c r="H82" t="n">
+        <v>294811778.85</v>
+      </c>
+      <c r="I82" t="n">
+        <v>379995272.78</v>
+      </c>
+      <c r="J82" t="n">
+        <v>674807051.63</v>
+      </c>
+      <c r="K82" t="n">
+        <v>85183493.93000001</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M82" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="N82" t="n">
+        <v>27569753658.92</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>600783.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>鲁信创投</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E83" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1370682396</v>
+      </c>
+      <c r="H83" t="n">
+        <v>172826934.02</v>
+      </c>
+      <c r="I83" t="n">
+        <v>226953909.36</v>
+      </c>
+      <c r="J83" t="n">
+        <v>399780843.38</v>
+      </c>
+      <c r="K83" t="n">
+        <v>54126975.34</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M83" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="N83" t="n">
+        <v>16308912131.54</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>600791.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>京能置业</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-4.4622</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G84" t="n">
+        <v>407727329</v>
+      </c>
+      <c r="H84" t="n">
+        <v>112270678.6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>63809257</v>
+      </c>
+      <c r="J84" t="n">
+        <v>176079935.6</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-48461421.6</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-11.89</v>
+      </c>
+      <c r="M84" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3776819361.6</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>600791.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>京能置业</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-4.4622</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G85" t="n">
+        <v>854254028</v>
+      </c>
+      <c r="H85" t="n">
+        <v>210964951.28</v>
+      </c>
+      <c r="I85" t="n">
+        <v>160689100.07</v>
+      </c>
+      <c r="J85" t="n">
+        <v>371654051.35</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-50275851.21</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="M85" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3776819361.6</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>600857.SH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>宁波中百</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1100151606</v>
+      </c>
+      <c r="H86" t="n">
+        <v>181499677.25</v>
+      </c>
+      <c r="I86" t="n">
+        <v>202167521.06</v>
+      </c>
+      <c r="J86" t="n">
+        <v>383667198.31</v>
+      </c>
+      <c r="K86" t="n">
+        <v>20667843.81</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M86" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4914849425.29</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>601162.SH</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>天风证券</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E87" t="n">
+        <v>10.089</v>
+      </c>
+      <c r="F87" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1618420500</v>
+      </c>
+      <c r="H87" t="n">
+        <v>59049791</v>
+      </c>
+      <c r="I87" t="n">
+        <v>220081713.4</v>
+      </c>
+      <c r="J87" t="n">
+        <v>279131504.4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>161031922.4</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="M87" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="N87" t="n">
+        <v>31898470458.54</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>603120.SH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>肯特催化</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="E88" t="n">
+        <v>10.0094</v>
+      </c>
+      <c r="F88" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="G88" t="n">
+        <v>598454804</v>
+      </c>
+      <c r="H88" t="n">
+        <v>79028083.75</v>
+      </c>
+      <c r="I88" t="n">
+        <v>134824476.85</v>
+      </c>
+      <c r="J88" t="n">
+        <v>213852560.6</v>
+      </c>
+      <c r="K88" t="n">
+        <v>55796393.1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="M88" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2224351000</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>603203.SH</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>快克智能</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-10.0026</v>
+      </c>
+      <c r="F89" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1773542164</v>
+      </c>
+      <c r="H89" t="n">
+        <v>124787393.63</v>
+      </c>
+      <c r="I89" t="n">
+        <v>146005197.84</v>
+      </c>
+      <c r="J89" t="n">
+        <v>270792591.47</v>
+      </c>
+      <c r="K89" t="n">
+        <v>21217804.21</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="N89" t="n">
+        <v>22381442528.3</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>603261.SH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>立航科技</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-9.809799999999999</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G90" t="n">
+        <v>292732414</v>
+      </c>
+      <c r="H90" t="n">
+        <v>120589138</v>
+      </c>
+      <c r="I90" t="n">
+        <v>36335963</v>
+      </c>
+      <c r="J90" t="n">
+        <v>156925101</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-84253175</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-28.78</v>
+      </c>
+      <c r="M90" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3491601241.1</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>603261.SH</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>立航科技</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-9.809799999999999</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="G91" t="n">
+        <v>880316850</v>
+      </c>
+      <c r="H91" t="n">
+        <v>245672229.35</v>
+      </c>
+      <c r="I91" t="n">
+        <v>112461656</v>
+      </c>
+      <c r="J91" t="n">
+        <v>358133885.35</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-133210573.35</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-15.13</v>
+      </c>
+      <c r="M91" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3491601241.1</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>603303.SH</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>得邦照明</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-9.981199999999999</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G92" t="n">
+        <v>243102884</v>
+      </c>
+      <c r="H92" t="n">
+        <v>81593403.31999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>69556867</v>
+      </c>
+      <c r="J92" t="n">
+        <v>151150270.32</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-12036536.32</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M92" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="N92" t="n">
+        <v>11398975342.5</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>603363.SH</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>傲农生物</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E93" t="n">
+        <v>10.0746</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G93" t="n">
+        <v>195180655</v>
+      </c>
+      <c r="H93" t="n">
+        <v>36116923</v>
+      </c>
+      <c r="I93" t="n">
+        <v>69630257</v>
+      </c>
+      <c r="J93" t="n">
+        <v>105747180</v>
+      </c>
+      <c r="K93" t="n">
+        <v>33513334</v>
+      </c>
+      <c r="L93" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="M93" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6332439520.6</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>603379.SH</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>三美股份</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="E94" t="n">
+        <v>10.0013</v>
+      </c>
+      <c r="F94" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5942046804</v>
+      </c>
+      <c r="H94" t="n">
+        <v>706734178.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>648021861.55</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1354756040.05</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-58712316.95</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="M94" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N94" t="n">
+        <v>50962790008.76</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>603389.SH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>亚振家居</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-2.264</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G95" t="n">
+        <v>273014567</v>
+      </c>
+      <c r="H95" t="n">
+        <v>68612903</v>
+      </c>
+      <c r="I95" t="n">
+        <v>25541879.2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>94154782.2</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-43071023.8</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-15.78</v>
+      </c>
+      <c r="M95" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="N95" t="n">
+        <v>15426169920</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>603399.SH</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>永杉锂业</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.0676</v>
+      </c>
+      <c r="F96" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2404211256</v>
+      </c>
+      <c r="H96" t="n">
+        <v>306302902.36</v>
+      </c>
+      <c r="I96" t="n">
+        <v>184983256.06</v>
+      </c>
+      <c r="J96" t="n">
+        <v>491286158.42</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-121319646.3</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="M96" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="N96" t="n">
+        <v>11639243545.28</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-2.6127</v>
+      </c>
+      <c r="F97" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="G97" t="n">
+        <v>944424948</v>
+      </c>
+      <c r="H97" t="n">
+        <v>154566382.52</v>
+      </c>
+      <c r="I97" t="n">
+        <v>176108515.32</v>
+      </c>
+      <c r="J97" t="n">
+        <v>330674897.84</v>
+      </c>
+      <c r="K97" t="n">
+        <v>21542132.8</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M97" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3707913174</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>603458.SH</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>勘设股份</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-9.965400000000001</v>
+      </c>
+      <c r="F98" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G98" t="n">
+        <v>589159559</v>
+      </c>
+      <c r="H98" t="n">
+        <v>81020964.09999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>58995573.54</v>
+      </c>
+      <c r="J98" t="n">
+        <v>140016537.64</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-22025390.56</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="M98" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N98" t="n">
+        <v>3982679927.14</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>603459.SH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>红板科技</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>104.69</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-6.7017</v>
+      </c>
+      <c r="F99" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3590030707</v>
+      </c>
+      <c r="H99" t="n">
+        <v>550071653.58</v>
+      </c>
+      <c r="I99" t="n">
+        <v>603739861.55</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1153811515.13</v>
+      </c>
+      <c r="K99" t="n">
+        <v>53668207.97</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M99" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="N99" t="n">
+        <v>8275939014.02</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>603567.SH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>珍宝岛</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E100" t="n">
+        <v>10.0457</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G100" t="n">
+        <v>151595538</v>
+      </c>
+      <c r="H100" t="n">
+        <v>19548958</v>
+      </c>
+      <c r="I100" t="n">
+        <v>35831289.35</v>
+      </c>
+      <c r="J100" t="n">
+        <v>55380247.35</v>
+      </c>
+      <c r="K100" t="n">
+        <v>16282331.35</v>
+      </c>
+      <c r="L100" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="M100" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="N100" t="n">
+        <v>4527923867.44</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>603922.SH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ST金鸿顺</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-5.0259</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="G101" t="n">
+        <v>81699979</v>
+      </c>
+      <c r="H101" t="n">
+        <v>28379870</v>
+      </c>
+      <c r="I101" t="n">
+        <v>23416925</v>
+      </c>
+      <c r="J101" t="n">
+        <v>51796795</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-4962945</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="M101" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="N101" t="n">
+        <v>2302720000</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格跌幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260702</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5517</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2219</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3162</v>
+      </c>
+      <c r="E2" t="n">
+        <v>136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34739.26</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4112.4453</v>
+        <v>4028.9038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44</v>
+        <v>-2.03</v>
       </c>
       <c r="F2" t="n">
-        <v>16984.88</v>
+        <v>15771.84</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16119.1683</v>
+        <v>15498.8101</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.53</v>
+        <v>-3.85</v>
       </c>
       <c r="F3" t="n">
-        <v>19615.04</v>
+        <v>18733.51</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4260.7208</v>
+        <v>4017.2735</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.89</v>
+        <v>-5.71</v>
       </c>
       <c r="F4" t="n">
-        <v>9815.209999999999</v>
+        <v>8903.73</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4958.9773</v>
+        <v>4812.2957</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.41</v>
+        <v>-2.96</v>
       </c>
       <c r="F5" t="n">
-        <v>11017.18</v>
+        <v>10277.97</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2153.0431</v>
+        <v>1987.291</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.48</v>
+        <v>-7.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2323.28</v>
+        <v>2149.53</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8876.630300000001</v>
+        <v>8625.3336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
+        <v>-2.83</v>
       </c>
       <c r="F7" t="n">
-        <v>7828</v>
+        <v>7178.67</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6514 @@
           <t>20260702</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>34739.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>616.5493</v>
+      </c>
+      <c r="J2" t="n">
+        <v>244119.92</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1478419.21715</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>001248.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="I3" t="n">
+        <v>136.8942</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7216977.18</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17692297.7802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>920221.BJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29.9453</v>
+      </c>
+      <c r="J4" t="n">
+        <v>105694.77</v>
+      </c>
+      <c r="K4" t="n">
+        <v>167469.12622</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300163.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.0371</v>
+      </c>
+      <c r="J5" t="n">
+        <v>349299.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>213434.58178</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301019.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0111</v>
+      </c>
+      <c r="J6" t="n">
+        <v>52195.32</v>
+      </c>
+      <c r="K6" t="n">
+        <v>105273.71125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301092.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="D7" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="G7" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.0041</v>
+      </c>
+      <c r="J7" t="n">
+        <v>94221.92</v>
+      </c>
+      <c r="K7" t="n">
+        <v>540178.70445</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688216.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>211472.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1024000.211</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300695.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="E9" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19.996</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37394.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>209819.97775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301008.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="E10" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="G10" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.9925</v>
+      </c>
+      <c r="J10" t="n">
+        <v>174160.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>527877.77721</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300740.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19.9892</v>
+      </c>
+      <c r="J11" t="n">
+        <v>360466.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>743594.65033</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301611.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>176</v>
+      </c>
+      <c r="E2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F2" t="n">
+        <v>154.06</v>
+      </c>
+      <c r="G2" t="n">
+        <v>184.48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-30.42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-16.4896</v>
+      </c>
+      <c r="J2" t="n">
+        <v>254764.65</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4090541.52639</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>688056.SH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E3" t="n">
+        <v>57</v>
+      </c>
+      <c r="F3" t="n">
+        <v>57</v>
+      </c>
+      <c r="G3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-16.1765</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48318</v>
+      </c>
+      <c r="K3" t="n">
+        <v>288577.04</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>688409.SH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>285</v>
+      </c>
+      <c r="D4" t="n">
+        <v>286.05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>242</v>
+      </c>
+      <c r="F4" t="n">
+        <v>248.07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>295.34</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-47.27</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-16.0053</v>
+      </c>
+      <c r="J4" t="n">
+        <v>187282.59</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4891587.05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688361.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>405.12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>412</v>
+      </c>
+      <c r="E5" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>356</v>
+      </c>
+      <c r="G5" t="n">
+        <v>422</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-15.6398</v>
+      </c>
+      <c r="J5" t="n">
+        <v>199656.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7445805.285</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688260.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>122.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>109</v>
+      </c>
+      <c r="F6" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="G6" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-19.81</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-15.1568</v>
+      </c>
+      <c r="J6" t="n">
+        <v>45221.09</v>
+      </c>
+      <c r="K6" t="n">
+        <v>526921.286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688020.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>240</v>
+      </c>
+      <c r="D7" t="n">
+        <v>260</v>
+      </c>
+      <c r="E7" t="n">
+        <v>227.29</v>
+      </c>
+      <c r="F7" t="n">
+        <v>229.26</v>
+      </c>
+      <c r="G7" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-40.82</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-15.114</v>
+      </c>
+      <c r="J7" t="n">
+        <v>56717.15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1371676.015</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688200.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>499.98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>513</v>
+      </c>
+      <c r="E8" t="n">
+        <v>439</v>
+      </c>
+      <c r="F8" t="n">
+        <v>450</v>
+      </c>
+      <c r="G8" t="n">
+        <v>529.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-79.84999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-15.0703</v>
+      </c>
+      <c r="J8" t="n">
+        <v>89194</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4211977.561</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>688120.SH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>307.86</v>
+      </c>
+      <c r="D9" t="n">
+        <v>312.93</v>
+      </c>
+      <c r="E9" t="n">
+        <v>275.98</v>
+      </c>
+      <c r="F9" t="n">
+        <v>281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>330</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-14.8485</v>
+      </c>
+      <c r="J9" t="n">
+        <v>244151.97</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7135138.987</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688008.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>294.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>298.56</v>
+      </c>
+      <c r="E10" t="n">
+        <v>268.78</v>
+      </c>
+      <c r="F10" t="n">
+        <v>269.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-46.74</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-14.7963</v>
+      </c>
+      <c r="J10" t="n">
+        <v>899764.08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25642706.037</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688233.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>224.26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>233.26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>196.12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>203.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>238.56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-34.59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-14.4995</v>
+      </c>
+      <c r="J11" t="n">
+        <v>241733.41</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5121298.325</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.8108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3823929</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1782158</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2510516.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4292674.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>728358.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>112.26</v>
+      </c>
+      <c r="N2" t="n">
+        <v>51778517.88</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000010.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>*ST美丽</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.0279</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="G3" t="n">
+        <v>87685390</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12935566</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12685470</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25621036</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-250096</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="M3" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1641343337.96</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000016.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*ST康佳A</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.9587</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>88453777</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18734126</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9842483.52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28576609.52</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-8891642.48</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-10.05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4655748441.92</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000021.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>深科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-10.0064</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9940689255</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1186951211.47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>910927356.24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2097878567.71</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-276023855.23</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>88199937147.39999</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000078.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST海王</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.1852</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>128962614</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11698963.26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15800802.86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27499766.12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4101839.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3727806299.68</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000520.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>凤凰航运</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>412857738</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46768648</v>
+      </c>
+      <c r="I7" t="n">
+        <v>96942469.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>143711117.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50173821.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4564496382.05</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000536.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华映科技</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.0271</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1008732067</v>
+      </c>
+      <c r="H8" t="n">
+        <v>107278651.17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>231576597.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>338855248.77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>124297946.43</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11218084564.96</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000601.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>韶能股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.937900000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>577297658</v>
+      </c>
+      <c r="H9" t="n">
+        <v>58778929.99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>111466777.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>170245707.39</v>
+      </c>
+      <c r="K9" t="n">
+        <v>52687847.41</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7431299149.92</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000632.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST三木</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>79588972</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12915138</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23023335</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35938473</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10108197</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1564018196.16</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000639.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST西王</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.1724</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G11" t="n">
+        <v>70938980</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6415296</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10224178</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16639474</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3808882</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1316900661.84</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000677.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST海龙</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.298</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>134429148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13431283</v>
+      </c>
+      <c r="I12" t="n">
+        <v>17264427</v>
+      </c>
+      <c r="J12" t="n">
+        <v>30695710</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3833144</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1373724937.32</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>000698.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST沈化</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.1118</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G13" t="n">
+        <v>56419265</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11315638</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8580403</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19896041</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-2735235</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2585000359.55</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>000700.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>模塑科技</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9.9739</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1877232158</v>
+      </c>
+      <c r="H14" t="n">
+        <v>202364015.72</v>
+      </c>
+      <c r="I14" t="n">
+        <v>346888543.17</v>
+      </c>
+      <c r="J14" t="n">
+        <v>549252558.89</v>
+      </c>
+      <c r="K14" t="n">
+        <v>144524527.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15486919612.43</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>000700.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>模塑科技</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.9739</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4293695300</v>
+      </c>
+      <c r="H15" t="n">
+        <v>395607583.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>496835277.72</v>
+      </c>
+      <c r="J15" t="n">
+        <v>892442860.89</v>
+      </c>
+      <c r="K15" t="n">
+        <v>101227694.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15486919612.43</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>000711.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST京蓝</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.0314</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G16" t="n">
+        <v>256948796</v>
+      </c>
+      <c r="H16" t="n">
+        <v>51184522.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23494445.96</v>
+      </c>
+      <c r="J16" t="n">
+        <v>74678968.44</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-27690076.52</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-10.78</v>
+      </c>
+      <c r="M16" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11930250299.85</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>000725.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>京东方A</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.7628</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="G17" t="n">
+        <v>49342409554</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5576922037.19</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7359613319.24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12936535356.43</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1782691282.05</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M17" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>325845790718.76</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>000820.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>*ST节能</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.8951</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G18" t="n">
+        <v>26926680</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10134803</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7337394</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17472197</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-2797409</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="N18" t="n">
+        <v>890900631</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>000821.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST京机</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.9608</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G19" t="n">
+        <v>315367220</v>
+      </c>
+      <c r="H19" t="n">
+        <v>58510567.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>46160388</v>
+      </c>
+      <c r="J19" t="n">
+        <v>104670955.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-12350179.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="M19" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4861392142.56</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>000909.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>*ST数源</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.0633</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35374508</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7062882</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11866869</v>
+      </c>
+      <c r="J20" t="n">
+        <v>18929751</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4803987</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1816498865.5</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>000972.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中基健康</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.1493</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G21" t="n">
+        <v>92018130</v>
+      </c>
+      <c r="H21" t="n">
+        <v>16752708.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22639167.22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>39391875.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5886458.97</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2846036406.51</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>000988.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>华工科技</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-9.9971</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12989369286</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1923021942.62</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1014027076.84</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2937049019.46</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-908994865.78</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="N22" t="n">
+        <v>156978759623.4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>001237.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>惠康科技</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>69.01000000000001</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-5.6854</v>
+      </c>
+      <c r="F23" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="G23" t="n">
+        <v>674559182</v>
+      </c>
+      <c r="H23" t="n">
+        <v>107419598.29</v>
+      </c>
+      <c r="I23" t="n">
+        <v>64020613.75</v>
+      </c>
+      <c r="J23" t="n">
+        <v>171440212.04</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-43398984.54</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25.42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2405414492.28</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>001248.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>华润新能源</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E24" t="n">
+        <v>136.8942</v>
+      </c>
+      <c r="F24" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17692297780</v>
+      </c>
+      <c r="H24" t="n">
+        <v>585036255.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1469066431.83</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2054102686.91</v>
+      </c>
+      <c r="K24" t="n">
+        <v>884030176.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="N24" t="n">
+        <v>25444570794.45</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>001313.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>粤海饲料</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G25" t="n">
+        <v>467684160</v>
+      </c>
+      <c r="H25" t="n">
+        <v>53530282</v>
+      </c>
+      <c r="I25" t="n">
+        <v>114534505</v>
+      </c>
+      <c r="J25" t="n">
+        <v>168064787</v>
+      </c>
+      <c r="K25" t="n">
+        <v>61004223</v>
+      </c>
+      <c r="L25" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="M25" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5998734893.58</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>001358.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>兴欣新材</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1881</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G26" t="n">
+        <v>396725241</v>
+      </c>
+      <c r="H26" t="n">
+        <v>72077188.78</v>
+      </c>
+      <c r="I26" t="n">
+        <v>88092553.52</v>
+      </c>
+      <c r="J26" t="n">
+        <v>160169742.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>16015364.74</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="M26" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1409392087.72</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002005.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ST德豪</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.1948</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G27" t="n">
+        <v>31297695</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5792419</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11114781</v>
+      </c>
+      <c r="J27" t="n">
+        <v>16907200</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5322362</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4257297446.94</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002102.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ST能特</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.8889</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G28" t="n">
+        <v>75742759</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10445955.95</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15917171</v>
+      </c>
+      <c r="J28" t="n">
+        <v>26363126.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5471215.05</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M28" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5127855752.24</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002109.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ST兴化</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.1383</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G29" t="n">
+        <v>27743358</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4519631</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7854273</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12373904</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3334642</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="M29" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3394877803.66</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002167.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>东方锆业</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F30" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5096818540</v>
+      </c>
+      <c r="H30" t="n">
+        <v>884148407.2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>816346174.41</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1700494581.61</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-67802232.79000001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="M30" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="N30" t="n">
+        <v>19764472686.15</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002167.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>东方锆业</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F31" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9062906869</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1136692120.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1327686238.62</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2464378358.77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>190994118.47</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M31" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19764472686.15</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002175.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>*ST东智</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5.0633</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4577568</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1682631</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4577568</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6260199</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2894937</v>
+      </c>
+      <c r="L32" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="M32" t="n">
+        <v>136.76</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3179184010.23</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002198.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ST嘉应</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.0314</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G33" t="n">
+        <v>43990809</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6367195</v>
+      </c>
+      <c r="I33" t="n">
+        <v>17706257</v>
+      </c>
+      <c r="J33" t="n">
+        <v>24073452</v>
+      </c>
+      <c r="K33" t="n">
+        <v>11339062</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="M33" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1694983861.32</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002273.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>水晶光电</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="F34" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12472092406</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2269444447.68</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2086004798.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4355449246.58</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-183439648.78</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="M34" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="N34" t="n">
+        <v>53148298348.58</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002305.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>*ST南置</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.9451</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G35" t="n">
+        <v>46745190</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10237393</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10072967</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20310360</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-164426</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M35" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3312137257.16</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>002326.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>永太科技</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>28</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.6095</v>
+      </c>
+      <c r="F36" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5988741380</v>
+      </c>
+      <c r="H36" t="n">
+        <v>347090311.65</v>
+      </c>
+      <c r="I36" t="n">
+        <v>714514160.66</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1061604472.31</v>
+      </c>
+      <c r="K36" t="n">
+        <v>367423849.01</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="M36" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="N36" t="n">
+        <v>22628453176</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>002326.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>永太科技</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>28</v>
+      </c>
+      <c r="E37" t="n">
+        <v>7.6095</v>
+      </c>
+      <c r="F37" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7481831383</v>
+      </c>
+      <c r="H37" t="n">
+        <v>451250592.49</v>
+      </c>
+      <c r="I37" t="n">
+        <v>932521667.99</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1383772260.48</v>
+      </c>
+      <c r="K37" t="n">
+        <v>481271075.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="M37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>22628453176</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>002360.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ST同德</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5.0607</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>45671842</v>
+      </c>
+      <c r="H38" t="n">
+        <v>13687810</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9743857</v>
+      </c>
+      <c r="J38" t="n">
+        <v>23431667</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-3943953</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="M38" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1689447336.42</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>002371.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北方华创</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>841.8200000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-10.0004</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10345919579</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2642488580.43</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1972240123.11</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4614728703.54</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-670248457.3200001</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="M39" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>610411972243.36</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>002384.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>221.68</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-9.999599999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18849580300</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2802768700.57</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2135585325.64</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4938354026.21</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-667183374.9299999</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="M40" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>307319799554.64</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>002396.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="F41" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3080229188</v>
+      </c>
+      <c r="H41" t="n">
+        <v>291114214.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>646773030.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>937887244.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>355658815.9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="M41" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="N41" t="n">
+        <v>16110219304.62</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>002403.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>爱仕达</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4.1794</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G42" t="n">
+        <v>315739805</v>
+      </c>
+      <c r="H42" t="n">
+        <v>69712387.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>67715530.7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>137427918.2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1996856.8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M42" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3036990059.88</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>002407.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>多氟多</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.7783</v>
+      </c>
+      <c r="F43" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="G43" t="n">
+        <v>20679906115</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2419387187.07</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2939369592.18</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5358756779.25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>519982405.11</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M43" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="N43" t="n">
+        <v>59138025852.9</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>002458.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>益生股份</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.0585</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1674018754</v>
+      </c>
+      <c r="H44" t="n">
+        <v>268306706.03</v>
+      </c>
+      <c r="I44" t="n">
+        <v>152573419.07</v>
+      </c>
+      <c r="J44" t="n">
+        <v>420880125.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-115733286.96</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="M44" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="N44" t="n">
+        <v>9093688241.93</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>002463.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>130.51</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-9.9993</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="G45" t="n">
+        <v>11770285306</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2140303859.55</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1120925579.22</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3261229438.77</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-1019378280.33</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="M45" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="N45" t="n">
+        <v>250945996527.86</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>002512.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ST达华</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.9231</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="G46" t="n">
+        <v>256928450</v>
+      </c>
+      <c r="H46" t="n">
+        <v>31813262.45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>24571951</v>
+      </c>
+      <c r="J46" t="n">
+        <v>56385213.45</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-7241311.45</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="M46" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3732080576.62</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>002522.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>浙江众成</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-10.0418</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2484514003</v>
+      </c>
+      <c r="H47" t="n">
+        <v>158376570.51</v>
+      </c>
+      <c r="I47" t="n">
+        <v>144274133.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>302650703.87</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-14102437.15</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="M47" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5837378219.55</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>002542.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>*ST中岩</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5.042</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G48" t="n">
+        <v>45986838</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6594622.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9172424</v>
+      </c>
+      <c r="J48" t="n">
+        <v>15767046.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2577801.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="M48" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2198464105</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>002547.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>*ST春兴</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G49" t="n">
+        <v>152358536</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19375981</v>
+      </c>
+      <c r="I49" t="n">
+        <v>21565058.78</v>
+      </c>
+      <c r="J49" t="n">
+        <v>40941039.78</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2189077.78</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M49" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2905642846.58</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.7608</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G50" t="n">
+        <v>825311416</v>
+      </c>
+      <c r="H50" t="n">
+        <v>68033932</v>
+      </c>
+      <c r="I50" t="n">
+        <v>84331475</v>
+      </c>
+      <c r="J50" t="n">
+        <v>152365407</v>
+      </c>
+      <c r="K50" t="n">
+        <v>16297543</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M50" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="N50" t="n">
+        <v>22574511484.14</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>002559.SZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>亚威股份</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0143</v>
+      </c>
+      <c r="F51" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1423648187</v>
+      </c>
+      <c r="H51" t="n">
+        <v>275121791.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>258707512.62</v>
+      </c>
+      <c r="J51" t="n">
+        <v>533829304.42</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-16414279.18</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="M51" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>7751597038.42</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>002559.SZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>亚威股份</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0143</v>
+      </c>
+      <c r="F52" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1712673503</v>
+      </c>
+      <c r="H52" t="n">
+        <v>278086949.8</v>
+      </c>
+      <c r="I52" t="n">
+        <v>418636138.62</v>
+      </c>
+      <c r="J52" t="n">
+        <v>696723088.42</v>
+      </c>
+      <c r="K52" t="n">
+        <v>140549188.82</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="N52" t="n">
+        <v>7751597038.42</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>002569.SZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>*ST步森</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5.0068</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G53" t="n">
+        <v>17929412</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7629054</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10895865</v>
+      </c>
+      <c r="J53" t="n">
+        <v>18524919</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3266811</v>
+      </c>
+      <c r="L53" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="M53" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2172955200</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>002580.SZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.0198</v>
+      </c>
+      <c r="F54" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1548160394</v>
+      </c>
+      <c r="H54" t="n">
+        <v>170399042.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>336655620.85</v>
+      </c>
+      <c r="J54" t="n">
+        <v>507054663.35</v>
+      </c>
+      <c r="K54" t="n">
+        <v>166256578.35</v>
+      </c>
+      <c r="L54" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="M54" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="N54" t="n">
+        <v>10032874584</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>002586.SZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ST围海</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.9223</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G55" t="n">
+        <v>75408854</v>
+      </c>
+      <c r="H55" t="n">
+        <v>22985353</v>
+      </c>
+      <c r="I55" t="n">
+        <v>15518188</v>
+      </c>
+      <c r="J55" t="n">
+        <v>38503541</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-7467165</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="M55" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4404447912.15</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>002592.SZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ST八菱</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5.0243</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>35960384</v>
+      </c>
+      <c r="H56" t="n">
+        <v>6080877</v>
+      </c>
+      <c r="I56" t="n">
+        <v>11328983</v>
+      </c>
+      <c r="J56" t="n">
+        <v>17409860</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5248106</v>
+      </c>
+      <c r="L56" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="M56" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1702402077.6</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>002620.SZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>*ST瑞和</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.0373</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G57" t="n">
+        <v>99461266</v>
+      </c>
+      <c r="H57" t="n">
+        <v>21375315</v>
+      </c>
+      <c r="I57" t="n">
+        <v>17746394</v>
+      </c>
+      <c r="J57" t="n">
+        <v>39121709</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-3628921</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="M57" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1779485528.9</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>002635.SZ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>安洁科技</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2592528833</v>
+      </c>
+      <c r="H58" t="n">
+        <v>221791452.95</v>
+      </c>
+      <c r="I58" t="n">
+        <v>285727442.15</v>
+      </c>
+      <c r="J58" t="n">
+        <v>507518895.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>63935989.2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M58" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8401123235.16</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>002653.SZ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>海思科</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>8.0044</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1755151019</v>
+      </c>
+      <c r="H59" t="n">
+        <v>245277466.59</v>
+      </c>
+      <c r="I59" t="n">
+        <v>158339189.48</v>
+      </c>
+      <c r="J59" t="n">
+        <v>403616656.07</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-86938277.11</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M59" t="n">
+        <v>23</v>
+      </c>
+      <c r="N59" t="n">
+        <v>42298747280.4</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>002656.SZ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>*ST摩登</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4.9645</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G60" t="n">
+        <v>40545944</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12433797</v>
+      </c>
+      <c r="I60" t="n">
+        <v>12895754</v>
+      </c>
+      <c r="J60" t="n">
+        <v>25329551</v>
+      </c>
+      <c r="K60" t="n">
+        <v>461957</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M60" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2032449569.28</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4.9645</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G61" t="n">
+        <v>232023913</v>
+      </c>
+      <c r="H61" t="n">
+        <v>41116690.2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>37766661</v>
+      </c>
+      <c r="J61" t="n">
+        <v>78883351.2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-3350029.2</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="M61" t="n">
+        <v>34</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2801474240</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>兴业科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.0078</v>
+      </c>
+      <c r="F62" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1113410650</v>
+      </c>
+      <c r="H62" t="n">
+        <v>62536773.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>73105964</v>
+      </c>
+      <c r="J62" t="n">
+        <v>135642737.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>10569190.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M62" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="N62" t="n">
+        <v>8264923169</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>002691.SZ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>*ST冀凯</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3.1175</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G63" t="n">
+        <v>59645274</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10999198.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>16253777</v>
+      </c>
+      <c r="J63" t="n">
+        <v>27252975.9</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5254578.1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="M63" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1444711549</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>002717.SZ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>*ST岭南</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9901</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>195565911</v>
+      </c>
+      <c r="H64" t="n">
+        <v>25330496.8</v>
+      </c>
+      <c r="I64" t="n">
+        <v>23435497.4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>48765994.2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-1894999.4</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="M64" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1752925045.32</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>002738.SZ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>中矿资源</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9403173225</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1585509616.15</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1852129463.54</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3437639079.69</v>
+      </c>
+      <c r="K65" t="n">
+        <v>266619847.39</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M65" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="N65" t="n">
+        <v>46578323422.74</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>002747.SZ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>埃斯顿</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.8768</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="G66" t="n">
+        <v>11880225616</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1264444993.58</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1659430501.25</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2923875494.83</v>
+      </c>
+      <c r="K66" t="n">
+        <v>394985507.67</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M66" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="N66" t="n">
+        <v>31843868359.6</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>8.6957</v>
+      </c>
+      <c r="F67" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5367795</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3032175</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2596529</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5628704</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-435646</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="M67" t="n">
+        <v>104.86</v>
+      </c>
+      <c r="N67" t="n">
+        <v>46715264</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>002826.SZ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>易明医药</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9.9819</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="G68" t="n">
+        <v>255471253</v>
+      </c>
+      <c r="H68" t="n">
+        <v>29034886</v>
+      </c>
+      <c r="I68" t="n">
+        <v>69090465</v>
+      </c>
+      <c r="J68" t="n">
+        <v>98125351</v>
+      </c>
+      <c r="K68" t="n">
+        <v>40055579</v>
+      </c>
+      <c r="L68" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M68" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3358378873.98</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>002842.SZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>翔鹭钨业</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9.9978</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2800589265</v>
+      </c>
+      <c r="H69" t="n">
+        <v>226795189</v>
+      </c>
+      <c r="I69" t="n">
+        <v>499021884.5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>725817073.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>272226695.5</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="N69" t="n">
+        <v>13468756551.03</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E70" t="n">
+        <v>5.7143</v>
+      </c>
+      <c r="F70" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3151001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1462294.76</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1322590.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2784885.26</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-139704.26</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="M70" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="N70" t="n">
+        <v>37467106.87</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>002971.SZ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1717412475</v>
+      </c>
+      <c r="H71" t="n">
+        <v>185396107.6</v>
+      </c>
+      <c r="I71" t="n">
+        <v>238223115</v>
+      </c>
+      <c r="J71" t="n">
+        <v>423619222.6</v>
+      </c>
+      <c r="K71" t="n">
+        <v>52827007.4</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M71" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="N71" t="n">
+        <v>11733229277</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>002971.SZ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3897254229</v>
+      </c>
+      <c r="H72" t="n">
+        <v>318705197.88</v>
+      </c>
+      <c r="I72" t="n">
+        <v>566861540.5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>885566738.38</v>
+      </c>
+      <c r="K72" t="n">
+        <v>248156342.62</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M72" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="N72" t="n">
+        <v>11733229277</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>002977.SZ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>*ST天箭</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4.9819</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G73" t="n">
+        <v>16917987</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3374668</v>
+      </c>
+      <c r="I73" t="n">
+        <v>9545725</v>
+      </c>
+      <c r="J73" t="n">
+        <v>12920393</v>
+      </c>
+      <c r="K73" t="n">
+        <v>6171057</v>
+      </c>
+      <c r="L73" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="M73" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1544881400.6</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>002979.SZ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>雷赛智能</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.0035</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2377247296</v>
+      </c>
+      <c r="H74" t="n">
+        <v>339577799.3</v>
+      </c>
+      <c r="I74" t="n">
+        <v>288532999.83</v>
+      </c>
+      <c r="J74" t="n">
+        <v>628110799.13</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-51044799.47</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="M74" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="N74" t="n">
+        <v>14084056266.57</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>111012.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>福新转债</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>381.865</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11.1006</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>7300066640</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1499017850</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1498228810</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2997246660</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-789040</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>123188.SZ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>水羊转债</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>166.169</v>
+      </c>
+      <c r="E76" t="n">
+        <v>18.6074</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>3254776216</v>
+      </c>
+      <c r="H76" t="n">
+        <v>805434127.35</v>
+      </c>
+      <c r="I76" t="n">
+        <v>813473528.78</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1618907656.13</v>
+      </c>
+      <c r="K76" t="n">
+        <v>8039401.43</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M76" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>200016.SZ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>*ST康佳B</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5.7143</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2331433</v>
+      </c>
+      <c r="H77" t="n">
+        <v>854470</v>
+      </c>
+      <c r="I77" t="n">
+        <v>888524</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1742994</v>
+      </c>
+      <c r="K77" t="n">
+        <v>34054</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M77" t="n">
+        <v>74.76000000000001</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4655748441.92</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>300020.SZ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ST银江</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E78" t="n">
+        <v>13.2565</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>423690331</v>
+      </c>
+      <c r="H78" t="n">
+        <v>42010141.04</v>
+      </c>
+      <c r="I78" t="n">
+        <v>45492980</v>
+      </c>
+      <c r="J78" t="n">
+        <v>87503121.04000001</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3482838.96</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M78" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3012673190.37</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E79" t="n">
+        <v>6.6667</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3930472</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1323444</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1789550.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3112994.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>466106.5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M79" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>32057640</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>300044.SZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>*ST赛为</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3.9568</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G80" t="n">
+        <v>732261853</v>
+      </c>
+      <c r="H80" t="n">
+        <v>84411563.11</v>
+      </c>
+      <c r="I80" t="n">
+        <v>60139666.4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>144551229.51</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-24271896.71</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="M80" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4134886013.34</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>300071.SZ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>福石控股</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>19.891</v>
+      </c>
+      <c r="F81" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G81" t="n">
+        <v>708058141</v>
+      </c>
+      <c r="H81" t="n">
+        <v>60405159.8</v>
+      </c>
+      <c r="I81" t="n">
+        <v>111027265</v>
+      </c>
+      <c r="J81" t="n">
+        <v>171432424.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>50622105.2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="M81" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4159543810.4</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>300071.SZ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>福石控股</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>19.891</v>
+      </c>
+      <c r="F82" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="G82" t="n">
+        <v>905716094</v>
+      </c>
+      <c r="H82" t="n">
+        <v>73514656.8</v>
+      </c>
+      <c r="I82" t="n">
+        <v>132568668</v>
+      </c>
+      <c r="J82" t="n">
+        <v>206083324.8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>59054011.2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="M82" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4159543810.4</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>300154.SZ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>瑞凌股份</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="E83" t="n">
+        <v>12.2353</v>
+      </c>
+      <c r="F83" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="G83" t="n">
+        <v>433267403</v>
+      </c>
+      <c r="H83" t="n">
+        <v>100035518.94</v>
+      </c>
+      <c r="I83" t="n">
+        <v>114685584</v>
+      </c>
+      <c r="J83" t="n">
+        <v>214721102.94</v>
+      </c>
+      <c r="K83" t="n">
+        <v>14650065.06</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M83" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3006573462.54</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>300163.SZ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>先锋新材</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E84" t="n">
+        <v>20.0371</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="G84" t="n">
+        <v>213434582</v>
+      </c>
+      <c r="H84" t="n">
+        <v>49191749</v>
+      </c>
+      <c r="I84" t="n">
+        <v>104184347.2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>153376096.2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>54992598.2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="M84" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2954177685.74</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>300345.SZ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>华民股份</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6.2767</v>
+      </c>
+      <c r="F85" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1555201823</v>
+      </c>
+      <c r="H85" t="n">
+        <v>171274262.68</v>
+      </c>
+      <c r="I85" t="n">
+        <v>297745689</v>
+      </c>
+      <c r="J85" t="n">
+        <v>469019951.68</v>
+      </c>
+      <c r="K85" t="n">
+        <v>126471426.32</v>
+      </c>
+      <c r="L85" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="M85" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3572991652.75</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>300694.SZ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>蠡湖股份</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9.8422</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>512240903</v>
+      </c>
+      <c r="H86" t="n">
+        <v>98035792.67</v>
+      </c>
+      <c r="I86" t="n">
+        <v>126293288.21</v>
+      </c>
+      <c r="J86" t="n">
+        <v>224329080.88</v>
+      </c>
+      <c r="K86" t="n">
+        <v>28257495.54</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="M86" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2564553253.08</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>300740.SZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>水羊股份</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="E87" t="n">
+        <v>19.9892</v>
+      </c>
+      <c r="F87" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="G87" t="n">
+        <v>743594650</v>
+      </c>
+      <c r="H87" t="n">
+        <v>133210589.18</v>
+      </c>
+      <c r="I87" t="n">
+        <v>155883552.35</v>
+      </c>
+      <c r="J87" t="n">
+        <v>289094141.53</v>
+      </c>
+      <c r="K87" t="n">
+        <v>22672963.17</v>
+      </c>
+      <c r="L87" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M87" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="N87" t="n">
+        <v>8051749700.27</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>300765.SZ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>石药创新</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="E88" t="n">
+        <v>12.1626</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2075434670</v>
+      </c>
+      <c r="H88" t="n">
+        <v>382916529.71</v>
+      </c>
+      <c r="I88" t="n">
+        <v>363367429.55</v>
+      </c>
+      <c r="J88" t="n">
+        <v>746283959.26</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-19549100.16</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M88" t="n">
+        <v>35.96</v>
+      </c>
+      <c r="N88" t="n">
+        <v>48444410638.56</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>300980.SZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>祥源新材</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6.8922</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1318359478</v>
+      </c>
+      <c r="H89" t="n">
+        <v>251908849.48</v>
+      </c>
+      <c r="I89" t="n">
+        <v>218914532.96</v>
+      </c>
+      <c r="J89" t="n">
+        <v>470823382.44</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-32994316.52</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="M89" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3294438508</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>301008.SZ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>宏昌科技</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="E90" t="n">
+        <v>19.9925</v>
+      </c>
+      <c r="F90" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G90" t="n">
+        <v>527877777</v>
+      </c>
+      <c r="H90" t="n">
+        <v>62883838.21</v>
+      </c>
+      <c r="I90" t="n">
+        <v>122170547.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>185054386.11</v>
+      </c>
+      <c r="K90" t="n">
+        <v>59286709.69</v>
+      </c>
+      <c r="L90" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="M90" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3692408636.62</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>301092.SZ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>争光股份</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="E91" t="n">
+        <v>20.0041</v>
+      </c>
+      <c r="F91" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G91" t="n">
+        <v>540178704</v>
+      </c>
+      <c r="H91" t="n">
+        <v>61742201</v>
+      </c>
+      <c r="I91" t="n">
+        <v>143105487.24</v>
+      </c>
+      <c r="J91" t="n">
+        <v>204847688.24</v>
+      </c>
+      <c r="K91" t="n">
+        <v>81363286.23999999</v>
+      </c>
+      <c r="L91" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="M91" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3589942056.94</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>301092.SZ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>争光股份</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="E92" t="n">
+        <v>20.0041</v>
+      </c>
+      <c r="F92" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G92" t="n">
+        <v>819171437</v>
+      </c>
+      <c r="H92" t="n">
+        <v>94395853.95</v>
+      </c>
+      <c r="I92" t="n">
+        <v>215825073.13</v>
+      </c>
+      <c r="J92" t="n">
+        <v>310220927.08</v>
+      </c>
+      <c r="K92" t="n">
+        <v>121429219.18</v>
+      </c>
+      <c r="L92" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="M92" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3589942056.94</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>301281.SZ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>科源制药</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.1267</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="G93" t="n">
+        <v>983696959</v>
+      </c>
+      <c r="H93" t="n">
+        <v>180179116.25</v>
+      </c>
+      <c r="I93" t="n">
+        <v>173168576.7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>353347692.95</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-7010539.55</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="M93" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="N93" t="n">
+        <v>4118763600</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.2903</v>
+      </c>
+      <c r="F94" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="G94" t="n">
+        <v>340772156</v>
+      </c>
+      <c r="H94" t="n">
+        <v>31246382.05</v>
+      </c>
+      <c r="I94" t="n">
+        <v>28367431.2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>59613813.25</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-2878950.85</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="M94" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1026731110.2</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>301611.SZ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>珂玛科技</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>154.06</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-16.4896</v>
+      </c>
+      <c r="F95" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4090541526</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1006025970</v>
+      </c>
+      <c r="I95" t="n">
+        <v>978105066.7</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1984131036.7</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-27920903.3</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="M95" t="n">
+        <v>48.51</v>
+      </c>
+      <c r="N95" t="n">
+        <v>22582528913.28</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>301696.SZ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>三瑞智能</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>135.05</v>
+      </c>
+      <c r="E96" t="n">
+        <v>14.2362</v>
+      </c>
+      <c r="F96" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1630192479</v>
+      </c>
+      <c r="H96" t="n">
+        <v>180830829.74</v>
+      </c>
+      <c r="I96" t="n">
+        <v>134204167.54</v>
+      </c>
+      <c r="J96" t="n">
+        <v>315034997.28</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-46626662.2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="M96" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4062756957.7</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>301696.SZ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>三瑞智能</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>135.05</v>
+      </c>
+      <c r="E97" t="n">
+        <v>14.2362</v>
+      </c>
+      <c r="F97" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2803961459</v>
+      </c>
+      <c r="H97" t="n">
+        <v>406803091.15</v>
+      </c>
+      <c r="I97" t="n">
+        <v>282054888.95</v>
+      </c>
+      <c r="J97" t="n">
+        <v>688857980.1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-124748202.2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="M97" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N97" t="n">
+        <v>4062756957.7</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>600076.SH</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>康欣新材</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-1.0989</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G98" t="n">
+        <v>635927632</v>
+      </c>
+      <c r="H98" t="n">
+        <v>85808302.51000001</v>
+      </c>
+      <c r="I98" t="n">
+        <v>84277300</v>
+      </c>
+      <c r="J98" t="n">
+        <v>170085602.51</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-1531002.51</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M98" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="N98" t="n">
+        <v>4840356121.2</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>600105.SH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>永鼎股份</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-10.0064</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5514778832</v>
+      </c>
+      <c r="H99" t="n">
+        <v>784345960.1900001</v>
+      </c>
+      <c r="I99" t="n">
+        <v>667207782.16</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1451553742.35</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-117138178.03</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="M99" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="N99" t="n">
+        <v>82178727820.42</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>600119.SH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>*ST长投</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E100" t="n">
+        <v>4.9107</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G100" t="n">
+        <v>48344094</v>
+      </c>
+      <c r="H100" t="n">
+        <v>12223241</v>
+      </c>
+      <c r="I100" t="n">
+        <v>15977510</v>
+      </c>
+      <c r="J100" t="n">
+        <v>28200751</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3754269</v>
+      </c>
+      <c r="L100" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="M100" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1716770739</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>600156.SH</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>华升股份</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E101" t="n">
+        <v>10.0462</v>
+      </c>
+      <c r="F101" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="G101" t="n">
+        <v>144929896</v>
+      </c>
+      <c r="H101" t="n">
+        <v>17451086</v>
+      </c>
+      <c r="I101" t="n">
+        <v>52090038</v>
+      </c>
+      <c r="J101" t="n">
+        <v>69541124</v>
+      </c>
+      <c r="K101" t="n">
+        <v>34638952</v>
+      </c>
+      <c r="L101" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M101" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3832114990.06</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5517</v>
+        <v>5516</v>
       </c>
       <c r="C2" t="n">
-        <v>2219</v>
+        <v>3804</v>
       </c>
       <c r="D2" t="n">
-        <v>3162</v>
+        <v>1628</v>
       </c>
       <c r="E2" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4028.9038</v>
+        <v>4043.6432</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.03</v>
+        <v>0.37</v>
       </c>
       <c r="F2" t="n">
-        <v>15771.84</v>
+        <v>14655.63</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15498.8101</v>
+        <v>15597.5116</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.85</v>
+        <v>0.64</v>
       </c>
       <c r="F3" t="n">
-        <v>18733.51</v>
+        <v>17168.8</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4017.2735</v>
+        <v>4019.9341</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.71</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>8903.73</v>
+        <v>8038.08</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4812.2957</v>
+        <v>4842.1737</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.96</v>
+        <v>0.62</v>
       </c>
       <c r="F5" t="n">
-        <v>10277.97</v>
+        <v>9425.700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1987.291</v>
+        <v>1975.6001</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.7</v>
+        <v>-0.59</v>
       </c>
       <c r="F6" t="n">
-        <v>2149.53</v>
+        <v>1748.47</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8625.3336</v>
+        <v>8620.7886</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.83</v>
+        <v>-0.05</v>
       </c>
       <c r="F7" t="n">
-        <v>7178.67</v>
+        <v>6749.95</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33317.19</v>
+        <v>37621.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37621.03</v>
+        <v>34660.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34660.27</v>
+        <v>33069.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33069.39</v>
+        <v>36189.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36189.44</v>
+        <v>35753.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35753.91</v>
+        <v>35393.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35393.41</v>
+        <v>32938.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32938.2</v>
+        <v>36827.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36827.97</v>
+        <v>34739.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>920510.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>69.54000000000001</v>
+        <v>32.76</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>25.1</v>
       </c>
       <c r="F2" t="n">
-        <v>61.05</v>
+        <v>32.76</v>
       </c>
       <c r="G2" t="n">
-        <v>8.52</v>
+        <v>25.2</v>
       </c>
       <c r="H2" t="n">
-        <v>52.53</v>
+        <v>7.56</v>
       </c>
       <c r="I2" t="n">
-        <v>616.5493</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>244119.92</v>
+        <v>289014.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1478419.21715</v>
+        <v>875181.94008</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>001248.SZ</t>
+          <t>920211.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>30.16</v>
+        <v>158.28</v>
       </c>
       <c r="E3" t="n">
-        <v>21.6</v>
+        <v>123</v>
       </c>
       <c r="F3" t="n">
-        <v>23.95</v>
+        <v>158.28</v>
       </c>
       <c r="G3" t="n">
-        <v>10.11</v>
+        <v>121.76</v>
       </c>
       <c r="H3" t="n">
-        <v>13.84</v>
+        <v>36.52</v>
       </c>
       <c r="I3" t="n">
-        <v>136.8942</v>
+        <v>29.9934</v>
       </c>
       <c r="J3" t="n">
-        <v>7216977.18</v>
+        <v>19947.81</v>
       </c>
       <c r="K3" t="n">
-        <v>17692297.7802</v>
+        <v>294886.75359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920221.BJ</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.8</v>
+        <v>62.01</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62</v>
+        <v>79.36</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7</v>
+        <v>59.8</v>
       </c>
       <c r="F4" t="n">
-        <v>16.62</v>
+        <v>79.36</v>
       </c>
       <c r="G4" t="n">
-        <v>12.79</v>
+        <v>61.05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.83</v>
+        <v>18.31</v>
       </c>
       <c r="I4" t="n">
-        <v>29.9453</v>
+        <v>29.9918</v>
       </c>
       <c r="J4" t="n">
-        <v>105694.77</v>
+        <v>196288.88</v>
       </c>
       <c r="K4" t="n">
-        <v>167469.12622</v>
+        <v>1287092.56683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300163.SZ</t>
+          <t>920002.BJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.41</v>
+        <v>53</v>
       </c>
       <c r="D5" t="n">
-        <v>6.47</v>
+        <v>66.66</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4</v>
+        <v>52.15</v>
       </c>
       <c r="F5" t="n">
-        <v>6.47</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>5.39</v>
+        <v>52.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08</v>
+        <v>13.22</v>
       </c>
       <c r="I5" t="n">
-        <v>20.0371</v>
+        <v>25.1331</v>
       </c>
       <c r="J5" t="n">
-        <v>349299.6</v>
+        <v>56254.51</v>
       </c>
       <c r="K5" t="n">
-        <v>213434.58178</v>
+        <v>345911.14755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>301019.SZ</t>
+          <t>920096.BJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.08</v>
+        <v>42.8</v>
       </c>
       <c r="D6" t="n">
-        <v>21.53</v>
+        <v>51.62</v>
       </c>
       <c r="E6" t="n">
-        <v>17.96</v>
+        <v>42.25</v>
       </c>
       <c r="F6" t="n">
-        <v>21.53</v>
+        <v>51.62</v>
       </c>
       <c r="G6" t="n">
-        <v>17.94</v>
+        <v>42.78</v>
       </c>
       <c r="H6" t="n">
-        <v>3.59</v>
+        <v>8.84</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0111</v>
+        <v>20.6639</v>
       </c>
       <c r="J6" t="n">
-        <v>52195.32</v>
+        <v>44655.49</v>
       </c>
       <c r="K6" t="n">
-        <v>105273.71125</v>
+        <v>214661.93739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301092.SZ</t>
+          <t>301199.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.09</v>
+        <v>17.99</v>
       </c>
       <c r="D7" t="n">
-        <v>58.91</v>
+        <v>21.28</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>17.92</v>
       </c>
       <c r="F7" t="n">
-        <v>58.91</v>
+        <v>21.28</v>
       </c>
       <c r="G7" t="n">
-        <v>49.09</v>
+        <v>17.73</v>
       </c>
       <c r="H7" t="n">
-        <v>9.82</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>20.0041</v>
+        <v>20.0226</v>
       </c>
       <c r="J7" t="n">
-        <v>94221.92</v>
+        <v>103286.37</v>
       </c>
       <c r="K7" t="n">
-        <v>540178.70445</v>
+        <v>207344.82787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688216.SH</t>
+          <t>300580.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42.22</v>
+        <v>21.95</v>
       </c>
       <c r="D8" t="n">
-        <v>51.3</v>
+        <v>25.96</v>
       </c>
       <c r="E8" t="n">
-        <v>42.22</v>
+        <v>21.83</v>
       </c>
       <c r="F8" t="n">
-        <v>51.3</v>
+        <v>25.96</v>
       </c>
       <c r="G8" t="n">
-        <v>42.75</v>
+        <v>21.63</v>
       </c>
       <c r="H8" t="n">
-        <v>8.550000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>20.0185</v>
       </c>
       <c r="J8" t="n">
-        <v>211472.95</v>
+        <v>438355.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1024000.211</v>
+        <v>1078714.72275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300695.SZ</t>
+          <t>300985.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50.5</v>
+        <v>43.1</v>
       </c>
       <c r="D9" t="n">
-        <v>60.37</v>
+        <v>49.67</v>
       </c>
       <c r="E9" t="n">
-        <v>49.89</v>
+        <v>41.78</v>
       </c>
       <c r="F9" t="n">
-        <v>60.37</v>
+        <v>49.67</v>
       </c>
       <c r="G9" t="n">
-        <v>50.31</v>
+        <v>41.39</v>
       </c>
       <c r="H9" t="n">
-        <v>10.06</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>19.996</v>
+        <v>20.0048</v>
       </c>
       <c r="J9" t="n">
-        <v>37394.5</v>
+        <v>80406.84</v>
       </c>
       <c r="K9" t="n">
-        <v>209819.97775</v>
+        <v>369561.81226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>301008.SZ</t>
+          <t>300779.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.1</v>
+        <v>49.39</v>
       </c>
       <c r="D10" t="n">
-        <v>31.93</v>
+        <v>59.27</v>
       </c>
       <c r="E10" t="n">
-        <v>25.88</v>
+        <v>48.9</v>
       </c>
       <c r="F10" t="n">
-        <v>31.93</v>
+        <v>59.27</v>
       </c>
       <c r="G10" t="n">
-        <v>26.61</v>
+        <v>49.39</v>
       </c>
       <c r="H10" t="n">
-        <v>5.32</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>19.9925</v>
+        <v>20.004</v>
       </c>
       <c r="J10" t="n">
-        <v>174160.82</v>
+        <v>129577.06</v>
       </c>
       <c r="K10" t="n">
-        <v>527877.77721</v>
+        <v>724193.57203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300740.SZ</t>
+          <t>300912.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.55</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>22.27</v>
+        <v>28.56</v>
       </c>
       <c r="E11" t="n">
-        <v>18.26</v>
+        <v>24.62</v>
       </c>
       <c r="F11" t="n">
-        <v>22.27</v>
+        <v>28.56</v>
       </c>
       <c r="G11" t="n">
-        <v>18.56</v>
+        <v>23.8</v>
       </c>
       <c r="H11" t="n">
-        <v>3.71</v>
+        <v>4.76</v>
       </c>
       <c r="I11" t="n">
-        <v>19.9892</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>360466.05</v>
+        <v>86276.21000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>743594.65033</v>
+        <v>235836.95164</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301611.SZ</t>
+          <t>688216.SH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>171.45</v>
+        <v>45.79</v>
       </c>
       <c r="D2" t="n">
-        <v>176</v>
+        <v>47.78</v>
       </c>
       <c r="E2" t="n">
-        <v>152</v>
+        <v>41.04</v>
       </c>
       <c r="F2" t="n">
-        <v>154.06</v>
+        <v>41.04</v>
       </c>
       <c r="G2" t="n">
-        <v>184.48</v>
+        <v>51.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-30.42</v>
+        <v>-10.26</v>
       </c>
       <c r="I2" t="n">
-        <v>-16.4896</v>
+        <v>-20</v>
       </c>
       <c r="J2" t="n">
-        <v>254764.65</v>
+        <v>213106.52</v>
       </c>
       <c r="K2" t="n">
-        <v>4090541.52639</v>
+        <v>915749.081</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>688056.SH</t>
+          <t>688096.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>12.23</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>12.33</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>9.93</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>9.93</v>
       </c>
       <c r="G3" t="n">
-        <v>68</v>
+        <v>12.41</v>
       </c>
       <c r="H3" t="n">
-        <v>-11</v>
+        <v>-2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>-16.1765</v>
+        <v>-19.9839</v>
       </c>
       <c r="J3" t="n">
-        <v>48318</v>
+        <v>295457.68</v>
       </c>
       <c r="K3" t="n">
-        <v>288577.04</v>
+        <v>315848.658</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688409.SH</t>
+          <t>688797.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>285</v>
+        <v>648</v>
       </c>
       <c r="D4" t="n">
-        <v>286.05</v>
+        <v>655</v>
       </c>
       <c r="E4" t="n">
-        <v>242</v>
+        <v>538</v>
       </c>
       <c r="F4" t="n">
-        <v>248.07</v>
+        <v>540.1</v>
       </c>
       <c r="G4" t="n">
-        <v>295.34</v>
+        <v>668.01</v>
       </c>
       <c r="H4" t="n">
-        <v>-47.27</v>
+        <v>-127.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-16.0053</v>
+        <v>-19.1479</v>
       </c>
       <c r="J4" t="n">
-        <v>187282.59</v>
+        <v>108526.64</v>
       </c>
       <c r="K4" t="n">
-        <v>4891587.05</v>
+        <v>6289738.191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688361.SH</t>
+          <t>688106.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>405.12</v>
+        <v>45.51</v>
       </c>
       <c r="D5" t="n">
-        <v>412</v>
+        <v>47.3</v>
       </c>
       <c r="E5" t="n">
-        <v>351.33</v>
+        <v>39.92</v>
       </c>
       <c r="F5" t="n">
-        <v>356</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>422</v>
+        <v>47.74</v>
       </c>
       <c r="H5" t="n">
-        <v>-66</v>
+        <v>-7.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-15.6398</v>
+        <v>-16.2128</v>
       </c>
       <c r="J5" t="n">
-        <v>199656.25</v>
+        <v>987892.01</v>
       </c>
       <c r="K5" t="n">
-        <v>7445805.285</v>
+        <v>4165239.407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688260.SH</t>
+          <t>688689.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>115.5</v>
+        <v>78</v>
       </c>
       <c r="D6" t="n">
-        <v>122.88</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>110.89</v>
+        <v>68.03</v>
       </c>
       <c r="G6" t="n">
-        <v>130.7</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>-19.81</v>
+        <v>-11.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-15.1568</v>
+        <v>-14.9625</v>
       </c>
       <c r="J6" t="n">
-        <v>45221.09</v>
+        <v>158489.24</v>
       </c>
       <c r="K6" t="n">
-        <v>526921.286</v>
+        <v>1139494.094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688020.SH</t>
+          <t>300323.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>240</v>
+        <v>19.82</v>
       </c>
       <c r="D7" t="n">
-        <v>260</v>
+        <v>20.39</v>
       </c>
       <c r="E7" t="n">
-        <v>227.29</v>
+        <v>17.9</v>
       </c>
       <c r="F7" t="n">
-        <v>229.26</v>
+        <v>17.95</v>
       </c>
       <c r="G7" t="n">
-        <v>270.08</v>
+        <v>20.69</v>
       </c>
       <c r="H7" t="n">
-        <v>-40.82</v>
+        <v>-2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>-15.114</v>
+        <v>-13.2431</v>
       </c>
       <c r="J7" t="n">
-        <v>56717.15</v>
+        <v>1653695.18</v>
       </c>
       <c r="K7" t="n">
-        <v>1371676.015</v>
+        <v>3081140.02194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688200.SH</t>
+          <t>300655.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>499.98</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="n">
-        <v>513</v>
+        <v>21.7</v>
       </c>
       <c r="E8" t="n">
-        <v>439</v>
+        <v>19.16</v>
       </c>
       <c r="F8" t="n">
-        <v>450</v>
+        <v>19.17</v>
       </c>
       <c r="G8" t="n">
-        <v>529.85</v>
+        <v>21.93</v>
       </c>
       <c r="H8" t="n">
-        <v>-79.84999999999999</v>
+        <v>-2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.0703</v>
+        <v>-12.5855</v>
       </c>
       <c r="J8" t="n">
-        <v>89194</v>
+        <v>1855800.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4211977.561</v>
+        <v>3689235.69411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688120.SH</t>
+          <t>301629.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>307.86</v>
+        <v>398.01</v>
       </c>
       <c r="D9" t="n">
-        <v>312.93</v>
+        <v>401.99</v>
       </c>
       <c r="E9" t="n">
-        <v>275.98</v>
+        <v>360</v>
       </c>
       <c r="F9" t="n">
-        <v>281</v>
+        <v>360.69</v>
       </c>
       <c r="G9" t="n">
-        <v>330</v>
+        <v>407</v>
       </c>
       <c r="H9" t="n">
-        <v>-49</v>
+        <v>-46.31</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.8485</v>
+        <v>-11.3784</v>
       </c>
       <c r="J9" t="n">
-        <v>244151.97</v>
+        <v>22968.45</v>
       </c>
       <c r="K9" t="n">
-        <v>7135138.987</v>
+        <v>872483.81865</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688008.SH</t>
+          <t>301319.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>294.98</v>
+        <v>177.8</v>
       </c>
       <c r="D10" t="n">
-        <v>298.56</v>
+        <v>181.24</v>
       </c>
       <c r="E10" t="n">
-        <v>268.78</v>
+        <v>157</v>
       </c>
       <c r="F10" t="n">
-        <v>269.15</v>
+        <v>157.4</v>
       </c>
       <c r="G10" t="n">
-        <v>315.89</v>
+        <v>176.99</v>
       </c>
       <c r="H10" t="n">
-        <v>-46.74</v>
+        <v>-19.59</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.7963</v>
+        <v>-11.0684</v>
       </c>
       <c r="J10" t="n">
-        <v>899764.08</v>
+        <v>110558.1</v>
       </c>
       <c r="K10" t="n">
-        <v>25642706.037</v>
+        <v>1823089.48516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688233.SH</t>
+          <t>301177.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>224.26</v>
+        <v>29.75</v>
       </c>
       <c r="D11" t="n">
-        <v>233.26</v>
+        <v>30.04</v>
       </c>
       <c r="E11" t="n">
-        <v>196.12</v>
+        <v>26.33</v>
       </c>
       <c r="F11" t="n">
-        <v>203.97</v>
+        <v>26.88</v>
       </c>
       <c r="G11" t="n">
-        <v>238.56</v>
+        <v>30.05</v>
       </c>
       <c r="H11" t="n">
-        <v>-34.59</v>
+        <v>-3.17</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.4995</v>
+        <v>-10.5491</v>
       </c>
       <c r="J11" t="n">
-        <v>241733.41</v>
+        <v>64899.64</v>
       </c>
       <c r="K11" t="n">
-        <v>5121298.325</v>
+        <v>177593.20339</v>
       </c>
     </row>
   </sheetData>
@@ -1819,7 +1819,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1833,37 +1833,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8108</v>
+        <v>9.7561</v>
       </c>
       <c r="F2" t="n">
-        <v>7.52</v>
+        <v>4.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3823929</v>
+        <v>2673076</v>
       </c>
       <c r="H2" t="n">
-        <v>1782158</v>
+        <v>1277293</v>
       </c>
       <c r="I2" t="n">
-        <v>2510516.8</v>
+        <v>1758769.41</v>
       </c>
       <c r="J2" t="n">
-        <v>4292674.8</v>
+        <v>3036062.41</v>
       </c>
       <c r="K2" t="n">
-        <v>728358.8</v>
+        <v>481476.41</v>
       </c>
       <c r="L2" t="n">
-        <v>19.05</v>
+        <v>18.01</v>
       </c>
       <c r="M2" t="n">
-        <v>112.26</v>
+        <v>113.58</v>
       </c>
       <c r="N2" t="n">
-        <v>51778517.88</v>
+        <v>56830080.6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1874,271 +1874,271 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000010.SZ</t>
+          <t>000506.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*ST美丽</t>
+          <t>招金黄金</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.88</v>
+        <v>13.87</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0279</v>
+        <v>9.992100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.33</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>87685390</v>
+        <v>1006370120</v>
       </c>
       <c r="H3" t="n">
-        <v>12935566</v>
+        <v>143682523.88</v>
       </c>
       <c r="I3" t="n">
-        <v>12685470</v>
+        <v>216989710.16</v>
       </c>
       <c r="J3" t="n">
-        <v>25621036</v>
+        <v>360672234.04</v>
       </c>
       <c r="K3" t="n">
-        <v>-250096</v>
+        <v>73307186.28</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.29</v>
+        <v>7.28</v>
       </c>
       <c r="M3" t="n">
-        <v>29.22</v>
+        <v>35.84</v>
       </c>
       <c r="N3" t="n">
-        <v>1641343337.96</v>
+        <v>12881165549.07</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000016.SZ</t>
+          <t>000566.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*ST康佳A</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.54</v>
+        <v>6.14</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9587</v>
+        <v>1.6556</v>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>27.67</v>
       </c>
       <c r="G4" t="n">
-        <v>88453777</v>
+        <v>2194105928</v>
       </c>
       <c r="H4" t="n">
-        <v>18734126</v>
+        <v>279408735.57</v>
       </c>
       <c r="I4" t="n">
-        <v>9842483.52</v>
+        <v>182934819.97</v>
       </c>
       <c r="J4" t="n">
-        <v>28576609.52</v>
+        <v>462343555.54</v>
       </c>
       <c r="K4" t="n">
-        <v>-8891642.48</v>
+        <v>-96473915.59999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-10.05</v>
+        <v>-4.4</v>
       </c>
       <c r="M4" t="n">
-        <v>32.31</v>
+        <v>21.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4655748441.92</v>
+        <v>7961956786.62</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000021.SZ</t>
+          <t>000576.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>甘化科工</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56.03</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.0064</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.19</v>
+        <v>5.63</v>
       </c>
       <c r="G5" t="n">
-        <v>9940689255</v>
+        <v>280654452</v>
       </c>
       <c r="H5" t="n">
-        <v>1186951211.47</v>
+        <v>42205475</v>
       </c>
       <c r="I5" t="n">
-        <v>910927356.24</v>
+        <v>93717574.17</v>
       </c>
       <c r="J5" t="n">
-        <v>2097878567.71</v>
+        <v>135923049.17</v>
       </c>
       <c r="K5" t="n">
-        <v>-276023855.23</v>
+        <v>51512099.17</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.78</v>
+        <v>18.35</v>
       </c>
       <c r="M5" t="n">
-        <v>21.1</v>
+        <v>48.43</v>
       </c>
       <c r="N5" t="n">
-        <v>88199937147.39999</v>
+        <v>3531256224.54</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000078.SZ</t>
+          <t>000592.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST海王</t>
+          <t>平潭发展</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.42</v>
+        <v>6.98</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1852</v>
+        <v>-10.0515</v>
       </c>
       <c r="F6" t="n">
-        <v>1.32</v>
+        <v>13.74</v>
       </c>
       <c r="G6" t="n">
-        <v>128962614</v>
+        <v>1863641622</v>
       </c>
       <c r="H6" t="n">
-        <v>11698963.26</v>
+        <v>401791971.74</v>
       </c>
       <c r="I6" t="n">
-        <v>15800802.86</v>
+        <v>151872444.72</v>
       </c>
       <c r="J6" t="n">
-        <v>27499766.12</v>
+        <v>553664416.46</v>
       </c>
       <c r="K6" t="n">
-        <v>4101839.6</v>
+        <v>-249919527.02</v>
       </c>
       <c r="L6" t="n">
-        <v>3.18</v>
+        <v>-13.41</v>
       </c>
       <c r="M6" t="n">
-        <v>21.32</v>
+        <v>29.71</v>
       </c>
       <c r="N6" t="n">
-        <v>3727806299.68</v>
+        <v>13367345294.02</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000520.SZ</t>
+          <t>000595.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>凤凰航运</t>
+          <t>宝塔实业</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.51</v>
+        <v>6.24</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>10.0529</v>
       </c>
       <c r="F7" t="n">
-        <v>3.72</v>
+        <v>1.34</v>
       </c>
       <c r="G7" t="n">
-        <v>412857738</v>
+        <v>103089945</v>
       </c>
       <c r="H7" t="n">
-        <v>46768648</v>
+        <v>44165823</v>
       </c>
       <c r="I7" t="n">
-        <v>96942469.75</v>
+        <v>42401727</v>
       </c>
       <c r="J7" t="n">
-        <v>143711117.75</v>
+        <v>86567550</v>
       </c>
       <c r="K7" t="n">
-        <v>50173821.75</v>
+        <v>-1764096</v>
       </c>
       <c r="L7" t="n">
-        <v>12.15</v>
+        <v>-1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>34.81</v>
+        <v>83.97</v>
       </c>
       <c r="N7" t="n">
-        <v>4564496382.05</v>
+        <v>7105215723.84</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -2149,51 +2149,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000536.SZ</t>
+          <t>000656.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>华映科技</t>
+          <t>金科股份</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.06</v>
+        <v>1.3</v>
       </c>
       <c r="E8" t="n">
-        <v>10.0271</v>
+        <v>10.1695</v>
       </c>
       <c r="F8" t="n">
-        <v>5.85</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1008732067</v>
+        <v>14173972</v>
       </c>
       <c r="H8" t="n">
-        <v>107278651.17</v>
+        <v>4419295.62</v>
       </c>
       <c r="I8" t="n">
-        <v>231576597.6</v>
+        <v>10516748</v>
       </c>
       <c r="J8" t="n">
-        <v>338855248.77</v>
+        <v>14936043.62</v>
       </c>
       <c r="K8" t="n">
-        <v>124297946.43</v>
+        <v>6097452.38</v>
       </c>
       <c r="L8" t="n">
-        <v>12.32</v>
+        <v>43.02</v>
       </c>
       <c r="M8" t="n">
-        <v>33.59</v>
+        <v>105.38</v>
       </c>
       <c r="N8" t="n">
-        <v>11218084564.96</v>
+        <v>9863553709.1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -2204,546 +2204,546 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000601.SZ</t>
+          <t>000838.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>*ST发展</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.08</v>
+        <v>1.77</v>
       </c>
       <c r="E9" t="n">
-        <v>9.937900000000001</v>
+        <v>4.7337</v>
       </c>
       <c r="F9" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
-        <v>577297658</v>
+        <v>96595868</v>
       </c>
       <c r="H9" t="n">
-        <v>58778929.99</v>
+        <v>10596221</v>
       </c>
       <c r="I9" t="n">
-        <v>111466777.4</v>
+        <v>18108766.44</v>
       </c>
       <c r="J9" t="n">
-        <v>170245707.39</v>
+        <v>28704987.44</v>
       </c>
       <c r="K9" t="n">
-        <v>52687847.41</v>
+        <v>7512545.44</v>
       </c>
       <c r="L9" t="n">
-        <v>9.130000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="M9" t="n">
-        <v>29.49</v>
+        <v>29.72</v>
       </c>
       <c r="N9" t="n">
-        <v>7431299149.92</v>
+        <v>1865165563.35</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000632.SZ</t>
+          <t>000908.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ST三木</t>
+          <t>石药景峰</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.36</v>
+        <v>6.88</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>10.08</v>
       </c>
       <c r="F10" t="n">
-        <v>3.73</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>79588972</v>
+        <v>598622860</v>
       </c>
       <c r="H10" t="n">
-        <v>12915138</v>
+        <v>62693625.42</v>
       </c>
       <c r="I10" t="n">
-        <v>23023335</v>
+        <v>55581591.9</v>
       </c>
       <c r="J10" t="n">
-        <v>35938473</v>
+        <v>118275217.32</v>
       </c>
       <c r="K10" t="n">
-        <v>10108197</v>
+        <v>-7112033.52</v>
       </c>
       <c r="L10" t="n">
-        <v>12.7</v>
+        <v>-1.19</v>
       </c>
       <c r="M10" t="n">
-        <v>45.16</v>
+        <v>19.76</v>
       </c>
       <c r="N10" t="n">
-        <v>1564018196.16</v>
+        <v>6052846158.88</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>000639.SZ</t>
+          <t>000975.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ST西王</t>
+          <t>山金国际</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.22</v>
+        <v>19.84</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1724</v>
+        <v>9.9778</v>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="G11" t="n">
-        <v>70938980</v>
+        <v>3231971328</v>
       </c>
       <c r="H11" t="n">
-        <v>6415296</v>
+        <v>476246385.64</v>
       </c>
       <c r="I11" t="n">
-        <v>10224178</v>
+        <v>723611189.98</v>
       </c>
       <c r="J11" t="n">
-        <v>16639474</v>
+        <v>1199857575.62</v>
       </c>
       <c r="K11" t="n">
-        <v>3808882</v>
+        <v>247364804.34</v>
       </c>
       <c r="L11" t="n">
-        <v>5.37</v>
+        <v>7.65</v>
       </c>
       <c r="M11" t="n">
-        <v>23.46</v>
+        <v>37.12</v>
       </c>
       <c r="N11" t="n">
-        <v>1316900661.84</v>
+        <v>50061028369.28</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000677.SZ</t>
+          <t>001317.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ST海龙</t>
+          <t>三羊马</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.59</v>
+        <v>48.43</v>
       </c>
       <c r="E12" t="n">
-        <v>5.298</v>
+        <v>9.9932</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1</v>
+        <v>4.84</v>
       </c>
       <c r="G12" t="n">
-        <v>134429148</v>
+        <v>429982738</v>
       </c>
       <c r="H12" t="n">
-        <v>13431283</v>
+        <v>50563819</v>
       </c>
       <c r="I12" t="n">
-        <v>17264427</v>
+        <v>77136111</v>
       </c>
       <c r="J12" t="n">
-        <v>30695710</v>
+        <v>127699930</v>
       </c>
       <c r="K12" t="n">
-        <v>3833144</v>
+        <v>26572292</v>
       </c>
       <c r="L12" t="n">
-        <v>2.85</v>
+        <v>6.18</v>
       </c>
       <c r="M12" t="n">
-        <v>22.83</v>
+        <v>29.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1373724937.32</v>
+        <v>4139865315.89</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>000698.SZ</t>
+          <t>001399.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ST沈化</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.29</v>
+        <v>42.14</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1118</v>
+        <v>-9.995699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.22</v>
+        <v>6.15</v>
       </c>
       <c r="G13" t="n">
-        <v>56419265</v>
+        <v>1146305084</v>
       </c>
       <c r="H13" t="n">
-        <v>11315638</v>
+        <v>105064640.14</v>
       </c>
       <c r="I13" t="n">
-        <v>8580403</v>
+        <v>125822126.54</v>
       </c>
       <c r="J13" t="n">
-        <v>19896041</v>
+        <v>230886766.68</v>
       </c>
       <c r="K13" t="n">
-        <v>-2735235</v>
+        <v>20757486.4</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.85</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>35.26</v>
+        <v>20.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2585000359.55</v>
+        <v>18144082044.34</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>000700.SZ</t>
+          <t>002020.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>京新药业</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.87</v>
+        <v>15.19</v>
       </c>
       <c r="E14" t="n">
-        <v>9.9739</v>
+        <v>3.6153</v>
       </c>
       <c r="F14" t="n">
-        <v>12.39</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1877232158</v>
+        <v>1439720588</v>
       </c>
       <c r="H14" t="n">
-        <v>202364015.72</v>
+        <v>189451248.9</v>
       </c>
       <c r="I14" t="n">
-        <v>346888543.17</v>
+        <v>183387704.99</v>
       </c>
       <c r="J14" t="n">
-        <v>549252558.89</v>
+        <v>372838953.89</v>
       </c>
       <c r="K14" t="n">
-        <v>144524527.45</v>
+        <v>-6063543.91</v>
       </c>
       <c r="L14" t="n">
-        <v>7.7</v>
+        <v>-0.42</v>
       </c>
       <c r="M14" t="n">
-        <v>29.26</v>
+        <v>25.9</v>
       </c>
       <c r="N14" t="n">
-        <v>15486919612.43</v>
+        <v>10997079008.65</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>000700.SZ</t>
+          <t>002056.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>模塑科技</t>
+          <t>横店东磁</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.87</v>
+        <v>32.82</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9739</v>
+        <v>7.045</v>
       </c>
       <c r="F15" t="n">
-        <v>12.39</v>
+        <v>7.74</v>
       </c>
       <c r="G15" t="n">
-        <v>4293695300</v>
+        <v>4065511535</v>
       </c>
       <c r="H15" t="n">
-        <v>395607583.17</v>
+        <v>468170764.44</v>
       </c>
       <c r="I15" t="n">
-        <v>496835277.72</v>
+        <v>1018191968.29</v>
       </c>
       <c r="J15" t="n">
-        <v>892442860.89</v>
+        <v>1486362732.73</v>
       </c>
       <c r="K15" t="n">
-        <v>101227694.55</v>
+        <v>550021203.85</v>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>13.53</v>
       </c>
       <c r="M15" t="n">
-        <v>20.78</v>
+        <v>36.56</v>
       </c>
       <c r="N15" t="n">
-        <v>15486919612.43</v>
+        <v>53333537407.38</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>000711.SZ</t>
+          <t>002106.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ST京蓝</t>
+          <t>莱宝高科</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.01</v>
+        <v>14.63</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0314</v>
+        <v>-9.969200000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>8.58</v>
       </c>
       <c r="G16" t="n">
-        <v>256948796</v>
+        <v>898007715</v>
       </c>
       <c r="H16" t="n">
-        <v>51184522.48</v>
+        <v>72619114.23</v>
       </c>
       <c r="I16" t="n">
-        <v>23494445.96</v>
+        <v>80227195</v>
       </c>
       <c r="J16" t="n">
-        <v>74678968.44</v>
+        <v>152846309.23</v>
       </c>
       <c r="K16" t="n">
-        <v>-27690076.52</v>
+        <v>7608080.77</v>
       </c>
       <c r="L16" t="n">
-        <v>-10.78</v>
+        <v>0.85</v>
       </c>
       <c r="M16" t="n">
-        <v>29.06</v>
+        <v>17.02</v>
       </c>
       <c r="N16" t="n">
-        <v>11930250299.85</v>
+        <v>10312723077.58</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>000725.SZ</t>
+          <t>002122.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>京东方A</t>
+          <t>ST汇洲</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9.1</v>
+        <v>2.55</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7628</v>
+        <v>4.9383</v>
       </c>
       <c r="F17" t="n">
-        <v>16.01</v>
+        <v>1.34</v>
       </c>
       <c r="G17" t="n">
-        <v>49342409554</v>
+        <v>115625768</v>
       </c>
       <c r="H17" t="n">
-        <v>5576922037.19</v>
+        <v>13240552</v>
       </c>
       <c r="I17" t="n">
-        <v>7359613319.24</v>
+        <v>15850516</v>
       </c>
       <c r="J17" t="n">
-        <v>12936535356.43</v>
+        <v>29091068</v>
       </c>
       <c r="K17" t="n">
-        <v>1782691282.05</v>
+        <v>2609964</v>
       </c>
       <c r="L17" t="n">
-        <v>3.61</v>
+        <v>2.26</v>
       </c>
       <c r="M17" t="n">
-        <v>26.22</v>
+        <v>25.16</v>
       </c>
       <c r="N17" t="n">
-        <v>325845790718.76</v>
+        <v>5068685905.65</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>000820.SZ</t>
+          <t>002193.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>*ST节能</t>
+          <t>ST如意</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4.59</v>
       </c>
       <c r="E18" t="n">
-        <v>4.8951</v>
+        <v>5.0343</v>
       </c>
       <c r="F18" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>26926680</v>
+        <v>58125873</v>
       </c>
       <c r="H18" t="n">
-        <v>10134803</v>
+        <v>14376781</v>
       </c>
       <c r="I18" t="n">
-        <v>7337394</v>
+        <v>12818356</v>
       </c>
       <c r="J18" t="n">
-        <v>17472197</v>
+        <v>27195137</v>
       </c>
       <c r="K18" t="n">
-        <v>-2797409</v>
+        <v>-1558425</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.39</v>
+        <v>-2.68</v>
       </c>
       <c r="M18" t="n">
-        <v>64.89</v>
+        <v>46.79</v>
       </c>
       <c r="N18" t="n">
-        <v>890900631</v>
+        <v>1201267489.5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2754,51 +2754,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>000821.SZ</t>
+          <t>002199.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ST京机</t>
+          <t>*ST东晶</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.039999999999999</v>
+        <v>12.89</v>
       </c>
       <c r="E19" t="n">
-        <v>4.9608</v>
+        <v>4.9674</v>
       </c>
       <c r="F19" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="G19" t="n">
-        <v>315367220</v>
+        <v>151871152</v>
       </c>
       <c r="H19" t="n">
-        <v>58510567.8</v>
+        <v>48043056</v>
       </c>
       <c r="I19" t="n">
-        <v>46160388</v>
+        <v>35881101</v>
       </c>
       <c r="J19" t="n">
-        <v>104670955.8</v>
+        <v>83924157</v>
       </c>
       <c r="K19" t="n">
-        <v>-12350179.8</v>
+        <v>-12161955</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.92</v>
+        <v>-8.01</v>
       </c>
       <c r="M19" t="n">
-        <v>33.19</v>
+        <v>55.26</v>
       </c>
       <c r="N19" t="n">
-        <v>4861392142.56</v>
+        <v>2976714678.77</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2809,546 +2809,546 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>000909.SZ</t>
+          <t>002235.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>*ST数源</t>
+          <t>安妮股份</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.15</v>
+        <v>9.31</v>
       </c>
       <c r="E20" t="n">
-        <v>5.0633</v>
+        <v>8.0046</v>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>10.85</v>
       </c>
       <c r="G20" t="n">
-        <v>35374508</v>
+        <v>1006166891</v>
       </c>
       <c r="H20" t="n">
-        <v>7062882</v>
+        <v>141385423.28</v>
       </c>
       <c r="I20" t="n">
-        <v>11866869</v>
+        <v>211966338.82</v>
       </c>
       <c r="J20" t="n">
-        <v>18929751</v>
+        <v>353351762.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4803987</v>
+        <v>70580915.54000001</v>
       </c>
       <c r="L20" t="n">
-        <v>13.58</v>
+        <v>7.01</v>
       </c>
       <c r="M20" t="n">
-        <v>53.51</v>
+        <v>35.12</v>
       </c>
       <c r="N20" t="n">
-        <v>1816498865.5</v>
+        <v>5153813991.62</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>000972.SZ</t>
+          <t>002294.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中基健康</t>
+          <t>信立泰</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3.69</v>
+        <v>40.08</v>
       </c>
       <c r="E21" t="n">
-        <v>10.1493</v>
+        <v>9.989000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.79</v>
+        <v>5.82</v>
       </c>
       <c r="G21" t="n">
-        <v>92018130</v>
+        <v>2505207346</v>
       </c>
       <c r="H21" t="n">
-        <v>16752708.25</v>
+        <v>213350700.46</v>
       </c>
       <c r="I21" t="n">
-        <v>22639167.22</v>
+        <v>320285063.46</v>
       </c>
       <c r="J21" t="n">
-        <v>39391875.47</v>
+        <v>533635763.92</v>
       </c>
       <c r="K21" t="n">
-        <v>5886458.97</v>
+        <v>106934363</v>
       </c>
       <c r="L21" t="n">
-        <v>6.4</v>
+        <v>4.27</v>
       </c>
       <c r="M21" t="n">
-        <v>42.81</v>
+        <v>21.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2846036406.51</v>
+        <v>44671794698.88</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>000988.SZ</t>
+          <t>002294.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>信立泰</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>156.2</v>
+        <v>40.08</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.9971</v>
+        <v>9.989000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>8.050000000000001</v>
+        <v>5.82</v>
       </c>
       <c r="G22" t="n">
-        <v>12989369286</v>
+        <v>6366586753</v>
       </c>
       <c r="H22" t="n">
-        <v>1923021942.62</v>
+        <v>586166054.61</v>
       </c>
       <c r="I22" t="n">
-        <v>1014027076.84</v>
+        <v>734529981.53</v>
       </c>
       <c r="J22" t="n">
-        <v>2937049019.46</v>
+        <v>1320696036.14</v>
       </c>
       <c r="K22" t="n">
-        <v>-908994865.78</v>
+        <v>148363926.92</v>
       </c>
       <c r="L22" t="n">
-        <v>-7</v>
+        <v>2.33</v>
       </c>
       <c r="M22" t="n">
-        <v>22.61</v>
+        <v>20.74</v>
       </c>
       <c r="N22" t="n">
-        <v>156978759623.4</v>
+        <v>44671794698.88</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>001237.SZ</t>
+          <t>002306.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>惠康科技</t>
+          <t>ST云网</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69.01000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6854</v>
+        <v>3.4826</v>
       </c>
       <c r="F23" t="n">
-        <v>26.92</v>
+        <v>1.35</v>
       </c>
       <c r="G23" t="n">
-        <v>674559182</v>
+        <v>76489359</v>
       </c>
       <c r="H23" t="n">
-        <v>107419598.29</v>
+        <v>9076501</v>
       </c>
       <c r="I23" t="n">
-        <v>64020613.75</v>
+        <v>15992458</v>
       </c>
       <c r="J23" t="n">
-        <v>171440212.04</v>
+        <v>25068959</v>
       </c>
       <c r="K23" t="n">
-        <v>-43398984.54</v>
+        <v>6915957</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.43</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>25.42</v>
+        <v>32.77</v>
       </c>
       <c r="N23" t="n">
-        <v>2405414492.28</v>
+        <v>1690392169.44</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>001248.SZ</t>
+          <t>002353.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>华润新能源</t>
+          <t>杰瑞股份</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.95</v>
+        <v>161.46</v>
       </c>
       <c r="E24" t="n">
-        <v>136.8942</v>
+        <v>10.0014</v>
       </c>
       <c r="F24" t="n">
-        <v>67.93000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="G24" t="n">
-        <v>17692297780</v>
+        <v>2566550608</v>
       </c>
       <c r="H24" t="n">
-        <v>585036255.08</v>
+        <v>479458956.27</v>
       </c>
       <c r="I24" t="n">
-        <v>1469066431.83</v>
+        <v>772283403.35</v>
       </c>
       <c r="J24" t="n">
-        <v>2054102686.91</v>
+        <v>1251742359.62</v>
       </c>
       <c r="K24" t="n">
-        <v>884030176.75</v>
+        <v>292824447.08</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>11.41</v>
       </c>
       <c r="M24" t="n">
-        <v>11.61</v>
+        <v>48.77</v>
       </c>
       <c r="N24" t="n">
-        <v>25444570794.45</v>
+        <v>111575094777.9</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>无价格涨跌幅限制的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>001313.SZ</t>
+          <t>002354.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>粤海饲料</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.58</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>-9.381</v>
       </c>
       <c r="F25" t="n">
-        <v>4.72</v>
+        <v>38.07</v>
       </c>
       <c r="G25" t="n">
-        <v>467684160</v>
+        <v>5895329300</v>
       </c>
       <c r="H25" t="n">
-        <v>53530282</v>
+        <v>692234133.8200001</v>
       </c>
       <c r="I25" t="n">
-        <v>114534505</v>
+        <v>842465328.16</v>
       </c>
       <c r="J25" t="n">
-        <v>168064787</v>
+        <v>1534699461.98</v>
       </c>
       <c r="K25" t="n">
-        <v>61004223</v>
+        <v>150231194.34</v>
       </c>
       <c r="L25" t="n">
-        <v>13.04</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>35.94</v>
+        <v>26.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5998734893.58</v>
+        <v>15232750709.23</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>001358.SZ</t>
+          <t>002384.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>兴欣新材</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.36</v>
+        <v>232.73</v>
       </c>
       <c r="E26" t="n">
-        <v>4.1881</v>
+        <v>4.9847</v>
       </c>
       <c r="F26" t="n">
-        <v>10.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>396725241</v>
+        <v>27821158389</v>
       </c>
       <c r="H26" t="n">
-        <v>72077188.78</v>
+        <v>3137110889.15</v>
       </c>
       <c r="I26" t="n">
-        <v>88092553.52</v>
+        <v>4262145497.45</v>
       </c>
       <c r="J26" t="n">
-        <v>160169742.3</v>
+        <v>7399256386.6</v>
       </c>
       <c r="K26" t="n">
-        <v>16015364.74</v>
+        <v>1125034608.3</v>
       </c>
       <c r="L26" t="n">
         <v>4.04</v>
       </c>
       <c r="M26" t="n">
-        <v>40.37</v>
+        <v>26.6</v>
       </c>
       <c r="N26" t="n">
-        <v>1409392087.72</v>
+        <v>322638654593.79</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002005.SZ</t>
+          <t>002407.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ST德豪</t>
+          <t>多氟多</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.43</v>
+        <v>49.34</v>
       </c>
       <c r="E27" t="n">
-        <v>5.1948</v>
+        <v>-9.9964</v>
       </c>
       <c r="F27" t="n">
-        <v>0.35</v>
+        <v>22.12</v>
       </c>
       <c r="G27" t="n">
-        <v>31297695</v>
+        <v>11962936166</v>
       </c>
       <c r="H27" t="n">
-        <v>5792419</v>
+        <v>1641684265.01</v>
       </c>
       <c r="I27" t="n">
-        <v>11114781</v>
+        <v>1550329683.81</v>
       </c>
       <c r="J27" t="n">
-        <v>16907200</v>
+        <v>3192013948.82</v>
       </c>
       <c r="K27" t="n">
-        <v>5322362</v>
+        <v>-91354581.2</v>
       </c>
       <c r="L27" t="n">
-        <v>17.01</v>
+        <v>-0.76</v>
       </c>
       <c r="M27" t="n">
-        <v>54.02</v>
+        <v>26.68</v>
       </c>
       <c r="N27" t="n">
-        <v>4257297446.94</v>
+        <v>53226380802.3</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002102.SZ</t>
+          <t>002422.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ST能特</t>
+          <t>科伦药业</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.36</v>
+        <v>47.98</v>
       </c>
       <c r="E28" t="n">
-        <v>4.8889</v>
+        <v>7.2179</v>
       </c>
       <c r="F28" t="n">
-        <v>0.71</v>
+        <v>4.13</v>
       </c>
       <c r="G28" t="n">
-        <v>75742759</v>
+        <v>6914975974</v>
       </c>
       <c r="H28" t="n">
-        <v>10445955.95</v>
+        <v>1130735839.31</v>
       </c>
       <c r="I28" t="n">
-        <v>15917171</v>
+        <v>604224972.96</v>
       </c>
       <c r="J28" t="n">
-        <v>26363126.95</v>
+        <v>1734960812.27</v>
       </c>
       <c r="K28" t="n">
-        <v>5471215.05</v>
+        <v>-526510866.35</v>
       </c>
       <c r="L28" t="n">
-        <v>7.22</v>
+        <v>-7.61</v>
       </c>
       <c r="M28" t="n">
-        <v>34.81</v>
+        <v>25.09</v>
       </c>
       <c r="N28" t="n">
-        <v>5127855752.24</v>
+        <v>62307420121.18</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002109.SZ</t>
+          <t>002431.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ST兴化</t>
+          <t>ST棕榈</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.66</v>
+        <v>1.36</v>
       </c>
       <c r="E29" t="n">
-        <v>5.1383</v>
+        <v>3.0303</v>
       </c>
       <c r="F29" t="n">
-        <v>0.37</v>
+        <v>2.26</v>
       </c>
       <c r="G29" t="n">
-        <v>27743358</v>
+        <v>121208437</v>
       </c>
       <c r="H29" t="n">
-        <v>4519631</v>
+        <v>16334332.96</v>
       </c>
       <c r="I29" t="n">
-        <v>7854273</v>
+        <v>12735827.65</v>
       </c>
       <c r="J29" t="n">
-        <v>12373904</v>
+        <v>29070160.61</v>
       </c>
       <c r="K29" t="n">
-        <v>3334642</v>
+        <v>-3598505.31</v>
       </c>
       <c r="L29" t="n">
-        <v>12.02</v>
+        <v>-2.97</v>
       </c>
       <c r="M29" t="n">
-        <v>44.6</v>
+        <v>23.98</v>
       </c>
       <c r="N29" t="n">
-        <v>3394877803.66</v>
+        <v>2451270480.4</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3359,106 +3359,106 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002167.SZ</t>
+          <t>002472.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>东方锆业</t>
+          <t>双环传动</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26.05</v>
+        <v>47.01</v>
       </c>
       <c r="E30" t="n">
-        <v>7.29</v>
+        <v>9.990600000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>26.16</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>5096818540</v>
+        <v>3412149027</v>
       </c>
       <c r="H30" t="n">
-        <v>884148407.2</v>
+        <v>464373642.98</v>
       </c>
       <c r="I30" t="n">
-        <v>816346174.41</v>
+        <v>784190730.65</v>
       </c>
       <c r="J30" t="n">
-        <v>1700494581.61</v>
+        <v>1248564373.63</v>
       </c>
       <c r="K30" t="n">
-        <v>-67802232.79000001</v>
+        <v>319817087.67</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.33</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>33.36</v>
+        <v>36.59</v>
       </c>
       <c r="N30" t="n">
-        <v>19764472686.15</v>
+        <v>35191468155.66</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002167.SZ</t>
+          <t>002496.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>东方锆业</t>
+          <t>辉丰股份</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.05</v>
+        <v>2.23</v>
       </c>
       <c r="E31" t="n">
-        <v>7.29</v>
+        <v>9.8522</v>
       </c>
       <c r="F31" t="n">
-        <v>26.16</v>
+        <v>8.84</v>
       </c>
       <c r="G31" t="n">
-        <v>9062906869</v>
+        <v>564417465</v>
       </c>
       <c r="H31" t="n">
-        <v>1136692120.15</v>
+        <v>81000062.90000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1327686238.62</v>
+        <v>78712028.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2464378358.77</v>
+        <v>159712091.7</v>
       </c>
       <c r="K31" t="n">
-        <v>190994118.47</v>
+        <v>-2288034.1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.11</v>
+        <v>-0.41</v>
       </c>
       <c r="M31" t="n">
-        <v>27.19</v>
+        <v>28.3</v>
       </c>
       <c r="N31" t="n">
-        <v>19764472686.15</v>
+        <v>2634184155</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3469,216 +3469,216 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002175.SZ</t>
+          <t>002536.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>*ST东智</t>
+          <t>飞龙股份</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.49</v>
+        <v>51.96</v>
       </c>
       <c r="E32" t="n">
-        <v>5.0633</v>
+        <v>9.9915</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>4577568</v>
+        <v>2577109516</v>
       </c>
       <c r="H32" t="n">
-        <v>1682631</v>
+        <v>313276269.51</v>
       </c>
       <c r="I32" t="n">
-        <v>4577568</v>
+        <v>484340194.22</v>
       </c>
       <c r="J32" t="n">
-        <v>6260199</v>
+        <v>797616463.73</v>
       </c>
       <c r="K32" t="n">
-        <v>2894937</v>
+        <v>171063924.71</v>
       </c>
       <c r="L32" t="n">
-        <v>63.24</v>
+        <v>6.64</v>
       </c>
       <c r="M32" t="n">
-        <v>136.76</v>
+        <v>30.95</v>
       </c>
       <c r="N32" t="n">
-        <v>3179184010.23</v>
+        <v>28287079857</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002198.SZ</t>
+          <t>002559.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ST嘉应</t>
+          <t>亚威股份</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3.34</v>
+        <v>14.24</v>
       </c>
       <c r="E33" t="n">
-        <v>5.0314</v>
+        <v>-7.4122</v>
       </c>
       <c r="F33" t="n">
-        <v>0.79</v>
+        <v>32.95</v>
       </c>
       <c r="G33" t="n">
-        <v>43990809</v>
+        <v>2374709604</v>
       </c>
       <c r="H33" t="n">
-        <v>6367195</v>
+        <v>416837558.23</v>
       </c>
       <c r="I33" t="n">
-        <v>17706257</v>
+        <v>482816604.57</v>
       </c>
       <c r="J33" t="n">
-        <v>24073452</v>
+        <v>899654162.8</v>
       </c>
       <c r="K33" t="n">
-        <v>11339062</v>
+        <v>65979046.34</v>
       </c>
       <c r="L33" t="n">
-        <v>25.78</v>
+        <v>2.78</v>
       </c>
       <c r="M33" t="n">
-        <v>54.72</v>
+        <v>37.88</v>
       </c>
       <c r="N33" t="n">
-        <v>1694983861.32</v>
+        <v>7177031328.16</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002273.SZ</t>
+          <t>002584.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>西陇科学</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>39.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0256</v>
+        <v>-9.545500000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>19.08</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
-        <v>12472092406</v>
+        <v>1238747424</v>
       </c>
       <c r="H34" t="n">
-        <v>2269444447.68</v>
+        <v>189570209</v>
       </c>
       <c r="I34" t="n">
-        <v>2086004798.9</v>
+        <v>175000996</v>
       </c>
       <c r="J34" t="n">
-        <v>4355449246.58</v>
+        <v>364571205</v>
       </c>
       <c r="K34" t="n">
-        <v>-183439648.78</v>
+        <v>-14569213</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.47</v>
+        <v>-1.18</v>
       </c>
       <c r="M34" t="n">
-        <v>34.92</v>
+        <v>29.43</v>
       </c>
       <c r="N34" t="n">
-        <v>53148298348.58</v>
+        <v>4660843943.65</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002305.SZ</t>
+          <t>002598.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>*ST南置</t>
+          <t>ST章鼓</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.91</v>
+        <v>6.99</v>
       </c>
       <c r="E35" t="n">
-        <v>4.9451</v>
+        <v>4.955</v>
       </c>
       <c r="F35" t="n">
-        <v>0.59</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>46745190</v>
+        <v>113800176</v>
       </c>
       <c r="H35" t="n">
-        <v>10237393</v>
+        <v>26275704.9</v>
       </c>
       <c r="I35" t="n">
-        <v>10072967</v>
+        <v>24433039.86</v>
       </c>
       <c r="J35" t="n">
-        <v>20310360</v>
+        <v>50708744.76</v>
       </c>
       <c r="K35" t="n">
-        <v>-164426</v>
+        <v>-1842665.04</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.35</v>
+        <v>-1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>43.45</v>
+        <v>44.56</v>
       </c>
       <c r="N35" t="n">
-        <v>3312137257.16</v>
+        <v>2002844867.76</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3689,161 +3689,161 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>002326.SZ</t>
+          <t>002674.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>永太科技</t>
+          <t>兴业科技</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28</v>
+        <v>29.03</v>
       </c>
       <c r="E36" t="n">
-        <v>7.6095</v>
+        <v>2.7611</v>
       </c>
       <c r="F36" t="n">
-        <v>26.42</v>
+        <v>14.2</v>
       </c>
       <c r="G36" t="n">
-        <v>5988741380</v>
+        <v>1163122299</v>
       </c>
       <c r="H36" t="n">
-        <v>347090311.65</v>
+        <v>83052612.3</v>
       </c>
       <c r="I36" t="n">
-        <v>714514160.66</v>
+        <v>58980431.31</v>
       </c>
       <c r="J36" t="n">
-        <v>1061604472.31</v>
+        <v>142033043.61</v>
       </c>
       <c r="K36" t="n">
-        <v>367423849.01</v>
+        <v>-24072180.99</v>
       </c>
       <c r="L36" t="n">
-        <v>6.14</v>
+        <v>-2.07</v>
       </c>
       <c r="M36" t="n">
-        <v>17.73</v>
+        <v>12.21</v>
       </c>
       <c r="N36" t="n">
-        <v>22628453176</v>
+        <v>8493122817.56</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>002326.SZ</t>
+          <t>002689.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>永太科技</t>
+          <t>ST远智</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>2.81</v>
       </c>
       <c r="E37" t="n">
-        <v>7.6095</v>
+        <v>3.69</v>
       </c>
       <c r="F37" t="n">
-        <v>26.42</v>
+        <v>1.42</v>
       </c>
       <c r="G37" t="n">
-        <v>7481831383</v>
+        <v>107256188</v>
       </c>
       <c r="H37" t="n">
-        <v>451250592.49</v>
+        <v>25157819.53</v>
       </c>
       <c r="I37" t="n">
-        <v>932521667.99</v>
+        <v>21917640.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1383772260.48</v>
+        <v>47075459.63</v>
       </c>
       <c r="K37" t="n">
-        <v>481271075.5</v>
+        <v>-3240179.43</v>
       </c>
       <c r="L37" t="n">
-        <v>6.43</v>
+        <v>-3.02</v>
       </c>
       <c r="M37" t="n">
-        <v>18.5</v>
+        <v>43.89</v>
       </c>
       <c r="N37" t="n">
-        <v>22628453176</v>
+        <v>2930581382.44</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>002360.SZ</t>
+          <t>002694.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ST同德</t>
+          <t>*ST顾地</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.19</v>
+        <v>2.31</v>
       </c>
       <c r="E38" t="n">
-        <v>5.0607</v>
+        <v>3.125</v>
       </c>
       <c r="F38" t="n">
-        <v>2.15</v>
+        <v>0.64</v>
       </c>
       <c r="G38" t="n">
-        <v>45671842</v>
+        <v>32769533</v>
       </c>
       <c r="H38" t="n">
-        <v>13687810</v>
+        <v>8864382</v>
       </c>
       <c r="I38" t="n">
-        <v>9743857</v>
+        <v>9861106.279999999</v>
       </c>
       <c r="J38" t="n">
-        <v>23431667</v>
+        <v>18725488.28</v>
       </c>
       <c r="K38" t="n">
-        <v>-3943953</v>
+        <v>996724.28</v>
       </c>
       <c r="L38" t="n">
-        <v>-8.640000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="M38" t="n">
-        <v>51.3</v>
+        <v>57.14</v>
       </c>
       <c r="N38" t="n">
-        <v>1689447336.42</v>
+        <v>1660422282.75</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3854,161 +3854,161 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>002371.SZ</t>
+          <t>002726.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北方华创</t>
+          <t>ST龙大</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>841.8200000000001</v>
+        <v>1.34</v>
       </c>
       <c r="E39" t="n">
-        <v>-10.0004</v>
+        <v>4.6875</v>
       </c>
       <c r="F39" t="n">
-        <v>1.67</v>
+        <v>6.79</v>
       </c>
       <c r="G39" t="n">
-        <v>10345919579</v>
+        <v>291091032</v>
       </c>
       <c r="H39" t="n">
-        <v>2642488580.43</v>
+        <v>50311813.76</v>
       </c>
       <c r="I39" t="n">
-        <v>1972240123.11</v>
+        <v>20467034.68</v>
       </c>
       <c r="J39" t="n">
-        <v>4614728703.54</v>
+        <v>70778848.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-670248457.3200001</v>
+        <v>-29844779.08</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.48</v>
+        <v>-10.25</v>
       </c>
       <c r="M39" t="n">
-        <v>44.6</v>
+        <v>24.32</v>
       </c>
       <c r="N39" t="n">
-        <v>610411972243.36</v>
+        <v>1555323588.3</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>002747.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>221.68</v>
+        <v>44.77</v>
       </c>
       <c r="E40" t="n">
-        <v>-9.999599999999999</v>
+        <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>6.09</v>
+        <v>16.2</v>
       </c>
       <c r="G40" t="n">
-        <v>18849580300</v>
+        <v>5508068594</v>
       </c>
       <c r="H40" t="n">
-        <v>2802768700.57</v>
+        <v>878697717.63</v>
       </c>
       <c r="I40" t="n">
-        <v>2135585325.64</v>
+        <v>679225612.22</v>
       </c>
       <c r="J40" t="n">
-        <v>4938354026.21</v>
+        <v>1557923329.85</v>
       </c>
       <c r="K40" t="n">
-        <v>-667183374.9299999</v>
+        <v>-199472105.41</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.54</v>
+        <v>-3.62</v>
       </c>
       <c r="M40" t="n">
-        <v>26.2</v>
+        <v>28.28</v>
       </c>
       <c r="N40" t="n">
-        <v>307319799554.64</v>
+        <v>35028255195.56</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>002396.SZ</t>
+          <t>002772.SZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>众兴菌业</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21.27</v>
+        <v>13.88</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8535</v>
+        <v>8.4375</v>
       </c>
       <c r="F41" t="n">
-        <v>11.12</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>3080229188</v>
+        <v>825013069</v>
       </c>
       <c r="H41" t="n">
-        <v>291114214.3</v>
+        <v>168827549.21</v>
       </c>
       <c r="I41" t="n">
-        <v>646773030.2</v>
+        <v>152660179.67</v>
       </c>
       <c r="J41" t="n">
-        <v>937887244.5</v>
+        <v>321487728.88</v>
       </c>
       <c r="K41" t="n">
-        <v>355658815.9</v>
+        <v>-16167369.54</v>
       </c>
       <c r="L41" t="n">
-        <v>11.55</v>
+        <v>-1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>30.45</v>
+        <v>38.97</v>
       </c>
       <c r="N41" t="n">
-        <v>16110219304.62</v>
+        <v>5158316382.76</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4019,106 +4019,106 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>002403.SZ</t>
+          <t>002808.SZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>爱仕达</t>
+          <t>恒久退</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.22</v>
+        <v>0.24</v>
       </c>
       <c r="E42" t="n">
-        <v>4.1794</v>
+        <v>-4</v>
       </c>
       <c r="F42" t="n">
-        <v>5.01</v>
+        <v>5.63</v>
       </c>
       <c r="G42" t="n">
-        <v>315739805</v>
+        <v>2534475</v>
       </c>
       <c r="H42" t="n">
-        <v>69712387.5</v>
+        <v>1070199.96</v>
       </c>
       <c r="I42" t="n">
-        <v>67715530.7</v>
+        <v>1110356.36</v>
       </c>
       <c r="J42" t="n">
-        <v>137427918.2</v>
+        <v>2180556.32</v>
       </c>
       <c r="K42" t="n">
-        <v>-1996856.8</v>
+        <v>40156.4</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.63</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>43.53</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>3036990059.88</v>
+        <v>44846653.44</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>002407.SZ</t>
+          <t>002842.SZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>多氟多</t>
+          <t>翔鹭钨业</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>54.82</v>
+        <v>45.15</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.7783</v>
+        <v>-10.006</v>
       </c>
       <c r="F43" t="n">
-        <v>34.66</v>
+        <v>24.62</v>
       </c>
       <c r="G43" t="n">
-        <v>20679906115</v>
+        <v>3041686297</v>
       </c>
       <c r="H43" t="n">
-        <v>2419387187.07</v>
+        <v>534118682.96</v>
       </c>
       <c r="I43" t="n">
-        <v>2939369592.18</v>
+        <v>427189687.12</v>
       </c>
       <c r="J43" t="n">
-        <v>5358756779.25</v>
+        <v>961308370.08</v>
       </c>
       <c r="K43" t="n">
-        <v>519982405.11</v>
+        <v>-106928995.84</v>
       </c>
       <c r="L43" t="n">
-        <v>2.51</v>
+        <v>-3.52</v>
       </c>
       <c r="M43" t="n">
-        <v>25.91</v>
+        <v>31.6</v>
       </c>
       <c r="N43" t="n">
-        <v>59138025852.9</v>
+        <v>12121075508.85</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4129,51 +4129,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>002458.SZ</t>
+          <t>002850.SZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>益生股份</t>
+          <t>科达利</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9.41</v>
+        <v>226.16</v>
       </c>
       <c r="E44" t="n">
-        <v>10.0585</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>10.83</v>
+        <v>4.27</v>
       </c>
       <c r="G44" t="n">
-        <v>1674018754</v>
+        <v>5895313098</v>
       </c>
       <c r="H44" t="n">
-        <v>268306706.03</v>
+        <v>1493731322.29</v>
       </c>
       <c r="I44" t="n">
-        <v>152573419.07</v>
+        <v>1040723736.51</v>
       </c>
       <c r="J44" t="n">
-        <v>420880125.1</v>
+        <v>2534455058.8</v>
       </c>
       <c r="K44" t="n">
-        <v>-115733286.96</v>
+        <v>-453007585.78</v>
       </c>
       <c r="L44" t="n">
-        <v>-6.91</v>
+        <v>-7.68</v>
       </c>
       <c r="M44" t="n">
-        <v>25.14</v>
+        <v>42.99</v>
       </c>
       <c r="N44" t="n">
-        <v>9093688241.93</v>
+        <v>47412159105.52</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4184,106 +4184,106 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>002463.SZ</t>
+          <t>002868.SZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>绿康生化</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>130.51</v>
+        <v>26.28</v>
       </c>
       <c r="E45" t="n">
-        <v>-9.9993</v>
+        <v>10.0042</v>
       </c>
       <c r="F45" t="n">
-        <v>4.57</v>
+        <v>1.58</v>
       </c>
       <c r="G45" t="n">
-        <v>11770285306</v>
+        <v>224702497</v>
       </c>
       <c r="H45" t="n">
-        <v>2140303859.55</v>
+        <v>32829428.9</v>
       </c>
       <c r="I45" t="n">
-        <v>1120925579.22</v>
+        <v>48316542.3</v>
       </c>
       <c r="J45" t="n">
-        <v>3261229438.77</v>
+        <v>81145971.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-1019378280.33</v>
+        <v>15487113.4</v>
       </c>
       <c r="L45" t="n">
-        <v>-8.66</v>
+        <v>6.89</v>
       </c>
       <c r="M45" t="n">
-        <v>27.71</v>
+        <v>36.11</v>
       </c>
       <c r="N45" t="n">
-        <v>250945996527.86</v>
+        <v>2812025805.12</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>002512.SZ</t>
+          <t>002872.SZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ST达华</t>
+          <t>ST天圣</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.41</v>
+        <v>5.03</v>
       </c>
       <c r="E46" t="n">
-        <v>4.9231</v>
+        <v>5.0104</v>
       </c>
       <c r="F46" t="n">
-        <v>3.61</v>
+        <v>1.93</v>
       </c>
       <c r="G46" t="n">
-        <v>256928450</v>
+        <v>46778583</v>
       </c>
       <c r="H46" t="n">
-        <v>31813262.45</v>
+        <v>8626649.359999999</v>
       </c>
       <c r="I46" t="n">
-        <v>24571951</v>
+        <v>10910410.5</v>
       </c>
       <c r="J46" t="n">
-        <v>56385213.45</v>
+        <v>19537059.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-7241311.45</v>
+        <v>2283761.14</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.82</v>
+        <v>4.88</v>
       </c>
       <c r="M46" t="n">
-        <v>21.95</v>
+        <v>41.76</v>
       </c>
       <c r="N46" t="n">
-        <v>3732080576.62</v>
+        <v>1081038214.02</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4294,3017 +4294,3017 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>002522.SZ</t>
+          <t>002898.SZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>浙江众成</t>
+          <t>赛隆退</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.45</v>
+        <v>0.36</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.0418</v>
+        <v>-2.7027</v>
       </c>
       <c r="F47" t="n">
-        <v>12.15</v>
+        <v>5.03</v>
       </c>
       <c r="G47" t="n">
-        <v>2484514003</v>
+        <v>1817587</v>
       </c>
       <c r="H47" t="n">
-        <v>158376570.51</v>
+        <v>903881</v>
       </c>
       <c r="I47" t="n">
-        <v>144274133.36</v>
+        <v>746157</v>
       </c>
       <c r="J47" t="n">
-        <v>302650703.87</v>
+        <v>1650038</v>
       </c>
       <c r="K47" t="n">
-        <v>-14102437.15</v>
+        <v>-157724</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.57</v>
+        <v>-8.68</v>
       </c>
       <c r="M47" t="n">
-        <v>12.18</v>
+        <v>90.78</v>
       </c>
       <c r="N47" t="n">
-        <v>5837378219.55</v>
+        <v>36454482.36</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>002542.SZ</t>
+          <t>123118.SZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>*ST中岩</t>
+          <t>惠城转债</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.25</v>
+        <v>738</v>
       </c>
       <c r="E48" t="n">
-        <v>5.042</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.68</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>45986838</v>
+        <v>2859442536</v>
       </c>
       <c r="H48" t="n">
-        <v>6594622.5</v>
+        <v>777351218.62</v>
       </c>
       <c r="I48" t="n">
-        <v>9172424</v>
+        <v>798265696.3099999</v>
       </c>
       <c r="J48" t="n">
-        <v>15767046.5</v>
+        <v>1575616914.93</v>
       </c>
       <c r="K48" t="n">
-        <v>2577801.5</v>
+        <v>20914477.69</v>
       </c>
       <c r="L48" t="n">
-        <v>5.61</v>
+        <v>0.73</v>
       </c>
       <c r="M48" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2198464105</v>
-      </c>
+        <v>55.1</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅达到15%的前5只可转债</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>002547.SZ</t>
+          <t>123273.SZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>*ST春兴</t>
+          <t>三江转债</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.63</v>
+        <v>157.3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3.97</v>
-      </c>
+        <v>57.3</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>152358536</v>
+        <v>10065822</v>
       </c>
       <c r="H49" t="n">
-        <v>19375981</v>
+        <v>1864896.8</v>
       </c>
       <c r="I49" t="n">
-        <v>21565058.78</v>
+        <v>10065822</v>
       </c>
       <c r="J49" t="n">
-        <v>40941039.78</v>
+        <v>11930718.8</v>
       </c>
       <c r="K49" t="n">
-        <v>2189077.78</v>
+        <v>8200925.2</v>
       </c>
       <c r="L49" t="n">
-        <v>1.44</v>
+        <v>81.47</v>
       </c>
       <c r="M49" t="n">
-        <v>26.87</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2905642846.58</v>
-      </c>
+        <v>118.53</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>上市首日可转债</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>002552.SZ</t>
+          <t>200725.SZ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>宝鼎科技</t>
+          <t>京东方B</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61.26</v>
+        <v>5.37</v>
       </c>
       <c r="E50" t="n">
-        <v>1.7608</v>
+        <v>-7.0934</v>
       </c>
       <c r="F50" t="n">
-        <v>3.67</v>
+        <v>1.37</v>
       </c>
       <c r="G50" t="n">
-        <v>825311416</v>
+        <v>45556817</v>
       </c>
       <c r="H50" t="n">
-        <v>68033932</v>
+        <v>7879313.07</v>
       </c>
       <c r="I50" t="n">
-        <v>84331475</v>
+        <v>5617724.48</v>
       </c>
       <c r="J50" t="n">
-        <v>152365407</v>
+        <v>13497037.55</v>
       </c>
       <c r="K50" t="n">
-        <v>16297543</v>
+        <v>-2261588.59</v>
       </c>
       <c r="L50" t="n">
-        <v>1.97</v>
+        <v>-4.96</v>
       </c>
       <c r="M50" t="n">
-        <v>18.46</v>
+        <v>29.63</v>
       </c>
       <c r="N50" t="n">
-        <v>22574511484.14</v>
+        <v>300097371662.45</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>002559.SZ</t>
+          <t>300018.SZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>亚威股份</t>
+          <t>中元股份</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.38</v>
+        <v>14.65</v>
       </c>
       <c r="E51" t="n">
-        <v>10.0143</v>
+        <v>19.9836</v>
       </c>
       <c r="F51" t="n">
-        <v>18.68</v>
+        <v>23.55</v>
       </c>
       <c r="G51" t="n">
-        <v>1423648187</v>
+        <v>1225192039</v>
       </c>
       <c r="H51" t="n">
-        <v>275121791.8</v>
+        <v>138008049.45</v>
       </c>
       <c r="I51" t="n">
-        <v>258707512.62</v>
+        <v>272348208.08</v>
       </c>
       <c r="J51" t="n">
-        <v>533829304.42</v>
+        <v>410356257.53</v>
       </c>
       <c r="K51" t="n">
-        <v>-16414279.18</v>
+        <v>134340158.63</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.15</v>
+        <v>10.96</v>
       </c>
       <c r="M51" t="n">
-        <v>37.5</v>
+        <v>33.49</v>
       </c>
       <c r="N51" t="n">
-        <v>7751597038.42</v>
+        <v>5333252496.35</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>002559.SZ</t>
+          <t>300029.SZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>亚威股份</t>
+          <t>天龙退</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.38</v>
+        <v>0.15</v>
       </c>
       <c r="E52" t="n">
-        <v>10.0143</v>
+        <v>-6.25</v>
       </c>
       <c r="F52" t="n">
-        <v>18.68</v>
+        <v>9.52</v>
       </c>
       <c r="G52" t="n">
-        <v>1712673503</v>
+        <v>2909054</v>
       </c>
       <c r="H52" t="n">
-        <v>278086949.8</v>
+        <v>1579081.9</v>
       </c>
       <c r="I52" t="n">
-        <v>418636138.62</v>
+        <v>922084</v>
       </c>
       <c r="J52" t="n">
-        <v>696723088.42</v>
+        <v>2501165.9</v>
       </c>
       <c r="K52" t="n">
-        <v>140549188.82</v>
+        <v>-656997.9</v>
       </c>
       <c r="L52" t="n">
-        <v>8.210000000000001</v>
+        <v>-22.58</v>
       </c>
       <c r="M52" t="n">
-        <v>40.68</v>
+        <v>85.98</v>
       </c>
       <c r="N52" t="n">
-        <v>7751597038.42</v>
+        <v>30054037.5</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>002569.SZ</t>
+          <t>300129.SZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>*ST步森</t>
+          <t>泰胜风能</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.52</v>
+        <v>10.63</v>
       </c>
       <c r="E53" t="n">
-        <v>5.0068</v>
+        <v>19.9774</v>
       </c>
       <c r="F53" t="n">
-        <v>0.45</v>
+        <v>11.47</v>
       </c>
       <c r="G53" t="n">
-        <v>17929412</v>
+        <v>823058485</v>
       </c>
       <c r="H53" t="n">
-        <v>7629054</v>
+        <v>75779988.14</v>
       </c>
       <c r="I53" t="n">
-        <v>10895865</v>
+        <v>256990495.88</v>
       </c>
       <c r="J53" t="n">
-        <v>18524919</v>
+        <v>332770484.02</v>
       </c>
       <c r="K53" t="n">
-        <v>3266811</v>
+        <v>181210507.74</v>
       </c>
       <c r="L53" t="n">
-        <v>18.22</v>
+        <v>22.02</v>
       </c>
       <c r="M53" t="n">
-        <v>103.32</v>
+        <v>40.43</v>
       </c>
       <c r="N53" t="n">
-        <v>2172955200</v>
+        <v>7639889277.18</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>002580.SZ</t>
+          <t>300139.SZ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
+          <t>晓程科技</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>22.18</v>
+        <v>44.05</v>
       </c>
       <c r="E54" t="n">
-        <v>10.0198</v>
+        <v>12.8619</v>
       </c>
       <c r="F54" t="n">
-        <v>16.28</v>
+        <v>30.65</v>
       </c>
       <c r="G54" t="n">
-        <v>1548160394</v>
+        <v>3088254312</v>
       </c>
       <c r="H54" t="n">
-        <v>170399042.5</v>
+        <v>339736675.9</v>
       </c>
       <c r="I54" t="n">
-        <v>336655620.85</v>
+        <v>305385827.58</v>
       </c>
       <c r="J54" t="n">
-        <v>507054663.35</v>
+        <v>645122503.48</v>
       </c>
       <c r="K54" t="n">
-        <v>166256578.35</v>
+        <v>-34350848.32</v>
       </c>
       <c r="L54" t="n">
-        <v>10.74</v>
+        <v>-1.11</v>
       </c>
       <c r="M54" t="n">
-        <v>32.75</v>
+        <v>20.89</v>
       </c>
       <c r="N54" t="n">
-        <v>10032874584</v>
+        <v>10292688861.25</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>002586.SZ</t>
+          <t>300163.SZ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ST围海</t>
+          <t>先锋新材</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.05</v>
+        <v>7.5</v>
       </c>
       <c r="E55" t="n">
-        <v>4.9223</v>
+        <v>15.9196</v>
       </c>
       <c r="F55" t="n">
-        <v>0.82</v>
+        <v>26.35</v>
       </c>
       <c r="G55" t="n">
-        <v>75408854</v>
+        <v>1130202680</v>
       </c>
       <c r="H55" t="n">
-        <v>22985353</v>
+        <v>252910264.28</v>
       </c>
       <c r="I55" t="n">
-        <v>15518188</v>
+        <v>238600635.66</v>
       </c>
       <c r="J55" t="n">
-        <v>38503541</v>
+        <v>491510899.94</v>
       </c>
       <c r="K55" t="n">
-        <v>-7467165</v>
+        <v>-14309628.62</v>
       </c>
       <c r="L55" t="n">
-        <v>-9.9</v>
+        <v>-1.27</v>
       </c>
       <c r="M55" t="n">
-        <v>51.06</v>
+        <v>43.49</v>
       </c>
       <c r="N55" t="n">
-        <v>4404447912.15</v>
+        <v>3424471815</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>002592.SZ</t>
+          <t>300385.SZ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ST八菱</t>
+          <t>ST雪浪</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6.48</v>
+        <v>12.77</v>
       </c>
       <c r="E56" t="n">
-        <v>5.0243</v>
+        <v>4.5008</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1</v>
+        <v>4.02</v>
       </c>
       <c r="G56" t="n">
-        <v>35960384</v>
+        <v>481139349</v>
       </c>
       <c r="H56" t="n">
-        <v>6080877</v>
+        <v>109550516</v>
       </c>
       <c r="I56" t="n">
-        <v>11328983</v>
+        <v>77204635.92</v>
       </c>
       <c r="J56" t="n">
-        <v>17409860</v>
+        <v>186755151.92</v>
       </c>
       <c r="K56" t="n">
-        <v>5248106</v>
+        <v>-32345880.08</v>
       </c>
       <c r="L56" t="n">
-        <v>14.59</v>
+        <v>-6.72</v>
       </c>
       <c r="M56" t="n">
-        <v>48.41</v>
+        <v>38.82</v>
       </c>
       <c r="N56" t="n">
-        <v>1702402077.6</v>
+        <v>3711761823.41</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>002620.SZ</t>
+          <t>300487.SZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>*ST瑞和</t>
+          <t>蓝晓科技</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.63</v>
+        <v>74.58</v>
       </c>
       <c r="E57" t="n">
-        <v>5.0373</v>
+        <v>10.4889</v>
       </c>
       <c r="F57" t="n">
-        <v>2.39</v>
+        <v>7.44</v>
       </c>
       <c r="G57" t="n">
-        <v>99461266</v>
+        <v>4909305358</v>
       </c>
       <c r="H57" t="n">
-        <v>21375315</v>
+        <v>1186977845.8</v>
       </c>
       <c r="I57" t="n">
-        <v>17746394</v>
+        <v>808324902.96</v>
       </c>
       <c r="J57" t="n">
-        <v>39121709</v>
+        <v>1995302748.76</v>
       </c>
       <c r="K57" t="n">
-        <v>-3628921</v>
+        <v>-378652942.84</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.65</v>
+        <v>-7.71</v>
       </c>
       <c r="M57" t="n">
-        <v>39.33</v>
+        <v>40.64</v>
       </c>
       <c r="N57" t="n">
-        <v>1779485528.9</v>
+        <v>22972088418.18</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>002635.SZ</t>
+          <t>300580.SZ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>安洁科技</t>
+          <t>贝斯特</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>21.24</v>
+        <v>25.96</v>
       </c>
       <c r="E58" t="n">
-        <v>-5.6</v>
+        <v>20.0185</v>
       </c>
       <c r="F58" t="n">
-        <v>28.81</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>2592528833</v>
+        <v>1078714723</v>
       </c>
       <c r="H58" t="n">
-        <v>221791452.95</v>
+        <v>165954327</v>
       </c>
       <c r="I58" t="n">
-        <v>285727442.15</v>
+        <v>199864209.51</v>
       </c>
       <c r="J58" t="n">
-        <v>507518895.1</v>
+        <v>365818536.51</v>
       </c>
       <c r="K58" t="n">
-        <v>63935989.2</v>
+        <v>33909882.51</v>
       </c>
       <c r="L58" t="n">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="M58" t="n">
-        <v>19.58</v>
+        <v>33.91</v>
       </c>
       <c r="N58" t="n">
-        <v>8401123235.16</v>
+        <v>12268500573.12</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>002653.SZ</t>
+          <t>300580.SZ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>海思科</t>
+          <t>贝斯特</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>78.8</v>
+        <v>25.96</v>
       </c>
       <c r="E59" t="n">
-        <v>8.0044</v>
+        <v>20.0185</v>
       </c>
       <c r="F59" t="n">
-        <v>4.47</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>1755151019</v>
+        <v>1928063999</v>
       </c>
       <c r="H59" t="n">
-        <v>245277466.59</v>
+        <v>289332306.08</v>
       </c>
       <c r="I59" t="n">
-        <v>158339189.48</v>
+        <v>376458101.29</v>
       </c>
       <c r="J59" t="n">
-        <v>403616656.07</v>
+        <v>665790407.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-86938277.11</v>
+        <v>87125795.20999999</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.95</v>
+        <v>4.52</v>
       </c>
       <c r="M59" t="n">
-        <v>23</v>
+        <v>34.53</v>
       </c>
       <c r="N59" t="n">
-        <v>42298747280.4</v>
+        <v>12268500573.12</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>002656.SZ</t>
+          <t>300607.SZ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>*ST摩登</t>
+          <t>拓斯达</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.96</v>
+        <v>52.96</v>
       </c>
       <c r="E60" t="n">
-        <v>4.9645</v>
+        <v>13.5506</v>
       </c>
       <c r="F60" t="n">
-        <v>0.36</v>
+        <v>26.86</v>
       </c>
       <c r="G60" t="n">
-        <v>40545944</v>
+        <v>10502306562</v>
       </c>
       <c r="H60" t="n">
-        <v>12433797</v>
+        <v>1406389635.15</v>
       </c>
       <c r="I60" t="n">
-        <v>12895754</v>
+        <v>1152054245.78</v>
       </c>
       <c r="J60" t="n">
-        <v>25329551</v>
+        <v>2558443880.93</v>
       </c>
       <c r="K60" t="n">
-        <v>461957</v>
+        <v>-254335389.37</v>
       </c>
       <c r="L60" t="n">
-        <v>1.14</v>
+        <v>-2.42</v>
       </c>
       <c r="M60" t="n">
-        <v>62.47</v>
+        <v>24.36</v>
       </c>
       <c r="N60" t="n">
-        <v>2032449569.28</v>
+        <v>17873966105.6</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>002667.SZ</t>
+          <t>300695.SZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>*ST威领</t>
+          <t>兆丰股份</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.84</v>
+        <v>68.16</v>
       </c>
       <c r="E61" t="n">
-        <v>4.9645</v>
+        <v>12.9038</v>
       </c>
       <c r="F61" t="n">
-        <v>0.12</v>
+        <v>5.98</v>
       </c>
       <c r="G61" t="n">
-        <v>232023913</v>
+        <v>610710683</v>
       </c>
       <c r="H61" t="n">
-        <v>41116690.2</v>
+        <v>103684216.5</v>
       </c>
       <c r="I61" t="n">
-        <v>37766661</v>
+        <v>129012720.5</v>
       </c>
       <c r="J61" t="n">
-        <v>78883351.2</v>
+        <v>232696937</v>
       </c>
       <c r="K61" t="n">
-        <v>-3350029.2</v>
+        <v>25328504</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.44</v>
+        <v>4.15</v>
       </c>
       <c r="M61" t="n">
-        <v>34</v>
+        <v>38.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2801474240</v>
+        <v>6969831939.84</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>002674.SZ</t>
+          <t>300718.SZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>兴业科技</t>
+          <t>长盛轴承</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>28.25</v>
+        <v>77.23</v>
       </c>
       <c r="E62" t="n">
-        <v>10.0078</v>
+        <v>19.9969</v>
       </c>
       <c r="F62" t="n">
-        <v>14.89</v>
+        <v>14.84</v>
       </c>
       <c r="G62" t="n">
-        <v>1113410650</v>
+        <v>2142139247</v>
       </c>
       <c r="H62" t="n">
-        <v>62536773.5</v>
+        <v>133080924.4</v>
       </c>
       <c r="I62" t="n">
-        <v>73105964</v>
+        <v>367394753.79</v>
       </c>
       <c r="J62" t="n">
-        <v>135642737.5</v>
+        <v>500475678.19</v>
       </c>
       <c r="K62" t="n">
-        <v>10569190.5</v>
+        <v>234313829.39</v>
       </c>
       <c r="L62" t="n">
-        <v>0.95</v>
+        <v>10.94</v>
       </c>
       <c r="M62" t="n">
-        <v>12.18</v>
+        <v>23.36</v>
       </c>
       <c r="N62" t="n">
-        <v>8264923169</v>
+        <v>15187842429.47</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>002691.SZ</t>
+          <t>300718.SZ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>*ST冀凯</t>
+          <t>长盛轴承</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.3</v>
+        <v>77.23</v>
       </c>
       <c r="E63" t="n">
-        <v>3.1175</v>
+        <v>19.9969</v>
       </c>
       <c r="F63" t="n">
-        <v>1.74</v>
+        <v>14.84</v>
       </c>
       <c r="G63" t="n">
-        <v>59645274</v>
+        <v>3495071943</v>
       </c>
       <c r="H63" t="n">
-        <v>10999198.9</v>
+        <v>205520178.9</v>
       </c>
       <c r="I63" t="n">
-        <v>16253777</v>
+        <v>409768244.71</v>
       </c>
       <c r="J63" t="n">
-        <v>27252975.9</v>
+        <v>615288423.61</v>
       </c>
       <c r="K63" t="n">
-        <v>5254578.1</v>
+        <v>204248065.81</v>
       </c>
       <c r="L63" t="n">
-        <v>8.81</v>
+        <v>5.84</v>
       </c>
       <c r="M63" t="n">
-        <v>45.69</v>
+        <v>17.6</v>
       </c>
       <c r="N63" t="n">
-        <v>1444711549</v>
+        <v>15187842429.47</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>002717.SZ</t>
+          <t>300985.SZ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>*ST岭南</t>
+          <t>致远新能</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.02</v>
+        <v>49.67</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9901</v>
+        <v>20.0048</v>
       </c>
       <c r="F64" t="n">
-        <v>6.05</v>
+        <v>4.31</v>
       </c>
       <c r="G64" t="n">
-        <v>195565911</v>
+        <v>863744038</v>
       </c>
       <c r="H64" t="n">
-        <v>25330496.8</v>
+        <v>205561395.84</v>
       </c>
       <c r="I64" t="n">
-        <v>23435497.4</v>
+        <v>163611620.75</v>
       </c>
       <c r="J64" t="n">
-        <v>48765994.2</v>
+        <v>369173016.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-1894999.4</v>
+        <v>-41949775.09</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.97</v>
+        <v>-4.86</v>
       </c>
       <c r="M64" t="n">
-        <v>24.94</v>
+        <v>42.74</v>
       </c>
       <c r="N64" t="n">
-        <v>1752925045.32</v>
+        <v>9264074881.6</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>002738.SZ</t>
+          <t>301008.SZ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>中矿资源</t>
+          <t>宏昌科技</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>65.48999999999999</v>
+        <v>33.64</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9246</v>
+        <v>5.3555</v>
       </c>
       <c r="F65" t="n">
-        <v>12.92</v>
+        <v>19.74</v>
       </c>
       <c r="G65" t="n">
-        <v>9403173225</v>
+        <v>1280230951</v>
       </c>
       <c r="H65" t="n">
-        <v>1585509616.15</v>
+        <v>195634382.22</v>
       </c>
       <c r="I65" t="n">
-        <v>1852129463.54</v>
+        <v>185184192.69</v>
       </c>
       <c r="J65" t="n">
-        <v>3437639079.69</v>
+        <v>380818574.91</v>
       </c>
       <c r="K65" t="n">
-        <v>266619847.39</v>
+        <v>-10450189.53</v>
       </c>
       <c r="L65" t="n">
-        <v>2.84</v>
+        <v>-0.82</v>
       </c>
       <c r="M65" t="n">
-        <v>36.56</v>
+        <v>29.75</v>
       </c>
       <c r="N65" t="n">
-        <v>46578323422.74</v>
+        <v>3890154291.76</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>002747.SZ</t>
+          <t>301379.SZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>天山电子</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>40.7</v>
+        <v>32.16</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8768</v>
+        <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>22.44</v>
+        <v>22.75</v>
       </c>
       <c r="G66" t="n">
-        <v>11880225616</v>
+        <v>1559512057</v>
       </c>
       <c r="H66" t="n">
-        <v>1264444993.58</v>
+        <v>158786114.35</v>
       </c>
       <c r="I66" t="n">
-        <v>1659430501.25</v>
+        <v>252698538.37</v>
       </c>
       <c r="J66" t="n">
-        <v>2923875494.83</v>
+        <v>411484652.72</v>
       </c>
       <c r="K66" t="n">
-        <v>394985507.67</v>
+        <v>93912424.02</v>
       </c>
       <c r="L66" t="n">
-        <v>3.32</v>
+        <v>6.02</v>
       </c>
       <c r="M66" t="n">
-        <v>24.61</v>
+        <v>26.39</v>
       </c>
       <c r="N66" t="n">
-        <v>31843868359.6</v>
+        <v>7000779991.2</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>002808.SZ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>恒久退</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.25</v>
+        <v>35.55</v>
       </c>
       <c r="E67" t="n">
-        <v>8.6957</v>
+        <v>13.2166</v>
       </c>
       <c r="F67" t="n">
-        <v>11.55</v>
+        <v>41.4</v>
       </c>
       <c r="G67" t="n">
-        <v>5367795</v>
+        <v>453284970</v>
       </c>
       <c r="H67" t="n">
-        <v>3032175</v>
+        <v>45583460.74</v>
       </c>
       <c r="I67" t="n">
-        <v>2596529</v>
+        <v>49030939.09</v>
       </c>
       <c r="J67" t="n">
-        <v>5628704</v>
+        <v>94614399.83</v>
       </c>
       <c r="K67" t="n">
-        <v>-435646</v>
+        <v>3447478.35</v>
       </c>
       <c r="L67" t="n">
-        <v>-8.119999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="M67" t="n">
-        <v>104.86</v>
+        <v>20.87</v>
       </c>
       <c r="N67" t="n">
-        <v>46715264</v>
+        <v>1162429648.65</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>002826.SZ</t>
+          <t>301529.SZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>易明医药</t>
+          <t>福赛科技</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>18.18</v>
+        <v>124.3</v>
       </c>
       <c r="E68" t="n">
-        <v>9.9819</v>
+        <v>10.9821</v>
       </c>
       <c r="F68" t="n">
-        <v>3.84</v>
+        <v>10.36</v>
       </c>
       <c r="G68" t="n">
-        <v>255471253</v>
+        <v>2328588965</v>
       </c>
       <c r="H68" t="n">
-        <v>29034886</v>
+        <v>610241829.72</v>
       </c>
       <c r="I68" t="n">
-        <v>69090465</v>
+        <v>499501367.67</v>
       </c>
       <c r="J68" t="n">
-        <v>98125351</v>
+        <v>1109743197.39</v>
       </c>
       <c r="K68" t="n">
-        <v>40055579</v>
+        <v>-110740462.05</v>
       </c>
       <c r="L68" t="n">
-        <v>15.68</v>
+        <v>-4.76</v>
       </c>
       <c r="M68" t="n">
-        <v>38.41</v>
+        <v>47.66</v>
       </c>
       <c r="N68" t="n">
-        <v>3358378873.98</v>
+        <v>7901337578.2</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>002842.SZ</t>
+          <t>301596.SZ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>瑞迪智驱</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>50.17</v>
+        <v>63.97</v>
       </c>
       <c r="E69" t="n">
-        <v>9.9978</v>
+        <v>19.9962</v>
       </c>
       <c r="F69" t="n">
-        <v>21.67</v>
+        <v>18.34</v>
       </c>
       <c r="G69" t="n">
-        <v>2800589265</v>
+        <v>740454652</v>
       </c>
       <c r="H69" t="n">
-        <v>226795189</v>
+        <v>95947164.44</v>
       </c>
       <c r="I69" t="n">
-        <v>499021884.5</v>
+        <v>162284073.72</v>
       </c>
       <c r="J69" t="n">
-        <v>725817073.5</v>
+        <v>258231238.16</v>
       </c>
       <c r="K69" t="n">
-        <v>272226695.5</v>
+        <v>66336909.28</v>
       </c>
       <c r="L69" t="n">
-        <v>9.720000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>25.92</v>
+        <v>34.87</v>
       </c>
       <c r="N69" t="n">
-        <v>13468756551.03</v>
+        <v>2804653214.26</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>002898.SZ</t>
+          <t>301696.SZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>赛隆退</t>
+          <t>三瑞智能</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.37</v>
+        <v>140.4</v>
       </c>
       <c r="E70" t="n">
-        <v>5.7143</v>
+        <v>3.9615</v>
       </c>
       <c r="F70" t="n">
-        <v>8.65</v>
+        <v>40.63</v>
       </c>
       <c r="G70" t="n">
-        <v>3151001</v>
+        <v>1678448786</v>
       </c>
       <c r="H70" t="n">
-        <v>1462294.76</v>
+        <v>146962724.79</v>
       </c>
       <c r="I70" t="n">
-        <v>1322590.5</v>
+        <v>108941867.86</v>
       </c>
       <c r="J70" t="n">
-        <v>2784885.26</v>
+        <v>255904592.65</v>
       </c>
       <c r="K70" t="n">
-        <v>-139704.26</v>
+        <v>-38020856.93</v>
       </c>
       <c r="L70" t="n">
-        <v>-4.43</v>
+        <v>-2.27</v>
       </c>
       <c r="M70" t="n">
-        <v>88.38</v>
+        <v>15.25</v>
       </c>
       <c r="N70" t="n">
-        <v>37467106.87</v>
+        <v>4223702901.6</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>002971.SZ</t>
+          <t>600053.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>和远气体</t>
+          <t>*ST九鼎</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>75.02</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>2.1531</v>
       </c>
       <c r="F71" t="n">
-        <v>15.14</v>
+        <v>0.71</v>
       </c>
       <c r="G71" t="n">
-        <v>1717412475</v>
+        <v>82287489</v>
       </c>
       <c r="H71" t="n">
-        <v>185396107.6</v>
+        <v>13239392</v>
       </c>
       <c r="I71" t="n">
-        <v>238223115</v>
+        <v>20701034</v>
       </c>
       <c r="J71" t="n">
-        <v>423619222.6</v>
+        <v>33940426</v>
       </c>
       <c r="K71" t="n">
-        <v>52827007.4</v>
+        <v>7461642</v>
       </c>
       <c r="L71" t="n">
-        <v>3.08</v>
+        <v>9.07</v>
       </c>
       <c r="M71" t="n">
-        <v>24.67</v>
+        <v>41.25</v>
       </c>
       <c r="N71" t="n">
-        <v>11733229277</v>
+        <v>3702438432</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>002971.SZ</t>
+          <t>600080.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>和远气体</t>
+          <t>ST金花</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>75.02</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>2.8807</v>
       </c>
       <c r="F72" t="n">
-        <v>15.14</v>
+        <v>1.85</v>
       </c>
       <c r="G72" t="n">
-        <v>3897254229</v>
+        <v>97791266</v>
       </c>
       <c r="H72" t="n">
-        <v>318705197.88</v>
+        <v>21648902.44</v>
       </c>
       <c r="I72" t="n">
-        <v>566861540.5</v>
+        <v>24929214</v>
       </c>
       <c r="J72" t="n">
-        <v>885566738.38</v>
+        <v>46578116.44</v>
       </c>
       <c r="K72" t="n">
-        <v>248156342.62</v>
+        <v>3280311.56</v>
       </c>
       <c r="L72" t="n">
-        <v>6.37</v>
+        <v>3.35</v>
       </c>
       <c r="M72" t="n">
-        <v>22.72</v>
+        <v>47.63</v>
       </c>
       <c r="N72" t="n">
-        <v>11733229277</v>
+        <v>1866351425</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>002977.SZ</t>
+          <t>600082.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>*ST天箭</t>
+          <t>ST海泰</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>23.18</v>
+        <v>2.95</v>
       </c>
       <c r="E73" t="n">
-        <v>4.9819</v>
+        <v>4.9822</v>
       </c>
       <c r="F73" t="n">
-        <v>0.37</v>
+        <v>1.29</v>
       </c>
       <c r="G73" t="n">
-        <v>16917987</v>
+        <v>42996809</v>
       </c>
       <c r="H73" t="n">
-        <v>3374668</v>
+        <v>10615335.06</v>
       </c>
       <c r="I73" t="n">
-        <v>9545725</v>
+        <v>10524810.99</v>
       </c>
       <c r="J73" t="n">
-        <v>12920393</v>
+        <v>21140146.05</v>
       </c>
       <c r="K73" t="n">
-        <v>6171057</v>
+        <v>-90524.07000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>36.48</v>
+        <v>-0.21</v>
       </c>
       <c r="M73" t="n">
-        <v>76.37</v>
+        <v>49.17</v>
       </c>
       <c r="N73" t="n">
-        <v>1544881400.6</v>
+        <v>1871289465.4</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>002979.SZ</t>
+          <t>600084.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>*ST尼雅</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>63.23</v>
+        <v>4.24</v>
       </c>
       <c r="E74" t="n">
-        <v>10.0035</v>
+        <v>4.9505</v>
       </c>
       <c r="F74" t="n">
-        <v>1.59</v>
+        <v>0.12</v>
       </c>
       <c r="G74" t="n">
-        <v>2377247296</v>
+        <v>40798495</v>
       </c>
       <c r="H74" t="n">
-        <v>339577799.3</v>
+        <v>9027363</v>
       </c>
       <c r="I74" t="n">
-        <v>288532999.83</v>
+        <v>14289559</v>
       </c>
       <c r="J74" t="n">
-        <v>628110799.13</v>
+        <v>23316922</v>
       </c>
       <c r="K74" t="n">
-        <v>-51044799.47</v>
+        <v>5262196</v>
       </c>
       <c r="L74" t="n">
-        <v>-2.15</v>
+        <v>12.9</v>
       </c>
       <c r="M74" t="n">
-        <v>26.42</v>
+        <v>57.15</v>
       </c>
       <c r="N74" t="n">
-        <v>14084056266.57</v>
+        <v>4764601759.2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>111012.SH</t>
+          <t>600165.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>福新转债</t>
+          <t>ST宁科</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>381.865</v>
+        <v>2.89</v>
       </c>
       <c r="E75" t="n">
-        <v>11.1006</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
+        <v>5.0909</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.78</v>
+      </c>
       <c r="G75" t="n">
-        <v>7300066640</v>
+        <v>73952251</v>
       </c>
       <c r="H75" t="n">
-        <v>1499017850</v>
+        <v>10938882</v>
       </c>
       <c r="I75" t="n">
-        <v>1498228810</v>
+        <v>11895574</v>
       </c>
       <c r="J75" t="n">
-        <v>2997246660</v>
+        <v>22834456</v>
       </c>
       <c r="K75" t="n">
-        <v>-789040</v>
+        <v>956692</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.01</v>
+        <v>1.29</v>
       </c>
       <c r="M75" t="n">
-        <v>41.06</v>
-      </c>
-      <c r="N75" t="inlineStr"/>
+        <v>30.88</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2118120436.94</v>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>123188.SZ</t>
+          <t>600172.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>水羊转债</t>
+          <t>黄河旋风</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>166.169</v>
+        <v>16.86</v>
       </c>
       <c r="E76" t="n">
-        <v>18.6074</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
+        <v>-6.4892</v>
+      </c>
+      <c r="F76" t="n">
+        <v>20.58</v>
+      </c>
       <c r="G76" t="n">
-        <v>3254776216</v>
+        <v>4447473172</v>
       </c>
       <c r="H76" t="n">
-        <v>805434127.35</v>
+        <v>716485928.8099999</v>
       </c>
       <c r="I76" t="n">
-        <v>813473528.78</v>
+        <v>658809758.17</v>
       </c>
       <c r="J76" t="n">
-        <v>1618907656.13</v>
+        <v>1375295686.98</v>
       </c>
       <c r="K76" t="n">
-        <v>8039401.43</v>
+        <v>-57676170.64</v>
       </c>
       <c r="L76" t="n">
-        <v>0.25</v>
+        <v>-1.3</v>
       </c>
       <c r="M76" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="N76" t="inlineStr"/>
+        <v>30.92</v>
+      </c>
+      <c r="N76" t="n">
+        <v>21517671945</v>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只可转债</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>200016.SZ</t>
+          <t>600182.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>*ST康佳B</t>
+          <t>S佳通</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.74</v>
+        <v>14.71</v>
       </c>
       <c r="E77" t="n">
-        <v>5.7143</v>
+        <v>3.9576</v>
       </c>
       <c r="F77" t="n">
-        <v>0.23</v>
+        <v>4.69</v>
       </c>
       <c r="G77" t="n">
-        <v>2331433</v>
+        <v>181294813</v>
       </c>
       <c r="H77" t="n">
-        <v>854470</v>
+        <v>35233251</v>
       </c>
       <c r="I77" t="n">
-        <v>888524</v>
+        <v>51714473</v>
       </c>
       <c r="J77" t="n">
-        <v>1742994</v>
+        <v>86947724</v>
       </c>
       <c r="K77" t="n">
-        <v>34054</v>
+        <v>16481222</v>
       </c>
       <c r="L77" t="n">
-        <v>1.46</v>
+        <v>9.09</v>
       </c>
       <c r="M77" t="n">
-        <v>74.76000000000001</v>
+        <v>47.96</v>
       </c>
       <c r="N77" t="n">
-        <v>4655748441.92</v>
+        <v>2500700000</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>S股连续三个交易日内收盘价格涨幅偏离值累计达到15%的证券</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>300020.SZ</t>
+          <t>600243.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ST银江</t>
+          <t>*ST海华</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3.93</v>
+        <v>3.64</v>
       </c>
       <c r="E78" t="n">
-        <v>13.2565</v>
+        <v>4.8991</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>1.79</v>
       </c>
       <c r="G78" t="n">
-        <v>423690331</v>
+        <v>81859952</v>
       </c>
       <c r="H78" t="n">
-        <v>42010141.04</v>
+        <v>15523068</v>
       </c>
       <c r="I78" t="n">
-        <v>45492980</v>
+        <v>17300765.28</v>
       </c>
       <c r="J78" t="n">
-        <v>87503121.04000001</v>
+        <v>32823833.28</v>
       </c>
       <c r="K78" t="n">
-        <v>3482838.96</v>
+        <v>1777697.28</v>
       </c>
       <c r="L78" t="n">
-        <v>0.82</v>
+        <v>2.17</v>
       </c>
       <c r="M78" t="n">
-        <v>20.65</v>
+        <v>40.1</v>
       </c>
       <c r="N78" t="n">
-        <v>3012673190.37</v>
+        <v>1597414000</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>300029.SZ</t>
+          <t>600376.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>天龙退</t>
+          <t>首开股份</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.16</v>
+        <v>3.81</v>
       </c>
       <c r="E79" t="n">
-        <v>6.6667</v>
+        <v>10.1156</v>
       </c>
       <c r="F79" t="n">
-        <v>12.22</v>
+        <v>1.44</v>
       </c>
       <c r="G79" t="n">
-        <v>3930472</v>
+        <v>141211805</v>
       </c>
       <c r="H79" t="n">
-        <v>1323444</v>
+        <v>25109805</v>
       </c>
       <c r="I79" t="n">
-        <v>1789550.5</v>
+        <v>91403805</v>
       </c>
       <c r="J79" t="n">
-        <v>3112994.5</v>
+        <v>116513610</v>
       </c>
       <c r="K79" t="n">
-        <v>466106.5</v>
+        <v>66294000</v>
       </c>
       <c r="L79" t="n">
-        <v>11.86</v>
+        <v>46.95</v>
       </c>
       <c r="M79" t="n">
-        <v>79.2</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="N79" t="n">
-        <v>32057640</v>
+        <v>9828143572.02</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>300044.SZ</t>
+          <t>600378.SH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>*ST赛为</t>
+          <t>昊华科技</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5.78</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>3.9568</v>
+        <v>-7.4967</v>
       </c>
       <c r="F80" t="n">
-        <v>4.92</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>732261853</v>
+        <v>8273815539</v>
       </c>
       <c r="H80" t="n">
-        <v>84411563.11</v>
+        <v>1297025388.3</v>
       </c>
       <c r="I80" t="n">
-        <v>60139666.4</v>
+        <v>1150502000.47</v>
       </c>
       <c r="J80" t="n">
-        <v>144551229.51</v>
+        <v>2447527388.77</v>
       </c>
       <c r="K80" t="n">
-        <v>-24271896.71</v>
+        <v>-146523387.83</v>
       </c>
       <c r="L80" t="n">
-        <v>-3.31</v>
+        <v>-1.77</v>
       </c>
       <c r="M80" t="n">
-        <v>19.74</v>
+        <v>29.58</v>
       </c>
       <c r="N80" t="n">
-        <v>4134886013.34</v>
+        <v>81525693241.63</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>300071.SZ</t>
+          <t>600397.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>福石控股</t>
+          <t>江钨装备</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.4</v>
+        <v>25.65</v>
       </c>
       <c r="E81" t="n">
-        <v>19.891</v>
+        <v>-10</v>
       </c>
       <c r="F81" t="n">
-        <v>17.85</v>
+        <v>14.46</v>
       </c>
       <c r="G81" t="n">
-        <v>708058141</v>
+        <v>3839382601</v>
       </c>
       <c r="H81" t="n">
-        <v>60405159.8</v>
+        <v>538711753.95</v>
       </c>
       <c r="I81" t="n">
-        <v>111027265</v>
+        <v>787037403.72</v>
       </c>
       <c r="J81" t="n">
-        <v>171432424.8</v>
+        <v>1325749157.67</v>
       </c>
       <c r="K81" t="n">
-        <v>50622105.2</v>
+        <v>248325649.77</v>
       </c>
       <c r="L81" t="n">
-        <v>7.15</v>
+        <v>6.47</v>
       </c>
       <c r="M81" t="n">
-        <v>24.21</v>
+        <v>34.53</v>
       </c>
       <c r="N81" t="n">
-        <v>4159543810.4</v>
+        <v>25392470973.3</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>300071.SZ</t>
+          <t>600530.SH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>福石控股</t>
+          <t>交大昂立</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="E82" t="n">
-        <v>19.891</v>
+        <v>10.0386</v>
       </c>
       <c r="F82" t="n">
-        <v>17.85</v>
+        <v>1.51</v>
       </c>
       <c r="G82" t="n">
-        <v>905716094</v>
+        <v>64902703</v>
       </c>
       <c r="H82" t="n">
-        <v>73514656.8</v>
+        <v>9206243</v>
       </c>
       <c r="I82" t="n">
-        <v>132568668</v>
+        <v>25241631</v>
       </c>
       <c r="J82" t="n">
-        <v>206083324.8</v>
+        <v>34447874</v>
       </c>
       <c r="K82" t="n">
-        <v>59054011.2</v>
+        <v>16035388</v>
       </c>
       <c r="L82" t="n">
-        <v>6.52</v>
+        <v>24.71</v>
       </c>
       <c r="M82" t="n">
-        <v>22.75</v>
+        <v>53.08</v>
       </c>
       <c r="N82" t="n">
-        <v>4159543810.4</v>
+        <v>4417044000</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>300154.SZ</t>
+          <t>600545.SH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>瑞凌股份</t>
+          <t>卓郎智能</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9.539999999999999</v>
+        <v>6.26</v>
       </c>
       <c r="E83" t="n">
-        <v>12.2353</v>
+        <v>-4.1348</v>
       </c>
       <c r="F83" t="n">
-        <v>10.63</v>
+        <v>8.08</v>
       </c>
       <c r="G83" t="n">
-        <v>433267403</v>
+        <v>3355872658</v>
       </c>
       <c r="H83" t="n">
-        <v>100035518.94</v>
+        <v>453704238.84</v>
       </c>
       <c r="I83" t="n">
-        <v>114685584</v>
+        <v>347801287.15</v>
       </c>
       <c r="J83" t="n">
-        <v>214721102.94</v>
+        <v>801505525.99</v>
       </c>
       <c r="K83" t="n">
-        <v>14650065.06</v>
+        <v>-105902951.69</v>
       </c>
       <c r="L83" t="n">
-        <v>3.38</v>
+        <v>-3.16</v>
       </c>
       <c r="M83" t="n">
-        <v>49.56</v>
+        <v>23.88</v>
       </c>
       <c r="N83" t="n">
-        <v>3006573462.54</v>
+        <v>11192330509.72</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>300163.SZ</t>
+          <t>600552.SH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>先锋新材</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6.47</v>
+        <v>25.39</v>
       </c>
       <c r="E84" t="n">
-        <v>20.0371</v>
+        <v>-5.0841</v>
       </c>
       <c r="F84" t="n">
-        <v>7.65</v>
+        <v>12.34</v>
       </c>
       <c r="G84" t="n">
-        <v>213434582</v>
+        <v>13113751610</v>
       </c>
       <c r="H84" t="n">
-        <v>49191749</v>
+        <v>1324665283.43</v>
       </c>
       <c r="I84" t="n">
-        <v>104184347.2</v>
+        <v>1278749131.78</v>
       </c>
       <c r="J84" t="n">
-        <v>153376096.2</v>
+        <v>2603414415.21</v>
       </c>
       <c r="K84" t="n">
-        <v>54992598.2</v>
+        <v>-45916151.65</v>
       </c>
       <c r="L84" t="n">
-        <v>25.77</v>
+        <v>-0.35</v>
       </c>
       <c r="M84" t="n">
-        <v>71.86</v>
+        <v>19.85</v>
       </c>
       <c r="N84" t="n">
-        <v>2954177685.74</v>
+        <v>23983569038.66</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>300345.SZ</t>
+          <t>600581.SH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>华民股份</t>
+          <t>*ST八钢</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7.45</v>
+        <v>2.36</v>
       </c>
       <c r="E85" t="n">
-        <v>6.2767</v>
+        <v>3.0568</v>
       </c>
       <c r="F85" t="n">
-        <v>24.81</v>
+        <v>1.18</v>
       </c>
       <c r="G85" t="n">
-        <v>1555201823</v>
+        <v>110648476</v>
       </c>
       <c r="H85" t="n">
-        <v>171274262.68</v>
+        <v>12315396.36</v>
       </c>
       <c r="I85" t="n">
-        <v>297745689</v>
+        <v>20801790</v>
       </c>
       <c r="J85" t="n">
-        <v>469019951.68</v>
+        <v>33117186.36</v>
       </c>
       <c r="K85" t="n">
-        <v>126471426.32</v>
+        <v>8486393.640000001</v>
       </c>
       <c r="L85" t="n">
-        <v>8.130000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="M85" t="n">
-        <v>30.16</v>
+        <v>29.93</v>
       </c>
       <c r="N85" t="n">
-        <v>3572991652.75</v>
+        <v>3617638973.2</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>300694.SZ</t>
+          <t>600624.SH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>蠡湖股份</t>
+          <t>ST复华</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.83</v>
+        <v>3.77</v>
       </c>
       <c r="E86" t="n">
-        <v>9.8422</v>
+        <v>5.0139</v>
       </c>
       <c r="F86" t="n">
-        <v>10.6</v>
+        <v>0.53</v>
       </c>
       <c r="G86" t="n">
-        <v>512240903</v>
+        <v>67332559</v>
       </c>
       <c r="H86" t="n">
-        <v>98035792.67</v>
+        <v>11349842.01</v>
       </c>
       <c r="I86" t="n">
-        <v>126293288.21</v>
+        <v>11957834.76</v>
       </c>
       <c r="J86" t="n">
-        <v>224329080.88</v>
+        <v>23307676.77</v>
       </c>
       <c r="K86" t="n">
-        <v>28257495.54</v>
+        <v>607992.75</v>
       </c>
       <c r="L86" t="n">
-        <v>5.52</v>
+        <v>0.9</v>
       </c>
       <c r="M86" t="n">
-        <v>43.79</v>
+        <v>34.62</v>
       </c>
       <c r="N86" t="n">
-        <v>2564553253.08</v>
+        <v>2561137971.34</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>300740.SZ</t>
+          <t>600630.SH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>水羊股份</t>
+          <t>龙头股份</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>22.27</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>19.9892</v>
+        <v>-10.0094</v>
       </c>
       <c r="F87" t="n">
-        <v>9.970000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="G87" t="n">
-        <v>743594650</v>
+        <v>264794850</v>
       </c>
       <c r="H87" t="n">
-        <v>133210589.18</v>
+        <v>50241270.97</v>
       </c>
       <c r="I87" t="n">
-        <v>155883552.35</v>
+        <v>23251074</v>
       </c>
       <c r="J87" t="n">
-        <v>289094141.53</v>
+        <v>73492344.97</v>
       </c>
       <c r="K87" t="n">
-        <v>22672963.17</v>
+        <v>-26990196.97</v>
       </c>
       <c r="L87" t="n">
-        <v>3.05</v>
+        <v>-10.19</v>
       </c>
       <c r="M87" t="n">
-        <v>38.88</v>
+        <v>27.75</v>
       </c>
       <c r="N87" t="n">
-        <v>8051749700.27</v>
+        <v>4087168563.14</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>300765.SZ</t>
+          <t>600707.SH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>石药创新</t>
+          <t>彩虹股份</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>34.49</v>
+        <v>15.02</v>
       </c>
       <c r="E88" t="n">
-        <v>12.1626</v>
+        <v>-10.006</v>
       </c>
       <c r="F88" t="n">
-        <v>2.79</v>
+        <v>7.78</v>
       </c>
       <c r="G88" t="n">
-        <v>2075434670</v>
+        <v>4263479007</v>
       </c>
       <c r="H88" t="n">
-        <v>382916529.71</v>
+        <v>468056033.96</v>
       </c>
       <c r="I88" t="n">
-        <v>363367429.55</v>
+        <v>478674918.96</v>
       </c>
       <c r="J88" t="n">
-        <v>746283959.26</v>
+        <v>946730952.92</v>
       </c>
       <c r="K88" t="n">
-        <v>-19549100.16</v>
+        <v>10618885</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M88" t="n">
-        <v>35.96</v>
+        <v>22.21</v>
       </c>
       <c r="N88" t="n">
-        <v>48444410638.56</v>
+        <v>53886799374.64</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>300980.SZ</t>
+          <t>600734.SH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>祥源新材</t>
+          <t>*ST实达</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>33.5</v>
+        <v>1.74</v>
       </c>
       <c r="E89" t="n">
-        <v>6.8922</v>
+        <v>4.8193</v>
       </c>
       <c r="F89" t="n">
-        <v>16.91</v>
+        <v>3.01</v>
       </c>
       <c r="G89" t="n">
-        <v>1318359478</v>
+        <v>323350755</v>
       </c>
       <c r="H89" t="n">
-        <v>251908849.48</v>
+        <v>25576638.99</v>
       </c>
       <c r="I89" t="n">
-        <v>218914532.96</v>
+        <v>26587820.67</v>
       </c>
       <c r="J89" t="n">
-        <v>470823382.44</v>
+        <v>52164459.66</v>
       </c>
       <c r="K89" t="n">
-        <v>-32994316.52</v>
+        <v>1011181.68</v>
       </c>
       <c r="L89" t="n">
-        <v>-2.5</v>
+        <v>0.31</v>
       </c>
       <c r="M89" t="n">
-        <v>35.71</v>
+        <v>16.13</v>
       </c>
       <c r="N89" t="n">
-        <v>3294438508</v>
+        <v>3789464404.44</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>301008.SZ</t>
+          <t>600759.SH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>宏昌科技</t>
+          <t>ST洲际</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>31.93</v>
+        <v>2.12</v>
       </c>
       <c r="E90" t="n">
-        <v>19.9925</v>
+        <v>4.9505</v>
       </c>
       <c r="F90" t="n">
-        <v>15.06</v>
+        <v>7.64</v>
       </c>
       <c r="G90" t="n">
-        <v>527877777</v>
+        <v>682355117</v>
       </c>
       <c r="H90" t="n">
-        <v>62883838.21</v>
+        <v>47574700.24</v>
       </c>
       <c r="I90" t="n">
-        <v>122170547.9</v>
+        <v>46010084.8</v>
       </c>
       <c r="J90" t="n">
-        <v>185054386.11</v>
+        <v>93584785.04000001</v>
       </c>
       <c r="K90" t="n">
-        <v>59286709.69</v>
+        <v>-1564615.44</v>
       </c>
       <c r="L90" t="n">
-        <v>11.23</v>
+        <v>-0.23</v>
       </c>
       <c r="M90" t="n">
-        <v>35.06</v>
+        <v>13.71</v>
       </c>
       <c r="N90" t="n">
-        <v>3692408636.62</v>
+        <v>8784613853.6</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>301092.SZ</t>
+          <t>600784.SH</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>争光股份</t>
+          <t>鲁银投资</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>58.91</v>
+        <v>7.8</v>
       </c>
       <c r="E91" t="n">
-        <v>20.0041</v>
+        <v>3.4483</v>
       </c>
       <c r="F91" t="n">
-        <v>15.46</v>
+        <v>3.38</v>
       </c>
       <c r="G91" t="n">
-        <v>540178704</v>
+        <v>467970337</v>
       </c>
       <c r="H91" t="n">
-        <v>61742201</v>
+        <v>63207961</v>
       </c>
       <c r="I91" t="n">
-        <v>143105487.24</v>
+        <v>89328712.52</v>
       </c>
       <c r="J91" t="n">
-        <v>204847688.24</v>
+        <v>152536673.52</v>
       </c>
       <c r="K91" t="n">
-        <v>81363286.23999999</v>
+        <v>26120751.52</v>
       </c>
       <c r="L91" t="n">
-        <v>15.06</v>
+        <v>5.58</v>
       </c>
       <c r="M91" t="n">
-        <v>37.92</v>
+        <v>32.6</v>
       </c>
       <c r="N91" t="n">
-        <v>3589942056.94</v>
+        <v>5270087760.6</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>301092.SZ</t>
+          <t>600857.SH</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>争光股份</t>
+          <t>宁波中百</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>58.91</v>
+        <v>21.3</v>
       </c>
       <c r="E92" t="n">
-        <v>20.0041</v>
+        <v>-5.8772</v>
       </c>
       <c r="F92" t="n">
-        <v>15.46</v>
+        <v>10.03</v>
       </c>
       <c r="G92" t="n">
-        <v>819171437</v>
+        <v>493583212</v>
       </c>
       <c r="H92" t="n">
-        <v>94395853.95</v>
+        <v>72236103.41</v>
       </c>
       <c r="I92" t="n">
-        <v>215825073.13</v>
+        <v>115841948.48</v>
       </c>
       <c r="J92" t="n">
-        <v>310220927.08</v>
+        <v>188078051.89</v>
       </c>
       <c r="K92" t="n">
-        <v>121429219.18</v>
+        <v>43605845.07</v>
       </c>
       <c r="L92" t="n">
-        <v>14.82</v>
+        <v>8.83</v>
       </c>
       <c r="M92" t="n">
-        <v>37.87</v>
+        <v>38.1</v>
       </c>
       <c r="N92" t="n">
-        <v>3589942056.94</v>
+        <v>4778014274.7</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>301281.SZ</t>
+          <t>600988.SH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>科源制药</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>58.05</v>
+        <v>31.23</v>
       </c>
       <c r="E93" t="n">
-        <v>3.1267</v>
+        <v>10.0035</v>
       </c>
       <c r="F93" t="n">
-        <v>10.34</v>
+        <v>2.24</v>
       </c>
       <c r="G93" t="n">
-        <v>983696959</v>
+        <v>2994947705</v>
       </c>
       <c r="H93" t="n">
-        <v>180179116.25</v>
+        <v>387357264.22</v>
       </c>
       <c r="I93" t="n">
-        <v>173168576.7</v>
+        <v>536265116.81</v>
       </c>
       <c r="J93" t="n">
-        <v>353347692.95</v>
+        <v>923622381.03</v>
       </c>
       <c r="K93" t="n">
-        <v>-7010539.55</v>
+        <v>148907852.59</v>
       </c>
       <c r="L93" t="n">
-        <v>-0.71</v>
+        <v>4.97</v>
       </c>
       <c r="M93" t="n">
-        <v>35.92</v>
+        <v>30.84</v>
       </c>
       <c r="N93" t="n">
-        <v>4118763600</v>
+        <v>51963952334.94</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>601678.SH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>滨化股份</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>31.4</v>
+        <v>6.93</v>
       </c>
       <c r="E94" t="n">
-        <v>1.2903</v>
+        <v>-10</v>
       </c>
       <c r="F94" t="n">
-        <v>33.91</v>
+        <v>20.9</v>
       </c>
       <c r="G94" t="n">
-        <v>340772156</v>
+        <v>3052366108</v>
       </c>
       <c r="H94" t="n">
-        <v>31246382.05</v>
+        <v>353086658.2</v>
       </c>
       <c r="I94" t="n">
-        <v>28367431.2</v>
+        <v>204194500.1</v>
       </c>
       <c r="J94" t="n">
-        <v>59613813.25</v>
+        <v>557281158.3</v>
       </c>
       <c r="K94" t="n">
-        <v>-2878950.85</v>
+        <v>-148892158.1</v>
       </c>
       <c r="L94" t="n">
-        <v>-0.84</v>
+        <v>-4.88</v>
       </c>
       <c r="M94" t="n">
-        <v>17.49</v>
+        <v>18.26</v>
       </c>
       <c r="N94" t="n">
-        <v>1026731110.2</v>
+        <v>14160320392.68</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>301611.SZ</t>
+          <t>603078.SH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>江化微</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>154.06</v>
+        <v>56.26</v>
       </c>
       <c r="E95" t="n">
-        <v>-16.4896</v>
+        <v>-1.1248</v>
       </c>
       <c r="F95" t="n">
-        <v>17.38</v>
+        <v>19.58</v>
       </c>
       <c r="G95" t="n">
-        <v>4090541526</v>
+        <v>4046044000</v>
       </c>
       <c r="H95" t="n">
-        <v>1006025970</v>
+        <v>739879002.59</v>
       </c>
       <c r="I95" t="n">
-        <v>978105066.7</v>
+        <v>641782032.98</v>
       </c>
       <c r="J95" t="n">
-        <v>1984131036.7</v>
+        <v>1381661035.57</v>
       </c>
       <c r="K95" t="n">
-        <v>-27920903.3</v>
+        <v>-98096969.61</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.68</v>
+        <v>-2.42</v>
       </c>
       <c r="M95" t="n">
-        <v>48.51</v>
+        <v>34.15</v>
       </c>
       <c r="N95" t="n">
-        <v>22582528913.28</v>
+        <v>21695951572.48</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>301696.SZ</t>
+          <t>603135.SH</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>三瑞智能</t>
+          <t>中重科技</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>135.05</v>
+        <v>14.56</v>
       </c>
       <c r="E96" t="n">
-        <v>14.2362</v>
+        <v>6.0452</v>
       </c>
       <c r="F96" t="n">
-        <v>40.44</v>
+        <v>9.19</v>
       </c>
       <c r="G96" t="n">
-        <v>1630192479</v>
+        <v>1312783192</v>
       </c>
       <c r="H96" t="n">
-        <v>180830829.74</v>
+        <v>177229535.4</v>
       </c>
       <c r="I96" t="n">
-        <v>134204167.54</v>
+        <v>205204593.66</v>
       </c>
       <c r="J96" t="n">
-        <v>315034997.28</v>
+        <v>382434129.06</v>
       </c>
       <c r="K96" t="n">
-        <v>-46626662.2</v>
+        <v>27975058.26</v>
       </c>
       <c r="L96" t="n">
-        <v>-2.86</v>
+        <v>2.13</v>
       </c>
       <c r="M96" t="n">
-        <v>19.33</v>
+        <v>29.13</v>
       </c>
       <c r="N96" t="n">
-        <v>4062756957.7</v>
+        <v>9166074444.799999</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>301696.SZ</t>
+          <t>603178.SH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>三瑞智能</t>
+          <t>圣龙股份</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>135.05</v>
+        <v>15.68</v>
       </c>
       <c r="E97" t="n">
-        <v>14.2362</v>
+        <v>10.0351</v>
       </c>
       <c r="F97" t="n">
-        <v>40.44</v>
+        <v>2.47</v>
       </c>
       <c r="G97" t="n">
-        <v>2803961459</v>
+        <v>89144363</v>
       </c>
       <c r="H97" t="n">
-        <v>406803091.15</v>
+        <v>14050367</v>
       </c>
       <c r="I97" t="n">
-        <v>282054888.95</v>
+        <v>29146972</v>
       </c>
       <c r="J97" t="n">
-        <v>688857980.1</v>
+        <v>43197339</v>
       </c>
       <c r="K97" t="n">
-        <v>-124748202.2</v>
+        <v>15096605</v>
       </c>
       <c r="L97" t="n">
-        <v>-4.45</v>
+        <v>16.94</v>
       </c>
       <c r="M97" t="n">
-        <v>24.57</v>
+        <v>48.46</v>
       </c>
       <c r="N97" t="n">
-        <v>4062756957.7</v>
+        <v>3706938294.08</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>600076.SH</t>
+          <t>603270.SH</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>康欣新材</t>
+          <t>金帝股份</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3.6</v>
+        <v>34.3</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.0989</v>
+        <v>-1.6628</v>
       </c>
       <c r="F98" t="n">
-        <v>8.25</v>
+        <v>23.54</v>
       </c>
       <c r="G98" t="n">
-        <v>635927632</v>
+        <v>574460092</v>
       </c>
       <c r="H98" t="n">
-        <v>85808302.51000001</v>
+        <v>43861439.84</v>
       </c>
       <c r="I98" t="n">
-        <v>84277300</v>
+        <v>29356334.52</v>
       </c>
       <c r="J98" t="n">
-        <v>170085602.51</v>
+        <v>73217774.36</v>
       </c>
       <c r="K98" t="n">
-        <v>-1531002.51</v>
+        <v>-14505105.32</v>
       </c>
       <c r="L98" t="n">
-        <v>-0.24</v>
+        <v>-2.52</v>
       </c>
       <c r="M98" t="n">
-        <v>26.75</v>
+        <v>12.75</v>
       </c>
       <c r="N98" t="n">
-        <v>4840356121.2</v>
+        <v>2425581678.1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>600105.SH</t>
+          <t>603286.SH</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>日盈电子</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>56.21</v>
+        <v>56.96</v>
       </c>
       <c r="E99" t="n">
-        <v>-10.0064</v>
+        <v>10.0039</v>
       </c>
       <c r="F99" t="n">
-        <v>6.54</v>
+        <v>6.17</v>
       </c>
       <c r="G99" t="n">
-        <v>5514778832</v>
+        <v>542413647</v>
       </c>
       <c r="H99" t="n">
-        <v>784345960.1900001</v>
+        <v>65579078.6</v>
       </c>
       <c r="I99" t="n">
-        <v>667207782.16</v>
+        <v>126443910.6</v>
       </c>
       <c r="J99" t="n">
-        <v>1451553742.35</v>
+        <v>192022989.2</v>
       </c>
       <c r="K99" t="n">
-        <v>-117138178.03</v>
+        <v>60864832</v>
       </c>
       <c r="L99" t="n">
-        <v>-2.12</v>
+        <v>11.22</v>
       </c>
       <c r="M99" t="n">
-        <v>26.32</v>
+        <v>35.4</v>
       </c>
       <c r="N99" t="n">
-        <v>82178727820.42</v>
+        <v>6620757048.96</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>600119.SH</t>
+          <t>603327.SH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>*ST长投</t>
+          <t>福蓉科技</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4.7</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E100" t="n">
-        <v>4.9107</v>
+        <v>10.0621</v>
       </c>
       <c r="F100" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="G100" t="n">
-        <v>48344094</v>
+        <v>149230781</v>
       </c>
       <c r="H100" t="n">
-        <v>12223241</v>
+        <v>19017606</v>
       </c>
       <c r="I100" t="n">
-        <v>15977510</v>
+        <v>97301458.04000001</v>
       </c>
       <c r="J100" t="n">
-        <v>28200751</v>
+        <v>116319064.04</v>
       </c>
       <c r="K100" t="n">
-        <v>3754269</v>
+        <v>78283852.04000001</v>
       </c>
       <c r="L100" t="n">
-        <v>7.77</v>
+        <v>52.46</v>
       </c>
       <c r="M100" t="n">
-        <v>58.33</v>
+        <v>77.95</v>
       </c>
       <c r="N100" t="n">
-        <v>1716770739</v>
+        <v>9262769929.6</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>600156.SH</t>
+          <t>603338.SH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>华升股份</t>
+          <t>浙江鼎力</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>9.529999999999999</v>
+        <v>51.67</v>
       </c>
       <c r="E101" t="n">
-        <v>10.0462</v>
+        <v>10.0064</v>
       </c>
       <c r="F101" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="G101" t="n">
-        <v>144929896</v>
+        <v>1462846975</v>
       </c>
       <c r="H101" t="n">
-        <v>17451086</v>
+        <v>296256173.61</v>
       </c>
       <c r="I101" t="n">
-        <v>52090038</v>
+        <v>489593091.81</v>
       </c>
       <c r="J101" t="n">
-        <v>69541124</v>
+        <v>785849265.42</v>
       </c>
       <c r="K101" t="n">
-        <v>34638952</v>
+        <v>193336918.2</v>
       </c>
       <c r="L101" t="n">
-        <v>23.9</v>
+        <v>13.22</v>
       </c>
       <c r="M101" t="n">
-        <v>47.98</v>
+        <v>53.72</v>
       </c>
       <c r="N101" t="n">
-        <v>3832114990.06</v>
+        <v>26162994907.93</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5516</v>
+        <v>5517</v>
       </c>
       <c r="C2" t="n">
-        <v>3804</v>
+        <v>1876</v>
       </c>
       <c r="D2" t="n">
-        <v>1628</v>
+        <v>3541</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4043.6432</v>
+        <v>4041.2382</v>
       </c>
       <c r="E2" t="n">
-        <v>0.37</v>
+        <v>-0.06</v>
       </c>
       <c r="F2" t="n">
-        <v>14655.63</v>
+        <v>14321.13</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15597.5116</v>
+        <v>15416.804</v>
       </c>
       <c r="E3" t="n">
-        <v>0.64</v>
+        <v>-1.16</v>
       </c>
       <c r="F3" t="n">
-        <v>17168.8</v>
+        <v>16589.99</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4019.9341</v>
+        <v>3948.86</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.77</v>
       </c>
       <c r="F4" t="n">
-        <v>8038.08</v>
+        <v>7640.16</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4842.1737</v>
+        <v>4841.998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.62</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>9425.700000000001</v>
+        <v>9079.459999999999</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1975.6001</v>
+        <v>1996.1029</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.59</v>
+        <v>1.04</v>
       </c>
       <c r="F6" t="n">
-        <v>1748.47</v>
+        <v>1735.37</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8620.7886</v>
+        <v>8472.602800000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05</v>
+        <v>-1.72</v>
       </c>
       <c r="F7" t="n">
-        <v>6749.95</v>
+        <v>6550.13</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37621.03</v>
+        <v>34660.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34660.27</v>
+        <v>33069.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33069.39</v>
+        <v>36189.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36189.44</v>
+        <v>35753.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35753.91</v>
+        <v>35393.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35393.41</v>
+        <v>32938.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32938.2</v>
+        <v>36827.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36827.97</v>
+        <v>34739.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920510.BJ</t>
+          <t>688206.SH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>42.47</v>
       </c>
       <c r="D2" t="n">
-        <v>32.76</v>
+        <v>48.76</v>
       </c>
       <c r="E2" t="n">
-        <v>25.1</v>
+        <v>42.47</v>
       </c>
       <c r="F2" t="n">
-        <v>32.76</v>
+        <v>48.76</v>
       </c>
       <c r="G2" t="n">
-        <v>25.2</v>
+        <v>40.63</v>
       </c>
       <c r="H2" t="n">
-        <v>7.56</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>20.0098</v>
       </c>
       <c r="J2" t="n">
-        <v>289014.25</v>
+        <v>243507.23</v>
       </c>
       <c r="K2" t="n">
-        <v>875181.94008</v>
+        <v>1151606.395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920211.BJ</t>
+          <t>301317.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>123</v>
+        <v>51.07</v>
       </c>
       <c r="D3" t="n">
-        <v>158.28</v>
+        <v>62.21</v>
       </c>
       <c r="E3" t="n">
-        <v>123</v>
+        <v>51.07</v>
       </c>
       <c r="F3" t="n">
-        <v>158.28</v>
+        <v>62.21</v>
       </c>
       <c r="G3" t="n">
-        <v>121.76</v>
+        <v>51.84</v>
       </c>
       <c r="H3" t="n">
-        <v>36.52</v>
+        <v>10.37</v>
       </c>
       <c r="I3" t="n">
-        <v>29.9934</v>
+        <v>20.0039</v>
       </c>
       <c r="J3" t="n">
-        <v>19947.81</v>
+        <v>63225.43</v>
       </c>
       <c r="K3" t="n">
-        <v>294886.75359</v>
+        <v>368279.85363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>688039.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62.01</v>
+        <v>36.31</v>
       </c>
       <c r="D4" t="n">
-        <v>79.36</v>
+        <v>43.56</v>
       </c>
       <c r="E4" t="n">
-        <v>59.8</v>
+        <v>36.31</v>
       </c>
       <c r="F4" t="n">
-        <v>79.36</v>
+        <v>43.56</v>
       </c>
       <c r="G4" t="n">
-        <v>61.05</v>
+        <v>36.3</v>
       </c>
       <c r="H4" t="n">
-        <v>18.31</v>
+        <v>7.26</v>
       </c>
       <c r="I4" t="n">
-        <v>29.9918</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>196288.88</v>
+        <v>81169.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1287092.56683</v>
+        <v>335890.034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>920002.BJ</t>
+          <t>301191.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
+        <v>114.7</v>
       </c>
       <c r="D5" t="n">
-        <v>66.66</v>
+        <v>135.01</v>
       </c>
       <c r="E5" t="n">
-        <v>52.15</v>
+        <v>111.01</v>
       </c>
       <c r="F5" t="n">
-        <v>65.81999999999999</v>
+        <v>135.01</v>
       </c>
       <c r="G5" t="n">
-        <v>52.6</v>
+        <v>112.51</v>
       </c>
       <c r="H5" t="n">
-        <v>13.22</v>
+        <v>22.5</v>
       </c>
       <c r="I5" t="n">
-        <v>25.1331</v>
+        <v>19.9982</v>
       </c>
       <c r="J5" t="n">
-        <v>56254.51</v>
+        <v>138094.24</v>
       </c>
       <c r="K5" t="n">
-        <v>345911.14755</v>
+        <v>1699984.94668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>920096.BJ</t>
+          <t>300684.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42.8</v>
+        <v>62.8</v>
       </c>
       <c r="D6" t="n">
-        <v>51.62</v>
+        <v>74.41</v>
       </c>
       <c r="E6" t="n">
-        <v>42.25</v>
+        <v>62.05</v>
       </c>
       <c r="F6" t="n">
-        <v>51.62</v>
+        <v>74.41</v>
       </c>
       <c r="G6" t="n">
-        <v>42.78</v>
+        <v>62.01</v>
       </c>
       <c r="H6" t="n">
-        <v>8.84</v>
+        <v>12.4</v>
       </c>
       <c r="I6" t="n">
-        <v>20.6639</v>
+        <v>19.9968</v>
       </c>
       <c r="J6" t="n">
-        <v>44655.49</v>
+        <v>465692.31</v>
       </c>
       <c r="K6" t="n">
-        <v>214661.93739</v>
+        <v>3357374.94565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301199.SZ</t>
+          <t>688496.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.99</v>
+        <v>0.89</v>
       </c>
       <c r="D7" t="n">
-        <v>21.28</v>
+        <v>1.03</v>
       </c>
       <c r="E7" t="n">
-        <v>17.92</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="n">
-        <v>21.28</v>
+        <v>1.03</v>
       </c>
       <c r="G7" t="n">
-        <v>17.73</v>
+        <v>0.86</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>0.17</v>
       </c>
       <c r="I7" t="n">
-        <v>20.0226</v>
+        <v>19.7674</v>
       </c>
       <c r="J7" t="n">
-        <v>103286.37</v>
+        <v>191881.92</v>
       </c>
       <c r="K7" t="n">
-        <v>207344.82787</v>
+        <v>19296.294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300580.SZ</t>
+          <t>300716.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.95</v>
+        <v>24.5</v>
       </c>
       <c r="D8" t="n">
-        <v>25.96</v>
+        <v>29.3</v>
       </c>
       <c r="E8" t="n">
-        <v>21.83</v>
+        <v>24.5</v>
       </c>
       <c r="F8" t="n">
-        <v>25.96</v>
+        <v>29.09</v>
       </c>
       <c r="G8" t="n">
-        <v>21.63</v>
+        <v>24.43</v>
       </c>
       <c r="H8" t="n">
-        <v>4.33</v>
+        <v>4.66</v>
       </c>
       <c r="I8" t="n">
-        <v>20.0185</v>
+        <v>19.0749</v>
       </c>
       <c r="J8" t="n">
-        <v>438355.2</v>
+        <v>128780.77</v>
       </c>
       <c r="K8" t="n">
-        <v>1078714.72275</v>
+        <v>359021.32752</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300985.SZ</t>
+          <t>688689.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>43.1</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>49.67</v>
+        <v>80.8</v>
       </c>
       <c r="E9" t="n">
-        <v>41.78</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>49.67</v>
+        <v>80.75</v>
       </c>
       <c r="G9" t="n">
-        <v>41.39</v>
+        <v>68.03</v>
       </c>
       <c r="H9" t="n">
-        <v>8.279999999999999</v>
+        <v>12.72</v>
       </c>
       <c r="I9" t="n">
-        <v>20.0048</v>
+        <v>18.6976</v>
       </c>
       <c r="J9" t="n">
-        <v>80406.84</v>
+        <v>163432.76</v>
       </c>
       <c r="K9" t="n">
-        <v>369561.81226</v>
+        <v>1238065.315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300779.SZ</t>
+          <t>688103.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49.39</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>59.27</v>
+        <v>87.61</v>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>59.27</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>49.39</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>9.880000000000001</v>
+        <v>12.25</v>
       </c>
       <c r="I10" t="n">
-        <v>20.004</v>
+        <v>16.7785</v>
       </c>
       <c r="J10" t="n">
-        <v>129577.06</v>
+        <v>90667.86</v>
       </c>
       <c r="K10" t="n">
-        <v>724193.57203</v>
+        <v>751003.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300912.SZ</t>
+          <t>920699.BJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>28.56</v>
+        <v>129</v>
       </c>
       <c r="E11" t="n">
-        <v>24.62</v>
+        <v>103.3</v>
       </c>
       <c r="F11" t="n">
-        <v>28.56</v>
+        <v>125.65</v>
       </c>
       <c r="G11" t="n">
-        <v>23.8</v>
+        <v>109.01</v>
       </c>
       <c r="H11" t="n">
-        <v>4.76</v>
+        <v>16.64</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>15.2647</v>
       </c>
       <c r="J11" t="n">
-        <v>86276.21000000001</v>
+        <v>22359.98</v>
       </c>
       <c r="K11" t="n">
-        <v>235836.95164</v>
+        <v>258832.8312</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>688216.SH</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45.79</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>47.78</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>41.04</v>
+        <v>55.56</v>
       </c>
       <c r="F2" t="n">
-        <v>41.04</v>
+        <v>55.56</v>
       </c>
       <c r="G2" t="n">
-        <v>51.3</v>
+        <v>79.36</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.26</v>
+        <v>-23.8</v>
       </c>
       <c r="I2" t="n">
-        <v>-20</v>
+        <v>-29.9899</v>
       </c>
       <c r="J2" t="n">
-        <v>213106.52</v>
+        <v>167524.98</v>
       </c>
       <c r="K2" t="n">
-        <v>915749.081</v>
+        <v>1060648.94366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>688096.SH</t>
+          <t>688622.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.23</v>
+        <v>118.88</v>
       </c>
       <c r="D3" t="n">
-        <v>12.33</v>
+        <v>129.4</v>
       </c>
       <c r="E3" t="n">
-        <v>9.93</v>
+        <v>102.3</v>
       </c>
       <c r="F3" t="n">
-        <v>9.93</v>
+        <v>102.3</v>
       </c>
       <c r="G3" t="n">
-        <v>12.41</v>
+        <v>127.88</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.48</v>
+        <v>-25.58</v>
       </c>
       <c r="I3" t="n">
-        <v>-19.9839</v>
+        <v>-20.0031</v>
       </c>
       <c r="J3" t="n">
-        <v>295457.68</v>
+        <v>18597.38</v>
       </c>
       <c r="K3" t="n">
-        <v>315848.658</v>
+        <v>199793.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688797.SH</t>
+          <t>688669.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>648</v>
+        <v>113.22</v>
       </c>
       <c r="D4" t="n">
-        <v>655</v>
+        <v>114.98</v>
       </c>
       <c r="E4" t="n">
-        <v>538</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>540.1</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>668.01</v>
+        <v>112.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-127.91</v>
+        <v>-22.44</v>
       </c>
       <c r="I4" t="n">
-        <v>-19.1479</v>
+        <v>-20</v>
       </c>
       <c r="J4" t="n">
-        <v>108526.64</v>
+        <v>74281.25999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>6289738.191</v>
+        <v>725707.421</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688106.SH</t>
+          <t>301197.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.51</v>
+        <v>30.3</v>
       </c>
       <c r="D5" t="n">
-        <v>47.3</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>39.92</v>
+        <v>26.49</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>26.49</v>
       </c>
       <c r="G5" t="n">
-        <v>47.74</v>
+        <v>33.11</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.74</v>
+        <v>-6.62</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.2128</v>
+        <v>-19.994</v>
       </c>
       <c r="J5" t="n">
-        <v>987892.01</v>
+        <v>92953.58</v>
       </c>
       <c r="K5" t="n">
-        <v>4165239.407</v>
+        <v>257434.73912</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688689.SH</t>
+          <t>300061.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>78</v>
+        <v>6.83</v>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>6.99</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>6.13</v>
       </c>
       <c r="F6" t="n">
-        <v>68.03</v>
+        <v>6.19</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>7.48</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.97</v>
+        <v>-1.29</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.9625</v>
+        <v>-17.246</v>
       </c>
       <c r="J6" t="n">
-        <v>158489.24</v>
+        <v>657349.36</v>
       </c>
       <c r="K6" t="n">
-        <v>1139494.094</v>
+        <v>422087.1682</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300323.SZ</t>
+          <t>001248.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.82</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="n">
-        <v>20.39</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="n">
-        <v>17.9</v>
+        <v>18.15</v>
       </c>
       <c r="F7" t="n">
-        <v>17.95</v>
+        <v>18.37</v>
       </c>
       <c r="G7" t="n">
-        <v>20.69</v>
+        <v>22.02</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.74</v>
+        <v>-3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.2431</v>
+        <v>-16.5758</v>
       </c>
       <c r="J7" t="n">
-        <v>1653695.18</v>
+        <v>3696906.37</v>
       </c>
       <c r="K7" t="n">
-        <v>3081140.02194</v>
+        <v>7131925.09688</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300655.SZ</t>
+          <t>688257.SH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>110.37</v>
       </c>
       <c r="D8" t="n">
-        <v>21.7</v>
+        <v>112.22</v>
       </c>
       <c r="E8" t="n">
-        <v>19.16</v>
+        <v>92.81</v>
       </c>
       <c r="F8" t="n">
-        <v>19.17</v>
+        <v>92.88</v>
       </c>
       <c r="G8" t="n">
-        <v>21.93</v>
+        <v>110.45</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.76</v>
+        <v>-17.57</v>
       </c>
       <c r="I8" t="n">
-        <v>-12.5855</v>
+        <v>-15.9077</v>
       </c>
       <c r="J8" t="n">
-        <v>1855800.8</v>
+        <v>298368.36</v>
       </c>
       <c r="K8" t="n">
-        <v>3689235.69411</v>
+        <v>2975348.524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>301629.SZ</t>
+          <t>688507.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>398.01</v>
+        <v>249.59</v>
       </c>
       <c r="D9" t="n">
-        <v>401.99</v>
+        <v>251.51</v>
       </c>
       <c r="E9" t="n">
-        <v>360</v>
+        <v>210.8</v>
       </c>
       <c r="F9" t="n">
-        <v>360.69</v>
+        <v>212</v>
       </c>
       <c r="G9" t="n">
-        <v>407</v>
+        <v>249.51</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.31</v>
+        <v>-37.51</v>
       </c>
       <c r="I9" t="n">
-        <v>-11.3784</v>
+        <v>-15.0335</v>
       </c>
       <c r="J9" t="n">
-        <v>22968.45</v>
+        <v>116741.93</v>
       </c>
       <c r="K9" t="n">
-        <v>872483.81865</v>
+        <v>2612866.294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>301319.SZ</t>
+          <t>300607.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>177.8</v>
+        <v>50.01</v>
       </c>
       <c r="D10" t="n">
-        <v>181.24</v>
+        <v>50.94</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>44.9</v>
       </c>
       <c r="F10" t="n">
-        <v>157.4</v>
+        <v>45.01</v>
       </c>
       <c r="G10" t="n">
-        <v>176.99</v>
+        <v>52.96</v>
       </c>
       <c r="H10" t="n">
-        <v>-19.59</v>
+        <v>-7.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-11.0684</v>
+        <v>-15.0113</v>
       </c>
       <c r="J10" t="n">
-        <v>110558.1</v>
+        <v>818625.64</v>
       </c>
       <c r="K10" t="n">
-        <v>1823089.48516</v>
+        <v>3861226.19841</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>301177.SZ</t>
+          <t>920510.BJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.75</v>
+        <v>31.45</v>
       </c>
       <c r="D11" t="n">
-        <v>30.04</v>
+        <v>31.86</v>
       </c>
       <c r="E11" t="n">
-        <v>26.33</v>
+        <v>27.88</v>
       </c>
       <c r="F11" t="n">
-        <v>26.88</v>
+        <v>27.9</v>
       </c>
       <c r="G11" t="n">
-        <v>30.05</v>
+        <v>32.76</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.17</v>
+        <v>-4.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-10.5491</v>
+        <v>-14.8352</v>
       </c>
       <c r="J11" t="n">
-        <v>64899.64</v>
+        <v>228405.05</v>
       </c>
       <c r="K11" t="n">
-        <v>177593.20339</v>
+        <v>675277.54368</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,7 +1819,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1833,37 +1833,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7561</v>
+        <v>-8.8889</v>
       </c>
       <c r="F2" t="n">
-        <v>4.96</v>
+        <v>5.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2673076</v>
+        <v>3103588</v>
       </c>
       <c r="H2" t="n">
-        <v>1277293</v>
+        <v>1675774.41</v>
       </c>
       <c r="I2" t="n">
-        <v>1758769.41</v>
+        <v>1495067.71</v>
       </c>
       <c r="J2" t="n">
-        <v>3036062.41</v>
+        <v>3170842.12</v>
       </c>
       <c r="K2" t="n">
-        <v>481476.41</v>
+        <v>-180706.7</v>
       </c>
       <c r="L2" t="n">
-        <v>18.01</v>
+        <v>-5.82</v>
       </c>
       <c r="M2" t="n">
-        <v>113.58</v>
+        <v>102.17</v>
       </c>
       <c r="N2" t="n">
-        <v>56830080.6</v>
+        <v>51778517.88</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1874,766 +1874,766 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000506.SZ</t>
+          <t>000066.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>招金黄金</t>
+          <t>中国长城</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.87</v>
+        <v>18.82</v>
       </c>
       <c r="E3" t="n">
-        <v>9.992100000000001</v>
+        <v>9.994199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.92</v>
+        <v>6.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1006370120</v>
+        <v>3729009536</v>
       </c>
       <c r="H3" t="n">
-        <v>143682523.88</v>
+        <v>304289316.12</v>
       </c>
       <c r="I3" t="n">
-        <v>216989710.16</v>
+        <v>931375363.97</v>
       </c>
       <c r="J3" t="n">
-        <v>360672234.04</v>
+        <v>1235664680.09</v>
       </c>
       <c r="K3" t="n">
-        <v>73307186.28</v>
+        <v>627086047.85</v>
       </c>
       <c r="L3" t="n">
-        <v>7.28</v>
+        <v>16.82</v>
       </c>
       <c r="M3" t="n">
-        <v>35.84</v>
+        <v>33.14</v>
       </c>
       <c r="N3" t="n">
-        <v>12881165549.07</v>
+        <v>60704847951.16</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000566.SZ</t>
+          <t>000301.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>海南海药</t>
+          <t>东方盛虹</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.14</v>
+        <v>13.81</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6556</v>
+        <v>10.0398</v>
       </c>
       <c r="F4" t="n">
-        <v>27.67</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>2194105928</v>
+        <v>1586288017</v>
       </c>
       <c r="H4" t="n">
-        <v>279408735.57</v>
+        <v>434340967.17</v>
       </c>
       <c r="I4" t="n">
-        <v>182934819.97</v>
+        <v>104302693.49</v>
       </c>
       <c r="J4" t="n">
-        <v>462343555.54</v>
+        <v>538643660.66</v>
       </c>
       <c r="K4" t="n">
-        <v>-96473915.59999999</v>
+        <v>-330038273.68</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.4</v>
+        <v>-20.81</v>
       </c>
       <c r="M4" t="n">
-        <v>21.07</v>
+        <v>33.96</v>
       </c>
       <c r="N4" t="n">
-        <v>7961956786.62</v>
+        <v>91261630411.88</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000576.SZ</t>
+          <t>000566.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>甘化科工</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.140000000000001</v>
+        <v>6.43</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>4.7231</v>
       </c>
       <c r="F5" t="n">
-        <v>5.63</v>
+        <v>26.98</v>
       </c>
       <c r="G5" t="n">
-        <v>280654452</v>
+        <v>2182211346</v>
       </c>
       <c r="H5" t="n">
-        <v>42205475</v>
+        <v>262437309.01</v>
       </c>
       <c r="I5" t="n">
-        <v>93717574.17</v>
+        <v>170237339.71</v>
       </c>
       <c r="J5" t="n">
-        <v>135923049.17</v>
+        <v>432674648.72</v>
       </c>
       <c r="K5" t="n">
-        <v>51512099.17</v>
+        <v>-92199969.3</v>
       </c>
       <c r="L5" t="n">
-        <v>18.35</v>
+        <v>-4.23</v>
       </c>
       <c r="M5" t="n">
-        <v>48.43</v>
+        <v>19.83</v>
       </c>
       <c r="N5" t="n">
-        <v>3531256224.54</v>
+        <v>8338010120.19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000592.SZ</t>
+          <t>000566.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>平潭发展</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.98</v>
+        <v>6.43</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.0515</v>
+        <v>4.7231</v>
       </c>
       <c r="F6" t="n">
-        <v>13.74</v>
+        <v>26.98</v>
       </c>
       <c r="G6" t="n">
-        <v>1863641622</v>
+        <v>5121768679</v>
       </c>
       <c r="H6" t="n">
-        <v>401791971.74</v>
+        <v>466098964.86</v>
       </c>
       <c r="I6" t="n">
-        <v>151872444.72</v>
+        <v>417178373.52</v>
       </c>
       <c r="J6" t="n">
-        <v>553664416.46</v>
+        <v>883277338.38</v>
       </c>
       <c r="K6" t="n">
-        <v>-249919527.02</v>
+        <v>-48920591.34</v>
       </c>
       <c r="L6" t="n">
-        <v>-13.41</v>
+        <v>-0.96</v>
       </c>
       <c r="M6" t="n">
-        <v>29.71</v>
+        <v>17.25</v>
       </c>
       <c r="N6" t="n">
-        <v>13367345294.02</v>
+        <v>8338010120.19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000595.SZ</t>
+          <t>000657.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>宝塔实业</t>
+          <t>中钨高新</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.24</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0529</v>
+        <v>-10</v>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>7.49</v>
       </c>
       <c r="G7" t="n">
-        <v>103089945</v>
+        <v>9138123574</v>
       </c>
       <c r="H7" t="n">
-        <v>44165823</v>
+        <v>1336370188.53</v>
       </c>
       <c r="I7" t="n">
-        <v>42401727</v>
+        <v>1411114111</v>
       </c>
       <c r="J7" t="n">
-        <v>86567550</v>
+        <v>2747484299.53</v>
       </c>
       <c r="K7" t="n">
-        <v>-1764096</v>
+        <v>74743922.47</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.71</v>
+        <v>0.82</v>
       </c>
       <c r="M7" t="n">
-        <v>83.97</v>
+        <v>30.07</v>
       </c>
       <c r="N7" t="n">
-        <v>7105215723.84</v>
+        <v>116902373017.32</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000656.SZ</t>
+          <t>000908.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>金科股份</t>
+          <t>石药景峰</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.3</v>
+        <v>7.17</v>
       </c>
       <c r="E8" t="n">
-        <v>10.1695</v>
+        <v>4.2151</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07000000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="G8" t="n">
-        <v>14173972</v>
+        <v>613837474</v>
       </c>
       <c r="H8" t="n">
-        <v>4419295.62</v>
+        <v>62756206.04</v>
       </c>
       <c r="I8" t="n">
-        <v>10516748</v>
+        <v>73266666</v>
       </c>
       <c r="J8" t="n">
-        <v>14936043.62</v>
+        <v>136022872.04</v>
       </c>
       <c r="K8" t="n">
-        <v>6097452.38</v>
+        <v>10510459.96</v>
       </c>
       <c r="L8" t="n">
-        <v>43.02</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>105.38</v>
+        <v>22.16</v>
       </c>
       <c r="N8" t="n">
-        <v>9863553709.1</v>
+        <v>6307980662.67</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000838.SZ</t>
+          <t>000938.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*ST发展</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.77</v>
+        <v>33.31</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7337</v>
+        <v>10.0066</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>11.04</v>
       </c>
       <c r="G9" t="n">
-        <v>96595868</v>
+        <v>9933778020</v>
       </c>
       <c r="H9" t="n">
-        <v>10596221</v>
+        <v>1160550445.41</v>
       </c>
       <c r="I9" t="n">
-        <v>18108766.44</v>
+        <v>1517813729.76</v>
       </c>
       <c r="J9" t="n">
-        <v>28704987.44</v>
+        <v>2678364175.17</v>
       </c>
       <c r="K9" t="n">
-        <v>7512545.44</v>
+        <v>357263284.35</v>
       </c>
       <c r="L9" t="n">
-        <v>7.78</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>29.72</v>
+        <v>26.96</v>
       </c>
       <c r="N9" t="n">
-        <v>1865165563.35</v>
+        <v>95269020770.94</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000908.SZ</t>
+          <t>000962.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>石药景峰</t>
+          <t>东方钽业</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.88</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08</v>
+        <v>-10.0053</v>
       </c>
       <c r="F10" t="n">
-        <v>8.859999999999999</v>
+        <v>6.64</v>
       </c>
       <c r="G10" t="n">
-        <v>598622860</v>
+        <v>2382389162</v>
       </c>
       <c r="H10" t="n">
-        <v>62693625.42</v>
+        <v>689569795.36</v>
       </c>
       <c r="I10" t="n">
-        <v>55581591.9</v>
+        <v>518596826.72</v>
       </c>
       <c r="J10" t="n">
-        <v>118275217.32</v>
+        <v>1208166622.08</v>
       </c>
       <c r="K10" t="n">
-        <v>-7112033.52</v>
+        <v>-170972968.64</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.19</v>
+        <v>-7.18</v>
       </c>
       <c r="M10" t="n">
-        <v>19.76</v>
+        <v>50.71</v>
       </c>
       <c r="N10" t="n">
-        <v>6052846158.88</v>
+        <v>34216086320</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>000975.SZ</t>
+          <t>001399.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>山金国际</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.84</v>
+        <v>38.12</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9778</v>
+        <v>-9.5396</v>
       </c>
       <c r="F11" t="n">
-        <v>2.65</v>
+        <v>35.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3231971328</v>
+        <v>6010094635</v>
       </c>
       <c r="H11" t="n">
-        <v>476246385.64</v>
+        <v>684753827.04</v>
       </c>
       <c r="I11" t="n">
-        <v>723611189.98</v>
+        <v>929699798.1799999</v>
       </c>
       <c r="J11" t="n">
-        <v>1199857575.62</v>
+        <v>1614453625.22</v>
       </c>
       <c r="K11" t="n">
-        <v>247364804.34</v>
+        <v>244945971.14</v>
       </c>
       <c r="L11" t="n">
-        <v>7.65</v>
+        <v>4.08</v>
       </c>
       <c r="M11" t="n">
-        <v>37.12</v>
+        <v>26.86</v>
       </c>
       <c r="N11" t="n">
-        <v>50061028369.28</v>
+        <v>16413203785.72</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>001317.SZ</t>
+          <t>002025.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>三羊马</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48.43</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.9932</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>4.84</v>
+        <v>6.35</v>
       </c>
       <c r="G12" t="n">
-        <v>429982738</v>
+        <v>2522432148</v>
       </c>
       <c r="H12" t="n">
-        <v>50563819</v>
+        <v>275589905.13</v>
       </c>
       <c r="I12" t="n">
-        <v>77136111</v>
+        <v>413893177.88</v>
       </c>
       <c r="J12" t="n">
-        <v>127699930</v>
+        <v>689483083.01</v>
       </c>
       <c r="K12" t="n">
-        <v>26572292</v>
+        <v>138303272.75</v>
       </c>
       <c r="L12" t="n">
-        <v>6.18</v>
+        <v>5.48</v>
       </c>
       <c r="M12" t="n">
-        <v>29.7</v>
+        <v>27.33</v>
       </c>
       <c r="N12" t="n">
-        <v>4139865315.89</v>
+        <v>41787930498.93</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>001399.SZ</t>
+          <t>002072.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>凯瑞德</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>42.14</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.995699999999999</v>
+        <v>-7.7801</v>
       </c>
       <c r="F13" t="n">
-        <v>6.15</v>
+        <v>17.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1146305084</v>
+        <v>621588377</v>
       </c>
       <c r="H13" t="n">
-        <v>105064640.14</v>
+        <v>107952232.69</v>
       </c>
       <c r="I13" t="n">
-        <v>125822126.54</v>
+        <v>80792562</v>
       </c>
       <c r="J13" t="n">
-        <v>230886766.68</v>
+        <v>188744794.69</v>
       </c>
       <c r="K13" t="n">
-        <v>20757486.4</v>
+        <v>-27159670.69</v>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>-4.37</v>
       </c>
       <c r="M13" t="n">
-        <v>20.14</v>
+        <v>30.36</v>
       </c>
       <c r="N13" t="n">
-        <v>18144082044.34</v>
+        <v>3267357702</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002020.SZ</t>
+          <t>002080.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>京新药业</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.19</v>
+        <v>76.58</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6153</v>
+        <v>-10.0012</v>
       </c>
       <c r="F14" t="n">
-        <v>8.710000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="G14" t="n">
-        <v>1439720588</v>
+        <v>3791204245</v>
       </c>
       <c r="H14" t="n">
-        <v>189451248.9</v>
+        <v>726709624.33</v>
       </c>
       <c r="I14" t="n">
-        <v>183387704.99</v>
+        <v>857403957.33</v>
       </c>
       <c r="J14" t="n">
-        <v>372838953.89</v>
+        <v>1584113581.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-6063543.91</v>
+        <v>130694333</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.42</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>25.9</v>
+        <v>41.78</v>
       </c>
       <c r="N14" t="n">
-        <v>10997079008.65</v>
+        <v>128510704062.72</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002056.SZ</t>
+          <t>002106.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>横店东磁</t>
+          <t>莱宝高科</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32.82</v>
+        <v>13.17</v>
       </c>
       <c r="E15" t="n">
-        <v>7.045</v>
+        <v>-9.9795</v>
       </c>
       <c r="F15" t="n">
-        <v>7.74</v>
+        <v>9.32</v>
       </c>
       <c r="G15" t="n">
-        <v>4065511535</v>
+        <v>3039420014</v>
       </c>
       <c r="H15" t="n">
-        <v>468170764.44</v>
+        <v>314606756.34</v>
       </c>
       <c r="I15" t="n">
-        <v>1018191968.29</v>
+        <v>226521032.24</v>
       </c>
       <c r="J15" t="n">
-        <v>1486362732.73</v>
+        <v>541127788.58</v>
       </c>
       <c r="K15" t="n">
-        <v>550021203.85</v>
+        <v>-88085724.09999999</v>
       </c>
       <c r="L15" t="n">
-        <v>13.53</v>
+        <v>-2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>36.56</v>
+        <v>17.8</v>
       </c>
       <c r="N15" t="n">
-        <v>53333537407.38</v>
+        <v>9283565477.219999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002106.SZ</t>
+          <t>002119.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>莱宝高科</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.63</v>
+        <v>35.14</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.969200000000001</v>
+        <v>-9.989800000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>8.58</v>
+        <v>20.54</v>
       </c>
       <c r="G16" t="n">
-        <v>898007715</v>
+        <v>2833924768</v>
       </c>
       <c r="H16" t="n">
-        <v>72619114.23</v>
+        <v>605053506.88</v>
       </c>
       <c r="I16" t="n">
-        <v>80227195</v>
+        <v>408373901.97</v>
       </c>
       <c r="J16" t="n">
-        <v>152846309.23</v>
+        <v>1013427408.85</v>
       </c>
       <c r="K16" t="n">
-        <v>7608080.77</v>
+        <v>-196679604.91</v>
       </c>
       <c r="L16" t="n">
-        <v>0.85</v>
+        <v>-6.94</v>
       </c>
       <c r="M16" t="n">
-        <v>17.02</v>
+        <v>35.76</v>
       </c>
       <c r="N16" t="n">
-        <v>10312723077.58</v>
+        <v>13187479760</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2644,4667 +2644,4368 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002122.SZ</t>
+          <t>002141.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ST汇洲</t>
+          <t>贤丰控股</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.55</v>
+        <v>5.65</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9383</v>
+        <v>9.9222</v>
       </c>
       <c r="F17" t="n">
-        <v>1.34</v>
+        <v>17.37</v>
       </c>
       <c r="G17" t="n">
-        <v>115625768</v>
+        <v>1908096239</v>
       </c>
       <c r="H17" t="n">
-        <v>13240552</v>
+        <v>200644731</v>
       </c>
       <c r="I17" t="n">
-        <v>15850516</v>
+        <v>281001434.8</v>
       </c>
       <c r="J17" t="n">
-        <v>29091068</v>
+        <v>481646165.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2609964</v>
+        <v>80356703.8</v>
       </c>
       <c r="L17" t="n">
-        <v>2.26</v>
+        <v>4.21</v>
       </c>
       <c r="M17" t="n">
-        <v>25.16</v>
+        <v>25.24</v>
       </c>
       <c r="N17" t="n">
-        <v>5068685905.65</v>
+        <v>5836087258.7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002193.SZ</t>
+          <t>002245.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ST如意</t>
+          <t>蔚蓝锂芯</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.59</v>
+        <v>22.37</v>
       </c>
       <c r="E18" t="n">
-        <v>5.0343</v>
+        <v>9.9803</v>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>8.5</v>
       </c>
       <c r="G18" t="n">
-        <v>58125873</v>
+        <v>3022765052</v>
       </c>
       <c r="H18" t="n">
-        <v>14376781</v>
+        <v>454398647.49</v>
       </c>
       <c r="I18" t="n">
-        <v>12818356</v>
+        <v>866243411.62</v>
       </c>
       <c r="J18" t="n">
-        <v>27195137</v>
+        <v>1320642059.11</v>
       </c>
       <c r="K18" t="n">
-        <v>-1558425</v>
+        <v>411844764.13</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.68</v>
+        <v>13.62</v>
       </c>
       <c r="M18" t="n">
-        <v>46.79</v>
+        <v>43.69</v>
       </c>
       <c r="N18" t="n">
-        <v>1201267489.5</v>
+        <v>35939636586.46</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002199.SZ</t>
+          <t>002245.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>*ST东晶</t>
+          <t>蔚蓝锂芯</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.89</v>
+        <v>22.37</v>
       </c>
       <c r="E19" t="n">
-        <v>4.9674</v>
+        <v>9.9803</v>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>151871152</v>
+        <v>9417287170</v>
       </c>
       <c r="H19" t="n">
-        <v>48043056</v>
+        <v>1560081174.46</v>
       </c>
       <c r="I19" t="n">
-        <v>35881101</v>
+        <v>2069840183.58</v>
       </c>
       <c r="J19" t="n">
-        <v>83924157</v>
+        <v>3629921358.04</v>
       </c>
       <c r="K19" t="n">
-        <v>-12161955</v>
+        <v>509759009.12</v>
       </c>
       <c r="L19" t="n">
-        <v>-8.01</v>
+        <v>5.41</v>
       </c>
       <c r="M19" t="n">
-        <v>55.26</v>
+        <v>38.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2976714678.77</v>
+        <v>35939636586.46</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002235.SZ</t>
+          <t>002354.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>安妮股份</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.31</v>
+        <v>8.43</v>
       </c>
       <c r="E20" t="n">
-        <v>8.0046</v>
+        <v>-10.032</v>
       </c>
       <c r="F20" t="n">
-        <v>10.85</v>
+        <v>29.54</v>
       </c>
       <c r="G20" t="n">
-        <v>1006166891</v>
+        <v>4307496781</v>
       </c>
       <c r="H20" t="n">
-        <v>141385423.28</v>
+        <v>651376706.88</v>
       </c>
       <c r="I20" t="n">
-        <v>211966338.82</v>
+        <v>453451014.09</v>
       </c>
       <c r="J20" t="n">
-        <v>353351762.1</v>
+        <v>1104827720.97</v>
       </c>
       <c r="K20" t="n">
-        <v>70580915.54000001</v>
+        <v>-197925692.79</v>
       </c>
       <c r="L20" t="n">
-        <v>7.01</v>
+        <v>-4.59</v>
       </c>
       <c r="M20" t="n">
-        <v>35.12</v>
+        <v>25.65</v>
       </c>
       <c r="N20" t="n">
-        <v>5153813991.62</v>
+        <v>13704598556.97</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002294.SZ</t>
+          <t>002396.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40.08</v>
+        <v>25.74</v>
       </c>
       <c r="E21" t="n">
-        <v>9.989000000000001</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="G21" t="n">
-        <v>2505207346</v>
+        <v>1339129705</v>
       </c>
       <c r="H21" t="n">
-        <v>213350700.46</v>
+        <v>171033390.72</v>
       </c>
       <c r="I21" t="n">
-        <v>320285063.46</v>
+        <v>370088137.32</v>
       </c>
       <c r="J21" t="n">
-        <v>533635763.92</v>
+        <v>541121528.04</v>
       </c>
       <c r="K21" t="n">
-        <v>106934363</v>
+        <v>199054746.6</v>
       </c>
       <c r="L21" t="n">
-        <v>4.27</v>
+        <v>14.86</v>
       </c>
       <c r="M21" t="n">
-        <v>21.3</v>
+        <v>40.41</v>
       </c>
       <c r="N21" t="n">
-        <v>44671794698.88</v>
+        <v>19495864828.44</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002294.SZ</t>
+          <t>002636.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>金安国纪</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>40.08</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>9.989000000000001</v>
+        <v>-9.4998</v>
       </c>
       <c r="F22" t="n">
-        <v>5.82</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>6366586753</v>
+        <v>6876329037</v>
       </c>
       <c r="H22" t="n">
-        <v>586166054.61</v>
+        <v>1319459989.33</v>
       </c>
       <c r="I22" t="n">
-        <v>734529981.53</v>
+        <v>1344441924.19</v>
       </c>
       <c r="J22" t="n">
-        <v>1320696036.14</v>
+        <v>2663901913.52</v>
       </c>
       <c r="K22" t="n">
-        <v>148363926.92</v>
+        <v>24981934.86</v>
       </c>
       <c r="L22" t="n">
-        <v>2.33</v>
+        <v>0.36</v>
       </c>
       <c r="M22" t="n">
-        <v>20.74</v>
+        <v>38.74</v>
       </c>
       <c r="N22" t="n">
-        <v>44671794698.88</v>
+        <v>70106489211.42999</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002306.SZ</t>
+          <t>002729.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ST云网</t>
+          <t>好利科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.08</v>
+        <v>17.48</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4826</v>
+        <v>-1.7978</v>
       </c>
       <c r="F23" t="n">
-        <v>1.35</v>
+        <v>13.16</v>
       </c>
       <c r="G23" t="n">
-        <v>76489359</v>
+        <v>410298002</v>
       </c>
       <c r="H23" t="n">
-        <v>9076501</v>
+        <v>84295538.59999999</v>
       </c>
       <c r="I23" t="n">
-        <v>15992458</v>
+        <v>47135689.56</v>
       </c>
       <c r="J23" t="n">
-        <v>25068959</v>
+        <v>131431228.16</v>
       </c>
       <c r="K23" t="n">
-        <v>6915957</v>
+        <v>-37159849.04</v>
       </c>
       <c r="L23" t="n">
-        <v>9.039999999999999</v>
+        <v>-9.06</v>
       </c>
       <c r="M23" t="n">
-        <v>32.77</v>
+        <v>32.03</v>
       </c>
       <c r="N23" t="n">
-        <v>1690392169.44</v>
+        <v>3067059451.16</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002353.SZ</t>
+          <t>002747.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>杰瑞股份</t>
+          <t>埃斯顿</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>161.46</v>
+        <v>46.03</v>
       </c>
       <c r="E24" t="n">
-        <v>10.0014</v>
+        <v>2.8144</v>
       </c>
       <c r="F24" t="n">
-        <v>2.36</v>
+        <v>24.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2566550608</v>
+        <v>9048470128</v>
       </c>
       <c r="H24" t="n">
-        <v>479458956.27</v>
+        <v>934589518.9</v>
       </c>
       <c r="I24" t="n">
-        <v>772283403.35</v>
+        <v>1131252641.49</v>
       </c>
       <c r="J24" t="n">
-        <v>1251742359.62</v>
+        <v>2065842160.39</v>
       </c>
       <c r="K24" t="n">
-        <v>292824447.08</v>
+        <v>196663122.59</v>
       </c>
       <c r="L24" t="n">
-        <v>11.41</v>
+        <v>2.17</v>
       </c>
       <c r="M24" t="n">
-        <v>48.77</v>
+        <v>22.83</v>
       </c>
       <c r="N24" t="n">
-        <v>111575094777.9</v>
+        <v>36014085026.84</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002354.SZ</t>
+          <t>002767.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>先锋电子</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.369999999999999</v>
+        <v>19.84</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.381</v>
+        <v>9.9778</v>
       </c>
       <c r="F25" t="n">
-        <v>38.07</v>
+        <v>1.47</v>
       </c>
       <c r="G25" t="n">
-        <v>5895329300</v>
+        <v>124179141</v>
       </c>
       <c r="H25" t="n">
-        <v>692234133.8200001</v>
+        <v>24365482</v>
       </c>
       <c r="I25" t="n">
-        <v>842465328.16</v>
+        <v>40199721</v>
       </c>
       <c r="J25" t="n">
-        <v>1534699461.98</v>
+        <v>64565203</v>
       </c>
       <c r="K25" t="n">
-        <v>150231194.34</v>
+        <v>15834239</v>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>12.75</v>
       </c>
       <c r="M25" t="n">
-        <v>26.03</v>
+        <v>51.99</v>
       </c>
       <c r="N25" t="n">
-        <v>15232750709.23</v>
+        <v>2583453120.64</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>002808.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>恒久退</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>232.73</v>
+        <v>0.24</v>
       </c>
       <c r="E26" t="n">
-        <v>4.9847</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8.960000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>27821158389</v>
+        <v>4275713</v>
       </c>
       <c r="H26" t="n">
-        <v>3137110889.15</v>
+        <v>2591485.68</v>
       </c>
       <c r="I26" t="n">
-        <v>4262145497.45</v>
+        <v>2773845.19</v>
       </c>
       <c r="J26" t="n">
-        <v>7399256386.6</v>
+        <v>5365330.87</v>
       </c>
       <c r="K26" t="n">
-        <v>1125034608.3</v>
+        <v>182359.51</v>
       </c>
       <c r="L26" t="n">
-        <v>4.04</v>
+        <v>4.27</v>
       </c>
       <c r="M26" t="n">
-        <v>26.6</v>
+        <v>125.48</v>
       </c>
       <c r="N26" t="n">
-        <v>322638654593.79</v>
+        <v>44846653.44</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002407.SZ</t>
+          <t>002860.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>多氟多</t>
+          <t>星帅尔</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49.34</v>
+        <v>17.56</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.9964</v>
+        <v>10.0251</v>
       </c>
       <c r="F27" t="n">
-        <v>22.12</v>
+        <v>12.37</v>
       </c>
       <c r="G27" t="n">
-        <v>11962936166</v>
+        <v>1694124496</v>
       </c>
       <c r="H27" t="n">
-        <v>1641684265.01</v>
+        <v>278196306.22</v>
       </c>
       <c r="I27" t="n">
-        <v>1550329683.81</v>
+        <v>278156775.69</v>
       </c>
       <c r="J27" t="n">
-        <v>3192013948.82</v>
+        <v>556353081.91</v>
       </c>
       <c r="K27" t="n">
-        <v>-91354581.2</v>
+        <v>-39530.53</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>26.68</v>
+        <v>32.84</v>
       </c>
       <c r="N27" t="n">
-        <v>53226380802.3</v>
+        <v>6040160928.08</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002422.SZ</t>
+          <t>002898.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>科伦药业</t>
+          <t>赛隆退</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47.98</v>
+        <v>0.35</v>
       </c>
       <c r="E28" t="n">
-        <v>7.2179</v>
+        <v>-2.7778</v>
       </c>
       <c r="F28" t="n">
-        <v>4.13</v>
+        <v>6.89</v>
       </c>
       <c r="G28" t="n">
-        <v>6914975974</v>
+        <v>2408372</v>
       </c>
       <c r="H28" t="n">
-        <v>1130735839.31</v>
+        <v>1564677</v>
       </c>
       <c r="I28" t="n">
-        <v>604224972.96</v>
+        <v>938179</v>
       </c>
       <c r="J28" t="n">
-        <v>1734960812.27</v>
+        <v>2502856</v>
       </c>
       <c r="K28" t="n">
-        <v>-526510866.35</v>
+        <v>-626498</v>
       </c>
       <c r="L28" t="n">
-        <v>-7.61</v>
+        <v>-26.01</v>
       </c>
       <c r="M28" t="n">
-        <v>25.09</v>
+        <v>103.92</v>
       </c>
       <c r="N28" t="n">
-        <v>62307420121.18</v>
+        <v>35441857.85</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002431.SZ</t>
+          <t>002931.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ST棕榈</t>
+          <t>锋龙股份</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.36</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>3.0303</v>
+        <v>5.6544</v>
       </c>
       <c r="F29" t="n">
-        <v>2.26</v>
+        <v>17.62</v>
       </c>
       <c r="G29" t="n">
-        <v>121208437</v>
+        <v>6714577434</v>
       </c>
       <c r="H29" t="n">
-        <v>16334332.96</v>
+        <v>981793954.54</v>
       </c>
       <c r="I29" t="n">
-        <v>12735827.65</v>
+        <v>893739914.9299999</v>
       </c>
       <c r="J29" t="n">
-        <v>29070160.61</v>
+        <v>1875533869.47</v>
       </c>
       <c r="K29" t="n">
-        <v>-3598505.31</v>
+        <v>-88054039.61</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.97</v>
+        <v>-1.31</v>
       </c>
       <c r="M29" t="n">
-        <v>23.98</v>
+        <v>27.93</v>
       </c>
       <c r="N29" t="n">
-        <v>2451270480.4</v>
+        <v>16019780828.8</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002472.SZ</t>
+          <t>002979.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>双环传动</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47.01</v>
+        <v>73.27</v>
       </c>
       <c r="E30" t="n">
-        <v>9.990600000000001</v>
+        <v>5.3487</v>
       </c>
       <c r="F30" t="n">
-        <v>9.970000000000001</v>
+        <v>26.67</v>
       </c>
       <c r="G30" t="n">
-        <v>3412149027</v>
+        <v>4423190761</v>
       </c>
       <c r="H30" t="n">
-        <v>464373642.98</v>
+        <v>766934122.16</v>
       </c>
       <c r="I30" t="n">
-        <v>784190730.65</v>
+        <v>685440123.54</v>
       </c>
       <c r="J30" t="n">
-        <v>1248564373.63</v>
+        <v>1452374245.7</v>
       </c>
       <c r="K30" t="n">
-        <v>319817087.67</v>
+        <v>-81493998.62</v>
       </c>
       <c r="L30" t="n">
-        <v>9.369999999999999</v>
+        <v>-1.84</v>
       </c>
       <c r="M30" t="n">
-        <v>36.59</v>
+        <v>32.84</v>
       </c>
       <c r="N30" t="n">
-        <v>35191468155.66</v>
+        <v>16320398586.93</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002496.SZ</t>
+          <t>118011.SH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>辉丰股份</t>
+          <t>银微转债</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.23</v>
+        <v>257.758</v>
       </c>
       <c r="E31" t="n">
-        <v>9.8522</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8.84</v>
-      </c>
+        <v>19.825</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>564417465</v>
+        <v>6687213570</v>
       </c>
       <c r="H31" t="n">
-        <v>81000062.90000001</v>
+        <v>1517594080</v>
       </c>
       <c r="I31" t="n">
-        <v>78712028.8</v>
+        <v>1520057170</v>
       </c>
       <c r="J31" t="n">
-        <v>159712091.7</v>
+        <v>3037651250</v>
       </c>
       <c r="K31" t="n">
-        <v>-2288034.1</v>
+        <v>2463090</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.41</v>
+        <v>0.04</v>
       </c>
       <c r="M31" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2634184155</v>
-      </c>
+        <v>45.42</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002536.SZ</t>
+          <t>118064.SH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>飞龙股份</t>
+          <t>联瑞转债</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>51.96</v>
+        <v>472.015</v>
       </c>
       <c r="E32" t="n">
-        <v>9.9915</v>
-      </c>
-      <c r="F32" t="n">
-        <v>9.279999999999999</v>
-      </c>
+        <v>-15.1978</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>2577109516</v>
+        <v>1497506270</v>
       </c>
       <c r="H32" t="n">
-        <v>313276269.51</v>
+        <v>355295950</v>
       </c>
       <c r="I32" t="n">
-        <v>484340194.22</v>
+        <v>323677720</v>
       </c>
       <c r="J32" t="n">
-        <v>797616463.73</v>
+        <v>678973670</v>
       </c>
       <c r="K32" t="n">
-        <v>171063924.71</v>
+        <v>-31618230</v>
       </c>
       <c r="L32" t="n">
-        <v>6.64</v>
+        <v>-2.11</v>
       </c>
       <c r="M32" t="n">
-        <v>30.95</v>
-      </c>
-      <c r="N32" t="n">
-        <v>28287079857</v>
-      </c>
+        <v>45.34</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>非上市首日,当日收盘价跌幅达15%的前五只可转债</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002559.SZ</t>
+          <t>123273.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>亚威股份</t>
+          <t>三江转债</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.24</v>
+        <v>188.76</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.4122</v>
-      </c>
-      <c r="F33" t="n">
-        <v>32.95</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>2374709604</v>
+        <v>7847697</v>
       </c>
       <c r="H33" t="n">
-        <v>416837558.23</v>
+        <v>620642.88</v>
       </c>
       <c r="I33" t="n">
-        <v>482816604.57</v>
+        <v>7847697</v>
       </c>
       <c r="J33" t="n">
-        <v>899654162.8</v>
+        <v>8468339.880000001</v>
       </c>
       <c r="K33" t="n">
-        <v>65979046.34</v>
+        <v>7227054.12</v>
       </c>
       <c r="L33" t="n">
-        <v>2.78</v>
+        <v>92.09</v>
       </c>
       <c r="M33" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="N33" t="n">
-        <v>7177031328.16</v>
-      </c>
+        <v>107.91</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅达到15%的前5只可转债</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002584.SZ</t>
+          <t>128119.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>西陇科学</t>
+          <t>龙大转债</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.949999999999999</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-9.545500000000001</v>
-      </c>
-      <c r="F34" t="n">
-        <v>26</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>1238747424</v>
+        <v>87735568</v>
       </c>
       <c r="H34" t="n">
-        <v>189570209</v>
+        <v>20873766.63</v>
       </c>
       <c r="I34" t="n">
-        <v>175000996</v>
+        <v>29286702.72</v>
       </c>
       <c r="J34" t="n">
-        <v>364571205</v>
+        <v>50160469.35</v>
       </c>
       <c r="K34" t="n">
-        <v>-14569213</v>
+        <v>8412936.09</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.18</v>
+        <v>9.59</v>
       </c>
       <c r="M34" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4660843943.65</v>
-      </c>
+        <v>57.17</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅达到15%的前5只可转债</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002598.SZ</t>
+          <t>128119.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ST章鼓</t>
+          <t>龙大转债</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.99</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>4.955</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.72</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>113800176</v>
+        <v>1131381258</v>
       </c>
       <c r="H35" t="n">
-        <v>26275704.9</v>
+        <v>297153847.1</v>
       </c>
       <c r="I35" t="n">
-        <v>24433039.86</v>
+        <v>290057494.63</v>
       </c>
       <c r="J35" t="n">
-        <v>50708744.76</v>
+        <v>587211341.73</v>
       </c>
       <c r="K35" t="n">
-        <v>-1842665.04</v>
+        <v>-7096352.47</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.62</v>
+        <v>-0.63</v>
       </c>
       <c r="M35" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2002844867.76</v>
-      </c>
+        <v>51.9</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的可转债</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>002674.SZ</t>
+          <t>200725.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>兴业科技</t>
+          <t>京东方B</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29.03</v>
+        <v>4.86</v>
       </c>
       <c r="E36" t="n">
-        <v>2.7611</v>
+        <v>-9.497199999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>14.2</v>
+        <v>1.88</v>
       </c>
       <c r="G36" t="n">
-        <v>1163122299</v>
+        <v>56880908</v>
       </c>
       <c r="H36" t="n">
-        <v>83052612.3</v>
+        <v>14142153.02</v>
       </c>
       <c r="I36" t="n">
-        <v>58980431.31</v>
+        <v>9782539.210000001</v>
       </c>
       <c r="J36" t="n">
-        <v>142033043.61</v>
+        <v>23924692.23</v>
       </c>
       <c r="K36" t="n">
-        <v>-24072180.99</v>
+        <v>-4359613.81</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.07</v>
+        <v>-7.66</v>
       </c>
       <c r="M36" t="n">
-        <v>12.21</v>
+        <v>42.06</v>
       </c>
       <c r="N36" t="n">
-        <v>8493122817.56</v>
+        <v>277816377605.14</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>002689.SZ</t>
+          <t>300029.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ST远智</t>
+          <t>天龙退</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.81</v>
+        <v>0.14</v>
       </c>
       <c r="E37" t="n">
-        <v>3.69</v>
+        <v>-6.6667</v>
       </c>
       <c r="F37" t="n">
-        <v>1.42</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>107256188</v>
+        <v>2720535</v>
       </c>
       <c r="H37" t="n">
-        <v>25157819.53</v>
+        <v>1215283.02</v>
       </c>
       <c r="I37" t="n">
-        <v>21917640.1</v>
+        <v>674075</v>
       </c>
       <c r="J37" t="n">
-        <v>47075459.63</v>
+        <v>1889358.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-3240179.43</v>
+        <v>-541208.02</v>
       </c>
       <c r="L37" t="n">
-        <v>-3.02</v>
+        <v>-19.89</v>
       </c>
       <c r="M37" t="n">
-        <v>43.89</v>
+        <v>69.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2930581382.44</v>
+        <v>28050435</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>002694.SZ</t>
+          <t>300061.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>*ST顾地</t>
+          <t>旗天科技</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.31</v>
+        <v>6.19</v>
       </c>
       <c r="E38" t="n">
-        <v>3.125</v>
+        <v>-17.246</v>
       </c>
       <c r="F38" t="n">
-        <v>0.64</v>
+        <v>10.57</v>
       </c>
       <c r="G38" t="n">
-        <v>32769533</v>
+        <v>422087168</v>
       </c>
       <c r="H38" t="n">
-        <v>8864382</v>
+        <v>43698730.7</v>
       </c>
       <c r="I38" t="n">
-        <v>9861106.279999999</v>
+        <v>66012909.88</v>
       </c>
       <c r="J38" t="n">
-        <v>18725488.28</v>
+        <v>109711640.58</v>
       </c>
       <c r="K38" t="n">
-        <v>996724.28</v>
+        <v>22314179.18</v>
       </c>
       <c r="L38" t="n">
-        <v>3.04</v>
+        <v>5.29</v>
       </c>
       <c r="M38" t="n">
-        <v>57.14</v>
+        <v>25.99</v>
       </c>
       <c r="N38" t="n">
-        <v>1660422282.75</v>
+        <v>3851230473.95</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>002726.SZ</t>
+          <t>300607.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ST龙大</t>
+          <t>拓斯达</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.34</v>
+        <v>45.01</v>
       </c>
       <c r="E39" t="n">
-        <v>4.6875</v>
+        <v>-15.0113</v>
       </c>
       <c r="F39" t="n">
-        <v>6.79</v>
+        <v>24.26</v>
       </c>
       <c r="G39" t="n">
-        <v>291091032</v>
+        <v>3861226198</v>
       </c>
       <c r="H39" t="n">
-        <v>50311813.76</v>
+        <v>535942538.76</v>
       </c>
       <c r="I39" t="n">
-        <v>20467034.68</v>
+        <v>394321513.42</v>
       </c>
       <c r="J39" t="n">
-        <v>70778848.44</v>
+        <v>930264052.1799999</v>
       </c>
       <c r="K39" t="n">
-        <v>-29844779.08</v>
+        <v>-141621025.34</v>
       </c>
       <c r="L39" t="n">
-        <v>-10.25</v>
+        <v>-3.67</v>
       </c>
       <c r="M39" t="n">
-        <v>24.32</v>
+        <v>24.09</v>
       </c>
       <c r="N39" t="n">
-        <v>1555323588.3</v>
+        <v>15190846193.6</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>002747.SZ</t>
+          <t>300684.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>埃斯顿</t>
+          <t>中石科技</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>44.77</v>
+        <v>74.41</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>19.9968</v>
       </c>
       <c r="F40" t="n">
-        <v>16.2</v>
+        <v>22.79</v>
       </c>
       <c r="G40" t="n">
-        <v>5508068594</v>
+        <v>3357374946</v>
       </c>
       <c r="H40" t="n">
-        <v>878697717.63</v>
+        <v>563989436</v>
       </c>
       <c r="I40" t="n">
-        <v>679225612.22</v>
+        <v>582295600.48</v>
       </c>
       <c r="J40" t="n">
-        <v>1557923329.85</v>
+        <v>1146285036.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-199472105.41</v>
+        <v>18306164.48</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.62</v>
+        <v>0.55</v>
       </c>
       <c r="M40" t="n">
-        <v>28.28</v>
+        <v>34.14</v>
       </c>
       <c r="N40" t="n">
-        <v>35028255195.56</v>
+        <v>15202188611.12</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>002772.SZ</t>
+          <t>300684.SZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>众兴菌业</t>
+          <t>中石科技</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.88</v>
+        <v>74.41</v>
       </c>
       <c r="E41" t="n">
-        <v>8.4375</v>
+        <v>19.9968</v>
       </c>
       <c r="F41" t="n">
-        <v>8.970000000000001</v>
+        <v>22.79</v>
       </c>
       <c r="G41" t="n">
-        <v>825013069</v>
+        <v>6191272277</v>
       </c>
       <c r="H41" t="n">
-        <v>168827549.21</v>
+        <v>1050881241.81</v>
       </c>
       <c r="I41" t="n">
-        <v>152660179.67</v>
+        <v>1194091652.14</v>
       </c>
       <c r="J41" t="n">
-        <v>321487728.88</v>
+        <v>2244972893.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-16167369.54</v>
+        <v>143210410.33</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.96</v>
+        <v>2.31</v>
       </c>
       <c r="M41" t="n">
-        <v>38.97</v>
+        <v>36.26</v>
       </c>
       <c r="N41" t="n">
-        <v>5158316382.76</v>
+        <v>15202188611.12</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>002808.SZ</t>
+          <t>300716.SZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>恒久退</t>
+          <t>*ST泉为</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.24</v>
+        <v>29.09</v>
       </c>
       <c r="E42" t="n">
-        <v>-4</v>
+        <v>19.0749</v>
       </c>
       <c r="F42" t="n">
-        <v>5.63</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>2534475</v>
+        <v>359021328</v>
       </c>
       <c r="H42" t="n">
-        <v>1070199.96</v>
+        <v>72082431</v>
       </c>
       <c r="I42" t="n">
-        <v>1110356.36</v>
+        <v>71011605.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2180556.32</v>
+        <v>143094036.5</v>
       </c>
       <c r="K42" t="n">
-        <v>40156.4</v>
+        <v>-1070825.5</v>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>-0.3</v>
       </c>
       <c r="M42" t="n">
-        <v>86.04000000000001</v>
+        <v>39.86</v>
       </c>
       <c r="N42" t="n">
-        <v>44846653.44</v>
+        <v>4654981800</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>002842.SZ</t>
+          <t>300716.SZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>*ST泉为</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>45.15</v>
+        <v>29.09</v>
       </c>
       <c r="E43" t="n">
-        <v>-10.006</v>
+        <v>19.0749</v>
       </c>
       <c r="F43" t="n">
-        <v>24.62</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>3041686297</v>
+        <v>606204810</v>
       </c>
       <c r="H43" t="n">
-        <v>534118682.96</v>
+        <v>126871478.14</v>
       </c>
       <c r="I43" t="n">
-        <v>427189687.12</v>
+        <v>112186442.16</v>
       </c>
       <c r="J43" t="n">
-        <v>961308370.08</v>
+        <v>239057920.3</v>
       </c>
       <c r="K43" t="n">
-        <v>-106928995.84</v>
+        <v>-14685035.98</v>
       </c>
       <c r="L43" t="n">
-        <v>-3.52</v>
+        <v>-2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>31.6</v>
+        <v>39.44</v>
       </c>
       <c r="N43" t="n">
-        <v>12121075508.85</v>
+        <v>4654981800</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>002850.SZ</t>
+          <t>301191.SZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>科达利</t>
+          <t>菲菱科思</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>226.16</v>
+        <v>135.01</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>19.9982</v>
       </c>
       <c r="F44" t="n">
-        <v>4.27</v>
+        <v>18.9</v>
       </c>
       <c r="G44" t="n">
-        <v>5895313098</v>
+        <v>1699984947</v>
       </c>
       <c r="H44" t="n">
-        <v>1493731322.29</v>
+        <v>327141642.75</v>
       </c>
       <c r="I44" t="n">
-        <v>1040723736.51</v>
+        <v>400837981.68</v>
       </c>
       <c r="J44" t="n">
-        <v>2534455058.8</v>
+        <v>727979624.4299999</v>
       </c>
       <c r="K44" t="n">
-        <v>-453007585.78</v>
+        <v>73696338.93000001</v>
       </c>
       <c r="L44" t="n">
-        <v>-7.68</v>
+        <v>4.34</v>
       </c>
       <c r="M44" t="n">
-        <v>42.99</v>
+        <v>42.82</v>
       </c>
       <c r="N44" t="n">
-        <v>47412159105.52</v>
+        <v>9863524667.34</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>002868.SZ</t>
+          <t>301197.SZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>绿康生化</t>
+          <t>工大科雅</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26.28</v>
+        <v>26.49</v>
       </c>
       <c r="E45" t="n">
-        <v>10.0042</v>
+        <v>-19.994</v>
       </c>
       <c r="F45" t="n">
-        <v>1.58</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>224702497</v>
+        <v>257434739</v>
       </c>
       <c r="H45" t="n">
-        <v>32829428.9</v>
+        <v>119729290.13</v>
       </c>
       <c r="I45" t="n">
-        <v>48316542.3</v>
+        <v>48324820.42</v>
       </c>
       <c r="J45" t="n">
-        <v>81145971.2</v>
+        <v>168054110.55</v>
       </c>
       <c r="K45" t="n">
-        <v>15487113.4</v>
+        <v>-71404469.70999999</v>
       </c>
       <c r="L45" t="n">
-        <v>6.89</v>
+        <v>-27.74</v>
       </c>
       <c r="M45" t="n">
-        <v>36.11</v>
+        <v>65.28</v>
       </c>
       <c r="N45" t="n">
-        <v>2812025805.12</v>
+        <v>2880767632.5</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>002872.SZ</t>
+          <t>301317.SZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ST天圣</t>
+          <t>鑫磊股份</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5.03</v>
+        <v>62.21</v>
       </c>
       <c r="E46" t="n">
-        <v>5.0104</v>
+        <v>20.0039</v>
       </c>
       <c r="F46" t="n">
-        <v>1.93</v>
+        <v>12.11</v>
       </c>
       <c r="G46" t="n">
-        <v>46778583</v>
+        <v>368279854</v>
       </c>
       <c r="H46" t="n">
-        <v>8626649.359999999</v>
+        <v>92119892.13</v>
       </c>
       <c r="I46" t="n">
-        <v>10910410.5</v>
+        <v>114629442.62</v>
       </c>
       <c r="J46" t="n">
-        <v>19537059.86</v>
+        <v>206749334.75</v>
       </c>
       <c r="K46" t="n">
-        <v>2283761.14</v>
+        <v>22509550.49</v>
       </c>
       <c r="L46" t="n">
-        <v>4.88</v>
+        <v>6.11</v>
       </c>
       <c r="M46" t="n">
-        <v>41.76</v>
+        <v>56.14</v>
       </c>
       <c r="N46" t="n">
-        <v>1081038214.02</v>
+        <v>3247158759.93</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>002898.SZ</t>
+          <t>301379.SZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>赛隆退</t>
+          <t>天山电子</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.36</v>
+        <v>35.61</v>
       </c>
       <c r="E47" t="n">
-        <v>-2.7027</v>
+        <v>10.7276</v>
       </c>
       <c r="F47" t="n">
-        <v>5.03</v>
+        <v>28.99</v>
       </c>
       <c r="G47" t="n">
-        <v>1817587</v>
+        <v>3807659622</v>
       </c>
       <c r="H47" t="n">
-        <v>903881</v>
+        <v>419704387.84</v>
       </c>
       <c r="I47" t="n">
-        <v>746157</v>
+        <v>643027522.38</v>
       </c>
       <c r="J47" t="n">
-        <v>1650038</v>
+        <v>1062731910.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-157724</v>
+        <v>223323134.54</v>
       </c>
       <c r="L47" t="n">
-        <v>-8.68</v>
+        <v>5.87</v>
       </c>
       <c r="M47" t="n">
-        <v>90.78</v>
+        <v>27.91</v>
       </c>
       <c r="N47" t="n">
-        <v>36454482.36</v>
+        <v>7751796501.45</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>123118.SZ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>惠城转债</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>738</v>
+        <v>38.03</v>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
+        <v>6.9761</v>
+      </c>
+      <c r="F48" t="n">
+        <v>45.9</v>
+      </c>
       <c r="G48" t="n">
-        <v>2859442536</v>
+        <v>554870073</v>
       </c>
       <c r="H48" t="n">
-        <v>777351218.62</v>
+        <v>50930873.68</v>
       </c>
       <c r="I48" t="n">
-        <v>798265696.3099999</v>
+        <v>39504032.38</v>
       </c>
       <c r="J48" t="n">
-        <v>1575616914.93</v>
+        <v>90434906.06</v>
       </c>
       <c r="K48" t="n">
-        <v>20914477.69</v>
+        <v>-11426841.3</v>
       </c>
       <c r="L48" t="n">
-        <v>0.73</v>
+        <v>-2.06</v>
       </c>
       <c r="M48" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>16.3</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1243521787.29</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只可转债</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>123273.SZ</t>
+          <t>600105.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>三江转债</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>157.3</v>
+        <v>50.05</v>
       </c>
       <c r="E49" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
+        <v>-8.2157</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.7</v>
+      </c>
       <c r="G49" t="n">
-        <v>10065822</v>
+        <v>8065477372</v>
       </c>
       <c r="H49" t="n">
-        <v>1864896.8</v>
+        <v>1741034940.23</v>
       </c>
       <c r="I49" t="n">
-        <v>10065822</v>
+        <v>1359879141.24</v>
       </c>
       <c r="J49" t="n">
-        <v>11930718.8</v>
+        <v>3100914081.47</v>
       </c>
       <c r="K49" t="n">
-        <v>8200925.2</v>
+        <v>-381155798.99</v>
       </c>
       <c r="L49" t="n">
-        <v>81.47</v>
+        <v>-4.73</v>
       </c>
       <c r="M49" t="n">
-        <v>118.53</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>38.45</v>
+      </c>
+      <c r="N49" t="n">
+        <v>73172839840.10001</v>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>上市首日可转债</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>200725.SZ</t>
+          <t>600172.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>京东方B</t>
+          <t>黄河旋风</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.37</v>
+        <v>18.55</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.0934</v>
+        <v>10.0237</v>
       </c>
       <c r="F50" t="n">
-        <v>1.37</v>
+        <v>22.58</v>
       </c>
       <c r="G50" t="n">
-        <v>45556817</v>
+        <v>5247582045</v>
       </c>
       <c r="H50" t="n">
-        <v>7879313.07</v>
+        <v>410087683.2</v>
       </c>
       <c r="I50" t="n">
-        <v>5617724.48</v>
+        <v>785705450.38</v>
       </c>
       <c r="J50" t="n">
-        <v>13497037.55</v>
+        <v>1195793133.58</v>
       </c>
       <c r="K50" t="n">
-        <v>-2261588.59</v>
+        <v>375617767.18</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.96</v>
+        <v>7.16</v>
       </c>
       <c r="M50" t="n">
-        <v>29.63</v>
+        <v>22.79</v>
       </c>
       <c r="N50" t="n">
-        <v>300097371662.45</v>
+        <v>23674544162.5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300018.SZ</t>
+          <t>600184.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>中元股份</t>
+          <t>光电股份</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.65</v>
+        <v>23.71</v>
       </c>
       <c r="E51" t="n">
-        <v>19.9836</v>
+        <v>-8.2075</v>
       </c>
       <c r="F51" t="n">
-        <v>23.55</v>
+        <v>7.39</v>
       </c>
       <c r="G51" t="n">
-        <v>1225192039</v>
+        <v>3393738914</v>
       </c>
       <c r="H51" t="n">
-        <v>138008049.45</v>
+        <v>329033354.9</v>
       </c>
       <c r="I51" t="n">
-        <v>272348208.08</v>
+        <v>328024957.4</v>
       </c>
       <c r="J51" t="n">
-        <v>410356257.53</v>
+        <v>657058312.3</v>
       </c>
       <c r="K51" t="n">
-        <v>134340158.63</v>
+        <v>-1008397.5</v>
       </c>
       <c r="L51" t="n">
-        <v>10.96</v>
+        <v>-0.03</v>
       </c>
       <c r="M51" t="n">
-        <v>33.49</v>
+        <v>19.36</v>
       </c>
       <c r="N51" t="n">
-        <v>5333252496.35</v>
+        <v>13816468266.28</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300029.SZ</t>
+          <t>600215.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>天龙退</t>
+          <t>派斯林</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.15</v>
+        <v>6.88</v>
       </c>
       <c r="E52" t="n">
-        <v>-6.25</v>
+        <v>10.08</v>
       </c>
       <c r="F52" t="n">
-        <v>9.52</v>
+        <v>7.07</v>
       </c>
       <c r="G52" t="n">
-        <v>2909054</v>
+        <v>218338593</v>
       </c>
       <c r="H52" t="n">
-        <v>1579081.9</v>
+        <v>23721758</v>
       </c>
       <c r="I52" t="n">
-        <v>922084</v>
+        <v>64916205.44</v>
       </c>
       <c r="J52" t="n">
-        <v>2501165.9</v>
+        <v>88637963.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-656997.9</v>
+        <v>41194447.44</v>
       </c>
       <c r="L52" t="n">
-        <v>-22.58</v>
+        <v>18.87</v>
       </c>
       <c r="M52" t="n">
-        <v>85.98</v>
+        <v>40.6</v>
       </c>
       <c r="N52" t="n">
-        <v>30054037.5</v>
+        <v>3143354214.4</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>300129.SZ</t>
+          <t>600288.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>泰胜风能</t>
+          <t>大恒科技</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.63</v>
+        <v>14.14</v>
       </c>
       <c r="E53" t="n">
-        <v>19.9774</v>
+        <v>10.0389</v>
       </c>
       <c r="F53" t="n">
-        <v>11.47</v>
+        <v>5.35</v>
       </c>
       <c r="G53" t="n">
-        <v>823058485</v>
+        <v>320408233</v>
       </c>
       <c r="H53" t="n">
-        <v>75779988.14</v>
+        <v>54284784</v>
       </c>
       <c r="I53" t="n">
-        <v>256990495.88</v>
+        <v>72703037.23999999</v>
       </c>
       <c r="J53" t="n">
-        <v>332770484.02</v>
+        <v>126987821.24</v>
       </c>
       <c r="K53" t="n">
-        <v>181210507.74</v>
+        <v>18418253.24</v>
       </c>
       <c r="L53" t="n">
-        <v>22.02</v>
+        <v>5.75</v>
       </c>
       <c r="M53" t="n">
-        <v>40.43</v>
+        <v>39.63</v>
       </c>
       <c r="N53" t="n">
-        <v>7639889277.18</v>
+        <v>6176352000</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>300139.SZ</t>
+          <t>600367.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>晓程科技</t>
+          <t>红星发展</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>44.05</v>
+        <v>47.68</v>
       </c>
       <c r="E54" t="n">
-        <v>12.8619</v>
+        <v>-10.0038</v>
       </c>
       <c r="F54" t="n">
-        <v>30.65</v>
+        <v>13.35</v>
       </c>
       <c r="G54" t="n">
-        <v>3088254312</v>
+        <v>8408415022</v>
       </c>
       <c r="H54" t="n">
-        <v>339736675.9</v>
+        <v>1074009488.15</v>
       </c>
       <c r="I54" t="n">
-        <v>305385827.58</v>
+        <v>1274812200.14</v>
       </c>
       <c r="J54" t="n">
-        <v>645122503.48</v>
+        <v>2348821688.29</v>
       </c>
       <c r="K54" t="n">
-        <v>-34350848.32</v>
+        <v>200802711.99</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.11</v>
+        <v>2.39</v>
       </c>
       <c r="M54" t="n">
-        <v>20.89</v>
+        <v>27.93</v>
       </c>
       <c r="N54" t="n">
-        <v>10292688861.25</v>
+        <v>15351681317.76</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>300163.SZ</t>
+          <t>600397.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>先锋新材</t>
+          <t>江钨装备</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7.5</v>
+        <v>23.09</v>
       </c>
       <c r="E55" t="n">
-        <v>15.9196</v>
+        <v>-9.980499999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>26.35</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>1130202680</v>
+        <v>10283369790</v>
       </c>
       <c r="H55" t="n">
-        <v>252910264.28</v>
+        <v>1579385014.72</v>
       </c>
       <c r="I55" t="n">
-        <v>238600635.66</v>
+        <v>1720196553.74</v>
       </c>
       <c r="J55" t="n">
-        <v>491510899.94</v>
+        <v>3299581568.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-14309628.62</v>
+        <v>140811539.02</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.27</v>
+        <v>1.37</v>
       </c>
       <c r="M55" t="n">
-        <v>43.49</v>
+        <v>32.09</v>
       </c>
       <c r="N55" t="n">
-        <v>3424471815</v>
+        <v>22858173675.38</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>300385.SZ</t>
+          <t>600449.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ST雪浪</t>
+          <t>宁夏建材</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.77</v>
+        <v>14</v>
       </c>
       <c r="E56" t="n">
-        <v>4.5008</v>
+        <v>6.0606</v>
       </c>
       <c r="F56" t="n">
-        <v>4.02</v>
+        <v>3.33</v>
       </c>
       <c r="G56" t="n">
-        <v>481139349</v>
+        <v>575658506</v>
       </c>
       <c r="H56" t="n">
-        <v>109550516</v>
+        <v>102185579.17</v>
       </c>
       <c r="I56" t="n">
-        <v>77204635.92</v>
+        <v>115372062.93</v>
       </c>
       <c r="J56" t="n">
-        <v>186755151.92</v>
+        <v>217557642.1</v>
       </c>
       <c r="K56" t="n">
-        <v>-32345880.08</v>
+        <v>13186483.76</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.72</v>
+        <v>2.29</v>
       </c>
       <c r="M56" t="n">
-        <v>38.82</v>
+        <v>37.79</v>
       </c>
       <c r="N56" t="n">
-        <v>3711761823.41</v>
+        <v>6694534588</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>300487.SZ</t>
+          <t>600707.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>蓝晓科技</t>
+          <t>彩虹股份</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>74.58</v>
+        <v>13.52</v>
       </c>
       <c r="E57" t="n">
-        <v>10.4889</v>
+        <v>-9.986700000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>7.44</v>
+        <v>6.31</v>
       </c>
       <c r="G57" t="n">
-        <v>4909305358</v>
+        <v>14289484498</v>
       </c>
       <c r="H57" t="n">
-        <v>1186977845.8</v>
+        <v>1616305411.79</v>
       </c>
       <c r="I57" t="n">
-        <v>808324902.96</v>
+        <v>1284502986.31</v>
       </c>
       <c r="J57" t="n">
-        <v>1995302748.76</v>
+        <v>2900808398.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-378652942.84</v>
+        <v>-331802425.48</v>
       </c>
       <c r="L57" t="n">
-        <v>-7.71</v>
+        <v>-2.32</v>
       </c>
       <c r="M57" t="n">
-        <v>40.64</v>
+        <v>20.3</v>
       </c>
       <c r="N57" t="n">
-        <v>22972088418.18</v>
+        <v>48505294776.64</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>300580.SZ</t>
+          <t>600730.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>贝斯特</t>
+          <t>*ST高科</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.96</v>
+        <v>10.94</v>
       </c>
       <c r="E58" t="n">
-        <v>20.0185</v>
+        <v>-10.0329</v>
       </c>
       <c r="F58" t="n">
-        <v>9.279999999999999</v>
+        <v>4.06</v>
       </c>
       <c r="G58" t="n">
-        <v>1078714723</v>
+        <v>268070205</v>
       </c>
       <c r="H58" t="n">
-        <v>165954327</v>
+        <v>53511979.4</v>
       </c>
       <c r="I58" t="n">
-        <v>199864209.51</v>
+        <v>26978047</v>
       </c>
       <c r="J58" t="n">
-        <v>365818536.51</v>
+        <v>80490026.40000001</v>
       </c>
       <c r="K58" t="n">
-        <v>33909882.51</v>
+        <v>-26533932.4</v>
       </c>
       <c r="L58" t="n">
-        <v>3.14</v>
+        <v>-9.9</v>
       </c>
       <c r="M58" t="n">
-        <v>33.91</v>
+        <v>30.03</v>
       </c>
       <c r="N58" t="n">
-        <v>12268500573.12</v>
+        <v>6418016661.88</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>300580.SZ</t>
+          <t>600769.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>贝斯特</t>
+          <t>祥龙电业</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>25.96</v>
+        <v>19.6</v>
       </c>
       <c r="E59" t="n">
-        <v>20.0185</v>
+        <v>-10.0092</v>
       </c>
       <c r="F59" t="n">
-        <v>9.279999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="G59" t="n">
-        <v>1928063999</v>
+        <v>679440747</v>
       </c>
       <c r="H59" t="n">
-        <v>289332306.08</v>
+        <v>135179918</v>
       </c>
       <c r="I59" t="n">
-        <v>376458101.29</v>
+        <v>89647525.09</v>
       </c>
       <c r="J59" t="n">
-        <v>665790407.37</v>
+        <v>224827443.09</v>
       </c>
       <c r="K59" t="n">
-        <v>87125795.20999999</v>
+        <v>-45532392.91</v>
       </c>
       <c r="L59" t="n">
-        <v>4.52</v>
+        <v>-6.7</v>
       </c>
       <c r="M59" t="n">
-        <v>34.53</v>
+        <v>33.09</v>
       </c>
       <c r="N59" t="n">
-        <v>12268500573.12</v>
+        <v>7349553120</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>300607.SZ</t>
+          <t>600793.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>拓斯达</t>
+          <t>宜宾纸业</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>52.96</v>
+        <v>17.61</v>
       </c>
       <c r="E60" t="n">
-        <v>13.5506</v>
+        <v>9.9938</v>
       </c>
       <c r="F60" t="n">
-        <v>26.86</v>
+        <v>10.48</v>
       </c>
       <c r="G60" t="n">
-        <v>10502306562</v>
+        <v>379976639</v>
       </c>
       <c r="H60" t="n">
-        <v>1406389635.15</v>
+        <v>53062355</v>
       </c>
       <c r="I60" t="n">
-        <v>1152054245.78</v>
+        <v>80670803.05</v>
       </c>
       <c r="J60" t="n">
-        <v>2558443880.93</v>
+        <v>133733158.05</v>
       </c>
       <c r="K60" t="n">
-        <v>-254335389.37</v>
+        <v>27608448.05</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.42</v>
+        <v>7.27</v>
       </c>
       <c r="M60" t="n">
-        <v>24.36</v>
+        <v>35.2</v>
       </c>
       <c r="N60" t="n">
-        <v>17873966105.6</v>
+        <v>3115279475.22</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>300695.SZ</t>
+          <t>601177.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>兆丰股份</t>
+          <t>杭齿前进</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>68.16</v>
+        <v>15.39</v>
       </c>
       <c r="E61" t="n">
-        <v>12.9038</v>
+        <v>7.5472</v>
       </c>
       <c r="F61" t="n">
-        <v>5.98</v>
+        <v>8.43</v>
       </c>
       <c r="G61" t="n">
-        <v>610710683</v>
+        <v>794251667</v>
       </c>
       <c r="H61" t="n">
-        <v>103684216.5</v>
+        <v>67470731.06999999</v>
       </c>
       <c r="I61" t="n">
-        <v>129012720.5</v>
+        <v>61036543.2</v>
       </c>
       <c r="J61" t="n">
-        <v>232696937</v>
+        <v>128507274.27</v>
       </c>
       <c r="K61" t="n">
-        <v>25328504</v>
+        <v>-6434187.87</v>
       </c>
       <c r="L61" t="n">
-        <v>4.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>38.1</v>
+        <v>16.18</v>
       </c>
       <c r="N61" t="n">
-        <v>6969831939.84</v>
+        <v>6193189935</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>300718.SZ</t>
+          <t>603001.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>长盛轴承</t>
+          <t>奥康国际</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>77.23</v>
+        <v>10.31</v>
       </c>
       <c r="E62" t="n">
-        <v>19.9969</v>
+        <v>-10.0349</v>
       </c>
       <c r="F62" t="n">
-        <v>14.84</v>
+        <v>0.71</v>
       </c>
       <c r="G62" t="n">
-        <v>2142139247</v>
+        <v>29554646</v>
       </c>
       <c r="H62" t="n">
-        <v>133080924.4</v>
+        <v>25543025</v>
       </c>
       <c r="I62" t="n">
-        <v>367394753.79</v>
+        <v>22341770</v>
       </c>
       <c r="J62" t="n">
-        <v>500475678.19</v>
+        <v>47884795</v>
       </c>
       <c r="K62" t="n">
-        <v>234313829.39</v>
+        <v>-3201255</v>
       </c>
       <c r="L62" t="n">
-        <v>10.94</v>
+        <v>-10.83</v>
       </c>
       <c r="M62" t="n">
-        <v>23.36</v>
+        <v>162.02</v>
       </c>
       <c r="N62" t="n">
-        <v>15187842429.47</v>
+        <v>4134103800</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>300718.SZ</t>
+          <t>603001.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>长盛轴承</t>
+          <t>奥康国际</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>77.23</v>
+        <v>10.31</v>
       </c>
       <c r="E63" t="n">
-        <v>19.9969</v>
+        <v>-10.0349</v>
       </c>
       <c r="F63" t="n">
-        <v>14.84</v>
+        <v>0.71</v>
       </c>
       <c r="G63" t="n">
-        <v>3495071943</v>
+        <v>38455673</v>
       </c>
       <c r="H63" t="n">
-        <v>205520178.9</v>
+        <v>31002399</v>
       </c>
       <c r="I63" t="n">
-        <v>409768244.71</v>
+        <v>24183201</v>
       </c>
       <c r="J63" t="n">
-        <v>615288423.61</v>
+        <v>55185600</v>
       </c>
       <c r="K63" t="n">
-        <v>204248065.81</v>
+        <v>-6819198</v>
       </c>
       <c r="L63" t="n">
-        <v>5.84</v>
+        <v>-17.73</v>
       </c>
       <c r="M63" t="n">
-        <v>17.6</v>
+        <v>143.5</v>
       </c>
       <c r="N63" t="n">
-        <v>15187842429.47</v>
+        <v>4134103800</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>300985.SZ</t>
+          <t>603020.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>致远新能</t>
+          <t>爱普股份</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>49.67</v>
+        <v>14.69</v>
       </c>
       <c r="E64" t="n">
-        <v>20.0048</v>
+        <v>10.0375</v>
       </c>
       <c r="F64" t="n">
-        <v>4.31</v>
+        <v>2.6</v>
       </c>
       <c r="G64" t="n">
-        <v>863744038</v>
+        <v>141429615</v>
       </c>
       <c r="H64" t="n">
-        <v>205561395.84</v>
+        <v>47824117</v>
       </c>
       <c r="I64" t="n">
-        <v>163611620.75</v>
+        <v>47579492</v>
       </c>
       <c r="J64" t="n">
-        <v>369173016.59</v>
+        <v>95403609</v>
       </c>
       <c r="K64" t="n">
-        <v>-41949775.09</v>
+        <v>-244625</v>
       </c>
       <c r="L64" t="n">
-        <v>-4.86</v>
+        <v>-0.17</v>
       </c>
       <c r="M64" t="n">
-        <v>42.74</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>9264074881.6</v>
+        <v>5518118900.06</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>301008.SZ</t>
+          <t>603078.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>宏昌科技</t>
+          <t>江化微</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>33.64</v>
+        <v>57.7</v>
       </c>
       <c r="E65" t="n">
-        <v>5.3555</v>
+        <v>2.5595</v>
       </c>
       <c r="F65" t="n">
-        <v>19.74</v>
+        <v>16.68</v>
       </c>
       <c r="G65" t="n">
-        <v>1280230951</v>
+        <v>3566284749</v>
       </c>
       <c r="H65" t="n">
-        <v>195634382.22</v>
+        <v>695227773.76</v>
       </c>
       <c r="I65" t="n">
-        <v>185184192.69</v>
+        <v>747734656.28</v>
       </c>
       <c r="J65" t="n">
-        <v>380818574.91</v>
+        <v>1442962430.04</v>
       </c>
       <c r="K65" t="n">
-        <v>-10450189.53</v>
+        <v>52506882.52</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.82</v>
+        <v>1.47</v>
       </c>
       <c r="M65" t="n">
-        <v>29.75</v>
+        <v>40.46</v>
       </c>
       <c r="N65" t="n">
-        <v>3890154291.76</v>
+        <v>22251269209.6</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>301379.SZ</t>
+          <t>603137.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>天山电子</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32.16</v>
+        <v>18.94</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>9.9884</v>
       </c>
       <c r="F66" t="n">
-        <v>22.75</v>
+        <v>0.4</v>
       </c>
       <c r="G66" t="n">
-        <v>1559512057</v>
+        <v>24147638</v>
       </c>
       <c r="H66" t="n">
-        <v>158786114.35</v>
+        <v>7584212</v>
       </c>
       <c r="I66" t="n">
-        <v>252698538.37</v>
+        <v>24147638</v>
       </c>
       <c r="J66" t="n">
-        <v>411484652.72</v>
+        <v>31731850</v>
       </c>
       <c r="K66" t="n">
-        <v>93912424.02</v>
+        <v>16563426</v>
       </c>
       <c r="L66" t="n">
-        <v>6.02</v>
+        <v>68.59</v>
       </c>
       <c r="M66" t="n">
-        <v>26.39</v>
+        <v>131.41</v>
       </c>
       <c r="N66" t="n">
-        <v>7000779991.2</v>
+        <v>3464757345.96</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>603211.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>晋拓股份</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35.55</v>
+        <v>39.53</v>
       </c>
       <c r="E67" t="n">
-        <v>13.2166</v>
+        <v>9.988899999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>41.4</v>
+        <v>5.08</v>
       </c>
       <c r="G67" t="n">
-        <v>453284970</v>
+        <v>810721910</v>
       </c>
       <c r="H67" t="n">
-        <v>45583460.74</v>
+        <v>55312687</v>
       </c>
       <c r="I67" t="n">
-        <v>49030939.09</v>
+        <v>116177070</v>
       </c>
       <c r="J67" t="n">
-        <v>94614399.83</v>
+        <v>171489757</v>
       </c>
       <c r="K67" t="n">
-        <v>3447478.35</v>
+        <v>60864383</v>
       </c>
       <c r="L67" t="n">
-        <v>0.76</v>
+        <v>7.51</v>
       </c>
       <c r="M67" t="n">
-        <v>20.87</v>
+        <v>21.15</v>
       </c>
       <c r="N67" t="n">
-        <v>1162429648.65</v>
+        <v>10744570240</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>301529.SZ</t>
+          <t>603270.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>福赛科技</t>
+          <t>金帝股份</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>124.3</v>
+        <v>31.22</v>
       </c>
       <c r="E68" t="n">
-        <v>10.9821</v>
+        <v>-8.9796</v>
       </c>
       <c r="F68" t="n">
-        <v>10.36</v>
+        <v>20.61</v>
       </c>
       <c r="G68" t="n">
-        <v>2328588965</v>
+        <v>466143048</v>
       </c>
       <c r="H68" t="n">
-        <v>610241829.72</v>
+        <v>37247291.51</v>
       </c>
       <c r="I68" t="n">
-        <v>499501367.67</v>
+        <v>82165318.06999999</v>
       </c>
       <c r="J68" t="n">
-        <v>1109743197.39</v>
+        <v>119412609.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-110740462.05</v>
+        <v>44918026.56</v>
       </c>
       <c r="L68" t="n">
-        <v>-4.76</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>47.66</v>
+        <v>25.62</v>
       </c>
       <c r="N68" t="n">
-        <v>7901337578.2</v>
+        <v>2207774343.74</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>301596.SZ</t>
+          <t>603356.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>瑞迪智驱</t>
+          <t>华菱精工</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>63.97</v>
+        <v>16.3</v>
       </c>
       <c r="E69" t="n">
-        <v>19.9962</v>
+        <v>-9.545</v>
       </c>
       <c r="F69" t="n">
-        <v>18.34</v>
+        <v>10.56</v>
       </c>
       <c r="G69" t="n">
-        <v>740454652</v>
+        <v>245335987</v>
       </c>
       <c r="H69" t="n">
-        <v>95947164.44</v>
+        <v>84455834</v>
       </c>
       <c r="I69" t="n">
-        <v>162284073.72</v>
+        <v>49632199</v>
       </c>
       <c r="J69" t="n">
-        <v>258231238.16</v>
+        <v>134088033</v>
       </c>
       <c r="K69" t="n">
-        <v>66336909.28</v>
+        <v>-34823635</v>
       </c>
       <c r="L69" t="n">
-        <v>8.960000000000001</v>
+        <v>-14.19</v>
       </c>
       <c r="M69" t="n">
-        <v>34.87</v>
+        <v>54.65</v>
       </c>
       <c r="N69" t="n">
-        <v>2804653214.26</v>
+        <v>2173442000</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>301696.SZ</t>
+          <t>603407.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>三瑞智能</t>
+          <t>长裕集团</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>140.4</v>
+        <v>88.03</v>
       </c>
       <c r="E70" t="n">
-        <v>3.9615</v>
+        <v>-9.999000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>40.63</v>
+        <v>12.36</v>
       </c>
       <c r="G70" t="n">
-        <v>1678448786</v>
+        <v>415696470</v>
       </c>
       <c r="H70" t="n">
-        <v>146962724.79</v>
+        <v>124117314.32</v>
       </c>
       <c r="I70" t="n">
-        <v>108941867.86</v>
+        <v>107855089</v>
       </c>
       <c r="J70" t="n">
-        <v>255904592.65</v>
+        <v>231972403.32</v>
       </c>
       <c r="K70" t="n">
-        <v>-38020856.93</v>
+        <v>-16262225.32</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.27</v>
+        <v>-3.91</v>
       </c>
       <c r="M70" t="n">
-        <v>15.25</v>
+        <v>55.8</v>
       </c>
       <c r="N70" t="n">
-        <v>4223702901.6</v>
+        <v>3161332655.76</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>600053.SH</t>
+          <t>603466.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>*ST九鼎</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.539999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1531</v>
+        <v>2.3216</v>
       </c>
       <c r="F71" t="n">
-        <v>0.71</v>
+        <v>24.22</v>
       </c>
       <c r="G71" t="n">
-        <v>82287489</v>
+        <v>1793581365</v>
       </c>
       <c r="H71" t="n">
-        <v>13239392</v>
+        <v>256130491.6</v>
       </c>
       <c r="I71" t="n">
-        <v>20701034</v>
+        <v>246217291.01</v>
       </c>
       <c r="J71" t="n">
-        <v>33940426</v>
+        <v>502347782.61</v>
       </c>
       <c r="K71" t="n">
-        <v>7461642</v>
+        <v>-9913200.59</v>
       </c>
       <c r="L71" t="n">
-        <v>9.07</v>
+        <v>-0.55</v>
       </c>
       <c r="M71" t="n">
-        <v>41.25</v>
+        <v>28.01</v>
       </c>
       <c r="N71" t="n">
-        <v>3702438432</v>
+        <v>7078459054.8</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>600080.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ST金花</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>41.58</v>
       </c>
       <c r="E72" t="n">
-        <v>2.8807</v>
+        <v>7.1373</v>
       </c>
       <c r="F72" t="n">
-        <v>1.85</v>
+        <v>29.89</v>
       </c>
       <c r="G72" t="n">
-        <v>97791266</v>
+        <v>2935460071</v>
       </c>
       <c r="H72" t="n">
-        <v>21648902.44</v>
+        <v>505571523.62</v>
       </c>
       <c r="I72" t="n">
-        <v>24929214</v>
+        <v>354919642.63</v>
       </c>
       <c r="J72" t="n">
-        <v>46578116.44</v>
+        <v>860491166.25</v>
       </c>
       <c r="K72" t="n">
-        <v>3280311.56</v>
+        <v>-150651880.99</v>
       </c>
       <c r="L72" t="n">
-        <v>3.35</v>
+        <v>-5.13</v>
       </c>
       <c r="M72" t="n">
-        <v>47.63</v>
+        <v>29.31</v>
       </c>
       <c r="N72" t="n">
-        <v>1866351425</v>
+        <v>10006522550.64</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>600082.SH</t>
+          <t>603618.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ST海泰</t>
+          <t>杭电股份</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.95</v>
+        <v>44.1</v>
       </c>
       <c r="E73" t="n">
-        <v>4.9822</v>
+        <v>-10</v>
       </c>
       <c r="F73" t="n">
-        <v>1.29</v>
+        <v>14.07</v>
       </c>
       <c r="G73" t="n">
-        <v>42996809</v>
+        <v>4449246013</v>
       </c>
       <c r="H73" t="n">
-        <v>10615335.06</v>
+        <v>1628486094.87</v>
       </c>
       <c r="I73" t="n">
-        <v>10524810.99</v>
+        <v>266096440.87</v>
       </c>
       <c r="J73" t="n">
-        <v>21140146.05</v>
+        <v>1894582535.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-90524.07000000001</v>
+        <v>-1362389654</v>
       </c>
       <c r="L73" t="n">
-        <v>-0.21</v>
+        <v>-30.62</v>
       </c>
       <c r="M73" t="n">
-        <v>49.17</v>
+        <v>42.58</v>
       </c>
       <c r="N73" t="n">
-        <v>1871289465.4</v>
+        <v>30489664665.6</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>600084.SH</t>
+          <t>603682.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>*ST尼雅</t>
+          <t>锦和商管</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.24</v>
+        <v>8.07</v>
       </c>
       <c r="E74" t="n">
-        <v>4.9505</v>
+        <v>-10.0334</v>
       </c>
       <c r="F74" t="n">
-        <v>0.12</v>
+        <v>4.21</v>
       </c>
       <c r="G74" t="n">
-        <v>40798495</v>
+        <v>163730718</v>
       </c>
       <c r="H74" t="n">
-        <v>9027363</v>
+        <v>43598137</v>
       </c>
       <c r="I74" t="n">
-        <v>14289559</v>
+        <v>26072978</v>
       </c>
       <c r="J74" t="n">
-        <v>23316922</v>
+        <v>69671115</v>
       </c>
       <c r="K74" t="n">
-        <v>5262196</v>
+        <v>-17525159</v>
       </c>
       <c r="L74" t="n">
-        <v>12.9</v>
+        <v>-10.7</v>
       </c>
       <c r="M74" t="n">
-        <v>57.15</v>
+        <v>42.55</v>
       </c>
       <c r="N74" t="n">
-        <v>4764601759.2</v>
+        <v>3813075000</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>600165.SH</t>
+          <t>603789.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ST宁科</t>
+          <t>ST星农</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.89</v>
+        <v>6.99</v>
       </c>
       <c r="E75" t="n">
-        <v>5.0909</v>
+        <v>10.0787</v>
       </c>
       <c r="F75" t="n">
-        <v>1.78</v>
+        <v>0.98</v>
       </c>
       <c r="G75" t="n">
-        <v>73952251</v>
+        <v>17843163</v>
       </c>
       <c r="H75" t="n">
-        <v>10938882</v>
+        <v>7577160</v>
       </c>
       <c r="I75" t="n">
-        <v>11895574</v>
+        <v>13063611</v>
       </c>
       <c r="J75" t="n">
-        <v>22834456</v>
+        <v>20640771</v>
       </c>
       <c r="K75" t="n">
-        <v>956692</v>
+        <v>5486451</v>
       </c>
       <c r="L75" t="n">
-        <v>1.29</v>
+        <v>30.75</v>
       </c>
       <c r="M75" t="n">
-        <v>30.88</v>
+        <v>115.68</v>
       </c>
       <c r="N75" t="n">
-        <v>2118120436.94</v>
+        <v>1817400000</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>600172.SH</t>
+          <t>603815.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>交建股份</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.86</v>
+        <v>6.11</v>
       </c>
       <c r="E76" t="n">
-        <v>-6.4892</v>
+        <v>10.0901</v>
       </c>
       <c r="F76" t="n">
-        <v>20.58</v>
+        <v>3.04</v>
       </c>
       <c r="G76" t="n">
-        <v>4447473172</v>
+        <v>109796538</v>
       </c>
       <c r="H76" t="n">
-        <v>716485928.8099999</v>
+        <v>15145068.48</v>
       </c>
       <c r="I76" t="n">
-        <v>658809758.17</v>
+        <v>26688135</v>
       </c>
       <c r="J76" t="n">
-        <v>1375295686.98</v>
+        <v>41833203.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-57676170.64</v>
+        <v>11543066.52</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.3</v>
+        <v>10.51</v>
       </c>
       <c r="M76" t="n">
-        <v>30.92</v>
+        <v>38.1</v>
       </c>
       <c r="N76" t="n">
-        <v>21517671945</v>
+        <v>3781627075.85</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>600182.SH</t>
+          <t>603978.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>S佳通</t>
+          <t>深圳新星</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.71</v>
+        <v>27.14</v>
       </c>
       <c r="E77" t="n">
-        <v>3.9576</v>
+        <v>-10.0133</v>
       </c>
       <c r="F77" t="n">
-        <v>4.69</v>
+        <v>8.99</v>
       </c>
       <c r="G77" t="n">
-        <v>181294813</v>
+        <v>538144854</v>
       </c>
       <c r="H77" t="n">
-        <v>35233251</v>
+        <v>99727751.48</v>
       </c>
       <c r="I77" t="n">
-        <v>51714473</v>
+        <v>73130678.40000001</v>
       </c>
       <c r="J77" t="n">
-        <v>86947724</v>
+        <v>172858429.88</v>
       </c>
       <c r="K77" t="n">
-        <v>16481222</v>
+        <v>-26597073.08</v>
       </c>
       <c r="L77" t="n">
-        <v>9.09</v>
+        <v>-4.94</v>
       </c>
       <c r="M77" t="n">
-        <v>47.96</v>
+        <v>32.12</v>
       </c>
       <c r="N77" t="n">
-        <v>2500700000</v>
+        <v>5729099274.86</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>S股连续三个交易日内收盘价格涨幅偏离值累计达到15%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>600243.SH</t>
+          <t>605358.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>*ST海华</t>
+          <t>立昂微</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>3.64</v>
+        <v>59.49</v>
       </c>
       <c r="E78" t="n">
-        <v>4.8991</v>
+        <v>-8.0099</v>
       </c>
       <c r="F78" t="n">
-        <v>1.79</v>
+        <v>10.23</v>
       </c>
       <c r="G78" t="n">
-        <v>81859952</v>
+        <v>15646133664</v>
       </c>
       <c r="H78" t="n">
-        <v>15523068</v>
+        <v>858994013.6</v>
       </c>
       <c r="I78" t="n">
-        <v>17300765.28</v>
+        <v>1337749994.56</v>
       </c>
       <c r="J78" t="n">
-        <v>32823833.28</v>
+        <v>2196744008.16</v>
       </c>
       <c r="K78" t="n">
-        <v>1777697.28</v>
+        <v>478755980.96</v>
       </c>
       <c r="L78" t="n">
-        <v>2.17</v>
+        <v>3.06</v>
       </c>
       <c r="M78" t="n">
-        <v>40.1</v>
+        <v>14.04</v>
       </c>
       <c r="N78" t="n">
-        <v>1597414000</v>
+        <v>45938140699.77</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>600376.SH</t>
+          <t>688039.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>首开股份</t>
+          <t>当虹科技</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3.81</v>
+        <v>43.56</v>
       </c>
       <c r="E79" t="n">
-        <v>10.1156</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>1.44</v>
+        <v>7.34</v>
       </c>
       <c r="G79" t="n">
-        <v>141211805</v>
+        <v>335890000</v>
       </c>
       <c r="H79" t="n">
-        <v>25109805</v>
+        <v>31558667.36</v>
       </c>
       <c r="I79" t="n">
-        <v>91403805</v>
+        <v>86480057.76000001</v>
       </c>
       <c r="J79" t="n">
-        <v>116513610</v>
+        <v>118038725.12</v>
       </c>
       <c r="K79" t="n">
-        <v>66294000</v>
+        <v>54921390.4</v>
       </c>
       <c r="L79" t="n">
-        <v>46.95</v>
+        <v>16.35</v>
       </c>
       <c r="M79" t="n">
-        <v>82.51000000000001</v>
+        <v>35.14</v>
       </c>
       <c r="N79" t="n">
-        <v>9828143572.02</v>
+        <v>4817798029.44</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>600378.SH</t>
+          <t>688103.SH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>昊华科技</t>
+          <t>国力电子</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>76.01000000000001</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>-7.4967</v>
+        <v>16.7785</v>
       </c>
       <c r="F80" t="n">
-        <v>9.949999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="G80" t="n">
-        <v>8273815539</v>
+        <v>751003800</v>
       </c>
       <c r="H80" t="n">
-        <v>1297025388.3</v>
+        <v>111178318.08</v>
       </c>
       <c r="I80" t="n">
-        <v>1150502000.47</v>
+        <v>155550965.06</v>
       </c>
       <c r="J80" t="n">
-        <v>2447527388.77</v>
+        <v>266729283.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-146523387.83</v>
+        <v>44372646.98</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.77</v>
+        <v>5.91</v>
       </c>
       <c r="M80" t="n">
-        <v>29.58</v>
+        <v>35.52</v>
       </c>
       <c r="N80" t="n">
-        <v>81525693241.63</v>
+        <v>8126605157.16</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>600397.SH</t>
+          <t>688103.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>江钨装备</t>
+          <t>国力电子</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>25.65</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>-10</v>
+        <v>16.7785</v>
       </c>
       <c r="F81" t="n">
-        <v>14.46</v>
+        <v>9.51</v>
       </c>
       <c r="G81" t="n">
-        <v>3839382601</v>
+        <v>1636628700</v>
       </c>
       <c r="H81" t="n">
-        <v>538711753.95</v>
+        <v>317073502.47</v>
       </c>
       <c r="I81" t="n">
-        <v>787037403.72</v>
+        <v>276181990.07</v>
       </c>
       <c r="J81" t="n">
-        <v>1325749157.67</v>
+        <v>593255492.54</v>
       </c>
       <c r="K81" t="n">
-        <v>248325649.77</v>
+        <v>-40891512.4</v>
       </c>
       <c r="L81" t="n">
-        <v>6.47</v>
+        <v>-2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>34.53</v>
+        <v>36.25</v>
       </c>
       <c r="N81" t="n">
-        <v>25392470973.3</v>
+        <v>8126605157.16</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>600530.SH</t>
+          <t>688206.SH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>交大昂立</t>
+          <t>概伦电子</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5.7</v>
+        <v>48.76</v>
       </c>
       <c r="E82" t="n">
-        <v>10.0386</v>
+        <v>20.0098</v>
       </c>
       <c r="F82" t="n">
-        <v>1.51</v>
+        <v>5.58</v>
       </c>
       <c r="G82" t="n">
-        <v>64902703</v>
+        <v>1151606400</v>
       </c>
       <c r="H82" t="n">
-        <v>9206243</v>
+        <v>161212140.99</v>
       </c>
       <c r="I82" t="n">
-        <v>25241631</v>
+        <v>256732009.73</v>
       </c>
       <c r="J82" t="n">
-        <v>34447874</v>
+        <v>417944150.72</v>
       </c>
       <c r="K82" t="n">
-        <v>16035388</v>
+        <v>95519868.73999999</v>
       </c>
       <c r="L82" t="n">
-        <v>24.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>53.08</v>
+        <v>36.29</v>
       </c>
       <c r="N82" t="n">
-        <v>4417044000</v>
+        <v>21287583994.6</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>600545.SH</t>
+          <t>688257.SH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>新锐股份</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6.26</v>
+        <v>92.88</v>
       </c>
       <c r="E83" t="n">
-        <v>-4.1348</v>
+        <v>-15.9077</v>
       </c>
       <c r="F83" t="n">
-        <v>8.08</v>
+        <v>8.4</v>
       </c>
       <c r="G83" t="n">
-        <v>3355872658</v>
+        <v>2975348500</v>
       </c>
       <c r="H83" t="n">
-        <v>453704238.84</v>
+        <v>488583031.22</v>
       </c>
       <c r="I83" t="n">
-        <v>347801287.15</v>
+        <v>487401365.28</v>
       </c>
       <c r="J83" t="n">
-        <v>801505525.99</v>
+        <v>975984396.5</v>
       </c>
       <c r="K83" t="n">
-        <v>-105902951.69</v>
+        <v>-1181665.94</v>
       </c>
       <c r="L83" t="n">
-        <v>-3.16</v>
+        <v>-0.04</v>
       </c>
       <c r="M83" t="n">
-        <v>23.88</v>
+        <v>32.8</v>
       </c>
       <c r="N83" t="n">
-        <v>11192330509.72</v>
+        <v>32996853353.52</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>600552.SH</t>
+          <t>688496.SH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>凯盛科技</t>
+          <t>*ST清越</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>25.39</v>
+        <v>1.03</v>
       </c>
       <c r="E84" t="n">
-        <v>-5.0841</v>
+        <v>19.7674</v>
       </c>
       <c r="F84" t="n">
-        <v>12.34</v>
+        <v>8.06</v>
       </c>
       <c r="G84" t="n">
-        <v>13113751610</v>
+        <v>19296300</v>
       </c>
       <c r="H84" t="n">
-        <v>1324665283.43</v>
+        <v>2242220.63</v>
       </c>
       <c r="I84" t="n">
-        <v>1278749131.78</v>
+        <v>2309353.8</v>
       </c>
       <c r="J84" t="n">
-        <v>2603414415.21</v>
+        <v>4551574.43</v>
       </c>
       <c r="K84" t="n">
-        <v>-45916151.65</v>
+        <v>67133.17</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.35</v>
+        <v>0.35</v>
       </c>
       <c r="M84" t="n">
-        <v>19.85</v>
+        <v>23.59</v>
       </c>
       <c r="N84" t="n">
-        <v>23983569038.66</v>
+        <v>245083968</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>600581.SH</t>
+          <t>688507.SH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>*ST八钢</t>
+          <t>索辰科技</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.36</v>
+        <v>212</v>
       </c>
       <c r="E85" t="n">
-        <v>3.0568</v>
+        <v>-15.0335</v>
       </c>
       <c r="F85" t="n">
-        <v>1.18</v>
+        <v>23.71</v>
       </c>
       <c r="G85" t="n">
-        <v>110648476</v>
+        <v>2612866300</v>
       </c>
       <c r="H85" t="n">
-        <v>12315396.36</v>
+        <v>206080171.32</v>
       </c>
       <c r="I85" t="n">
-        <v>20801790</v>
+        <v>354756566.72</v>
       </c>
       <c r="J85" t="n">
-        <v>33117186.36</v>
+        <v>560836738.04</v>
       </c>
       <c r="K85" t="n">
-        <v>8486393.640000001</v>
+        <v>148676395.4</v>
       </c>
       <c r="L85" t="n">
-        <v>7.67</v>
+        <v>5.69</v>
       </c>
       <c r="M85" t="n">
-        <v>29.93</v>
+        <v>21.46</v>
       </c>
       <c r="N85" t="n">
-        <v>3617638973.2</v>
+        <v>10437974760</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>600624.SH</t>
+          <t>688622.SH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ST复华</t>
+          <t>*ST禾信</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.77</v>
+        <v>102.3</v>
       </c>
       <c r="E86" t="n">
-        <v>5.0139</v>
+        <v>-20.0031</v>
       </c>
       <c r="F86" t="n">
-        <v>0.53</v>
+        <v>2.64</v>
       </c>
       <c r="G86" t="n">
-        <v>67332559</v>
+        <v>199793100</v>
       </c>
       <c r="H86" t="n">
-        <v>11349842.01</v>
+        <v>85508884.44</v>
       </c>
       <c r="I86" t="n">
-        <v>11957834.76</v>
+        <v>33012318.68</v>
       </c>
       <c r="J86" t="n">
-        <v>23307676.77</v>
+        <v>118521203.12</v>
       </c>
       <c r="K86" t="n">
-        <v>607992.75</v>
+        <v>-52496565.76</v>
       </c>
       <c r="L86" t="n">
-        <v>0.9</v>
+        <v>-26.28</v>
       </c>
       <c r="M86" t="n">
-        <v>34.62</v>
+        <v>59.32</v>
       </c>
       <c r="N86" t="n">
-        <v>2561137971.34</v>
+        <v>7208622798.3</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>600630.SH</t>
+          <t>688669.SH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>龙头股份</t>
+          <t>聚石化学</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>9.619999999999999</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>-10.0094</v>
+        <v>-20</v>
       </c>
       <c r="F87" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="G87" t="n">
-        <v>264794850</v>
+        <v>725707400</v>
       </c>
       <c r="H87" t="n">
-        <v>50241270.97</v>
+        <v>124599194.97</v>
       </c>
       <c r="I87" t="n">
-        <v>23251074</v>
+        <v>146999468.62</v>
       </c>
       <c r="J87" t="n">
-        <v>73492344.97</v>
+        <v>271598663.59</v>
       </c>
       <c r="K87" t="n">
-        <v>-26990196.97</v>
+        <v>22400273.65</v>
       </c>
       <c r="L87" t="n">
-        <v>-10.19</v>
+        <v>3.09</v>
       </c>
       <c r="M87" t="n">
-        <v>27.75</v>
+        <v>37.43</v>
       </c>
       <c r="N87" t="n">
-        <v>4087168563.14</v>
+        <v>10890880059.84</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>600707.SH</t>
+          <t>688689.SH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>彩虹股份</t>
+          <t>银河微电</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>15.02</v>
+        <v>80.75</v>
       </c>
       <c r="E88" t="n">
-        <v>-10.006</v>
+        <v>18.6976</v>
       </c>
       <c r="F88" t="n">
-        <v>7.78</v>
+        <v>12.41</v>
       </c>
       <c r="G88" t="n">
-        <v>4263479007</v>
+        <v>1238065300</v>
       </c>
       <c r="H88" t="n">
-        <v>468056033.96</v>
+        <v>208658692.49</v>
       </c>
       <c r="I88" t="n">
-        <v>478674918.96</v>
+        <v>186310118.72</v>
       </c>
       <c r="J88" t="n">
-        <v>946730952.92</v>
+        <v>394968811.21</v>
       </c>
       <c r="K88" t="n">
-        <v>10618885</v>
+        <v>-22348573.77</v>
       </c>
       <c r="L88" t="n">
-        <v>0.25</v>
+        <v>-1.81</v>
       </c>
       <c r="M88" t="n">
-        <v>22.21</v>
+        <v>31.9</v>
       </c>
       <c r="N88" t="n">
-        <v>53886799374.64</v>
+        <v>10632860740.5</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>600734.SH</t>
+          <t>688797.SH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>*ST实达</t>
+          <t>臻宝科技</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.74</v>
+        <v>479.08</v>
       </c>
       <c r="E89" t="n">
-        <v>4.8193</v>
+        <v>-11.2979</v>
       </c>
       <c r="F89" t="n">
-        <v>3.01</v>
+        <v>31.3</v>
       </c>
       <c r="G89" t="n">
-        <v>323350755</v>
+        <v>4594643900</v>
       </c>
       <c r="H89" t="n">
-        <v>25576638.99</v>
+        <v>437451366.8</v>
       </c>
       <c r="I89" t="n">
-        <v>26587820.67</v>
+        <v>647558431.1</v>
       </c>
       <c r="J89" t="n">
-        <v>52164459.66</v>
+        <v>1085009797.9</v>
       </c>
       <c r="K89" t="n">
-        <v>1011181.68</v>
+        <v>210107064.3</v>
       </c>
       <c r="L89" t="n">
-        <v>0.31</v>
+        <v>4.57</v>
       </c>
       <c r="M89" t="n">
-        <v>16.13</v>
+        <v>23.61</v>
       </c>
       <c r="N89" t="n">
-        <v>3789464404.44</v>
+        <v>13985637757.84</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>600759.SH</t>
+          <t>920072.BJ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ST洲际</t>
+          <t>科莱瑞迪</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.12</v>
+        <v>34.93</v>
       </c>
       <c r="E90" t="n">
-        <v>4.9505</v>
+        <v>2.8563</v>
       </c>
       <c r="F90" t="n">
-        <v>7.64</v>
+        <v>29.99</v>
       </c>
       <c r="G90" t="n">
-        <v>682355117</v>
+        <v>153620200</v>
       </c>
       <c r="H90" t="n">
-        <v>47574700.24</v>
+        <v>22826063.47</v>
       </c>
       <c r="I90" t="n">
-        <v>46010084.8</v>
+        <v>13418946.11</v>
       </c>
       <c r="J90" t="n">
-        <v>93584785.04000001</v>
+        <v>36245009.58</v>
       </c>
       <c r="K90" t="n">
-        <v>-1564615.44</v>
+        <v>-9407117.359999999</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.23</v>
+        <v>-6.12</v>
       </c>
       <c r="M90" t="n">
-        <v>13.71</v>
+        <v>23.59</v>
       </c>
       <c r="N90" t="n">
-        <v>8784613853.6</v>
+        <v>505262450</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>ST、*ST证券连续三个交易日内收盘价格涨幅偏离值累计达到12%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>600784.SH</t>
+          <t>920161.BJ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>鲁银投资</t>
+          <t>龙辰科技</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7.8</v>
+        <v>38.1</v>
       </c>
       <c r="E91" t="n">
-        <v>3.4483</v>
+        <v>11.1435</v>
       </c>
       <c r="F91" t="n">
-        <v>3.38</v>
+        <v>26.74</v>
       </c>
       <c r="G91" t="n">
-        <v>467970337</v>
+        <v>364370400</v>
       </c>
       <c r="H91" t="n">
-        <v>63207961</v>
+        <v>33060641.23</v>
       </c>
       <c r="I91" t="n">
-        <v>89328712.52</v>
+        <v>55826833.32</v>
       </c>
       <c r="J91" t="n">
-        <v>152536673.52</v>
+        <v>88887474.55</v>
       </c>
       <c r="K91" t="n">
-        <v>26120751.52</v>
+        <v>22766192.09</v>
       </c>
       <c r="L91" t="n">
-        <v>5.58</v>
+        <v>6.25</v>
       </c>
       <c r="M91" t="n">
-        <v>32.6</v>
+        <v>24.39</v>
       </c>
       <c r="N91" t="n">
-        <v>5270087760.6</v>
+        <v>1405845804</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>600857.SH</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>宁波中百</t>
+          <t>吉和昌</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>21.3</v>
+        <v>55.56</v>
       </c>
       <c r="E92" t="n">
-        <v>-5.8772</v>
+        <v>-29.9899</v>
       </c>
       <c r="F92" t="n">
-        <v>10.03</v>
+        <v>66.48</v>
       </c>
       <c r="G92" t="n">
-        <v>493583212</v>
+        <v>1060648900</v>
       </c>
       <c r="H92" t="n">
-        <v>72236103.41</v>
+        <v>136804903.82</v>
       </c>
       <c r="I92" t="n">
-        <v>115841948.48</v>
+        <v>94045981.54000001</v>
       </c>
       <c r="J92" t="n">
-        <v>188078051.89</v>
+        <v>230850885.36</v>
       </c>
       <c r="K92" t="n">
-        <v>43605845.07</v>
+        <v>-42758922.28</v>
       </c>
       <c r="L92" t="n">
-        <v>8.83</v>
+        <v>-4.03</v>
       </c>
       <c r="M92" t="n">
-        <v>38.1</v>
+        <v>21.77</v>
       </c>
       <c r="N92" t="n">
-        <v>4778014274.7</v>
+        <v>1400112000</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>600988.SH</t>
+          <t>920211.BJ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>新睿电子</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>31.23</v>
+        <v>180.5</v>
       </c>
       <c r="E93" t="n">
-        <v>10.0035</v>
+        <v>14.0384</v>
       </c>
       <c r="F93" t="n">
-        <v>2.24</v>
+        <v>53.54</v>
       </c>
       <c r="G93" t="n">
-        <v>2994947705</v>
-      </c>
-      <c r="H93" t="n">
-        <v>387357264.22</v>
-      </c>
-      <c r="I93" t="n">
-        <v>536265116.81</v>
-      </c>
-      <c r="J93" t="n">
-        <v>923622381.03</v>
-      </c>
-      <c r="K93" t="n">
-        <v>148907852.59</v>
-      </c>
-      <c r="L93" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="M93" t="n">
-        <v>30.84</v>
-      </c>
+        <v>831086200</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>51963952334.94</v>
+        <v>1039680000</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>601678.SH</t>
+          <t>920211.BJ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>滨化股份</t>
+          <t>新睿电子</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6.93</v>
+        <v>180.5</v>
       </c>
       <c r="E94" t="n">
-        <v>-10</v>
+        <v>14.0384</v>
       </c>
       <c r="F94" t="n">
-        <v>20.9</v>
+        <v>53.54</v>
       </c>
       <c r="G94" t="n">
-        <v>3052366108</v>
+        <v>536199400</v>
       </c>
       <c r="H94" t="n">
-        <v>353086658.2</v>
+        <v>72184692.08</v>
       </c>
       <c r="I94" t="n">
-        <v>204194500.1</v>
+        <v>69608916.34</v>
       </c>
       <c r="J94" t="n">
-        <v>557281158.3</v>
+        <v>141793608.42</v>
       </c>
       <c r="K94" t="n">
-        <v>-148892158.1</v>
+        <v>-2575775.74</v>
       </c>
       <c r="L94" t="n">
-        <v>-4.88</v>
+        <v>-0.48</v>
       </c>
       <c r="M94" t="n">
-        <v>18.26</v>
+        <v>26.44</v>
       </c>
       <c r="N94" t="n">
-        <v>14160320392.68</v>
+        <v>1039680000</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>603078.SH</t>
+          <t>920211.BJ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>江化微</t>
+          <t>新睿电子</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>56.26</v>
+        <v>180.5</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.1248</v>
+        <v>14.0384</v>
       </c>
       <c r="F95" t="n">
-        <v>19.58</v>
+        <v>53.54</v>
       </c>
       <c r="G95" t="n">
-        <v>4046044000</v>
+        <v>831086200</v>
       </c>
       <c r="H95" t="n">
-        <v>739879002.59</v>
+        <v>80742933.2</v>
       </c>
       <c r="I95" t="n">
-        <v>641782032.98</v>
+        <v>120952075.83</v>
       </c>
       <c r="J95" t="n">
-        <v>1381661035.57</v>
+        <v>201695009.03</v>
       </c>
       <c r="K95" t="n">
-        <v>-98096969.61</v>
+        <v>40209142.63</v>
       </c>
       <c r="L95" t="n">
-        <v>-2.42</v>
+        <v>4.84</v>
       </c>
       <c r="M95" t="n">
-        <v>34.15</v>
+        <v>24.27</v>
       </c>
       <c r="N95" t="n">
-        <v>21695951572.48</v>
+        <v>1039680000</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>603135.SH</t>
+          <t>920222.BJ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>中重科技</t>
+          <t>益坤电气</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>14.56</v>
+        <v>29.37</v>
       </c>
       <c r="E96" t="n">
-        <v>6.0452</v>
+        <v>-7.4961</v>
       </c>
       <c r="F96" t="n">
-        <v>9.19</v>
+        <v>31.85</v>
       </c>
       <c r="G96" t="n">
-        <v>1312783192</v>
+        <v>113875500</v>
       </c>
       <c r="H96" t="n">
-        <v>177229535.4</v>
+        <v>15009301.45</v>
       </c>
       <c r="I96" t="n">
-        <v>205204593.66</v>
+        <v>12687965.42</v>
       </c>
       <c r="J96" t="n">
-        <v>382434129.06</v>
+        <v>27697266.87</v>
       </c>
       <c r="K96" t="n">
-        <v>27975058.26</v>
+        <v>-2321336.03</v>
       </c>
       <c r="L96" t="n">
-        <v>2.13</v>
+        <v>-2.04</v>
       </c>
       <c r="M96" t="n">
-        <v>29.13</v>
+        <v>24.32</v>
       </c>
       <c r="N96" t="n">
-        <v>9166074444.799999</v>
+        <v>339593268.3</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>603178.SH</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>圣龙股份</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="E97" t="n">
-        <v>10.0351</v>
-      </c>
-      <c r="F97" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="G97" t="n">
-        <v>89144363</v>
-      </c>
-      <c r="H97" t="n">
-        <v>14050367</v>
-      </c>
-      <c r="I97" t="n">
-        <v>29146972</v>
-      </c>
-      <c r="J97" t="n">
-        <v>43197339</v>
-      </c>
-      <c r="K97" t="n">
-        <v>15096605</v>
-      </c>
-      <c r="L97" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="M97" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="N97" t="n">
-        <v>3706938294.08</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>603270.SH</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>金帝股份</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-1.6628</v>
-      </c>
-      <c r="F98" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="G98" t="n">
-        <v>574460092</v>
-      </c>
-      <c r="H98" t="n">
-        <v>43861439.84</v>
-      </c>
-      <c r="I98" t="n">
-        <v>29356334.52</v>
-      </c>
-      <c r="J98" t="n">
-        <v>73217774.36</v>
-      </c>
-      <c r="K98" t="n">
-        <v>-14505105.32</v>
-      </c>
-      <c r="L98" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="M98" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="N98" t="n">
-        <v>2425581678.1</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>603286.SH</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>日盈电子</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>56.96</v>
-      </c>
-      <c r="E99" t="n">
-        <v>10.0039</v>
-      </c>
-      <c r="F99" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="G99" t="n">
-        <v>542413647</v>
-      </c>
-      <c r="H99" t="n">
-        <v>65579078.6</v>
-      </c>
-      <c r="I99" t="n">
-        <v>126443910.6</v>
-      </c>
-      <c r="J99" t="n">
-        <v>192022989.2</v>
-      </c>
-      <c r="K99" t="n">
-        <v>60864832</v>
-      </c>
-      <c r="L99" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="M99" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="N99" t="n">
-        <v>6620757048.96</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>603327.SH</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>福蓉科技</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="E100" t="n">
-        <v>10.0621</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G100" t="n">
-        <v>149230781</v>
-      </c>
-      <c r="H100" t="n">
-        <v>19017606</v>
-      </c>
-      <c r="I100" t="n">
-        <v>97301458.04000001</v>
-      </c>
-      <c r="J100" t="n">
-        <v>116319064.04</v>
-      </c>
-      <c r="K100" t="n">
-        <v>78283852.04000001</v>
-      </c>
-      <c r="L100" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="M100" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="N100" t="n">
-        <v>9262769929.6</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>603338.SH</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>浙江鼎力</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="E101" t="n">
-        <v>10.0064</v>
-      </c>
-      <c r="F101" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1462846975</v>
-      </c>
-      <c r="H101" t="n">
-        <v>296256173.61</v>
-      </c>
-      <c r="I101" t="n">
-        <v>489593091.81</v>
-      </c>
-      <c r="J101" t="n">
-        <v>785849265.42</v>
-      </c>
-      <c r="K101" t="n">
-        <v>193336918.2</v>
-      </c>
-      <c r="L101" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="M101" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="N101" t="n">
-        <v>26162994907.93</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260707</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5517</v>
+      </c>
+      <c r="C2" t="n">
+        <v>693</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4797</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25984.66</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4041.2382</v>
+        <v>3990.2353</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.06</v>
+        <v>-1.26</v>
       </c>
       <c r="F2" t="n">
-        <v>14321.13</v>
+        <v>11963.71</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15416.804</v>
+        <v>15225.1136</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="F3" t="n">
-        <v>16589.99</v>
+        <v>8279.379999999999</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3948.86</v>
+        <v>3911.9075</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.77</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>7640.16</v>
+        <v>2887.63</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4841.998</v>
+        <v>4792.2624</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>-1.03</v>
       </c>
       <c r="F5" t="n">
-        <v>9079.459999999999</v>
+        <v>7626.18</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1996.1029</v>
+        <v>2001.5859</v>
       </c>
       <c r="E6" t="n">
-        <v>1.04</v>
+        <v>0.27</v>
       </c>
       <c r="F6" t="n">
-        <v>1735.37</v>
+        <v>1595.6</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8472.602800000001</v>
+        <v>8301.8035</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.72</v>
+        <v>-2.02</v>
       </c>
       <c r="F7" t="n">
-        <v>6550.13</v>
+        <v>5444.56</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,5956 @@
           <t>20260707</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>25984.66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920527.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25.0551</v>
+      </c>
+      <c r="J2" t="n">
+        <v>76094.85000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>126673.06209</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301516.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>233851.24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>417897.94614</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>765659.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3389040.404</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19.9953</v>
+      </c>
+      <c r="J5" t="n">
+        <v>42328.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>214899.7637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688261.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="D6" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>88.39</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="G6" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.332</v>
+      </c>
+      <c r="J6" t="n">
+        <v>193266.41</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1902863.506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688584.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15.3051</v>
+      </c>
+      <c r="J7" t="n">
+        <v>333682.92</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1139623.041</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688605.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="D8" t="n">
+        <v>115.85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="F8" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15.2161</v>
+      </c>
+      <c r="J8" t="n">
+        <v>128471.79</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1363704.609</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301237.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14.6325</v>
+      </c>
+      <c r="J9" t="n">
+        <v>89719.86</v>
+      </c>
+      <c r="K9" t="n">
+        <v>742801.26036</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300985.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="D10" t="n">
+        <v>58</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14.4276</v>
+      </c>
+      <c r="J10" t="n">
+        <v>115692.37</v>
+      </c>
+      <c r="K10" t="n">
+        <v>627669.62758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300043.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1757167.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>900976.5008799999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-20.0617</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4373.63</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2265.54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300716.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-20.0069</v>
+      </c>
+      <c r="J3" t="n">
+        <v>150751.59</v>
+      </c>
+      <c r="K3" t="n">
+        <v>370763.98293</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301067.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-19.7294</v>
+      </c>
+      <c r="J4" t="n">
+        <v>128494.31</v>
+      </c>
+      <c r="K4" t="n">
+        <v>407261.16262</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-16.3366</v>
+      </c>
+      <c r="J5" t="n">
+        <v>194291.73</v>
+      </c>
+      <c r="K5" t="n">
+        <v>67351.45564</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-15.3736</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38049.16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>116614.38672</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301365.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="G7" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-14.3511</v>
+      </c>
+      <c r="J7" t="n">
+        <v>116078.51</v>
+      </c>
+      <c r="K7" t="n">
+        <v>421302.80647</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688272.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-14.2857</v>
+      </c>
+      <c r="J8" t="n">
+        <v>45026.11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>178646.163</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301418.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="E9" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-14.0374</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53926.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>259659.21356</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>920083.BJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="D10" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-13.848</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50701.13</v>
+      </c>
+      <c r="K10" t="n">
+        <v>233747.54807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>920206.BJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-13.7415</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26838</v>
+      </c>
+      <c r="K11" t="n">
+        <v>121421.11945</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.439</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3102426</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1571137</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1860432.23</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3431569.23</v>
+      </c>
+      <c r="K2" t="n">
+        <v>289295.23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="M2" t="n">
+        <v>110.61</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50515627.2</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000007.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>全新好</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-10.0155</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G3" t="n">
+        <v>203058414</v>
+      </c>
+      <c r="H3" t="n">
+        <v>61680370.13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34658101</v>
+      </c>
+      <c r="J3" t="n">
+        <v>96338471.13</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-27022269.13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-13.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4015332829.96</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000078.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ST海王</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.7561</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>606420000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>43299703.96</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39702888.51</v>
+      </c>
+      <c r="J4" t="n">
+        <v>83002592.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-3596815.45</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4725388267.2</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000078.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ST海王</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.7561</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>606422445</v>
+      </c>
+      <c r="H5" t="n">
+        <v>43299704</v>
+      </c>
+      <c r="I5" t="n">
+        <v>39702889</v>
+      </c>
+      <c r="J5" t="n">
+        <v>83002593</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-3596815</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4725388267.2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到12%的ST证券、*ST证券和未完成股改证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000301.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>东方盛虹</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.992800000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1133871941</v>
+      </c>
+      <c r="H6" t="n">
+        <v>113241588.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>65308063</v>
+      </c>
+      <c r="J6" t="n">
+        <v>178549651.09</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-47933525.09</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>82142075743.64</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000593.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>德龙汇能</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.4477</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1263732212</v>
+      </c>
+      <c r="H7" t="n">
+        <v>172194087.28</v>
+      </c>
+      <c r="I7" t="n">
+        <v>155709303.66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>327903390.94</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-16484783.62</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9410183186.25</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000593.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>德龙汇能</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.4477</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1678979623</v>
+      </c>
+      <c r="H8" t="n">
+        <v>197042590.68</v>
+      </c>
+      <c r="I8" t="n">
+        <v>208457033.03</v>
+      </c>
+      <c r="J8" t="n">
+        <v>405499623.71</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11414442.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9410183186.25</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000838.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>*ST发展</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G9" t="n">
+        <v>119960040</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18314972</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10438333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28753305</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-7876639</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="M9" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1801939612.05</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000949.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>新乡化纤</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-10.0324</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G10" t="n">
+        <v>464105975</v>
+      </c>
+      <c r="H10" t="n">
+        <v>122017630.83</v>
+      </c>
+      <c r="I10" t="n">
+        <v>85725738.09999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>207743368.93</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-36291892.73</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9209833771.879999</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000962.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>东方钽业</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-6.3824</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7609670897</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1551426898.06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1699127288.99</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3250554187.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>147700390.93</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M11" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="N11" t="n">
+        <v>32032294928.4</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000973.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>佛塑科技</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0377</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1442843986</v>
+      </c>
+      <c r="H12" t="n">
+        <v>93483438.78</v>
+      </c>
+      <c r="I12" t="n">
+        <v>220940368.89</v>
+      </c>
+      <c r="J12" t="n">
+        <v>314423807.67</v>
+      </c>
+      <c r="K12" t="n">
+        <v>127456930.11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14105029833.18</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>001311.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>多利科技</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.0112</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G13" t="n">
+        <v>312402415</v>
+      </c>
+      <c r="H13" t="n">
+        <v>70823815.05</v>
+      </c>
+      <c r="I13" t="n">
+        <v>82951631.02</v>
+      </c>
+      <c r="J13" t="n">
+        <v>153775446.07</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12127815.97</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="M13" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3484158193.88</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-8.761799999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3998353594</v>
+      </c>
+      <c r="H14" t="n">
+        <v>450309079.21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>571398112.89</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1021707192.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>121089033.68</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14975110904.18</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-8.761799999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11154753313</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1088961811.72</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1562559630.01</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2651521441.73</v>
+      </c>
+      <c r="K15" t="n">
+        <v>473597818.29</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14975110904.18</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002129.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TCL中环</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3797452155</v>
+      </c>
+      <c r="H16" t="n">
+        <v>410936662.38</v>
+      </c>
+      <c r="I16" t="n">
+        <v>885052707.61</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1295989369.99</v>
+      </c>
+      <c r="K16" t="n">
+        <v>474116045.23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="M16" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="N16" t="n">
+        <v>44518373396</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002137.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>实益达</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.0096</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1120029795</v>
+      </c>
+      <c r="H17" t="n">
+        <v>75522696</v>
+      </c>
+      <c r="I17" t="n">
+        <v>239235630</v>
+      </c>
+      <c r="J17" t="n">
+        <v>314758326</v>
+      </c>
+      <c r="K17" t="n">
+        <v>163712934</v>
+      </c>
+      <c r="L17" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4531515865.83</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002141.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>贤丰控股</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.5398</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1470983788</v>
+      </c>
+      <c r="H18" t="n">
+        <v>219569902.85</v>
+      </c>
+      <c r="I18" t="n">
+        <v>192952554.39</v>
+      </c>
+      <c r="J18" t="n">
+        <v>412522457.24</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-26617348.46</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="M18" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6042674418.3</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002185.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.979900000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11999102685</v>
+      </c>
+      <c r="H19" t="n">
+        <v>678020834</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2255004980.49</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2933025814.49</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1576984146.49</v>
+      </c>
+      <c r="L19" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N19" t="n">
+        <v>72865753031.00999</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002329.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>皇氏集团</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.1162</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>708471765</v>
+      </c>
+      <c r="H20" t="n">
+        <v>97754232.13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>115477289.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>213231521.49</v>
+      </c>
+      <c r="K20" t="n">
+        <v>17723057.23</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2261027446.28</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.3215</v>
+      </c>
+      <c r="F21" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3850158179</v>
+      </c>
+      <c r="H21" t="n">
+        <v>507320404.89</v>
+      </c>
+      <c r="I21" t="n">
+        <v>412351738.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>919672143.24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-94968666.54000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14159792815.09</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002457.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>青龙管业</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.5387</v>
+      </c>
+      <c r="F22" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1383427146</v>
+      </c>
+      <c r="H22" t="n">
+        <v>174952236.64</v>
+      </c>
+      <c r="I22" t="n">
+        <v>89063284.59</v>
+      </c>
+      <c r="J22" t="n">
+        <v>264015521.23</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-85888952.05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="M22" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4995722531.51</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002457.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>青龙管业</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.5387</v>
+      </c>
+      <c r="F23" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2105119266</v>
+      </c>
+      <c r="H23" t="n">
+        <v>204086378.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>194693949.09</v>
+      </c>
+      <c r="J23" t="n">
+        <v>398780327.99</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-9392429.810000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4995722531.51</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002585.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>双星新材</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9.9613</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G24" t="n">
+        <v>481444990</v>
+      </c>
+      <c r="H24" t="n">
+        <v>38078103.19</v>
+      </c>
+      <c r="I24" t="n">
+        <v>236793963.54</v>
+      </c>
+      <c r="J24" t="n">
+        <v>274872066.73</v>
+      </c>
+      <c r="K24" t="n">
+        <v>198715860.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="M24" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10082424065.58</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002607.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>中公教育</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8.134</v>
+      </c>
+      <c r="F25" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1917428022</v>
+      </c>
+      <c r="H25" t="n">
+        <v>153664655.84</v>
+      </c>
+      <c r="I25" t="n">
+        <v>181646604.33</v>
+      </c>
+      <c r="J25" t="n">
+        <v>335311260.17</v>
+      </c>
+      <c r="K25" t="n">
+        <v>27981948.49</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12528174879.12</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002747.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>埃斯顿</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>49</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.4523</v>
+      </c>
+      <c r="F26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>22860974026</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2877265647.35</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2573285187.23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5450550834.58</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-303980460.12</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="N26" t="n">
+        <v>38337826772</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002767.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>先锋电子</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-6.754</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>331115445</v>
+      </c>
+      <c r="H27" t="n">
+        <v>75499794.91</v>
+      </c>
+      <c r="I27" t="n">
+        <v>39235424.68</v>
+      </c>
+      <c r="J27" t="n">
+        <v>114735219.59</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-36264370.23</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="M27" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2408965863.5</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002774.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>快意电梯</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-9.981</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="G28" t="n">
+        <v>295335723</v>
+      </c>
+      <c r="H28" t="n">
+        <v>70935492</v>
+      </c>
+      <c r="I28" t="n">
+        <v>39431727</v>
+      </c>
+      <c r="J28" t="n">
+        <v>110367219</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-31503765</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="M28" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4015196636.25</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-8.333299999999999</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1944373</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1013479.08</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1082494.28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2095973.36</v>
+      </c>
+      <c r="K29" t="n">
+        <v>69015.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>41109432.32</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002841.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>视源股份</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.0102</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1266125229</v>
+      </c>
+      <c r="H30" t="n">
+        <v>233628403.24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>319608720.48</v>
+      </c>
+      <c r="J30" t="n">
+        <v>553237123.72</v>
+      </c>
+      <c r="K30" t="n">
+        <v>85980317.23999999</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="M30" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>22459561813.68</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002842.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>翔鹭钨业</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-7.2589</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6455768467</v>
+      </c>
+      <c r="H31" t="n">
+        <v>907628313.4400001</v>
+      </c>
+      <c r="I31" t="n">
+        <v>869338736.4400001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1776967049.88</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-38289577</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10118346310.71</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002856.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>*ST美芝</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-9.9945</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G32" t="n">
+        <v>454451364</v>
+      </c>
+      <c r="H32" t="n">
+        <v>122692535.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>96759652.59999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>219452187.8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-25932882.6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="M32" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2030793820.77</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-5.7143</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1798700</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1002309.07</v>
+      </c>
+      <c r="I33" t="n">
+        <v>696036</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1698345.07</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-306273.07</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-17.03</v>
+      </c>
+      <c r="M33" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="N33" t="n">
+        <v>33416608.83</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002931.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>锋龙股份</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1303242529</v>
+      </c>
+      <c r="H34" t="n">
+        <v>201556857</v>
+      </c>
+      <c r="I34" t="n">
+        <v>222518895</v>
+      </c>
+      <c r="J34" t="n">
+        <v>424075752</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20962038</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M34" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14417802745.92</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002989.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>中天精装</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-9.994</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G35" t="n">
+        <v>332222082</v>
+      </c>
+      <c r="H35" t="n">
+        <v>61527193.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>54192692</v>
+      </c>
+      <c r="J35" t="n">
+        <v>115719885.4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-7334501.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="M35" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5968648370.79</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>003009.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>中天火箭</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-10.0047</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="G36" t="n">
+        <v>532874045</v>
+      </c>
+      <c r="H36" t="n">
+        <v>32086927.06</v>
+      </c>
+      <c r="I36" t="n">
+        <v>74648618.27</v>
+      </c>
+      <c r="J36" t="n">
+        <v>106735545.33</v>
+      </c>
+      <c r="K36" t="n">
+        <v>42561691.21</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9540335462.790001</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>113703.SH</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N翔26转</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>144.634</v>
+      </c>
+      <c r="E37" t="n">
+        <v>44.634</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>231374660</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50185200</v>
+      </c>
+      <c r="I37" t="n">
+        <v>45348690</v>
+      </c>
+      <c r="J37" t="n">
+        <v>95533890</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-4836510</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M37" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>113704.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N春风转</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>169465990</v>
+      </c>
+      <c r="H38" t="n">
+        <v>65095560</v>
+      </c>
+      <c r="I38" t="n">
+        <v>121729750</v>
+      </c>
+      <c r="J38" t="n">
+        <v>186825310</v>
+      </c>
+      <c r="K38" t="n">
+        <v>56634190</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="M38" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>123273.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>三江转债</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>226.512</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>13041881</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3090076.71</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13041881.42</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16131958.13</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9951804.710000001</v>
+      </c>
+      <c r="L39" t="n">
+        <v>76.31</v>
+      </c>
+      <c r="M39" t="n">
+        <v>123.69</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>123273.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>三江转债</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>226.512</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>20889578</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3099514.71</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20889578.42</v>
+      </c>
+      <c r="J40" t="n">
+        <v>23989093.13</v>
+      </c>
+      <c r="K40" t="n">
+        <v>17790063.71</v>
+      </c>
+      <c r="L40" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="M40" t="n">
+        <v>114.84</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.1429</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1915109</v>
+      </c>
+      <c r="H41" t="n">
+        <v>811791</v>
+      </c>
+      <c r="I41" t="n">
+        <v>514578.9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1326369.9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-297212.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-15.52</v>
+      </c>
+      <c r="M41" t="n">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>26046832.5</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>300716.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>*ST泉为</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-20.0069</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="G42" t="n">
+        <v>370763983</v>
+      </c>
+      <c r="H42" t="n">
+        <v>76231908.05</v>
+      </c>
+      <c r="I42" t="n">
+        <v>42295892</v>
+      </c>
+      <c r="J42" t="n">
+        <v>118527800.05</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-33936016.05</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-9.15</v>
+      </c>
+      <c r="M42" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3723665400</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>300745.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>欣锐科技</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12.7189</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3166987368</v>
+      </c>
+      <c r="H43" t="n">
+        <v>685763926.24</v>
+      </c>
+      <c r="I43" t="n">
+        <v>555882157.83</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1241646084.07</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-129881768.41</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7970868851.31</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>301067.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>显盈科技</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-19.7294</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="G44" t="n">
+        <v>407261163</v>
+      </c>
+      <c r="H44" t="n">
+        <v>75601045.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>89049530.67</v>
+      </c>
+      <c r="J44" t="n">
+        <v>164650576.47</v>
+      </c>
+      <c r="K44" t="n">
+        <v>13448484.87</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1893165174</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>301139.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>*ST元道</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-16.3366</v>
+      </c>
+      <c r="F45" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="G45" t="n">
+        <v>67351456</v>
+      </c>
+      <c r="H45" t="n">
+        <v>14991499</v>
+      </c>
+      <c r="I45" t="n">
+        <v>5540692.4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>20532191.4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-9450806.6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-14.03</v>
+      </c>
+      <c r="M45" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="N45" t="n">
+        <v>257444960.24</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19.9953</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>214899764</v>
+      </c>
+      <c r="H46" t="n">
+        <v>37305796</v>
+      </c>
+      <c r="I46" t="n">
+        <v>142110307</v>
+      </c>
+      <c r="J46" t="n">
+        <v>179416103</v>
+      </c>
+      <c r="K46" t="n">
+        <v>104804511</v>
+      </c>
+      <c r="L46" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="M46" t="n">
+        <v>83.48999999999999</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3837690490.56</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>301516.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>中远通</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="E47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="G47" t="n">
+        <v>417897946</v>
+      </c>
+      <c r="H47" t="n">
+        <v>71364218.42</v>
+      </c>
+      <c r="I47" t="n">
+        <v>77820677.84999999</v>
+      </c>
+      <c r="J47" t="n">
+        <v>149184896.27</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6456459.43</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M47" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1313684218.08</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>301516.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>中远通</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="E48" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="G48" t="n">
+        <v>614969195</v>
+      </c>
+      <c r="H48" t="n">
+        <v>108753914.43</v>
+      </c>
+      <c r="I48" t="n">
+        <v>113214080.85</v>
+      </c>
+      <c r="J48" t="n">
+        <v>221967995.28</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4460166.42</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M48" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1313684218.08</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>37.74</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.7625999999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>499302058</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47560763.32</v>
+      </c>
+      <c r="I49" t="n">
+        <v>43929277.09</v>
+      </c>
+      <c r="J49" t="n">
+        <v>91490040.41</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-3631486.23</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M49" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1234039238.82</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600094.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>大名城</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0287</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G50" t="n">
+        <v>122700371</v>
+      </c>
+      <c r="H50" t="n">
+        <v>22998403.2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>39694088.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>62692491.8</v>
+      </c>
+      <c r="K50" t="n">
+        <v>16695685.4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="M50" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8207845268.62</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600172.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-1.0243</v>
+      </c>
+      <c r="F51" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6860525095</v>
+      </c>
+      <c r="H51" t="n">
+        <v>903814003.88</v>
+      </c>
+      <c r="I51" t="n">
+        <v>535181491.17</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1438995495.05</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-368632512.71</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="M51" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="N51" t="n">
+        <v>23432055570</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>600187.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>*ST国中</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-10.2564</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G52" t="n">
+        <v>86393222</v>
+      </c>
+      <c r="H52" t="n">
+        <v>11430556</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5550668</v>
+      </c>
+      <c r="J52" t="n">
+        <v>16981224</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-5879888</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="M52" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2259293544.2</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>600246.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>万通发展</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9.9941</v>
+      </c>
+      <c r="F53" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6727777317</v>
+      </c>
+      <c r="H53" t="n">
+        <v>692688048.47</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1023335439.2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1716023487.67</v>
+      </c>
+      <c r="K53" t="n">
+        <v>330647390.73</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N53" t="n">
+        <v>35161672053.6</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>600288.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>大恒科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9.9717</v>
+      </c>
+      <c r="F54" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1869913047</v>
+      </c>
+      <c r="H54" t="n">
+        <v>434631478.52</v>
+      </c>
+      <c r="I54" t="n">
+        <v>242092910.53</v>
+      </c>
+      <c r="J54" t="n">
+        <v>676724389.05</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-192538567.99</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="M54" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6792240000</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>600288.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>大恒科技</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.9717</v>
+      </c>
+      <c r="F55" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2190321280</v>
+      </c>
+      <c r="H55" t="n">
+        <v>473147287.52</v>
+      </c>
+      <c r="I55" t="n">
+        <v>271240121.53</v>
+      </c>
+      <c r="J55" t="n">
+        <v>744387409.05</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-201907165.99</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="M55" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="N55" t="n">
+        <v>6792240000</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>600376.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>首开股份</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-10.0756</v>
+      </c>
+      <c r="F56" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="G56" t="n">
+        <v>577534096</v>
+      </c>
+      <c r="H56" t="n">
+        <v>51273440.03</v>
+      </c>
+      <c r="I56" t="n">
+        <v>68385675</v>
+      </c>
+      <c r="J56" t="n">
+        <v>119659115.03</v>
+      </c>
+      <c r="K56" t="n">
+        <v>17112234.97</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M56" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="N56" t="n">
+        <v>9209047913.940001</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>600379.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>宝光股份</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="F57" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="G57" t="n">
+        <v>683222727</v>
+      </c>
+      <c r="H57" t="n">
+        <v>38423140.36</v>
+      </c>
+      <c r="I57" t="n">
+        <v>41237808.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>79660949.16</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2814668.44</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5580406431.6</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-10.0462</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="G58" t="n">
+        <v>274169554</v>
+      </c>
+      <c r="H58" t="n">
+        <v>37389578</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24763233</v>
+      </c>
+      <c r="J58" t="n">
+        <v>62152811</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-12626345</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="M58" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3309671840.63</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>600630.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>龙头股份</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-10.0462</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="G59" t="n">
+        <v>710109377</v>
+      </c>
+      <c r="H59" t="n">
+        <v>101093595.97</v>
+      </c>
+      <c r="I59" t="n">
+        <v>45728206</v>
+      </c>
+      <c r="J59" t="n">
+        <v>146821801.97</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-55365389.97</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3309671840.63</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>600791.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>京能置业</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-9.977600000000001</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G60" t="n">
+        <v>374923133</v>
+      </c>
+      <c r="H60" t="n">
+        <v>62917260</v>
+      </c>
+      <c r="I60" t="n">
+        <v>83455291</v>
+      </c>
+      <c r="J60" t="n">
+        <v>146372551</v>
+      </c>
+      <c r="K60" t="n">
+        <v>20538031</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M60" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3632078978.88</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>600843.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>上工申贝</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10.0112</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G61" t="n">
+        <v>205233181</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24031236</v>
+      </c>
+      <c r="I61" t="n">
+        <v>11999009.1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>36030245.1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-12032226.9</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="M61" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3830624121.25</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>601121.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>宝地矿业</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.034</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G62" t="n">
+        <v>50482822</v>
+      </c>
+      <c r="H62" t="n">
+        <v>14180299</v>
+      </c>
+      <c r="I62" t="n">
+        <v>33323735</v>
+      </c>
+      <c r="J62" t="n">
+        <v>47504034</v>
+      </c>
+      <c r="K62" t="n">
+        <v>19143436</v>
+      </c>
+      <c r="L62" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="M62" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5176000000</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>601678.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>滨化股份</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-4.8077</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6119358586</v>
+      </c>
+      <c r="H63" t="n">
+        <v>583418805.26</v>
+      </c>
+      <c r="I63" t="n">
+        <v>492701384.23</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1076120189.49</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-90717421.03</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="M63" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="N63" t="n">
+        <v>12137417479.44</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>603020.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>爱普股份</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-10.0068</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="G64" t="n">
+        <v>276914681</v>
+      </c>
+      <c r="H64" t="n">
+        <v>68204682</v>
+      </c>
+      <c r="I64" t="n">
+        <v>55634193.44</v>
+      </c>
+      <c r="J64" t="n">
+        <v>123838875.44</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-12570488.56</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="M64" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4965931372.28</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>603178.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>圣龙股份</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.0269</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="G65" t="n">
+        <v>147152966</v>
+      </c>
+      <c r="H65" t="n">
+        <v>20224098.95</v>
+      </c>
+      <c r="I65" t="n">
+        <v>40449392</v>
+      </c>
+      <c r="J65" t="n">
+        <v>60673490.95</v>
+      </c>
+      <c r="K65" t="n">
+        <v>20225293.05</v>
+      </c>
+      <c r="L65" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="M65" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3865334254.35</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>603211.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>晋拓股份</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-6.299</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1294031584</v>
+      </c>
+      <c r="H66" t="n">
+        <v>192963900</v>
+      </c>
+      <c r="I66" t="n">
+        <v>234363239</v>
+      </c>
+      <c r="J66" t="n">
+        <v>427327139</v>
+      </c>
+      <c r="K66" t="n">
+        <v>41399339</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10067768320</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>603272.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>*ST联翔</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G67" t="n">
+        <v>331379862</v>
+      </c>
+      <c r="H67" t="n">
+        <v>48713281.17</v>
+      </c>
+      <c r="I67" t="n">
+        <v>58425830.34</v>
+      </c>
+      <c r="J67" t="n">
+        <v>107139111.51</v>
+      </c>
+      <c r="K67" t="n">
+        <v>9712549.17</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M67" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2107773180</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-9.894399999999999</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="G68" t="n">
+        <v>638904297</v>
+      </c>
+      <c r="H68" t="n">
+        <v>133295794.44</v>
+      </c>
+      <c r="I68" t="n">
+        <v>226502085.62</v>
+      </c>
+      <c r="J68" t="n">
+        <v>359797880.06</v>
+      </c>
+      <c r="K68" t="n">
+        <v>93206291.18000001</v>
+      </c>
+      <c r="L68" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="M68" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2848539205.44</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-9.894399999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1541381299</v>
+      </c>
+      <c r="H69" t="n">
+        <v>269958974.84</v>
+      </c>
+      <c r="I69" t="n">
+        <v>445286505.89</v>
+      </c>
+      <c r="J69" t="n">
+        <v>715245480.73</v>
+      </c>
+      <c r="K69" t="n">
+        <v>175327531.05</v>
+      </c>
+      <c r="L69" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="M69" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2848539205.44</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>603458.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>勘设股份</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-9.9497</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="G70" t="n">
+        <v>973170718</v>
+      </c>
+      <c r="H70" t="n">
+        <v>150971560.51</v>
+      </c>
+      <c r="I70" t="n">
+        <v>171471972.27</v>
+      </c>
+      <c r="J70" t="n">
+        <v>322443532.78</v>
+      </c>
+      <c r="K70" t="n">
+        <v>20500411.76</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M70" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2742875645.44</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>603538.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>美诺华</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5.0986</v>
+      </c>
+      <c r="F71" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3530538715</v>
+      </c>
+      <c r="H71" t="n">
+        <v>344945929.93</v>
+      </c>
+      <c r="I71" t="n">
+        <v>303090864.86</v>
+      </c>
+      <c r="J71" t="n">
+        <v>648036794.79</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-41855065.07</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M71" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="N71" t="n">
+        <v>10516715619.6</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>603757.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>大元泵业</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-6.3266</v>
+      </c>
+      <c r="F72" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1650329558</v>
+      </c>
+      <c r="H72" t="n">
+        <v>303794337.56</v>
+      </c>
+      <c r="I72" t="n">
+        <v>171825804.88</v>
+      </c>
+      <c r="J72" t="n">
+        <v>475620142.44</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-131968532.68</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M72" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="N72" t="n">
+        <v>13838075672.62</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>603778.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>国晟科技</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4.6845</v>
+      </c>
+      <c r="F73" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1499716237</v>
+      </c>
+      <c r="H73" t="n">
+        <v>219895960.02</v>
+      </c>
+      <c r="I73" t="n">
+        <v>283766874</v>
+      </c>
+      <c r="J73" t="n">
+        <v>503662834.02</v>
+      </c>
+      <c r="K73" t="n">
+        <v>63870913.98</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M73" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="N73" t="n">
+        <v>7039285704.9</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>603823.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.0061</v>
+      </c>
+      <c r="F74" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2118297989</v>
+      </c>
+      <c r="H74" t="n">
+        <v>289083981.12</v>
+      </c>
+      <c r="I74" t="n">
+        <v>309142485.36</v>
+      </c>
+      <c r="J74" t="n">
+        <v>598226466.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>20058504.24</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M74" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="N74" t="n">
+        <v>30165840154.8</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>603823.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10.0061</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3948883092</v>
+      </c>
+      <c r="H75" t="n">
+        <v>583913286.8200001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>598867666.9400001</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1182780953.76</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14954380.12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30165840154.8</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>603861.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>白云电器</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>9.9855</v>
+      </c>
+      <c r="F76" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="G76" t="n">
+        <v>933915468</v>
+      </c>
+      <c r="H76" t="n">
+        <v>100274998.35</v>
+      </c>
+      <c r="I76" t="n">
+        <v>253190173.96</v>
+      </c>
+      <c r="J76" t="n">
+        <v>353465172.31</v>
+      </c>
+      <c r="K76" t="n">
+        <v>152915175.61</v>
+      </c>
+      <c r="L76" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="M76" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="N76" t="n">
+        <v>8034514465.6</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>603903.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>中持股份</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.6057</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1512250438</v>
+      </c>
+      <c r="H77" t="n">
+        <v>167041868.48</v>
+      </c>
+      <c r="I77" t="n">
+        <v>230284660.96</v>
+      </c>
+      <c r="J77" t="n">
+        <v>397326529.44</v>
+      </c>
+      <c r="K77" t="n">
+        <v>63242792.48</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M77" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4039154173.6</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>603937.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>丽岛新材</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4.3866</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G78" t="n">
+        <v>400407223</v>
+      </c>
+      <c r="H78" t="n">
+        <v>62391585.27</v>
+      </c>
+      <c r="I78" t="n">
+        <v>40316170.07</v>
+      </c>
+      <c r="J78" t="n">
+        <v>102707755.34</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-22075415.2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="M78" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3181425022.93</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>603978.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>深圳新星</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-4.9374</v>
+      </c>
+      <c r="F79" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1780942176</v>
+      </c>
+      <c r="H79" t="n">
+        <v>291993617.16</v>
+      </c>
+      <c r="I79" t="n">
+        <v>279327033.17</v>
+      </c>
+      <c r="J79" t="n">
+        <v>571320650.33</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-12666583.99</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="M79" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5446232914.2</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>非ST、*ST和S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>605399.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>晨光新材</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="E80" t="n">
+        <v>10.0076</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G80" t="n">
+        <v>144535988</v>
+      </c>
+      <c r="H80" t="n">
+        <v>18122364.03</v>
+      </c>
+      <c r="I80" t="n">
+        <v>47897323.28</v>
+      </c>
+      <c r="J80" t="n">
+        <v>66019687.31</v>
+      </c>
+      <c r="K80" t="n">
+        <v>29774959.25</v>
+      </c>
+      <c r="L80" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4520261529.28</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-20.0617</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2265500</v>
+      </c>
+      <c r="H81" t="n">
+        <v>2039795.94</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1503142.76</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3542938.7</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-536653.1800000001</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-23.69</v>
+      </c>
+      <c r="M81" t="n">
+        <v>156.39</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1049813335.06</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>688261.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>东微半导</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="E82" t="n">
+        <v>16.332</v>
+      </c>
+      <c r="F82" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1902863500</v>
+      </c>
+      <c r="H82" t="n">
+        <v>166477548.73</v>
+      </c>
+      <c r="I82" t="n">
+        <v>310605972.36</v>
+      </c>
+      <c r="J82" t="n">
+        <v>477083521.09</v>
+      </c>
+      <c r="K82" t="n">
+        <v>144128423.63</v>
+      </c>
+      <c r="L82" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="M82" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="N82" t="n">
+        <v>12097330038.12</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>688432.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>有研硅</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="E83" t="n">
+        <v>20</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3389040400</v>
+      </c>
+      <c r="H83" t="n">
+        <v>421404338.59</v>
+      </c>
+      <c r="I83" t="n">
+        <v>465078908.98</v>
+      </c>
+      <c r="J83" t="n">
+        <v>886483247.5700001</v>
+      </c>
+      <c r="K83" t="n">
+        <v>43674570.39</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M83" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="N83" t="n">
+        <v>57688927728.12</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>688584.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>上海合晶</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="E84" t="n">
+        <v>15.3051</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1139623000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>143202708.91</v>
+      </c>
+      <c r="I84" t="n">
+        <v>176561142.49</v>
+      </c>
+      <c r="J84" t="n">
+        <v>319763851.4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>33358433.58</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M84" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="N84" t="n">
+        <v>12259251213.3</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>688605.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>先锋精科</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="E85" t="n">
+        <v>15.2161</v>
+      </c>
+      <c r="F85" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1363704600</v>
+      </c>
+      <c r="H85" t="n">
+        <v>216515668.31</v>
+      </c>
+      <c r="I85" t="n">
+        <v>259974060.04</v>
+      </c>
+      <c r="J85" t="n">
+        <v>476489728.35</v>
+      </c>
+      <c r="K85" t="n">
+        <v>43458391.73</v>
+      </c>
+      <c r="L85" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M85" t="n">
+        <v>34.94</v>
+      </c>
+      <c r="N85" t="n">
+        <v>12249163076.5</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>科莱瑞迪</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-15.3736</v>
+      </c>
+      <c r="F86" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>116614400</v>
+      </c>
+      <c r="H86" t="n">
+        <v>11469191.94</v>
+      </c>
+      <c r="I86" t="n">
+        <v>19415816.28</v>
+      </c>
+      <c r="J86" t="n">
+        <v>30885008.22</v>
+      </c>
+      <c r="K86" t="n">
+        <v>7946624.34</v>
+      </c>
+      <c r="L86" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="M86" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="N86" t="n">
+        <v>427585400</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>920083.BJ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>金戈新材</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-13.848</v>
+      </c>
+      <c r="F87" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="G87" t="n">
+        <v>233747500</v>
+      </c>
+      <c r="H87" t="n">
+        <v>40423953.02</v>
+      </c>
+      <c r="I87" t="n">
+        <v>15500116.07</v>
+      </c>
+      <c r="J87" t="n">
+        <v>55924069.09</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-24923836.95</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-10.66</v>
+      </c>
+      <c r="M87" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="N87" t="n">
+        <v>869870673.6</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>吉和昌</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>49</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-11.8071</v>
+      </c>
+      <c r="F88" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="G88" t="n">
+        <v>612498100</v>
+      </c>
+      <c r="H88" t="n">
+        <v>69690949.59999999</v>
+      </c>
+      <c r="I88" t="n">
+        <v>56618968.26</v>
+      </c>
+      <c r="J88" t="n">
+        <v>126309917.86</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-13071981.34</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="M88" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1234800000</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-6.5319</v>
+      </c>
+      <c r="F89" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="G89" t="n">
+        <v>272613300</v>
+      </c>
+      <c r="H89" t="n">
+        <v>34330392.48</v>
+      </c>
+      <c r="I89" t="n">
+        <v>51266642.02</v>
+      </c>
+      <c r="J89" t="n">
+        <v>85597034.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>16936249.54</v>
+      </c>
+      <c r="L89" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M89" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>971769600</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>920222.BJ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>益坤电气</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-6.1287</v>
+      </c>
+      <c r="F90" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="G90" t="n">
+        <v>75444700</v>
+      </c>
+      <c r="H90" t="n">
+        <v>9684635.98</v>
+      </c>
+      <c r="I90" t="n">
+        <v>16158761.52</v>
+      </c>
+      <c r="J90" t="n">
+        <v>25843397.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>6474125.54</v>
+      </c>
+      <c r="L90" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="M90" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="N90" t="n">
+        <v>318780606.3</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>920527.BJ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>夜光明</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="E91" t="n">
+        <v>25.0551</v>
+      </c>
+      <c r="F91" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="G91" t="n">
+        <v>126673100</v>
+      </c>
+      <c r="H91" t="n">
+        <v>31856380.25</v>
+      </c>
+      <c r="I91" t="n">
+        <v>19655234.94</v>
+      </c>
+      <c r="J91" t="n">
+        <v>51511615.19</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-12201145.31</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="M91" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="N91" t="n">
+        <v>792405194.9400001</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260708</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5518</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1593</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3790</v>
+      </c>
+      <c r="E2" t="n">
+        <v>135</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25825.92</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3990.2353</v>
+        <v>3970.8797</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.26</v>
+        <v>-0.49</v>
       </c>
       <c r="F2" t="n">
-        <v>11963.71</v>
+        <v>11923.56</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15225.1136</v>
+        <v>14939.7268</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.24</v>
+        <v>-1.87</v>
       </c>
       <c r="F3" t="n">
-        <v>8279.379999999999</v>
+        <v>8439.9</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3911.9075</v>
+        <v>3845.3513</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.7</v>
       </c>
       <c r="F4" t="n">
-        <v>2887.63</v>
+        <v>3247.84</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4792.2624</v>
+        <v>4755.5338</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.03</v>
+        <v>-0.77</v>
       </c>
       <c r="F5" t="n">
-        <v>7626.18</v>
+        <v>7832.49</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2001.5859</v>
+        <v>2016.2327</v>
       </c>
       <c r="E6" t="n">
-        <v>0.27</v>
+        <v>0.73</v>
       </c>
       <c r="F6" t="n">
-        <v>1595.6</v>
+        <v>1693.5</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8301.8035</v>
+        <v>8117.8607</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.02</v>
+        <v>-2.22</v>
       </c>
       <c r="F7" t="n">
-        <v>5444.56</v>
+        <v>5276.41</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6074 @@
           <t>20260708</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>25825.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920189.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D2" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="I2" t="n">
+        <v>400.6143</v>
+      </c>
+      <c r="J2" t="n">
+        <v>338956.55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1557659.75055</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920857.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.959</v>
+      </c>
+      <c r="J3" t="n">
+        <v>62540.32</v>
+      </c>
+      <c r="K3" t="n">
+        <v>110013.24806</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300454.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="D4" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="E4" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="G4" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>262262.64</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2653158.56552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300369.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>889852</v>
+      </c>
+      <c r="K5" t="n">
+        <v>539650.85739</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301321.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="D6" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>19.9952</v>
+      </c>
+      <c r="J6" t="n">
+        <v>141613.55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>631378.47194</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301202.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="D7" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="F7" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.9939</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44569.12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>169938.66248</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>59.23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19.9921</v>
+      </c>
+      <c r="J8" t="n">
+        <v>223802.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1354131.0781</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300017.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19.9673</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2852982.28</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4050609.65086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>920090.BJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.6078</v>
+      </c>
+      <c r="J10" t="n">
+        <v>109091.82</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38286.87113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300588.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I11" t="n">
+        <v>17.1911</v>
+      </c>
+      <c r="J11" t="n">
+        <v>235373.16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>590747.09954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-20.0772</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15242.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6310.374</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>169.88</v>
+      </c>
+      <c r="D3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E3" t="n">
+        <v>136.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>137</v>
+      </c>
+      <c r="G3" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-31.71</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-18.7956</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17411.88</v>
+      </c>
+      <c r="K3" t="n">
+        <v>259043.61756</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301237.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>84</v>
+      </c>
+      <c r="E4" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>85</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-15.59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-18.3412</v>
+      </c>
+      <c r="J4" t="n">
+        <v>85965.88</v>
+      </c>
+      <c r="K4" t="n">
+        <v>623108.6365199999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688156.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="D5" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-16.2805</v>
+      </c>
+      <c r="J5" t="n">
+        <v>82981.08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>235796.757</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688017.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>446.99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>449</v>
+      </c>
+      <c r="E6" t="n">
+        <v>391</v>
+      </c>
+      <c r="F6" t="n">
+        <v>391</v>
+      </c>
+      <c r="G6" t="n">
+        <v>465.07</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-74.06999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-15.9266</v>
+      </c>
+      <c r="J6" t="n">
+        <v>196843.51</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8041401.153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>920510.BJ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-15.8859</v>
+      </c>
+      <c r="J7" t="n">
+        <v>159567.75</v>
+      </c>
+      <c r="K7" t="n">
+        <v>413451.86884</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300390.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>81.02</v>
+      </c>
+      <c r="G8" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-15.24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-15.8321</v>
+      </c>
+      <c r="J8" t="n">
+        <v>761722.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6685075.79803</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301282.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-15.625</v>
+      </c>
+      <c r="J9" t="n">
+        <v>226538.94</v>
+      </c>
+      <c r="K9" t="n">
+        <v>642948.19439</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688813.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>187</v>
+      </c>
+      <c r="D10" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>158.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>161</v>
+      </c>
+      <c r="G10" t="n">
+        <v>185.97</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-24.97</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-13.4269</v>
+      </c>
+      <c r="J10" t="n">
+        <v>55831.91</v>
+      </c>
+      <c r="K10" t="n">
+        <v>959297.333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>920725.BJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>112</v>
+      </c>
+      <c r="D11" t="n">
+        <v>123.33</v>
+      </c>
+      <c r="E11" t="n">
+        <v>101</v>
+      </c>
+      <c r="F11" t="n">
+        <v>101</v>
+      </c>
+      <c r="G11" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-13.3791</v>
+      </c>
+      <c r="J11" t="n">
+        <v>94182.57000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1071783.44652</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1799704</v>
+      </c>
+      <c r="H2" t="n">
+        <v>661273</v>
+      </c>
+      <c r="I2" t="n">
+        <v>897375</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1558648</v>
+      </c>
+      <c r="K2" t="n">
+        <v>236102</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="N2" t="n">
+        <v>47989845.84</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000566.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>海南海药</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-10.0173</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1567554024</v>
+      </c>
+      <c r="H3" t="n">
+        <v>147044459.81</v>
+      </c>
+      <c r="I3" t="n">
+        <v>147626928.55</v>
+      </c>
+      <c r="J3" t="n">
+        <v>294671388.36</v>
+      </c>
+      <c r="K3" t="n">
+        <v>582468.74</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6755992647.93</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000838.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*ST发展</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9.9415</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>91133281</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9205061.359999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13359308</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22564369.36</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4154246.64</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1981079807.4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000973.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>佛塑科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-9.9451</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1555126110</v>
+      </c>
+      <c r="H5" t="n">
+        <v>233080032.18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>141293894</v>
+      </c>
+      <c r="J5" t="n">
+        <v>374373926.18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-91786138.18000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12702266235.23</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000977.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>浪潮信息</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.0056</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3193011084</v>
+      </c>
+      <c r="H6" t="n">
+        <v>449716856.54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>950429945</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1400146801.54</v>
+      </c>
+      <c r="K6" t="n">
+        <v>500713088.46</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>114662242118.68</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000977.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>浪潮信息</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.0056</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18417078546</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2541658183.41</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3272238066.36</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5813896249.77</v>
+      </c>
+      <c r="K7" t="n">
+        <v>730579882.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="N7" t="n">
+        <v>114662242118.68</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001206.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>依依股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.5783</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="G8" t="n">
+        <v>491115481</v>
+      </c>
+      <c r="H8" t="n">
+        <v>51839478.96</v>
+      </c>
+      <c r="I8" t="n">
+        <v>62084087.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>113923566.08</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10244608.16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2204613768.54</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>001229.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>魅视科技</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.9948</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>118583465</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15455677</v>
+      </c>
+      <c r="I9" t="n">
+        <v>71340447.42</v>
+      </c>
+      <c r="J9" t="n">
+        <v>86796124.42</v>
+      </c>
+      <c r="K9" t="n">
+        <v>55884770.42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3149176453.5</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>001365.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>天海电子</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.0092</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1310972943</v>
+      </c>
+      <c r="H10" t="n">
+        <v>139837296.31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>175119652.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>314956948.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35282356.08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2749344935.26</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>001365.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>天海电子</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0092</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="G11" t="n">
+        <v>973310977</v>
+      </c>
+      <c r="H11" t="n">
+        <v>140397478.41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>102219204.74</v>
+      </c>
+      <c r="J11" t="n">
+        <v>242616683.15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-38178273.67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="M11" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2749344935.26</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.1564</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3907528697</v>
+      </c>
+      <c r="H12" t="n">
+        <v>489529400.05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>592244447.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1081773847.65</v>
+      </c>
+      <c r="K12" t="n">
+        <v>102715047.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15298035952.43</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002137.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>实益达</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.5372</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2054966150</v>
+      </c>
+      <c r="H13" t="n">
+        <v>280895072.38</v>
+      </c>
+      <c r="I13" t="n">
+        <v>156316366</v>
+      </c>
+      <c r="J13" t="n">
+        <v>437211438.38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-124578706.38</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-6.06</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4646488709.32</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002268.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>电科网安</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.6341</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1252209552</v>
+      </c>
+      <c r="H14" t="n">
+        <v>114181237.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>82326378.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>196507616.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-31854859.65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13228232658.95</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002396.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.0189</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1563518119</v>
+      </c>
+      <c r="H15" t="n">
+        <v>309277126.52</v>
+      </c>
+      <c r="I15" t="n">
+        <v>441693216.22</v>
+      </c>
+      <c r="J15" t="n">
+        <v>750970342.74</v>
+      </c>
+      <c r="K15" t="n">
+        <v>132416089.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22040779584.6</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002428.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>云南锗业</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6704682407</v>
+      </c>
+      <c r="H16" t="n">
+        <v>747893284.3099999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>812990756.52</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1560884040.83</v>
+      </c>
+      <c r="K16" t="n">
+        <v>65097472.21</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M16" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="N16" t="n">
+        <v>64650526875</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002457.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>青龙管业</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.2688</v>
+      </c>
+      <c r="F17" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1313594073</v>
+      </c>
+      <c r="H17" t="n">
+        <v>85235015.73999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>101845126.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>187080141.94</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16610110.46</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5159025002.52</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002466.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天齐锂业</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-10.0017</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3671353354</v>
+      </c>
+      <c r="H18" t="n">
+        <v>399352915.99</v>
+      </c>
+      <c r="I18" t="n">
+        <v>191788433.56</v>
+      </c>
+      <c r="J18" t="n">
+        <v>591141349.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-207564482.43</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="M18" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>78611817213.64999</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002497.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>雅化集团</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-9.979699999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2999888390</v>
+      </c>
+      <c r="H19" t="n">
+        <v>613453182.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>322558257.02</v>
+      </c>
+      <c r="J19" t="n">
+        <v>936011439.16</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-290894925.12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23512249176.85</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002667.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>*ST威领</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.3365</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>346507917</v>
+      </c>
+      <c r="H20" t="n">
+        <v>55824072</v>
+      </c>
+      <c r="I20" t="n">
+        <v>57913668.93</v>
+      </c>
+      <c r="J20" t="n">
+        <v>113737740.93</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2089596.93</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2564863240</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002674.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>兴业科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>742043936</v>
+      </c>
+      <c r="H21" t="n">
+        <v>48109788.94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>68067952.78</v>
+      </c>
+      <c r="J21" t="n">
+        <v>116177741.72</v>
+      </c>
+      <c r="K21" t="n">
+        <v>19958163.84</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8528230455.8</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002709.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>天赐材料</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-9.991899999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4638318544</v>
+      </c>
+      <c r="H22" t="n">
+        <v>222523189.89</v>
+      </c>
+      <c r="I22" t="n">
+        <v>382482492.88</v>
+      </c>
+      <c r="J22" t="n">
+        <v>605005682.77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>159959302.99</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>67286801337.21</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002726.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST龙大</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>168527903</v>
+      </c>
+      <c r="H23" t="n">
+        <v>16330018.59</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14708460.18</v>
+      </c>
+      <c r="J23" t="n">
+        <v>31038478.77</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1621558.41</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1694606297.7</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-9.0909</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1646542</v>
+      </c>
+      <c r="H24" t="n">
+        <v>916800.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>806984</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1723784.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-109816.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>104.69</v>
+      </c>
+      <c r="N24" t="n">
+        <v>37372211.2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002812.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>恩捷股份</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-9.997</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2774312449</v>
+      </c>
+      <c r="H25" t="n">
+        <v>549616414.98</v>
+      </c>
+      <c r="I25" t="n">
+        <v>541414483.86</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1091030898.84</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-8201931.12</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="N25" t="n">
+        <v>50140948294.6</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002828.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>贝肯能源</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.6335</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1180560358</v>
+      </c>
+      <c r="H26" t="n">
+        <v>235819557.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>206025409.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>441844967.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-29794148.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="M26" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2496265992</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002841.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>视源股份</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10.0046</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1348194675</v>
+      </c>
+      <c r="H27" t="n">
+        <v>184893313.27</v>
+      </c>
+      <c r="I27" t="n">
+        <v>201345770.46</v>
+      </c>
+      <c r="J27" t="n">
+        <v>386239083.73</v>
+      </c>
+      <c r="K27" t="n">
+        <v>16452457.19</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M27" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>24706560685.94</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.0303</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1141399</v>
+      </c>
+      <c r="H28" t="n">
+        <v>509690.93</v>
+      </c>
+      <c r="I28" t="n">
+        <v>797469.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1307160.53</v>
+      </c>
+      <c r="K28" t="n">
+        <v>287778.67</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M28" t="n">
+        <v>114.52</v>
+      </c>
+      <c r="N28" t="n">
+        <v>34429233.34</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002910.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>庄园牧场</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1110866809</v>
+      </c>
+      <c r="H29" t="n">
+        <v>159342973.74</v>
+      </c>
+      <c r="I29" t="n">
+        <v>153959284.91</v>
+      </c>
+      <c r="J29" t="n">
+        <v>313302258.65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-5383688.83</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M29" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2201567296.5</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002951.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>金时科技</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.973000000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>407389276</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48262260</v>
+      </c>
+      <c r="I30" t="n">
+        <v>129998886</v>
+      </c>
+      <c r="J30" t="n">
+        <v>178261146</v>
+      </c>
+      <c r="K30" t="n">
+        <v>81736626</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="M30" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6546350616</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002951.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>金时科技</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9.973000000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G31" t="n">
+        <v>494941446</v>
+      </c>
+      <c r="H31" t="n">
+        <v>53461216</v>
+      </c>
+      <c r="I31" t="n">
+        <v>156365932</v>
+      </c>
+      <c r="J31" t="n">
+        <v>209827148</v>
+      </c>
+      <c r="K31" t="n">
+        <v>102904716</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="M31" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="N31" t="n">
+        <v>6546350616</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>123273.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>三江转债</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>271.814</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19.9998</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>35474989</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14631747.62</v>
+      </c>
+      <c r="I32" t="n">
+        <v>35474988.77</v>
+      </c>
+      <c r="J32" t="n">
+        <v>50106736.39</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20843241.15</v>
+      </c>
+      <c r="L32" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>300017.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>网宿科技</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19.9673</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4050609651</v>
+      </c>
+      <c r="H33" t="n">
+        <v>239128406.73</v>
+      </c>
+      <c r="I33" t="n">
+        <v>825745249.1799999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1064873655.91</v>
+      </c>
+      <c r="K33" t="n">
+        <v>586616842.45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="N33" t="n">
+        <v>34325497631.14</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>300029.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>天龙退</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.6923</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2538625</v>
+      </c>
+      <c r="H34" t="n">
+        <v>802137.86</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1007877</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1810014.86</v>
+      </c>
+      <c r="K34" t="n">
+        <v>205739.14</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>28050435</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>300164.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>通源石油</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.3976</v>
+      </c>
+      <c r="F35" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1429828155</v>
+      </c>
+      <c r="H35" t="n">
+        <v>308783388.95</v>
+      </c>
+      <c r="I35" t="n">
+        <v>219148821.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>527932210.55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-89634567.34999999</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="M35" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4741503625.14</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>300369.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>绿盟科技</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="G36" t="n">
+        <v>539650857</v>
+      </c>
+      <c r="H36" t="n">
+        <v>67263826.42</v>
+      </c>
+      <c r="I36" t="n">
+        <v>91622539.72</v>
+      </c>
+      <c r="J36" t="n">
+        <v>158886366.14</v>
+      </c>
+      <c r="K36" t="n">
+        <v>24358713.3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M36" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5233914519.84</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>300390.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>天华新能</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>81.02</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-15.8321</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6685075798</v>
+      </c>
+      <c r="H37" t="n">
+        <v>542310569.76</v>
+      </c>
+      <c r="I37" t="n">
+        <v>384720016.19</v>
+      </c>
+      <c r="J37" t="n">
+        <v>927030585.95</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-157590553.57</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="N37" t="n">
+        <v>54467119412.62</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>300454.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>深信服</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>106.56</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2653158566</v>
+      </c>
+      <c r="H38" t="n">
+        <v>220888278.64</v>
+      </c>
+      <c r="I38" t="n">
+        <v>608625564.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>829513842.74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>387737285.46</v>
+      </c>
+      <c r="L38" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="M38" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="N38" t="n">
+        <v>30689593073.28</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>300821.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>东岳硅材</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="E39" t="n">
+        <v>13.4764</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="G39" t="n">
+        <v>12994629858</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1147236094.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1610862736.34</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2758098830.54</v>
+      </c>
+      <c r="K39" t="n">
+        <v>463626642.14</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M39" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="N39" t="n">
+        <v>31722467430</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>301237.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>和顺科技</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-18.3412</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G40" t="n">
+        <v>623108637</v>
+      </c>
+      <c r="H40" t="n">
+        <v>76919838.88</v>
+      </c>
+      <c r="I40" t="n">
+        <v>98857669.15000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>175777508.03</v>
+      </c>
+      <c r="K40" t="n">
+        <v>21937830.27</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M40" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4043132500</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E41" t="n">
+        <v>19.9921</v>
+      </c>
+      <c r="F41" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1569030842</v>
+      </c>
+      <c r="H41" t="n">
+        <v>311151571.18</v>
+      </c>
+      <c r="I41" t="n">
+        <v>350772614.69</v>
+      </c>
+      <c r="J41" t="n">
+        <v>661924185.87</v>
+      </c>
+      <c r="K41" t="n">
+        <v>39621043.51</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M41" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4604926229.76</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>301251.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>威尔高</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19.9921</v>
+      </c>
+      <c r="F42" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1354131078</v>
+      </c>
+      <c r="H42" t="n">
+        <v>326087787.68</v>
+      </c>
+      <c r="I42" t="n">
+        <v>294184055.09</v>
+      </c>
+      <c r="J42" t="n">
+        <v>620271842.77</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-31903732.59</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="M42" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4604926229.76</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>301282.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金禄电子</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-15.625</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="G43" t="n">
+        <v>642948194</v>
+      </c>
+      <c r="H43" t="n">
+        <v>73694147.31</v>
+      </c>
+      <c r="I43" t="n">
+        <v>47540376.39</v>
+      </c>
+      <c r="J43" t="n">
+        <v>121234523.7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-26153770.92</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="M43" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4719926598.75</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>301321.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>翰博高新</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="E44" t="n">
+        <v>19.9952</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G44" t="n">
+        <v>631378472</v>
+      </c>
+      <c r="H44" t="n">
+        <v>136388114.61</v>
+      </c>
+      <c r="I44" t="n">
+        <v>216228390.25</v>
+      </c>
+      <c r="J44" t="n">
+        <v>352616504.86</v>
+      </c>
+      <c r="K44" t="n">
+        <v>79840275.64</v>
+      </c>
+      <c r="L44" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="M44" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7352746185.84</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>301321.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>翰博高新</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19.9952</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="G45" t="n">
+        <v>997252423</v>
+      </c>
+      <c r="H45" t="n">
+        <v>227892565.67</v>
+      </c>
+      <c r="I45" t="n">
+        <v>256659415.41</v>
+      </c>
+      <c r="J45" t="n">
+        <v>484551981.08</v>
+      </c>
+      <c r="K45" t="n">
+        <v>28766849.74</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M45" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7352746185.84</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>301516.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>中远通</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.1368</v>
+      </c>
+      <c r="F46" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>616887148</v>
+      </c>
+      <c r="H46" t="n">
+        <v>95472839</v>
+      </c>
+      <c r="I46" t="n">
+        <v>89039684.73</v>
+      </c>
+      <c r="J46" t="n">
+        <v>184512523.73</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-6433154.27</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="M46" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1341754393.68</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="E47" t="n">
+        <v>13.2485</v>
+      </c>
+      <c r="F47" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="G47" t="n">
+        <v>596328247</v>
+      </c>
+      <c r="H47" t="n">
+        <v>59144947.46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>51885208.25</v>
+      </c>
+      <c r="J47" t="n">
+        <v>111030155.71</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-7259739.21</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M47" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1397531453.82</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600094.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>大名城</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.895799999999999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G48" t="n">
+        <v>197127146</v>
+      </c>
+      <c r="H48" t="n">
+        <v>30303323.2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>43237505.46</v>
+      </c>
+      <c r="J48" t="n">
+        <v>73540828.66</v>
+      </c>
+      <c r="K48" t="n">
+        <v>12934182.26</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="M48" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="N48" t="n">
+        <v>9017402410.379999</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600172.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-4.1939</v>
+      </c>
+      <c r="F49" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5907720790</v>
+      </c>
+      <c r="H49" t="n">
+        <v>632433579.77</v>
+      </c>
+      <c r="I49" t="n">
+        <v>554680926.6900001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1187114506.46</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-77752653.08</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="M49" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="N49" t="n">
+        <v>22449338642.5</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600288.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>大恒科技</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="E50" t="n">
+        <v>10.0322</v>
+      </c>
+      <c r="F50" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1953207110</v>
+      </c>
+      <c r="H50" t="n">
+        <v>272001943.87</v>
+      </c>
+      <c r="I50" t="n">
+        <v>275890304.89</v>
+      </c>
+      <c r="J50" t="n">
+        <v>547892248.76</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3888361.02</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7473648000</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600350.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>山东高速</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0326</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G51" t="n">
+        <v>152092181</v>
+      </c>
+      <c r="H51" t="n">
+        <v>23189408.6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>28231269.52</v>
+      </c>
+      <c r="J51" t="n">
+        <v>51420678.12</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5041860.92</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M51" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="N51" t="n">
+        <v>65218360429.25</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>600458.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>时代新材</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-10.0193</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G52" t="n">
+        <v>833324486</v>
+      </c>
+      <c r="H52" t="n">
+        <v>176947347</v>
+      </c>
+      <c r="I52" t="n">
+        <v>172888208.48</v>
+      </c>
+      <c r="J52" t="n">
+        <v>349835555.48</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-4059138.52</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M52" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="N52" t="n">
+        <v>12168079451.55</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>600562.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>国睿科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-10.0085</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G53" t="n">
+        <v>504728724</v>
+      </c>
+      <c r="H53" t="n">
+        <v>94355413</v>
+      </c>
+      <c r="I53" t="n">
+        <v>66255972.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>160611385.8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-28099440.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="M53" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="N53" t="n">
+        <v>26240456159.2</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>600745.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>*ST闻泰</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.404</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1511949419</v>
+      </c>
+      <c r="H54" t="n">
+        <v>117413769.81</v>
+      </c>
+      <c r="I54" t="n">
+        <v>128406148.17</v>
+      </c>
+      <c r="J54" t="n">
+        <v>245819917.98</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10992378.36</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M54" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="N54" t="n">
+        <v>23604797183.97</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>600756.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>浪潮软件</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.975099999999999</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G55" t="n">
+        <v>79030575</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="J55" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="K55" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="L55" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="M55" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4287826502.19</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>600756.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>浪潮软件</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.975099999999999</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G56" t="n">
+        <v>79030575</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="J56" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="K56" t="n">
+        <v>53340921</v>
+      </c>
+      <c r="L56" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>67.48999999999999</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4287826502.19</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>600759.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ST洲际</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10.0457</v>
+      </c>
+      <c r="F57" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G57" t="n">
+        <v>620005764</v>
+      </c>
+      <c r="H57" t="n">
+        <v>46111485</v>
+      </c>
+      <c r="I57" t="n">
+        <v>48106605</v>
+      </c>
+      <c r="J57" t="n">
+        <v>94218090</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1995120</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M57" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>9986282729.799999</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>601010.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ST文峰</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10.0671</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G58" t="n">
+        <v>85815322</v>
+      </c>
+      <c r="H58" t="n">
+        <v>7790187</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8997193</v>
+      </c>
+      <c r="J58" t="n">
+        <v>16787380</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1207006</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3030720000</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603065.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>宿迁联盛</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E59" t="n">
+        <v>8.1975</v>
+      </c>
+      <c r="F59" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2933273159</v>
+      </c>
+      <c r="H59" t="n">
+        <v>369290169.1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>229257329</v>
+      </c>
+      <c r="J59" t="n">
+        <v>598547498.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-140032840.1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="N59" t="n">
+        <v>9179579502.52</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603118.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>共进股份</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="E60" t="n">
+        <v>6.8838</v>
+      </c>
+      <c r="F60" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3721671929</v>
+      </c>
+      <c r="H60" t="n">
+        <v>192546721.97</v>
+      </c>
+      <c r="I60" t="n">
+        <v>181315050.06</v>
+      </c>
+      <c r="J60" t="n">
+        <v>373861772.03</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-11231671.91</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="N60" t="n">
+        <v>11368271302.64</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603137.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>恒尚节能</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.9856</v>
+      </c>
+      <c r="F61" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1070203845</v>
+      </c>
+      <c r="H61" t="n">
+        <v>149763586.4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>134577904</v>
+      </c>
+      <c r="J61" t="n">
+        <v>284341490.4</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-15185682.4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="M61" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4191002681.94</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>603137.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>恒尚节能</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9.9856</v>
+      </c>
+      <c r="F62" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1085387811</v>
+      </c>
+      <c r="H62" t="n">
+        <v>149851072.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>134577904</v>
+      </c>
+      <c r="J62" t="n">
+        <v>284428976.4</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-15273168.4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="M62" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4191002681.94</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>603166.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>福达股份</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-6.7349</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1050796852</v>
+      </c>
+      <c r="H63" t="n">
+        <v>333110860.34</v>
+      </c>
+      <c r="I63" t="n">
+        <v>136845721.57</v>
+      </c>
+      <c r="J63" t="n">
+        <v>469956581.91</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-196265138.77</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-18.68</v>
+      </c>
+      <c r="M63" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7009429221.94</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>603178.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>圣龙股份</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9.113099999999999</v>
+      </c>
+      <c r="F64" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="G64" t="n">
+        <v>819064109</v>
+      </c>
+      <c r="H64" t="n">
+        <v>96774375.69</v>
+      </c>
+      <c r="I64" t="n">
+        <v>60927033.82</v>
+      </c>
+      <c r="J64" t="n">
+        <v>157701409.51</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-35847341.87</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="M64" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4217587957.04</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>603183.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>建研院</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.0543</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="G65" t="n">
+        <v>221499679</v>
+      </c>
+      <c r="H65" t="n">
+        <v>59870063.34</v>
+      </c>
+      <c r="I65" t="n">
+        <v>45674307</v>
+      </c>
+      <c r="J65" t="n">
+        <v>105544370.34</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-14195756.34</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-6.41</v>
+      </c>
+      <c r="M65" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2013470666.55</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>603313.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>梦百合</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9.9688</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>620174256</v>
+      </c>
+      <c r="H66" t="n">
+        <v>53659219.7</v>
+      </c>
+      <c r="I66" t="n">
+        <v>63888412.58</v>
+      </c>
+      <c r="J66" t="n">
+        <v>117547632.28</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10229192.88</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M66" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4028343408.1</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>603407.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>长裕集团</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>72.98</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-7.9929</v>
+      </c>
+      <c r="F67" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="G67" t="n">
+        <v>508372436</v>
+      </c>
+      <c r="H67" t="n">
+        <v>168445187.74</v>
+      </c>
+      <c r="I67" t="n">
+        <v>134190423.79</v>
+      </c>
+      <c r="J67" t="n">
+        <v>302635611.53</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-34254763.95</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-6.74</v>
+      </c>
+      <c r="M67" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2620857176.16</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>603538.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>美诺华</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2177828509</v>
+      </c>
+      <c r="H68" t="n">
+        <v>270142534.39</v>
+      </c>
+      <c r="I68" t="n">
+        <v>239821992.15</v>
+      </c>
+      <c r="J68" t="n">
+        <v>509964526.54</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-30320542.24</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M68" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="N68" t="n">
+        <v>9465044057.639999</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>603610.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>麒盛科技</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-10.0188</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G69" t="n">
+        <v>174245974</v>
+      </c>
+      <c r="H69" t="n">
+        <v>33731924</v>
+      </c>
+      <c r="I69" t="n">
+        <v>41568453.08</v>
+      </c>
+      <c r="J69" t="n">
+        <v>75300377.08</v>
+      </c>
+      <c r="K69" t="n">
+        <v>7836529.08</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M69" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5072489593.77</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>603610.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>麒盛科技</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-10.0188</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G70" t="n">
+        <v>589282841</v>
+      </c>
+      <c r="H70" t="n">
+        <v>115992989.95</v>
+      </c>
+      <c r="I70" t="n">
+        <v>102908912.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>218901902.45</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-13084077.45</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="M70" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5072489593.77</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>603618.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>杭电股份</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-8.0373</v>
+      </c>
+      <c r="F71" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="G71" t="n">
+        <v>9972594594</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1937441999.14</v>
+      </c>
+      <c r="I71" t="n">
+        <v>921558368.96</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2859000368.1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-1015883630.18</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-10.19</v>
+      </c>
+      <c r="M71" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="N71" t="n">
+        <v>25235209984</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>603667.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>五洲新春</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-7.3462</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="G72" t="n">
+        <v>7212436241</v>
+      </c>
+      <c r="H72" t="n">
+        <v>927251429.47</v>
+      </c>
+      <c r="I72" t="n">
+        <v>941296587.54</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1868548017.01</v>
+      </c>
+      <c r="K72" t="n">
+        <v>14045158.07</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M72" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="N72" t="n">
+        <v>21569343153</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>603678.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>火炬电子</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-9.994199999999999</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="G73" t="n">
+        <v>7459950346</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1003630704.24</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1139648354.81</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2143279059.05</v>
+      </c>
+      <c r="K73" t="n">
+        <v>136017650.57</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M73" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="N73" t="n">
+        <v>29637312443.92</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>603789.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ST星农</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.0156</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G74" t="n">
+        <v>120810978</v>
+      </c>
+      <c r="H74" t="n">
+        <v>12631976.64</v>
+      </c>
+      <c r="I74" t="n">
+        <v>16887553.25</v>
+      </c>
+      <c r="J74" t="n">
+        <v>29519529.89</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4255576.61</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M74" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1827800000</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>603815.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>交建股份</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3.4268</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>589457571</v>
+      </c>
+      <c r="H75" t="n">
+        <v>91653964.17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>101429599.92</v>
+      </c>
+      <c r="J75" t="n">
+        <v>193083564.09</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9775635.75</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4109656920.4</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>603826.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>坤彩科技</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-10.0162</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G76" t="n">
+        <v>460928681</v>
+      </c>
+      <c r="H76" t="n">
+        <v>119132763.8</v>
+      </c>
+      <c r="I76" t="n">
+        <v>73176939</v>
+      </c>
+      <c r="J76" t="n">
+        <v>192309702.8</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-45955824.8</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="M76" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="N76" t="n">
+        <v>14597856000</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>603843.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>*ST正平</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-9.985900000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>541011010</v>
+      </c>
+      <c r="H77" t="n">
+        <v>48232263.86</v>
+      </c>
+      <c r="I77" t="n">
+        <v>55720577.8</v>
+      </c>
+      <c r="J77" t="n">
+        <v>103952841.66</v>
+      </c>
+      <c r="K77" t="n">
+        <v>7488313.94</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M77" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4477588716.8</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>603861.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>白云电器</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G78" t="n">
+        <v>677357618</v>
+      </c>
+      <c r="H78" t="n">
+        <v>146624260.1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>99474897</v>
+      </c>
+      <c r="J78" t="n">
+        <v>246099157.1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-47149363.1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="M78" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="N78" t="n">
+        <v>7231063019.04</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>605580.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>恒盛能源</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-10.0161</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G79" t="n">
+        <v>182147508</v>
+      </c>
+      <c r="H79" t="n">
+        <v>19021536.01</v>
+      </c>
+      <c r="I79" t="n">
+        <v>16754326.8</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35775862.81</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-2267209.21</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M79" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="N79" t="n">
+        <v>6263600000</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>605598.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>上海港湾</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-4.9242</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G80" t="n">
+        <v>813733516</v>
+      </c>
+      <c r="H80" t="n">
+        <v>189136449.28</v>
+      </c>
+      <c r="I80" t="n">
+        <v>146376764.04</v>
+      </c>
+      <c r="J80" t="n">
+        <v>335513213.32</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-42759685.24</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="M80" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="N80" t="n">
+        <v>7929638477.67</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>688017.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>绿的谐波</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>391</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-15.9266</v>
+      </c>
+      <c r="F81" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8041401200</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1274369949.36</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1078646035.66</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2353015985.02</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-195723913.7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="M81" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="N81" t="n">
+        <v>71682078875</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-20.0772</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G82" t="n">
+        <v>6310400</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3627563.22</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4109214.96</v>
+      </c>
+      <c r="J82" t="n">
+        <v>7736778.18</v>
+      </c>
+      <c r="K82" t="n">
+        <v>481651.74</v>
+      </c>
+      <c r="L82" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="M82" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="N82" t="n">
+        <v>839040001.38</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>688121.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>*ST卓然</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-20.0772</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8575900</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5384930.02</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5223261.02</v>
+      </c>
+      <c r="J83" t="n">
+        <v>10608191.04</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-161669</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="M83" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="N83" t="n">
+        <v>839040001.38</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格跌幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>688156.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>路德科技</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-16.2805</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G84" t="n">
+        <v>235796800</v>
+      </c>
+      <c r="H84" t="n">
+        <v>59220056.4</v>
+      </c>
+      <c r="I84" t="n">
+        <v>49760865.06</v>
+      </c>
+      <c r="J84" t="n">
+        <v>108980921.46</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-9459191.34</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="M84" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2729353654.7</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>688508.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>芯朋微</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>98.09</v>
+      </c>
+      <c r="E85" t="n">
+        <v>16.8016</v>
+      </c>
+      <c r="F85" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1915422300</v>
+      </c>
+      <c r="H85" t="n">
+        <v>480914743.58</v>
+      </c>
+      <c r="I85" t="n">
+        <v>429749986.35</v>
+      </c>
+      <c r="J85" t="n">
+        <v>910664729.9299999</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-51164757.23</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="M85" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="N85" t="n">
+        <v>12989111739.14</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>688691.SH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>灿芯股份</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>113.98</v>
+      </c>
+      <c r="E86" t="n">
+        <v>15.8687</v>
+      </c>
+      <c r="F86" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2967830400</v>
+      </c>
+      <c r="H86" t="n">
+        <v>440210863.47</v>
+      </c>
+      <c r="I86" t="n">
+        <v>455650674.09</v>
+      </c>
+      <c r="J86" t="n">
+        <v>895861537.5599999</v>
+      </c>
+      <c r="K86" t="n">
+        <v>15439810.62</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M86" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="N86" t="n">
+        <v>8316551839.8</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>920088.BJ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>科力股份</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11.1324</v>
+      </c>
+      <c r="F87" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="G87" t="n">
+        <v>230332100</v>
+      </c>
+      <c r="H87" t="n">
+        <v>36209865.24</v>
+      </c>
+      <c r="I87" t="n">
+        <v>19559466.6</v>
+      </c>
+      <c r="J87" t="n">
+        <v>55769331.84</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-16650398.64</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-7.23</v>
+      </c>
+      <c r="M87" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1134607453.2</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>920090.BJ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>*ST同辉</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E88" t="n">
+        <v>19.6078</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="G88" t="n">
+        <v>38286900</v>
+      </c>
+      <c r="H88" t="n">
+        <v>6061081.3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>6032607.88</v>
+      </c>
+      <c r="J88" t="n">
+        <v>12093689.18</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-28473.42</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M88" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="N88" t="n">
+        <v>545094022.38</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>吉和昌</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-12.5918</v>
+      </c>
+      <c r="F89" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="G89" t="n">
+        <v>477452100</v>
+      </c>
+      <c r="H89" t="n">
+        <v>43773363.12</v>
+      </c>
+      <c r="I89" t="n">
+        <v>44253614.47</v>
+      </c>
+      <c r="J89" t="n">
+        <v>88026977.59</v>
+      </c>
+      <c r="K89" t="n">
+        <v>480251.35</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1079316000</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>137</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-18.7956</v>
+      </c>
+      <c r="F90" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="G90" t="n">
+        <v>259043600</v>
+      </c>
+      <c r="H90" t="n">
+        <v>48576351.54</v>
+      </c>
+      <c r="I90" t="n">
+        <v>38199653.17</v>
+      </c>
+      <c r="J90" t="n">
+        <v>86776004.70999999</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-10376698.37</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="M90" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>789120000</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>920725.BJ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>惠丰钻石</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>101</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-13.3791</v>
+      </c>
+      <c r="F91" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1071783400</v>
+      </c>
+      <c r="H91" t="n">
+        <v>97118795.98</v>
+      </c>
+      <c r="I91" t="n">
+        <v>84363722.34999999</v>
+      </c>
+      <c r="J91" t="n">
+        <v>181482518.33</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-12755073.63</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M91" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4462249185</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>920857.BJ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>泓禧科技</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>19</v>
+      </c>
+      <c r="E92" t="n">
+        <v>29.959</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="G92" t="n">
+        <v>110013200</v>
+      </c>
+      <c r="H92" t="n">
+        <v>21452180.43</v>
+      </c>
+      <c r="I92" t="n">
+        <v>49899359.08</v>
+      </c>
+      <c r="J92" t="n">
+        <v>71351539.51000001</v>
+      </c>
+      <c r="K92" t="n">
+        <v>28447178.65</v>
+      </c>
+      <c r="L92" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="M92" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1406135888</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>920857.BJ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>泓禧科技</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>19</v>
+      </c>
+      <c r="E93" t="n">
+        <v>29.959</v>
+      </c>
+      <c r="F93" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="G93" t="n">
+        <v>163066900</v>
+      </c>
+      <c r="H93" t="n">
+        <v>26583328.22</v>
+      </c>
+      <c r="I93" t="n">
+        <v>53420721.82</v>
+      </c>
+      <c r="J93" t="n">
+        <v>80004050.04000001</v>
+      </c>
+      <c r="K93" t="n">
+        <v>26837393.6</v>
+      </c>
+      <c r="L93" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="M93" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1406135888</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4841,50 +4841,48 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>600759.SH</t>
+          <t>600756.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ST洲际</t>
+          <t>浪潮软件</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.41</v>
+        <v>13.23</v>
       </c>
       <c r="E57" t="n">
-        <v>10.0457</v>
+        <v>9.975099999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>6.34</v>
+        <v>1.85</v>
       </c>
       <c r="G57" t="n">
-        <v>620005764</v>
-      </c>
-      <c r="H57" t="n">
-        <v>46111485</v>
-      </c>
+        <v>79030575</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>48106605</v>
+        <v>53340921</v>
       </c>
       <c r="J57" t="n">
-        <v>94218090</v>
+        <v>53340921</v>
       </c>
       <c r="K57" t="n">
-        <v>1995120</v>
+        <v>53340921</v>
       </c>
       <c r="L57" t="n">
-        <v>0.32</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>15.2</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>9986282729.799999</v>
+        <v>4287826502.19</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
         </is>
       </c>
     </row>
@@ -4896,46 +4894,46 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>601010.SH</t>
+          <t>600759.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ST文峰</t>
+          <t>ST洲际</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.64</v>
+        <v>2.41</v>
       </c>
       <c r="E58" t="n">
-        <v>10.0671</v>
+        <v>10.0457</v>
       </c>
       <c r="F58" t="n">
-        <v>2.9</v>
+        <v>6.34</v>
       </c>
       <c r="G58" t="n">
-        <v>85815322</v>
+        <v>620005764</v>
       </c>
       <c r="H58" t="n">
-        <v>7790187</v>
+        <v>46111485</v>
       </c>
       <c r="I58" t="n">
-        <v>8997193</v>
+        <v>48106605</v>
       </c>
       <c r="J58" t="n">
-        <v>16787380</v>
+        <v>94218090</v>
       </c>
       <c r="K58" t="n">
-        <v>1207006</v>
+        <v>1995120</v>
       </c>
       <c r="L58" t="n">
-        <v>1.41</v>
+        <v>0.32</v>
       </c>
       <c r="M58" t="n">
-        <v>19.56</v>
+        <v>15.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3030720000</v>
+        <v>9986282729.799999</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4951,50 +4949,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603065.SH</t>
+          <t>601010.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>宿迁联盛</t>
+          <t>ST文峰</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.91</v>
+        <v>1.64</v>
       </c>
       <c r="E59" t="n">
-        <v>8.1975</v>
+        <v>10.0671</v>
       </c>
       <c r="F59" t="n">
-        <v>17.88</v>
+        <v>2.9</v>
       </c>
       <c r="G59" t="n">
-        <v>2933273159</v>
+        <v>85815322</v>
       </c>
       <c r="H59" t="n">
-        <v>369290169.1</v>
+        <v>7790187</v>
       </c>
       <c r="I59" t="n">
-        <v>229257329</v>
+        <v>8997193</v>
       </c>
       <c r="J59" t="n">
-        <v>598547498.1</v>
+        <v>16787380</v>
       </c>
       <c r="K59" t="n">
-        <v>-140032840.1</v>
+        <v>1207006</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.77</v>
+        <v>1.41</v>
       </c>
       <c r="M59" t="n">
-        <v>20.41</v>
+        <v>19.56</v>
       </c>
       <c r="N59" t="n">
-        <v>9179579502.52</v>
+        <v>3030720000</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5006,46 +5004,46 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603118.SH</t>
+          <t>603065.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>宿迁联盛</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.44</v>
+        <v>21.91</v>
       </c>
       <c r="E60" t="n">
-        <v>6.8838</v>
+        <v>8.1975</v>
       </c>
       <c r="F60" t="n">
-        <v>13.66</v>
+        <v>17.88</v>
       </c>
       <c r="G60" t="n">
-        <v>3721671929</v>
+        <v>2933273159</v>
       </c>
       <c r="H60" t="n">
-        <v>192546721.97</v>
+        <v>369290169.1</v>
       </c>
       <c r="I60" t="n">
-        <v>181315050.06</v>
+        <v>229257329</v>
       </c>
       <c r="J60" t="n">
-        <v>373861772.03</v>
+        <v>598547498.1</v>
       </c>
       <c r="K60" t="n">
-        <v>-11231671.91</v>
+        <v>-140032840.1</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.3</v>
+        <v>-4.77</v>
       </c>
       <c r="M60" t="n">
-        <v>10.05</v>
+        <v>20.41</v>
       </c>
       <c r="N60" t="n">
-        <v>11368271302.64</v>
+        <v>9179579502.52</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5061,50 +5059,50 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>603137.SH</t>
+          <t>603118.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>恒尚节能</t>
+          <t>共进股份</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.91</v>
+        <v>14.44</v>
       </c>
       <c r="E61" t="n">
-        <v>9.9856</v>
+        <v>6.8838</v>
       </c>
       <c r="F61" t="n">
-        <v>25.54</v>
+        <v>13.66</v>
       </c>
       <c r="G61" t="n">
-        <v>1070203845</v>
+        <v>3721671929</v>
       </c>
       <c r="H61" t="n">
-        <v>149763586.4</v>
+        <v>192546721.97</v>
       </c>
       <c r="I61" t="n">
-        <v>134577904</v>
+        <v>181315050.06</v>
       </c>
       <c r="J61" t="n">
-        <v>284341490.4</v>
+        <v>373861772.03</v>
       </c>
       <c r="K61" t="n">
-        <v>-15185682.4</v>
+        <v>-11231671.91</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.42</v>
+        <v>-0.3</v>
       </c>
       <c r="M61" t="n">
-        <v>26.57</v>
+        <v>10.05</v>
       </c>
       <c r="N61" t="n">
-        <v>4191002681.94</v>
+        <v>11368271302.64</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5134,32 +5132,32 @@
         <v>25.54</v>
       </c>
       <c r="G62" t="n">
-        <v>1085387811</v>
+        <v>1070203845</v>
       </c>
       <c r="H62" t="n">
-        <v>149851072.4</v>
+        <v>149763586.4</v>
       </c>
       <c r="I62" t="n">
         <v>134577904</v>
       </c>
       <c r="J62" t="n">
-        <v>284428976.4</v>
+        <v>284341490.4</v>
       </c>
       <c r="K62" t="n">
-        <v>-15273168.4</v>
+        <v>-15185682.4</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="M62" t="n">
-        <v>26.21</v>
+        <v>26.57</v>
       </c>
       <c r="N62" t="n">
         <v>4191002681.94</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5171,50 +5169,50 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>603166.SH</t>
+          <t>603137.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>福达股份</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.94</v>
+        <v>22.91</v>
       </c>
       <c r="E63" t="n">
-        <v>-6.7349</v>
+        <v>9.9856</v>
       </c>
       <c r="F63" t="n">
-        <v>3.5</v>
+        <v>25.54</v>
       </c>
       <c r="G63" t="n">
-        <v>1050796852</v>
+        <v>1085387811</v>
       </c>
       <c r="H63" t="n">
-        <v>333110860.34</v>
+        <v>149851072.4</v>
       </c>
       <c r="I63" t="n">
-        <v>136845721.57</v>
+        <v>134577904</v>
       </c>
       <c r="J63" t="n">
-        <v>469956581.91</v>
+        <v>284428976.4</v>
       </c>
       <c r="K63" t="n">
-        <v>-196265138.77</v>
+        <v>-15273168.4</v>
       </c>
       <c r="L63" t="n">
-        <v>-18.68</v>
+        <v>-1.41</v>
       </c>
       <c r="M63" t="n">
-        <v>44.72</v>
+        <v>26.21</v>
       </c>
       <c r="N63" t="n">
-        <v>7009429221.94</v>
+        <v>4191002681.94</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5226,50 +5224,50 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>603178.SH</t>
+          <t>603166.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>圣龙股份</t>
+          <t>福达股份</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17.84</v>
+        <v>10.94</v>
       </c>
       <c r="E64" t="n">
-        <v>9.113099999999999</v>
+        <v>-6.7349</v>
       </c>
       <c r="F64" t="n">
-        <v>16.82</v>
+        <v>3.5</v>
       </c>
       <c r="G64" t="n">
-        <v>819064109</v>
+        <v>1050796852</v>
       </c>
       <c r="H64" t="n">
-        <v>96774375.69</v>
+        <v>333110860.34</v>
       </c>
       <c r="I64" t="n">
-        <v>60927033.82</v>
+        <v>136845721.57</v>
       </c>
       <c r="J64" t="n">
-        <v>157701409.51</v>
+        <v>469956581.91</v>
       </c>
       <c r="K64" t="n">
-        <v>-35847341.87</v>
+        <v>-196265138.77</v>
       </c>
       <c r="L64" t="n">
-        <v>-4.38</v>
+        <v>-18.68</v>
       </c>
       <c r="M64" t="n">
-        <v>19.25</v>
+        <v>44.72</v>
       </c>
       <c r="N64" t="n">
-        <v>4217587957.04</v>
+        <v>7009429221.94</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5281,50 +5279,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>603183.SH</t>
+          <t>603178.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>建研院</t>
+          <t>圣龙股份</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4.05</v>
+        <v>17.84</v>
       </c>
       <c r="E65" t="n">
-        <v>10.0543</v>
+        <v>9.113099999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>11.26</v>
+        <v>16.82</v>
       </c>
       <c r="G65" t="n">
-        <v>221499679</v>
+        <v>819064109</v>
       </c>
       <c r="H65" t="n">
-        <v>59870063.34</v>
+        <v>96774375.69</v>
       </c>
       <c r="I65" t="n">
-        <v>45674307</v>
+        <v>60927033.82</v>
       </c>
       <c r="J65" t="n">
-        <v>105544370.34</v>
+        <v>157701409.51</v>
       </c>
       <c r="K65" t="n">
-        <v>-14195756.34</v>
+        <v>-35847341.87</v>
       </c>
       <c r="L65" t="n">
-        <v>-6.41</v>
+        <v>-4.38</v>
       </c>
       <c r="M65" t="n">
-        <v>47.65</v>
+        <v>19.25</v>
       </c>
       <c r="N65" t="n">
-        <v>2013470666.55</v>
+        <v>4217587957.04</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5336,50 +5334,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>603313.SH</t>
+          <t>603183.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>梦百合</t>
+          <t>建研院</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.06</v>
+        <v>4.05</v>
       </c>
       <c r="E66" t="n">
-        <v>9.9688</v>
+        <v>10.0543</v>
       </c>
       <c r="F66" t="n">
-        <v>7.8</v>
+        <v>11.26</v>
       </c>
       <c r="G66" t="n">
-        <v>620174256</v>
+        <v>221499679</v>
       </c>
       <c r="H66" t="n">
-        <v>53659219.7</v>
+        <v>59870063.34</v>
       </c>
       <c r="I66" t="n">
-        <v>63888412.58</v>
+        <v>45674307</v>
       </c>
       <c r="J66" t="n">
-        <v>117547632.28</v>
+        <v>105544370.34</v>
       </c>
       <c r="K66" t="n">
-        <v>10229192.88</v>
+        <v>-14195756.34</v>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>-6.41</v>
       </c>
       <c r="M66" t="n">
-        <v>18.95</v>
+        <v>47.65</v>
       </c>
       <c r="N66" t="n">
-        <v>4028343408.1</v>
+        <v>2013470666.55</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5391,50 +5389,50 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>603407.SH</t>
+          <t>603313.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>长裕集团</t>
+          <t>梦百合</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>72.98</v>
+        <v>7.06</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.9929</v>
+        <v>9.9688</v>
       </c>
       <c r="F67" t="n">
-        <v>18.47</v>
+        <v>7.8</v>
       </c>
       <c r="G67" t="n">
-        <v>508372436</v>
+        <v>620174256</v>
       </c>
       <c r="H67" t="n">
-        <v>168445187.74</v>
+        <v>53659219.7</v>
       </c>
       <c r="I67" t="n">
-        <v>134190423.79</v>
+        <v>63888412.58</v>
       </c>
       <c r="J67" t="n">
-        <v>302635611.53</v>
+        <v>117547632.28</v>
       </c>
       <c r="K67" t="n">
-        <v>-34254763.95</v>
+        <v>10229192.88</v>
       </c>
       <c r="L67" t="n">
-        <v>-6.74</v>
+        <v>1.65</v>
       </c>
       <c r="M67" t="n">
-        <v>59.53</v>
+        <v>18.95</v>
       </c>
       <c r="N67" t="n">
-        <v>2620857176.16</v>
+        <v>4028343408.1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5446,50 +5444,50 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>603538.SH</t>
+          <t>603407.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>长裕集团</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>39.33</v>
+        <v>72.98</v>
       </c>
       <c r="E68" t="n">
-        <v>-10</v>
+        <v>-7.9929</v>
       </c>
       <c r="F68" t="n">
-        <v>22.35</v>
+        <v>18.47</v>
       </c>
       <c r="G68" t="n">
-        <v>2177828509</v>
+        <v>508372436</v>
       </c>
       <c r="H68" t="n">
-        <v>270142534.39</v>
+        <v>168445187.74</v>
       </c>
       <c r="I68" t="n">
-        <v>239821992.15</v>
+        <v>134190423.79</v>
       </c>
       <c r="J68" t="n">
-        <v>509964526.54</v>
+        <v>302635611.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-30320542.24</v>
+        <v>-34254763.95</v>
       </c>
       <c r="L68" t="n">
-        <v>-1.39</v>
+        <v>-6.74</v>
       </c>
       <c r="M68" t="n">
-        <v>23.42</v>
+        <v>59.53</v>
       </c>
       <c r="N68" t="n">
-        <v>9465044057.639999</v>
+        <v>2620857176.16</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5501,50 +5499,50 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>603610.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>麒盛科技</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.37</v>
+        <v>39.33</v>
       </c>
       <c r="E69" t="n">
-        <v>-10.0188</v>
+        <v>-10</v>
       </c>
       <c r="F69" t="n">
-        <v>3.32</v>
+        <v>22.35</v>
       </c>
       <c r="G69" t="n">
-        <v>174245974</v>
+        <v>2177828509</v>
       </c>
       <c r="H69" t="n">
-        <v>33731924</v>
+        <v>270142534.39</v>
       </c>
       <c r="I69" t="n">
-        <v>41568453.08</v>
+        <v>239821992.15</v>
       </c>
       <c r="J69" t="n">
-        <v>75300377.08</v>
+        <v>509964526.54</v>
       </c>
       <c r="K69" t="n">
-        <v>7836529.08</v>
+        <v>-30320542.24</v>
       </c>
       <c r="L69" t="n">
-        <v>4.5</v>
+        <v>-1.39</v>
       </c>
       <c r="M69" t="n">
-        <v>43.21</v>
+        <v>23.42</v>
       </c>
       <c r="N69" t="n">
-        <v>5072489593.77</v>
+        <v>9465044057.639999</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5574,32 +5572,32 @@
         <v>3.32</v>
       </c>
       <c r="G70" t="n">
-        <v>589282841</v>
+        <v>174245974</v>
       </c>
       <c r="H70" t="n">
-        <v>115992989.95</v>
+        <v>33731924</v>
       </c>
       <c r="I70" t="n">
-        <v>102908912.5</v>
+        <v>41568453.08</v>
       </c>
       <c r="J70" t="n">
-        <v>218901902.45</v>
+        <v>75300377.08</v>
       </c>
       <c r="K70" t="n">
-        <v>-13084077.45</v>
+        <v>7836529.08</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.22</v>
+        <v>4.5</v>
       </c>
       <c r="M70" t="n">
-        <v>37.15</v>
+        <v>43.21</v>
       </c>
       <c r="N70" t="n">
         <v>5072489593.77</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5611,46 +5609,46 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>603618.SH</t>
+          <t>603610.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>杭电股份</t>
+          <t>麒盛科技</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>36.5</v>
+        <v>14.37</v>
       </c>
       <c r="E71" t="n">
-        <v>-8.0373</v>
+        <v>-10.0188</v>
       </c>
       <c r="F71" t="n">
-        <v>12.29</v>
+        <v>3.32</v>
       </c>
       <c r="G71" t="n">
-        <v>9972594594</v>
+        <v>589282841</v>
       </c>
       <c r="H71" t="n">
-        <v>1937441999.14</v>
+        <v>115992989.95</v>
       </c>
       <c r="I71" t="n">
-        <v>921558368.96</v>
+        <v>102908912.5</v>
       </c>
       <c r="J71" t="n">
-        <v>2859000368.1</v>
+        <v>218901902.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-1015883630.18</v>
+        <v>-13084077.45</v>
       </c>
       <c r="L71" t="n">
-        <v>-10.19</v>
+        <v>-2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>28.67</v>
+        <v>37.15</v>
       </c>
       <c r="N71" t="n">
-        <v>25235209984</v>
+        <v>5072489593.77</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5666,46 +5664,46 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>603667.SH</t>
+          <t>603618.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>杭电股份</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>58.9</v>
+        <v>36.5</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.3462</v>
+        <v>-8.0373</v>
       </c>
       <c r="F72" t="n">
-        <v>7.41</v>
+        <v>12.29</v>
       </c>
       <c r="G72" t="n">
-        <v>7212436241</v>
+        <v>9972594594</v>
       </c>
       <c r="H72" t="n">
-        <v>927251429.47</v>
+        <v>1937441999.14</v>
       </c>
       <c r="I72" t="n">
-        <v>941296587.54</v>
+        <v>921558368.96</v>
       </c>
       <c r="J72" t="n">
-        <v>1868548017.01</v>
+        <v>2859000368.1</v>
       </c>
       <c r="K72" t="n">
-        <v>14045158.07</v>
+        <v>-1015883630.18</v>
       </c>
       <c r="L72" t="n">
-        <v>0.19</v>
+        <v>-10.19</v>
       </c>
       <c r="M72" t="n">
-        <v>25.91</v>
+        <v>28.67</v>
       </c>
       <c r="N72" t="n">
-        <v>21569343153</v>
+        <v>25235209984</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5721,46 +5719,46 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>603678.SH</t>
+          <t>603667.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>火炬电子</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>62.32</v>
+        <v>58.9</v>
       </c>
       <c r="E73" t="n">
-        <v>-9.994199999999999</v>
+        <v>-7.3462</v>
       </c>
       <c r="F73" t="n">
-        <v>7.91</v>
+        <v>7.41</v>
       </c>
       <c r="G73" t="n">
-        <v>7459950346</v>
+        <v>7212436241</v>
       </c>
       <c r="H73" t="n">
-        <v>1003630704.24</v>
+        <v>927251429.47</v>
       </c>
       <c r="I73" t="n">
-        <v>1139648354.81</v>
+        <v>941296587.54</v>
       </c>
       <c r="J73" t="n">
-        <v>2143279059.05</v>
+        <v>1868548017.01</v>
       </c>
       <c r="K73" t="n">
-        <v>136017650.57</v>
+        <v>14045158.07</v>
       </c>
       <c r="L73" t="n">
-        <v>1.82</v>
+        <v>0.19</v>
       </c>
       <c r="M73" t="n">
-        <v>28.73</v>
+        <v>25.91</v>
       </c>
       <c r="N73" t="n">
-        <v>29637312443.92</v>
+        <v>21569343153</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5776,50 +5774,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>603789.SH</t>
+          <t>603678.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ST星农</t>
+          <t>火炬电子</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7.03</v>
+        <v>62.32</v>
       </c>
       <c r="E74" t="n">
-        <v>10.0156</v>
+        <v>-9.994199999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>6.99</v>
+        <v>7.91</v>
       </c>
       <c r="G74" t="n">
-        <v>120810978</v>
+        <v>7459950346</v>
       </c>
       <c r="H74" t="n">
-        <v>12631976.64</v>
+        <v>1003630704.24</v>
       </c>
       <c r="I74" t="n">
-        <v>16887553.25</v>
+        <v>1139648354.81</v>
       </c>
       <c r="J74" t="n">
-        <v>29519529.89</v>
+        <v>2143279059.05</v>
       </c>
       <c r="K74" t="n">
-        <v>4255576.61</v>
+        <v>136017650.57</v>
       </c>
       <c r="L74" t="n">
-        <v>3.52</v>
+        <v>1.82</v>
       </c>
       <c r="M74" t="n">
-        <v>24.43</v>
+        <v>28.73</v>
       </c>
       <c r="N74" t="n">
-        <v>1827800000</v>
+        <v>29637312443.92</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5831,50 +5829,50 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>603815.SH</t>
+          <t>603789.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>交建股份</t>
+          <t>ST星农</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6.64</v>
+        <v>7.03</v>
       </c>
       <c r="E75" t="n">
-        <v>3.4268</v>
+        <v>10.0156</v>
       </c>
       <c r="F75" t="n">
-        <v>5.03</v>
+        <v>6.99</v>
       </c>
       <c r="G75" t="n">
-        <v>589457571</v>
+        <v>120810978</v>
       </c>
       <c r="H75" t="n">
-        <v>91653964.17</v>
+        <v>12631976.64</v>
       </c>
       <c r="I75" t="n">
-        <v>101429599.92</v>
+        <v>16887553.25</v>
       </c>
       <c r="J75" t="n">
-        <v>193083564.09</v>
+        <v>29519529.89</v>
       </c>
       <c r="K75" t="n">
-        <v>9775635.75</v>
+        <v>4255576.61</v>
       </c>
       <c r="L75" t="n">
-        <v>1.66</v>
+        <v>3.52</v>
       </c>
       <c r="M75" t="n">
-        <v>32.76</v>
+        <v>24.43</v>
       </c>
       <c r="N75" t="n">
-        <v>4109656920.4</v>
+        <v>1827800000</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5886,50 +5884,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>603826.SH</t>
+          <t>603815.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>坤彩科技</t>
+          <t>交建股份</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.28</v>
+        <v>6.64</v>
       </c>
       <c r="E76" t="n">
-        <v>-10.0162</v>
+        <v>3.4268</v>
       </c>
       <c r="F76" t="n">
-        <v>3.04</v>
+        <v>5.03</v>
       </c>
       <c r="G76" t="n">
-        <v>460928681</v>
+        <v>589457571</v>
       </c>
       <c r="H76" t="n">
-        <v>119132763.8</v>
+        <v>91653964.17</v>
       </c>
       <c r="I76" t="n">
-        <v>73176939</v>
+        <v>101429599.92</v>
       </c>
       <c r="J76" t="n">
-        <v>192309702.8</v>
+        <v>193083564.09</v>
       </c>
       <c r="K76" t="n">
-        <v>-45955824.8</v>
+        <v>9775635.75</v>
       </c>
       <c r="L76" t="n">
-        <v>-9.970000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="M76" t="n">
-        <v>41.72</v>
+        <v>32.76</v>
       </c>
       <c r="N76" t="n">
-        <v>14597856000</v>
+        <v>4109656920.4</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -5941,50 +5939,50 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>603843.SH</t>
+          <t>603826.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>*ST正平</t>
+          <t>坤彩科技</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6.4</v>
+        <v>22.28</v>
       </c>
       <c r="E77" t="n">
-        <v>-9.985900000000001</v>
+        <v>-10.0162</v>
       </c>
       <c r="F77" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="G77" t="n">
-        <v>541011010</v>
+        <v>460928681</v>
       </c>
       <c r="H77" t="n">
-        <v>48232263.86</v>
+        <v>119132763.8</v>
       </c>
       <c r="I77" t="n">
-        <v>55720577.8</v>
+        <v>73176939</v>
       </c>
       <c r="J77" t="n">
-        <v>103952841.66</v>
+        <v>192309702.8</v>
       </c>
       <c r="K77" t="n">
-        <v>7488313.94</v>
+        <v>-45955824.8</v>
       </c>
       <c r="L77" t="n">
-        <v>1.38</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M77" t="n">
-        <v>19.21</v>
+        <v>41.72</v>
       </c>
       <c r="N77" t="n">
-        <v>4477588716.8</v>
+        <v>14597856000</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -5996,50 +5994,50 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>603861.SH</t>
+          <t>603843.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>白云电器</t>
+          <t>*ST正平</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.68</v>
+        <v>6.4</v>
       </c>
       <c r="E78" t="n">
-        <v>-10</v>
+        <v>-9.985900000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>8.869999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="G78" t="n">
-        <v>677357618</v>
+        <v>541011010</v>
       </c>
       <c r="H78" t="n">
-        <v>146624260.1</v>
+        <v>48232263.86</v>
       </c>
       <c r="I78" t="n">
-        <v>99474897</v>
+        <v>55720577.8</v>
       </c>
       <c r="J78" t="n">
-        <v>246099157.1</v>
+        <v>103952841.66</v>
       </c>
       <c r="K78" t="n">
-        <v>-47149363.1</v>
+        <v>7488313.94</v>
       </c>
       <c r="L78" t="n">
-        <v>-6.96</v>
+        <v>1.38</v>
       </c>
       <c r="M78" t="n">
-        <v>36.33</v>
+        <v>19.21</v>
       </c>
       <c r="N78" t="n">
-        <v>7231063019.04</v>
+        <v>4477588716.8</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -6051,50 +6049,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>605580.SH</t>
+          <t>603861.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>恒盛能源</t>
+          <t>白云电器</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.37</v>
+        <v>13.68</v>
       </c>
       <c r="E79" t="n">
-        <v>-10.0161</v>
+        <v>-10</v>
       </c>
       <c r="F79" t="n">
-        <v>2.84</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>182147508</v>
+        <v>677357618</v>
       </c>
       <c r="H79" t="n">
-        <v>19021536.01</v>
+        <v>146624260.1</v>
       </c>
       <c r="I79" t="n">
-        <v>16754326.8</v>
+        <v>99474897</v>
       </c>
       <c r="J79" t="n">
-        <v>35775862.81</v>
+        <v>246099157.1</v>
       </c>
       <c r="K79" t="n">
-        <v>-2267209.21</v>
+        <v>-47149363.1</v>
       </c>
       <c r="L79" t="n">
-        <v>-1.24</v>
+        <v>-6.96</v>
       </c>
       <c r="M79" t="n">
-        <v>19.64</v>
+        <v>36.33</v>
       </c>
       <c r="N79" t="n">
-        <v>6263600000</v>
+        <v>7231063019.04</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -6106,50 +6104,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>605598.SH</t>
+          <t>605580.SH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>上海港湾</t>
+          <t>恒盛能源</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>32.63</v>
+        <v>22.37</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.9242</v>
+        <v>-10.0161</v>
       </c>
       <c r="F80" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="G80" t="n">
-        <v>813733516</v>
+        <v>182147508</v>
       </c>
       <c r="H80" t="n">
-        <v>189136449.28</v>
+        <v>19021536.01</v>
       </c>
       <c r="I80" t="n">
-        <v>146376764.04</v>
+        <v>16754326.8</v>
       </c>
       <c r="J80" t="n">
-        <v>335513213.32</v>
+        <v>35775862.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-42759685.24</v>
+        <v>-2267209.21</v>
       </c>
       <c r="L80" t="n">
-        <v>-5.25</v>
+        <v>-1.24</v>
       </c>
       <c r="M80" t="n">
-        <v>41.23</v>
+        <v>19.64</v>
       </c>
       <c r="N80" t="n">
-        <v>7929638477.67</v>
+        <v>6263600000</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -6161,50 +6159,50 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>688017.SH</t>
+          <t>605598.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>绿的谐波</t>
+          <t>上海港湾</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>391</v>
+        <v>32.63</v>
       </c>
       <c r="E81" t="n">
-        <v>-15.9266</v>
+        <v>-4.9242</v>
       </c>
       <c r="F81" t="n">
-        <v>10.74</v>
+        <v>2.77</v>
       </c>
       <c r="G81" t="n">
-        <v>8041401200</v>
+        <v>813733516</v>
       </c>
       <c r="H81" t="n">
-        <v>1274369949.36</v>
+        <v>189136449.28</v>
       </c>
       <c r="I81" t="n">
-        <v>1078646035.66</v>
+        <v>146376764.04</v>
       </c>
       <c r="J81" t="n">
-        <v>2353015985.02</v>
+        <v>335513213.32</v>
       </c>
       <c r="K81" t="n">
-        <v>-195723913.7</v>
+        <v>-42759685.24</v>
       </c>
       <c r="L81" t="n">
-        <v>-2.43</v>
+        <v>-5.25</v>
       </c>
       <c r="M81" t="n">
-        <v>29.26</v>
+        <v>41.23</v>
       </c>
       <c r="N81" t="n">
-        <v>71682078875</v>
+        <v>7929638477.67</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
@@ -6216,46 +6214,46 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>688121.SH</t>
+          <t>688017.SH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>*ST卓然</t>
+          <t>绿的谐波</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.14</v>
+        <v>391</v>
       </c>
       <c r="E82" t="n">
-        <v>-20.0772</v>
+        <v>-15.9266</v>
       </c>
       <c r="F82" t="n">
-        <v>0.75</v>
+        <v>10.74</v>
       </c>
       <c r="G82" t="n">
-        <v>6310400</v>
+        <v>8041401200</v>
       </c>
       <c r="H82" t="n">
-        <v>3627563.22</v>
+        <v>1274369949.36</v>
       </c>
       <c r="I82" t="n">
-        <v>4109214.96</v>
+        <v>1078646035.66</v>
       </c>
       <c r="J82" t="n">
-        <v>7736778.18</v>
+        <v>2353015985.02</v>
       </c>
       <c r="K82" t="n">
-        <v>481651.74</v>
+        <v>-195723913.7</v>
       </c>
       <c r="L82" t="n">
-        <v>7.63</v>
+        <v>-2.43</v>
       </c>
       <c r="M82" t="n">
-        <v>122.6</v>
+        <v>29.26</v>
       </c>
       <c r="N82" t="n">
-        <v>839040001.38</v>
+        <v>71682078875</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -6289,32 +6287,32 @@
         <v>0.75</v>
       </c>
       <c r="G83" t="n">
-        <v>8575900</v>
+        <v>6310400</v>
       </c>
       <c r="H83" t="n">
-        <v>5384930.02</v>
+        <v>3627563.22</v>
       </c>
       <c r="I83" t="n">
-        <v>5223261.02</v>
+        <v>4109214.96</v>
       </c>
       <c r="J83" t="n">
-        <v>10608191.04</v>
+        <v>7736778.18</v>
       </c>
       <c r="K83" t="n">
-        <v>-161669</v>
+        <v>481651.74</v>
       </c>
       <c r="L83" t="n">
-        <v>-1.89</v>
+        <v>7.63</v>
       </c>
       <c r="M83" t="n">
-        <v>123.7</v>
+        <v>122.6</v>
       </c>
       <c r="N83" t="n">
         <v>839040001.38</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格跌幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -6326,50 +6324,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>688156.SH</t>
+          <t>688121.SH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>路德科技</t>
+          <t>*ST卓然</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>27.1</v>
+        <v>4.14</v>
       </c>
       <c r="E84" t="n">
-        <v>-16.2805</v>
+        <v>-20.0772</v>
       </c>
       <c r="F84" t="n">
-        <v>8.24</v>
+        <v>0.75</v>
       </c>
       <c r="G84" t="n">
-        <v>235796800</v>
+        <v>8575900</v>
       </c>
       <c r="H84" t="n">
-        <v>59220056.4</v>
+        <v>5384930.02</v>
       </c>
       <c r="I84" t="n">
-        <v>49760865.06</v>
+        <v>5223261.02</v>
       </c>
       <c r="J84" t="n">
-        <v>108980921.46</v>
+        <v>10608191.04</v>
       </c>
       <c r="K84" t="n">
-        <v>-9459191.34</v>
+        <v>-161669</v>
       </c>
       <c r="L84" t="n">
-        <v>-4.01</v>
+        <v>-1.89</v>
       </c>
       <c r="M84" t="n">
-        <v>46.22</v>
+        <v>123.7</v>
       </c>
       <c r="N84" t="n">
-        <v>2729353654.7</v>
+        <v>839040001.38</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格跌幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
@@ -6381,50 +6379,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>688508.SH</t>
+          <t>688156.SH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>芯朋微</t>
+          <t>路德科技</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>98.09</v>
+        <v>27.1</v>
       </c>
       <c r="E85" t="n">
-        <v>16.8016</v>
+        <v>-16.2805</v>
       </c>
       <c r="F85" t="n">
-        <v>15.4</v>
+        <v>8.24</v>
       </c>
       <c r="G85" t="n">
-        <v>1915422300</v>
+        <v>235796800</v>
       </c>
       <c r="H85" t="n">
-        <v>480914743.58</v>
+        <v>59220056.4</v>
       </c>
       <c r="I85" t="n">
-        <v>429749986.35</v>
+        <v>49760865.06</v>
       </c>
       <c r="J85" t="n">
-        <v>910664729.9299999</v>
+        <v>108980921.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-51164757.23</v>
+        <v>-9459191.34</v>
       </c>
       <c r="L85" t="n">
-        <v>-2.67</v>
+        <v>-4.01</v>
       </c>
       <c r="M85" t="n">
-        <v>47.54</v>
+        <v>46.22</v>
       </c>
       <c r="N85" t="n">
-        <v>12989111739.14</v>
+        <v>2729353654.7</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -6436,46 +6434,46 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>688691.SH</t>
+          <t>688508.SH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>灿芯股份</t>
+          <t>芯朋微</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>113.98</v>
+        <v>98.09</v>
       </c>
       <c r="E86" t="n">
-        <v>15.8687</v>
+        <v>16.8016</v>
       </c>
       <c r="F86" t="n">
-        <v>35.81</v>
+        <v>15.4</v>
       </c>
       <c r="G86" t="n">
-        <v>2967830400</v>
+        <v>1915422300</v>
       </c>
       <c r="H86" t="n">
-        <v>440210863.47</v>
+        <v>480914743.58</v>
       </c>
       <c r="I86" t="n">
-        <v>455650674.09</v>
+        <v>429749986.35</v>
       </c>
       <c r="J86" t="n">
-        <v>895861537.5599999</v>
+        <v>910664729.9299999</v>
       </c>
       <c r="K86" t="n">
-        <v>15439810.62</v>
+        <v>-51164757.23</v>
       </c>
       <c r="L86" t="n">
-        <v>0.52</v>
+        <v>-2.67</v>
       </c>
       <c r="M86" t="n">
-        <v>30.19</v>
+        <v>47.54</v>
       </c>
       <c r="N86" t="n">
-        <v>8316551839.8</v>
+        <v>12989111739.14</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -6491,50 +6489,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>920088.BJ</t>
+          <t>688691.SH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>科力股份</t>
+          <t>灿芯股份</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>34.84</v>
+        <v>113.98</v>
       </c>
       <c r="E87" t="n">
-        <v>11.1324</v>
+        <v>15.8687</v>
       </c>
       <c r="F87" t="n">
-        <v>20.43</v>
+        <v>35.81</v>
       </c>
       <c r="G87" t="n">
-        <v>230332100</v>
+        <v>2967830400</v>
       </c>
       <c r="H87" t="n">
-        <v>36209865.24</v>
+        <v>440210863.47</v>
       </c>
       <c r="I87" t="n">
-        <v>19559466.6</v>
+        <v>455650674.09</v>
       </c>
       <c r="J87" t="n">
-        <v>55769331.84</v>
+        <v>895861537.5599999</v>
       </c>
       <c r="K87" t="n">
-        <v>-16650398.64</v>
+        <v>15439810.62</v>
       </c>
       <c r="L87" t="n">
-        <v>-7.23</v>
+        <v>0.52</v>
       </c>
       <c r="M87" t="n">
-        <v>24.21</v>
+        <v>30.19</v>
       </c>
       <c r="N87" t="n">
-        <v>1134607453.2</v>
+        <v>8316551839.8</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
@@ -6546,50 +6544,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>920090.BJ</t>
+          <t>920088.BJ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>*ST同辉</t>
+          <t>科力股份</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3.66</v>
+        <v>34.84</v>
       </c>
       <c r="E88" t="n">
-        <v>19.6078</v>
+        <v>11.1324</v>
       </c>
       <c r="F88" t="n">
-        <v>7.32</v>
+        <v>20.43</v>
       </c>
       <c r="G88" t="n">
-        <v>38286900</v>
+        <v>230332100</v>
       </c>
       <c r="H88" t="n">
-        <v>6061081.3</v>
+        <v>36209865.24</v>
       </c>
       <c r="I88" t="n">
-        <v>6032607.88</v>
+        <v>19559466.6</v>
       </c>
       <c r="J88" t="n">
-        <v>12093689.18</v>
+        <v>55769331.84</v>
       </c>
       <c r="K88" t="n">
-        <v>-28473.42</v>
+        <v>-16650398.64</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-7.23</v>
       </c>
       <c r="M88" t="n">
-        <v>31.59</v>
+        <v>24.21</v>
       </c>
       <c r="N88" t="n">
-        <v>545094022.38</v>
+        <v>1134607453.2</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
@@ -6601,50 +6599,50 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>920090.BJ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>吉和昌</t>
+          <t>*ST同辉</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>42.83</v>
+        <v>3.66</v>
       </c>
       <c r="E89" t="n">
-        <v>-12.5918</v>
+        <v>19.6078</v>
       </c>
       <c r="F89" t="n">
-        <v>42.68</v>
+        <v>7.32</v>
       </c>
       <c r="G89" t="n">
-        <v>477452100</v>
+        <v>38286900</v>
       </c>
       <c r="H89" t="n">
-        <v>43773363.12</v>
+        <v>6061081.3</v>
       </c>
       <c r="I89" t="n">
-        <v>44253614.47</v>
+        <v>6032607.88</v>
       </c>
       <c r="J89" t="n">
-        <v>88026977.59</v>
+        <v>12093689.18</v>
       </c>
       <c r="K89" t="n">
-        <v>480251.35</v>
+        <v>-28473.42</v>
       </c>
       <c r="L89" t="n">
-        <v>0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>18.44</v>
+        <v>31.59</v>
       </c>
       <c r="N89" t="n">
-        <v>1079316000</v>
+        <v>545094022.38</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>当日价格振幅达到30%的前5只股票</t>
         </is>
       </c>
     </row>
@@ -6656,46 +6654,46 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>920211.BJ</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>新睿电子</t>
+          <t>吉和昌</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>137</v>
+        <v>42.83</v>
       </c>
       <c r="E90" t="n">
-        <v>-18.7956</v>
+        <v>-12.5918</v>
       </c>
       <c r="F90" t="n">
-        <v>30.23</v>
+        <v>42.68</v>
       </c>
       <c r="G90" t="n">
-        <v>259043600</v>
+        <v>477452100</v>
       </c>
       <c r="H90" t="n">
-        <v>48576351.54</v>
+        <v>43773363.12</v>
       </c>
       <c r="I90" t="n">
-        <v>38199653.17</v>
+        <v>44253614.47</v>
       </c>
       <c r="J90" t="n">
-        <v>86776004.70999999</v>
+        <v>88026977.59</v>
       </c>
       <c r="K90" t="n">
-        <v>-10376698.37</v>
+        <v>480251.35</v>
       </c>
       <c r="L90" t="n">
-        <v>-4.01</v>
+        <v>0.1</v>
       </c>
       <c r="M90" t="n">
-        <v>33.5</v>
+        <v>18.44</v>
       </c>
       <c r="N90" t="n">
-        <v>789120000</v>
+        <v>1079316000</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -6711,46 +6709,46 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>920725.BJ</t>
+          <t>920211.BJ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>惠丰钻石</t>
+          <t>新睿电子</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="E91" t="n">
-        <v>-13.3791</v>
+        <v>-18.7956</v>
       </c>
       <c r="F91" t="n">
-        <v>21.32</v>
+        <v>30.23</v>
       </c>
       <c r="G91" t="n">
-        <v>1071783400</v>
+        <v>259043600</v>
       </c>
       <c r="H91" t="n">
-        <v>97118795.98</v>
+        <v>48576351.54</v>
       </c>
       <c r="I91" t="n">
-        <v>84363722.34999999</v>
+        <v>38199653.17</v>
       </c>
       <c r="J91" t="n">
-        <v>181482518.33</v>
+        <v>86776004.70999999</v>
       </c>
       <c r="K91" t="n">
-        <v>-12755073.63</v>
+        <v>-10376698.37</v>
       </c>
       <c r="L91" t="n">
-        <v>-1.19</v>
+        <v>-4.01</v>
       </c>
       <c r="M91" t="n">
-        <v>16.93</v>
+        <v>33.5</v>
       </c>
       <c r="N91" t="n">
-        <v>4462249185</v>
+        <v>789120000</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -6766,50 +6764,50 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>920857.BJ</t>
+          <t>920725.BJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>泓禧科技</t>
+          <t>惠丰钻石</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="E92" t="n">
-        <v>29.959</v>
+        <v>-13.3791</v>
       </c>
       <c r="F92" t="n">
-        <v>8.449999999999999</v>
+        <v>21.32</v>
       </c>
       <c r="G92" t="n">
-        <v>110013200</v>
+        <v>1071783400</v>
       </c>
       <c r="H92" t="n">
-        <v>21452180.43</v>
+        <v>97118795.98</v>
       </c>
       <c r="I92" t="n">
-        <v>49899359.08</v>
+        <v>84363722.34999999</v>
       </c>
       <c r="J92" t="n">
-        <v>71351539.51000001</v>
+        <v>181482518.33</v>
       </c>
       <c r="K92" t="n">
-        <v>28447178.65</v>
+        <v>-12755073.63</v>
       </c>
       <c r="L92" t="n">
-        <v>25.86</v>
+        <v>-1.19</v>
       </c>
       <c r="M92" t="n">
-        <v>64.86</v>
+        <v>16.93</v>
       </c>
       <c r="N92" t="n">
-        <v>1406135888</v>
+        <v>4462249185</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
@@ -6839,30 +6837,85 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>163066900</v>
+        <v>110013200</v>
       </c>
       <c r="H93" t="n">
-        <v>26583328.22</v>
+        <v>21452180.43</v>
       </c>
       <c r="I93" t="n">
-        <v>53420721.82</v>
+        <v>49899359.08</v>
       </c>
       <c r="J93" t="n">
-        <v>80004050.04000001</v>
+        <v>71351539.51000001</v>
       </c>
       <c r="K93" t="n">
-        <v>26837393.6</v>
+        <v>28447178.65</v>
       </c>
       <c r="L93" t="n">
-        <v>16.46</v>
+        <v>25.86</v>
       </c>
       <c r="M93" t="n">
-        <v>49.06</v>
+        <v>64.86</v>
       </c>
       <c r="N93" t="n">
         <v>1406135888</v>
       </c>
       <c r="O93" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>920857.BJ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>泓禧科技</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>19</v>
+      </c>
+      <c r="E94" t="n">
+        <v>29.959</v>
+      </c>
+      <c r="F94" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="G94" t="n">
+        <v>163066900</v>
+      </c>
+      <c r="H94" t="n">
+        <v>26583328.22</v>
+      </c>
+      <c r="I94" t="n">
+        <v>53420721.82</v>
+      </c>
+      <c r="J94" t="n">
+        <v>80004050.04000001</v>
+      </c>
+      <c r="K94" t="n">
+        <v>26837393.6</v>
+      </c>
+      <c r="L94" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="M94" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1406135888</v>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260710</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5521</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3772</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1678</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34106.93</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4036.5879</v>
+        <v>3996.1616</v>
       </c>
       <c r="E2" t="n">
-        <v>1.65</v>
+        <v>-1</v>
       </c>
       <c r="F2" t="n">
-        <v>13641.77</v>
+        <v>15631.09</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15398.7281</v>
+        <v>15046.6695</v>
       </c>
       <c r="E3" t="n">
-        <v>3.07</v>
+        <v>-2.29</v>
       </c>
       <c r="F3" t="n">
-        <v>9856.200000000001</v>
+        <v>11441.21</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4018.1744</v>
+        <v>3842.7314</v>
       </c>
       <c r="E4" t="n">
-        <v>4.49</v>
+        <v>-4.37</v>
       </c>
       <c r="F4" t="n">
-        <v>3682.65</v>
+        <v>4241.91</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4876.3125</v>
+        <v>4780.7867</v>
       </c>
       <c r="E5" t="n">
-        <v>2.54</v>
+        <v>-1.96</v>
       </c>
       <c r="F5" t="n">
-        <v>9471.190000000001</v>
+        <v>10839.13</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2185.8251</v>
+        <v>2064.9756</v>
       </c>
       <c r="E6" t="n">
-        <v>8.41</v>
+        <v>-5.53</v>
       </c>
       <c r="F6" t="n">
-        <v>2245.12</v>
+        <v>2350.96</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8300.076999999999</v>
+        <v>8198.3078</v>
       </c>
       <c r="E7" t="n">
-        <v>2.24</v>
+        <v>-1.23</v>
       </c>
       <c r="F7" t="n">
-        <v>5804.22</v>
+        <v>6918.14</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,6384 @@
           <t>20260710</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>34106.93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>264.42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>858.8496</v>
+      </c>
+      <c r="J2" t="n">
+        <v>250811.68</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5943898.88669</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920943.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.9918</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32696.77</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48775.20716</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>920267.BJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29.9427</v>
+      </c>
+      <c r="J4" t="n">
+        <v>78578.13</v>
+      </c>
+      <c r="K4" t="n">
+        <v>137787.20433</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>920081.BJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.5301</v>
+      </c>
+      <c r="J5" t="n">
+        <v>151702.37</v>
+      </c>
+      <c r="K5" t="n">
+        <v>782923.21071</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300065.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0083</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1235071.06</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3279324.85092</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688523.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="D7" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.0078</v>
+      </c>
+      <c r="J7" t="n">
+        <v>162299.79</v>
+      </c>
+      <c r="K7" t="n">
+        <v>929854.518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688710.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="D8" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="E8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="G8" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.0031</v>
+      </c>
+      <c r="J8" t="n">
+        <v>68577.49000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>503467.138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300255.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>702690.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1766605.47086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301117.SZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.9882</v>
+      </c>
+      <c r="J10" t="n">
+        <v>314573.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>570694.10893</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300069.SZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19.987</v>
+      </c>
+      <c r="J11" t="n">
+        <v>155192.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>541282.2732000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920136.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-24.9118</v>
+      </c>
+      <c r="J2" t="n">
+        <v>121898.86</v>
+      </c>
+      <c r="K2" t="n">
+        <v>325073.71754</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>688146.SH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>341</v>
+      </c>
+      <c r="D3" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>293.99</v>
+      </c>
+      <c r="G3" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-69.61</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-19.1447</v>
+      </c>
+      <c r="J3" t="n">
+        <v>198706.66</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6477248.049</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-18.8406</v>
+      </c>
+      <c r="J4" t="n">
+        <v>155180.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8948.03961</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>688549.SH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="E5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F5" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17.1001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1309432.28</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4211699.558</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>688249.SH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-17.0066</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1089386.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6385492.739</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688392.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>241.81</v>
+      </c>
+      <c r="D7" t="n">
+        <v>248</v>
+      </c>
+      <c r="E7" t="n">
+        <v>203.89</v>
+      </c>
+      <c r="F7" t="n">
+        <v>203.89</v>
+      </c>
+      <c r="G7" t="n">
+        <v>241.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-37.91</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-15.6782</v>
+      </c>
+      <c r="J7" t="n">
+        <v>76041.82000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1732468.453</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>688596.SH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>81</v>
+      </c>
+      <c r="E8" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="G8" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-15.3118</v>
+      </c>
+      <c r="J8" t="n">
+        <v>423030.16</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3142666.349</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>688268.SH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>229.21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>233.33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>194</v>
+      </c>
+      <c r="F9" t="n">
+        <v>195.22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>229.21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-33.99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-14.8292</v>
+      </c>
+      <c r="J9" t="n">
+        <v>106946.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2320445.357</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688396.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>78.98</v>
+      </c>
+      <c r="F10" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-14.671</v>
+      </c>
+      <c r="J10" t="n">
+        <v>590513.34</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5095354.535</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688548.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="D11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-14.3418</v>
+      </c>
+      <c r="J11" t="n">
+        <v>658367.72</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3141526.867</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000004.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>国华退</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.5238</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1667187</v>
+      </c>
+      <c r="H2" t="n">
+        <v>570680.14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1250538</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1821218.14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>679857.86</v>
+      </c>
+      <c r="L2" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="M2" t="n">
+        <v>109.24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>58092971.28</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000078.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ST海王</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.6129</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>444851360</v>
+      </c>
+      <c r="H3" t="n">
+        <v>40199841.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43865546</v>
+      </c>
+      <c r="J3" t="n">
+        <v>84065387.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3665704.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4961657680.56</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000524.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>岭南控股</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.9628</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G4" t="n">
+        <v>354803183</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39453686.43</v>
+      </c>
+      <c r="I4" t="n">
+        <v>42305988.25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>81759674.68000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2852301.82</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6612577626.06</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>000547.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>航天发展</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.9879</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2343222112</v>
+      </c>
+      <c r="H5" t="n">
+        <v>196321675.95</v>
+      </c>
+      <c r="I5" t="n">
+        <v>413168285.15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>609489961.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>216846609.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28874329696.54</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>000566.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>海南海药</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.6512</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1344186898</v>
+      </c>
+      <c r="H6" t="n">
+        <v>187068686.07</v>
+      </c>
+      <c r="I6" t="n">
+        <v>189487349.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>376556035.77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2418663.63</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6418841383.35</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>000779.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>甘咨询</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.053000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2260246924</v>
+      </c>
+      <c r="H7" t="n">
+        <v>405619988.41</v>
+      </c>
+      <c r="I7" t="n">
+        <v>379195329.23</v>
+      </c>
+      <c r="J7" t="n">
+        <v>784815317.64</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-26424659.18</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4926593853</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>000838.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>*ST发展</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9.950200000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G8" t="n">
+        <v>411208176</v>
+      </c>
+      <c r="H8" t="n">
+        <v>40906172.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>39330623</v>
+      </c>
+      <c r="J8" t="n">
+        <v>80236795.06</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1575549.06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2328822539.55</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>000887.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中鼎股份</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2234005909</v>
+      </c>
+      <c r="H9" t="n">
+        <v>206994845.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>513705732.31</v>
+      </c>
+      <c r="J9" t="n">
+        <v>720700577.61</v>
+      </c>
+      <c r="K9" t="n">
+        <v>306710887.01</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="M9" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>27181184173.44</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>000887.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中鼎股份</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3336260844</v>
+      </c>
+      <c r="H10" t="n">
+        <v>286927711.16</v>
+      </c>
+      <c r="I10" t="n">
+        <v>752138922.83</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1039066633.99</v>
+      </c>
+      <c r="K10" t="n">
+        <v>465211211.67</v>
+      </c>
+      <c r="L10" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="M10" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27181184173.44</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>000892.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>欢瑞世纪</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.9476</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1033876821</v>
+      </c>
+      <c r="H11" t="n">
+        <v>180324838.26</v>
+      </c>
+      <c r="I11" t="n">
+        <v>143711834</v>
+      </c>
+      <c r="J11" t="n">
+        <v>324036672.26</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-36613004.26</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2985513106.8</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>000933.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>神火股份</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.0234</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2426165549</v>
+      </c>
+      <c r="H12" t="n">
+        <v>482461183</v>
+      </c>
+      <c r="I12" t="n">
+        <v>533682585.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1016143768.65</v>
+      </c>
+      <c r="K12" t="n">
+        <v>51221402.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="N12" t="n">
+        <v>52791897773.16</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>000938.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>紫光股份</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.6513</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="G13" t="n">
+        <v>49984898822</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4161734745.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6410003418.08</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10571738163.83</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2248268672.33</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="N13" t="n">
+        <v>109855391408.34</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>001365.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天海电子</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.6189</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1082306430</v>
+      </c>
+      <c r="H14" t="n">
+        <v>100543031.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>118315364.49</v>
+      </c>
+      <c r="J14" t="n">
+        <v>218858396.19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17772332.79</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2875282300</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>001395.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>亚联机械</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.9885</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>124334139</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23751424.53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>30861682.32</v>
+      </c>
+      <c r="J15" t="n">
+        <v>54613106.85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7110257.79</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="M15" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1488946095</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.9678</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4593485406</v>
+      </c>
+      <c r="H16" t="n">
+        <v>597851555.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>696879570.85</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1294731126.83</v>
+      </c>
+      <c r="K16" t="n">
+        <v>99028014.87</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15943886048.93</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002057.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中钢天源</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-5.8763</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1762221471</v>
+      </c>
+      <c r="H17" t="n">
+        <v>335867379.06</v>
+      </c>
+      <c r="I17" t="n">
+        <v>345036750.87</v>
+      </c>
+      <c r="J17" t="n">
+        <v>680904129.9299999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9169371.810000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M17" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6877755989.17</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002137.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>实益达</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.8776</v>
+      </c>
+      <c r="F18" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1371063496</v>
+      </c>
+      <c r="H18" t="n">
+        <v>175145725.69</v>
+      </c>
+      <c r="I18" t="n">
+        <v>159703791.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>334849517.49</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-15441933.89</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4765426133.62</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002192.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>融捷股份</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-10.0051</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2661277605</v>
+      </c>
+      <c r="H19" t="n">
+        <v>500154057.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>258676091.94</v>
+      </c>
+      <c r="J19" t="n">
+        <v>758830149.04</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-241477965.16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-9.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="N19" t="n">
+        <v>18436222789.7</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002192.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>融捷股份</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-10.0051</v>
+      </c>
+      <c r="F20" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6092062410</v>
+      </c>
+      <c r="H20" t="n">
+        <v>797919649.24</v>
+      </c>
+      <c r="I20" t="n">
+        <v>567059139.78</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1364978789.02</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-230860509.46</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="M20" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18436222789.7</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002202.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>金风科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9.985200000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5809635624</v>
+      </c>
+      <c r="H21" t="n">
+        <v>338776417.84</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1101206511.19</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1439982929.03</v>
+      </c>
+      <c r="K21" t="n">
+        <v>762430093.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="N21" t="n">
+        <v>75207973611.16</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002346.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>柘中股份</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.9849</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G22" t="n">
+        <v>265915131</v>
+      </c>
+      <c r="H22" t="n">
+        <v>83214242</v>
+      </c>
+      <c r="I22" t="n">
+        <v>89394763.81999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>172609005.82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6180521.82</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M22" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8551994889.75</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002353.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>杰瑞股份</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3093496149</v>
+      </c>
+      <c r="H23" t="n">
+        <v>732586374.5599999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>567466767.41</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1300053141.97</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-165119607.15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="M23" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="N23" t="n">
+        <v>104485038588</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002354.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>天娱数科</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.6931</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4654743548</v>
+      </c>
+      <c r="H24" t="n">
+        <v>312396206.94</v>
+      </c>
+      <c r="I24" t="n">
+        <v>723358243.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1035754450.24</v>
+      </c>
+      <c r="K24" t="n">
+        <v>410962036.36</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13883424872.66</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002414.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高德红外</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.9925</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2979367023</v>
+      </c>
+      <c r="H25" t="n">
+        <v>334747148.97</v>
+      </c>
+      <c r="I25" t="n">
+        <v>405028311.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>739775460.67</v>
+      </c>
+      <c r="K25" t="n">
+        <v>70281162.73</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="N25" t="n">
+        <v>49755685989.84</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002414.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>高德红外</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.9925</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3256007001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>347919949.49</v>
+      </c>
+      <c r="I26" t="n">
+        <v>405028311.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>752948261.1900001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>57108362.21</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>49755685989.84</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002497.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>雅化集团</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-7.4257</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7656357952</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1450181711.81</v>
+      </c>
+      <c r="I27" t="n">
+        <v>926343676.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2376525387.91</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-523838035.71</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="M27" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>19814288400.5</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-6.5076</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2327191918</v>
+      </c>
+      <c r="H28" t="n">
+        <v>406927284</v>
+      </c>
+      <c r="I28" t="n">
+        <v>398556894.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>805484178.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-8370389.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>34.61</v>
+      </c>
+      <c r="N28" t="n">
+        <v>22235488458.26</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002617.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>露笑科技</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-10.0213</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2939208489</v>
+      </c>
+      <c r="H29" t="n">
+        <v>494743324.49</v>
+      </c>
+      <c r="I29" t="n">
+        <v>304737168.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>799480493.09</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-190006155.89</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="M29" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>15847128093.28</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002808.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>恒久退</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10.5263</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2382516</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1106274.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1245040.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2351315.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>138766</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="M30" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="N30" t="n">
+        <v>39240821.76</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002828.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>贝肯能源</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10.0408</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G31" t="n">
+        <v>590259563</v>
+      </c>
+      <c r="H31" t="n">
+        <v>76469807.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>177180546.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>253650354.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>100710739.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="M31" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2709312848</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002829.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>星网宇达</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.9831</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G32" t="n">
+        <v>344881724</v>
+      </c>
+      <c r="H32" t="n">
+        <v>67632442.58</v>
+      </c>
+      <c r="I32" t="n">
+        <v>85154940.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>152787383.38</v>
+      </c>
+      <c r="K32" t="n">
+        <v>17522498.22</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M32" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2848024218</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.9412</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1852989</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1012635</v>
+      </c>
+      <c r="I33" t="n">
+        <v>926020.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1938655.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-86614.60000000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="M33" t="n">
+        <v>104.62</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35441857.85</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002903.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>宇环数控</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-10.0081</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>607617546</v>
+      </c>
+      <c r="H34" t="n">
+        <v>119301169.08</v>
+      </c>
+      <c r="I34" t="n">
+        <v>138047059.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>257348228.48</v>
+      </c>
+      <c r="K34" t="n">
+        <v>18745890.32</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M34" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3558366050.64</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002910.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>庄园牧场</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-8.1174</v>
+      </c>
+      <c r="F35" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="G35" t="n">
+        <v>472649226</v>
+      </c>
+      <c r="H35" t="n">
+        <v>61913215.36</v>
+      </c>
+      <c r="I35" t="n">
+        <v>122936073.7</v>
+      </c>
+      <c r="J35" t="n">
+        <v>184849289.06</v>
+      </c>
+      <c r="K35" t="n">
+        <v>61022858.34</v>
+      </c>
+      <c r="L35" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="M35" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1820099148</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>003020.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>立方制药</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.9765</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="G36" t="n">
+        <v>587201869</v>
+      </c>
+      <c r="H36" t="n">
+        <v>148550058.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>111839850.44</v>
+      </c>
+      <c r="J36" t="n">
+        <v>260389908.64</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-36710207.76</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="M36" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3158594298.7</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>003043.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>华亚智能</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1120382795</v>
+      </c>
+      <c r="H37" t="n">
+        <v>233822411.15</v>
+      </c>
+      <c r="I37" t="n">
+        <v>253889660.89</v>
+      </c>
+      <c r="J37" t="n">
+        <v>487712072.04</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20067249.74</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M37" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8779022574.299999</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>113705.SH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N豪26转</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>131.072</v>
+      </c>
+      <c r="E38" t="n">
+        <v>31.072</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>354427020</v>
+      </c>
+      <c r="H38" t="n">
+        <v>39783460</v>
+      </c>
+      <c r="I38" t="n">
+        <v>74541700</v>
+      </c>
+      <c r="J38" t="n">
+        <v>114325160</v>
+      </c>
+      <c r="K38" t="n">
+        <v>34758240</v>
+      </c>
+      <c r="L38" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="M38" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>113706.SH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N金帝转</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>89926480</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11417890</v>
+      </c>
+      <c r="I39" t="n">
+        <v>71754880</v>
+      </c>
+      <c r="J39" t="n">
+        <v>83172770</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60336990</v>
+      </c>
+      <c r="L39" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="M39" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>118053.SH</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>正帆转债</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>186.345</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-18.8007</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>2512824870</v>
+      </c>
+      <c r="H40" t="n">
+        <v>493008410</v>
+      </c>
+      <c r="I40" t="n">
+        <v>491709330</v>
+      </c>
+      <c r="J40" t="n">
+        <v>984717740</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-1299080</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M40" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价跌幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>118069.SH</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>爱科转债</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>188.76</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>31185040</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10772530</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31113310</v>
+      </c>
+      <c r="J41" t="n">
+        <v>41885840</v>
+      </c>
+      <c r="K41" t="n">
+        <v>20340780</v>
+      </c>
+      <c r="L41" t="n">
+        <v>65.23</v>
+      </c>
+      <c r="M41" t="n">
+        <v>134.31</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>118070.SH</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>N南芯转</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>177397080</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39370620</v>
+      </c>
+      <c r="I42" t="n">
+        <v>157835000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>197205620</v>
+      </c>
+      <c r="K42" t="n">
+        <v>118464380</v>
+      </c>
+      <c r="L42" t="n">
+        <v>66.78</v>
+      </c>
+      <c r="M42" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>123273.SZ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>三江转债</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>347</v>
+      </c>
+      <c r="E43" t="n">
+        <v>13.9659</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>8115168566.39</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8115168566.39</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8115168566.38</v>
+      </c>
+      <c r="J43" t="n">
+        <v>16230337132.77</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>200</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>123274.SZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>维科转债</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>36717703</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6397365</v>
+      </c>
+      <c r="I44" t="n">
+        <v>32623483.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>39020848.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>26226118.1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="M44" t="n">
+        <v>106.27</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>300065.SZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20.0083</v>
+      </c>
+      <c r="F45" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3279324851</v>
+      </c>
+      <c r="H45" t="n">
+        <v>103637817.97</v>
+      </c>
+      <c r="I45" t="n">
+        <v>536592434.97</v>
+      </c>
+      <c r="J45" t="n">
+        <v>640230252.9400001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>432954617</v>
+      </c>
+      <c r="L45" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="N45" t="n">
+        <v>18912009698.68</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>300069.SZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金利华电</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="E46" t="n">
+        <v>19.987</v>
+      </c>
+      <c r="F46" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>541282273</v>
+      </c>
+      <c r="H46" t="n">
+        <v>83218602</v>
+      </c>
+      <c r="I46" t="n">
+        <v>140353565.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>223572167.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>57134963.2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M46" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4312620000</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>300071.SZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>福石控股</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E47" t="n">
+        <v>19.1748</v>
+      </c>
+      <c r="F47" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1493332631</v>
+      </c>
+      <c r="H47" t="n">
+        <v>255534565</v>
+      </c>
+      <c r="I47" t="n">
+        <v>187483718.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>443018283.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-68050846.2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="M47" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4641672752.06</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>300071.SZ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>福石控股</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.1748</v>
+      </c>
+      <c r="F48" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2386366267</v>
+      </c>
+      <c r="H48" t="n">
+        <v>255865874</v>
+      </c>
+      <c r="I48" t="n">
+        <v>351771031.92</v>
+      </c>
+      <c r="J48" t="n">
+        <v>607636905.92</v>
+      </c>
+      <c r="K48" t="n">
+        <v>95905157.92</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M48" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4641672752.06</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>300164.SZ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>通源石油</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-3.4858</v>
+      </c>
+      <c r="F49" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1624578892</v>
+      </c>
+      <c r="H49" t="n">
+        <v>210856140.98</v>
+      </c>
+      <c r="I49" t="n">
+        <v>220279203.84</v>
+      </c>
+      <c r="J49" t="n">
+        <v>431135344.82</v>
+      </c>
+      <c r="K49" t="n">
+        <v>9423062.859999999</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M49" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5167247493.08</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>300255.SZ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>常山药业</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1766605471</v>
+      </c>
+      <c r="H50" t="n">
+        <v>129571817.41</v>
+      </c>
+      <c r="I50" t="n">
+        <v>377844752.95</v>
+      </c>
+      <c r="J50" t="n">
+        <v>507416570.36</v>
+      </c>
+      <c r="K50" t="n">
+        <v>248272935.54</v>
+      </c>
+      <c r="L50" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="M50" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="N50" t="n">
+        <v>24170199776.52</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>300390.SZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>天华新能</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-4.9204</v>
+      </c>
+      <c r="F51" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>18671370919</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1632569745.38</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1559844361.48</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3192414106.86</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-72725383.90000001</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M51" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>44167980071.7</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>300786.SZ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>国林科技</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E52" t="n">
+        <v>19.9799</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>237383545</v>
+      </c>
+      <c r="H52" t="n">
+        <v>43517221</v>
+      </c>
+      <c r="I52" t="n">
+        <v>64026647</v>
+      </c>
+      <c r="J52" t="n">
+        <v>107543868</v>
+      </c>
+      <c r="K52" t="n">
+        <v>20509426</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3498821834.1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>301117.SZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>佳缘科技</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="E53" t="n">
+        <v>19.9882</v>
+      </c>
+      <c r="F53" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="G53" t="n">
+        <v>570694109</v>
+      </c>
+      <c r="H53" t="n">
+        <v>58586907.74</v>
+      </c>
+      <c r="I53" t="n">
+        <v>122285183.08</v>
+      </c>
+      <c r="J53" t="n">
+        <v>180872090.82</v>
+      </c>
+      <c r="K53" t="n">
+        <v>63698275.34</v>
+      </c>
+      <c r="L53" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="M53" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2350697645.65</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>301516.SZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>中远通</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7.9456</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="G54" t="n">
+        <v>492685223</v>
+      </c>
+      <c r="H54" t="n">
+        <v>55951714.56</v>
+      </c>
+      <c r="I54" t="n">
+        <v>84822579.77</v>
+      </c>
+      <c r="J54" t="n">
+        <v>140774294.33</v>
+      </c>
+      <c r="K54" t="n">
+        <v>28870865.21</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="M54" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1449122815.35</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="E55" t="n">
+        <v>8.6058</v>
+      </c>
+      <c r="F55" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="G55" t="n">
+        <v>644817883</v>
+      </c>
+      <c r="H55" t="n">
+        <v>74164688.59999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>75033362.47</v>
+      </c>
+      <c r="J55" t="n">
+        <v>149198051.07</v>
+      </c>
+      <c r="K55" t="n">
+        <v>868673.87</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M55" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1477315654.74</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>托伦斯</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>858.8496</v>
+      </c>
+      <c r="F56" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5943898887</v>
+      </c>
+      <c r="H56" t="n">
+        <v>122073905.8</v>
+      </c>
+      <c r="I56" t="n">
+        <v>773096095.33</v>
+      </c>
+      <c r="J56" t="n">
+        <v>895170001.13</v>
+      </c>
+      <c r="K56" t="n">
+        <v>651022189.53</v>
+      </c>
+      <c r="L56" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="M56" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="N56" t="n">
+        <v>6681158529.1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>无价格涨跌幅限制的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>600129.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>太极集团</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7.7323</v>
+      </c>
+      <c r="F57" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2017659333</v>
+      </c>
+      <c r="H57" t="n">
+        <v>151744879.14</v>
+      </c>
+      <c r="I57" t="n">
+        <v>165046914.8</v>
+      </c>
+      <c r="J57" t="n">
+        <v>316791793.94</v>
+      </c>
+      <c r="K57" t="n">
+        <v>13302035.66</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M57" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N57" t="n">
+        <v>9142513507.299999</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>600172.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-9.0909</v>
+      </c>
+      <c r="F58" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5935782022</v>
+      </c>
+      <c r="H58" t="n">
+        <v>894318751.79</v>
+      </c>
+      <c r="I58" t="n">
+        <v>476778432.75</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1371097184.54</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-417540319.04</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-7.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>21696347750</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>600192.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>长城电工</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.0826</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G59" t="n">
+        <v>74609381</v>
+      </c>
+      <c r="H59" t="n">
+        <v>7691061</v>
+      </c>
+      <c r="I59" t="n">
+        <v>28170348</v>
+      </c>
+      <c r="J59" t="n">
+        <v>35861409</v>
+      </c>
+      <c r="K59" t="n">
+        <v>20479287</v>
+      </c>
+      <c r="L59" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="M59" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2942041680</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>600288.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>大恒科技</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-1.4303</v>
+      </c>
+      <c r="F60" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1834283719</v>
+      </c>
+      <c r="H60" t="n">
+        <v>381021806.85</v>
+      </c>
+      <c r="I60" t="n">
+        <v>219518990.83</v>
+      </c>
+      <c r="J60" t="n">
+        <v>600540797.6799999</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-161502816.02</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M60" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7224672000</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>600360.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>华微电子</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5.0031</v>
+      </c>
+      <c r="F61" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4791002850</v>
+      </c>
+      <c r="H61" t="n">
+        <v>337621357.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>699699370.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1037320727.79</v>
+      </c>
+      <c r="K61" t="n">
+        <v>362078012.79</v>
+      </c>
+      <c r="L61" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M61" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="N61" t="n">
+        <v>16123358154.16</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>600378.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>昊华科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-8.4894</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6221047413</v>
+      </c>
+      <c r="H62" t="n">
+        <v>892408211.38</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1008178005.87</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1900586217.25</v>
+      </c>
+      <c r="K62" t="n">
+        <v>115769794.49</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M62" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="N62" t="n">
+        <v>64976009690.54</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>600664.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.1307</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="G63" t="n">
+        <v>336874466</v>
+      </c>
+      <c r="H63" t="n">
+        <v>38957566.4</v>
+      </c>
+      <c r="I63" t="n">
+        <v>165439029</v>
+      </c>
+      <c r="J63" t="n">
+        <v>204396595.4</v>
+      </c>
+      <c r="K63" t="n">
+        <v>126481462.6</v>
+      </c>
+      <c r="L63" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="M63" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N63" t="n">
+        <v>8487378282.12</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>600821.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>金开新能</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.0901</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="G64" t="n">
+        <v>555091511</v>
+      </c>
+      <c r="H64" t="n">
+        <v>47503889.12</v>
+      </c>
+      <c r="I64" t="n">
+        <v>214123355.86</v>
+      </c>
+      <c r="J64" t="n">
+        <v>261627244.98</v>
+      </c>
+      <c r="K64" t="n">
+        <v>166619466.74</v>
+      </c>
+      <c r="L64" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="M64" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="N64" t="n">
+        <v>12020355462.83</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>600992.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>贵绳股份</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.0207</v>
+      </c>
+      <c r="F65" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="G65" t="n">
+        <v>223946213</v>
+      </c>
+      <c r="H65" t="n">
+        <v>24622735</v>
+      </c>
+      <c r="I65" t="n">
+        <v>56340783</v>
+      </c>
+      <c r="J65" t="n">
+        <v>80963518</v>
+      </c>
+      <c r="K65" t="n">
+        <v>31718048</v>
+      </c>
+      <c r="L65" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="M65" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2610208500</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>601608.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>中信重工</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10.0437</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G66" t="n">
+        <v>376969926</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64321836.62</v>
+      </c>
+      <c r="I66" t="n">
+        <v>76453556.56999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>140775393.19</v>
+      </c>
+      <c r="K66" t="n">
+        <v>12131719.95</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="M66" t="n">
+        <v>37.34</v>
+      </c>
+      <c r="N66" t="n">
+        <v>23080949322.48</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>603137.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>恒尚节能</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="E67" t="n">
+        <v>6.1508</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2516541500</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2516541400</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2516541500</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5033082900</v>
+      </c>
+      <c r="K67" t="n">
+        <v>100</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>200</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4893466684.5</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>603183.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>建研院</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4.4706</v>
+      </c>
+      <c r="F68" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="G68" t="n">
+        <v>934293644</v>
+      </c>
+      <c r="H68" t="n">
+        <v>136210835.22</v>
+      </c>
+      <c r="I68" t="n">
+        <v>177094324.55</v>
+      </c>
+      <c r="J68" t="n">
+        <v>313305159.77</v>
+      </c>
+      <c r="K68" t="n">
+        <v>40883489.33</v>
+      </c>
+      <c r="L68" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="M68" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2207360434.44</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>603203.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>快克智能</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-9.959099999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1764861960</v>
+      </c>
+      <c r="H69" t="n">
+        <v>220660249.04</v>
+      </c>
+      <c r="I69" t="n">
+        <v>116848012.51</v>
+      </c>
+      <c r="J69" t="n">
+        <v>337508261.55</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-103812236.53</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="M69" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="N69" t="n">
+        <v>19268770130.37</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>603459.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>红板科技</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-2.9318</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1701985101</v>
+      </c>
+      <c r="H70" t="n">
+        <v>374788764.41</v>
+      </c>
+      <c r="I70" t="n">
+        <v>330515485.34</v>
+      </c>
+      <c r="J70" t="n">
+        <v>705304249.75</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-44273279.07</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M70" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="N70" t="n">
+        <v>7197671670.9</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>603578.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>三星新材</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.0412</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G71" t="n">
+        <v>67180351</v>
+      </c>
+      <c r="H71" t="n">
+        <v>13674118.96</v>
+      </c>
+      <c r="I71" t="n">
+        <v>29019924</v>
+      </c>
+      <c r="J71" t="n">
+        <v>42694042.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>15345805.04</v>
+      </c>
+      <c r="L71" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="M71" t="n">
+        <v>63.55</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2411373517.84</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>603687.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-9.803900000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="G72" t="n">
+        <v>692387016</v>
+      </c>
+      <c r="H72" t="n">
+        <v>106498935.3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>63014307</v>
+      </c>
+      <c r="J72" t="n">
+        <v>169513242.3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-43484628.3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="M72" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="N72" t="n">
+        <v>8349483695.52</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>603898.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>好莱客</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="E73" t="n">
+        <v>10.0144</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G73" t="n">
+        <v>190625489</v>
+      </c>
+      <c r="H73" t="n">
+        <v>39711759</v>
+      </c>
+      <c r="I73" t="n">
+        <v>63073201</v>
+      </c>
+      <c r="J73" t="n">
+        <v>102784960</v>
+      </c>
+      <c r="K73" t="n">
+        <v>23361442</v>
+      </c>
+      <c r="L73" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="M73" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4584504190.14</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>603906.SH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>龙蟠科技</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-9.991899999999999</v>
+      </c>
+      <c r="F74" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1524730618</v>
+      </c>
+      <c r="H74" t="n">
+        <v>82487191.34</v>
+      </c>
+      <c r="I74" t="n">
+        <v>172571200.4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>255058391.74</v>
+      </c>
+      <c r="K74" t="n">
+        <v>90084009.06</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="M74" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="N74" t="n">
+        <v>12476002506.48</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>603928.SH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>兴业股份</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4.4444</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1516056639</v>
+      </c>
+      <c r="H75" t="n">
+        <v>96726747.05</v>
+      </c>
+      <c r="I75" t="n">
+        <v>93510522.02</v>
+      </c>
+      <c r="J75" t="n">
+        <v>190237269.07</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3216225.03</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6405235200</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>603928.SH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>兴业股份</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4.4444</v>
+      </c>
+      <c r="F76" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3470791080</v>
+      </c>
+      <c r="H76" t="n">
+        <v>267560026.1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>198250261.67</v>
+      </c>
+      <c r="J76" t="n">
+        <v>465810287.77</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-69309764.43000001</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="N76" t="n">
+        <v>6405235200</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>603931.SH</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>格林达</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.2806</v>
+      </c>
+      <c r="F77" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1251567652</v>
+      </c>
+      <c r="H77" t="n">
+        <v>244023722</v>
+      </c>
+      <c r="I77" t="n">
+        <v>321245418.06</v>
+      </c>
+      <c r="J77" t="n">
+        <v>565269140.0599999</v>
+      </c>
+      <c r="K77" t="n">
+        <v>77221696.06</v>
+      </c>
+      <c r="L77" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M77" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="N77" t="n">
+        <v>11570394872.4</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>603937.SH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>丽岛新材</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-9.4003</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="G78" t="n">
+        <v>237002991</v>
+      </c>
+      <c r="H78" t="n">
+        <v>21325935.8</v>
+      </c>
+      <c r="I78" t="n">
+        <v>15159529.88</v>
+      </c>
+      <c r="J78" t="n">
+        <v>36485465.68</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-6166405.92</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2335412459.38</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>603986.SH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>612</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-7.7605</v>
+      </c>
+      <c r="F79" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="G79" t="n">
+        <v>59381239201</v>
+      </c>
+      <c r="H79" t="n">
+        <v>9178558971.559999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5037007172.44</v>
+      </c>
+      <c r="J79" t="n">
+        <v>14215566144</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-4141551799.12</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-6.97</v>
+      </c>
+      <c r="M79" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="N79" t="n">
+        <v>409117063608</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>688146.SH</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>中船特气</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>293.99</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-19.1447</v>
+      </c>
+      <c r="F80" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="G80" t="n">
+        <v>6477248000</v>
+      </c>
+      <c r="H80" t="n">
+        <v>382093123.92</v>
+      </c>
+      <c r="I80" t="n">
+        <v>325553393.4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>707646517.3200001</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-56539730.52</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M80" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="N80" t="n">
+        <v>42619977839.58</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>688238.SH</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>和元生物</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="E81" t="n">
+        <v>16.6957</v>
+      </c>
+      <c r="F81" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="G81" t="n">
+        <v>466462600</v>
+      </c>
+      <c r="H81" t="n">
+        <v>44070976.12</v>
+      </c>
+      <c r="I81" t="n">
+        <v>92272560.7</v>
+      </c>
+      <c r="J81" t="n">
+        <v>136343536.82</v>
+      </c>
+      <c r="K81" t="n">
+        <v>48201584.58</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="M81" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4302087647</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>688249.SH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>晶合集成</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-17.0066</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G82" t="n">
+        <v>6385492700</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1316898933.53</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1476370210.92</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2793269144.45</v>
+      </c>
+      <c r="K82" t="n">
+        <v>159471277.39</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="N82" t="n">
+        <v>108650862641.64</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>688328.SH</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>深科达</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="E83" t="n">
+        <v>15.889</v>
+      </c>
+      <c r="F83" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2451972400</v>
+      </c>
+      <c r="H83" t="n">
+        <v>269209148.88</v>
+      </c>
+      <c r="I83" t="n">
+        <v>557355961.34</v>
+      </c>
+      <c r="J83" t="n">
+        <v>826565110.22</v>
+      </c>
+      <c r="K83" t="n">
+        <v>288146812.46</v>
+      </c>
+      <c r="L83" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M83" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="N83" t="n">
+        <v>11167567757.85</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>688328.SH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>深科达</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="E84" t="n">
+        <v>15.889</v>
+      </c>
+      <c r="F84" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3594163300</v>
+      </c>
+      <c r="H84" t="n">
+        <v>348432284.99</v>
+      </c>
+      <c r="I84" t="n">
+        <v>798357147.41</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1146789432.4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>449924862.42</v>
+      </c>
+      <c r="L84" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="M84" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="N84" t="n">
+        <v>11167567757.85</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>688392.SH</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>骄成超声</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>203.89</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-15.6782</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1732468500</v>
+      </c>
+      <c r="H85" t="n">
+        <v>370553796.79</v>
+      </c>
+      <c r="I85" t="n">
+        <v>416953656.58</v>
+      </c>
+      <c r="J85" t="n">
+        <v>787507453.37</v>
+      </c>
+      <c r="K85" t="n">
+        <v>46399859.79</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M85" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="N85" t="n">
+        <v>23596874770.4</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>688523.SH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>航天环宇</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="E86" t="n">
+        <v>20.0078</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G86" t="n">
+        <v>929854500</v>
+      </c>
+      <c r="H86" t="n">
+        <v>90782193.89</v>
+      </c>
+      <c r="I86" t="n">
+        <v>178657450.04</v>
+      </c>
+      <c r="J86" t="n">
+        <v>269439643.93</v>
+      </c>
+      <c r="K86" t="n">
+        <v>87875256.15000001</v>
+      </c>
+      <c r="L86" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M86" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="N86" t="n">
+        <v>24892918400</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>688549.SH</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>中巨芯</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-17.1001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4211699600</v>
+      </c>
+      <c r="H87" t="n">
+        <v>378171929.86</v>
+      </c>
+      <c r="I87" t="n">
+        <v>347277419.49</v>
+      </c>
+      <c r="J87" t="n">
+        <v>725449349.35</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-30894510.37</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M87" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="N87" t="n">
+        <v>17284726270</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>688596.SH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>正帆科技</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-15.3118</v>
+      </c>
+      <c r="F88" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3142666300</v>
+      </c>
+      <c r="H88" t="n">
+        <v>491825320.36</v>
+      </c>
+      <c r="I88" t="n">
+        <v>564489481.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1056314801.46</v>
+      </c>
+      <c r="K88" t="n">
+        <v>72664160.73999999</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M88" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="N88" t="n">
+        <v>20009794449.57</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>688710.SH</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>益诺思</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="E89" t="n">
+        <v>20.0031</v>
+      </c>
+      <c r="F89" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G89" t="n">
+        <v>503467100</v>
+      </c>
+      <c r="H89" t="n">
+        <v>150105517.65</v>
+      </c>
+      <c r="I89" t="n">
+        <v>161570879.17</v>
+      </c>
+      <c r="J89" t="n">
+        <v>311676396.82</v>
+      </c>
+      <c r="K89" t="n">
+        <v>11465361.52</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M89" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="N89" t="n">
+        <v>7062338976.68</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>688722.SH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>同益中</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="E90" t="n">
+        <v>19.9869</v>
+      </c>
+      <c r="F90" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="G90" t="n">
+        <v>360849600</v>
+      </c>
+      <c r="H90" t="n">
+        <v>57964613.17</v>
+      </c>
+      <c r="I90" t="n">
+        <v>73458555.97</v>
+      </c>
+      <c r="J90" t="n">
+        <v>131423169.14</v>
+      </c>
+      <c r="K90" t="n">
+        <v>15493942.8</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M90" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4103366212</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>688797.SH</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>臻宝科技</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>445.25</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-13.5638</v>
+      </c>
+      <c r="F91" t="n">
+        <v>31.46</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4587798000</v>
+      </c>
+      <c r="H91" t="n">
+        <v>656554419.41</v>
+      </c>
+      <c r="I91" t="n">
+        <v>446038362.04</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1102592781.45</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-210516057.37</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="M91" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="N91" t="n">
+        <v>12998048784.5</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>920136.BJ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>永励精密</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-24.9118</v>
+      </c>
+      <c r="F92" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="G92" t="n">
+        <v>325073700</v>
+      </c>
+      <c r="H92" t="n">
+        <v>26519045.16</v>
+      </c>
+      <c r="I92" t="n">
+        <v>20667530.02</v>
+      </c>
+      <c r="J92" t="n">
+        <v>47186575.18</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-5851515.14</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="N92" t="n">
+        <v>536130000</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>当日收盘价跌幅达到-20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>吉和昌</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-2.8775</v>
+      </c>
+      <c r="F93" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="G93" t="n">
+        <v>398713400</v>
+      </c>
+      <c r="H93" t="n">
+        <v>37054306.99</v>
+      </c>
+      <c r="I93" t="n">
+        <v>35924832.75</v>
+      </c>
+      <c r="J93" t="n">
+        <v>72979139.73999999</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-1129474.24</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M93" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N93" t="n">
+        <v>995148000</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>139.49</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.8175</v>
+      </c>
+      <c r="F94" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="G94" t="n">
+        <v>228732600</v>
+      </c>
+      <c r="H94" t="n">
+        <v>47141092.98</v>
+      </c>
+      <c r="I94" t="n">
+        <v>23527812.71</v>
+      </c>
+      <c r="J94" t="n">
+        <v>70668905.69</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-23613280.27</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="M94" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="N94" t="n">
+        <v>803462400</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>920267.BJ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>鑫汇科</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="E95" t="n">
+        <v>29.9427</v>
+      </c>
+      <c r="F95" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="G95" t="n">
+        <v>137787200</v>
+      </c>
+      <c r="H95" t="n">
+        <v>49755674.18</v>
+      </c>
+      <c r="I95" t="n">
+        <v>55616147.37</v>
+      </c>
+      <c r="J95" t="n">
+        <v>105371821.55</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5860473.19</v>
+      </c>
+      <c r="L95" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M95" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="N95" t="n">
+        <v>492991650.72</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-18.8406</v>
+      </c>
+      <c r="F96" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8948000</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1742314.45</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1928315.92</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3670630.37</v>
+      </c>
+      <c r="K96" t="n">
+        <v>186001.47</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M96" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="N96" t="n">
+        <v>45416490</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>920576.BJ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>天力复合</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E97" t="n">
+        <v>15.5713</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="G97" t="n">
+        <v>482174100</v>
+      </c>
+      <c r="H97" t="n">
+        <v>56820227.06</v>
+      </c>
+      <c r="I97" t="n">
+        <v>58047028.43</v>
+      </c>
+      <c r="J97" t="n">
+        <v>114867255.49</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1226801.37</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M97" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="N97" t="n">
+        <v>6677162532.6</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>920885.BJ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>星辰科技</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="E98" t="n">
+        <v>19.4421</v>
+      </c>
+      <c r="F98" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="G98" t="n">
+        <v>139453200</v>
+      </c>
+      <c r="H98" t="n">
+        <v>20641634.83</v>
+      </c>
+      <c r="I98" t="n">
+        <v>17985166.39</v>
+      </c>
+      <c r="J98" t="n">
+        <v>38626801.22</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-2656468.44</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="M98" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1250550159.48</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>920943.BJ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>优机股份</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="E99" t="n">
+        <v>29.9918</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="G99" t="n">
+        <v>48775200</v>
+      </c>
+      <c r="H99" t="n">
+        <v>7945516.92</v>
+      </c>
+      <c r="I99" t="n">
+        <v>18483624.89</v>
+      </c>
+      <c r="J99" t="n">
+        <v>26429141.81</v>
+      </c>
+      <c r="K99" t="n">
+        <v>10538107.97</v>
+      </c>
+      <c r="L99" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="M99" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="N99" t="n">
+        <v>819599918.0599999</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5521</v>
+        <v>5524</v>
       </c>
       <c r="C2" t="n">
-        <v>3772</v>
+        <v>801</v>
       </c>
       <c r="D2" t="n">
-        <v>1678</v>
+        <v>4683</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>34106.93</v>
+        <v>28347.13</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3996.1616</v>
+        <v>3913.794</v>
       </c>
       <c r="E2" t="n">
-        <v>-1</v>
+        <v>-2.06</v>
       </c>
       <c r="F2" t="n">
-        <v>15631.09</v>
+        <v>13348.72</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15046.6695</v>
+        <v>14522.8547</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.29</v>
+        <v>-3.48</v>
       </c>
       <c r="F3" t="n">
-        <v>11441.21</v>
+        <v>9044.6</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3842.7314</v>
+        <v>3723.5166</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.37</v>
+        <v>-3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>4241.91</v>
+        <v>3355.87</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4780.7867</v>
+        <v>4695.383</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.96</v>
+        <v>-1.79</v>
       </c>
       <c r="F5" t="n">
-        <v>10839.13</v>
+        <v>9079.450000000001</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2064.9756</v>
+        <v>1994.3192</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.53</v>
+        <v>-3.42</v>
       </c>
       <c r="F6" t="n">
-        <v>2350.96</v>
+        <v>2148.51</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8198.3078</v>
+        <v>7787.8529</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.23</v>
+        <v>-5.01</v>
       </c>
       <c r="F7" t="n">
-        <v>6918.14</v>
+        <v>5737.88</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35393.41</v>
+        <v>32938.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32938.2</v>
+        <v>36827.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36827.97</v>
+        <v>34739.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31124.37</v>
+        <v>25984.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25984.66</v>
+        <v>25825.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25825.92</v>
+        <v>29322.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29322.57</v>
+        <v>34106.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34106.93</v>
+        <v>28347.13</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>203.4</v>
+        <v>0.54</v>
       </c>
       <c r="D2" t="n">
-        <v>264.42</v>
+        <v>0.72</v>
       </c>
       <c r="E2" t="n">
-        <v>203.4</v>
+        <v>0.52</v>
       </c>
       <c r="F2" t="n">
-        <v>216.7</v>
+        <v>0.72</v>
       </c>
       <c r="G2" t="n">
-        <v>22.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>194.1</v>
+        <v>0.16</v>
       </c>
       <c r="I2" t="n">
-        <v>858.8496</v>
+        <v>28.5714</v>
       </c>
       <c r="J2" t="n">
-        <v>250811.68</v>
+        <v>146418.88</v>
       </c>
       <c r="K2" t="n">
-        <v>5943898.88669</v>
+        <v>9992.910690000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920943.BJ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.27</v>
+        <v>45.27</v>
       </c>
       <c r="D3" t="n">
-        <v>15.82</v>
+        <v>54.22</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>45.27</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82</v>
+        <v>54.22</v>
       </c>
       <c r="G3" t="n">
-        <v>12.17</v>
+        <v>45.18</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>29.9918</v>
+        <v>20.0089</v>
       </c>
       <c r="J3" t="n">
-        <v>32696.77</v>
+        <v>177997.99</v>
       </c>
       <c r="K3" t="n">
-        <v>48775.20716</v>
+        <v>907872.41285</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920267.BJ</t>
+          <t>300214.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13.97</v>
+        <v>12.3</v>
       </c>
       <c r="D4" t="n">
-        <v>18.14</v>
+        <v>12.3</v>
       </c>
       <c r="E4" t="n">
-        <v>13.97</v>
+        <v>12.3</v>
       </c>
       <c r="F4" t="n">
-        <v>18.14</v>
+        <v>12.3</v>
       </c>
       <c r="G4" t="n">
-        <v>13.96</v>
+        <v>10.25</v>
       </c>
       <c r="H4" t="n">
-        <v>4.18</v>
+        <v>2.05</v>
       </c>
       <c r="I4" t="n">
-        <v>29.9427</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>78578.13</v>
+        <v>63600.34</v>
       </c>
       <c r="K4" t="n">
-        <v>137787.20433</v>
+        <v>78228.4182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>920081.BJ</t>
+          <t>300534.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>7.81</v>
       </c>
       <c r="D5" t="n">
-        <v>58.88</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>46.88</v>
+        <v>7.79</v>
       </c>
       <c r="F5" t="n">
-        <v>47.02</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>38.69</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
-        <v>8.33</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>21.5301</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>151702.37</v>
+        <v>528881</v>
       </c>
       <c r="K5" t="n">
-        <v>782923.21071</v>
+        <v>461973.28398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300065.SZ</t>
+          <t>920943.BJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.57</v>
+        <v>16.97</v>
       </c>
       <c r="D6" t="n">
-        <v>28.79</v>
+        <v>19.15</v>
       </c>
       <c r="E6" t="n">
-        <v>23.32</v>
+        <v>16.22</v>
       </c>
       <c r="F6" t="n">
-        <v>28.79</v>
+        <v>18.78</v>
       </c>
       <c r="G6" t="n">
-        <v>23.99</v>
+        <v>15.82</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>2.96</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0083</v>
+        <v>18.7105</v>
       </c>
       <c r="J6" t="n">
-        <v>1235071.06</v>
+        <v>94924.00999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>3279324.85092</v>
+        <v>170758.30732</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688523.SH</t>
+          <t>301310.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49.99</v>
+        <v>60.34</v>
       </c>
       <c r="D7" t="n">
-        <v>61.18</v>
+        <v>70.37</v>
       </c>
       <c r="E7" t="n">
-        <v>49.34</v>
+        <v>60.34</v>
       </c>
       <c r="F7" t="n">
-        <v>61.18</v>
+        <v>68.84</v>
       </c>
       <c r="G7" t="n">
-        <v>50.98</v>
+        <v>58.64</v>
       </c>
       <c r="H7" t="n">
         <v>10.2</v>
       </c>
       <c r="I7" t="n">
-        <v>20.0078</v>
+        <v>17.3943</v>
       </c>
       <c r="J7" t="n">
-        <v>162299.79</v>
+        <v>238334.46</v>
       </c>
       <c r="K7" t="n">
-        <v>929854.518</v>
+        <v>1621500.85106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688710.SH</t>
+          <t>300039.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.88</v>
+        <v>4.51</v>
       </c>
       <c r="D8" t="n">
-        <v>77.87</v>
+        <v>5.27</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="n">
-        <v>77.87</v>
+        <v>5.2</v>
       </c>
       <c r="G8" t="n">
-        <v>64.89</v>
+        <v>4.49</v>
       </c>
       <c r="H8" t="n">
-        <v>12.98</v>
+        <v>0.71</v>
       </c>
       <c r="I8" t="n">
-        <v>20.0031</v>
+        <v>15.8129</v>
       </c>
       <c r="J8" t="n">
-        <v>68577.49000000001</v>
+        <v>912980.17</v>
       </c>
       <c r="K8" t="n">
-        <v>503467.138</v>
+        <v>458357.0106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300255.SZ</t>
+          <t>688176.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.57</v>
+        <v>12.57</v>
       </c>
       <c r="D9" t="n">
-        <v>26.34</v>
+        <v>15.1</v>
       </c>
       <c r="E9" t="n">
-        <v>21.43</v>
+        <v>12.57</v>
       </c>
       <c r="F9" t="n">
-        <v>26.34</v>
+        <v>14.7</v>
       </c>
       <c r="G9" t="n">
-        <v>21.95</v>
+        <v>12.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.39</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>14.8438</v>
       </c>
       <c r="J9" t="n">
-        <v>702690.3</v>
+        <v>536594</v>
       </c>
       <c r="K9" t="n">
-        <v>1766605.47086</v>
+        <v>748081.875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>301117.SZ</t>
+          <t>301092.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.86</v>
+        <v>53.91</v>
       </c>
       <c r="D10" t="n">
-        <v>20.29</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>15.86</v>
+        <v>53.9</v>
       </c>
       <c r="F10" t="n">
-        <v>20.29</v>
+        <v>61.28</v>
       </c>
       <c r="G10" t="n">
-        <v>16.91</v>
+        <v>55</v>
       </c>
       <c r="H10" t="n">
-        <v>3.38</v>
+        <v>6.28</v>
       </c>
       <c r="I10" t="n">
-        <v>19.9882</v>
+        <v>11.4182</v>
       </c>
       <c r="J10" t="n">
-        <v>314573.5</v>
+        <v>164203.58</v>
       </c>
       <c r="K10" t="n">
-        <v>570694.10893</v>
+        <v>989736.57407</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300069.SZ</t>
+          <t>920266.BJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30.31</v>
+        <v>6.56</v>
       </c>
       <c r="D11" t="n">
-        <v>36.86</v>
+        <v>8.01</v>
       </c>
       <c r="E11" t="n">
-        <v>30.11</v>
+        <v>6.56</v>
       </c>
       <c r="F11" t="n">
-        <v>36.86</v>
+        <v>7.19</v>
       </c>
       <c r="G11" t="n">
-        <v>30.72</v>
+        <v>6.48</v>
       </c>
       <c r="H11" t="n">
-        <v>6.14</v>
+        <v>0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>19.987</v>
+        <v>10.9568</v>
       </c>
       <c r="J11" t="n">
-        <v>155192.1</v>
+        <v>105120.85</v>
       </c>
       <c r="K11" t="n">
-        <v>541282.2732000001</v>
+        <v>77751.42294</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920136.BJ</t>
+          <t>301307.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>91.66</v>
       </c>
       <c r="D2" t="n">
-        <v>29.2</v>
+        <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>25.5</v>
+        <v>75.23</v>
       </c>
       <c r="F2" t="n">
-        <v>25.53</v>
+        <v>75.23</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.470000000000001</v>
+        <v>-18.81</v>
       </c>
       <c r="I2" t="n">
-        <v>-24.9118</v>
+        <v>-20.0021</v>
       </c>
       <c r="J2" t="n">
-        <v>121898.86</v>
+        <v>174350.27</v>
       </c>
       <c r="K2" t="n">
-        <v>325073.71754</v>
+        <v>1430403.2468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>688146.SH</t>
+          <t>688143.SH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>341</v>
+        <v>152.51</v>
       </c>
       <c r="D3" t="n">
-        <v>352.99</v>
+        <v>160</v>
       </c>
       <c r="E3" t="n">
-        <v>291.8</v>
+        <v>125.28</v>
       </c>
       <c r="F3" t="n">
-        <v>293.99</v>
+        <v>125.28</v>
       </c>
       <c r="G3" t="n">
-        <v>363.6</v>
+        <v>156.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-69.61</v>
+        <v>-31.32</v>
       </c>
       <c r="I3" t="n">
-        <v>-19.1447</v>
+        <v>-20</v>
       </c>
       <c r="J3" t="n">
-        <v>198706.66</v>
+        <v>158808.55</v>
       </c>
       <c r="K3" t="n">
-        <v>6477248.049</v>
+        <v>2188904.015</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>300475.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>244.9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.65</v>
+        <v>253.65</v>
       </c>
       <c r="E4" t="n">
-        <v>0.54</v>
+        <v>216.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5600000000000001</v>
+        <v>216.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6899999999999999</v>
+        <v>271</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.13</v>
+        <v>-54.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-18.8406</v>
+        <v>-20</v>
       </c>
       <c r="J4" t="n">
-        <v>155180.1</v>
+        <v>573960.74</v>
       </c>
       <c r="K4" t="n">
-        <v>8948.03961</v>
+        <v>13123767.0576</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688549.SH</t>
+          <t>301326.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.3</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>35.44</v>
+        <v>152.38</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>119.98</v>
       </c>
       <c r="F5" t="n">
-        <v>29.33</v>
+        <v>119.98</v>
       </c>
       <c r="G5" t="n">
-        <v>35.38</v>
+        <v>149.97</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.05</v>
+        <v>-29.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-17.1001</v>
+        <v>-19.9973</v>
       </c>
       <c r="J5" t="n">
-        <v>1309432.28</v>
+        <v>40138.51</v>
       </c>
       <c r="K5" t="n">
-        <v>4211699.558</v>
+        <v>522144.10744</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688249.SH</t>
+          <t>688450.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65.20999999999999</v>
+        <v>50.06</v>
       </c>
       <c r="D6" t="n">
-        <v>65.20999999999999</v>
+        <v>51.99</v>
       </c>
       <c r="E6" t="n">
-        <v>53.96</v>
+        <v>43.26</v>
       </c>
       <c r="F6" t="n">
-        <v>54.12</v>
+        <v>43.26</v>
       </c>
       <c r="G6" t="n">
-        <v>65.20999999999999</v>
+        <v>54.07</v>
       </c>
       <c r="H6" t="n">
-        <v>-11.09</v>
+        <v>-10.81</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.0066</v>
+        <v>-19.9926</v>
       </c>
       <c r="J6" t="n">
-        <v>1089386.25</v>
+        <v>60127.02</v>
       </c>
       <c r="K6" t="n">
-        <v>6385492.739</v>
+        <v>280356.888</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688392.SH</t>
+          <t>300147.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>241.81</v>
+        <v>8.85</v>
       </c>
       <c r="D7" t="n">
-        <v>248</v>
+        <v>8.85</v>
       </c>
       <c r="E7" t="n">
-        <v>203.89</v>
+        <v>7.34</v>
       </c>
       <c r="F7" t="n">
-        <v>203.89</v>
+        <v>7.34</v>
       </c>
       <c r="G7" t="n">
-        <v>241.8</v>
+        <v>9.17</v>
       </c>
       <c r="H7" t="n">
-        <v>-37.91</v>
+        <v>-1.83</v>
       </c>
       <c r="I7" t="n">
-        <v>-15.6782</v>
+        <v>-19.9564</v>
       </c>
       <c r="J7" t="n">
-        <v>76041.82000000001</v>
+        <v>348392</v>
       </c>
       <c r="K7" t="n">
-        <v>1732468.453</v>
+        <v>272960.4309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688596.SH</t>
+          <t>688319.SH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80.67</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>42.8</v>
       </c>
       <c r="E8" t="n">
-        <v>68.03</v>
+        <v>35.6</v>
       </c>
       <c r="F8" t="n">
-        <v>68.03</v>
+        <v>35.7</v>
       </c>
       <c r="G8" t="n">
-        <v>80.33</v>
+        <v>44.38</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.3</v>
+        <v>-8.68</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.3118</v>
+        <v>-19.5584</v>
       </c>
       <c r="J8" t="n">
-        <v>423030.16</v>
+        <v>321385.87</v>
       </c>
       <c r="K8" t="n">
-        <v>3142666.349</v>
+        <v>1251523.542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688268.SH</t>
+          <t>301588.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>229.21</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>233.33</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>194</v>
+        <v>44.34</v>
       </c>
       <c r="F9" t="n">
-        <v>195.22</v>
+        <v>44.63</v>
       </c>
       <c r="G9" t="n">
-        <v>229.21</v>
+        <v>55.43</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.99</v>
+        <v>-10.8</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.8292</v>
+        <v>-19.484</v>
       </c>
       <c r="J9" t="n">
-        <v>106946.72</v>
+        <v>93769.10000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2320445.357</v>
+        <v>445261.72857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688396.SH</t>
+          <t>301306.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>92.90000000000001</v>
+        <v>164.22</v>
       </c>
       <c r="D10" t="n">
-        <v>94.59999999999999</v>
+        <v>167.79</v>
       </c>
       <c r="E10" t="n">
-        <v>78.98</v>
+        <v>134.25</v>
       </c>
       <c r="F10" t="n">
-        <v>79.09999999999999</v>
+        <v>135.13</v>
       </c>
       <c r="G10" t="n">
-        <v>92.7</v>
+        <v>167.8</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.6</v>
+        <v>-32.67</v>
       </c>
       <c r="I10" t="n">
-        <v>-14.671</v>
+        <v>-19.4696</v>
       </c>
       <c r="J10" t="n">
-        <v>590513.34</v>
+        <v>78296.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5095354.535</v>
+        <v>1121068.12021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688548.SH</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51.51</v>
+        <v>25.13</v>
       </c>
       <c r="D11" t="n">
-        <v>52.5</v>
+        <v>25.58</v>
       </c>
       <c r="E11" t="n">
-        <v>43.1</v>
+        <v>21.6</v>
       </c>
       <c r="F11" t="n">
-        <v>43.6</v>
+        <v>21.92</v>
       </c>
       <c r="G11" t="n">
-        <v>50.9</v>
+        <v>26.96</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.3</v>
+        <v>-5.04</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.3418</v>
+        <v>-18.6944</v>
       </c>
       <c r="J11" t="n">
-        <v>658367.72</v>
+        <v>1843692.28</v>
       </c>
       <c r="K11" t="n">
-        <v>3141526.867</v>
+        <v>4312989.63941</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,7 +1819,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1833,37 +1833,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5238</v>
+        <v>10.8696</v>
       </c>
       <c r="F2" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1667187</v>
+        <v>1779195</v>
       </c>
       <c r="H2" t="n">
-        <v>570680.14</v>
+        <v>685185</v>
       </c>
       <c r="I2" t="n">
-        <v>1250538</v>
+        <v>1717578</v>
       </c>
       <c r="J2" t="n">
-        <v>1821218.14</v>
+        <v>2402763</v>
       </c>
       <c r="K2" t="n">
-        <v>679857.86</v>
+        <v>1032393</v>
       </c>
       <c r="L2" t="n">
-        <v>40.78</v>
+        <v>58.03</v>
       </c>
       <c r="M2" t="n">
-        <v>109.24</v>
+        <v>135.05</v>
       </c>
       <c r="N2" t="n">
-        <v>58092971.28</v>
+        <v>64407424.68</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -1874,51 +1874,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000078.SZ</t>
+          <t>000048.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST海王</t>
+          <t>京基智农</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.89</v>
+        <v>22.96</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6129</v>
+        <v>-4.7303</v>
       </c>
       <c r="F3" t="n">
-        <v>9.41</v>
+        <v>8.65</v>
       </c>
       <c r="G3" t="n">
-        <v>444851360</v>
+        <v>1119798947</v>
       </c>
       <c r="H3" t="n">
-        <v>40199841.8</v>
+        <v>303625125.51</v>
       </c>
       <c r="I3" t="n">
-        <v>43865546</v>
+        <v>243684011.81</v>
       </c>
       <c r="J3" t="n">
-        <v>84065387.8</v>
+        <v>547309137.3200001</v>
       </c>
       <c r="K3" t="n">
-        <v>3665704.2</v>
+        <v>-59941113.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.82</v>
+        <v>-5.35</v>
       </c>
       <c r="M3" t="n">
-        <v>18.9</v>
+        <v>48.88</v>
       </c>
       <c r="N3" t="n">
-        <v>4961657680.56</v>
+        <v>12152791140</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1929,216 +1929,216 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000524.SZ</t>
+          <t>000078.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>岭南控股</t>
+          <t>ST海王</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.869999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9628</v>
+        <v>10.0529</v>
       </c>
       <c r="F4" t="n">
-        <v>5.79</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>354803183</v>
+        <v>490270882</v>
       </c>
       <c r="H4" t="n">
-        <v>39453686.43</v>
+        <v>44044430.9</v>
       </c>
       <c r="I4" t="n">
-        <v>42305988.25</v>
+        <v>45041265</v>
       </c>
       <c r="J4" t="n">
-        <v>81759674.68000001</v>
+        <v>89085695.90000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2852301.82</v>
+        <v>996834.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>23.04</v>
+        <v>18.17</v>
       </c>
       <c r="N4" t="n">
-        <v>6612577626.06</v>
+        <v>5460448664.32</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000547.SZ</t>
+          <t>000892.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>欢瑞世纪</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.17</v>
+        <v>3.98</v>
       </c>
       <c r="E5" t="n">
-        <v>9.9879</v>
+        <v>-5.2381</v>
       </c>
       <c r="F5" t="n">
-        <v>8.390000000000001</v>
+        <v>27.21</v>
       </c>
       <c r="G5" t="n">
-        <v>2343222112</v>
+        <v>813917299</v>
       </c>
       <c r="H5" t="n">
-        <v>196321675.95</v>
+        <v>113702568</v>
       </c>
       <c r="I5" t="n">
-        <v>413168285.15</v>
+        <v>137302111</v>
       </c>
       <c r="J5" t="n">
-        <v>609489961.1</v>
+        <v>251004679</v>
       </c>
       <c r="K5" t="n">
-        <v>216846609.2</v>
+        <v>23599543</v>
       </c>
       <c r="L5" t="n">
-        <v>9.25</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>26.01</v>
+        <v>30.84</v>
       </c>
       <c r="N5" t="n">
-        <v>28874329696.54</v>
+        <v>2829129086.92</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>000566.SZ</t>
+          <t>000920.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>海南海药</t>
+          <t>沃顿科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.95</v>
+        <v>14.03</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6512</v>
+        <v>10.0392</v>
       </c>
       <c r="F6" t="n">
-        <v>21.17</v>
+        <v>10.15</v>
       </c>
       <c r="G6" t="n">
-        <v>1344186898</v>
+        <v>657440325</v>
       </c>
       <c r="H6" t="n">
-        <v>187068686.07</v>
+        <v>86861605.87</v>
       </c>
       <c r="I6" t="n">
-        <v>189487349.7</v>
+        <v>109360576.5</v>
       </c>
       <c r="J6" t="n">
-        <v>376556035.77</v>
+        <v>196222182.37</v>
       </c>
       <c r="K6" t="n">
-        <v>2418663.63</v>
+        <v>22498970.63</v>
       </c>
       <c r="L6" t="n">
-        <v>0.18</v>
+        <v>3.42</v>
       </c>
       <c r="M6" t="n">
-        <v>28.01</v>
+        <v>29.85</v>
       </c>
       <c r="N6" t="n">
-        <v>6418841383.35</v>
+        <v>6630558610.54</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000779.SZ</t>
+          <t>000920.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>甘咨询</t>
+          <t>沃顿科技</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.6</v>
+        <v>14.03</v>
       </c>
       <c r="E7" t="n">
-        <v>8.053000000000001</v>
+        <v>10.0392</v>
       </c>
       <c r="F7" t="n">
-        <v>18.33</v>
+        <v>10.15</v>
       </c>
       <c r="G7" t="n">
-        <v>2260246924</v>
+        <v>836384067</v>
       </c>
       <c r="H7" t="n">
-        <v>405619988.41</v>
+        <v>92065975.62</v>
       </c>
       <c r="I7" t="n">
-        <v>379195329.23</v>
+        <v>147638306.5</v>
       </c>
       <c r="J7" t="n">
-        <v>784815317.64</v>
+        <v>239704282.12</v>
       </c>
       <c r="K7" t="n">
-        <v>-26424659.18</v>
+        <v>55572330.88</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.17</v>
+        <v>6.64</v>
       </c>
       <c r="M7" t="n">
-        <v>34.72</v>
+        <v>28.66</v>
       </c>
       <c r="N7" t="n">
-        <v>4926593853</v>
+        <v>6630558610.54</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -2149,106 +2149,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000838.SZ</t>
+          <t>000925.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*ST发展</t>
+          <t>众合科技</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.21</v>
+        <v>7.82</v>
       </c>
       <c r="E8" t="n">
-        <v>9.950200000000001</v>
+        <v>-7.1259</v>
       </c>
       <c r="F8" t="n">
-        <v>6.43</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>411208176</v>
+        <v>560100426</v>
       </c>
       <c r="H8" t="n">
-        <v>40906172.06</v>
+        <v>170325932.33</v>
       </c>
       <c r="I8" t="n">
-        <v>39330623</v>
+        <v>72263141</v>
       </c>
       <c r="J8" t="n">
-        <v>80236795.06</v>
+        <v>242589073.33</v>
       </c>
       <c r="K8" t="n">
-        <v>-1575549.06</v>
+        <v>-98062791.33</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.38</v>
+        <v>-17.51</v>
       </c>
       <c r="M8" t="n">
-        <v>19.51</v>
+        <v>43.31</v>
       </c>
       <c r="N8" t="n">
-        <v>2328822539.55</v>
+        <v>5248412065.16</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>000887.SZ</t>
+          <t>000989.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>九芝堂</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.68</v>
+        <v>8.98</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>10.049</v>
       </c>
       <c r="F9" t="n">
-        <v>8.25</v>
+        <v>10.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2234005909</v>
+        <v>670064701</v>
       </c>
       <c r="H9" t="n">
-        <v>206994845.3</v>
+        <v>53707121</v>
       </c>
       <c r="I9" t="n">
-        <v>513705732.31</v>
+        <v>74560831.52</v>
       </c>
       <c r="J9" t="n">
-        <v>720700577.61</v>
+        <v>128267952.52</v>
       </c>
       <c r="K9" t="n">
-        <v>306710887.01</v>
+        <v>20853710.52</v>
       </c>
       <c r="L9" t="n">
-        <v>13.73</v>
+        <v>3.11</v>
       </c>
       <c r="M9" t="n">
-        <v>32.26</v>
+        <v>19.14</v>
       </c>
       <c r="N9" t="n">
-        <v>27181184173.44</v>
+        <v>6233500701.94</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2259,106 +2259,106 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>000887.SZ</t>
+          <t>001395.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>亚联机械</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.68</v>
+        <v>31.49</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>9.9895</v>
       </c>
       <c r="F10" t="n">
-        <v>8.25</v>
+        <v>22.38</v>
       </c>
       <c r="G10" t="n">
-        <v>3336260844</v>
+        <v>357072174</v>
       </c>
       <c r="H10" t="n">
-        <v>286927711.16</v>
+        <v>57019950.07</v>
       </c>
       <c r="I10" t="n">
-        <v>752138922.83</v>
+        <v>39147346.07</v>
       </c>
       <c r="J10" t="n">
-        <v>1039066633.99</v>
+        <v>96167296.14</v>
       </c>
       <c r="K10" t="n">
-        <v>465211211.67</v>
+        <v>-17872604</v>
       </c>
       <c r="L10" t="n">
-        <v>13.94</v>
+        <v>-5.01</v>
       </c>
       <c r="M10" t="n">
-        <v>31.14</v>
+        <v>26.93</v>
       </c>
       <c r="N10" t="n">
-        <v>27181184173.44</v>
+        <v>1637684685</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>000892.SZ</t>
+          <t>002038.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>欢瑞世纪</t>
+          <t>双鹭药业</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.2</v>
+        <v>6.72</v>
       </c>
       <c r="E11" t="n">
-        <v>9.9476</v>
+        <v>5.3292</v>
       </c>
       <c r="F11" t="n">
-        <v>20.22</v>
+        <v>13.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1033876821</v>
+        <v>1220822281</v>
       </c>
       <c r="H11" t="n">
-        <v>180324838.26</v>
+        <v>182319818.03</v>
       </c>
       <c r="I11" t="n">
-        <v>143711834</v>
+        <v>184380074.72</v>
       </c>
       <c r="J11" t="n">
-        <v>324036672.26</v>
+        <v>366699892.75</v>
       </c>
       <c r="K11" t="n">
-        <v>-36613004.26</v>
+        <v>2060256.69</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.54</v>
+        <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>31.34</v>
+        <v>30.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2985513106.8</v>
+        <v>5724844043.52</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2369,216 +2369,216 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>000933.SZ</t>
+          <t>002115.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>神火股份</t>
+          <t>三维通信</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23.49</v>
+        <v>11.6</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0234</v>
+        <v>5.9361</v>
       </c>
       <c r="F12" t="n">
-        <v>4.71</v>
+        <v>21.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2426165549</v>
+        <v>1995660255</v>
       </c>
       <c r="H12" t="n">
-        <v>482461183</v>
+        <v>178401283.91</v>
       </c>
       <c r="I12" t="n">
-        <v>533682585.65</v>
+        <v>205488276.81</v>
       </c>
       <c r="J12" t="n">
-        <v>1016143768.65</v>
+        <v>383889560.72</v>
       </c>
       <c r="K12" t="n">
-        <v>51221402.65</v>
+        <v>27086992.9</v>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>41.88</v>
+        <v>19.24</v>
       </c>
       <c r="N12" t="n">
-        <v>52791897773.16</v>
+        <v>8656688001.200001</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>000938.SZ</t>
+          <t>002185.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>38.41</v>
+        <v>24.13</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6513</v>
+        <v>-4.6622</v>
       </c>
       <c r="F13" t="n">
-        <v>16.88</v>
+        <v>24.55</v>
       </c>
       <c r="G13" t="n">
-        <v>49984898822</v>
+        <v>20770697680</v>
       </c>
       <c r="H13" t="n">
-        <v>4161734745.75</v>
+        <v>3054545337.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6410003418.08</v>
+        <v>3323616639.41</v>
       </c>
       <c r="J13" t="n">
-        <v>10571738163.83</v>
+        <v>6378161977.01</v>
       </c>
       <c r="K13" t="n">
-        <v>2248268672.33</v>
+        <v>269071301.81</v>
       </c>
       <c r="L13" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
-        <v>21.15</v>
+        <v>30.71</v>
       </c>
       <c r="N13" t="n">
-        <v>109855391408.34</v>
+        <v>80175586896.41</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>001365.SZ</t>
+          <t>002208.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>天海电子</t>
+          <t>合肥城建</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>20.88</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6189</v>
+        <v>7.4627</v>
       </c>
       <c r="F14" t="n">
-        <v>39.15</v>
+        <v>14.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1082306430</v>
+        <v>5397157740</v>
       </c>
       <c r="H14" t="n">
-        <v>100543031.7</v>
+        <v>808938742.8</v>
       </c>
       <c r="I14" t="n">
-        <v>118315364.49</v>
+        <v>559643629.8</v>
       </c>
       <c r="J14" t="n">
-        <v>218858396.19</v>
+        <v>1368582372.6</v>
       </c>
       <c r="K14" t="n">
-        <v>17772332.79</v>
+        <v>-249295113</v>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>-4.62</v>
       </c>
       <c r="M14" t="n">
-        <v>20.22</v>
+        <v>25.36</v>
       </c>
       <c r="N14" t="n">
-        <v>2875282300</v>
+        <v>16768148934.96</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>001395.SZ</t>
+          <t>002317.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>亚联机械</t>
+          <t>众生药业</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>28.63</v>
+        <v>31.6</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9885</v>
+        <v>6.9736</v>
       </c>
       <c r="F15" t="n">
-        <v>7.3</v>
+        <v>11.46</v>
       </c>
       <c r="G15" t="n">
-        <v>124334139</v>
+        <v>4648209584</v>
       </c>
       <c r="H15" t="n">
-        <v>23751424.53</v>
+        <v>698188456.79</v>
       </c>
       <c r="I15" t="n">
-        <v>30861682.32</v>
+        <v>987763283.48</v>
       </c>
       <c r="J15" t="n">
-        <v>54613106.85</v>
+        <v>1685951740.27</v>
       </c>
       <c r="K15" t="n">
-        <v>7110257.79</v>
+        <v>289574826.69</v>
       </c>
       <c r="L15" t="n">
-        <v>5.72</v>
+        <v>6.23</v>
       </c>
       <c r="M15" t="n">
-        <v>43.92</v>
+        <v>36.27</v>
       </c>
       <c r="N15" t="n">
-        <v>1488946095</v>
+        <v>24067110029.6</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -2589,51 +2589,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>001399.SZ</t>
+          <t>002354.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37.03</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.9678</v>
+        <v>-6.3232</v>
       </c>
       <c r="F16" t="n">
-        <v>27.37</v>
+        <v>27.4</v>
       </c>
       <c r="G16" t="n">
-        <v>4593485406</v>
+        <v>3747121658</v>
       </c>
       <c r="H16" t="n">
-        <v>597851555.98</v>
+        <v>642640828.49</v>
       </c>
       <c r="I16" t="n">
-        <v>696879570.85</v>
+        <v>398726640.86</v>
       </c>
       <c r="J16" t="n">
-        <v>1294731126.83</v>
+        <v>1041367469.35</v>
       </c>
       <c r="K16" t="n">
-        <v>99028014.87</v>
+        <v>-243914187.63</v>
       </c>
       <c r="L16" t="n">
-        <v>2.16</v>
+        <v>-6.51</v>
       </c>
       <c r="M16" t="n">
-        <v>28.19</v>
+        <v>27.79</v>
       </c>
       <c r="N16" t="n">
-        <v>15943886048.93</v>
+        <v>13005550232</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2644,2223 +2644,2247 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002057.SZ</t>
+          <t>002379.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中钢天源</t>
+          <t>宏桥控股</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9.130000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.8763</v>
+        <v>10.0346</v>
       </c>
       <c r="F17" t="n">
-        <v>8.73</v>
+        <v>5.36</v>
       </c>
       <c r="G17" t="n">
-        <v>1762221471</v>
+        <v>947477175</v>
       </c>
       <c r="H17" t="n">
-        <v>335867379.06</v>
+        <v>203009596.5</v>
       </c>
       <c r="I17" t="n">
-        <v>345036750.87</v>
+        <v>179714684</v>
       </c>
       <c r="J17" t="n">
-        <v>680904129.9299999</v>
+        <v>382724280.5</v>
       </c>
       <c r="K17" t="n">
-        <v>9169371.810000001</v>
+        <v>-23294912.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.52</v>
+        <v>-2.46</v>
       </c>
       <c r="M17" t="n">
-        <v>38.64</v>
+        <v>40.39</v>
       </c>
       <c r="N17" t="n">
-        <v>6877755989.17</v>
+        <v>18068342672.7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002137.SZ</t>
+          <t>002674.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>实益达</t>
+          <t>兴业科技</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.02</v>
+        <v>32.96</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8776</v>
+        <v>7.013</v>
       </c>
       <c r="F18" t="n">
-        <v>29.13</v>
+        <v>15.59</v>
       </c>
       <c r="G18" t="n">
-        <v>1371063496</v>
+        <v>1497243135</v>
       </c>
       <c r="H18" t="n">
-        <v>175145725.69</v>
+        <v>165687532.38</v>
       </c>
       <c r="I18" t="n">
-        <v>159703791.8</v>
+        <v>84134178</v>
       </c>
       <c r="J18" t="n">
-        <v>334849517.49</v>
+        <v>249821710.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-15441933.89</v>
+        <v>-81553354.38</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.13</v>
+        <v>-5.45</v>
       </c>
       <c r="M18" t="n">
-        <v>24.42</v>
+        <v>16.69</v>
       </c>
       <c r="N18" t="n">
-        <v>4765426133.62</v>
+        <v>9642897969.92</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002192.SZ</t>
+          <t>002726.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>融捷股份</t>
+          <t>ST龙大</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71.15000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.0051</v>
+        <v>8.860799999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>14.27</v>
+        <v>10.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2661277605</v>
+        <v>577293038</v>
       </c>
       <c r="H19" t="n">
-        <v>500154057.1</v>
+        <v>71443456.09999999</v>
       </c>
       <c r="I19" t="n">
-        <v>258676091.94</v>
+        <v>50758454.99</v>
       </c>
       <c r="J19" t="n">
-        <v>758830149.04</v>
+        <v>122201911.09</v>
       </c>
       <c r="K19" t="n">
-        <v>-241477965.16</v>
+        <v>-20685001.11</v>
       </c>
       <c r="L19" t="n">
-        <v>-9.07</v>
+        <v>-3.58</v>
       </c>
       <c r="M19" t="n">
-        <v>28.51</v>
+        <v>21.17</v>
       </c>
       <c r="N19" t="n">
-        <v>18436222789.7</v>
+        <v>2259959887.24</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002192.SZ</t>
+          <t>002768.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>融捷股份</t>
+          <t>国恩股份</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71.15000000000001</v>
+        <v>52.23</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.0051</v>
+        <v>-8.1266</v>
       </c>
       <c r="F20" t="n">
-        <v>14.27</v>
+        <v>10.72</v>
       </c>
       <c r="G20" t="n">
-        <v>6092062410</v>
+        <v>1601669588</v>
       </c>
       <c r="H20" t="n">
-        <v>797919649.24</v>
+        <v>350906677.15</v>
       </c>
       <c r="I20" t="n">
-        <v>567059139.78</v>
+        <v>391216288.38</v>
       </c>
       <c r="J20" t="n">
-        <v>1364978789.02</v>
+        <v>742122965.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-230860509.46</v>
+        <v>40309611.23</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.79</v>
+        <v>2.52</v>
       </c>
       <c r="M20" t="n">
-        <v>22.41</v>
+        <v>46.33</v>
       </c>
       <c r="N20" t="n">
-        <v>18436222789.7</v>
+        <v>13506010761.75</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002202.SZ</t>
+          <t>002808.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>恒久退</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.36</v>
+        <v>0.22</v>
       </c>
       <c r="E21" t="n">
-        <v>9.985200000000001</v>
+        <v>4.7619</v>
       </c>
       <c r="F21" t="n">
-        <v>7.96</v>
+        <v>7.43</v>
       </c>
       <c r="G21" t="n">
-        <v>5809635624</v>
+        <v>3058849</v>
       </c>
       <c r="H21" t="n">
-        <v>338776417.84</v>
+        <v>962929</v>
       </c>
       <c r="I21" t="n">
-        <v>1101206511.19</v>
+        <v>1435142.02</v>
       </c>
       <c r="J21" t="n">
-        <v>1439982929.03</v>
+        <v>2398071.02</v>
       </c>
       <c r="K21" t="n">
-        <v>762430093.35</v>
+        <v>472213.02</v>
       </c>
       <c r="L21" t="n">
-        <v>13.12</v>
+        <v>15.44</v>
       </c>
       <c r="M21" t="n">
-        <v>24.79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>75207973611.16</v>
+        <v>41109432.32</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002346.SZ</t>
+          <t>002829.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>柘中股份</t>
+          <t>星网宇达</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.81</v>
+        <v>20.49</v>
       </c>
       <c r="E22" t="n">
-        <v>9.9849</v>
+        <v>5.0769</v>
       </c>
       <c r="F22" t="n">
-        <v>2.43</v>
+        <v>25.26</v>
       </c>
       <c r="G22" t="n">
-        <v>265915131</v>
+        <v>751967410</v>
       </c>
       <c r="H22" t="n">
-        <v>83214242</v>
+        <v>104685781.85</v>
       </c>
       <c r="I22" t="n">
-        <v>89394763.81999999</v>
+        <v>79001824.64</v>
       </c>
       <c r="J22" t="n">
-        <v>172609005.82</v>
+        <v>183687606.49</v>
       </c>
       <c r="K22" t="n">
-        <v>6180521.82</v>
+        <v>-25683957.21</v>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>-3.42</v>
       </c>
       <c r="M22" t="n">
-        <v>64.91</v>
+        <v>24.43</v>
       </c>
       <c r="N22" t="n">
-        <v>8551994889.75</v>
+        <v>2992616216.76</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002353.SZ</t>
+          <t>002842.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>杰瑞股份</t>
+          <t>翔鹭钨业</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>151.2</v>
+        <v>37.17</v>
       </c>
       <c r="E23" t="n">
-        <v>-10</v>
+        <v>5.1485</v>
       </c>
       <c r="F23" t="n">
-        <v>2.86</v>
+        <v>25.23</v>
       </c>
       <c r="G23" t="n">
-        <v>3093496149</v>
+        <v>2552248402</v>
       </c>
       <c r="H23" t="n">
-        <v>732586374.5599999</v>
+        <v>356014641</v>
       </c>
       <c r="I23" t="n">
-        <v>567466767.41</v>
+        <v>462232021</v>
       </c>
       <c r="J23" t="n">
-        <v>1300053141.97</v>
+        <v>818246662</v>
       </c>
       <c r="K23" t="n">
-        <v>-165119607.15</v>
+        <v>106217380</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.34</v>
+        <v>4.16</v>
       </c>
       <c r="M23" t="n">
-        <v>42.03</v>
+        <v>32.06</v>
       </c>
       <c r="N23" t="n">
-        <v>104485038588</v>
+        <v>9978745884.030001</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002354.SZ</t>
+          <t>002898.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>天娱数科</t>
+          <t>赛隆退</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.539999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="E24" t="n">
-        <v>5.6931</v>
+        <v>8.571400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>33.09</v>
+        <v>11.28</v>
       </c>
       <c r="G24" t="n">
-        <v>4654743548</v>
+        <v>4273676</v>
       </c>
       <c r="H24" t="n">
-        <v>312396206.94</v>
+        <v>1348808</v>
       </c>
       <c r="I24" t="n">
-        <v>723358243.3</v>
+        <v>1844821</v>
       </c>
       <c r="J24" t="n">
-        <v>1035754450.24</v>
+        <v>3193629</v>
       </c>
       <c r="K24" t="n">
-        <v>410962036.36</v>
+        <v>496013</v>
       </c>
       <c r="L24" t="n">
-        <v>8.83</v>
+        <v>11.61</v>
       </c>
       <c r="M24" t="n">
-        <v>22.25</v>
+        <v>74.73</v>
       </c>
       <c r="N24" t="n">
-        <v>13883424872.66</v>
+        <v>38479731.38</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002414.SZ</t>
+          <t>002910.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高德红外</t>
+          <t>庄园牧场</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.64</v>
+        <v>9.58</v>
       </c>
       <c r="E25" t="n">
-        <v>9.9925</v>
+        <v>-9.962400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>14.34</v>
       </c>
       <c r="G25" t="n">
-        <v>2979367023</v>
+        <v>999000647</v>
       </c>
       <c r="H25" t="n">
-        <v>334747148.97</v>
+        <v>149055234.36</v>
       </c>
       <c r="I25" t="n">
-        <v>405028311.7</v>
+        <v>196474231.7</v>
       </c>
       <c r="J25" t="n">
-        <v>739775460.67</v>
+        <v>345529466.06</v>
       </c>
       <c r="K25" t="n">
-        <v>70281162.73</v>
+        <v>47418997.34</v>
       </c>
       <c r="L25" t="n">
-        <v>2.36</v>
+        <v>4.75</v>
       </c>
       <c r="M25" t="n">
-        <v>24.83</v>
+        <v>34.59</v>
       </c>
       <c r="N25" t="n">
-        <v>49755685989.84</v>
+        <v>1638773481</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002414.SZ</t>
+          <t>118069.SH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>高德红外</t>
+          <t>爱科转债</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.64</v>
+        <v>203.772</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9925</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
+        <v>7.953</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>3256007001</v>
+        <v>2620623150</v>
       </c>
       <c r="H26" t="n">
-        <v>347919949.49</v>
+        <v>533889240</v>
       </c>
       <c r="I26" t="n">
-        <v>405028311.7</v>
+        <v>529137790</v>
       </c>
       <c r="J26" t="n">
-        <v>752948261.1900001</v>
+        <v>1063027030</v>
       </c>
       <c r="K26" t="n">
-        <v>57108362.21</v>
+        <v>-4751450</v>
       </c>
       <c r="L26" t="n">
-        <v>1.75</v>
+        <v>-0.18</v>
       </c>
       <c r="M26" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="N26" t="n">
-        <v>49755685989.84</v>
-      </c>
+        <v>40.56</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>连续3个交易日内日收盘价格涨幅偏离值达到30%的可转债</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>002497.SZ</t>
+          <t>300039.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>雅化集团</t>
+          <t>上海凯宝</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18.7</v>
+        <v>5.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.4257</v>
+        <v>15.8129</v>
       </c>
       <c r="F27" t="n">
-        <v>10.44</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>7656357952</v>
+        <v>458357011</v>
       </c>
       <c r="H27" t="n">
-        <v>1450181711.81</v>
+        <v>41196920.14</v>
       </c>
       <c r="I27" t="n">
-        <v>926343676.1</v>
+        <v>47244046.44</v>
       </c>
       <c r="J27" t="n">
-        <v>2376525387.91</v>
+        <v>88440966.58</v>
       </c>
       <c r="K27" t="n">
-        <v>-523838035.71</v>
+        <v>6047126.3</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.84</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
-        <v>31.04</v>
+        <v>19.3</v>
       </c>
       <c r="N27" t="n">
-        <v>19814288400.5</v>
+        <v>4768016375.2</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>002552.SZ</t>
+          <t>300069.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>宝鼎科技</t>
+          <t>金利华电</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>60.34</v>
+        <v>40.1</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.5076</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>9.369999999999999</v>
+        <v>27.98</v>
       </c>
       <c r="G28" t="n">
-        <v>2327191918</v>
+        <v>1831342062</v>
       </c>
       <c r="H28" t="n">
-        <v>406927284</v>
+        <v>217557537.85</v>
       </c>
       <c r="I28" t="n">
-        <v>398556894.8</v>
+        <v>297353255.2</v>
       </c>
       <c r="J28" t="n">
-        <v>805484178.8</v>
+        <v>514910793.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-8370389.2</v>
+        <v>79795717.34999999</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.36</v>
+        <v>4.36</v>
       </c>
       <c r="M28" t="n">
-        <v>34.61</v>
+        <v>28.12</v>
       </c>
       <c r="N28" t="n">
-        <v>22235488458.26</v>
+        <v>4691700000</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>002617.SZ</t>
+          <t>300147.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>*ST香雪</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.44</v>
+        <v>7.34</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.0213</v>
+        <v>-19.9564</v>
       </c>
       <c r="F29" t="n">
-        <v>17.43</v>
+        <v>5.3</v>
       </c>
       <c r="G29" t="n">
-        <v>2939208489</v>
+        <v>272960431</v>
       </c>
       <c r="H29" t="n">
-        <v>494743324.49</v>
+        <v>95124530.02</v>
       </c>
       <c r="I29" t="n">
-        <v>304737168.6</v>
+        <v>25481717.24</v>
       </c>
       <c r="J29" t="n">
-        <v>799480493.09</v>
+        <v>120606247.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-190006155.89</v>
+        <v>-69642812.78</v>
       </c>
       <c r="L29" t="n">
-        <v>-6.46</v>
+        <v>-25.51</v>
       </c>
       <c r="M29" t="n">
-        <v>27.2</v>
+        <v>44.18</v>
       </c>
       <c r="N29" t="n">
-        <v>15847128093.28</v>
+        <v>4825072730.38</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>002808.SZ</t>
+          <t>300164.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>恒久退</t>
+          <t>通源石油</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.21</v>
+        <v>9.48</v>
       </c>
       <c r="E30" t="n">
-        <v>10.5263</v>
+        <v>6.9977</v>
       </c>
       <c r="F30" t="n">
-        <v>6.22</v>
+        <v>41.96</v>
       </c>
       <c r="G30" t="n">
-        <v>2382516</v>
+        <v>2235433928</v>
       </c>
       <c r="H30" t="n">
-        <v>1106274.8</v>
+        <v>329681795.45</v>
       </c>
       <c r="I30" t="n">
-        <v>1245040.8</v>
+        <v>151925365.38</v>
       </c>
       <c r="J30" t="n">
-        <v>2351315.6</v>
+        <v>481607160.83</v>
       </c>
       <c r="K30" t="n">
-        <v>138766</v>
+        <v>-177756430.07</v>
       </c>
       <c r="L30" t="n">
-        <v>5.82</v>
+        <v>-7.95</v>
       </c>
       <c r="M30" t="n">
-        <v>98.69</v>
+        <v>21.54</v>
       </c>
       <c r="N30" t="n">
-        <v>39240821.76</v>
+        <v>5528838175.44</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>002828.SZ</t>
+          <t>300214.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>贝肯能源</t>
+          <t>日科化学</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.48</v>
+        <v>12.3</v>
       </c>
       <c r="E31" t="n">
-        <v>10.0408</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>22.64</v>
+        <v>1.37</v>
       </c>
       <c r="G31" t="n">
-        <v>590259563</v>
+        <v>78228418</v>
       </c>
       <c r="H31" t="n">
-        <v>76469807.5</v>
+        <v>21720570</v>
       </c>
       <c r="I31" t="n">
-        <v>177180546.7</v>
+        <v>27199408.2</v>
       </c>
       <c r="J31" t="n">
-        <v>253650354.2</v>
+        <v>48919978.2</v>
       </c>
       <c r="K31" t="n">
-        <v>100710739.2</v>
+        <v>5478838.2</v>
       </c>
       <c r="L31" t="n">
-        <v>17.06</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>42.97</v>
+        <v>62.53</v>
       </c>
       <c r="N31" t="n">
-        <v>2709312848</v>
+        <v>5718302152.2</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>002829.SZ</t>
+          <t>300475.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>星网宇达</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19.5</v>
+        <v>216.8</v>
       </c>
       <c r="E32" t="n">
-        <v>9.9831</v>
+        <v>-20</v>
       </c>
       <c r="F32" t="n">
-        <v>10.21</v>
+        <v>12.75</v>
       </c>
       <c r="G32" t="n">
-        <v>344881724</v>
+        <v>13123767058</v>
       </c>
       <c r="H32" t="n">
-        <v>67632442.58</v>
+        <v>4191918497.01</v>
       </c>
       <c r="I32" t="n">
-        <v>85154940.8</v>
+        <v>1704736590.11</v>
       </c>
       <c r="J32" t="n">
-        <v>152787383.38</v>
+        <v>5896655087.12</v>
       </c>
       <c r="K32" t="n">
-        <v>17522498.22</v>
+        <v>-2487181906.9</v>
       </c>
       <c r="L32" t="n">
-        <v>5.08</v>
+        <v>-18.95</v>
       </c>
       <c r="M32" t="n">
-        <v>44.3</v>
+        <v>44.93</v>
       </c>
       <c r="N32" t="n">
-        <v>2848024218</v>
+        <v>97567754285.60001</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>002898.SZ</t>
+          <t>300522.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>赛隆退</t>
+          <t>世名科技</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.35</v>
+        <v>15.5</v>
       </c>
       <c r="E33" t="n">
-        <v>2.9412</v>
+        <v>-11.2765</v>
       </c>
       <c r="F33" t="n">
-        <v>5.28</v>
+        <v>14.15</v>
       </c>
       <c r="G33" t="n">
-        <v>1852989</v>
+        <v>2065794644</v>
       </c>
       <c r="H33" t="n">
-        <v>1012635</v>
+        <v>221055325.94</v>
       </c>
       <c r="I33" t="n">
-        <v>926020.4</v>
+        <v>312786070.53</v>
       </c>
       <c r="J33" t="n">
-        <v>1938655.4</v>
+        <v>533841396.47</v>
       </c>
       <c r="K33" t="n">
-        <v>-86614.60000000001</v>
+        <v>91730744.59</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.67</v>
+        <v>4.44</v>
       </c>
       <c r="M33" t="n">
-        <v>104.62</v>
+        <v>25.84</v>
       </c>
       <c r="N33" t="n">
-        <v>35441857.85</v>
+        <v>4078137125.5</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>002903.SZ</t>
+          <t>300534.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>33.36</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>-10.0081</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>16.11</v>
+        <v>17.51</v>
       </c>
       <c r="G34" t="n">
-        <v>607617546</v>
+        <v>461973284</v>
       </c>
       <c r="H34" t="n">
-        <v>119301169.08</v>
+        <v>59160397.5</v>
       </c>
       <c r="I34" t="n">
-        <v>138047059.4</v>
+        <v>76740977.5</v>
       </c>
       <c r="J34" t="n">
-        <v>257348228.48</v>
+        <v>135901375</v>
       </c>
       <c r="K34" t="n">
-        <v>18745890.32</v>
+        <v>17580580</v>
       </c>
       <c r="L34" t="n">
-        <v>3.09</v>
+        <v>3.81</v>
       </c>
       <c r="M34" t="n">
-        <v>42.35</v>
+        <v>29.42</v>
       </c>
       <c r="N34" t="n">
-        <v>3558366050.64</v>
+        <v>2718463392</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>002910.SZ</t>
+          <t>301092.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>庄园牧场</t>
+          <t>争光股份</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.64</v>
+        <v>61.28</v>
       </c>
       <c r="E35" t="n">
-        <v>-8.1174</v>
+        <v>11.4182</v>
       </c>
       <c r="F35" t="n">
-        <v>25.58</v>
+        <v>26.95</v>
       </c>
       <c r="G35" t="n">
-        <v>472649226</v>
+        <v>1763529092</v>
       </c>
       <c r="H35" t="n">
-        <v>61913215.36</v>
+        <v>293323047.86</v>
       </c>
       <c r="I35" t="n">
-        <v>122936073.7</v>
+        <v>224971577.52</v>
       </c>
       <c r="J35" t="n">
-        <v>184849289.06</v>
+        <v>518294625.38</v>
       </c>
       <c r="K35" t="n">
-        <v>61022858.34</v>
+        <v>-68351470.34</v>
       </c>
       <c r="L35" t="n">
-        <v>12.91</v>
+        <v>-3.88</v>
       </c>
       <c r="M35" t="n">
-        <v>39.11</v>
+        <v>29.39</v>
       </c>
       <c r="N35" t="n">
-        <v>1820099148</v>
+        <v>3734368515.52</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>003020.SZ</t>
+          <t>301307.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>立方制药</t>
+          <t>美利信</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.74</v>
+        <v>75.23</v>
       </c>
       <c r="E36" t="n">
-        <v>9.9765</v>
+        <v>-20.0021</v>
       </c>
       <c r="F36" t="n">
-        <v>10.58</v>
+        <v>16.03</v>
       </c>
       <c r="G36" t="n">
-        <v>587201869</v>
+        <v>1430403247</v>
       </c>
       <c r="H36" t="n">
-        <v>148550058.2</v>
+        <v>413073403.35</v>
       </c>
       <c r="I36" t="n">
-        <v>111839850.44</v>
+        <v>291027458.57</v>
       </c>
       <c r="J36" t="n">
-        <v>260389908.64</v>
+        <v>704100861.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-36710207.76</v>
+        <v>-122045944.78</v>
       </c>
       <c r="L36" t="n">
-        <v>-6.25</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>44.34</v>
+        <v>49.22</v>
       </c>
       <c r="N36" t="n">
-        <v>3158594298.7</v>
+        <v>8183620208.2</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>003043.SZ</t>
+          <t>301310.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>华亚智能</t>
+          <t>鑫宏业</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>94.05</v>
+        <v>68.84</v>
       </c>
       <c r="E37" t="n">
-        <v>-10</v>
+        <v>17.3943</v>
       </c>
       <c r="F37" t="n">
-        <v>12.21</v>
+        <v>39.08</v>
       </c>
       <c r="G37" t="n">
-        <v>1120382795</v>
+        <v>1621500851</v>
       </c>
       <c r="H37" t="n">
-        <v>233822411.15</v>
+        <v>408926629.28</v>
       </c>
       <c r="I37" t="n">
-        <v>253889660.89</v>
+        <v>371624938.31</v>
       </c>
       <c r="J37" t="n">
-        <v>487712072.04</v>
+        <v>780551567.59</v>
       </c>
       <c r="K37" t="n">
-        <v>20067249.74</v>
+        <v>-37301690.97</v>
       </c>
       <c r="L37" t="n">
-        <v>1.79</v>
+        <v>-2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>43.53</v>
+        <v>48.14</v>
       </c>
       <c r="N37" t="n">
-        <v>8779022574.299999</v>
+        <v>4198271008.16</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>113705.SH</t>
+          <t>301310.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>N豪26转</t>
+          <t>鑫宏业</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>131.072</v>
+        <v>68.84</v>
       </c>
       <c r="E38" t="n">
-        <v>31.072</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>17.3943</v>
+      </c>
+      <c r="F38" t="n">
+        <v>39.08</v>
+      </c>
       <c r="G38" t="n">
-        <v>354427020</v>
+        <v>2440012462</v>
       </c>
       <c r="H38" t="n">
-        <v>39783460</v>
+        <v>578822552.36</v>
       </c>
       <c r="I38" t="n">
-        <v>74541700</v>
+        <v>566673442.46</v>
       </c>
       <c r="J38" t="n">
-        <v>114325160</v>
+        <v>1145495994.82</v>
       </c>
       <c r="K38" t="n">
-        <v>34758240</v>
+        <v>-12149109.9</v>
       </c>
       <c r="L38" t="n">
-        <v>9.81</v>
+        <v>-0.5</v>
       </c>
       <c r="M38" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>46.95</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4198271008.16</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>113706.SH</t>
+          <t>301326.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>N金帝转</t>
+          <t>捷邦科技</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>157.3</v>
+        <v>119.98</v>
       </c>
       <c r="E39" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+        <v>-19.9973</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.57</v>
+      </c>
       <c r="G39" t="n">
-        <v>89926480</v>
+        <v>522144107</v>
       </c>
       <c r="H39" t="n">
-        <v>11417890</v>
+        <v>128042393.67</v>
       </c>
       <c r="I39" t="n">
-        <v>71754880</v>
+        <v>145884033.86</v>
       </c>
       <c r="J39" t="n">
-        <v>83172770</v>
+        <v>273926427.53</v>
       </c>
       <c r="K39" t="n">
-        <v>60336990</v>
+        <v>17841640.19</v>
       </c>
       <c r="L39" t="n">
-        <v>67.09999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="M39" t="n">
-        <v>92.48999999999999</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
+        <v>52.46</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8647548061.74</v>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>118053.SH</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>正帆转债</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>186.345</v>
+        <v>54.22</v>
       </c>
       <c r="E40" t="n">
-        <v>-18.8007</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>20.0089</v>
+      </c>
+      <c r="F40" t="n">
+        <v>54.44</v>
+      </c>
       <c r="G40" t="n">
-        <v>2512824870</v>
+        <v>907872413</v>
       </c>
       <c r="H40" t="n">
-        <v>493008410</v>
+        <v>80105668.3</v>
       </c>
       <c r="I40" t="n">
-        <v>491709330</v>
+        <v>110465449.98</v>
       </c>
       <c r="J40" t="n">
-        <v>984717740</v>
+        <v>190571118.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-1299080</v>
+        <v>30359781.68</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.05</v>
+        <v>3.34</v>
       </c>
       <c r="M40" t="n">
-        <v>39.19</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
+        <v>20.99</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1772909579.46</v>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>非上市首日,当日收盘价跌幅达15%的前五只可转债</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>118069.SH</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>爱科转债</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>188.76</v>
+        <v>54.22</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>20.0089</v>
+      </c>
+      <c r="F41" t="n">
+        <v>54.44</v>
+      </c>
       <c r="G41" t="n">
-        <v>31185040</v>
+        <v>1552690296</v>
       </c>
       <c r="H41" t="n">
-        <v>10772530</v>
+        <v>122203581.39</v>
       </c>
       <c r="I41" t="n">
-        <v>31113310</v>
+        <v>145423241.1</v>
       </c>
       <c r="J41" t="n">
-        <v>41885840</v>
+        <v>267626822.49</v>
       </c>
       <c r="K41" t="n">
-        <v>20340780</v>
+        <v>23219659.71</v>
       </c>
       <c r="L41" t="n">
-        <v>65.23</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>134.31</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
+        <v>17.24</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1772909579.46</v>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>非上市首日,当日收盘价涨幅达15%的前五只可转债</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>118070.SH</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>N南芯转</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>157.3</v>
+        <v>54.22</v>
       </c>
       <c r="E42" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+        <v>20.0089</v>
+      </c>
+      <c r="F42" t="n">
+        <v>54.44</v>
+      </c>
       <c r="G42" t="n">
-        <v>177397080</v>
+        <v>5360999244.46</v>
       </c>
       <c r="H42" t="n">
-        <v>39370620</v>
+        <v>5360999244.46</v>
       </c>
       <c r="I42" t="n">
-        <v>157835000</v>
+        <v>5360999244.46</v>
       </c>
       <c r="J42" t="n">
-        <v>197205620</v>
+        <v>10721998488.92</v>
       </c>
       <c r="K42" t="n">
-        <v>118464380</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>66.78</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>111.17</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1772909579.46</v>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
+          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>123273.SZ</t>
+          <t>301588.SZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>三江转债</t>
+          <t>美新科技</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>347</v>
+        <v>44.63</v>
       </c>
       <c r="E43" t="n">
-        <v>13.9659</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
+        <v>-19.484</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.78</v>
+      </c>
       <c r="G43" t="n">
-        <v>8115168566.39</v>
+        <v>445261729</v>
       </c>
       <c r="H43" t="n">
-        <v>8115168566.39</v>
+        <v>96980345.33</v>
       </c>
       <c r="I43" t="n">
-        <v>8115168566.38</v>
+        <v>124582681.08</v>
       </c>
       <c r="J43" t="n">
-        <v>16230337132.77</v>
+        <v>221563026.41</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01</v>
+        <v>27602335.75</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="M43" t="n">
-        <v>200</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>49.76</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3274020337.29</v>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>严重异常期间日收盘价格涨幅偏离值累计达到100%的可转债</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>123274.SZ</t>
+          <t>600151.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>维科转债</t>
+          <t>航天机电</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>157.3</v>
+        <v>10.14</v>
       </c>
       <c r="E44" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
+        <v>-10.0266</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.46</v>
+      </c>
       <c r="G44" t="n">
-        <v>36717703</v>
+        <v>509853885</v>
       </c>
       <c r="H44" t="n">
-        <v>6397365</v>
+        <v>96162999.84</v>
       </c>
       <c r="I44" t="n">
-        <v>32623483.1</v>
+        <v>30526557</v>
       </c>
       <c r="J44" t="n">
-        <v>39020848.1</v>
+        <v>126689556.84</v>
       </c>
       <c r="K44" t="n">
-        <v>26226118.1</v>
+        <v>-65636442.84</v>
       </c>
       <c r="L44" t="n">
-        <v>71.43000000000001</v>
+        <v>-12.87</v>
       </c>
       <c r="M44" t="n">
-        <v>106.27</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
+        <v>24.85</v>
+      </c>
+      <c r="N44" t="n">
+        <v>14543318190.18</v>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>上市首日可转债</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300065.SZ</t>
+          <t>600288.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>海兰信</t>
+          <t>大恒科技</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.79</v>
+        <v>16.64</v>
       </c>
       <c r="E45" t="n">
-        <v>20.0083</v>
+        <v>0.6046</v>
       </c>
       <c r="F45" t="n">
-        <v>18.8</v>
+        <v>23.26</v>
       </c>
       <c r="G45" t="n">
-        <v>3279324851</v>
+        <v>1707435727</v>
       </c>
       <c r="H45" t="n">
-        <v>103637817.97</v>
+        <v>365970456.82</v>
       </c>
       <c r="I45" t="n">
-        <v>536592434.97</v>
+        <v>265416236.65</v>
       </c>
       <c r="J45" t="n">
-        <v>640230252.9400001</v>
+        <v>631386693.47</v>
       </c>
       <c r="K45" t="n">
-        <v>432954617</v>
+        <v>-100554220.17</v>
       </c>
       <c r="L45" t="n">
-        <v>13.2</v>
+        <v>-5.89</v>
       </c>
       <c r="M45" t="n">
-        <v>19.52</v>
+        <v>36.98</v>
       </c>
       <c r="N45" t="n">
-        <v>18912009698.68</v>
+        <v>7268352000</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>300069.SZ</t>
+          <t>600293.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>金利华电</t>
+          <t>三峡新材</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>36.86</v>
+        <v>2.51</v>
       </c>
       <c r="E46" t="n">
-        <v>19.987</v>
+        <v>-10.0358</v>
       </c>
       <c r="F46" t="n">
-        <v>13.26</v>
+        <v>7.01</v>
       </c>
       <c r="G46" t="n">
-        <v>541282273</v>
+        <v>210379398</v>
       </c>
       <c r="H46" t="n">
-        <v>83218602</v>
+        <v>34407743.23</v>
       </c>
       <c r="I46" t="n">
-        <v>140353565.2</v>
+        <v>27953675</v>
       </c>
       <c r="J46" t="n">
-        <v>223572167.2</v>
+        <v>62361418.23</v>
       </c>
       <c r="K46" t="n">
-        <v>57134963.2</v>
+        <v>-6454068.23</v>
       </c>
       <c r="L46" t="n">
-        <v>10.56</v>
+        <v>-3.07</v>
       </c>
       <c r="M46" t="n">
-        <v>41.3</v>
+        <v>29.64</v>
       </c>
       <c r="N46" t="n">
-        <v>4312620000</v>
+        <v>2911964065.46</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>300071.SZ</t>
+          <t>600353.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>福石控股</t>
+          <t>旭光电子</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.91</v>
+        <v>38.19</v>
       </c>
       <c r="E47" t="n">
-        <v>19.1748</v>
+        <v>-9.5024</v>
       </c>
       <c r="F47" t="n">
-        <v>33.86</v>
+        <v>8.51</v>
       </c>
       <c r="G47" t="n">
-        <v>1493332631</v>
+        <v>2884805850</v>
       </c>
       <c r="H47" t="n">
-        <v>255534565</v>
+        <v>729199483.16</v>
       </c>
       <c r="I47" t="n">
-        <v>187483718.8</v>
+        <v>510899962.73</v>
       </c>
       <c r="J47" t="n">
-        <v>443018283.8</v>
+        <v>1240099445.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-68050846.2</v>
+        <v>-218299520.43</v>
       </c>
       <c r="L47" t="n">
-        <v>-4.56</v>
+        <v>-7.57</v>
       </c>
       <c r="M47" t="n">
-        <v>29.67</v>
+        <v>42.99</v>
       </c>
       <c r="N47" t="n">
-        <v>4641672752.06</v>
+        <v>31652298162.21</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>300071.SZ</t>
+          <t>600360.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>福石控股</t>
+          <t>华微电子</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.91</v>
+        <v>17.02</v>
       </c>
       <c r="E48" t="n">
-        <v>19.1748</v>
+        <v>1.3699</v>
       </c>
       <c r="F48" t="n">
-        <v>33.86</v>
+        <v>27.25</v>
       </c>
       <c r="G48" t="n">
-        <v>2386366267</v>
+        <v>4535298130</v>
       </c>
       <c r="H48" t="n">
-        <v>255865874</v>
+        <v>630782699.9400001</v>
       </c>
       <c r="I48" t="n">
-        <v>351771031.92</v>
+        <v>578921013.84</v>
       </c>
       <c r="J48" t="n">
-        <v>607636905.92</v>
+        <v>1209703713.78</v>
       </c>
       <c r="K48" t="n">
-        <v>95905157.92</v>
+        <v>-51861686.1</v>
       </c>
       <c r="L48" t="n">
-        <v>4.02</v>
+        <v>-1.14</v>
       </c>
       <c r="M48" t="n">
-        <v>25.46</v>
+        <v>26.67</v>
       </c>
       <c r="N48" t="n">
-        <v>4641672752.06</v>
+        <v>16344226074.08</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>300164.SZ</t>
+          <t>600379.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>通源石油</t>
+          <t>宝光股份</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8.859999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.4858</v>
+        <v>-8.322100000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>31.9</v>
+        <v>9.58</v>
       </c>
       <c r="G49" t="n">
-        <v>1624578892</v>
+        <v>447877226</v>
       </c>
       <c r="H49" t="n">
-        <v>210856140.98</v>
+        <v>74812112.58</v>
       </c>
       <c r="I49" t="n">
-        <v>220279203.84</v>
+        <v>65448139.25</v>
       </c>
       <c r="J49" t="n">
-        <v>431135344.82</v>
+        <v>140260251.83</v>
       </c>
       <c r="K49" t="n">
-        <v>9423062.859999999</v>
+        <v>-9363973.33</v>
       </c>
       <c r="L49" t="n">
-        <v>0.58</v>
+        <v>-2.09</v>
       </c>
       <c r="M49" t="n">
-        <v>26.54</v>
+        <v>31.32</v>
       </c>
       <c r="N49" t="n">
-        <v>5167247493.08</v>
+        <v>4474231192.2</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300255.SZ</t>
+          <t>600428.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>常山药业</t>
+          <t>中远海特</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>26.34</v>
+        <v>9.82</v>
       </c>
       <c r="E50" t="n">
-        <v>20</v>
+        <v>9.2325</v>
       </c>
       <c r="F50" t="n">
-        <v>7.66</v>
+        <v>8.91</v>
       </c>
       <c r="G50" t="n">
-        <v>1766605471</v>
+        <v>2507092031</v>
       </c>
       <c r="H50" t="n">
-        <v>129571817.41</v>
+        <v>568128128.75</v>
       </c>
       <c r="I50" t="n">
-        <v>377844752.95</v>
+        <v>509408905.3</v>
       </c>
       <c r="J50" t="n">
-        <v>507416570.36</v>
+        <v>1077537034.05</v>
       </c>
       <c r="K50" t="n">
-        <v>248272935.54</v>
+        <v>-58719223.45</v>
       </c>
       <c r="L50" t="n">
-        <v>14.05</v>
+        <v>-2.34</v>
       </c>
       <c r="M50" t="n">
-        <v>28.72</v>
+        <v>42.98</v>
       </c>
       <c r="N50" t="n">
-        <v>24170199776.52</v>
+        <v>24012704425.06</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300390.SZ</t>
+          <t>600470.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>天华新能</t>
+          <t>六国化工</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>65.7</v>
+        <v>6.26</v>
       </c>
       <c r="E51" t="n">
-        <v>-4.9204</v>
+        <v>-10.0575</v>
       </c>
       <c r="F51" t="n">
-        <v>11.12</v>
+        <v>10.53</v>
       </c>
       <c r="G51" t="n">
-        <v>18671370919</v>
+        <v>350897228</v>
       </c>
       <c r="H51" t="n">
-        <v>1632569745.38</v>
+        <v>30264642.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1559844361.48</v>
+        <v>26698197</v>
       </c>
       <c r="J51" t="n">
-        <v>3192414106.86</v>
+        <v>56962839.44</v>
       </c>
       <c r="K51" t="n">
-        <v>-72725383.90000001</v>
+        <v>-3566445.44</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.39</v>
+        <v>-1.02</v>
       </c>
       <c r="M51" t="n">
-        <v>17.1</v>
+        <v>16.23</v>
       </c>
       <c r="N51" t="n">
-        <v>44167980071.7</v>
+        <v>3265216000</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到30%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300786.SZ</t>
+          <t>600491.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>国林科技</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>23.9</v>
+        <v>1.23</v>
       </c>
       <c r="E52" t="n">
-        <v>19.9799</v>
+        <v>9.821400000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>7.07</v>
+        <v>4.12</v>
       </c>
       <c r="G52" t="n">
-        <v>237383545</v>
+        <v>78267130</v>
       </c>
       <c r="H52" t="n">
-        <v>43517221</v>
+        <v>10836724.23</v>
       </c>
       <c r="I52" t="n">
-        <v>64026647</v>
+        <v>7823784</v>
       </c>
       <c r="J52" t="n">
-        <v>107543868</v>
+        <v>18660508.23</v>
       </c>
       <c r="K52" t="n">
-        <v>20509426</v>
+        <v>-3012940.23</v>
       </c>
       <c r="L52" t="n">
-        <v>8.640000000000001</v>
+        <v>-3.85</v>
       </c>
       <c r="M52" t="n">
-        <v>45.3</v>
+        <v>23.84</v>
       </c>
       <c r="N52" t="n">
-        <v>3498821834.1</v>
+        <v>1881602284.65</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>301117.SZ</t>
+          <t>600513.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>佳缘科技</t>
+          <t>联环药业</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>20.29</v>
+        <v>17.04</v>
       </c>
       <c r="E53" t="n">
-        <v>19.9882</v>
+        <v>10.0065</v>
       </c>
       <c r="F53" t="n">
-        <v>27.15</v>
+        <v>14.86</v>
       </c>
       <c r="G53" t="n">
-        <v>570694109</v>
+        <v>931298287</v>
       </c>
       <c r="H53" t="n">
-        <v>58586907.74</v>
+        <v>215075789.98</v>
       </c>
       <c r="I53" t="n">
-        <v>122285183.08</v>
+        <v>225085858.95</v>
       </c>
       <c r="J53" t="n">
-        <v>180872090.82</v>
+        <v>440161648.93</v>
       </c>
       <c r="K53" t="n">
-        <v>63698275.34</v>
+        <v>10010068.97</v>
       </c>
       <c r="L53" t="n">
-        <v>11.16</v>
+        <v>1.07</v>
       </c>
       <c r="M53" t="n">
-        <v>31.69</v>
+        <v>47.26</v>
       </c>
       <c r="N53" t="n">
-        <v>2350697645.65</v>
+        <v>4864174840.8</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>301516.SZ</t>
+          <t>600629.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中远通</t>
+          <t>华建集团</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>20.65</v>
+        <v>14.03</v>
       </c>
       <c r="E54" t="n">
-        <v>7.9456</v>
+        <v>10.0392</v>
       </c>
       <c r="F54" t="n">
-        <v>33.87</v>
+        <v>4.42</v>
       </c>
       <c r="G54" t="n">
-        <v>492685223</v>
+        <v>678286926</v>
       </c>
       <c r="H54" t="n">
-        <v>55951714.56</v>
+        <v>123933690.66</v>
       </c>
       <c r="I54" t="n">
-        <v>84822579.77</v>
+        <v>110607855.78</v>
       </c>
       <c r="J54" t="n">
-        <v>140774294.33</v>
+        <v>234541546.44</v>
       </c>
       <c r="K54" t="n">
-        <v>28870865.21</v>
+        <v>-13325834.88</v>
       </c>
       <c r="L54" t="n">
-        <v>5.86</v>
+        <v>-1.96</v>
       </c>
       <c r="M54" t="n">
-        <v>28.57</v>
+        <v>34.58</v>
       </c>
       <c r="N54" t="n">
-        <v>1449122815.35</v>
+        <v>16131762438.34</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>600629.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>华建集团</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>45.18</v>
+        <v>14.03</v>
       </c>
       <c r="E55" t="n">
-        <v>8.6058</v>
+        <v>10.0392</v>
       </c>
       <c r="F55" t="n">
-        <v>46.06</v>
+        <v>4.42</v>
       </c>
       <c r="G55" t="n">
-        <v>644817883</v>
+        <v>1017789740</v>
       </c>
       <c r="H55" t="n">
-        <v>74164688.59999999</v>
+        <v>178041320.26</v>
       </c>
       <c r="I55" t="n">
-        <v>75033362.47</v>
+        <v>186366141.83</v>
       </c>
       <c r="J55" t="n">
-        <v>149198051.07</v>
+        <v>364407462.09</v>
       </c>
       <c r="K55" t="n">
-        <v>868673.87</v>
+        <v>8324821.57</v>
       </c>
       <c r="L55" t="n">
-        <v>0.13</v>
+        <v>0.82</v>
       </c>
       <c r="M55" t="n">
-        <v>23.14</v>
+        <v>35.8</v>
       </c>
       <c r="N55" t="n">
-        <v>1477315654.74</v>
+        <v>16131762438.34</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>600664.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>托伦斯</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>216.7</v>
+        <v>3.71</v>
       </c>
       <c r="E56" t="n">
-        <v>858.8496</v>
+        <v>10.089</v>
       </c>
       <c r="F56" t="n">
-        <v>81.34999999999999</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>5943898887</v>
+        <v>737706217</v>
       </c>
       <c r="H56" t="n">
-        <v>122073905.8</v>
+        <v>171376111.88</v>
       </c>
       <c r="I56" t="n">
-        <v>773096095.33</v>
+        <v>106176966.74</v>
       </c>
       <c r="J56" t="n">
-        <v>895170001.13</v>
+        <v>277553078.62</v>
       </c>
       <c r="K56" t="n">
-        <v>651022189.53</v>
+        <v>-65199145.14</v>
       </c>
       <c r="L56" t="n">
-        <v>10.95</v>
+        <v>-8.84</v>
       </c>
       <c r="M56" t="n">
-        <v>15.06</v>
+        <v>37.62</v>
       </c>
       <c r="N56" t="n">
-        <v>6681158529.1</v>
+        <v>9343671639.959999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>无价格涨跌幅限制的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>600129.SH</t>
+          <t>600664.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>太极集团</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16.58</v>
+        <v>3.71</v>
       </c>
       <c r="E57" t="n">
-        <v>7.7323</v>
+        <v>10.089</v>
       </c>
       <c r="F57" t="n">
-        <v>9.58</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>2017659333</v>
+        <v>1074580683</v>
       </c>
       <c r="H57" t="n">
-        <v>151744879.14</v>
+        <v>191067605.88</v>
       </c>
       <c r="I57" t="n">
-        <v>165046914.8</v>
+        <v>235165113.74</v>
       </c>
       <c r="J57" t="n">
-        <v>316791793.94</v>
+        <v>426232719.62</v>
       </c>
       <c r="K57" t="n">
-        <v>13302035.66</v>
+        <v>44097507.86</v>
       </c>
       <c r="L57" t="n">
-        <v>0.66</v>
+        <v>4.1</v>
       </c>
       <c r="M57" t="n">
-        <v>15.7</v>
+        <v>39.67</v>
       </c>
       <c r="N57" t="n">
-        <v>9142513507.299999</v>
+        <v>9343671639.959999</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4871,51 +4895,51 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>600172.SH</t>
+          <t>600756.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>浪潮软件</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>14.85</v>
       </c>
       <c r="E58" t="n">
-        <v>-9.0909</v>
+        <v>6.7577</v>
       </c>
       <c r="F58" t="n">
-        <v>25.34</v>
+        <v>11.09</v>
       </c>
       <c r="G58" t="n">
-        <v>5935782022</v>
+        <v>512155334</v>
       </c>
       <c r="H58" t="n">
-        <v>894318751.79</v>
+        <v>43361744.45</v>
       </c>
       <c r="I58" t="n">
-        <v>476778432.75</v>
+        <v>57756296.19</v>
       </c>
       <c r="J58" t="n">
-        <v>1371097184.54</v>
+        <v>101118040.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-417540319.04</v>
+        <v>14394551.74</v>
       </c>
       <c r="L58" t="n">
-        <v>-7.03</v>
+        <v>2.81</v>
       </c>
       <c r="M58" t="n">
-        <v>23.1</v>
+        <v>19.74</v>
       </c>
       <c r="N58" t="n">
-        <v>21696347750</v>
+        <v>4812866482.05</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4926,436 +4950,436 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>600192.SH</t>
+          <t>600990.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>长城电工</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.66</v>
+        <v>17.33</v>
       </c>
       <c r="E59" t="n">
-        <v>10.0826</v>
+        <v>-10.0208</v>
       </c>
       <c r="F59" t="n">
-        <v>2.63</v>
+        <v>3.54</v>
       </c>
       <c r="G59" t="n">
-        <v>74609381</v>
+        <v>169643443</v>
       </c>
       <c r="H59" t="n">
-        <v>7691061</v>
+        <v>24634784.06</v>
       </c>
       <c r="I59" t="n">
-        <v>28170348</v>
+        <v>23879921.84</v>
       </c>
       <c r="J59" t="n">
-        <v>35861409</v>
+        <v>48514705.9</v>
       </c>
       <c r="K59" t="n">
-        <v>20479287</v>
+        <v>-754862.22</v>
       </c>
       <c r="L59" t="n">
-        <v>27.45</v>
+        <v>-0.44</v>
       </c>
       <c r="M59" t="n">
-        <v>48.07</v>
+        <v>28.6</v>
       </c>
       <c r="N59" t="n">
-        <v>2942041680</v>
+        <v>4661990021.68</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>600288.SH</t>
+          <t>600992.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>大恒科技</t>
+          <t>贵绳股份</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16.54</v>
+        <v>11.72</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4303</v>
+        <v>10.0469</v>
       </c>
       <c r="F60" t="n">
-        <v>24.61</v>
+        <v>2.22</v>
       </c>
       <c r="G60" t="n">
-        <v>1834283719</v>
+        <v>63778201</v>
       </c>
       <c r="H60" t="n">
-        <v>381021806.85</v>
+        <v>7137480</v>
       </c>
       <c r="I60" t="n">
-        <v>219518990.83</v>
+        <v>53644784</v>
       </c>
       <c r="J60" t="n">
-        <v>600540797.6799999</v>
+        <v>60782264</v>
       </c>
       <c r="K60" t="n">
-        <v>-161502816.02</v>
+        <v>46507304</v>
       </c>
       <c r="L60" t="n">
-        <v>-8.800000000000001</v>
+        <v>72.92</v>
       </c>
       <c r="M60" t="n">
-        <v>32.74</v>
+        <v>95.3</v>
       </c>
       <c r="N60" t="n">
-        <v>7224672000</v>
+        <v>2872454800</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>600360.SH</t>
+          <t>601608.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>华微电子</t>
+          <t>中信重工</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16.79</v>
+        <v>5.54</v>
       </c>
       <c r="E61" t="n">
-        <v>5.0031</v>
+        <v>9.9206</v>
       </c>
       <c r="F61" t="n">
-        <v>29.05</v>
+        <v>4.47</v>
       </c>
       <c r="G61" t="n">
-        <v>4791002850</v>
+        <v>1500031017</v>
       </c>
       <c r="H61" t="n">
-        <v>337621357.5</v>
+        <v>175847554.08</v>
       </c>
       <c r="I61" t="n">
-        <v>699699370.29</v>
+        <v>199609595.21</v>
       </c>
       <c r="J61" t="n">
-        <v>1037320727.79</v>
+        <v>375457149.29</v>
       </c>
       <c r="K61" t="n">
-        <v>362078012.79</v>
+        <v>23762041.13</v>
       </c>
       <c r="L61" t="n">
-        <v>7.56</v>
+        <v>1.58</v>
       </c>
       <c r="M61" t="n">
-        <v>21.65</v>
+        <v>25.03</v>
       </c>
       <c r="N61" t="n">
-        <v>16123358154.16</v>
+        <v>25370726040.98</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>600378.SH</t>
+          <t>603006.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>昊华科技</t>
+          <t>联明股份</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>60.58</v>
+        <v>11.22</v>
       </c>
       <c r="E62" t="n">
-        <v>-8.4894</v>
+        <v>-10.0241</v>
       </c>
       <c r="F62" t="n">
-        <v>8.91</v>
+        <v>2.43</v>
       </c>
       <c r="G62" t="n">
-        <v>6221047413</v>
+        <v>72135807</v>
       </c>
       <c r="H62" t="n">
-        <v>892408211.38</v>
+        <v>22918597</v>
       </c>
       <c r="I62" t="n">
-        <v>1008178005.87</v>
+        <v>11800755</v>
       </c>
       <c r="J62" t="n">
-        <v>1900586217.25</v>
+        <v>34719352</v>
       </c>
       <c r="K62" t="n">
-        <v>115769794.49</v>
+        <v>-11117842</v>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>-15.41</v>
       </c>
       <c r="M62" t="n">
-        <v>30.55</v>
+        <v>48.13</v>
       </c>
       <c r="N62" t="n">
-        <v>64976009690.54</v>
+        <v>2852732685</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>600664.SH</t>
+          <t>603137.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3.37</v>
+        <v>29.43</v>
       </c>
       <c r="E63" t="n">
-        <v>10.1307</v>
+        <v>10.0187</v>
       </c>
       <c r="F63" t="n">
-        <v>3.97</v>
+        <v>15.17</v>
       </c>
       <c r="G63" t="n">
-        <v>336874466</v>
+        <v>2176296806</v>
       </c>
       <c r="H63" t="n">
-        <v>38957566.4</v>
+        <v>188480267.8</v>
       </c>
       <c r="I63" t="n">
-        <v>165439029</v>
+        <v>162033858.53</v>
       </c>
       <c r="J63" t="n">
-        <v>204396595.4</v>
+        <v>350514126.33</v>
       </c>
       <c r="K63" t="n">
-        <v>126481462.6</v>
+        <v>-26446409.27</v>
       </c>
       <c r="L63" t="n">
-        <v>37.55</v>
+        <v>-1.22</v>
       </c>
       <c r="M63" t="n">
-        <v>60.67</v>
+        <v>16.11</v>
       </c>
       <c r="N63" t="n">
-        <v>8487378282.12</v>
+        <v>5383728019.62</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>600821.SH</t>
+          <t>603137.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>恒尚节能</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6.11</v>
+        <v>29.43</v>
       </c>
       <c r="E64" t="n">
-        <v>10.0901</v>
+        <v>10.0187</v>
       </c>
       <c r="F64" t="n">
-        <v>4.76</v>
+        <v>15.17</v>
       </c>
       <c r="G64" t="n">
-        <v>555091511</v>
+        <v>3298802100</v>
       </c>
       <c r="H64" t="n">
-        <v>47503889.12</v>
+        <v>3298802200</v>
       </c>
       <c r="I64" t="n">
-        <v>214123355.86</v>
+        <v>3298802100</v>
       </c>
       <c r="J64" t="n">
-        <v>261627244.98</v>
+        <v>6597604300</v>
       </c>
       <c r="K64" t="n">
-        <v>166619466.74</v>
+        <v>-100</v>
       </c>
       <c r="L64" t="n">
-        <v>30.02</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>47.13</v>
+        <v>200</v>
       </c>
       <c r="N64" t="n">
-        <v>12020355462.83</v>
+        <v>5383728019.62</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>连续10个交易日内4次出现同正向异常波动的证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>600992.SH</t>
+          <t>603223.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>贵绳股份</t>
+          <t>恒通股份</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.65</v>
+        <v>12.55</v>
       </c>
       <c r="E65" t="n">
-        <v>10.0207</v>
+        <v>-8.527699999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>7.03</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>223946213</v>
+        <v>835277564</v>
       </c>
       <c r="H65" t="n">
-        <v>24622735</v>
+        <v>193191838.85</v>
       </c>
       <c r="I65" t="n">
-        <v>56340783</v>
+        <v>202567680.04</v>
       </c>
       <c r="J65" t="n">
-        <v>80963518</v>
+        <v>395759518.89</v>
       </c>
       <c r="K65" t="n">
-        <v>31718048</v>
+        <v>9375841.189999999</v>
       </c>
       <c r="L65" t="n">
-        <v>14.16</v>
+        <v>1.12</v>
       </c>
       <c r="M65" t="n">
-        <v>36.15</v>
+        <v>47.38</v>
       </c>
       <c r="N65" t="n">
-        <v>2610208500</v>
+        <v>8858068522.15</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>601608.SH</t>
+          <t>603313.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>中信重工</t>
+          <t>梦百合</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.04</v>
+        <v>7.99</v>
       </c>
       <c r="E66" t="n">
-        <v>10.0437</v>
+        <v>10.0551</v>
       </c>
       <c r="F66" t="n">
-        <v>1.7</v>
+        <v>12.99</v>
       </c>
       <c r="G66" t="n">
-        <v>376969926</v>
+        <v>564258154</v>
       </c>
       <c r="H66" t="n">
-        <v>64321836.62</v>
+        <v>98705885.59999999</v>
       </c>
       <c r="I66" t="n">
-        <v>76453556.56999999</v>
+        <v>66654107.28</v>
       </c>
       <c r="J66" t="n">
-        <v>140775393.19</v>
+        <v>165359992.88</v>
       </c>
       <c r="K66" t="n">
-        <v>12131719.95</v>
+        <v>-32051778.32</v>
       </c>
       <c r="L66" t="n">
-        <v>3.22</v>
+        <v>-5.68</v>
       </c>
       <c r="M66" t="n">
-        <v>37.34</v>
+        <v>29.31</v>
       </c>
       <c r="N66" t="n">
-        <v>23080949322.48</v>
+        <v>4558989211.15</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5366,722 +5390,716 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>603137.SH</t>
+          <t>603318.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>恒尚节能</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>26.75</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>6.1508</v>
+        <v>10.0386</v>
       </c>
       <c r="F67" t="n">
-        <v>21.16</v>
+        <v>2.23</v>
       </c>
       <c r="G67" t="n">
-        <v>2516541500</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2516541400</v>
-      </c>
+        <v>87558849</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>2516541500</v>
+        <v>65798243.55</v>
       </c>
       <c r="J67" t="n">
-        <v>5033082900</v>
+        <v>65798243.55</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>65798243.55</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>200</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>4893466684.5</v>
+        <v>3925056400.2</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续10个交易日内收盘价格涨幅偏离值累计达到100%的证券</t>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>603183.SH</t>
+          <t>603318.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>建研院</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4.44</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>4.4706</v>
+        <v>10.0386</v>
       </c>
       <c r="F68" t="n">
-        <v>16.73</v>
+        <v>2.23</v>
       </c>
       <c r="G68" t="n">
-        <v>934293644</v>
-      </c>
-      <c r="H68" t="n">
-        <v>136210835.22</v>
-      </c>
+        <v>87558849</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>177094324.55</v>
+        <v>65798243.55</v>
       </c>
       <c r="J68" t="n">
-        <v>313305159.77</v>
+        <v>65798243.55</v>
       </c>
       <c r="K68" t="n">
-        <v>40883489.33</v>
+        <v>65798243.55</v>
       </c>
       <c r="L68" t="n">
-        <v>4.38</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="M68" t="n">
-        <v>33.53</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N68" t="n">
-        <v>2207360434.44</v>
+        <v>3925056400.2</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>603203.SH</t>
+          <t>603318.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>快克智能</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>59.49</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-9.959099999999999</v>
+        <v>10.0386</v>
       </c>
       <c r="F69" t="n">
-        <v>8.43</v>
+        <v>2.23</v>
       </c>
       <c r="G69" t="n">
-        <v>1764861960</v>
-      </c>
-      <c r="H69" t="n">
-        <v>220660249.04</v>
-      </c>
+        <v>87558849</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>116848012.51</v>
+        <v>65798243.55</v>
       </c>
       <c r="J69" t="n">
-        <v>337508261.55</v>
+        <v>65798243.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-103812236.53</v>
+        <v>65798243.55</v>
       </c>
       <c r="L69" t="n">
-        <v>-5.88</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="M69" t="n">
-        <v>19.12</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="N69" t="n">
-        <v>19268770130.37</v>
+        <v>3925056400.2</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>单只标的证券的当日融资买入数量达到当日该证券总交易量的50％以上</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>603459.SH</t>
+          <t>603318.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>红板科技</t>
+          <t>水发燃气</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>91.05</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.9318</v>
+        <v>10.0386</v>
       </c>
       <c r="F70" t="n">
-        <v>22.68</v>
+        <v>2.23</v>
       </c>
       <c r="G70" t="n">
-        <v>1701985101</v>
+        <v>87558849</v>
       </c>
       <c r="H70" t="n">
-        <v>374788764.41</v>
+        <v>8113095</v>
       </c>
       <c r="I70" t="n">
-        <v>330515485.34</v>
+        <v>66224888.55</v>
       </c>
       <c r="J70" t="n">
-        <v>705304249.75</v>
+        <v>74337983.55</v>
       </c>
       <c r="K70" t="n">
-        <v>-44273279.07</v>
+        <v>58111793.55</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.6</v>
+        <v>66.37</v>
       </c>
       <c r="M70" t="n">
-        <v>41.44</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>7197671670.9</v>
+        <v>3925056400.2</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>603578.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>三星新材</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.37</v>
+        <v>33</v>
       </c>
       <c r="E71" t="n">
-        <v>10.0412</v>
+        <v>6.8653</v>
       </c>
       <c r="F71" t="n">
-        <v>2.86</v>
+        <v>30.13</v>
       </c>
       <c r="G71" t="n">
-        <v>67180351</v>
+        <v>3235533493</v>
       </c>
       <c r="H71" t="n">
-        <v>13674118.96</v>
+        <v>526665709.88</v>
       </c>
       <c r="I71" t="n">
-        <v>29019924</v>
+        <v>213363666.17</v>
       </c>
       <c r="J71" t="n">
-        <v>42694042.96</v>
+        <v>740029376.05</v>
       </c>
       <c r="K71" t="n">
-        <v>15345805.04</v>
+        <v>-313302043.71</v>
       </c>
       <c r="L71" t="n">
-        <v>22.84</v>
+        <v>-9.68</v>
       </c>
       <c r="M71" t="n">
-        <v>63.55</v>
+        <v>22.87</v>
       </c>
       <c r="N71" t="n">
-        <v>2411373517.84</v>
+        <v>11118358383</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>603687.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>大胜达</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15.18</v>
+        <v>33</v>
       </c>
       <c r="E72" t="n">
-        <v>-9.803900000000001</v>
+        <v>6.8653</v>
       </c>
       <c r="F72" t="n">
-        <v>7.93</v>
+        <v>30.13</v>
       </c>
       <c r="G72" t="n">
-        <v>692387016</v>
+        <v>5370192227</v>
       </c>
       <c r="H72" t="n">
-        <v>106498935.3</v>
+        <v>700900320.87</v>
       </c>
       <c r="I72" t="n">
-        <v>63014307</v>
+        <v>450080775.04</v>
       </c>
       <c r="J72" t="n">
-        <v>169513242.3</v>
+        <v>1150981095.91</v>
       </c>
       <c r="K72" t="n">
-        <v>-43484628.3</v>
+        <v>-250819545.83</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.28</v>
+        <v>-4.67</v>
       </c>
       <c r="M72" t="n">
-        <v>24.48</v>
+        <v>21.43</v>
       </c>
       <c r="N72" t="n">
-        <v>8349483695.52</v>
+        <v>11118358383</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>603898.SH</t>
+          <t>603949.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>好莱客</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.27</v>
+        <v>16.99</v>
       </c>
       <c r="E73" t="n">
-        <v>10.0144</v>
+        <v>-10.0106</v>
       </c>
       <c r="F73" t="n">
-        <v>1.89</v>
+        <v>7.24</v>
       </c>
       <c r="G73" t="n">
-        <v>190625489</v>
+        <v>280830792</v>
       </c>
       <c r="H73" t="n">
-        <v>39711759</v>
+        <v>51346191.76</v>
       </c>
       <c r="I73" t="n">
-        <v>63073201</v>
+        <v>32609450</v>
       </c>
       <c r="J73" t="n">
-        <v>102784960</v>
+        <v>83955641.76000001</v>
       </c>
       <c r="K73" t="n">
-        <v>23361442</v>
+        <v>-18736741.76</v>
       </c>
       <c r="L73" t="n">
-        <v>12.26</v>
+        <v>-6.67</v>
       </c>
       <c r="M73" t="n">
-        <v>53.92</v>
+        <v>29.9</v>
       </c>
       <c r="N73" t="n">
-        <v>4584504190.14</v>
+        <v>3571387605.26</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>603906.SH</t>
+          <t>603950.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>龙蟠科技</t>
+          <t>长源东谷</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22.16</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>-9.991899999999999</v>
+        <v>-10</v>
       </c>
       <c r="F74" t="n">
-        <v>11.71</v>
+        <v>2.74</v>
       </c>
       <c r="G74" t="n">
-        <v>1524730618</v>
+        <v>2571728628</v>
       </c>
       <c r="H74" t="n">
-        <v>82487191.34</v>
+        <v>589811766.5700001</v>
       </c>
       <c r="I74" t="n">
-        <v>172571200.4</v>
+        <v>507283210.7</v>
       </c>
       <c r="J74" t="n">
-        <v>255058391.74</v>
+        <v>1097094977.27</v>
       </c>
       <c r="K74" t="n">
-        <v>90084009.06</v>
+        <v>-82528555.87</v>
       </c>
       <c r="L74" t="n">
-        <v>5.91</v>
+        <v>-3.21</v>
       </c>
       <c r="M74" t="n">
-        <v>16.73</v>
+        <v>42.66</v>
       </c>
       <c r="N74" t="n">
-        <v>12476002506.48</v>
+        <v>20840957280</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>605090.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>九丰能源</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>18.8</v>
+        <v>41.78</v>
       </c>
       <c r="E75" t="n">
-        <v>4.4444</v>
+        <v>10.0053</v>
       </c>
       <c r="F75" t="n">
-        <v>24.33</v>
+        <v>7.99</v>
       </c>
       <c r="G75" t="n">
-        <v>1516056639</v>
+        <v>3670777322</v>
       </c>
       <c r="H75" t="n">
-        <v>96726747.05</v>
+        <v>694109796.12</v>
       </c>
       <c r="I75" t="n">
-        <v>93510522.02</v>
+        <v>501654631.54</v>
       </c>
       <c r="J75" t="n">
-        <v>190237269.07</v>
+        <v>1195764427.66</v>
       </c>
       <c r="K75" t="n">
-        <v>-3216225.03</v>
+        <v>-192455164.58</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.21</v>
+        <v>-5.24</v>
       </c>
       <c r="M75" t="n">
-        <v>12.55</v>
+        <v>32.58</v>
       </c>
       <c r="N75" t="n">
-        <v>6405235200</v>
+        <v>29435136723.04</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>688072.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>拓荆科技</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>18.8</v>
+        <v>845</v>
       </c>
       <c r="E76" t="n">
-        <v>4.4444</v>
+        <v>1.5625</v>
       </c>
       <c r="F76" t="n">
-        <v>24.33</v>
+        <v>7.95</v>
       </c>
       <c r="G76" t="n">
-        <v>3470791080</v>
+        <v>19426827300</v>
       </c>
       <c r="H76" t="n">
-        <v>267560026.1</v>
+        <v>3744725492.07</v>
       </c>
       <c r="I76" t="n">
-        <v>198250261.67</v>
+        <v>5352706751.5</v>
       </c>
       <c r="J76" t="n">
-        <v>465810287.77</v>
+        <v>9097432243.57</v>
       </c>
       <c r="K76" t="n">
-        <v>-69309764.43000001</v>
+        <v>1607981259.43</v>
       </c>
       <c r="L76" t="n">
-        <v>-2</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>13.42</v>
+        <v>46.83</v>
       </c>
       <c r="N76" t="n">
-        <v>6405235200</v>
+        <v>238875595140</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>603931.SH</t>
+          <t>688101.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>格林达</t>
+          <t>三达膜</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>57.98</v>
+        <v>18.78</v>
       </c>
       <c r="E77" t="n">
-        <v>4.2806</v>
+        <v>9.760400000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>11.24</v>
+        <v>7.34</v>
       </c>
       <c r="G77" t="n">
-        <v>1251567652</v>
+        <v>773231100</v>
       </c>
       <c r="H77" t="n">
-        <v>244023722</v>
+        <v>224573257.39</v>
       </c>
       <c r="I77" t="n">
-        <v>321245418.06</v>
+        <v>128064206.25</v>
       </c>
       <c r="J77" t="n">
-        <v>565269140.0599999</v>
+        <v>352637463.64</v>
       </c>
       <c r="K77" t="n">
-        <v>77221696.06</v>
+        <v>-96509051.14</v>
       </c>
       <c r="L77" t="n">
-        <v>6.17</v>
+        <v>-12.48</v>
       </c>
       <c r="M77" t="n">
-        <v>45.16</v>
+        <v>45.61</v>
       </c>
       <c r="N77" t="n">
-        <v>11570394872.4</v>
+        <v>6235186599.48</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>603937.SH</t>
+          <t>688121.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>丽岛新材</t>
+          <t>*ST卓然</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.18</v>
+        <v>2.75</v>
       </c>
       <c r="E78" t="n">
-        <v>-9.4003</v>
+        <v>-12.1406</v>
       </c>
       <c r="F78" t="n">
-        <v>10.11</v>
+        <v>10.53</v>
       </c>
       <c r="G78" t="n">
-        <v>237002991</v>
+        <v>271021900</v>
       </c>
       <c r="H78" t="n">
-        <v>21325935.8</v>
+        <v>26291209.26</v>
       </c>
       <c r="I78" t="n">
-        <v>15159529.88</v>
+        <v>17976058.6</v>
       </c>
       <c r="J78" t="n">
-        <v>36485465.68</v>
+        <v>44267267.86</v>
       </c>
       <c r="K78" t="n">
-        <v>-6166405.92</v>
+        <v>-8315150.66</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.6</v>
+        <v>-3.07</v>
       </c>
       <c r="M78" t="n">
-        <v>15.39</v>
+        <v>16.33</v>
       </c>
       <c r="N78" t="n">
-        <v>2335412459.38</v>
+        <v>557333334.25</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格跌幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>603986.SH</t>
+          <t>688143.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>长盈通</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>612</v>
+        <v>125.28</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.7605</v>
+        <v>-20</v>
       </c>
       <c r="F79" t="n">
-        <v>13.28</v>
+        <v>12.98</v>
       </c>
       <c r="G79" t="n">
-        <v>59381239201</v>
+        <v>2188904000</v>
       </c>
       <c r="H79" t="n">
-        <v>9178558971.559999</v>
+        <v>619188048.78</v>
       </c>
       <c r="I79" t="n">
-        <v>5037007172.44</v>
+        <v>420760009.16</v>
       </c>
       <c r="J79" t="n">
-        <v>14215566144</v>
+        <v>1039948057.94</v>
       </c>
       <c r="K79" t="n">
-        <v>-4141551799.12</v>
+        <v>-198428039.62</v>
       </c>
       <c r="L79" t="n">
-        <v>-6.97</v>
+        <v>-9.07</v>
       </c>
       <c r="M79" t="n">
-        <v>23.94</v>
+        <v>47.51</v>
       </c>
       <c r="N79" t="n">
-        <v>409117063608</v>
+        <v>15331068089.28</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6095,147 +6113,147 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>293.99</v>
+        <v>244.5</v>
       </c>
       <c r="E80" t="n">
-        <v>-19.1447</v>
+        <v>-16.8339</v>
       </c>
       <c r="F80" t="n">
-        <v>13.71</v>
+        <v>15.28</v>
       </c>
       <c r="G80" t="n">
-        <v>6477248000</v>
+        <v>5858644400</v>
       </c>
       <c r="H80" t="n">
-        <v>382093123.92</v>
+        <v>547610206.5599999</v>
       </c>
       <c r="I80" t="n">
-        <v>325553393.4</v>
+        <v>222518683.51</v>
       </c>
       <c r="J80" t="n">
-        <v>707646517.3200001</v>
+        <v>770128890.0700001</v>
       </c>
       <c r="K80" t="n">
-        <v>-56539730.52</v>
+        <v>-325091523.05</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.87</v>
+        <v>-5.55</v>
       </c>
       <c r="M80" t="n">
-        <v>10.93</v>
+        <v>13.15</v>
       </c>
       <c r="N80" t="n">
-        <v>42619977839.58</v>
+        <v>35445370869</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到30%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>688238.SH</t>
+          <t>688319.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>和元生物</t>
+          <t>欧林生物</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.71</v>
+        <v>35.7</v>
       </c>
       <c r="E81" t="n">
-        <v>16.6957</v>
+        <v>-19.5584</v>
       </c>
       <c r="F81" t="n">
-        <v>10.84</v>
+        <v>7.93</v>
       </c>
       <c r="G81" t="n">
-        <v>466462600</v>
+        <v>1251523500</v>
       </c>
       <c r="H81" t="n">
-        <v>44070976.12</v>
+        <v>307233382.05</v>
       </c>
       <c r="I81" t="n">
-        <v>92272560.7</v>
+        <v>371299726.31</v>
       </c>
       <c r="J81" t="n">
-        <v>136343536.82</v>
+        <v>678533108.36</v>
       </c>
       <c r="K81" t="n">
-        <v>48201584.58</v>
+        <v>64066344.26</v>
       </c>
       <c r="L81" t="n">
-        <v>10.33</v>
+        <v>5.12</v>
       </c>
       <c r="M81" t="n">
-        <v>29.23</v>
+        <v>54.22</v>
       </c>
       <c r="N81" t="n">
-        <v>4302087647</v>
+        <v>14473112010</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>688249.SH</t>
+          <t>688450.SH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>晶合集成</t>
+          <t>光格科技</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>54.12</v>
+        <v>43.26</v>
       </c>
       <c r="E82" t="n">
-        <v>-17.0066</v>
+        <v>-19.9926</v>
       </c>
       <c r="F82" t="n">
-        <v>5.43</v>
+        <v>12.29</v>
       </c>
       <c r="G82" t="n">
-        <v>6385492700</v>
+        <v>280356900</v>
       </c>
       <c r="H82" t="n">
-        <v>1316898933.53</v>
+        <v>69550694.47</v>
       </c>
       <c r="I82" t="n">
-        <v>1476370210.92</v>
+        <v>51241987.52</v>
       </c>
       <c r="J82" t="n">
-        <v>2793269144.45</v>
+        <v>120792681.99</v>
       </c>
       <c r="K82" t="n">
-        <v>159471277.39</v>
+        <v>-18308706.95</v>
       </c>
       <c r="L82" t="n">
-        <v>2.5</v>
+        <v>-6.53</v>
       </c>
       <c r="M82" t="n">
-        <v>43.74</v>
+        <v>43.09</v>
       </c>
       <c r="N82" t="n">
-        <v>108650862641.64</v>
+        <v>2116740870.72</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -6246,106 +6264,106 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>688328.SH</t>
+          <t>688479.SH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>深科达</t>
+          <t>友车科技</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>118.23</v>
+        <v>29.96</v>
       </c>
       <c r="E83" t="n">
-        <v>15.889</v>
+        <v>-18.5205</v>
       </c>
       <c r="F83" t="n">
-        <v>21.56</v>
+        <v>9.33</v>
       </c>
       <c r="G83" t="n">
-        <v>2451972400</v>
+        <v>263505200</v>
       </c>
       <c r="H83" t="n">
-        <v>269209148.88</v>
+        <v>87170877.90000001</v>
       </c>
       <c r="I83" t="n">
-        <v>557355961.34</v>
+        <v>60662741.47</v>
       </c>
       <c r="J83" t="n">
-        <v>826565110.22</v>
+        <v>147833619.37</v>
       </c>
       <c r="K83" t="n">
-        <v>288146812.46</v>
+        <v>-26508136.43</v>
       </c>
       <c r="L83" t="n">
-        <v>11.75</v>
+        <v>-10.06</v>
       </c>
       <c r="M83" t="n">
-        <v>33.71</v>
+        <v>56.1</v>
       </c>
       <c r="N83" t="n">
-        <v>11167567757.85</v>
+        <v>2592269825.6</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>688328.SH</t>
+          <t>688584.SH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>深科达</t>
+          <t>上海合晶</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>118.23</v>
+        <v>46.25</v>
       </c>
       <c r="E84" t="n">
-        <v>15.889</v>
+        <v>6.616</v>
       </c>
       <c r="F84" t="n">
-        <v>21.56</v>
+        <v>12.27</v>
       </c>
       <c r="G84" t="n">
-        <v>3594163300</v>
+        <v>5577920900</v>
       </c>
       <c r="H84" t="n">
-        <v>348432284.99</v>
+        <v>840383692.88</v>
       </c>
       <c r="I84" t="n">
-        <v>798357147.41</v>
+        <v>815600879.99</v>
       </c>
       <c r="J84" t="n">
-        <v>1146789432.4</v>
+        <v>1655984572.87</v>
       </c>
       <c r="K84" t="n">
-        <v>449924862.42</v>
+        <v>-24782812.89</v>
       </c>
       <c r="L84" t="n">
-        <v>12.52</v>
+        <v>-0.44</v>
       </c>
       <c r="M84" t="n">
-        <v>31.91</v>
+        <v>29.69</v>
       </c>
       <c r="N84" t="n">
-        <v>11167567757.85</v>
+        <v>15877635637.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -6356,825 +6374,440 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>688392.SH</t>
+          <t>688710.SH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>骄成超声</t>
+          <t>益诺思</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>203.89</v>
+        <v>84.02</v>
       </c>
       <c r="E85" t="n">
-        <v>-15.6782</v>
+        <v>7.8978</v>
       </c>
       <c r="F85" t="n">
-        <v>6.57</v>
+        <v>9.66</v>
       </c>
       <c r="G85" t="n">
-        <v>1732468500</v>
+        <v>1210955000</v>
       </c>
       <c r="H85" t="n">
-        <v>370553796.79</v>
+        <v>308034076.26</v>
       </c>
       <c r="I85" t="n">
-        <v>416953656.58</v>
+        <v>227872560.65</v>
       </c>
       <c r="J85" t="n">
-        <v>787507453.37</v>
+        <v>535906636.91</v>
       </c>
       <c r="K85" t="n">
-        <v>46399859.79</v>
+        <v>-80161515.61</v>
       </c>
       <c r="L85" t="n">
-        <v>2.68</v>
+        <v>-6.62</v>
       </c>
       <c r="M85" t="n">
-        <v>45.46</v>
+        <v>44.25</v>
       </c>
       <c r="N85" t="n">
-        <v>23596874770.4</v>
+        <v>7620106855.28</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>688523.SH</t>
+          <t>920081.BJ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>航天环宇</t>
+          <t>欧伦电气</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>61.18</v>
+        <v>40.03</v>
       </c>
       <c r="E86" t="n">
-        <v>20.0078</v>
+        <v>-14.866</v>
       </c>
       <c r="F86" t="n">
-        <v>3.99</v>
+        <v>44.47</v>
       </c>
       <c r="G86" t="n">
-        <v>929854500</v>
+        <v>314360300</v>
       </c>
       <c r="H86" t="n">
-        <v>90782193.89</v>
+        <v>33385753.07</v>
       </c>
       <c r="I86" t="n">
-        <v>178657450.04</v>
+        <v>29155258.34</v>
       </c>
       <c r="J86" t="n">
-        <v>269439643.93</v>
+        <v>62541011.41</v>
       </c>
       <c r="K86" t="n">
-        <v>87875256.15000001</v>
+        <v>-4230494.73</v>
       </c>
       <c r="L86" t="n">
-        <v>9.449999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="M86" t="n">
-        <v>28.98</v>
+        <v>19.89</v>
       </c>
       <c r="N86" t="n">
-        <v>24892918400</v>
+        <v>684513000</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>688549.SH</t>
+          <t>920088.BJ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>中巨芯</t>
+          <t>科力股份</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>29.33</v>
+        <v>40.9</v>
       </c>
       <c r="E87" t="n">
-        <v>-17.1001</v>
+        <v>3.7018</v>
       </c>
       <c r="F87" t="n">
-        <v>22.22</v>
+        <v>25.41</v>
       </c>
       <c r="G87" t="n">
-        <v>4211699600</v>
+        <v>345585500</v>
       </c>
       <c r="H87" t="n">
-        <v>378171929.86</v>
+        <v>77720573.59999999</v>
       </c>
       <c r="I87" t="n">
-        <v>347277419.49</v>
+        <v>31448440.31</v>
       </c>
       <c r="J87" t="n">
-        <v>725449349.35</v>
+        <v>109169013.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-30894510.37</v>
+        <v>-46272133.29</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.73</v>
+        <v>-13.39</v>
       </c>
       <c r="M87" t="n">
-        <v>17.22</v>
+        <v>31.59</v>
       </c>
       <c r="N87" t="n">
-        <v>17284726270</v>
+        <v>1331958807</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>688596.SH</t>
+          <t>920136.BJ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>正帆科技</t>
+          <t>永励精密</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>68.03</v>
+        <v>21.78</v>
       </c>
       <c r="E88" t="n">
-        <v>-15.3118</v>
+        <v>-14.6886</v>
       </c>
       <c r="F88" t="n">
-        <v>14.38</v>
+        <v>38</v>
       </c>
       <c r="G88" t="n">
-        <v>3142666300</v>
+        <v>181698800</v>
       </c>
       <c r="H88" t="n">
-        <v>491825320.36</v>
+        <v>16126019.35</v>
       </c>
       <c r="I88" t="n">
-        <v>564489481.1</v>
+        <v>20964712.15</v>
       </c>
       <c r="J88" t="n">
-        <v>1056314801.46</v>
+        <v>37090731.5</v>
       </c>
       <c r="K88" t="n">
-        <v>72664160.73999999</v>
+        <v>4838692.8</v>
       </c>
       <c r="L88" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="M88" t="n">
-        <v>33.61</v>
+        <v>20.41</v>
       </c>
       <c r="N88" t="n">
-        <v>20009794449.57</v>
+        <v>457380000</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>688710.SH</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>益诺思</t>
+          <t>吉和昌</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>77.87</v>
+        <v>40.62</v>
       </c>
       <c r="E89" t="n">
-        <v>20.0031</v>
+        <v>2.8615</v>
       </c>
       <c r="F89" t="n">
-        <v>7.56</v>
+        <v>34.53</v>
       </c>
       <c r="G89" t="n">
-        <v>503467100</v>
+        <v>340305100</v>
       </c>
       <c r="H89" t="n">
-        <v>150105517.65</v>
+        <v>22010408.3</v>
       </c>
       <c r="I89" t="n">
-        <v>161570879.17</v>
+        <v>59544839.47</v>
       </c>
       <c r="J89" t="n">
-        <v>311676396.82</v>
+        <v>81555247.77</v>
       </c>
       <c r="K89" t="n">
-        <v>11465361.52</v>
+        <v>37534431.17</v>
       </c>
       <c r="L89" t="n">
-        <v>2.28</v>
+        <v>11.03</v>
       </c>
       <c r="M89" t="n">
-        <v>61.91</v>
+        <v>23.97</v>
       </c>
       <c r="N89" t="n">
-        <v>7062338976.68</v>
+        <v>1023624000</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>688722.SH</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>同益中</t>
+          <t>云创退</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>18.31</v>
+        <v>0.72</v>
       </c>
       <c r="E90" t="n">
-        <v>19.9869</v>
+        <v>28.5714</v>
       </c>
       <c r="F90" t="n">
-        <v>9.220000000000001</v>
+        <v>18.05</v>
       </c>
       <c r="G90" t="n">
-        <v>360849600</v>
+        <v>9992900</v>
       </c>
       <c r="H90" t="n">
-        <v>57964613.17</v>
+        <v>1921173.86</v>
       </c>
       <c r="I90" t="n">
-        <v>73458555.97</v>
+        <v>2753061.54</v>
       </c>
       <c r="J90" t="n">
-        <v>131423169.14</v>
+        <v>4674235.4</v>
       </c>
       <c r="K90" t="n">
-        <v>15493942.8</v>
+        <v>831887.6800000001</v>
       </c>
       <c r="L90" t="n">
-        <v>4.29</v>
+        <v>8.32</v>
       </c>
       <c r="M90" t="n">
-        <v>36.42</v>
+        <v>46.78</v>
       </c>
       <c r="N90" t="n">
-        <v>4103366212</v>
+        <v>58392630</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>688797.SH</t>
+          <t>920367.BJ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>臻宝科技</t>
+          <t>新赣江</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>445.25</v>
+        <v>26.44</v>
       </c>
       <c r="E91" t="n">
-        <v>-13.5638</v>
+        <v>8.139099999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>31.46</v>
+        <v>23.72</v>
       </c>
       <c r="G91" t="n">
-        <v>4587798000</v>
+        <v>258057500</v>
       </c>
       <c r="H91" t="n">
-        <v>656554419.41</v>
+        <v>28468769.32</v>
       </c>
       <c r="I91" t="n">
-        <v>446038362.04</v>
+        <v>22106038.86</v>
       </c>
       <c r="J91" t="n">
-        <v>1102592781.45</v>
+        <v>50574808.18</v>
       </c>
       <c r="K91" t="n">
-        <v>-210516057.37</v>
+        <v>-6362730.46</v>
       </c>
       <c r="L91" t="n">
-        <v>-4.59</v>
+        <v>-2.47</v>
       </c>
       <c r="M91" t="n">
-        <v>24.03</v>
+        <v>19.6</v>
       </c>
       <c r="N91" t="n">
-        <v>12998048784.5</v>
+        <v>1110283762.32</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到30%的前五只证券</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>920136.BJ</t>
+          <t>920943.BJ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>永励精密</t>
+          <t>优机股份</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>25.53</v>
+        <v>18.78</v>
       </c>
       <c r="E92" t="n">
-        <v>-24.9118</v>
+        <v>18.7105</v>
       </c>
       <c r="F92" t="n">
-        <v>58.05</v>
+        <v>18.32</v>
       </c>
       <c r="G92" t="n">
-        <v>325073700</v>
+        <v>219533500</v>
       </c>
       <c r="H92" t="n">
-        <v>26519045.16</v>
+        <v>23751627.33</v>
       </c>
       <c r="I92" t="n">
-        <v>20667530.02</v>
+        <v>20601015.37</v>
       </c>
       <c r="J92" t="n">
-        <v>47186575.18</v>
+        <v>44352642.7</v>
       </c>
       <c r="K92" t="n">
-        <v>-5851515.14</v>
+        <v>-3150611.96</v>
       </c>
       <c r="L92" t="n">
-        <v>-1.8</v>
+        <v>-1.44</v>
       </c>
       <c r="M92" t="n">
-        <v>14.52</v>
+        <v>20.2</v>
       </c>
       <c r="N92" t="n">
-        <v>536130000</v>
+        <v>972951103.74</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>当日收盘价跌幅达到-20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>920193.BJ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>吉和昌</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-2.8775</v>
-      </c>
-      <c r="F93" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G93" t="n">
-        <v>398713400</v>
-      </c>
-      <c r="H93" t="n">
-        <v>37054306.99</v>
-      </c>
-      <c r="I93" t="n">
-        <v>35924832.75</v>
-      </c>
-      <c r="J93" t="n">
-        <v>72979139.73999999</v>
-      </c>
-      <c r="K93" t="n">
-        <v>-1129474.24</v>
-      </c>
-      <c r="L93" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="M93" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N93" t="n">
-        <v>995148000</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>920211.BJ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>新睿电子</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>139.49</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1.8175</v>
-      </c>
-      <c r="F94" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="G94" t="n">
-        <v>228732600</v>
-      </c>
-      <c r="H94" t="n">
-        <v>47141092.98</v>
-      </c>
-      <c r="I94" t="n">
-        <v>23527812.71</v>
-      </c>
-      <c r="J94" t="n">
-        <v>70668905.69</v>
-      </c>
-      <c r="K94" t="n">
-        <v>-23613280.27</v>
-      </c>
-      <c r="L94" t="n">
-        <v>-10.32</v>
-      </c>
-      <c r="M94" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="N94" t="n">
-        <v>803462400</v>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>920267.BJ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>鑫汇科</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="E95" t="n">
-        <v>29.9427</v>
-      </c>
-      <c r="F95" t="n">
-        <v>28.91</v>
-      </c>
-      <c r="G95" t="n">
-        <v>137787200</v>
-      </c>
-      <c r="H95" t="n">
-        <v>49755674.18</v>
-      </c>
-      <c r="I95" t="n">
-        <v>55616147.37</v>
-      </c>
-      <c r="J95" t="n">
-        <v>105371821.55</v>
-      </c>
-      <c r="K95" t="n">
-        <v>5860473.19</v>
-      </c>
-      <c r="L95" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="M95" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="N95" t="n">
-        <v>492991650.72</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>当日换手率达到20%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>920305.BJ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>云创退</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-18.8406</v>
-      </c>
-      <c r="F96" t="n">
-        <v>19.13</v>
-      </c>
-      <c r="G96" t="n">
-        <v>8948000</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1742314.45</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1928315.92</v>
-      </c>
-      <c r="J96" t="n">
-        <v>3670630.37</v>
-      </c>
-      <c r="K96" t="n">
-        <v>186001.47</v>
-      </c>
-      <c r="L96" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M96" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="N96" t="n">
-        <v>45416490</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>退市整理期</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>920576.BJ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>天力复合</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="E97" t="n">
-        <v>15.5713</v>
-      </c>
-      <c r="F97" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="G97" t="n">
-        <v>482174100</v>
-      </c>
-      <c r="H97" t="n">
-        <v>56820227.06</v>
-      </c>
-      <c r="I97" t="n">
-        <v>58047028.43</v>
-      </c>
-      <c r="J97" t="n">
-        <v>114867255.49</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1226801.37</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M97" t="n">
-        <v>23.82</v>
-      </c>
-      <c r="N97" t="n">
-        <v>6677162532.6</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>920885.BJ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>星辰科技</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="E98" t="n">
-        <v>19.4421</v>
-      </c>
-      <c r="F98" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="G98" t="n">
-        <v>139453200</v>
-      </c>
-      <c r="H98" t="n">
-        <v>20641634.83</v>
-      </c>
-      <c r="I98" t="n">
-        <v>17985166.39</v>
-      </c>
-      <c r="J98" t="n">
-        <v>38626801.22</v>
-      </c>
-      <c r="K98" t="n">
-        <v>-2656468.44</v>
-      </c>
-      <c r="L98" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="M98" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1250550159.48</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260710</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>920943.BJ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>优机股份</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>15.82</v>
-      </c>
-      <c r="E99" t="n">
-        <v>29.9918</v>
-      </c>
-      <c r="F99" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="G99" t="n">
-        <v>48775200</v>
-      </c>
-      <c r="H99" t="n">
-        <v>7945516.92</v>
-      </c>
-      <c r="I99" t="n">
-        <v>18483624.89</v>
-      </c>
-      <c r="J99" t="n">
-        <v>26429141.81</v>
-      </c>
-      <c r="K99" t="n">
-        <v>10538107.97</v>
-      </c>
-      <c r="L99" t="n">
-        <v>21.61</v>
-      </c>
-      <c r="M99" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="N99" t="n">
-        <v>819599918.0599999</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>当日收盘价涨幅达到20%的前5只股票</t>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="turnover_10d" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_gainers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_losers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_list" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +427,52 @@
           <t>trade_date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>stock_count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>up_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>down_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flat_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_amount_yi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>20260714</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5524</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27194.94</v>
       </c>
     </row>
   </sheetData>
@@ -491,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3913.794</v>
+        <v>3967.1262</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.06</v>
+        <v>1.36</v>
       </c>
       <c r="F2" t="n">
-        <v>13348.72</v>
+        <v>12717.97</v>
       </c>
     </row>
     <row r="3">
@@ -517,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14522.8547</v>
+        <v>14924.8678</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.48</v>
+        <v>2.77</v>
       </c>
       <c r="F3" t="n">
-        <v>9044.6</v>
+        <v>9202.530000000001</v>
       </c>
     </row>
     <row r="4">
@@ -543,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3723.5166</v>
+        <v>3851.1372</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.1</v>
+        <v>3.43</v>
       </c>
       <c r="F4" t="n">
-        <v>3355.87</v>
+        <v>3412.97</v>
       </c>
     </row>
     <row r="5">
@@ -569,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4695.383</v>
+        <v>4796.502</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.79</v>
+        <v>2.15</v>
       </c>
       <c r="F5" t="n">
-        <v>9079.450000000001</v>
+        <v>9240.969999999999</v>
       </c>
     </row>
     <row r="6">
@@ -595,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1994.3192</v>
+        <v>2009.7296</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.42</v>
+        <v>0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>2148.51</v>
+        <v>2020.6</v>
       </c>
     </row>
     <row r="7">
@@ -621,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7787.8529</v>
+        <v>7925.1232</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.01</v>
+        <v>1.76</v>
       </c>
       <c r="F7" t="n">
-        <v>5737.88</v>
+        <v>5192.31</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +799,5418 @@
           <t>20260714</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>27194.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>920821.BJ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="I2" t="n">
+        <v>29.9687</v>
+      </c>
+      <c r="J2" t="n">
+        <v>92069.92999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>177006.68184</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.1667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>207198.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17903.01983</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>920088.BJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24.2054</v>
+      </c>
+      <c r="J4" t="n">
+        <v>110434.94</v>
+      </c>
+      <c r="K4" t="n">
+        <v>522160.51892</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23.5102</v>
+      </c>
+      <c r="J5" t="n">
+        <v>56312.49</v>
+      </c>
+      <c r="K5" t="n">
+        <v>164884.70932</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300532.SZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.0658</v>
+      </c>
+      <c r="J6" t="n">
+        <v>561237.29</v>
+      </c>
+      <c r="K6" t="n">
+        <v>402196.53407</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300164.SZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20.0422</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2564703.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2730225.89725</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300566.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.0144</v>
+      </c>
+      <c r="J8" t="n">
+        <v>333036.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1050917.20078</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300937.SZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.0103</v>
+      </c>
+      <c r="J9" t="n">
+        <v>109275.33</v>
+      </c>
+      <c r="K9" t="n">
+        <v>240011.78912</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688216.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20.0058</v>
+      </c>
+      <c r="J10" t="n">
+        <v>158147.32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>627800.8689999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688192.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="D11" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="G11" t="n">
+        <v>46.94</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20.0043</v>
+      </c>
+      <c r="J11" t="n">
+        <v>85845.25999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>436508.638</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pre_close</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pct_chg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300444.SZ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>232084</v>
+      </c>
+      <c r="K2" t="n">
+        <v>199970.849</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301295.SZ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-19.857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>67858.92999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>292607.05366</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301583.SZ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>210</v>
+      </c>
+      <c r="D4" t="n">
+        <v>213</v>
+      </c>
+      <c r="E4" t="n">
+        <v>163.13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>179.03</v>
+      </c>
+      <c r="G4" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-42.77</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-19.2831</v>
+      </c>
+      <c r="J4" t="n">
+        <v>180087.51</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3288638.56159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300065.SZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17.7847</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1313199.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2898291.18071</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>920943.BJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-14.59</v>
+      </c>
+      <c r="J6" t="n">
+        <v>70664.00999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>113318.23355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>688523.SH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-13.9447</v>
+      </c>
+      <c r="J7" t="n">
+        <v>139566.43</v>
+      </c>
+      <c r="K7" t="n">
+        <v>707305.777</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>301005.SZ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>93</v>
+      </c>
+      <c r="D8" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-11.8272</v>
+      </c>
+      <c r="J8" t="n">
+        <v>169533.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1449971.99829</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>688629.SH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>217</v>
+      </c>
+      <c r="D9" t="n">
+        <v>217.78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>168</v>
+      </c>
+      <c r="F9" t="n">
+        <v>180.35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-24.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-11.8093</v>
+      </c>
+      <c r="J9" t="n">
+        <v>422495.68</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7694476.296</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>688375.SH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>98</v>
+      </c>
+      <c r="E10" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-10.9262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>87119.25999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>775971.752</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>688387.SH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-10.914</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1092211.56</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1822038.533</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ts_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>l_sell</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>l_buy</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>l_amount</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>net_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>amount_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>float_values</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>000078.SZ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ST海王</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.0962</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1259692238</v>
+      </c>
+      <c r="H2" t="n">
+        <v>96461838.54000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>106373577</v>
+      </c>
+      <c r="J2" t="n">
+        <v>202835415.54</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9911738.460000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6011743962.16</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>000636.SZ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风华高科</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.998100000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7331329500</v>
+      </c>
+      <c r="H3" t="n">
+        <v>621165698.25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1195024051.76</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1816189750.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>573858353.51</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="N3" t="n">
+        <v>68738148924.50999</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>000989.SZ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>九芝堂</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.4566</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1817725006</v>
+      </c>
+      <c r="H4" t="n">
+        <v>146074889.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>123637625.47</v>
+      </c>
+      <c r="J4" t="n">
+        <v>269712514.93</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-22437263.99</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6573636040.91</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>001270.SZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>铖昌科技</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>134.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-10.002</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1205557641</v>
+      </c>
+      <c r="H5" t="n">
+        <v>206661543.62</v>
+      </c>
+      <c r="I5" t="n">
+        <v>110384446.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>317045990.02</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-96277097.22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>27586998583.2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>001365.SZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>天海电子</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9.1556</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="G6" t="n">
+        <v>599848889</v>
+      </c>
+      <c r="H6" t="n">
+        <v>52467240.61</v>
+      </c>
+      <c r="I6" t="n">
+        <v>95232709.84</v>
+      </c>
+      <c r="J6" t="n">
+        <v>147699950.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>42765469.23</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2350830808.48</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>001388.SZ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>信通电子</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.0034</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>224531180</v>
+      </c>
+      <c r="H7" t="n">
+        <v>43458165.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>51254896.01</v>
+      </c>
+      <c r="J7" t="n">
+        <v>94713061.81</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7796730.21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2742463845.44</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>001399.SZ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>惠科股份</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-9.991</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2291303850</v>
+      </c>
+      <c r="H8" t="n">
+        <v>307002366.41</v>
+      </c>
+      <c r="I8" t="n">
+        <v>320918133.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>627920500.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13915767.28</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12917001930</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>002079.SZ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>苏州固锝</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-9.9923</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="G9" t="n">
+        <v>822759237</v>
+      </c>
+      <c r="H9" t="n">
+        <v>148199132</v>
+      </c>
+      <c r="I9" t="n">
+        <v>152153664.04</v>
+      </c>
+      <c r="J9" t="n">
+        <v>300352796.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3954532.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9423045585.1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>002185.SZ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>华天科技</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.4235</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21083239147</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4627263020.37</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2065492176.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6692755197.32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2561770843.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-12.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>85325697119.75999</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>002245.SZ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>蔚蓝锂芯</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.0053</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3489028234</v>
+      </c>
+      <c r="H11" t="n">
+        <v>568051503.92</v>
+      </c>
+      <c r="I11" t="n">
+        <v>766731492.26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1334782996.18</v>
+      </c>
+      <c r="K11" t="n">
+        <v>198679988.34</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="M11" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="N11" t="n">
+        <v>33561868944.62</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>002379.SZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>宏桥控股</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2775542286</v>
+      </c>
+      <c r="H12" t="n">
+        <v>550327285.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>517483526.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1067810812.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-32843759.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M12" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="N12" t="n">
+        <v>19875176939.97</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002384.SZ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>260.37</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23856271061</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2871849510.32</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4207142451.43</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7078991961.75</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1335292941.11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="N13" t="n">
+        <v>360956587017.51</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002396.SZ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.2763</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5185131546</v>
+      </c>
+      <c r="H14" t="n">
+        <v>734403473.65</v>
+      </c>
+      <c r="I14" t="n">
+        <v>758571649.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1492975123.03</v>
+      </c>
+      <c r="K14" t="n">
+        <v>24168175.73</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="N14" t="n">
+        <v>21677220333.72</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002457.SZ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>青龙管业</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-10.0141</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G15" t="n">
+        <v>509794382</v>
+      </c>
+      <c r="H15" t="n">
+        <v>107774656</v>
+      </c>
+      <c r="I15" t="n">
+        <v>42455402.98</v>
+      </c>
+      <c r="J15" t="n">
+        <v>150230058.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-65319253.02</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-12.81</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4252529653.24</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002463.SZ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>137.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.0032</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12553796133</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1148714567.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2385480544.79</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3534195112.04</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1236765977.54</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>263675001945.18</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002490.SZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>山东墨龙</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.5642</v>
+      </c>
+      <c r="F17" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2576349949</v>
+      </c>
+      <c r="H17" t="n">
+        <v>222189120.96</v>
+      </c>
+      <c r="I17" t="n">
+        <v>237813914.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>460003035.56</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15624793.64</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4902584100</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002549.SZ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>凯美特气</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-10.0112</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1144304860</v>
+      </c>
+      <c r="H18" t="n">
+        <v>196972058.96</v>
+      </c>
+      <c r="I18" t="n">
+        <v>71639382.34999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>268611441.31</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-125332676.61</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>11140064773.34</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002552.SZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>宝鼎科技</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7.1626</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1636777745</v>
+      </c>
+      <c r="H19" t="n">
+        <v>341214157</v>
+      </c>
+      <c r="I19" t="n">
+        <v>348783881</v>
+      </c>
+      <c r="J19" t="n">
+        <v>689998038</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7569724</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M19" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21446891419.8</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002581.SZ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>*ST未名</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.2342</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G20" t="n">
+        <v>133430911</v>
+      </c>
+      <c r="H20" t="n">
+        <v>33465903.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>23892295.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>57358199.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9573608</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1531022235.02</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002617.SZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>露笑科技</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-8.684200000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6016180166</v>
+      </c>
+      <c r="H21" t="n">
+        <v>823904915.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>767747173.33</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1591652088.53</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-56157741.87</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="M21" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13030695375.28</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002636.SZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>金安国纪</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10.0023</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4708658892</v>
+      </c>
+      <c r="H22" t="n">
+        <v>873580157.72</v>
+      </c>
+      <c r="I22" t="n">
+        <v>932541806.79</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1806121964.51</v>
+      </c>
+      <c r="K22" t="n">
+        <v>58961649.07</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="N22" t="n">
+        <v>69302499098.56</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002731.SZ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>*ST萃华</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10.1167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6077488</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2914837</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2207316</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5122153</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-707521</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-11.64</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="N23" t="n">
+        <v>530506284</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002842.SZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>翔鹭钨业</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.8518</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2406574471</v>
+      </c>
+      <c r="H24" t="n">
+        <v>504023113.75</v>
+      </c>
+      <c r="I24" t="n">
+        <v>234733176.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>738756290.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-269289937.49</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="M24" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10263315984.57</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002898.SZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>赛隆退</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5.2632</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3446883</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1598044.67</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1220207.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2818252.27</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-377837.07</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="M25" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="N25" t="n">
+        <v>40504980.4</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>退市整理期</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9.9796</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>262810915</v>
+      </c>
+      <c r="H26" t="n">
+        <v>36842609.53</v>
+      </c>
+      <c r="I26" t="n">
+        <v>66879651.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>103722260.63</v>
+      </c>
+      <c r="K26" t="n">
+        <v>30037041.57</v>
+      </c>
+      <c r="L26" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="M26" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1852738628.4</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>日振幅值达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>003001.SZ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中岩大地</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9.9796</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="G27" t="n">
+        <v>611444567</v>
+      </c>
+      <c r="H27" t="n">
+        <v>96297377</v>
+      </c>
+      <c r="I27" t="n">
+        <v>128806260.51</v>
+      </c>
+      <c r="J27" t="n">
+        <v>225103637.51</v>
+      </c>
+      <c r="K27" t="n">
+        <v>32508883.51</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="M27" t="n">
+        <v>36.82</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1852738628.4</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>003020.SZ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>立方制药</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9219000000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1006677409</v>
+      </c>
+      <c r="H28" t="n">
+        <v>157382883.21</v>
+      </c>
+      <c r="I28" t="n">
+        <v>63158338.56</v>
+      </c>
+      <c r="J28" t="n">
+        <v>220541221.77</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-94224544.65000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="M28" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3505803704</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>日换手率达到20%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>003030.SZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>祖名股份</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8.9803</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="G29" t="n">
+        <v>510984802</v>
+      </c>
+      <c r="H29" t="n">
+        <v>117021914.68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>134499514</v>
+      </c>
+      <c r="J29" t="n">
+        <v>251521428.68</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17477599.32</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M29" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2102503282.25</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>127114.SZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>宜化转债</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>130</v>
+      </c>
+      <c r="E30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>541407100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>71246500</v>
+      </c>
+      <c r="I30" t="n">
+        <v>154820900</v>
+      </c>
+      <c r="J30" t="n">
+        <v>226067400</v>
+      </c>
+      <c r="K30" t="n">
+        <v>83574400</v>
+      </c>
+      <c r="L30" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="M30" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>上市首日可转债</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>300065.SZ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-17.7847</v>
+      </c>
+      <c r="F31" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2898291181</v>
+      </c>
+      <c r="H31" t="n">
+        <v>160632090.47</v>
+      </c>
+      <c r="I31" t="n">
+        <v>235838963.06</v>
+      </c>
+      <c r="J31" t="n">
+        <v>396471053.53</v>
+      </c>
+      <c r="K31" t="n">
+        <v>75206872.59</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13847348539.36</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>300164.SZ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>通源石油</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.0422</v>
+      </c>
+      <c r="F32" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2730225897</v>
+      </c>
+      <c r="H32" t="n">
+        <v>153846947.91</v>
+      </c>
+      <c r="I32" t="n">
+        <v>288566954.11</v>
+      </c>
+      <c r="J32" t="n">
+        <v>442413902.02</v>
+      </c>
+      <c r="K32" t="n">
+        <v>134720006.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M32" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>6636938653.64</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>300164.SZ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>通源石油</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20.0422</v>
+      </c>
+      <c r="F33" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4965659825</v>
+      </c>
+      <c r="H33" t="n">
+        <v>503058411.56</v>
+      </c>
+      <c r="I33" t="n">
+        <v>443447071.61</v>
+      </c>
+      <c r="J33" t="n">
+        <v>946505483.17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-59611339.95</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6636938653.64</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>300209.SZ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>行云科技</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3732478467</v>
+      </c>
+      <c r="H34" t="n">
+        <v>378603661.26</v>
+      </c>
+      <c r="I34" t="n">
+        <v>934559964.72</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1313163625.98</v>
+      </c>
+      <c r="K34" t="n">
+        <v>555956303.46</v>
+      </c>
+      <c r="L34" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="N34" t="n">
+        <v>22301236620.96</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>300214.SZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>日科化学</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.943099999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1264943056</v>
+      </c>
+      <c r="H35" t="n">
+        <v>160730697.46</v>
+      </c>
+      <c r="I35" t="n">
+        <v>207273918.04</v>
+      </c>
+      <c r="J35" t="n">
+        <v>368004615.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>46543220.58</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6229695027.6</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>300444.SZ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>双杰电气</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>199970849</v>
+      </c>
+      <c r="H36" t="n">
+        <v>14931476</v>
+      </c>
+      <c r="I36" t="n">
+        <v>31486795</v>
+      </c>
+      <c r="J36" t="n">
+        <v>46418271</v>
+      </c>
+      <c r="K36" t="n">
+        <v>16555319</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="M36" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5370900943.44</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>300532.SZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>今天国际</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.0658</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>402196534</v>
+      </c>
+      <c r="H37" t="n">
+        <v>53561875.33</v>
+      </c>
+      <c r="I37" t="n">
+        <v>86758042.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>140319918.03</v>
+      </c>
+      <c r="K37" t="n">
+        <v>33196167.37</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4413445023</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>300534.SZ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>陇神戎发</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.3333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1350922747</v>
+      </c>
+      <c r="H38" t="n">
+        <v>93800403.92</v>
+      </c>
+      <c r="I38" t="n">
+        <v>132932607.54</v>
+      </c>
+      <c r="J38" t="n">
+        <v>226733011.46</v>
+      </c>
+      <c r="K38" t="n">
+        <v>39132203.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M38" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3162479079.36</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>300566.SZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>激智科技</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20.0144</v>
+      </c>
+      <c r="F39" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1050917201</v>
+      </c>
+      <c r="H39" t="n">
+        <v>266073426.16</v>
+      </c>
+      <c r="I39" t="n">
+        <v>210612922.41</v>
+      </c>
+      <c r="J39" t="n">
+        <v>476686348.57</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-55460503.75</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="M39" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7571126395.4</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>301259.SZ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>艾布鲁</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19.982</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="G40" t="n">
+        <v>470495766</v>
+      </c>
+      <c r="H40" t="n">
+        <v>176831713.69</v>
+      </c>
+      <c r="I40" t="n">
+        <v>182814738.27</v>
+      </c>
+      <c r="J40" t="n">
+        <v>359646451.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5983024.58</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M40" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3858579933.6</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>日涨幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>301295.SZ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>美硕科技</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-19.857</v>
+      </c>
+      <c r="F41" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="G41" t="n">
+        <v>292607054</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66110822.98</v>
+      </c>
+      <c r="I41" t="n">
+        <v>59516056</v>
+      </c>
+      <c r="J41" t="n">
+        <v>125626878.98</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-6594766.98</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1153362000</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>日跌幅达到15%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>301520.SZ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>万邦医药</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-9.645899999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>781086441</v>
+      </c>
+      <c r="H42" t="n">
+        <v>101911824.81</v>
+      </c>
+      <c r="I42" t="n">
+        <v>39122918.92</v>
+      </c>
+      <c r="J42" t="n">
+        <v>141034743.73</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-62788905.89</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1601896722.57</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>日换手率达到30%的前5只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600129.SH</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>太极集团</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.728</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1253240806</v>
+      </c>
+      <c r="H43" t="n">
+        <v>90394667.31</v>
+      </c>
+      <c r="I43" t="n">
+        <v>65893170.05</v>
+      </c>
+      <c r="J43" t="n">
+        <v>156287837.36</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-24501497.26</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="N43" t="n">
+        <v>9721502601.549999</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>600288.SH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>大恒科技</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.2452</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1590619812</v>
+      </c>
+      <c r="H44" t="n">
+        <v>223311970.97</v>
+      </c>
+      <c r="I44" t="n">
+        <v>224579549.56</v>
+      </c>
+      <c r="J44" t="n">
+        <v>447891520.53</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1267578.59</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M44" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7504224000</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>600302.SH</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ST标准</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-10.0509</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G45" t="n">
+        <v>69561699</v>
+      </c>
+      <c r="H45" t="n">
+        <v>26614179.68</v>
+      </c>
+      <c r="I45" t="n">
+        <v>16866981.7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>43481161.38</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-9747197.98</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-14.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2446289314.28</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>600360.SH</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>华微电子</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-6.5805</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3677142349</v>
+      </c>
+      <c r="H46" t="n">
+        <v>591042227.45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>472990363.03</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1064032590.48</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-118051864.42</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="M46" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="N46" t="n">
+        <v>15268695333.6</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>600403.SH</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>大有能源</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E47" t="n">
+        <v>10.1075</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G47" t="n">
+        <v>187082122</v>
+      </c>
+      <c r="H47" t="n">
+        <v>41106807.92</v>
+      </c>
+      <c r="I47" t="n">
+        <v>49748921</v>
+      </c>
+      <c r="J47" t="n">
+        <v>90855728.92</v>
+      </c>
+      <c r="K47" t="n">
+        <v>8642113.08</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="M47" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="N47" t="n">
+        <v>12240959498.24</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>600470.SH</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>六国化工</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-10.0639</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="G48" t="n">
+        <v>255716174</v>
+      </c>
+      <c r="H48" t="n">
+        <v>17758262</v>
+      </c>
+      <c r="I48" t="n">
+        <v>23906762.47</v>
+      </c>
+      <c r="J48" t="n">
+        <v>41665024.47</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6148500.47</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M48" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2936608000</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>600488.SH</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.4751</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1139641909</v>
+      </c>
+      <c r="H49" t="n">
+        <v>82882337</v>
+      </c>
+      <c r="I49" t="n">
+        <v>100150801.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>183033138.36</v>
+      </c>
+      <c r="K49" t="n">
+        <v>17268464.36</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M49" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7064506819.6</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>600488.SH</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7.4751</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3066885699</v>
+      </c>
+      <c r="H50" t="n">
+        <v>340642827.41</v>
+      </c>
+      <c r="I50" t="n">
+        <v>298947330.95</v>
+      </c>
+      <c r="J50" t="n">
+        <v>639590158.36</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-41695496.46</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="M50" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="N50" t="n">
+        <v>7064506819.6</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>600759.SH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ST洲际</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E51" t="n">
+        <v>10.0746</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1243089807</v>
+      </c>
+      <c r="H51" t="n">
+        <v>96277986.95999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>108153114.04</v>
+      </c>
+      <c r="J51" t="n">
+        <v>204431101</v>
+      </c>
+      <c r="K51" t="n">
+        <v>11875127.08</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M51" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="N51" t="n">
+        <v>12223873051</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>600759.SH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ST洲际</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E52" t="n">
+        <v>10.0746</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3148170881</v>
+      </c>
+      <c r="H52" t="n">
+        <v>239553323.98</v>
+      </c>
+      <c r="I52" t="n">
+        <v>265211148.75</v>
+      </c>
+      <c r="J52" t="n">
+        <v>504764472.73</v>
+      </c>
+      <c r="K52" t="n">
+        <v>25657824.77</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M52" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="N52" t="n">
+        <v>12223873051</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>600785.SH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>新华百货</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-10.0467</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G53" t="n">
+        <v>29547210</v>
+      </c>
+      <c r="H53" t="n">
+        <v>21423248</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9797480</v>
+      </c>
+      <c r="J53" t="n">
+        <v>31220728</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-11625768</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-39.35</v>
+      </c>
+      <c r="M53" t="n">
+        <v>105.66</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2432305198.4</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>600844.SH</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>金煤科技</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>10.2041</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G54" t="n">
+        <v>73474758</v>
+      </c>
+      <c r="H54" t="n">
+        <v>19808593</v>
+      </c>
+      <c r="I54" t="n">
+        <v>21557552</v>
+      </c>
+      <c r="J54" t="n">
+        <v>41366145</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1748959</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M54" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2255092799.24</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>603065.SH</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>宿迁联盛</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2104133595</v>
+      </c>
+      <c r="H55" t="n">
+        <v>204342691</v>
+      </c>
+      <c r="I55" t="n">
+        <v>337411419.23</v>
+      </c>
+      <c r="J55" t="n">
+        <v>541754110.23</v>
+      </c>
+      <c r="K55" t="n">
+        <v>133068728.23</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="M55" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="N55" t="n">
+        <v>9862496644.879999</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>603065.SH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>宿迁联盛</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="G56" t="n">
+        <v>22543008300</v>
+      </c>
+      <c r="H56" t="n">
+        <v>22543008200</v>
+      </c>
+      <c r="I56" t="n">
+        <v>22543008300</v>
+      </c>
+      <c r="J56" t="n">
+        <v>45086016500</v>
+      </c>
+      <c r="K56" t="n">
+        <v>100</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>200</v>
+      </c>
+      <c r="N56" t="n">
+        <v>9862496644.879999</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续30个交易日内收盘价格涨幅偏离值累计达到200%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>603077.SH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>和邦生物</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10.0962</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="G57" t="n">
+        <v>695154384</v>
+      </c>
+      <c r="H57" t="n">
+        <v>60228170.25</v>
+      </c>
+      <c r="I57" t="n">
+        <v>129868122.52</v>
+      </c>
+      <c r="J57" t="n">
+        <v>190096292.77</v>
+      </c>
+      <c r="K57" t="n">
+        <v>69639952.27</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M57" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="N57" t="n">
+        <v>20224599247.12</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>603127.SH</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>昭衍新药</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6.9984</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2997726247</v>
+      </c>
+      <c r="H58" t="n">
+        <v>395791974.65</v>
+      </c>
+      <c r="I58" t="n">
+        <v>287197489</v>
+      </c>
+      <c r="J58" t="n">
+        <v>682989463.65</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-108594485.65</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="N58" t="n">
+        <v>29008845704.28</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>603313.SH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>梦百合</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7.5094</v>
+      </c>
+      <c r="F59" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1627277494</v>
+      </c>
+      <c r="H59" t="n">
+        <v>194237862.12</v>
+      </c>
+      <c r="I59" t="n">
+        <v>137360370.18</v>
+      </c>
+      <c r="J59" t="n">
+        <v>331598232.3</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-56877491.94</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4901341342.15</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>603318.SH</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>水发燃气</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.7427</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="G60" t="n">
+        <v>874038279</v>
+      </c>
+      <c r="H60" t="n">
+        <v>173900604.85</v>
+      </c>
+      <c r="I60" t="n">
+        <v>77444272</v>
+      </c>
+      <c r="J60" t="n">
+        <v>251344876.85</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-96456332.84999999</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="M60" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4071959095.88</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>603339.SH</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>四方科技</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10.0125</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="G61" t="n">
+        <v>337105284</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20827817.2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>25802359.52</v>
+      </c>
+      <c r="J61" t="n">
+        <v>46630176.72</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4974542.32</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M61" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4449764096.5</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>603459.SH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>红板科技</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7.5697</v>
+      </c>
+      <c r="F62" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1491713128</v>
+      </c>
+      <c r="H62" t="n">
+        <v>176146678.67</v>
+      </c>
+      <c r="I62" t="n">
+        <v>208611046.56</v>
+      </c>
+      <c r="J62" t="n">
+        <v>384757725.23</v>
+      </c>
+      <c r="K62" t="n">
+        <v>32464367.89</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7470400581</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>603466.SH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>风语筑</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.0474</v>
+      </c>
+      <c r="F63" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="G63" t="n">
+        <v>670348312</v>
+      </c>
+      <c r="H63" t="n">
+        <v>117169767.56</v>
+      </c>
+      <c r="I63" t="n">
+        <v>139831372.2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>257001139.76</v>
+      </c>
+      <c r="K63" t="n">
+        <v>22661604.64</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M63" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="N63" t="n">
+        <v>6905958792.12</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>603538.SH</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>美诺华</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7.4242</v>
+      </c>
+      <c r="F64" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3515050760</v>
+      </c>
+      <c r="H64" t="n">
+        <v>254949180.3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>364338345.74</v>
+      </c>
+      <c r="J64" t="n">
+        <v>619287526.04</v>
+      </c>
+      <c r="K64" t="n">
+        <v>109389165.44</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M64" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="N64" t="n">
+        <v>11943812262.95</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>603669.SH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>灵康药业</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>8.823499999999999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="G65" t="n">
+        <v>727836292</v>
+      </c>
+      <c r="H65" t="n">
+        <v>104910946.91</v>
+      </c>
+      <c r="I65" t="n">
+        <v>88093320.76000001</v>
+      </c>
+      <c r="J65" t="n">
+        <v>193004267.67</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-16817626.15</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="M65" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5271250621</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>603669.SH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>灵康药业</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8.823499999999999</v>
+      </c>
+      <c r="F66" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1167966972</v>
+      </c>
+      <c r="H66" t="n">
+        <v>166002923.91</v>
+      </c>
+      <c r="I66" t="n">
+        <v>131919602.78</v>
+      </c>
+      <c r="J66" t="n">
+        <v>297922526.69</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-34083321.13</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="M66" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5271250621</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>605598.SH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>上海港湾</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-10.0119</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G67" t="n">
+        <v>60236084</v>
+      </c>
+      <c r="H67" t="n">
+        <v>16215993</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6032684</v>
+      </c>
+      <c r="J67" t="n">
+        <v>22248677</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-10183309</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-16.91</v>
+      </c>
+      <c r="M67" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="N67" t="n">
+        <v>7360979144.61</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>688189.SH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ST南新</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E68" t="n">
+        <v>15.0972</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="G68" t="n">
+        <v>136920200</v>
+      </c>
+      <c r="H68" t="n">
+        <v>26173060.13</v>
+      </c>
+      <c r="I68" t="n">
+        <v>49965302.83</v>
+      </c>
+      <c r="J68" t="n">
+        <v>76138362.95999999</v>
+      </c>
+      <c r="K68" t="n">
+        <v>23792242.7</v>
+      </c>
+      <c r="L68" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="M68" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2100786487.8</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>688189.SH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ST南新</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15.0972</v>
+      </c>
+      <c r="F69" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="G69" t="n">
+        <v>253823700</v>
+      </c>
+      <c r="H69" t="n">
+        <v>52377130.44</v>
+      </c>
+      <c r="I69" t="n">
+        <v>87834563.95</v>
+      </c>
+      <c r="J69" t="n">
+        <v>140211694.39</v>
+      </c>
+      <c r="K69" t="n">
+        <v>35457433.51</v>
+      </c>
+      <c r="L69" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="M69" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2100786487.8</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>688192.SH</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>迪哲医药</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20.0043</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G70" t="n">
+        <v>436508600</v>
+      </c>
+      <c r="H70" t="n">
+        <v>87334019.84999999</v>
+      </c>
+      <c r="I70" t="n">
+        <v>96668765.89</v>
+      </c>
+      <c r="J70" t="n">
+        <v>184002785.74</v>
+      </c>
+      <c r="K70" t="n">
+        <v>9334746.039999999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M70" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="N70" t="n">
+        <v>25980189802.36</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>688216.SH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>气派科技</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="E71" t="n">
+        <v>20.0058</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="G71" t="n">
+        <v>627800900</v>
+      </c>
+      <c r="H71" t="n">
+        <v>86359757.06</v>
+      </c>
+      <c r="I71" t="n">
+        <v>125348705.48</v>
+      </c>
+      <c r="J71" t="n">
+        <v>211708462.54</v>
+      </c>
+      <c r="K71" t="n">
+        <v>38988948.42</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M71" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4403719335.45</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>688458.SH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>美芯晟</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="E72" t="n">
+        <v>18.235</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>371731200</v>
+      </c>
+      <c r="H72" t="n">
+        <v>56916572.08</v>
+      </c>
+      <c r="I72" t="n">
+        <v>122890543</v>
+      </c>
+      <c r="J72" t="n">
+        <v>179807115.08</v>
+      </c>
+      <c r="K72" t="n">
+        <v>65973970.92</v>
+      </c>
+      <c r="L72" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="M72" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3980780584.83</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>688519.SH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>南亚新材</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="E73" t="n">
+        <v>18.4312</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3553864700</v>
+      </c>
+      <c r="H73" t="n">
+        <v>905549202.71</v>
+      </c>
+      <c r="I73" t="n">
+        <v>938761507.78</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1844310710.49</v>
+      </c>
+      <c r="K73" t="n">
+        <v>33212305.07</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M73" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="N73" t="n">
+        <v>86287704169.8</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>科莱瑞迪</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="E74" t="n">
+        <v>23.5102</v>
+      </c>
+      <c r="F74" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="G74" t="n">
+        <v>164884700</v>
+      </c>
+      <c r="H74" t="n">
+        <v>17501259.09</v>
+      </c>
+      <c r="I74" t="n">
+        <v>24694907.55</v>
+      </c>
+      <c r="J74" t="n">
+        <v>42196166.64</v>
+      </c>
+      <c r="K74" t="n">
+        <v>7193648.46</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M74" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="N74" t="n">
+        <v>437710900</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>920081.BJ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>欧伦电气</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.3982</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>189122400</v>
+      </c>
+      <c r="H75" t="n">
+        <v>30795748.16</v>
+      </c>
+      <c r="I75" t="n">
+        <v>29833443.98</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60629192.14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-962304.1800000001</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="N75" t="n">
+        <v>700929000</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>920088.BJ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>科力股份</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>24.2054</v>
+      </c>
+      <c r="F76" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="G76" t="n">
+        <v>522160500</v>
+      </c>
+      <c r="H76" t="n">
+        <v>42705765.68</v>
+      </c>
+      <c r="I76" t="n">
+        <v>49108113.1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>91813878.78</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6402347.42</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M76" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1654364484</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>920125.BJ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>鸿仕达</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="E77" t="n">
+        <v>18.5053</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="G77" t="n">
+        <v>271990900</v>
+      </c>
+      <c r="H77" t="n">
+        <v>64384256.4</v>
+      </c>
+      <c r="I77" t="n">
+        <v>49918414.37</v>
+      </c>
+      <c r="J77" t="n">
+        <v>114302670.77</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-14465842.03</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="M77" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2305108044.54</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>吉和昌</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.8464</v>
+      </c>
+      <c r="F78" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="G78" t="n">
+        <v>299748400</v>
+      </c>
+      <c r="H78" t="n">
+        <v>52221661.71</v>
+      </c>
+      <c r="I78" t="n">
+        <v>48030769.59</v>
+      </c>
+      <c r="J78" t="n">
+        <v>100252431.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-4190892.12</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M78" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1042524000</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E79" t="n">
+        <v>29.1667</v>
+      </c>
+      <c r="F79" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="G79" t="n">
+        <v>17903000</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3544440.46</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3586200.67</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7130641.13</v>
+      </c>
+      <c r="K79" t="n">
+        <v>41760.21</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M79" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="N79" t="n">
+        <v>75423813.75</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E80" t="n">
+        <v>29.1667</v>
+      </c>
+      <c r="F80" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="G80" t="n">
+        <v>27895900</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4562893.13</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4848159.23</v>
+      </c>
+      <c r="J80" t="n">
+        <v>9411052.359999999</v>
+      </c>
+      <c r="K80" t="n">
+        <v>285266.1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M80" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="N80" t="n">
+        <v>75423813.75</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>920821.BJ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>则成电子</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E81" t="n">
+        <v>29.9687</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="G81" t="n">
+        <v>177006700</v>
+      </c>
+      <c r="H81" t="n">
+        <v>28579496.81</v>
+      </c>
+      <c r="I81" t="n">
+        <v>44050025.56</v>
+      </c>
+      <c r="J81" t="n">
+        <v>72629522.37</v>
+      </c>
+      <c r="K81" t="n">
+        <v>15470528.75</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M81" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1510251438.06</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -2527,7 +2527,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="C2" t="n">
-        <v>4211</v>
+        <v>3351</v>
       </c>
       <c r="D2" t="n">
-        <v>1247</v>
+        <v>2098</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>27194.94</v>
+        <v>25874.11</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3967.1262</v>
+        <v>3955.5781</v>
       </c>
       <c r="E2" t="n">
-        <v>1.36</v>
+        <v>-0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>12717.97</v>
+        <v>12262.98</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14924.8678</v>
+        <v>14779.3965</v>
       </c>
       <c r="E3" t="n">
-        <v>2.77</v>
+        <v>-0.97</v>
       </c>
       <c r="F3" t="n">
-        <v>9202.530000000001</v>
+        <v>8388.370000000001</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3851.1372</v>
+        <v>3804.7038</v>
       </c>
       <c r="E4" t="n">
-        <v>3.43</v>
+        <v>-1.21</v>
       </c>
       <c r="F4" t="n">
-        <v>3412.97</v>
+        <v>2919.79</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4796.502</v>
+        <v>4786.7828</v>
       </c>
       <c r="E5" t="n">
-        <v>2.15</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>9240.969999999999</v>
+        <v>8583.15</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2009.7296</v>
+        <v>1924.2735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.77</v>
+        <v>-4.25</v>
       </c>
       <c r="F6" t="n">
-        <v>2020.6</v>
+        <v>1696.45</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7925.1232</v>
+        <v>7817.8313</v>
       </c>
       <c r="E7" t="n">
-        <v>1.76</v>
+        <v>-1.35</v>
       </c>
       <c r="F7" t="n">
-        <v>5192.31</v>
+        <v>5042.68</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36827.97</v>
+        <v>34739.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31124.37</v>
+        <v>25984.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25984.66</v>
+        <v>25825.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25825.92</v>
+        <v>29322.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29322.57</v>
+        <v>34106.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34106.93</v>
+        <v>28347.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28347.13</v>
+        <v>27194.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27194.94</v>
+        <v>25874.11</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920821.BJ</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15.99</v>
+        <v>0.92</v>
       </c>
       <c r="D2" t="n">
-        <v>20.73</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
-        <v>15.99</v>
+        <v>0.91</v>
       </c>
       <c r="F2" t="n">
-        <v>20.73</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>15.95</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="n">
-        <v>4.78</v>
+        <v>0.27</v>
       </c>
       <c r="I2" t="n">
-        <v>29.9687</v>
+        <v>29.0323</v>
       </c>
       <c r="J2" t="n">
-        <v>92069.92999999999</v>
+        <v>155239.34</v>
       </c>
       <c r="K2" t="n">
-        <v>177006.68184</v>
+        <v>17665.73141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>920266.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>6.89</v>
       </c>
       <c r="D3" t="n">
-        <v>0.93</v>
+        <v>8.99</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>6.77</v>
       </c>
       <c r="F3" t="n">
-        <v>0.93</v>
+        <v>8.75</v>
       </c>
       <c r="G3" t="n">
-        <v>0.72</v>
+        <v>6.92</v>
       </c>
       <c r="H3" t="n">
-        <v>0.21</v>
+        <v>1.83</v>
       </c>
       <c r="I3" t="n">
-        <v>29.1667</v>
+        <v>26.4451</v>
       </c>
       <c r="J3" t="n">
-        <v>207198.95</v>
+        <v>232229.61</v>
       </c>
       <c r="K3" t="n">
-        <v>17903.01983</v>
+        <v>196894.82333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920088.BJ</t>
+          <t>688166.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44.53</v>
+        <v>30.19</v>
       </c>
       <c r="D4" t="n">
-        <v>51.27</v>
+        <v>35.44</v>
       </c>
       <c r="E4" t="n">
-        <v>43.9</v>
+        <v>29.74</v>
       </c>
       <c r="F4" t="n">
-        <v>50.8</v>
+        <v>35.44</v>
       </c>
       <c r="G4" t="n">
-        <v>40.9</v>
+        <v>29.53</v>
       </c>
       <c r="H4" t="n">
-        <v>9.9</v>
+        <v>5.91</v>
       </c>
       <c r="I4" t="n">
-        <v>24.2054</v>
+        <v>20.0135</v>
       </c>
       <c r="J4" t="n">
-        <v>110434.94</v>
+        <v>120833.14</v>
       </c>
       <c r="K4" t="n">
-        <v>522160.51892</v>
+        <v>412524.776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>920072.BJ</t>
+          <t>688192.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25.02</v>
+        <v>62.66</v>
       </c>
       <c r="D5" t="n">
-        <v>31.85</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>24.5</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>30.26</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>24.5</v>
+        <v>56.33</v>
       </c>
       <c r="H5" t="n">
-        <v>5.76</v>
+        <v>11.27</v>
       </c>
       <c r="I5" t="n">
-        <v>23.5102</v>
+        <v>20.0071</v>
       </c>
       <c r="J5" t="n">
-        <v>56312.49</v>
+        <v>157964.05</v>
       </c>
       <c r="K5" t="n">
-        <v>164884.70932</v>
+        <v>1056557.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300532.SZ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.72</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3</v>
+        <v>58.79</v>
       </c>
       <c r="E6" t="n">
-        <v>6.72</v>
+        <v>47.2</v>
       </c>
       <c r="F6" t="n">
-        <v>7.3</v>
+        <v>58.79</v>
       </c>
       <c r="G6" t="n">
-        <v>6.08</v>
+        <v>48.99</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0658</v>
+        <v>20.0041</v>
       </c>
       <c r="J6" t="n">
-        <v>561237.29</v>
+        <v>176762.44</v>
       </c>
       <c r="K6" t="n">
-        <v>402196.53407</v>
+        <v>964698.38056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300164.SZ</t>
+          <t>300528.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.1</v>
+        <v>14.49</v>
       </c>
       <c r="D7" t="n">
-        <v>11.38</v>
+        <v>16.99</v>
       </c>
       <c r="E7" t="n">
-        <v>9.68</v>
+        <v>14.38</v>
       </c>
       <c r="F7" t="n">
-        <v>11.38</v>
+        <v>16.99</v>
       </c>
       <c r="G7" t="n">
-        <v>9.48</v>
+        <v>14.16</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="I7" t="n">
-        <v>20.0422</v>
+        <v>19.9859</v>
       </c>
       <c r="J7" t="n">
-        <v>2564703.1</v>
+        <v>389898.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2730225.89725</v>
+        <v>633217.88728</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300566.SZ</t>
+          <t>300149.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.6</v>
+        <v>8.75</v>
       </c>
       <c r="D8" t="n">
-        <v>33.4</v>
+        <v>10.39</v>
       </c>
       <c r="E8" t="n">
-        <v>27.54</v>
+        <v>8.67</v>
       </c>
       <c r="F8" t="n">
-        <v>33.4</v>
+        <v>10.39</v>
       </c>
       <c r="G8" t="n">
-        <v>27.83</v>
+        <v>8.66</v>
       </c>
       <c r="H8" t="n">
-        <v>5.57</v>
+        <v>1.73</v>
       </c>
       <c r="I8" t="n">
-        <v>20.0144</v>
+        <v>19.9769</v>
       </c>
       <c r="J8" t="n">
-        <v>333036.55</v>
+        <v>739566.52</v>
       </c>
       <c r="K8" t="n">
-        <v>1050917.20078</v>
+        <v>750365.4693699999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300937.SZ</t>
+          <t>300231.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.3</v>
+        <v>7.55</v>
       </c>
       <c r="D9" t="n">
-        <v>23.21</v>
+        <v>9.08</v>
       </c>
       <c r="E9" t="n">
-        <v>19.03</v>
+        <v>7.51</v>
       </c>
       <c r="F9" t="n">
-        <v>23.21</v>
+        <v>9.08</v>
       </c>
       <c r="G9" t="n">
-        <v>19.34</v>
+        <v>7.57</v>
       </c>
       <c r="H9" t="n">
-        <v>3.87</v>
+        <v>1.51</v>
       </c>
       <c r="I9" t="n">
-        <v>20.0103</v>
+        <v>19.9472</v>
       </c>
       <c r="J9" t="n">
-        <v>109275.33</v>
+        <v>517140.6</v>
       </c>
       <c r="K9" t="n">
-        <v>240011.78912</v>
+        <v>446358.62436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688216.SH</t>
+          <t>300692.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>41.45</v>
+        <v>9.82</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>41.45</v>
+        <v>9.67</v>
       </c>
       <c r="G10" t="n">
-        <v>34.54</v>
+        <v>8.18</v>
       </c>
       <c r="H10" t="n">
-        <v>6.91</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>20.0058</v>
+        <v>18.2152</v>
       </c>
       <c r="J10" t="n">
-        <v>158147.32</v>
+        <v>1023459.4</v>
       </c>
       <c r="K10" t="n">
-        <v>627800.8689999999</v>
+        <v>959526.17724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688192.SH</t>
+          <t>688046.SH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.63</v>
+        <v>24.79</v>
       </c>
       <c r="D11" t="n">
-        <v>56.33</v>
+        <v>29.54</v>
       </c>
       <c r="E11" t="n">
-        <v>45.45</v>
+        <v>24.62</v>
       </c>
       <c r="F11" t="n">
-        <v>56.33</v>
+        <v>28.81</v>
       </c>
       <c r="G11" t="n">
-        <v>46.94</v>
+        <v>24.62</v>
       </c>
       <c r="H11" t="n">
-        <v>9.390000000000001</v>
+        <v>4.19</v>
       </c>
       <c r="I11" t="n">
-        <v>20.0043</v>
+        <v>17.0187</v>
       </c>
       <c r="J11" t="n">
-        <v>85845.25999999999</v>
+        <v>240515.94</v>
       </c>
       <c r="K11" t="n">
-        <v>436508.638</v>
+        <v>678745.786</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300444.SZ</t>
+          <t>301583.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.56</v>
+        <v>176.99</v>
       </c>
       <c r="D2" t="n">
-        <v>9.029999999999999</v>
+        <v>176.99</v>
       </c>
       <c r="E2" t="n">
-        <v>8.56</v>
+        <v>138.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.56</v>
+        <v>139.66</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7</v>
+        <v>179.03</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.14</v>
+        <v>-39.37</v>
       </c>
       <c r="I2" t="n">
-        <v>-20</v>
+        <v>-21.9907</v>
       </c>
       <c r="J2" t="n">
-        <v>232084</v>
+        <v>164749.75</v>
       </c>
       <c r="K2" t="n">
-        <v>199970.849</v>
+        <v>2520033.96111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301295.SZ</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>49.64</v>
+        <v>22.81</v>
       </c>
       <c r="D3" t="n">
-        <v>50.66</v>
+        <v>22.88</v>
       </c>
       <c r="E3" t="n">
-        <v>39.16</v>
+        <v>19.35</v>
       </c>
       <c r="F3" t="n">
-        <v>39.23</v>
+        <v>19.51</v>
       </c>
       <c r="G3" t="n">
-        <v>48.95</v>
+        <v>23.23</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.720000000000001</v>
+        <v>-3.72</v>
       </c>
       <c r="I3" t="n">
-        <v>-19.857</v>
+        <v>-16.0138</v>
       </c>
       <c r="J3" t="n">
-        <v>67858.92999999999</v>
+        <v>1658337.13</v>
       </c>
       <c r="K3" t="n">
-        <v>292607.05366</v>
+        <v>3394372.82942</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>688525.SH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="D4" t="n">
-        <v>213</v>
+        <v>351.6</v>
       </c>
       <c r="E4" t="n">
-        <v>163.13</v>
+        <v>303</v>
       </c>
       <c r="F4" t="n">
-        <v>179.03</v>
+        <v>304.4</v>
       </c>
       <c r="G4" t="n">
-        <v>221.8</v>
+        <v>358.37</v>
       </c>
       <c r="H4" t="n">
-        <v>-42.77</v>
+        <v>-53.97</v>
       </c>
       <c r="I4" t="n">
-        <v>-19.2831</v>
+        <v>-15.0599</v>
       </c>
       <c r="J4" t="n">
-        <v>180087.51</v>
+        <v>523410.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3288638.56159</v>
+        <v>16799676.182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>300065.SZ</t>
+          <t>920189.BJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.62</v>
+        <v>27.91</v>
       </c>
       <c r="D5" t="n">
-        <v>24.86</v>
+        <v>28.07</v>
       </c>
       <c r="E5" t="n">
-        <v>20.58</v>
+        <v>24.01</v>
       </c>
       <c r="F5" t="n">
-        <v>21.08</v>
+        <v>24.05</v>
       </c>
       <c r="G5" t="n">
-        <v>25.64</v>
+        <v>28.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.56</v>
+        <v>-4.25</v>
       </c>
       <c r="I5" t="n">
-        <v>-17.7847</v>
+        <v>-15.0177</v>
       </c>
       <c r="J5" t="n">
-        <v>1313199.4</v>
+        <v>134569.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2898291.18071</v>
+        <v>345353.73319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>920943.BJ</t>
+          <t>688432.SH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.42</v>
+        <v>47.18</v>
       </c>
       <c r="D6" t="n">
-        <v>17.7</v>
+        <v>47.37</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05</v>
+        <v>41.46</v>
       </c>
       <c r="F6" t="n">
-        <v>16.04</v>
+        <v>41.46</v>
       </c>
       <c r="G6" t="n">
-        <v>18.78</v>
+        <v>48.38</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.74</v>
+        <v>-6.92</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.59</v>
+        <v>-14.3034</v>
       </c>
       <c r="J6" t="n">
-        <v>70664.00999999999</v>
+        <v>455585.55</v>
       </c>
       <c r="K6" t="n">
-        <v>113318.23355</v>
+        <v>2003048.417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688523.SH</t>
+          <t>688359.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.06</v>
+        <v>199.95</v>
       </c>
       <c r="D7" t="n">
-        <v>57.57</v>
+        <v>199.95</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="F7" t="n">
-        <v>50.11</v>
+        <v>168</v>
       </c>
       <c r="G7" t="n">
-        <v>58.23</v>
+        <v>196.03</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.119999999999999</v>
+        <v>-28.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.9447</v>
+        <v>-14.2988</v>
       </c>
       <c r="J7" t="n">
-        <v>139566.43</v>
+        <v>97599.89</v>
       </c>
       <c r="K7" t="n">
-        <v>707305.777</v>
+        <v>1700698.576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>301005.SZ</t>
+          <t>688138.SH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>48.17</v>
       </c>
       <c r="D8" t="n">
-        <v>94.78</v>
+        <v>48.19</v>
       </c>
       <c r="E8" t="n">
-        <v>80.59999999999999</v>
+        <v>40.5</v>
       </c>
       <c r="F8" t="n">
-        <v>85.51000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="G8" t="n">
-        <v>96.98</v>
+        <v>48.16</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.47</v>
+        <v>-6.86</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.8272</v>
+        <v>-14.2442</v>
       </c>
       <c r="J8" t="n">
-        <v>169533.7</v>
+        <v>253716.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1449971.99829</v>
+        <v>1093985.193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688629.SH</t>
+          <t>920116.BJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>217</v>
+        <v>55.14</v>
       </c>
       <c r="D9" t="n">
-        <v>217.78</v>
+        <v>55.85</v>
       </c>
       <c r="E9" t="n">
-        <v>168</v>
+        <v>49.95</v>
       </c>
       <c r="F9" t="n">
-        <v>180.35</v>
+        <v>49.99</v>
       </c>
       <c r="G9" t="n">
-        <v>204.5</v>
+        <v>58.18</v>
       </c>
       <c r="H9" t="n">
-        <v>-24.15</v>
+        <v>-8.19</v>
       </c>
       <c r="I9" t="n">
-        <v>-11.8093</v>
+        <v>-14.077</v>
       </c>
       <c r="J9" t="n">
-        <v>422495.68</v>
+        <v>75140.97</v>
       </c>
       <c r="K9" t="n">
-        <v>7694476.296</v>
+        <v>397706.09552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>688375.SH</t>
+          <t>920193.BJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>98</v>
+        <v>41.78</v>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>42.37</v>
       </c>
       <c r="E10" t="n">
-        <v>85.45</v>
+        <v>35.55</v>
       </c>
       <c r="F10" t="n">
-        <v>87.8</v>
+        <v>35.61</v>
       </c>
       <c r="G10" t="n">
-        <v>98.56999999999999</v>
+        <v>41.37</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.77</v>
+        <v>-5.76</v>
       </c>
       <c r="I10" t="n">
-        <v>-10.9262</v>
+        <v>-13.9231</v>
       </c>
       <c r="J10" t="n">
-        <v>87119.25999999999</v>
+        <v>74268.07000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>775971.752</v>
+        <v>280801.97793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688387.SH</t>
+          <t>300214.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.98</v>
+        <v>13.14</v>
       </c>
       <c r="D11" t="n">
-        <v>17.98</v>
+        <v>14.12</v>
       </c>
       <c r="E11" t="n">
-        <v>15.94</v>
+        <v>10.86</v>
       </c>
       <c r="F11" t="n">
-        <v>16.57</v>
+        <v>11.58</v>
       </c>
       <c r="G11" t="n">
-        <v>18.6</v>
+        <v>13.4</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.03</v>
+        <v>-1.82</v>
       </c>
       <c r="I11" t="n">
-        <v>-10.914</v>
+        <v>-13.5821</v>
       </c>
       <c r="J11" t="n">
-        <v>1092211.56</v>
+        <v>814989.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1822038.533</v>
+        <v>993879.1355</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,337 +1819,337 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000078.SZ</t>
+          <t>000021.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST海王</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.29</v>
+        <v>47.26</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0962</v>
+        <v>-9.998100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>13.13</v>
+        <v>11.66</v>
       </c>
       <c r="G2" t="n">
-        <v>1259692238</v>
+        <v>9081246721</v>
       </c>
       <c r="H2" t="n">
-        <v>96461838.54000001</v>
+        <v>1305481357.84</v>
       </c>
       <c r="I2" t="n">
-        <v>106373577</v>
+        <v>909610681.71</v>
       </c>
       <c r="J2" t="n">
-        <v>202835415.54</v>
+        <v>2215092039.55</v>
       </c>
       <c r="K2" t="n">
-        <v>9911738.460000001</v>
+        <v>-395870676.13</v>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>-4.36</v>
       </c>
       <c r="M2" t="n">
-        <v>16.1</v>
+        <v>24.39</v>
       </c>
       <c r="N2" t="n">
-        <v>6011743962.16</v>
+        <v>74394592710.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000636.SZ</t>
+          <t>000036.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>华联控股</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59.41</v>
+        <v>4.82</v>
       </c>
       <c r="E3" t="n">
-        <v>9.998100000000001</v>
+        <v>4.1037</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>4.44</v>
       </c>
       <c r="G3" t="n">
-        <v>7331329500</v>
+        <v>774773809</v>
       </c>
       <c r="H3" t="n">
-        <v>621165698.25</v>
+        <v>127431068.41</v>
       </c>
       <c r="I3" t="n">
-        <v>1195024051.76</v>
+        <v>160073149.88</v>
       </c>
       <c r="J3" t="n">
-        <v>1816189750.01</v>
+        <v>287504218.29</v>
       </c>
       <c r="K3" t="n">
-        <v>573858353.51</v>
+        <v>32642081.47</v>
       </c>
       <c r="L3" t="n">
-        <v>7.83</v>
+        <v>4.21</v>
       </c>
       <c r="M3" t="n">
-        <v>24.77</v>
+        <v>37.11</v>
       </c>
       <c r="N3" t="n">
-        <v>68738148924.50999</v>
+        <v>6762369533.42</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>000989.SZ</t>
+          <t>000566.SZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>九芝堂</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.470000000000001</v>
+        <v>5.15</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4566</v>
+        <v>10.0427</v>
       </c>
       <c r="F4" t="n">
-        <v>16.15</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1817725006</v>
+        <v>538337018</v>
       </c>
       <c r="H4" t="n">
-        <v>146074889.46</v>
+        <v>41238100.71</v>
       </c>
       <c r="I4" t="n">
-        <v>123637625.47</v>
+        <v>120019935.13</v>
       </c>
       <c r="J4" t="n">
-        <v>269712514.93</v>
+        <v>161258035.84</v>
       </c>
       <c r="K4" t="n">
-        <v>-22437263.99</v>
+        <v>78781834.42</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.23</v>
+        <v>14.63</v>
       </c>
       <c r="M4" t="n">
-        <v>14.84</v>
+        <v>29.95</v>
       </c>
       <c r="N4" t="n">
-        <v>6573636040.91</v>
+        <v>6678188509.95</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>001270.SZ</t>
+          <t>000759.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>铖昌科技</t>
+          <t>中百集团</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134.7</v>
+        <v>6.87</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.002</v>
+        <v>1.7778</v>
       </c>
       <c r="F5" t="n">
-        <v>4.34</v>
+        <v>24.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1205557641</v>
+        <v>1084916081</v>
       </c>
       <c r="H5" t="n">
-        <v>206661543.62</v>
+        <v>142142504.63</v>
       </c>
       <c r="I5" t="n">
-        <v>110384446.4</v>
+        <v>116518348</v>
       </c>
       <c r="J5" t="n">
-        <v>317045990.02</v>
+        <v>258660852.63</v>
       </c>
       <c r="K5" t="n">
-        <v>-96277097.22</v>
+        <v>-25624156.63</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.99</v>
+        <v>-2.36</v>
       </c>
       <c r="M5" t="n">
-        <v>26.3</v>
+        <v>23.84</v>
       </c>
       <c r="N5" t="n">
-        <v>27586998583.2</v>
+        <v>4504700391.75</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001365.SZ</t>
+          <t>001270.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>天海电子</t>
+          <t>铖昌科技</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.88</v>
+        <v>121.61</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.1556</v>
+        <v>-9.7179</v>
       </c>
       <c r="F6" t="n">
-        <v>25.51</v>
+        <v>7.91</v>
       </c>
       <c r="G6" t="n">
-        <v>599848889</v>
+        <v>3250733953</v>
       </c>
       <c r="H6" t="n">
-        <v>52467240.61</v>
+        <v>418093844.98</v>
       </c>
       <c r="I6" t="n">
-        <v>95232709.84</v>
+        <v>376658952.4</v>
       </c>
       <c r="J6" t="n">
-        <v>147699950.45</v>
+        <v>794752797.38</v>
       </c>
       <c r="K6" t="n">
-        <v>42765469.23</v>
+        <v>-41434892.58</v>
       </c>
       <c r="L6" t="n">
-        <v>7.13</v>
+        <v>-1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>24.62</v>
+        <v>24.45</v>
       </c>
       <c r="N6" t="n">
-        <v>2350830808.48</v>
+        <v>24906123962.16</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>001388.SZ</t>
+          <t>001309.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>信通电子</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.44</v>
+        <v>662.4</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0034</v>
+        <v>-10</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>224531180</v>
+        <v>1755624960</v>
       </c>
       <c r="H7" t="n">
-        <v>43458165.8</v>
+        <v>354074659.2</v>
       </c>
       <c r="I7" t="n">
-        <v>51254896.01</v>
+        <v>285825600</v>
       </c>
       <c r="J7" t="n">
-        <v>94713061.81</v>
+        <v>639900259.2</v>
       </c>
       <c r="K7" t="n">
-        <v>7796730.21</v>
+        <v>-68249059.2</v>
       </c>
       <c r="L7" t="n">
-        <v>3.47</v>
+        <v>-3.89</v>
       </c>
       <c r="M7" t="n">
-        <v>42.18</v>
+        <v>36.45</v>
       </c>
       <c r="N7" t="n">
-        <v>2742463845.44</v>
+        <v>109341049824</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2163,807 +2163,807 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>27.07</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.991</v>
+        <v>-9.7667</v>
       </c>
       <c r="F8" t="n">
-        <v>17.64</v>
+        <v>23.89</v>
       </c>
       <c r="G8" t="n">
-        <v>2291303850</v>
+        <v>2861541795</v>
       </c>
       <c r="H8" t="n">
-        <v>307002366.41</v>
+        <v>477742368.04</v>
       </c>
       <c r="I8" t="n">
-        <v>320918133.69</v>
+        <v>476272058.89</v>
       </c>
       <c r="J8" t="n">
-        <v>627920500.1</v>
+        <v>954014426.9299999</v>
       </c>
       <c r="K8" t="n">
-        <v>13915767.28</v>
+        <v>-1470309.15</v>
       </c>
       <c r="L8" t="n">
-        <v>0.61</v>
+        <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>27.4</v>
+        <v>33.34</v>
       </c>
       <c r="N8" t="n">
-        <v>12917001930</v>
+        <v>11655441408.17</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002079.SZ</t>
+          <t>001399.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>苏州固锝</t>
+          <t>惠科股份</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.62</v>
+        <v>27.07</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.9923</v>
+        <v>-9.7667</v>
       </c>
       <c r="F9" t="n">
-        <v>8.57</v>
+        <v>23.89</v>
       </c>
       <c r="G9" t="n">
-        <v>822759237</v>
+        <v>5152845645</v>
       </c>
       <c r="H9" t="n">
-        <v>148199132</v>
+        <v>643271665.04</v>
       </c>
       <c r="I9" t="n">
-        <v>152153664.04</v>
+        <v>767617383.13</v>
       </c>
       <c r="J9" t="n">
-        <v>300352796.04</v>
+        <v>1410889048.17</v>
       </c>
       <c r="K9" t="n">
-        <v>3954532.04</v>
+        <v>124345718.09</v>
       </c>
       <c r="L9" t="n">
-        <v>0.48</v>
+        <v>2.41</v>
       </c>
       <c r="M9" t="n">
-        <v>36.51</v>
+        <v>27.38</v>
       </c>
       <c r="N9" t="n">
-        <v>9423045585.1</v>
+        <v>11655441408.17</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002185.SZ</t>
+          <t>001896.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>豫能控股</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.68</v>
+        <v>14.95</v>
       </c>
       <c r="E10" t="n">
-        <v>6.4235</v>
+        <v>10.0074</v>
       </c>
       <c r="F10" t="n">
-        <v>25.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>21083239147</v>
+        <v>2006496280</v>
       </c>
       <c r="H10" t="n">
-        <v>4627263020.37</v>
+        <v>294014341.94</v>
       </c>
       <c r="I10" t="n">
-        <v>2065492176.95</v>
+        <v>650697596.45</v>
       </c>
       <c r="J10" t="n">
-        <v>6692755197.32</v>
+        <v>944711938.39</v>
       </c>
       <c r="K10" t="n">
-        <v>-2561770843.42</v>
+        <v>356683254.51</v>
       </c>
       <c r="L10" t="n">
-        <v>-12.15</v>
+        <v>17.78</v>
       </c>
       <c r="M10" t="n">
-        <v>31.74</v>
+        <v>47.08</v>
       </c>
       <c r="N10" t="n">
-        <v>85325697119.75999</v>
+        <v>22810430883.5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002245.SZ</t>
+          <t>002137.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>蔚蓝锂芯</t>
+          <t>实益达</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.89</v>
+        <v>8.77</v>
       </c>
       <c r="E11" t="n">
-        <v>10.0053</v>
+        <v>-9.9589</v>
       </c>
       <c r="F11" t="n">
-        <v>10.6</v>
+        <v>20.66</v>
       </c>
       <c r="G11" t="n">
-        <v>3489028234</v>
+        <v>872429523</v>
       </c>
       <c r="H11" t="n">
-        <v>568051503.92</v>
+        <v>113591423.26</v>
       </c>
       <c r="I11" t="n">
-        <v>766731492.26</v>
+        <v>153224537</v>
       </c>
       <c r="J11" t="n">
-        <v>1334782996.18</v>
+        <v>266815960.26</v>
       </c>
       <c r="K11" t="n">
-        <v>198679988.34</v>
+        <v>39633113.74</v>
       </c>
       <c r="L11" t="n">
-        <v>5.69</v>
+        <v>4.54</v>
       </c>
       <c r="M11" t="n">
-        <v>38.26</v>
+        <v>30.58</v>
       </c>
       <c r="N11" t="n">
-        <v>33561868944.62</v>
+        <v>3476937370.37</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002379.SZ</t>
+          <t>002137.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>宏桥控股</t>
+          <t>实益达</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.49</v>
+        <v>8.77</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>-9.9589</v>
       </c>
       <c r="F12" t="n">
-        <v>9.74</v>
+        <v>20.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2775542286</v>
+        <v>731779646</v>
       </c>
       <c r="H12" t="n">
-        <v>550327285.9</v>
+        <v>113710683.26</v>
       </c>
       <c r="I12" t="n">
-        <v>517483526.3</v>
+        <v>146031688</v>
       </c>
       <c r="J12" t="n">
-        <v>1067810812.2</v>
+        <v>259742371.26</v>
       </c>
       <c r="K12" t="n">
-        <v>-32843759.6</v>
+        <v>32321004.74</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.18</v>
+        <v>4.42</v>
       </c>
       <c r="M12" t="n">
-        <v>38.47</v>
+        <v>35.49</v>
       </c>
       <c r="N12" t="n">
-        <v>19875176939.97</v>
+        <v>3476937370.37</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>002185.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>260.37</v>
+        <v>23.11</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>-10.0078</v>
       </c>
       <c r="F13" t="n">
-        <v>6.89</v>
+        <v>19.3</v>
       </c>
       <c r="G13" t="n">
-        <v>23856271061</v>
+        <v>15104876982</v>
       </c>
       <c r="H13" t="n">
-        <v>2871849510.32</v>
+        <v>2410003070.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4207142451.43</v>
+        <v>1298956062.61</v>
       </c>
       <c r="J13" t="n">
-        <v>7078991961.75</v>
+        <v>3708959133.01</v>
       </c>
       <c r="K13" t="n">
-        <v>1335292941.11</v>
+        <v>-1111047007.79</v>
       </c>
       <c r="L13" t="n">
-        <v>5.6</v>
+        <v>-7.36</v>
       </c>
       <c r="M13" t="n">
-        <v>29.67</v>
+        <v>24.55</v>
       </c>
       <c r="N13" t="n">
-        <v>360956587017.51</v>
+        <v>76786482104.27</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002396.SZ</t>
+          <t>002208.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>合肥城建</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.62</v>
+        <v>16.91</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2763</v>
+        <v>-10.0053</v>
       </c>
       <c r="F14" t="n">
-        <v>23.5</v>
+        <v>11.88</v>
       </c>
       <c r="G14" t="n">
-        <v>5185131546</v>
+        <v>1650521091</v>
       </c>
       <c r="H14" t="n">
-        <v>734403473.65</v>
+        <v>212985619.5</v>
       </c>
       <c r="I14" t="n">
-        <v>758571649.38</v>
+        <v>193965597.52</v>
       </c>
       <c r="J14" t="n">
-        <v>1492975123.03</v>
+        <v>406951217.02</v>
       </c>
       <c r="K14" t="n">
-        <v>24168175.73</v>
+        <v>-19020021.98</v>
       </c>
       <c r="L14" t="n">
-        <v>0.47</v>
+        <v>-1.15</v>
       </c>
       <c r="M14" t="n">
-        <v>28.79</v>
+        <v>24.66</v>
       </c>
       <c r="N14" t="n">
-        <v>21677220333.72</v>
+        <v>13579952034.97</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002457.SZ</t>
+          <t>002208.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>青龙管业</t>
+          <t>合肥城建</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.76</v>
+        <v>16.91</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.0141</v>
+        <v>-10.0053</v>
       </c>
       <c r="F15" t="n">
-        <v>11.98</v>
+        <v>11.88</v>
       </c>
       <c r="G15" t="n">
-        <v>509794382</v>
+        <v>2032609074</v>
       </c>
       <c r="H15" t="n">
-        <v>107774656</v>
+        <v>238625926.5</v>
       </c>
       <c r="I15" t="n">
-        <v>42455402.98</v>
+        <v>209482269.52</v>
       </c>
       <c r="J15" t="n">
-        <v>150230058.98</v>
+        <v>448108196.02</v>
       </c>
       <c r="K15" t="n">
-        <v>-65319253.02</v>
+        <v>-29143656.98</v>
       </c>
       <c r="L15" t="n">
-        <v>-12.81</v>
+        <v>-1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>29.47</v>
+        <v>22.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4252529653.24</v>
+        <v>13579952034.97</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002463.SZ</t>
+          <t>002342.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>巨力索具</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>137.13</v>
+        <v>8.23</v>
       </c>
       <c r="E16" t="n">
-        <v>10.0032</v>
+        <v>-8.1473</v>
       </c>
       <c r="F16" t="n">
-        <v>4.89</v>
+        <v>18.74</v>
       </c>
       <c r="G16" t="n">
-        <v>12553796133</v>
+        <v>4044898070</v>
       </c>
       <c r="H16" t="n">
-        <v>1148714567.25</v>
+        <v>476357791.22</v>
       </c>
       <c r="I16" t="n">
-        <v>2385480544.79</v>
+        <v>378862480.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3534195112.04</v>
+        <v>855220271.72</v>
       </c>
       <c r="K16" t="n">
-        <v>1236765977.54</v>
+        <v>-97495310.72</v>
       </c>
       <c r="L16" t="n">
-        <v>9.85</v>
+        <v>-2.41</v>
       </c>
       <c r="M16" t="n">
-        <v>28.15</v>
+        <v>21.14</v>
       </c>
       <c r="N16" t="n">
-        <v>263675001945.18</v>
+        <v>7857098700</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002490.SZ</t>
+          <t>002350.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>山东墨龙</t>
+          <t>北京科锐</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9.050000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="n">
-        <v>9.5642</v>
+        <v>-6.9471</v>
       </c>
       <c r="F17" t="n">
-        <v>19.96</v>
+        <v>6.64</v>
       </c>
       <c r="G17" t="n">
-        <v>2576349949</v>
+        <v>556799785</v>
       </c>
       <c r="H17" t="n">
-        <v>222189120.96</v>
+        <v>80093595.81</v>
       </c>
       <c r="I17" t="n">
-        <v>237813914.6</v>
+        <v>85048083</v>
       </c>
       <c r="J17" t="n">
-        <v>460003035.56</v>
+        <v>165141678.81</v>
       </c>
       <c r="K17" t="n">
-        <v>15624793.64</v>
+        <v>4954487.19</v>
       </c>
       <c r="L17" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="M17" t="n">
-        <v>17.85</v>
+        <v>29.66</v>
       </c>
       <c r="N17" t="n">
-        <v>4902584100</v>
+        <v>7746031036.6</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002549.SZ</t>
+          <t>002457.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>凯美特气</t>
+          <t>青龙管业</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.09</v>
+        <v>11.7</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.0112</v>
+        <v>-8.3072</v>
       </c>
       <c r="F18" t="n">
-        <v>10.19</v>
+        <v>17.07</v>
       </c>
       <c r="G18" t="n">
-        <v>1144304860</v>
+        <v>1537183461</v>
       </c>
       <c r="H18" t="n">
-        <v>196972058.96</v>
+        <v>165044412</v>
       </c>
       <c r="I18" t="n">
-        <v>71639382.34999999</v>
+        <v>117698856.64</v>
       </c>
       <c r="J18" t="n">
-        <v>268611441.31</v>
+        <v>282743268.64</v>
       </c>
       <c r="K18" t="n">
-        <v>-125332676.61</v>
+        <v>-47345555.36</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.95</v>
+        <v>-3.08</v>
       </c>
       <c r="M18" t="n">
-        <v>23.47</v>
+        <v>18.39</v>
       </c>
       <c r="N18" t="n">
-        <v>11140064773.34</v>
+        <v>3899263083.3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002552.SZ</t>
+          <t>002517.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>宝鼎科技</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.2</v>
+        <v>17.18</v>
       </c>
       <c r="E19" t="n">
-        <v>7.1626</v>
+        <v>9.9872</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>6.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1636777745</v>
+        <v>1990256490</v>
       </c>
       <c r="H19" t="n">
-        <v>341214157</v>
+        <v>191746596.16</v>
       </c>
       <c r="I19" t="n">
-        <v>348783881</v>
+        <v>473090855.07</v>
       </c>
       <c r="J19" t="n">
-        <v>689998038</v>
+        <v>664837451.23</v>
       </c>
       <c r="K19" t="n">
-        <v>7569724</v>
+        <v>281344258.91</v>
       </c>
       <c r="L19" t="n">
-        <v>0.46</v>
+        <v>14.14</v>
       </c>
       <c r="M19" t="n">
-        <v>42.16</v>
+        <v>33.4</v>
       </c>
       <c r="N19" t="n">
-        <v>21446891419.8</v>
+        <v>32454509042.14</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002581.SZ</t>
+          <t>002558.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>*ST未名</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3.82</v>
+        <v>29.56</v>
       </c>
       <c r="E20" t="n">
-        <v>5.2342</v>
+        <v>10.0112</v>
       </c>
       <c r="F20" t="n">
-        <v>5.37</v>
+        <v>7.95</v>
       </c>
       <c r="G20" t="n">
-        <v>133430911</v>
+        <v>4256003148</v>
       </c>
       <c r="H20" t="n">
-        <v>33465903.7</v>
+        <v>323896300.17</v>
       </c>
       <c r="I20" t="n">
-        <v>23892295.7</v>
+        <v>1018478268.06</v>
       </c>
       <c r="J20" t="n">
-        <v>57358199.4</v>
+        <v>1342374568.23</v>
       </c>
       <c r="K20" t="n">
-        <v>-9573608</v>
+        <v>694581967.89</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.17</v>
+        <v>16.32</v>
       </c>
       <c r="M20" t="n">
-        <v>42.99</v>
+        <v>31.54</v>
       </c>
       <c r="N20" t="n">
-        <v>1531022235.02</v>
+        <v>56180611862.76</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002617.SZ</t>
+          <t>002731.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>露笑科技</t>
+          <t>*ST萃华</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.94</v>
+        <v>2.09</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.684200000000001</v>
+        <v>-9.5238</v>
       </c>
       <c r="F21" t="n">
-        <v>12.58</v>
+        <v>38.61</v>
       </c>
       <c r="G21" t="n">
-        <v>6016180166</v>
+        <v>188730743</v>
       </c>
       <c r="H21" t="n">
-        <v>823904915.2</v>
+        <v>34858860.26</v>
       </c>
       <c r="I21" t="n">
-        <v>767747173.33</v>
+        <v>13271712</v>
       </c>
       <c r="J21" t="n">
-        <v>1591652088.53</v>
+        <v>48130572.26</v>
       </c>
       <c r="K21" t="n">
-        <v>-56157741.87</v>
+        <v>-21587148.26</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.93</v>
+        <v>-11.44</v>
       </c>
       <c r="M21" t="n">
-        <v>26.46</v>
+        <v>25.5</v>
       </c>
       <c r="N21" t="n">
-        <v>13030695375.28</v>
+        <v>479981876</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002636.SZ</t>
+          <t>002739.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>金安国纪</t>
+          <t>儒意电影</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>95.68000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>10.0023</v>
+        <v>9.9648</v>
       </c>
       <c r="F22" t="n">
-        <v>7.28</v>
+        <v>4.61</v>
       </c>
       <c r="G22" t="n">
-        <v>4708658892</v>
+        <v>891958056</v>
       </c>
       <c r="H22" t="n">
-        <v>873580157.72</v>
+        <v>67359937</v>
       </c>
       <c r="I22" t="n">
-        <v>932541806.79</v>
+        <v>372397890</v>
       </c>
       <c r="J22" t="n">
-        <v>1806121964.51</v>
+        <v>439757827</v>
       </c>
       <c r="K22" t="n">
-        <v>58961649.07</v>
+        <v>305037953</v>
       </c>
       <c r="L22" t="n">
-        <v>1.25</v>
+        <v>34.2</v>
       </c>
       <c r="M22" t="n">
-        <v>38.36</v>
+        <v>49.3</v>
       </c>
       <c r="N22" t="n">
-        <v>69302499098.56</v>
+        <v>19529177334.24</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2974,117 +2974,117 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002731.SZ</t>
+          <t>002821.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>*ST萃华</t>
+          <t>凯莱英</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.31</v>
+        <v>195.75</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.1167</v>
+        <v>10.0028</v>
       </c>
       <c r="F23" t="n">
-        <v>0.31</v>
+        <v>7.09</v>
       </c>
       <c r="G23" t="n">
-        <v>6077488</v>
+        <v>4240287773</v>
       </c>
       <c r="H23" t="n">
-        <v>2914837</v>
+        <v>408376896.33</v>
       </c>
       <c r="I23" t="n">
-        <v>2207316</v>
+        <v>821238856.85</v>
       </c>
       <c r="J23" t="n">
-        <v>5122153</v>
+        <v>1229615753.18</v>
       </c>
       <c r="K23" t="n">
-        <v>-707521</v>
+        <v>412861960.52</v>
       </c>
       <c r="L23" t="n">
-        <v>-11.64</v>
+        <v>9.74</v>
       </c>
       <c r="M23" t="n">
-        <v>84.28</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>530506284</v>
+        <v>62061335203.5</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002842.SZ</t>
+          <t>002821.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>翔鹭钨业</t>
+          <t>凯莱英</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38.23</v>
+        <v>195.75</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8518</v>
+        <v>10.0028</v>
       </c>
       <c r="F24" t="n">
-        <v>23.74</v>
+        <v>7.09</v>
       </c>
       <c r="G24" t="n">
-        <v>2406574471</v>
+        <v>9559452050</v>
       </c>
       <c r="H24" t="n">
-        <v>504023113.75</v>
+        <v>1070230024.64</v>
       </c>
       <c r="I24" t="n">
-        <v>234733176.26</v>
+        <v>1312420073.63</v>
       </c>
       <c r="J24" t="n">
-        <v>738756290.01</v>
+        <v>2382650098.27</v>
       </c>
       <c r="K24" t="n">
-        <v>-269289937.49</v>
+        <v>242190048.99</v>
       </c>
       <c r="L24" t="n">
-        <v>-11.19</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
-        <v>30.7</v>
+        <v>24.92</v>
       </c>
       <c r="N24" t="n">
-        <v>10263315984.57</v>
+        <v>62061335203.5</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3098,37 +3098,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="E25" t="n">
-        <v>5.2632</v>
+        <v>-5</v>
       </c>
       <c r="F25" t="n">
-        <v>8.69</v>
+        <v>6.36</v>
       </c>
       <c r="G25" t="n">
-        <v>3446883</v>
+        <v>2513402</v>
       </c>
       <c r="H25" t="n">
-        <v>1598044.67</v>
+        <v>977312.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1220207.6</v>
+        <v>1205485</v>
       </c>
       <c r="J25" t="n">
-        <v>2818252.27</v>
+        <v>2182797.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-377837.07</v>
+        <v>228172.5</v>
       </c>
       <c r="L25" t="n">
-        <v>-10.96</v>
+        <v>9.08</v>
       </c>
       <c r="M25" t="n">
-        <v>81.76000000000001</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>40504980.4</v>
+        <v>38479731.38</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3139,333 +3139,337 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>003001.SZ</t>
+          <t>002975.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>博杰股份</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.2</v>
+        <v>112.07</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9796</v>
+        <v>-9.9984</v>
       </c>
       <c r="F26" t="n">
-        <v>15.38</v>
+        <v>10.18</v>
       </c>
       <c r="G26" t="n">
-        <v>262810915</v>
+        <v>1629317633</v>
       </c>
       <c r="H26" t="n">
-        <v>36842609.53</v>
+        <v>422002194.64</v>
       </c>
       <c r="I26" t="n">
-        <v>66879651.1</v>
+        <v>267026893.24</v>
       </c>
       <c r="J26" t="n">
-        <v>103722260.63</v>
+        <v>689029087.88</v>
       </c>
       <c r="K26" t="n">
-        <v>30037041.57</v>
+        <v>-154975301.4</v>
       </c>
       <c r="L26" t="n">
-        <v>11.43</v>
+        <v>-9.51</v>
       </c>
       <c r="M26" t="n">
-        <v>39.47</v>
+        <v>42.29</v>
       </c>
       <c r="N26" t="n">
-        <v>1852738628.4</v>
+        <v>15393267150.73</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>003001.SZ</t>
+          <t>003020.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中岩大地</t>
+          <t>立方制药</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.2</v>
+        <v>21.91</v>
       </c>
       <c r="E27" t="n">
-        <v>9.9796</v>
+        <v>5.3365</v>
       </c>
       <c r="F27" t="n">
-        <v>15.38</v>
+        <v>27.48</v>
       </c>
       <c r="G27" t="n">
-        <v>611444567</v>
+        <v>970974940</v>
       </c>
       <c r="H27" t="n">
-        <v>96297377</v>
+        <v>59612146.16</v>
       </c>
       <c r="I27" t="n">
-        <v>128806260.51</v>
+        <v>77412344.09999999</v>
       </c>
       <c r="J27" t="n">
-        <v>225103637.51</v>
+        <v>137024490.26</v>
       </c>
       <c r="K27" t="n">
-        <v>32508883.51</v>
+        <v>17800197.94</v>
       </c>
       <c r="L27" t="n">
-        <v>5.32</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>36.82</v>
+        <v>14.11</v>
       </c>
       <c r="N27" t="n">
-        <v>1852738628.4</v>
+        <v>3692892267.05</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>003020.SZ</t>
+          <t>200016.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>立方制药</t>
+          <t>*ST康佳B</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20.8</v>
+        <v>0.74</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9219000000000001</v>
+        <v>8.823499999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>27.96</v>
+        <v>0.3</v>
       </c>
       <c r="G28" t="n">
-        <v>1006677409</v>
+        <v>1521864</v>
       </c>
       <c r="H28" t="n">
-        <v>157382883.21</v>
+        <v>698310.71</v>
       </c>
       <c r="I28" t="n">
-        <v>63158338.56</v>
+        <v>720637.72</v>
       </c>
       <c r="J28" t="n">
-        <v>220541221.77</v>
+        <v>1418948.43</v>
       </c>
       <c r="K28" t="n">
-        <v>-94224544.65000001</v>
+        <v>22327.01</v>
       </c>
       <c r="L28" t="n">
-        <v>-9.359999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>21.91</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>3505803704</v>
+        <v>4751544069.92</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>003030.SZ</t>
+          <t>200521.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>祖名股份</t>
+          <t>虹美菱B</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.97</v>
+        <v>2.6</v>
       </c>
       <c r="E29" t="n">
-        <v>8.9803</v>
+        <v>-10.0346</v>
       </c>
       <c r="F29" t="n">
-        <v>15.22</v>
+        <v>0.3</v>
       </c>
       <c r="G29" t="n">
-        <v>510984802</v>
+        <v>1008932</v>
       </c>
       <c r="H29" t="n">
-        <v>117021914.68</v>
+        <v>1008931.67</v>
       </c>
       <c r="I29" t="n">
-        <v>134499514</v>
+        <v>409166.56</v>
       </c>
       <c r="J29" t="n">
-        <v>251521428.68</v>
+        <v>1418098.23</v>
       </c>
       <c r="K29" t="n">
-        <v>17477599.32</v>
+        <v>-599765.11</v>
       </c>
       <c r="L29" t="n">
-        <v>3.42</v>
+        <v>-59.45</v>
       </c>
       <c r="M29" t="n">
-        <v>49.22</v>
+        <v>140.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2102503282.25</v>
+        <v>4848965650.4</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>127114.SZ</t>
+          <t>200553.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>宜化转债</t>
+          <t>安道麦B</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>130</v>
+        <v>2.71</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+        <v>-8.1356</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.65</v>
+      </c>
       <c r="G30" t="n">
-        <v>541407100</v>
+        <v>2330701</v>
       </c>
       <c r="H30" t="n">
-        <v>71246500</v>
+        <v>1302512.41</v>
       </c>
       <c r="I30" t="n">
-        <v>154820900</v>
+        <v>924015.98</v>
       </c>
       <c r="J30" t="n">
-        <v>226067400</v>
+        <v>2226528.39</v>
       </c>
       <c r="K30" t="n">
-        <v>83574400</v>
+        <v>-378496.43</v>
       </c>
       <c r="L30" t="n">
-        <v>15.44</v>
+        <v>-16.24</v>
       </c>
       <c r="M30" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>95.53</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12257196339.39</v>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>上市首日可转债</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300065.SZ</t>
+          <t>300149.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>海兰信</t>
+          <t>睿智医药</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.08</v>
+        <v>10.39</v>
       </c>
       <c r="E31" t="n">
-        <v>-17.7847</v>
+        <v>19.9769</v>
       </c>
       <c r="F31" t="n">
-        <v>19.99</v>
+        <v>15.58</v>
       </c>
       <c r="G31" t="n">
-        <v>2898291181</v>
+        <v>750365469</v>
       </c>
       <c r="H31" t="n">
-        <v>160632090.47</v>
+        <v>44637194.19</v>
       </c>
       <c r="I31" t="n">
-        <v>235838963.06</v>
+        <v>174894161.4</v>
       </c>
       <c r="J31" t="n">
-        <v>396471053.53</v>
+        <v>219531355.59</v>
       </c>
       <c r="K31" t="n">
-        <v>75206872.59</v>
+        <v>130256967.21</v>
       </c>
       <c r="L31" t="n">
-        <v>2.59</v>
+        <v>17.36</v>
       </c>
       <c r="M31" t="n">
-        <v>13.68</v>
+        <v>29.26</v>
       </c>
       <c r="N31" t="n">
-        <v>13847348539.36</v>
+        <v>4930714442.91</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3479,147 +3483,147 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.38</v>
+        <v>10.83</v>
       </c>
       <c r="E32" t="n">
-        <v>20.0422</v>
+        <v>-4.833</v>
       </c>
       <c r="F32" t="n">
-        <v>43.98</v>
+        <v>40.18</v>
       </c>
       <c r="G32" t="n">
-        <v>2730225897</v>
+        <v>2560677564</v>
       </c>
       <c r="H32" t="n">
-        <v>153846947.91</v>
+        <v>261307127.39</v>
       </c>
       <c r="I32" t="n">
-        <v>288566954.11</v>
+        <v>343857583.54</v>
       </c>
       <c r="J32" t="n">
-        <v>442413902.02</v>
+        <v>605164710.9299999</v>
       </c>
       <c r="K32" t="n">
-        <v>134720006.2</v>
+        <v>82550456.15000001</v>
       </c>
       <c r="L32" t="n">
-        <v>4.93</v>
+        <v>3.22</v>
       </c>
       <c r="M32" t="n">
-        <v>16.2</v>
+        <v>23.63</v>
       </c>
       <c r="N32" t="n">
-        <v>6636938653.64</v>
+        <v>6316172725.74</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300164.SZ</t>
+          <t>300214.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>通源石油</t>
+          <t>日科化学</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.38</v>
+        <v>11.58</v>
       </c>
       <c r="E33" t="n">
-        <v>20.0422</v>
+        <v>-13.5821</v>
       </c>
       <c r="F33" t="n">
-        <v>43.98</v>
+        <v>17.53</v>
       </c>
       <c r="G33" t="n">
-        <v>4965659825</v>
+        <v>993879136</v>
       </c>
       <c r="H33" t="n">
-        <v>503058411.56</v>
+        <v>186640655</v>
       </c>
       <c r="I33" t="n">
-        <v>443447071.61</v>
+        <v>195630090</v>
       </c>
       <c r="J33" t="n">
-        <v>946505483.17</v>
+        <v>382270745</v>
       </c>
       <c r="K33" t="n">
-        <v>-59611339.95</v>
+        <v>8989435</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.2</v>
+        <v>0.9</v>
       </c>
       <c r="M33" t="n">
-        <v>19.06</v>
+        <v>38.46</v>
       </c>
       <c r="N33" t="n">
-        <v>6636938653.64</v>
+        <v>5383572270.12</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日振幅值达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300209.SZ</t>
+          <t>300231.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>行云科技</t>
+          <t>银信科技</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.36</v>
+        <v>9.08</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>19.9472</v>
       </c>
       <c r="F34" t="n">
-        <v>17.79</v>
+        <v>11.64</v>
       </c>
       <c r="G34" t="n">
-        <v>3732478467</v>
+        <v>446358624</v>
       </c>
       <c r="H34" t="n">
-        <v>378603661.26</v>
+        <v>53784744.61</v>
       </c>
       <c r="I34" t="n">
-        <v>934559964.72</v>
+        <v>125731415.72</v>
       </c>
       <c r="J34" t="n">
-        <v>1313163625.98</v>
+        <v>179516160.33</v>
       </c>
       <c r="K34" t="n">
-        <v>555956303.46</v>
+        <v>71946671.11</v>
       </c>
       <c r="L34" t="n">
-        <v>14.9</v>
+        <v>16.12</v>
       </c>
       <c r="M34" t="n">
-        <v>35.18</v>
+        <v>40.22</v>
       </c>
       <c r="N34" t="n">
-        <v>22301236620.96</v>
+        <v>4034194949.84</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3630,161 +3634,161 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300214.SZ</t>
+          <t>300528.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>日科化学</t>
+          <t>幸福蓝海</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.4</v>
+        <v>16.99</v>
       </c>
       <c r="E35" t="n">
-        <v>8.943099999999999</v>
+        <v>19.9859</v>
       </c>
       <c r="F35" t="n">
-        <v>20.12</v>
+        <v>10.46</v>
       </c>
       <c r="G35" t="n">
-        <v>1264943056</v>
+        <v>633217887</v>
       </c>
       <c r="H35" t="n">
-        <v>160730697.46</v>
+        <v>80367513.19</v>
       </c>
       <c r="I35" t="n">
-        <v>207273918.04</v>
+        <v>123944152.86</v>
       </c>
       <c r="J35" t="n">
-        <v>368004615.5</v>
+        <v>204311666.05</v>
       </c>
       <c r="K35" t="n">
-        <v>46543220.58</v>
+        <v>43576639.67</v>
       </c>
       <c r="L35" t="n">
-        <v>3.68</v>
+        <v>6.88</v>
       </c>
       <c r="M35" t="n">
-        <v>29.09</v>
+        <v>32.27</v>
       </c>
       <c r="N35" t="n">
-        <v>6229695027.6</v>
+        <v>6330610837.46</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300444.SZ</t>
+          <t>300534.SZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>双杰电气</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.56</v>
+        <v>10.8</v>
       </c>
       <c r="E36" t="n">
-        <v>-20</v>
+        <v>3.1519</v>
       </c>
       <c r="F36" t="n">
-        <v>3.7</v>
+        <v>30.1</v>
       </c>
       <c r="G36" t="n">
-        <v>199970849</v>
+        <v>989128857</v>
       </c>
       <c r="H36" t="n">
-        <v>14931476</v>
+        <v>95114349.95999999</v>
       </c>
       <c r="I36" t="n">
-        <v>31486795</v>
+        <v>69473498.40000001</v>
       </c>
       <c r="J36" t="n">
-        <v>46418271</v>
+        <v>164587848.36</v>
       </c>
       <c r="K36" t="n">
-        <v>16555319</v>
+        <v>-25640851.56</v>
       </c>
       <c r="L36" t="n">
-        <v>8.279999999999999</v>
+        <v>-2.59</v>
       </c>
       <c r="M36" t="n">
-        <v>23.21</v>
+        <v>16.64</v>
       </c>
       <c r="N36" t="n">
-        <v>5370900943.44</v>
+        <v>3262156070.4</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300532.SZ</t>
+          <t>300692.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>今天国际</t>
+          <t>中赋科技</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.3</v>
+        <v>9.67</v>
       </c>
       <c r="E37" t="n">
-        <v>20.0658</v>
+        <v>18.2152</v>
       </c>
       <c r="F37" t="n">
-        <v>9.279999999999999</v>
+        <v>19.95</v>
       </c>
       <c r="G37" t="n">
-        <v>402196534</v>
+        <v>959526177</v>
       </c>
       <c r="H37" t="n">
-        <v>53561875.33</v>
+        <v>87361666.8</v>
       </c>
       <c r="I37" t="n">
-        <v>86758042.7</v>
+        <v>190580073.41</v>
       </c>
       <c r="J37" t="n">
-        <v>140319918.03</v>
+        <v>277941740.21</v>
       </c>
       <c r="K37" t="n">
-        <v>33196167.37</v>
+        <v>103218406.61</v>
       </c>
       <c r="L37" t="n">
-        <v>8.25</v>
+        <v>10.76</v>
       </c>
       <c r="M37" t="n">
-        <v>34.89</v>
+        <v>28.97</v>
       </c>
       <c r="N37" t="n">
-        <v>4413445023</v>
+        <v>4961503336.47</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3795,161 +3799,161 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300534.SZ</t>
+          <t>300821.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.47</v>
+        <v>19.51</v>
       </c>
       <c r="E38" t="n">
-        <v>16.3333</v>
+        <v>-16.0138</v>
       </c>
       <c r="F38" t="n">
-        <v>29.87</v>
+        <v>13.82</v>
       </c>
       <c r="G38" t="n">
-        <v>1350922747</v>
+        <v>3394372829</v>
       </c>
       <c r="H38" t="n">
-        <v>93800403.92</v>
+        <v>418623965.76</v>
       </c>
       <c r="I38" t="n">
-        <v>132932607.54</v>
+        <v>540987767.22</v>
       </c>
       <c r="J38" t="n">
-        <v>226733011.46</v>
+        <v>959611732.98</v>
       </c>
       <c r="K38" t="n">
-        <v>39132203.62</v>
+        <v>122363801.46</v>
       </c>
       <c r="L38" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="M38" t="n">
-        <v>16.78</v>
+        <v>28.27</v>
       </c>
       <c r="N38" t="n">
-        <v>3162479079.36</v>
+        <v>23407917532.5</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300566.SZ</t>
+          <t>300937.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>激智科技</t>
+          <t>药易购</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>33.4</v>
+        <v>25.36</v>
       </c>
       <c r="E39" t="n">
-        <v>20.0144</v>
+        <v>9.263199999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>14.69</v>
+        <v>29.62</v>
       </c>
       <c r="G39" t="n">
-        <v>1050917201</v>
+        <v>763570310</v>
       </c>
       <c r="H39" t="n">
-        <v>266073426.16</v>
+        <v>152311490.08</v>
       </c>
       <c r="I39" t="n">
-        <v>210612922.41</v>
+        <v>98321155.18000001</v>
       </c>
       <c r="J39" t="n">
-        <v>476686348.57</v>
+        <v>250632645.26</v>
       </c>
       <c r="K39" t="n">
-        <v>-55460503.75</v>
+        <v>-53990334.9</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.28</v>
+        <v>-7.07</v>
       </c>
       <c r="M39" t="n">
-        <v>45.36</v>
+        <v>32.82</v>
       </c>
       <c r="N39" t="n">
-        <v>7571126395.4</v>
+        <v>1644955655.52</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>301259.SZ</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>艾布鲁</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26.6</v>
+        <v>58.79</v>
       </c>
       <c r="E40" t="n">
-        <v>19.982</v>
+        <v>20.0041</v>
       </c>
       <c r="F40" t="n">
-        <v>13.22</v>
+        <v>54.06</v>
       </c>
       <c r="G40" t="n">
-        <v>470495766</v>
+        <v>964698381</v>
       </c>
       <c r="H40" t="n">
-        <v>176831713.69</v>
+        <v>56026477.65</v>
       </c>
       <c r="I40" t="n">
-        <v>182814738.27</v>
+        <v>72697628.52</v>
       </c>
       <c r="J40" t="n">
-        <v>359646451.96</v>
+        <v>128724106.17</v>
       </c>
       <c r="K40" t="n">
-        <v>5983024.58</v>
+        <v>16671150.87</v>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="M40" t="n">
-        <v>76.44</v>
+        <v>13.34</v>
       </c>
       <c r="N40" t="n">
-        <v>3858579933.6</v>
+        <v>1922341463.97</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3960,161 +3964,161 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>301295.SZ</t>
+          <t>600058.SH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>美硕科技</t>
+          <t>五矿发展</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>39.23</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>-19.857</v>
+        <v>-3.6876</v>
       </c>
       <c r="F41" t="n">
-        <v>23.08</v>
+        <v>1.87</v>
       </c>
       <c r="G41" t="n">
-        <v>292607054</v>
+        <v>599713397</v>
       </c>
       <c r="H41" t="n">
-        <v>66110822.98</v>
+        <v>95712397.23999999</v>
       </c>
       <c r="I41" t="n">
-        <v>59516056</v>
+        <v>59230802.5</v>
       </c>
       <c r="J41" t="n">
-        <v>125626878.98</v>
+        <v>154943199.74</v>
       </c>
       <c r="K41" t="n">
-        <v>-6594766.98</v>
+        <v>-36481594.74</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.25</v>
+        <v>-6.08</v>
       </c>
       <c r="M41" t="n">
-        <v>42.93</v>
+        <v>25.84</v>
       </c>
       <c r="N41" t="n">
-        <v>1153362000</v>
+        <v>9518567113.68</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>600118.SH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>中国卫星</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>48.99</v>
+        <v>73.92</v>
       </c>
       <c r="E42" t="n">
-        <v>-9.645899999999999</v>
+        <v>-9.9963</v>
       </c>
       <c r="F42" t="n">
-        <v>48.5</v>
+        <v>7.11</v>
       </c>
       <c r="G42" t="n">
-        <v>781086441</v>
+        <v>8561449632</v>
       </c>
       <c r="H42" t="n">
-        <v>101911824.81</v>
+        <v>745201508.27</v>
       </c>
       <c r="I42" t="n">
-        <v>39122918.92</v>
+        <v>468488193.56</v>
       </c>
       <c r="J42" t="n">
-        <v>141034743.73</v>
+        <v>1213689701.83</v>
       </c>
       <c r="K42" t="n">
-        <v>-62788905.89</v>
+        <v>-276713314.71</v>
       </c>
       <c r="L42" t="n">
-        <v>-8.039999999999999</v>
+        <v>-3.23</v>
       </c>
       <c r="M42" t="n">
-        <v>18.06</v>
+        <v>14.18</v>
       </c>
       <c r="N42" t="n">
-        <v>1601896722.57</v>
+        <v>87409596859.2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600129.SH</t>
+          <t>600186.SH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>太极集团</t>
+          <t>莲花控股</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.63</v>
+        <v>10.25</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.728</v>
+        <v>3.0151</v>
       </c>
       <c r="F43" t="n">
-        <v>12.96</v>
+        <v>15.29</v>
       </c>
       <c r="G43" t="n">
-        <v>1253240806</v>
+        <v>2822522723</v>
       </c>
       <c r="H43" t="n">
-        <v>90394667.31</v>
+        <v>368066675.2</v>
       </c>
       <c r="I43" t="n">
-        <v>65893170.05</v>
+        <v>688002016.64</v>
       </c>
       <c r="J43" t="n">
-        <v>156287837.36</v>
+        <v>1056068691.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-24501497.26</v>
+        <v>319935341.44</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.96</v>
+        <v>11.34</v>
       </c>
       <c r="M43" t="n">
-        <v>12.47</v>
+        <v>37.42</v>
       </c>
       <c r="N43" t="n">
-        <v>9721502601.549999</v>
+        <v>18338667482.75</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4125,271 +4129,271 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600288.SH</t>
+          <t>600227.SH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>大恒科技</t>
+          <t>赤天化</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.18</v>
+        <v>2.92</v>
       </c>
       <c r="E44" t="n">
-        <v>3.2452</v>
+        <v>10.1887</v>
       </c>
       <c r="F44" t="n">
-        <v>22.18</v>
+        <v>13.28</v>
       </c>
       <c r="G44" t="n">
-        <v>1590619812</v>
+        <v>478566762</v>
       </c>
       <c r="H44" t="n">
-        <v>223311970.97</v>
+        <v>79245379</v>
       </c>
       <c r="I44" t="n">
-        <v>224579549.56</v>
+        <v>67909384</v>
       </c>
       <c r="J44" t="n">
-        <v>447891520.53</v>
+        <v>147154763</v>
       </c>
       <c r="K44" t="n">
-        <v>1267578.59</v>
+        <v>-11335995</v>
       </c>
       <c r="L44" t="n">
-        <v>0.08</v>
+        <v>-2.37</v>
       </c>
       <c r="M44" t="n">
-        <v>28.16</v>
+        <v>30.75</v>
       </c>
       <c r="N44" t="n">
-        <v>7504224000</v>
+        <v>3730591424.76</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600302.SH</t>
+          <t>600227.SH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ST标准</t>
+          <t>赤天化</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7.07</v>
+        <v>2.92</v>
       </c>
       <c r="E45" t="n">
-        <v>-10.0509</v>
+        <v>10.1887</v>
       </c>
       <c r="F45" t="n">
-        <v>2.71</v>
+        <v>13.28</v>
       </c>
       <c r="G45" t="n">
-        <v>69561699</v>
+        <v>839279692</v>
       </c>
       <c r="H45" t="n">
-        <v>26614179.68</v>
+        <v>133837648.1</v>
       </c>
       <c r="I45" t="n">
-        <v>16866981.7</v>
+        <v>126651965</v>
       </c>
       <c r="J45" t="n">
-        <v>43481161.38</v>
+        <v>260489613.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-9747197.98</v>
+        <v>-7185683.1</v>
       </c>
       <c r="L45" t="n">
-        <v>-14.01</v>
+        <v>-0.86</v>
       </c>
       <c r="M45" t="n">
-        <v>62.51</v>
+        <v>31.04</v>
       </c>
       <c r="N45" t="n">
-        <v>2446289314.28</v>
+        <v>3730591424.76</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600360.SH</t>
+          <t>600257.SH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>华微电子</t>
+          <t>大湖股份</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.9</v>
+        <v>4.9</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.5805</v>
+        <v>10.1124</v>
       </c>
       <c r="F46" t="n">
-        <v>23.92</v>
+        <v>2.68</v>
       </c>
       <c r="G46" t="n">
-        <v>3677142349</v>
+        <v>62644856</v>
       </c>
       <c r="H46" t="n">
-        <v>591042227.45</v>
+        <v>7450166</v>
       </c>
       <c r="I46" t="n">
-        <v>472990363.03</v>
+        <v>18156622.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1064032590.48</v>
+        <v>25606788.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-118051864.42</v>
+        <v>10706456.8</v>
       </c>
       <c r="L46" t="n">
-        <v>-3.21</v>
+        <v>17.09</v>
       </c>
       <c r="M46" t="n">
-        <v>28.94</v>
+        <v>40.88</v>
       </c>
       <c r="N46" t="n">
-        <v>15268695333.6</v>
+        <v>2358062221.2</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600403.SH</t>
+          <t>600288.SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>大恒科技</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5.12</v>
+        <v>15.46</v>
       </c>
       <c r="E47" t="n">
-        <v>10.1075</v>
+        <v>-10.0116</v>
       </c>
       <c r="F47" t="n">
-        <v>1.58</v>
+        <v>3.3</v>
       </c>
       <c r="G47" t="n">
-        <v>187082122</v>
+        <v>226137313</v>
       </c>
       <c r="H47" t="n">
-        <v>41106807.92</v>
+        <v>60348868.14</v>
       </c>
       <c r="I47" t="n">
-        <v>49748921</v>
+        <v>30309424</v>
       </c>
       <c r="J47" t="n">
-        <v>90855728.92</v>
+        <v>90658292.14</v>
       </c>
       <c r="K47" t="n">
-        <v>8642113.08</v>
+        <v>-30039444.14</v>
       </c>
       <c r="L47" t="n">
-        <v>4.62</v>
+        <v>-13.28</v>
       </c>
       <c r="M47" t="n">
-        <v>48.56</v>
+        <v>40.09</v>
       </c>
       <c r="N47" t="n">
-        <v>12240959498.24</v>
+        <v>6752928000</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600470.SH</t>
+          <t>600343.SH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>六国化工</t>
+          <t>航天动力</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5.63</v>
+        <v>20.21</v>
       </c>
       <c r="E48" t="n">
-        <v>-10.0639</v>
+        <v>-10.0178</v>
       </c>
       <c r="F48" t="n">
-        <v>8.59</v>
+        <v>7.55</v>
       </c>
       <c r="G48" t="n">
-        <v>255716174</v>
+        <v>1000237660</v>
       </c>
       <c r="H48" t="n">
-        <v>17758262</v>
+        <v>97404023.18000001</v>
       </c>
       <c r="I48" t="n">
-        <v>23906762.47</v>
+        <v>103315481.6</v>
       </c>
       <c r="J48" t="n">
-        <v>41665024.47</v>
+        <v>200719504.78</v>
       </c>
       <c r="K48" t="n">
-        <v>6148500.47</v>
+        <v>5911458.42</v>
       </c>
       <c r="L48" t="n">
-        <v>2.4</v>
+        <v>0.59</v>
       </c>
       <c r="M48" t="n">
-        <v>16.29</v>
+        <v>20.07</v>
       </c>
       <c r="N48" t="n">
-        <v>2936608000</v>
+        <v>12898150293.08</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4400,106 +4404,106 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>600488.SH</t>
+          <t>600343.SH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>航天动力</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6.47</v>
+        <v>20.21</v>
       </c>
       <c r="E49" t="n">
-        <v>7.4751</v>
+        <v>-10.0178</v>
       </c>
       <c r="F49" t="n">
-        <v>16.94</v>
+        <v>7.55</v>
       </c>
       <c r="G49" t="n">
-        <v>1139641909</v>
+        <v>1279356349</v>
       </c>
       <c r="H49" t="n">
-        <v>82882337</v>
+        <v>107505838.18</v>
       </c>
       <c r="I49" t="n">
-        <v>100150801.36</v>
+        <v>104109213.6</v>
       </c>
       <c r="J49" t="n">
-        <v>183033138.36</v>
+        <v>211615051.78</v>
       </c>
       <c r="K49" t="n">
-        <v>17268464.36</v>
+        <v>-3396624.58</v>
       </c>
       <c r="L49" t="n">
-        <v>1.52</v>
+        <v>-0.27</v>
       </c>
       <c r="M49" t="n">
-        <v>16.06</v>
+        <v>16.54</v>
       </c>
       <c r="N49" t="n">
-        <v>7064506819.6</v>
+        <v>12898150293.08</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>600488.SH</t>
+          <t>600403.SH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6.47</v>
+        <v>5.63</v>
       </c>
       <c r="E50" t="n">
-        <v>7.4751</v>
+        <v>9.960900000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>16.94</v>
+        <v>2.91</v>
       </c>
       <c r="G50" t="n">
-        <v>3066885699</v>
+        <v>560509448</v>
       </c>
       <c r="H50" t="n">
-        <v>340642827.41</v>
+        <v>111197961.44</v>
       </c>
       <c r="I50" t="n">
-        <v>298947330.95</v>
+        <v>94893858.94</v>
       </c>
       <c r="J50" t="n">
-        <v>639590158.36</v>
+        <v>206091820.38</v>
       </c>
       <c r="K50" t="n">
-        <v>-41695496.46</v>
+        <v>-16304102.5</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.36</v>
+        <v>-2.91</v>
       </c>
       <c r="M50" t="n">
-        <v>20.85</v>
+        <v>36.77</v>
       </c>
       <c r="N50" t="n">
-        <v>7064506819.6</v>
+        <v>13460273823.26</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4510,271 +4514,271 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>600759.SH</t>
+          <t>600488.SH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ST洲际</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.95</v>
+        <v>6.98</v>
       </c>
       <c r="E51" t="n">
-        <v>10.0746</v>
+        <v>7.8825</v>
       </c>
       <c r="F51" t="n">
-        <v>10.52</v>
+        <v>16.86</v>
       </c>
       <c r="G51" t="n">
-        <v>1243089807</v>
+        <v>1230457536</v>
       </c>
       <c r="H51" t="n">
-        <v>96277986.95999999</v>
+        <v>108405816.55</v>
       </c>
       <c r="I51" t="n">
-        <v>108153114.04</v>
+        <v>77102900</v>
       </c>
       <c r="J51" t="n">
-        <v>204431101</v>
+        <v>185508716.55</v>
       </c>
       <c r="K51" t="n">
-        <v>11875127.08</v>
+        <v>-31302916.55</v>
       </c>
       <c r="L51" t="n">
-        <v>0.96</v>
+        <v>-2.54</v>
       </c>
       <c r="M51" t="n">
-        <v>16.45</v>
+        <v>15.08</v>
       </c>
       <c r="N51" t="n">
-        <v>12223873051</v>
+        <v>7621369026.4</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>600759.SH</t>
+          <t>600664.SH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ST洲际</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.95</v>
+        <v>4.49</v>
       </c>
       <c r="E52" t="n">
-        <v>10.0746</v>
+        <v>10.049</v>
       </c>
       <c r="F52" t="n">
-        <v>10.52</v>
+        <v>4.43</v>
       </c>
       <c r="G52" t="n">
-        <v>3148170881</v>
+        <v>494184337</v>
       </c>
       <c r="H52" t="n">
-        <v>239553323.98</v>
+        <v>35222688</v>
       </c>
       <c r="I52" t="n">
-        <v>265211148.75</v>
+        <v>147476110.77</v>
       </c>
       <c r="J52" t="n">
-        <v>504764472.73</v>
+        <v>182698798.77</v>
       </c>
       <c r="K52" t="n">
-        <v>25657824.77</v>
+        <v>112253422.77</v>
       </c>
       <c r="L52" t="n">
-        <v>0.82</v>
+        <v>22.71</v>
       </c>
       <c r="M52" t="n">
-        <v>16.03</v>
+        <v>36.97</v>
       </c>
       <c r="N52" t="n">
-        <v>12223873051</v>
+        <v>11308109343.24</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>600785.SH</t>
+          <t>600721.SH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>新华百货</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.7</v>
+        <v>7.57</v>
       </c>
       <c r="E53" t="n">
-        <v>-10.0467</v>
+        <v>10.0291</v>
       </c>
       <c r="F53" t="n">
-        <v>1.21</v>
+        <v>5.98</v>
       </c>
       <c r="G53" t="n">
-        <v>29547210</v>
+        <v>171244390</v>
       </c>
       <c r="H53" t="n">
-        <v>21423248</v>
+        <v>19906914</v>
       </c>
       <c r="I53" t="n">
-        <v>9797480</v>
+        <v>37592674</v>
       </c>
       <c r="J53" t="n">
-        <v>31220728</v>
+        <v>57499588</v>
       </c>
       <c r="K53" t="n">
-        <v>-11625768</v>
+        <v>17685760</v>
       </c>
       <c r="L53" t="n">
-        <v>-39.35</v>
+        <v>10.33</v>
       </c>
       <c r="M53" t="n">
-        <v>105.66</v>
+        <v>33.58</v>
       </c>
       <c r="N53" t="n">
-        <v>2432305198.4</v>
+        <v>2911025596.95</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>600844.SH</t>
+          <t>600746.SH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>金煤科技</t>
+          <t>江苏索普</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.7</v>
+        <v>6.31</v>
       </c>
       <c r="E54" t="n">
-        <v>10.2041</v>
+        <v>9.930300000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>3.32</v>
+        <v>3.93</v>
       </c>
       <c r="G54" t="n">
-        <v>73474758</v>
+        <v>388211469</v>
       </c>
       <c r="H54" t="n">
-        <v>19808593</v>
+        <v>72574092.68000001</v>
       </c>
       <c r="I54" t="n">
-        <v>21557552</v>
+        <v>83389806.18000001</v>
       </c>
       <c r="J54" t="n">
-        <v>41366145</v>
+        <v>155963898.86</v>
       </c>
       <c r="K54" t="n">
-        <v>1748959</v>
+        <v>10815713.5</v>
       </c>
       <c r="L54" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="M54" t="n">
-        <v>56.3</v>
+        <v>40.17</v>
       </c>
       <c r="N54" t="n">
-        <v>2255092799.24</v>
+        <v>7369088598.04</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>603065.SH</t>
+          <t>600829.SH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>宿迁联盛</t>
+          <t>人民同泰</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23.54</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>10.0111</v>
       </c>
       <c r="F55" t="n">
-        <v>12.98</v>
+        <v>4.24</v>
       </c>
       <c r="G55" t="n">
-        <v>2104133595</v>
+        <v>394598105</v>
       </c>
       <c r="H55" t="n">
-        <v>204342691</v>
+        <v>57693646</v>
       </c>
       <c r="I55" t="n">
-        <v>337411419.23</v>
+        <v>75987873.56</v>
       </c>
       <c r="J55" t="n">
-        <v>541754110.23</v>
+        <v>133681519.56</v>
       </c>
       <c r="K55" t="n">
-        <v>133068728.23</v>
+        <v>18294227.56</v>
       </c>
       <c r="L55" t="n">
-        <v>6.32</v>
+        <v>4.64</v>
       </c>
       <c r="M55" t="n">
-        <v>25.75</v>
+        <v>33.88</v>
       </c>
       <c r="N55" t="n">
-        <v>9862496644.879999</v>
+        <v>5735098224.33</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4785,282 +4789,282 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>603065.SH</t>
+          <t>600844.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>宿迁联盛</t>
+          <t>金煤科技</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>23.54</v>
+        <v>2.97</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>12.98</v>
+        <v>11.29</v>
       </c>
       <c r="G56" t="n">
-        <v>22543008300</v>
+        <v>337597693</v>
       </c>
       <c r="H56" t="n">
-        <v>22543008200</v>
+        <v>65931657</v>
       </c>
       <c r="I56" t="n">
-        <v>22543008300</v>
+        <v>60403066</v>
       </c>
       <c r="J56" t="n">
-        <v>45086016500</v>
+        <v>126334723</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>-5528591</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.64</v>
       </c>
       <c r="M56" t="n">
-        <v>200</v>
+        <v>37.42</v>
       </c>
       <c r="N56" t="n">
-        <v>9862496644.879999</v>
+        <v>2478005244.85</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续30个交易日内收盘价格涨幅偏离值累计达到200%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>603077.SH</t>
+          <t>600879.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>和邦生物</t>
+          <t>航天电子</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.29</v>
+        <v>17.38</v>
       </c>
       <c r="E57" t="n">
-        <v>10.0962</v>
+        <v>-9.9948</v>
       </c>
       <c r="F57" t="n">
-        <v>3.54</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>695154384</v>
+        <v>14972467733</v>
       </c>
       <c r="H57" t="n">
-        <v>60228170.25</v>
+        <v>1042229880.97</v>
       </c>
       <c r="I57" t="n">
-        <v>129868122.52</v>
+        <v>907308535.8099999</v>
       </c>
       <c r="J57" t="n">
-        <v>190096292.77</v>
+        <v>1949538416.78</v>
       </c>
       <c r="K57" t="n">
-        <v>69639952.27</v>
+        <v>-134921345.16</v>
       </c>
       <c r="L57" t="n">
-        <v>10.02</v>
+        <v>-0.9</v>
       </c>
       <c r="M57" t="n">
-        <v>27.35</v>
+        <v>13.02</v>
       </c>
       <c r="N57" t="n">
-        <v>20224599247.12</v>
+        <v>57341822424.92</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603127.SH</t>
+          <t>603201.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>常润股份</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>46.02</v>
+        <v>16.9</v>
       </c>
       <c r="E58" t="n">
-        <v>6.9984</v>
+        <v>7.0298</v>
       </c>
       <c r="F58" t="n">
-        <v>10.96</v>
+        <v>6.38</v>
       </c>
       <c r="G58" t="n">
-        <v>2997726247</v>
+        <v>455679610</v>
       </c>
       <c r="H58" t="n">
-        <v>395791974.65</v>
+        <v>60931798.42</v>
       </c>
       <c r="I58" t="n">
-        <v>287197489</v>
+        <v>91246169.70999999</v>
       </c>
       <c r="J58" t="n">
-        <v>682989463.65</v>
+        <v>152177968.13</v>
       </c>
       <c r="K58" t="n">
-        <v>-108594485.65</v>
+        <v>30314371.29</v>
       </c>
       <c r="L58" t="n">
-        <v>-3.62</v>
+        <v>6.65</v>
       </c>
       <c r="M58" t="n">
-        <v>22.78</v>
+        <v>33.4</v>
       </c>
       <c r="N58" t="n">
-        <v>29008845704.28</v>
+        <v>3183195139.8</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603313.SH</t>
+          <t>603272.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>梦百合</t>
+          <t>*ST联翔</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>8.59</v>
+        <v>16.23</v>
       </c>
       <c r="E59" t="n">
-        <v>7.5094</v>
+        <v>-9.9834</v>
       </c>
       <c r="F59" t="n">
-        <v>14.79</v>
+        <v>5.97</v>
       </c>
       <c r="G59" t="n">
-        <v>1627277494</v>
+        <v>279033238</v>
       </c>
       <c r="H59" t="n">
-        <v>194237862.12</v>
+        <v>55086760</v>
       </c>
       <c r="I59" t="n">
-        <v>137360370.18</v>
+        <v>98128197.8</v>
       </c>
       <c r="J59" t="n">
-        <v>331598232.3</v>
+        <v>153214957.8</v>
       </c>
       <c r="K59" t="n">
-        <v>-56877491.94</v>
+        <v>43041437.8</v>
       </c>
       <c r="L59" t="n">
-        <v>-3.5</v>
+        <v>15.43</v>
       </c>
       <c r="M59" t="n">
-        <v>20.38</v>
+        <v>54.91</v>
       </c>
       <c r="N59" t="n">
-        <v>4901341342.15</v>
+        <v>1681866210</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603318.SH</t>
+          <t>603339.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>四方科技</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8.869999999999999</v>
+        <v>12.94</v>
       </c>
       <c r="E60" t="n">
-        <v>3.7427</v>
+        <v>-10.0139</v>
       </c>
       <c r="F60" t="n">
-        <v>21.59</v>
+        <v>6.54</v>
       </c>
       <c r="G60" t="n">
-        <v>874038279</v>
+        <v>264583684</v>
       </c>
       <c r="H60" t="n">
-        <v>173900604.85</v>
+        <v>23983173.4</v>
       </c>
       <c r="I60" t="n">
-        <v>77444272</v>
+        <v>28764350</v>
       </c>
       <c r="J60" t="n">
-        <v>251344876.85</v>
+        <v>52747523.4</v>
       </c>
       <c r="K60" t="n">
-        <v>-96456332.84999999</v>
+        <v>4781176.6</v>
       </c>
       <c r="L60" t="n">
-        <v>-11.04</v>
+        <v>1.81</v>
       </c>
       <c r="M60" t="n">
-        <v>28.76</v>
+        <v>19.94</v>
       </c>
       <c r="N60" t="n">
-        <v>4071959095.88</v>
+        <v>4004168804.5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5074,48 +5078,48 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.38</v>
+        <v>12.94</v>
       </c>
       <c r="E61" t="n">
-        <v>-10.0125</v>
+        <v>-10.0139</v>
       </c>
       <c r="F61" t="n">
-        <v>7.48</v>
+        <v>6.54</v>
       </c>
       <c r="G61" t="n">
-        <v>337105284</v>
+        <v>601688968</v>
       </c>
       <c r="H61" t="n">
-        <v>20827817.2</v>
+        <v>40398652.71</v>
       </c>
       <c r="I61" t="n">
-        <v>25802359.52</v>
+        <v>46952331.52</v>
       </c>
       <c r="J61" t="n">
-        <v>46630176.72</v>
+        <v>87350984.23</v>
       </c>
       <c r="K61" t="n">
-        <v>4974542.32</v>
+        <v>6553678.81</v>
       </c>
       <c r="L61" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="M61" t="n">
-        <v>13.83</v>
+        <v>14.52</v>
       </c>
       <c r="N61" t="n">
-        <v>4449764096.5</v>
+        <v>4004168804.5</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5129,37 +5133,37 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>94.5</v>
+        <v>85.05</v>
       </c>
       <c r="E62" t="n">
-        <v>7.5697</v>
+        <v>-10</v>
       </c>
       <c r="F62" t="n">
-        <v>20.61</v>
+        <v>20.1</v>
       </c>
       <c r="G62" t="n">
-        <v>1491713128</v>
+        <v>1410741955</v>
       </c>
       <c r="H62" t="n">
-        <v>176146678.67</v>
+        <v>328754988.69</v>
       </c>
       <c r="I62" t="n">
-        <v>208611046.56</v>
+        <v>132108808.55</v>
       </c>
       <c r="J62" t="n">
-        <v>384757725.23</v>
+        <v>460863797.24</v>
       </c>
       <c r="K62" t="n">
-        <v>32464367.89</v>
+        <v>-196646180.14</v>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>-13.94</v>
       </c>
       <c r="M62" t="n">
-        <v>25.79</v>
+        <v>32.67</v>
       </c>
       <c r="N62" t="n">
-        <v>7470400581</v>
+        <v>6723360522.9</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5170,62 +5174,62 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>603466.SH</t>
+          <t>603516.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>风语筑</t>
+          <t>淳中科技</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.61</v>
+        <v>98.14</v>
       </c>
       <c r="E63" t="n">
-        <v>10.0474</v>
+        <v>-9.9963</v>
       </c>
       <c r="F63" t="n">
-        <v>10.18</v>
+        <v>5.51</v>
       </c>
       <c r="G63" t="n">
-        <v>670348312</v>
+        <v>1163871060</v>
       </c>
       <c r="H63" t="n">
-        <v>117169767.56</v>
+        <v>116953920.71</v>
       </c>
       <c r="I63" t="n">
-        <v>139831372.2</v>
+        <v>139730047.49</v>
       </c>
       <c r="J63" t="n">
-        <v>257001139.76</v>
+        <v>256683968.2</v>
       </c>
       <c r="K63" t="n">
-        <v>22661604.64</v>
+        <v>22776126.78</v>
       </c>
       <c r="L63" t="n">
-        <v>3.38</v>
+        <v>1.96</v>
       </c>
       <c r="M63" t="n">
-        <v>38.34</v>
+        <v>22.05</v>
       </c>
       <c r="N63" t="n">
-        <v>6905958792.12</v>
+        <v>19948748901.06</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5239,37 +5243,37 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>35.45</v>
+        <v>39</v>
       </c>
       <c r="E64" t="n">
-        <v>7.4242</v>
+        <v>10.0141</v>
       </c>
       <c r="F64" t="n">
-        <v>31.48</v>
+        <v>30.43</v>
       </c>
       <c r="G64" t="n">
-        <v>3515050760</v>
+        <v>3865780275</v>
       </c>
       <c r="H64" t="n">
-        <v>254949180.3</v>
+        <v>421747711.71</v>
       </c>
       <c r="I64" t="n">
-        <v>364338345.74</v>
+        <v>416902590.64</v>
       </c>
       <c r="J64" t="n">
-        <v>619287526.04</v>
+        <v>838650302.35</v>
       </c>
       <c r="K64" t="n">
-        <v>109389165.44</v>
+        <v>-4845121.07</v>
       </c>
       <c r="L64" t="n">
-        <v>3.11</v>
+        <v>-0.13</v>
       </c>
       <c r="M64" t="n">
-        <v>17.62</v>
+        <v>21.69</v>
       </c>
       <c r="N64" t="n">
-        <v>11943812262.95</v>
+        <v>13139878089</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5280,7 +5284,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5294,37 +5298,37 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7.4</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>8.823499999999999</v>
+        <v>9.5946</v>
       </c>
       <c r="F65" t="n">
-        <v>14.27</v>
+        <v>14.65</v>
       </c>
       <c r="G65" t="n">
-        <v>727836292</v>
+        <v>785412835</v>
       </c>
       <c r="H65" t="n">
-        <v>104910946.91</v>
+        <v>102552754.35</v>
       </c>
       <c r="I65" t="n">
-        <v>88093320.76000001</v>
+        <v>63027211.88</v>
       </c>
       <c r="J65" t="n">
-        <v>193004267.67</v>
+        <v>165579966.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-16817626.15</v>
+        <v>-39525542.47</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.31</v>
+        <v>-5.03</v>
       </c>
       <c r="M65" t="n">
-        <v>26.52</v>
+        <v>21.08</v>
       </c>
       <c r="N65" t="n">
-        <v>5271250621</v>
+        <v>5777005748.15</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5335,880 +5339,1265 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>603669.SH</t>
+          <t>603698.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>灵康药业</t>
+          <t>航天工程</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.4</v>
+        <v>32.14</v>
       </c>
       <c r="E66" t="n">
-        <v>8.823499999999999</v>
+        <v>-9.997199999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>14.27</v>
+        <v>2.33</v>
       </c>
       <c r="G66" t="n">
-        <v>1167966972</v>
+        <v>481945974</v>
       </c>
       <c r="H66" t="n">
-        <v>166002923.91</v>
+        <v>60376719</v>
       </c>
       <c r="I66" t="n">
-        <v>131919602.78</v>
+        <v>37147678.72</v>
       </c>
       <c r="J66" t="n">
-        <v>297922526.69</v>
+        <v>97524397.72</v>
       </c>
       <c r="K66" t="n">
-        <v>-34083321.13</v>
+        <v>-23229040.28</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.92</v>
+        <v>-4.82</v>
       </c>
       <c r="M66" t="n">
-        <v>25.51</v>
+        <v>20.24</v>
       </c>
       <c r="N66" t="n">
-        <v>5271250621</v>
+        <v>17226718600</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>605598.SH</t>
+          <t>603800.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>上海港湾</t>
+          <t>洪田股份</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30.29</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-10.0119</v>
+        <v>4.9695</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8100000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="G67" t="n">
-        <v>60236084</v>
+        <v>1127609992</v>
       </c>
       <c r="H67" t="n">
-        <v>16215993</v>
+        <v>232882456.83</v>
       </c>
       <c r="I67" t="n">
-        <v>6032684</v>
+        <v>309758040.48</v>
       </c>
       <c r="J67" t="n">
-        <v>22248677</v>
+        <v>542640497.3099999</v>
       </c>
       <c r="K67" t="n">
-        <v>-10183309</v>
+        <v>76875583.65000001</v>
       </c>
       <c r="L67" t="n">
-        <v>-16.91</v>
+        <v>6.82</v>
       </c>
       <c r="M67" t="n">
-        <v>36.94</v>
+        <v>48.12</v>
       </c>
       <c r="N67" t="n">
-        <v>7360979144.61</v>
+        <v>16475680000</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>688189.SH</t>
+          <t>603839.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ST南新</t>
+          <t>安正时尚</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7.7</v>
+        <v>6.47</v>
       </c>
       <c r="E68" t="n">
-        <v>15.0972</v>
+        <v>10.034</v>
       </c>
       <c r="F68" t="n">
-        <v>6.73</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>136920200</v>
+        <v>48893977</v>
       </c>
       <c r="H68" t="n">
-        <v>26173060.13</v>
+        <v>12371294.22</v>
       </c>
       <c r="I68" t="n">
-        <v>49965302.83</v>
+        <v>15177837</v>
       </c>
       <c r="J68" t="n">
-        <v>76138362.95999999</v>
+        <v>27549131.22</v>
       </c>
       <c r="K68" t="n">
-        <v>23792242.7</v>
+        <v>2806542.78</v>
       </c>
       <c r="L68" t="n">
-        <v>17.38</v>
+        <v>5.74</v>
       </c>
       <c r="M68" t="n">
-        <v>55.61</v>
+        <v>56.34</v>
       </c>
       <c r="N68" t="n">
-        <v>2100786487.8</v>
+        <v>2503994814</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>688189.SH</t>
+          <t>603928.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ST南新</t>
+          <t>兴业股份</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.7</v>
+        <v>13.71</v>
       </c>
       <c r="E69" t="n">
-        <v>15.0972</v>
+        <v>-9.9803</v>
       </c>
       <c r="F69" t="n">
-        <v>6.73</v>
+        <v>11.45</v>
       </c>
       <c r="G69" t="n">
-        <v>253823700</v>
+        <v>1274165383</v>
       </c>
       <c r="H69" t="n">
-        <v>52377130.44</v>
+        <v>91024367.42</v>
       </c>
       <c r="I69" t="n">
-        <v>87834563.95</v>
+        <v>136781908.85</v>
       </c>
       <c r="J69" t="n">
-        <v>140211694.39</v>
+        <v>227806276.27</v>
       </c>
       <c r="K69" t="n">
-        <v>35457433.51</v>
+        <v>45757541.43</v>
       </c>
       <c r="L69" t="n">
-        <v>13.97</v>
+        <v>3.59</v>
       </c>
       <c r="M69" t="n">
-        <v>55.24</v>
+        <v>17.88</v>
       </c>
       <c r="N69" t="n">
-        <v>2100786487.8</v>
+        <v>4671051840</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>688192.SH</t>
+          <t>603949.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>56.33</v>
+        <v>13.76</v>
       </c>
       <c r="E70" t="n">
-        <v>20.0043</v>
+        <v>-10.0065</v>
       </c>
       <c r="F70" t="n">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="G70" t="n">
-        <v>436508600</v>
+        <v>32737792</v>
       </c>
       <c r="H70" t="n">
-        <v>87334019.84999999</v>
+        <v>23744256</v>
       </c>
       <c r="I70" t="n">
-        <v>96668765.89</v>
+        <v>4697664</v>
       </c>
       <c r="J70" t="n">
-        <v>184002785.74</v>
+        <v>28441920</v>
       </c>
       <c r="K70" t="n">
-        <v>9334746.039999999</v>
+        <v>-19046592</v>
       </c>
       <c r="L70" t="n">
-        <v>2.14</v>
+        <v>-58.18</v>
       </c>
       <c r="M70" t="n">
-        <v>42.15</v>
+        <v>86.88</v>
       </c>
       <c r="N70" t="n">
-        <v>25980189802.36</v>
+        <v>2892424570.24</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>688216.SH</t>
+          <t>603949.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>气派科技</t>
+          <t>雪龙集团</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>41.45</v>
+        <v>13.76</v>
       </c>
       <c r="E71" t="n">
-        <v>20.0058</v>
+        <v>-10.0065</v>
       </c>
       <c r="F71" t="n">
-        <v>14.89</v>
+        <v>1.13</v>
       </c>
       <c r="G71" t="n">
-        <v>627800900</v>
+        <v>50481837</v>
       </c>
       <c r="H71" t="n">
-        <v>86359757.06</v>
+        <v>36828348</v>
       </c>
       <c r="I71" t="n">
-        <v>125348705.48</v>
+        <v>6333256</v>
       </c>
       <c r="J71" t="n">
-        <v>211708462.54</v>
+        <v>43161604</v>
       </c>
       <c r="K71" t="n">
-        <v>38988948.42</v>
+        <v>-30495092</v>
       </c>
       <c r="L71" t="n">
-        <v>6.21</v>
+        <v>-60.41</v>
       </c>
       <c r="M71" t="n">
-        <v>33.72</v>
+        <v>85.5</v>
       </c>
       <c r="N71" t="n">
-        <v>4403719335.45</v>
+        <v>2892424570.24</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>688458.SH</t>
+          <t>605133.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>美芯晟</t>
+          <t>嵘泰股份</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>42.47</v>
+        <v>31.21</v>
       </c>
       <c r="E72" t="n">
-        <v>18.235</v>
+        <v>-10.0058</v>
       </c>
       <c r="F72" t="n">
-        <v>10.09</v>
+        <v>4.71</v>
       </c>
       <c r="G72" t="n">
-        <v>371731200</v>
+        <v>427854069</v>
       </c>
       <c r="H72" t="n">
-        <v>56916572.08</v>
+        <v>144229876.6</v>
       </c>
       <c r="I72" t="n">
-        <v>122890543</v>
+        <v>62940285</v>
       </c>
       <c r="J72" t="n">
-        <v>179807115.08</v>
+        <v>207170161.6</v>
       </c>
       <c r="K72" t="n">
-        <v>65973970.92</v>
+        <v>-81289591.59999999</v>
       </c>
       <c r="L72" t="n">
-        <v>17.75</v>
+        <v>-19</v>
       </c>
       <c r="M72" t="n">
-        <v>48.37</v>
+        <v>48.42</v>
       </c>
       <c r="N72" t="n">
-        <v>3980780584.83</v>
+        <v>8804906275.52</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>688519.SH</t>
+          <t>605255.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>南亚新材</t>
+          <t>天普股份</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>366.9</v>
+        <v>87.19</v>
       </c>
       <c r="E73" t="n">
-        <v>18.4312</v>
+        <v>10.005</v>
       </c>
       <c r="F73" t="n">
-        <v>4.43</v>
+        <v>0.89</v>
       </c>
       <c r="G73" t="n">
-        <v>3553864700</v>
+        <v>245564722</v>
       </c>
       <c r="H73" t="n">
-        <v>905549202.71</v>
+        <v>16708767</v>
       </c>
       <c r="I73" t="n">
-        <v>938761507.78</v>
+        <v>36459173.38</v>
       </c>
       <c r="J73" t="n">
-        <v>1844310710.49</v>
+        <v>53167940.38</v>
       </c>
       <c r="K73" t="n">
-        <v>33212305.07</v>
+        <v>19750406.38</v>
       </c>
       <c r="L73" t="n">
-        <v>0.93</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M73" t="n">
-        <v>51.9</v>
+        <v>21.65</v>
       </c>
       <c r="N73" t="n">
-        <v>86287704169.8</v>
+        <v>11690435200</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>920072.BJ</t>
+          <t>605598.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>科莱瑞迪</t>
+          <t>上海港湾</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30.26</v>
+        <v>29.36</v>
       </c>
       <c r="E74" t="n">
-        <v>23.5102</v>
+        <v>-3.0703</v>
       </c>
       <c r="F74" t="n">
-        <v>38.93</v>
+        <v>4.46</v>
       </c>
       <c r="G74" t="n">
-        <v>164884700</v>
+        <v>482120915</v>
       </c>
       <c r="H74" t="n">
-        <v>17501259.09</v>
+        <v>68611980</v>
       </c>
       <c r="I74" t="n">
-        <v>24694907.55</v>
+        <v>100851436</v>
       </c>
       <c r="J74" t="n">
-        <v>42196166.64</v>
+        <v>169463416</v>
       </c>
       <c r="K74" t="n">
-        <v>7193648.46</v>
+        <v>32239456</v>
       </c>
       <c r="L74" t="n">
-        <v>4.36</v>
+        <v>6.69</v>
       </c>
       <c r="M74" t="n">
-        <v>25.59</v>
+        <v>35.15</v>
       </c>
       <c r="N74" t="n">
-        <v>437710900</v>
+        <v>7134973512.24</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>920081.BJ</t>
+          <t>688046.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>欧伦电气</t>
+          <t>药康生物</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>40.99</v>
+        <v>28.81</v>
       </c>
       <c r="E75" t="n">
-        <v>2.3982</v>
+        <v>17.0187</v>
       </c>
       <c r="F75" t="n">
-        <v>27.07</v>
+        <v>5.87</v>
       </c>
       <c r="G75" t="n">
-        <v>189122400</v>
+        <v>678745800</v>
       </c>
       <c r="H75" t="n">
-        <v>30795748.16</v>
+        <v>149641147.6</v>
       </c>
       <c r="I75" t="n">
-        <v>29833443.98</v>
+        <v>115383052.1</v>
       </c>
       <c r="J75" t="n">
-        <v>60629192.14</v>
+        <v>265024199.7</v>
       </c>
       <c r="K75" t="n">
-        <v>-962304.1800000001</v>
+        <v>-34258095.5</v>
       </c>
       <c r="L75" t="n">
-        <v>-0.51</v>
+        <v>-5.05</v>
       </c>
       <c r="M75" t="n">
-        <v>32.06</v>
+        <v>39.05</v>
       </c>
       <c r="N75" t="n">
-        <v>700929000</v>
+        <v>11812100000</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>920088.BJ</t>
+          <t>688166.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>科力股份</t>
+          <t>博瑞医药</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>50.8</v>
+        <v>35.44</v>
       </c>
       <c r="E76" t="n">
-        <v>24.2054</v>
+        <v>20.0135</v>
       </c>
       <c r="F76" t="n">
-        <v>33.91</v>
+        <v>2.77</v>
       </c>
       <c r="G76" t="n">
-        <v>522160500</v>
+        <v>412524800</v>
       </c>
       <c r="H76" t="n">
-        <v>42705765.68</v>
+        <v>87527029.31999999</v>
       </c>
       <c r="I76" t="n">
-        <v>49108113.1</v>
+        <v>78605231.65000001</v>
       </c>
       <c r="J76" t="n">
-        <v>91813878.78</v>
+        <v>166132260.97</v>
       </c>
       <c r="K76" t="n">
-        <v>6402347.42</v>
+        <v>-8921797.67</v>
       </c>
       <c r="L76" t="n">
-        <v>1.23</v>
+        <v>-2.16</v>
       </c>
       <c r="M76" t="n">
-        <v>17.58</v>
+        <v>40.27</v>
       </c>
       <c r="N76" t="n">
-        <v>1654364484</v>
+        <v>15444574481.04</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>920125.BJ</t>
+          <t>688192.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>鸿仕达</t>
+          <t>迪哲医药</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>139.86</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>18.5053</v>
+        <v>20.0071</v>
       </c>
       <c r="F77" t="n">
-        <v>12.71</v>
+        <v>3.43</v>
       </c>
       <c r="G77" t="n">
-        <v>271990900</v>
+        <v>1056557700</v>
       </c>
       <c r="H77" t="n">
-        <v>64384256.4</v>
+        <v>263185439.83</v>
       </c>
       <c r="I77" t="n">
-        <v>49918414.37</v>
+        <v>247980524.01</v>
       </c>
       <c r="J77" t="n">
-        <v>114302670.77</v>
+        <v>511165963.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-14465842.03</v>
+        <v>-15204915.82</v>
       </c>
       <c r="L77" t="n">
-        <v>-5.32</v>
+        <v>-1.44</v>
       </c>
       <c r="M77" t="n">
-        <v>42.02</v>
+        <v>48.38</v>
       </c>
       <c r="N77" t="n">
-        <v>2305108044.54</v>
+        <v>31178072619.2</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>688192.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>吉和昌</t>
+          <t>迪哲医药</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>41.37</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>1.8464</v>
+        <v>20.0071</v>
       </c>
       <c r="F78" t="n">
-        <v>29.84</v>
+        <v>3.43</v>
       </c>
       <c r="G78" t="n">
-        <v>299748400</v>
+        <v>1493066300</v>
       </c>
       <c r="H78" t="n">
-        <v>52221661.71</v>
+        <v>305030793.79</v>
       </c>
       <c r="I78" t="n">
-        <v>48030769.59</v>
+        <v>255528728.81</v>
       </c>
       <c r="J78" t="n">
-        <v>100252431.3</v>
+        <v>560559522.6</v>
       </c>
       <c r="K78" t="n">
-        <v>-4190892.12</v>
+        <v>-49502064.98</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.4</v>
+        <v>-3.32</v>
       </c>
       <c r="M78" t="n">
-        <v>33.45</v>
+        <v>37.54</v>
       </c>
       <c r="N78" t="n">
-        <v>1042524000</v>
+        <v>31178072619.2</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>688333.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>云创退</t>
+          <t>铂力特</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.93</v>
+        <v>116.2</v>
       </c>
       <c r="E79" t="n">
-        <v>29.1667</v>
+        <v>16.7135</v>
       </c>
       <c r="F79" t="n">
-        <v>25.55</v>
+        <v>11.82</v>
       </c>
       <c r="G79" t="n">
-        <v>17903000</v>
+        <v>3777863100</v>
       </c>
       <c r="H79" t="n">
-        <v>3544440.46</v>
+        <v>527118194.25</v>
       </c>
       <c r="I79" t="n">
-        <v>3586200.67</v>
+        <v>868248332.88</v>
       </c>
       <c r="J79" t="n">
-        <v>7130641.13</v>
+        <v>1395366527.13</v>
       </c>
       <c r="K79" t="n">
-        <v>41760.21</v>
+        <v>341130138.63</v>
       </c>
       <c r="L79" t="n">
-        <v>0.23</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>39.83</v>
+        <v>36.94</v>
       </c>
       <c r="N79" t="n">
-        <v>75423813.75</v>
+        <v>31876236618.8</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>当日收盘价涨幅达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>688433.SH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>云创退</t>
+          <t>华曙高科</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.93</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>29.1667</v>
+        <v>15.0048</v>
       </c>
       <c r="F80" t="n">
-        <v>25.55</v>
+        <v>2.55</v>
       </c>
       <c r="G80" t="n">
-        <v>27895900</v>
+        <v>1015325700</v>
       </c>
       <c r="H80" t="n">
-        <v>4562893.13</v>
+        <v>164570731.21</v>
       </c>
       <c r="I80" t="n">
-        <v>4848159.23</v>
+        <v>287406217.68</v>
       </c>
       <c r="J80" t="n">
-        <v>9411052.359999999</v>
+        <v>451976948.89</v>
       </c>
       <c r="K80" t="n">
-        <v>285266.1</v>
+        <v>122835486.47</v>
       </c>
       <c r="L80" t="n">
-        <v>1.02</v>
+        <v>12.1</v>
       </c>
       <c r="M80" t="n">
-        <v>33.74</v>
+        <v>44.52</v>
       </c>
       <c r="N80" t="n">
-        <v>75423813.75</v>
+        <v>40165569917.55</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>920821.BJ</t>
+          <t>688525.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>则成电子</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>20.73</v>
+        <v>304.4</v>
       </c>
       <c r="E81" t="n">
-        <v>29.9687</v>
+        <v>-15.0599</v>
       </c>
       <c r="F81" t="n">
-        <v>12.64</v>
+        <v>11.1</v>
       </c>
       <c r="G81" t="n">
-        <v>177006700</v>
+        <v>16799676200</v>
       </c>
       <c r="H81" t="n">
-        <v>28579496.81</v>
+        <v>1472525361.73</v>
       </c>
       <c r="I81" t="n">
-        <v>44050025.56</v>
+        <v>1231874526.21</v>
       </c>
       <c r="J81" t="n">
-        <v>72629522.37</v>
+        <v>2704399887.94</v>
       </c>
       <c r="K81" t="n">
-        <v>15470528.75</v>
+        <v>-240650835.52</v>
       </c>
       <c r="L81" t="n">
-        <v>8.74</v>
+        <v>-1.43</v>
       </c>
       <c r="M81" t="n">
-        <v>41.03</v>
+        <v>16.1</v>
       </c>
       <c r="N81" t="n">
-        <v>1510251438.06</v>
+        <v>143544890086.4</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>当日收盘价涨幅达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>920072.BJ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>科莱瑞迪</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E82" t="n">
+        <v>7.4025</v>
+      </c>
+      <c r="F82" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="G82" t="n">
+        <v>229415200</v>
+      </c>
+      <c r="H82" t="n">
+        <v>39041341.72</v>
+      </c>
+      <c r="I82" t="n">
+        <v>24322273.99</v>
+      </c>
+      <c r="J82" t="n">
+        <v>63363615.71</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-14719067.73</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-6.42</v>
+      </c>
+      <c r="M82" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="N82" t="n">
+        <v>470112500</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>920088.BJ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>科力股份</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-9.4094</v>
+      </c>
+      <c r="F83" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="G83" t="n">
+        <v>388516600</v>
+      </c>
+      <c r="H83" t="n">
+        <v>38972059.75</v>
+      </c>
+      <c r="I83" t="n">
+        <v>59634885.58</v>
+      </c>
+      <c r="J83" t="n">
+        <v>98606945.33</v>
+      </c>
+      <c r="K83" t="n">
+        <v>20662825.83</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="M83" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1498697904.6</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>920193.BJ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>吉和昌</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-13.9231</v>
+      </c>
+      <c r="F84" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="G84" t="n">
+        <v>280802000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>46772603.78</v>
+      </c>
+      <c r="I84" t="n">
+        <v>23899122.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>70671726.38</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-22873481.18</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-8.15</v>
+      </c>
+      <c r="M84" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="N84" t="n">
+        <v>897372000</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>920266.BJ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>生物谷</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E85" t="n">
+        <v>26.4451</v>
+      </c>
+      <c r="F85" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>196894800</v>
+      </c>
+      <c r="H85" t="n">
+        <v>32704691.72</v>
+      </c>
+      <c r="I85" t="n">
+        <v>32239550.08</v>
+      </c>
+      <c r="J85" t="n">
+        <v>64944241.8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-465141.64</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M85" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1036791498.75</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>920266.BJ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>生物谷</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E86" t="n">
+        <v>26.4451</v>
+      </c>
+      <c r="F86" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>334447300</v>
+      </c>
+      <c r="H86" t="n">
+        <v>49600297.37</v>
+      </c>
+      <c r="I86" t="n">
+        <v>39144174</v>
+      </c>
+      <c r="J86" t="n">
+        <v>88744471.37</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-10456123.37</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="M86" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1036791498.75</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>29.0323</v>
+      </c>
+      <c r="F87" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="G87" t="n">
+        <v>17665700</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2882967.14</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3855745.42</v>
+      </c>
+      <c r="J87" t="n">
+        <v>6738712.56</v>
+      </c>
+      <c r="K87" t="n">
+        <v>972778.28</v>
+      </c>
+      <c r="L87" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M87" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="N87" t="n">
+        <v>97321050</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>920367.BJ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>新赣江</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>12.5675</v>
+      </c>
+      <c r="F88" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="G88" t="n">
+        <v>314494700</v>
+      </c>
+      <c r="H88" t="n">
+        <v>26218412.97</v>
+      </c>
+      <c r="I88" t="n">
+        <v>21597474.46</v>
+      </c>
+      <c r="J88" t="n">
+        <v>47815887.43</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-4620938.51</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="M88" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1226183277.6</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -3187,7 +3187,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
         <v>19.9472</v>
       </c>
       <c r="F34" t="n">
-        <v>11.64</v>
+        <v>11.63</v>
       </c>
       <c r="G34" t="n">
         <v>446358624</v>
@@ -3623,7 +3623,7 @@
         <v>40.22</v>
       </c>
       <c r="N34" t="n">
-        <v>4034194949.84</v>
+        <v>4038091522.88</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>当日价格振幅达到30%的前5只股票</t>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5525</v>
+        <v>5524</v>
       </c>
       <c r="C2" t="n">
-        <v>3351</v>
+        <v>2499</v>
       </c>
       <c r="D2" t="n">
-        <v>2098</v>
+        <v>2861</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="F2" t="n">
-        <v>25874.11</v>
+        <v>24189.45</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3955.5781</v>
+        <v>3882.4126</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.29</v>
+        <v>-1.85</v>
       </c>
       <c r="F2" t="n">
-        <v>12262.98</v>
+        <v>11242.08</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14779.3965</v>
+        <v>14488.6541</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.97</v>
+        <v>-1.97</v>
       </c>
       <c r="F3" t="n">
-        <v>8388.370000000001</v>
+        <v>7937.97</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3804.7038</v>
+        <v>3692.4573</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.21</v>
+        <v>-2.95</v>
       </c>
       <c r="F4" t="n">
-        <v>2919.79</v>
+        <v>2852.36</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4786.7828</v>
+        <v>4698.4344</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>-1.85</v>
       </c>
       <c r="F5" t="n">
-        <v>8583.15</v>
+        <v>7988.3</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1924.2735</v>
+        <v>1846.8766</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.25</v>
+        <v>-4.02</v>
       </c>
       <c r="F6" t="n">
-        <v>1696.45</v>
+        <v>1748.21</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7817.8313</v>
+        <v>7631.7622</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.35</v>
+        <v>-2.38</v>
       </c>
       <c r="F7" t="n">
-        <v>5042.68</v>
+        <v>4730.91</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34739.26</v>
+        <v>32052.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31124.37</v>
+        <v>25984.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25984.66</v>
+        <v>25825.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25825.92</v>
+        <v>29322.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29322.57</v>
+        <v>34106.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34106.93</v>
+        <v>28347.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28347.13</v>
+        <v>27194.94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27194.94</v>
+        <v>25874.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25874.11</v>
+        <v>24189.45</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>920117.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.92</v>
+        <v>36.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>40.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.91</v>
+        <v>35.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>35.34</v>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>17.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.27</v>
+        <v>17.51</v>
       </c>
       <c r="I2" t="n">
-        <v>29.0323</v>
+        <v>98.20529999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>155239.34</v>
+        <v>188353.33</v>
       </c>
       <c r="K2" t="n">
-        <v>17665.73141</v>
+        <v>709339.71156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920266.BJ</t>
+          <t>920701.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.89</v>
+        <v>11.13</v>
       </c>
       <c r="D3" t="n">
-        <v>8.99</v>
+        <v>13.52</v>
       </c>
       <c r="E3" t="n">
-        <v>6.77</v>
+        <v>10.9</v>
       </c>
       <c r="F3" t="n">
-        <v>8.75</v>
+        <v>13.52</v>
       </c>
       <c r="G3" t="n">
-        <v>6.92</v>
+        <v>10.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>3.12</v>
       </c>
       <c r="I3" t="n">
-        <v>26.4451</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>232229.61</v>
+        <v>82915.52</v>
       </c>
       <c r="K3" t="n">
-        <v>196894.82333</v>
+        <v>108155.97627</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688166.SH</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.19</v>
+        <v>1.4</v>
       </c>
       <c r="D4" t="n">
-        <v>35.44</v>
+        <v>1.56</v>
       </c>
       <c r="E4" t="n">
-        <v>29.74</v>
+        <v>1.32</v>
       </c>
       <c r="F4" t="n">
-        <v>35.44</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>29.53</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>5.91</v>
+        <v>0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>20.0135</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>120833.14</v>
+        <v>188379.99</v>
       </c>
       <c r="K4" t="n">
-        <v>412524.776</v>
+        <v>28797.49011</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688192.SH</t>
+          <t>920367.BJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.66</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59999999999999</v>
+        <v>36.8</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>27.59</v>
       </c>
       <c r="F5" t="n">
-        <v>67.59999999999999</v>
+        <v>35.22</v>
       </c>
       <c r="G5" t="n">
-        <v>56.33</v>
+        <v>29.2</v>
       </c>
       <c r="H5" t="n">
-        <v>11.27</v>
+        <v>6.02</v>
       </c>
       <c r="I5" t="n">
-        <v>20.0071</v>
+        <v>20.6164</v>
       </c>
       <c r="J5" t="n">
-        <v>157964.05</v>
+        <v>133155.59</v>
       </c>
       <c r="K5" t="n">
-        <v>1056557.67</v>
+        <v>422583.76016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>300968.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>58.79</v>
+        <v>10.24</v>
       </c>
       <c r="E6" t="n">
-        <v>47.2</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>58.79</v>
+        <v>10.24</v>
       </c>
       <c r="G6" t="n">
-        <v>48.99</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0041</v>
+        <v>20.0469</v>
       </c>
       <c r="J6" t="n">
-        <v>176762.44</v>
+        <v>162653.5</v>
       </c>
       <c r="K6" t="n">
-        <v>964698.38056</v>
+        <v>164026.361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300528.SZ</t>
+          <t>301176.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.49</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>16.99</v>
+        <v>58.2</v>
       </c>
       <c r="E7" t="n">
-        <v>14.38</v>
+        <v>48.51</v>
       </c>
       <c r="F7" t="n">
-        <v>16.99</v>
+        <v>58.2</v>
       </c>
       <c r="G7" t="n">
-        <v>14.16</v>
+        <v>48.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.83</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>19.9859</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>389898.4</v>
+        <v>110575.2</v>
       </c>
       <c r="K7" t="n">
-        <v>633217.88728</v>
+        <v>606740.14151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300149.SZ</t>
+          <t>300805.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.75</v>
+        <v>7.4</v>
       </c>
       <c r="D8" t="n">
-        <v>10.39</v>
+        <v>8.83</v>
       </c>
       <c r="E8" t="n">
-        <v>8.67</v>
+        <v>7.33</v>
       </c>
       <c r="F8" t="n">
-        <v>10.39</v>
+        <v>8.83</v>
       </c>
       <c r="G8" t="n">
-        <v>8.66</v>
+        <v>7.36</v>
       </c>
       <c r="H8" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>19.9769</v>
+        <v>19.9728</v>
       </c>
       <c r="J8" t="n">
-        <v>739566.52</v>
+        <v>433633.77</v>
       </c>
       <c r="K8" t="n">
-        <v>750365.4693699999</v>
+        <v>367283.66845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300231.SZ</t>
+          <t>688166.SH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.55</v>
+        <v>36.86</v>
       </c>
       <c r="D9" t="n">
-        <v>9.08</v>
+        <v>42.52</v>
       </c>
       <c r="E9" t="n">
-        <v>7.51</v>
+        <v>36.29</v>
       </c>
       <c r="F9" t="n">
-        <v>9.08</v>
+        <v>42.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.57</v>
+        <v>35.44</v>
       </c>
       <c r="H9" t="n">
-        <v>1.51</v>
+        <v>7.06</v>
       </c>
       <c r="I9" t="n">
-        <v>19.9472</v>
+        <v>19.921</v>
       </c>
       <c r="J9" t="n">
-        <v>517140.6</v>
+        <v>483938.23</v>
       </c>
       <c r="K9" t="n">
-        <v>446358.62436</v>
+        <v>1945541.496</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300692.SZ</t>
+          <t>300591.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.210000000000001</v>
+        <v>6.03</v>
       </c>
       <c r="D10" t="n">
-        <v>9.82</v>
+        <v>7.37</v>
       </c>
       <c r="E10" t="n">
-        <v>8.119999999999999</v>
+        <v>6.03</v>
       </c>
       <c r="F10" t="n">
-        <v>9.67</v>
+        <v>7.3</v>
       </c>
       <c r="G10" t="n">
-        <v>8.18</v>
+        <v>6.14</v>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>18.2152</v>
+        <v>18.8925</v>
       </c>
       <c r="J10" t="n">
-        <v>1023459.4</v>
+        <v>664279.96</v>
       </c>
       <c r="K10" t="n">
-        <v>959526.17724</v>
+        <v>470686.95204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>688046.SH</t>
+          <t>301257.SZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.79</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>29.54</v>
+        <v>61.62</v>
       </c>
       <c r="E11" t="n">
-        <v>24.62</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>28.81</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>24.62</v>
+        <v>53.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.19</v>
+        <v>7.5</v>
       </c>
       <c r="I11" t="n">
-        <v>17.0187</v>
+        <v>14.0187</v>
       </c>
       <c r="J11" t="n">
-        <v>240515.94</v>
+        <v>144053.43</v>
       </c>
       <c r="K11" t="n">
-        <v>678745.786</v>
+        <v>832125.34752</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301583.SZ</t>
+          <t>301042.SZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>176.99</v>
+        <v>63.9</v>
       </c>
       <c r="D2" t="n">
-        <v>176.99</v>
+        <v>63.9</v>
       </c>
       <c r="E2" t="n">
-        <v>138.02</v>
+        <v>51.56</v>
       </c>
       <c r="F2" t="n">
-        <v>139.66</v>
+        <v>52.04</v>
       </c>
       <c r="G2" t="n">
-        <v>179.03</v>
+        <v>64.45</v>
       </c>
       <c r="H2" t="n">
-        <v>-39.37</v>
+        <v>-12.41</v>
       </c>
       <c r="I2" t="n">
-        <v>-21.9907</v>
+        <v>-19.2552</v>
       </c>
       <c r="J2" t="n">
-        <v>164749.75</v>
+        <v>35339.96</v>
       </c>
       <c r="K2" t="n">
-        <v>2520033.96111</v>
+        <v>210251.8998</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300821.SZ</t>
+          <t>300590.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.81</v>
+        <v>14.15</v>
       </c>
       <c r="D3" t="n">
-        <v>22.88</v>
+        <v>14.17</v>
       </c>
       <c r="E3" t="n">
-        <v>19.35</v>
+        <v>12.1</v>
       </c>
       <c r="F3" t="n">
-        <v>19.51</v>
+        <v>12.22</v>
       </c>
       <c r="G3" t="n">
-        <v>23.23</v>
+        <v>14.88</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.72</v>
+        <v>-2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>-16.0138</v>
+        <v>-17.8763</v>
       </c>
       <c r="J3" t="n">
-        <v>1658337.13</v>
+        <v>621321.24</v>
       </c>
       <c r="K3" t="n">
-        <v>3394372.82942</v>
+        <v>796017.62595</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>688525.SH</t>
+          <t>300689.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>351</v>
+        <v>64.75</v>
       </c>
       <c r="D4" t="n">
-        <v>351.6</v>
+        <v>65.72</v>
       </c>
       <c r="E4" t="n">
-        <v>303</v>
+        <v>54.13</v>
       </c>
       <c r="F4" t="n">
-        <v>304.4</v>
+        <v>54.75</v>
       </c>
       <c r="G4" t="n">
-        <v>358.37</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>-53.97</v>
+        <v>-11.25</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.0599</v>
+        <v>-17.0455</v>
       </c>
       <c r="J4" t="n">
-        <v>523410.02</v>
+        <v>78060.46000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>16799676.182</v>
+        <v>461467.2437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>920189.BJ</t>
+          <t>688008.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27.91</v>
+        <v>233.03</v>
       </c>
       <c r="D5" t="n">
-        <v>28.07</v>
+        <v>241.38</v>
       </c>
       <c r="E5" t="n">
-        <v>24.01</v>
+        <v>204.12</v>
       </c>
       <c r="F5" t="n">
-        <v>24.05</v>
+        <v>211.13</v>
       </c>
       <c r="G5" t="n">
-        <v>28.3</v>
+        <v>252.68</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.25</v>
+        <v>-41.55</v>
       </c>
       <c r="I5" t="n">
-        <v>-15.0177</v>
+        <v>-16.4437</v>
       </c>
       <c r="J5" t="n">
-        <v>134569.1</v>
+        <v>1160079.57</v>
       </c>
       <c r="K5" t="n">
-        <v>345353.73319</v>
+        <v>25578638.046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>688432.SH</t>
+          <t>300596.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47.18</v>
+        <v>45.3</v>
       </c>
       <c r="D6" t="n">
-        <v>47.37</v>
+        <v>45.3</v>
       </c>
       <c r="E6" t="n">
-        <v>41.46</v>
+        <v>37.96</v>
       </c>
       <c r="F6" t="n">
-        <v>41.46</v>
+        <v>38.07</v>
       </c>
       <c r="G6" t="n">
-        <v>48.38</v>
+        <v>45.45</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.92</v>
+        <v>-7.38</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.3034</v>
+        <v>-16.2376</v>
       </c>
       <c r="J6" t="n">
-        <v>455585.55</v>
+        <v>178059.57</v>
       </c>
       <c r="K6" t="n">
-        <v>2003048.417</v>
+        <v>719134.78528</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>688359.SH</t>
+          <t>301379.SZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>199.95</v>
+        <v>32.81</v>
       </c>
       <c r="D7" t="n">
-        <v>199.95</v>
+        <v>34.4</v>
       </c>
       <c r="E7" t="n">
-        <v>162</v>
+        <v>30.6</v>
       </c>
       <c r="F7" t="n">
-        <v>168</v>
+        <v>30.98</v>
       </c>
       <c r="G7" t="n">
-        <v>196.03</v>
+        <v>36.42</v>
       </c>
       <c r="H7" t="n">
-        <v>-28.03</v>
+        <v>-5.44</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.2988</v>
+        <v>-14.9368</v>
       </c>
       <c r="J7" t="n">
-        <v>97599.89</v>
+        <v>389859.24</v>
       </c>
       <c r="K7" t="n">
-        <v>1700698.576</v>
+        <v>1258433.8089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>688138.SH</t>
+          <t>300666.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48.17</v>
+        <v>253.75</v>
       </c>
       <c r="D8" t="n">
-        <v>48.19</v>
+        <v>264.48</v>
       </c>
       <c r="E8" t="n">
-        <v>40.5</v>
+        <v>233.42</v>
       </c>
       <c r="F8" t="n">
-        <v>41.3</v>
+        <v>240</v>
       </c>
       <c r="G8" t="n">
-        <v>48.16</v>
+        <v>282.14</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.86</v>
+        <v>-42.14</v>
       </c>
       <c r="I8" t="n">
-        <v>-14.2442</v>
+        <v>-14.9358</v>
       </c>
       <c r="J8" t="n">
-        <v>253716.5</v>
+        <v>334662.16</v>
       </c>
       <c r="K8" t="n">
-        <v>1093985.193</v>
+        <v>8390678.398429999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>920116.BJ</t>
+          <t>301031.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55.14</v>
+        <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>55.85</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>49.95</v>
+        <v>80.8</v>
       </c>
       <c r="F9" t="n">
-        <v>49.99</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>58.18</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.19</v>
+        <v>-13.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.077</v>
+        <v>-14.1956</v>
       </c>
       <c r="J9" t="n">
-        <v>75140.97</v>
+        <v>100732.84</v>
       </c>
       <c r="K9" t="n">
-        <v>397706.09552</v>
+        <v>852588.3994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>688248.SH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.78</v>
+        <v>48.53</v>
       </c>
       <c r="D10" t="n">
-        <v>42.37</v>
+        <v>48.68</v>
       </c>
       <c r="E10" t="n">
-        <v>35.55</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>35.61</v>
+        <v>41.63</v>
       </c>
       <c r="G10" t="n">
-        <v>41.37</v>
+        <v>48.05</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.76</v>
+        <v>-6.42</v>
       </c>
       <c r="I10" t="n">
-        <v>-13.9231</v>
+        <v>-13.3611</v>
       </c>
       <c r="J10" t="n">
-        <v>74268.07000000001</v>
+        <v>132256.68</v>
       </c>
       <c r="K10" t="n">
-        <v>280801.97793</v>
+        <v>579366.052</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>300214.SZ</t>
+          <t>688319.SH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13.14</v>
+        <v>37.6</v>
       </c>
       <c r="D11" t="n">
-        <v>14.12</v>
+        <v>37.6</v>
       </c>
       <c r="E11" t="n">
-        <v>10.86</v>
+        <v>32.22</v>
       </c>
       <c r="F11" t="n">
-        <v>11.58</v>
+        <v>33.07</v>
       </c>
       <c r="G11" t="n">
-        <v>13.4</v>
+        <v>38.16</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.82</v>
+        <v>-5.09</v>
       </c>
       <c r="I11" t="n">
-        <v>-13.5821</v>
+        <v>-13.3386</v>
       </c>
       <c r="J11" t="n">
-        <v>814989.5</v>
+        <v>167088.04</v>
       </c>
       <c r="K11" t="n">
-        <v>993879.1355</v>
+        <v>589062.028</v>
       </c>
     </row>
   </sheetData>
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,117 +1819,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>000021.SZ</t>
+          <t>000504.SZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>南华生物</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>47.26</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.998100000000001</v>
+        <v>9.988200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>11.66</v>
+        <v>8.73</v>
       </c>
       <c r="G2" t="n">
-        <v>9081246721</v>
+        <v>368862178</v>
       </c>
       <c r="H2" t="n">
-        <v>1305481357.84</v>
+        <v>75523906</v>
       </c>
       <c r="I2" t="n">
-        <v>909610681.71</v>
+        <v>96386004.36</v>
       </c>
       <c r="J2" t="n">
-        <v>2215092039.55</v>
+        <v>171909910.36</v>
       </c>
       <c r="K2" t="n">
-        <v>-395870676.13</v>
+        <v>20862098.36</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.36</v>
+        <v>5.66</v>
       </c>
       <c r="M2" t="n">
-        <v>24.39</v>
+        <v>46.61</v>
       </c>
       <c r="N2" t="n">
-        <v>74394592710.8</v>
+        <v>3080585645.28</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>000036.SZ</t>
+          <t>000566.SZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>华联控股</t>
+          <t>海南海药</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.82</v>
+        <v>5.67</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1037</v>
+        <v>10.0971</v>
       </c>
       <c r="F3" t="n">
-        <v>4.44</v>
+        <v>22.75</v>
       </c>
       <c r="G3" t="n">
-        <v>774773809</v>
+        <v>1614644689</v>
       </c>
       <c r="H3" t="n">
-        <v>127431068.41</v>
+        <v>173310439.63</v>
       </c>
       <c r="I3" t="n">
-        <v>160073149.88</v>
+        <v>155758950.66</v>
       </c>
       <c r="J3" t="n">
-        <v>287504218.29</v>
+        <v>329069390.29</v>
       </c>
       <c r="K3" t="n">
-        <v>32642081.47</v>
+        <v>-17551488.97</v>
       </c>
       <c r="L3" t="n">
-        <v>4.21</v>
+        <v>-1.09</v>
       </c>
       <c r="M3" t="n">
-        <v>37.11</v>
+        <v>20.38</v>
       </c>
       <c r="N3" t="n">
-        <v>6762369533.42</v>
+        <v>7352491039.11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1943,587 +1943,587 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.15</v>
+        <v>5.67</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0427</v>
+        <v>10.0971</v>
       </c>
       <c r="F4" t="n">
-        <v>8.380000000000001</v>
+        <v>22.75</v>
       </c>
       <c r="G4" t="n">
-        <v>538337018</v>
+        <v>2152981707</v>
       </c>
       <c r="H4" t="n">
-        <v>41238100.71</v>
+        <v>215865759.31</v>
       </c>
       <c r="I4" t="n">
-        <v>120019935.13</v>
+        <v>249465950.76</v>
       </c>
       <c r="J4" t="n">
-        <v>161258035.84</v>
+        <v>465331710.07</v>
       </c>
       <c r="K4" t="n">
-        <v>78781834.42</v>
+        <v>33600191.45</v>
       </c>
       <c r="L4" t="n">
-        <v>14.63</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
-        <v>29.95</v>
+        <v>21.61</v>
       </c>
       <c r="N4" t="n">
-        <v>6678188509.95</v>
+        <v>7352491039.11</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000759.SZ</t>
+          <t>000676.SZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>中百集团</t>
+          <t>智度股份</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.87</v>
+        <v>6.22</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7778</v>
+        <v>10.0885</v>
       </c>
       <c r="F5" t="n">
-        <v>24.06</v>
+        <v>6.61</v>
       </c>
       <c r="G5" t="n">
-        <v>1084916081</v>
+        <v>492758983</v>
       </c>
       <c r="H5" t="n">
-        <v>142142504.63</v>
+        <v>80679164</v>
       </c>
       <c r="I5" t="n">
-        <v>116518348</v>
+        <v>88673712.2</v>
       </c>
       <c r="J5" t="n">
-        <v>258660852.63</v>
+        <v>169352876.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-25624156.63</v>
+        <v>7994548.2</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.36</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>23.84</v>
+        <v>34.37</v>
       </c>
       <c r="N5" t="n">
-        <v>4504700391.75</v>
+        <v>7831157469.04</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>001270.SZ</t>
+          <t>000676.SZ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>铖昌科技</t>
+          <t>智度股份</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>121.61</v>
+        <v>6.22</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.7179</v>
+        <v>10.0885</v>
       </c>
       <c r="F6" t="n">
-        <v>7.91</v>
+        <v>6.61</v>
       </c>
       <c r="G6" t="n">
-        <v>3250733953</v>
+        <v>763732978</v>
       </c>
       <c r="H6" t="n">
-        <v>418093844.98</v>
+        <v>111205912</v>
       </c>
       <c r="I6" t="n">
-        <v>376658952.4</v>
+        <v>134626188.2</v>
       </c>
       <c r="J6" t="n">
-        <v>794752797.38</v>
+        <v>245832100.2</v>
       </c>
       <c r="K6" t="n">
-        <v>-41434892.58</v>
+        <v>23420276.2</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.27</v>
+        <v>3.07</v>
       </c>
       <c r="M6" t="n">
-        <v>24.45</v>
+        <v>32.19</v>
       </c>
       <c r="N6" t="n">
-        <v>24906123962.16</v>
+        <v>7831157469.04</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>001309.SZ</t>
+          <t>000677.SZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>ST海龙</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>662.4</v>
+        <v>1.98</v>
       </c>
       <c r="E7" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>10.17</v>
       </c>
       <c r="G7" t="n">
-        <v>1755624960</v>
+        <v>485557697</v>
       </c>
       <c r="H7" t="n">
-        <v>354074659.2</v>
+        <v>36516285</v>
       </c>
       <c r="I7" t="n">
-        <v>285825600</v>
+        <v>43677897.5</v>
       </c>
       <c r="J7" t="n">
-        <v>639900259.2</v>
+        <v>80194182.5</v>
       </c>
       <c r="K7" t="n">
-        <v>-68249059.2</v>
+        <v>7161612.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.89</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>36.45</v>
+        <v>16.52</v>
       </c>
       <c r="N7" t="n">
-        <v>109341049824</v>
+        <v>1710676337.04</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>001399.SZ</t>
+          <t>000838.SZ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>*ST发展</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.07</v>
+        <v>2.12</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.7667</v>
+        <v>-9.7872</v>
       </c>
       <c r="F8" t="n">
-        <v>23.89</v>
+        <v>6.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2861541795</v>
+        <v>154919215</v>
       </c>
       <c r="H8" t="n">
-        <v>477742368.04</v>
+        <v>27879843.68</v>
       </c>
       <c r="I8" t="n">
-        <v>476272058.89</v>
+        <v>13907001</v>
       </c>
       <c r="J8" t="n">
-        <v>954014426.9299999</v>
+        <v>41786844.68</v>
       </c>
       <c r="K8" t="n">
-        <v>-1470309.15</v>
+        <v>-13972842.68</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05</v>
+        <v>-9.02</v>
       </c>
       <c r="M8" t="n">
-        <v>33.34</v>
+        <v>26.97</v>
       </c>
       <c r="N8" t="n">
-        <v>11655441408.17</v>
+        <v>2233983612.6</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>001399.SZ</t>
+          <t>000988.SZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>惠科股份</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.07</v>
+        <v>130.69</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.7667</v>
+        <v>-9.9993</v>
       </c>
       <c r="F9" t="n">
-        <v>23.89</v>
+        <v>6.28</v>
       </c>
       <c r="G9" t="n">
-        <v>5152845645</v>
+        <v>8439029396</v>
       </c>
       <c r="H9" t="n">
-        <v>643271665.04</v>
+        <v>528920230.17</v>
       </c>
       <c r="I9" t="n">
-        <v>767617383.13</v>
+        <v>646269793.99</v>
       </c>
       <c r="J9" t="n">
-        <v>1410889048.17</v>
+        <v>1175190024.16</v>
       </c>
       <c r="K9" t="n">
-        <v>124345718.09</v>
+        <v>117349563.82</v>
       </c>
       <c r="L9" t="n">
-        <v>2.41</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>27.38</v>
+        <v>13.93</v>
       </c>
       <c r="N9" t="n">
-        <v>11655441408.17</v>
+        <v>131341575513.33</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>001896.SZ</t>
+          <t>002079.SZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>苏州固锝</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.95</v>
+        <v>10.21</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0074</v>
+        <v>-5.8986</v>
       </c>
       <c r="F10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="G10" t="n">
-        <v>2006496280</v>
+        <v>2425270565</v>
       </c>
       <c r="H10" t="n">
-        <v>294014341.94</v>
+        <v>514484645.73</v>
       </c>
       <c r="I10" t="n">
-        <v>650697596.45</v>
+        <v>458281260.54</v>
       </c>
       <c r="J10" t="n">
-        <v>944711938.39</v>
+        <v>972765906.27</v>
       </c>
       <c r="K10" t="n">
-        <v>356683254.51</v>
+        <v>-56203385.19</v>
       </c>
       <c r="L10" t="n">
-        <v>17.78</v>
+        <v>-2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>47.08</v>
+        <v>40.11</v>
       </c>
       <c r="N10" t="n">
-        <v>22810430883.5</v>
+        <v>8279698982.55</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002137.SZ</t>
+          <t>002080.SZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>实益达</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.77</v>
+        <v>60.86</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.9589</v>
+        <v>-9.997</v>
       </c>
       <c r="F11" t="n">
-        <v>20.66</v>
+        <v>2.91</v>
       </c>
       <c r="G11" t="n">
-        <v>872429523</v>
+        <v>3069865722</v>
       </c>
       <c r="H11" t="n">
-        <v>113591423.26</v>
+        <v>940321159.0599999</v>
       </c>
       <c r="I11" t="n">
-        <v>153224537</v>
+        <v>855215472.5</v>
       </c>
       <c r="J11" t="n">
-        <v>266815960.26</v>
+        <v>1795536631.56</v>
       </c>
       <c r="K11" t="n">
-        <v>39633113.74</v>
+        <v>-85105686.56</v>
       </c>
       <c r="L11" t="n">
-        <v>4.54</v>
+        <v>-2.77</v>
       </c>
       <c r="M11" t="n">
-        <v>30.58</v>
+        <v>58.49</v>
       </c>
       <c r="N11" t="n">
-        <v>3476937370.37</v>
+        <v>102130601322.24</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002137.SZ</t>
+          <t>002141.SZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>实益达</t>
+          <t>贤丰控股</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.77</v>
+        <v>5.91</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.9589</v>
+        <v>5.3476</v>
       </c>
       <c r="F12" t="n">
-        <v>20.66</v>
+        <v>18.95</v>
       </c>
       <c r="G12" t="n">
-        <v>731779646</v>
+        <v>2113300931</v>
       </c>
       <c r="H12" t="n">
-        <v>113710683.26</v>
+        <v>280337340</v>
       </c>
       <c r="I12" t="n">
-        <v>146031688</v>
+        <v>320601154</v>
       </c>
       <c r="J12" t="n">
-        <v>259742371.26</v>
+        <v>600938494</v>
       </c>
       <c r="K12" t="n">
-        <v>32321004.74</v>
+        <v>40263814</v>
       </c>
       <c r="L12" t="n">
-        <v>4.42</v>
+        <v>1.91</v>
       </c>
       <c r="M12" t="n">
-        <v>35.49</v>
+        <v>28.44</v>
       </c>
       <c r="N12" t="n">
-        <v>3476937370.37</v>
+        <v>6104650566.18</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>002185.SZ</t>
+          <t>002173.SZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>创新医疗</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.11</v>
+        <v>17.44</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.0078</v>
+        <v>10.0315</v>
       </c>
       <c r="F13" t="n">
-        <v>19.3</v>
+        <v>11.64</v>
       </c>
       <c r="G13" t="n">
-        <v>15104876982</v>
+        <v>828419439</v>
       </c>
       <c r="H13" t="n">
-        <v>2410003070.4</v>
+        <v>90376552.09</v>
       </c>
       <c r="I13" t="n">
-        <v>1298956062.61</v>
+        <v>175274930.42</v>
       </c>
       <c r="J13" t="n">
-        <v>3708959133.01</v>
+        <v>265651482.51</v>
       </c>
       <c r="K13" t="n">
-        <v>-1111047007.79</v>
+        <v>84898378.33</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.36</v>
+        <v>10.25</v>
       </c>
       <c r="M13" t="n">
-        <v>24.55</v>
+        <v>32.07</v>
       </c>
       <c r="N13" t="n">
-        <v>76786482104.27</v>
+        <v>7339886140.64</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>002208.SZ</t>
+          <t>002185.SZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>合肥城建</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.91</v>
+        <v>20.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.0053</v>
+        <v>-9.995699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.88</v>
+        <v>15.43</v>
       </c>
       <c r="G14" t="n">
-        <v>1650521091</v>
+        <v>10816341183</v>
       </c>
       <c r="H14" t="n">
-        <v>212985619.5</v>
+        <v>1229201129.66</v>
       </c>
       <c r="I14" t="n">
-        <v>193965597.52</v>
+        <v>1386489936.51</v>
       </c>
       <c r="J14" t="n">
-        <v>406951217.02</v>
+        <v>2615691066.17</v>
       </c>
       <c r="K14" t="n">
-        <v>-19020021.98</v>
+        <v>157288806.85</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.15</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>24.66</v>
+        <v>24.18</v>
       </c>
       <c r="N14" t="n">
-        <v>13579952034.97</v>
+        <v>69111156545.60001</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2534,546 +2534,546 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>002208.SZ</t>
+          <t>002309.SZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>合肥城建</t>
+          <t>中利集团</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.91</v>
+        <v>2.93</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.0053</v>
+        <v>6.9343</v>
       </c>
       <c r="F15" t="n">
-        <v>11.88</v>
+        <v>17.97</v>
       </c>
       <c r="G15" t="n">
-        <v>2032609074</v>
+        <v>1604282001</v>
       </c>
       <c r="H15" t="n">
-        <v>238625926.5</v>
+        <v>306994545.47</v>
       </c>
       <c r="I15" t="n">
-        <v>209482269.52</v>
+        <v>285649711.58</v>
       </c>
       <c r="J15" t="n">
-        <v>448108196.02</v>
+        <v>592644257.05</v>
       </c>
       <c r="K15" t="n">
-        <v>-29143656.98</v>
+        <v>-21344833.89</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.43</v>
+        <v>-1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>22.05</v>
+        <v>36.94</v>
       </c>
       <c r="N15" t="n">
-        <v>13579952034.97</v>
+        <v>7049967662.44</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>002342.SZ</t>
+          <t>002317.SZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>巨力索具</t>
+          <t>众生药业</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.23</v>
+        <v>29.96</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.1473</v>
+        <v>-10.003</v>
       </c>
       <c r="F16" t="n">
-        <v>18.74</v>
+        <v>12.79</v>
       </c>
       <c r="G16" t="n">
-        <v>4044898070</v>
+        <v>3039594332</v>
       </c>
       <c r="H16" t="n">
-        <v>476357791.22</v>
+        <v>297589618.66</v>
       </c>
       <c r="I16" t="n">
-        <v>378862480.5</v>
+        <v>328469520.98</v>
       </c>
       <c r="J16" t="n">
-        <v>855220271.72</v>
+        <v>626059139.64</v>
       </c>
       <c r="K16" t="n">
-        <v>-97495310.72</v>
+        <v>30879902.32</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.41</v>
+        <v>1.02</v>
       </c>
       <c r="M16" t="n">
-        <v>21.14</v>
+        <v>20.6</v>
       </c>
       <c r="N16" t="n">
-        <v>7857098700</v>
+        <v>22818057483.76</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>002350.SZ</t>
+          <t>002354.SZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京科锐</t>
+          <t>天娱数科</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>7.96</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.9471</v>
+        <v>3.5111</v>
       </c>
       <c r="F17" t="n">
-        <v>6.64</v>
+        <v>24.33</v>
       </c>
       <c r="G17" t="n">
-        <v>556799785</v>
+        <v>3119798509</v>
       </c>
       <c r="H17" t="n">
-        <v>80093595.81</v>
+        <v>451601338.71</v>
       </c>
       <c r="I17" t="n">
-        <v>85048083</v>
+        <v>307300160.79</v>
       </c>
       <c r="J17" t="n">
-        <v>165141678.81</v>
+        <v>758901499.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4954487.19</v>
+        <v>-144301177.92</v>
       </c>
       <c r="L17" t="n">
-        <v>0.89</v>
+        <v>-4.63</v>
       </c>
       <c r="M17" t="n">
-        <v>29.66</v>
+        <v>24.33</v>
       </c>
       <c r="N17" t="n">
-        <v>7746031036.6</v>
+        <v>12940522480.84</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>002457.SZ</t>
+          <t>002365.SZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>青龙管业</t>
+          <t>永安药业</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.7</v>
+        <v>13.18</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.3072</v>
+        <v>10.0167</v>
       </c>
       <c r="F18" t="n">
-        <v>17.07</v>
+        <v>10.52</v>
       </c>
       <c r="G18" t="n">
-        <v>1537183461</v>
+        <v>616707827</v>
       </c>
       <c r="H18" t="n">
-        <v>165044412</v>
+        <v>97118076.62</v>
       </c>
       <c r="I18" t="n">
-        <v>117698856.64</v>
+        <v>113595988.8</v>
       </c>
       <c r="J18" t="n">
-        <v>282743268.64</v>
+        <v>210714065.42</v>
       </c>
       <c r="K18" t="n">
-        <v>-47345555.36</v>
+        <v>16477912.18</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.08</v>
+        <v>2.67</v>
       </c>
       <c r="M18" t="n">
-        <v>18.39</v>
+        <v>34.17</v>
       </c>
       <c r="N18" t="n">
-        <v>3899263083.3</v>
+        <v>3232901995.06</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>002517.SZ</t>
+          <t>002396.SZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.18</v>
+        <v>28.51</v>
       </c>
       <c r="E19" t="n">
-        <v>9.9872</v>
+        <v>3.5974</v>
       </c>
       <c r="F19" t="n">
-        <v>6.31</v>
+        <v>23.22</v>
       </c>
       <c r="G19" t="n">
-        <v>1990256490</v>
+        <v>4904851814</v>
       </c>
       <c r="H19" t="n">
-        <v>191746596.16</v>
+        <v>958901937.3</v>
       </c>
       <c r="I19" t="n">
-        <v>473090855.07</v>
+        <v>960723411.3099999</v>
       </c>
       <c r="J19" t="n">
-        <v>664837451.23</v>
+        <v>1919625348.61</v>
       </c>
       <c r="K19" t="n">
-        <v>281344258.91</v>
+        <v>1821474.01</v>
       </c>
       <c r="L19" t="n">
-        <v>14.14</v>
+        <v>0.04</v>
       </c>
       <c r="M19" t="n">
-        <v>33.4</v>
+        <v>39.14</v>
       </c>
       <c r="N19" t="n">
-        <v>32454509042.14</v>
+        <v>21593904672.06</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>002558.SZ</t>
+          <t>002432.SZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>九安医疗</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.56</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>10.0112</v>
+        <v>7.4787</v>
       </c>
       <c r="F20" t="n">
-        <v>7.95</v>
+        <v>14.13</v>
       </c>
       <c r="G20" t="n">
-        <v>4256003148</v>
+        <v>4953862823</v>
       </c>
       <c r="H20" t="n">
-        <v>323896300.17</v>
+        <v>1045649353.96</v>
       </c>
       <c r="I20" t="n">
-        <v>1018478268.06</v>
+        <v>745041225.65</v>
       </c>
       <c r="J20" t="n">
-        <v>1342374568.23</v>
+        <v>1790690579.61</v>
       </c>
       <c r="K20" t="n">
-        <v>694581967.89</v>
+        <v>-300608128.31</v>
       </c>
       <c r="L20" t="n">
-        <v>16.32</v>
+        <v>-6.07</v>
       </c>
       <c r="M20" t="n">
-        <v>31.54</v>
+        <v>36.15</v>
       </c>
       <c r="N20" t="n">
-        <v>56180611862.76</v>
+        <v>33499607040</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>002731.SZ</t>
+          <t>002549.SZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>*ST萃华</t>
+          <t>凯美特气</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.09</v>
+        <v>14.19</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.5238</v>
+        <v>-4.1864</v>
       </c>
       <c r="F21" t="n">
-        <v>38.61</v>
+        <v>5.7</v>
       </c>
       <c r="G21" t="n">
-        <v>188730743</v>
+        <v>2558760206</v>
       </c>
       <c r="H21" t="n">
-        <v>34858860.26</v>
+        <v>303029119.46</v>
       </c>
       <c r="I21" t="n">
-        <v>13271712</v>
+        <v>292838205.85</v>
       </c>
       <c r="J21" t="n">
-        <v>48130572.26</v>
+        <v>595867325.3099999</v>
       </c>
       <c r="K21" t="n">
-        <v>-21587148.26</v>
+        <v>-10190913.61</v>
       </c>
       <c r="L21" t="n">
-        <v>-11.44</v>
+        <v>-0.4</v>
       </c>
       <c r="M21" t="n">
-        <v>25.5</v>
+        <v>23.29</v>
       </c>
       <c r="N21" t="n">
-        <v>479981876</v>
+        <v>9824581673.940001</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>002739.SZ</t>
+          <t>002653.SZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>儒意电影</t>
+          <t>海思科</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.380000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="E22" t="n">
-        <v>9.9648</v>
+        <v>6.8258</v>
       </c>
       <c r="F22" t="n">
-        <v>4.61</v>
+        <v>4.74</v>
       </c>
       <c r="G22" t="n">
-        <v>891958056</v>
+        <v>1885098591</v>
       </c>
       <c r="H22" t="n">
-        <v>67359937</v>
+        <v>205424166.61</v>
       </c>
       <c r="I22" t="n">
-        <v>372397890</v>
+        <v>338851295.91</v>
       </c>
       <c r="J22" t="n">
-        <v>439757827</v>
+        <v>544275462.52</v>
       </c>
       <c r="K22" t="n">
-        <v>305037953</v>
+        <v>133427129.3</v>
       </c>
       <c r="L22" t="n">
-        <v>34.2</v>
+        <v>7.08</v>
       </c>
       <c r="M22" t="n">
-        <v>49.3</v>
+        <v>28.87</v>
       </c>
       <c r="N22" t="n">
-        <v>19529177334.24</v>
+        <v>42508093872.27</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>002821.SZ</t>
+          <t>002674.SZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>凯莱英</t>
+          <t>兴业科技</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>195.75</v>
+        <v>25.84</v>
       </c>
       <c r="E23" t="n">
-        <v>10.0028</v>
+        <v>-9.996499999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7.09</v>
+        <v>7.42</v>
       </c>
       <c r="G23" t="n">
-        <v>4240287773</v>
+        <v>2606927409</v>
       </c>
       <c r="H23" t="n">
-        <v>408376896.33</v>
+        <v>147761928.51</v>
       </c>
       <c r="I23" t="n">
-        <v>821238856.85</v>
+        <v>142877904.76</v>
       </c>
       <c r="J23" t="n">
-        <v>1229615753.18</v>
+        <v>290639833.27</v>
       </c>
       <c r="K23" t="n">
-        <v>412861960.52</v>
+        <v>-4884023.75</v>
       </c>
       <c r="L23" t="n">
-        <v>9.74</v>
+        <v>-0.19</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>11.15</v>
       </c>
       <c r="N23" t="n">
-        <v>62061335203.5</v>
+        <v>7559844767.68</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>002821.SZ</t>
+          <t>002726.SZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>凯莱英</t>
+          <t>ST龙大</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>195.75</v>
+        <v>2.01</v>
       </c>
       <c r="E24" t="n">
-        <v>10.0028</v>
+        <v>9.8361</v>
       </c>
       <c r="F24" t="n">
-        <v>7.09</v>
+        <v>6.46</v>
       </c>
       <c r="G24" t="n">
-        <v>9559452050</v>
+        <v>377928829</v>
       </c>
       <c r="H24" t="n">
-        <v>1070230024.64</v>
+        <v>37450914.25</v>
       </c>
       <c r="I24" t="n">
-        <v>1312420073.63</v>
+        <v>32393474.52</v>
       </c>
       <c r="J24" t="n">
-        <v>2382650098.27</v>
+        <v>69844388.77</v>
       </c>
       <c r="K24" t="n">
-        <v>242190048.99</v>
+        <v>-5057439.73</v>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>-1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>24.92</v>
+        <v>18.48</v>
       </c>
       <c r="N24" t="n">
-        <v>62061335203.5</v>
+        <v>2734234366.05</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3084,271 +3084,271 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>002898.SZ</t>
+          <t>002731.SZ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>赛隆退</t>
+          <t>*ST萃华</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.38</v>
+        <v>2.3</v>
       </c>
       <c r="E25" t="n">
-        <v>-5</v>
+        <v>10.0478</v>
       </c>
       <c r="F25" t="n">
-        <v>6.36</v>
+        <v>35.19</v>
       </c>
       <c r="G25" t="n">
-        <v>2513402</v>
+        <v>164052964</v>
       </c>
       <c r="H25" t="n">
-        <v>977312.5</v>
+        <v>14358209.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1205485</v>
+        <v>18441441.2</v>
       </c>
       <c r="J25" t="n">
-        <v>2182797.5</v>
+        <v>32799650.7</v>
       </c>
       <c r="K25" t="n">
-        <v>228172.5</v>
+        <v>4083231.7</v>
       </c>
       <c r="L25" t="n">
-        <v>9.08</v>
+        <v>2.49</v>
       </c>
       <c r="M25" t="n">
-        <v>86.84999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="N25" t="n">
-        <v>38479731.38</v>
+        <v>528209720</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>日振幅值达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>002975.SZ</t>
+          <t>002739.SZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>博杰股份</t>
+          <t>儒意电影</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>112.07</v>
+        <v>10.32</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.9984</v>
+        <v>10.0213</v>
       </c>
       <c r="F26" t="n">
-        <v>10.18</v>
+        <v>3.98</v>
       </c>
       <c r="G26" t="n">
-        <v>1629317633</v>
+        <v>847772743</v>
       </c>
       <c r="H26" t="n">
-        <v>422002194.64</v>
+        <v>123451287.56</v>
       </c>
       <c r="I26" t="n">
-        <v>267026893.24</v>
+        <v>264143678.43</v>
       </c>
       <c r="J26" t="n">
-        <v>689029087.88</v>
+        <v>387594965.99</v>
       </c>
       <c r="K26" t="n">
-        <v>-154975301.4</v>
+        <v>140692390.87</v>
       </c>
       <c r="L26" t="n">
-        <v>-9.51</v>
+        <v>16.6</v>
       </c>
       <c r="M26" t="n">
-        <v>42.29</v>
+        <v>45.72</v>
       </c>
       <c r="N26" t="n">
-        <v>15393267150.73</v>
+        <v>21486259071.36</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>日振幅值达到15%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>003020.SZ</t>
+          <t>002739.SZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>立方制药</t>
+          <t>儒意电影</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21.91</v>
+        <v>10.32</v>
       </c>
       <c r="E27" t="n">
-        <v>5.3365</v>
+        <v>10.0213</v>
       </c>
       <c r="F27" t="n">
-        <v>27.48</v>
+        <v>3.98</v>
       </c>
       <c r="G27" t="n">
-        <v>970974940</v>
+        <v>1739730799</v>
       </c>
       <c r="H27" t="n">
-        <v>59612146.16</v>
+        <v>157574484.55</v>
       </c>
       <c r="I27" t="n">
-        <v>77412344.09999999</v>
+        <v>539872202.67</v>
       </c>
       <c r="J27" t="n">
-        <v>137024490.26</v>
+        <v>697446687.22</v>
       </c>
       <c r="K27" t="n">
-        <v>17800197.94</v>
+        <v>382297718.12</v>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>21.97</v>
       </c>
       <c r="M27" t="n">
-        <v>14.11</v>
+        <v>40.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3692892267.05</v>
+        <v>21486259071.36</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>日换手率达到20%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200016.SZ</t>
+          <t>002788.SZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>*ST康佳B</t>
+          <t>鹭燕医药</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.74</v>
+        <v>12.3</v>
       </c>
       <c r="E28" t="n">
-        <v>8.823499999999999</v>
+        <v>9.821400000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>1521864</v>
+        <v>1568219453</v>
       </c>
       <c r="H28" t="n">
-        <v>698310.71</v>
+        <v>173706204.75</v>
       </c>
       <c r="I28" t="n">
-        <v>720637.72</v>
+        <v>160227173.53</v>
       </c>
       <c r="J28" t="n">
-        <v>1418948.43</v>
+        <v>333933378.28</v>
       </c>
       <c r="K28" t="n">
-        <v>22327.01</v>
+        <v>-13479031.22</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>-0.86</v>
       </c>
       <c r="M28" t="n">
-        <v>93.23999999999999</v>
+        <v>21.29</v>
       </c>
       <c r="N28" t="n">
-        <v>4751544069.92</v>
+        <v>4696467585.9</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>日涨幅偏离值达到7%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200521.SZ</t>
+          <t>002851.SZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>虹美菱B</t>
+          <t>麦格米特</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.6</v>
+        <v>151.77</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.0346</v>
+        <v>-9.998200000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3</v>
+        <v>7.52</v>
       </c>
       <c r="G29" t="n">
-        <v>1008932</v>
+        <v>5347065613</v>
       </c>
       <c r="H29" t="n">
-        <v>1008931.67</v>
+        <v>1361986176.14</v>
       </c>
       <c r="I29" t="n">
-        <v>409166.56</v>
+        <v>1171657657.51</v>
       </c>
       <c r="J29" t="n">
-        <v>1418098.23</v>
+        <v>2533643833.65</v>
       </c>
       <c r="K29" t="n">
-        <v>-599765.11</v>
+        <v>-190328518.63</v>
       </c>
       <c r="L29" t="n">
-        <v>-59.45</v>
+        <v>-3.56</v>
       </c>
       <c r="M29" t="n">
-        <v>140.55</v>
+        <v>47.38</v>
       </c>
       <c r="N29" t="n">
-        <v>4848965650.4</v>
+        <v>69996510221.78999</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3359,1481 +3359,1473 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200553.SZ</t>
+          <t>002881.SZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>安道麦B</t>
+          <t>美格智能</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.71</v>
+        <v>39.05</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.1356</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>0.65</v>
+        <v>6.79</v>
       </c>
       <c r="G30" t="n">
-        <v>2330701</v>
+        <v>470338400</v>
       </c>
       <c r="H30" t="n">
-        <v>1302512.41</v>
+        <v>82387761.18000001</v>
       </c>
       <c r="I30" t="n">
-        <v>924015.98</v>
+        <v>167249308.45</v>
       </c>
       <c r="J30" t="n">
-        <v>2226528.39</v>
+        <v>249637069.63</v>
       </c>
       <c r="K30" t="n">
-        <v>-378496.43</v>
+        <v>84861547.27</v>
       </c>
       <c r="L30" t="n">
-        <v>-16.24</v>
+        <v>18.04</v>
       </c>
       <c r="M30" t="n">
-        <v>95.53</v>
+        <v>53.08</v>
       </c>
       <c r="N30" t="n">
-        <v>12257196339.39</v>
+        <v>7106704033</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>日跌幅偏离值达到7%的前5只证券</t>
+          <t>日涨幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300149.SZ</t>
+          <t>002898.SZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>睿智医药</t>
+          <t>赛隆退</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.39</v>
+        <v>0.37</v>
       </c>
       <c r="E31" t="n">
-        <v>19.9769</v>
+        <v>-2.6316</v>
       </c>
       <c r="F31" t="n">
-        <v>15.58</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>750365469</v>
+        <v>3762649</v>
       </c>
       <c r="H31" t="n">
-        <v>44637194.19</v>
+        <v>1881528.99</v>
       </c>
       <c r="I31" t="n">
-        <v>174894161.4</v>
+        <v>1465052</v>
       </c>
       <c r="J31" t="n">
-        <v>219531355.59</v>
+        <v>3346580.99</v>
       </c>
       <c r="K31" t="n">
-        <v>130256967.21</v>
+        <v>-416476.99</v>
       </c>
       <c r="L31" t="n">
-        <v>17.36</v>
+        <v>-11.07</v>
       </c>
       <c r="M31" t="n">
-        <v>29.26</v>
+        <v>88.94</v>
       </c>
       <c r="N31" t="n">
-        <v>4930714442.91</v>
+        <v>37467106.87</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>退市整理期</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300164.SZ</t>
+          <t>002900.SZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>通源石油</t>
+          <t>哈三联</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.83</v>
+        <v>12.11</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.833</v>
+        <v>8.2216</v>
       </c>
       <c r="F32" t="n">
-        <v>40.18</v>
+        <v>20.92</v>
       </c>
       <c r="G32" t="n">
-        <v>2560677564</v>
+        <v>523549498</v>
       </c>
       <c r="H32" t="n">
-        <v>261307127.39</v>
+        <v>75214988.19</v>
       </c>
       <c r="I32" t="n">
-        <v>343857583.54</v>
+        <v>48783869.06</v>
       </c>
       <c r="J32" t="n">
-        <v>605164710.9299999</v>
+        <v>123998857.25</v>
       </c>
       <c r="K32" t="n">
-        <v>82550456.15000001</v>
+        <v>-26431119.13</v>
       </c>
       <c r="L32" t="n">
-        <v>3.22</v>
+        <v>-5.05</v>
       </c>
       <c r="M32" t="n">
-        <v>23.63</v>
+        <v>23.68</v>
       </c>
       <c r="N32" t="n">
-        <v>6316172725.74</v>
+        <v>1951192264</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300214.SZ</t>
+          <t>002980.SZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>日科化学</t>
+          <t>华盛昌</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.58</v>
+        <v>107.37</v>
       </c>
       <c r="E33" t="n">
-        <v>-13.5821</v>
+        <v>5.1204</v>
       </c>
       <c r="F33" t="n">
-        <v>17.53</v>
+        <v>17.94</v>
       </c>
       <c r="G33" t="n">
-        <v>993879136</v>
+        <v>3187547026</v>
       </c>
       <c r="H33" t="n">
-        <v>186640655</v>
+        <v>737841149.42</v>
       </c>
       <c r="I33" t="n">
-        <v>195630090</v>
+        <v>695233507.4</v>
       </c>
       <c r="J33" t="n">
-        <v>382270745</v>
+        <v>1433074656.82</v>
       </c>
       <c r="K33" t="n">
-        <v>8989435</v>
+        <v>-42607642.02</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9</v>
+        <v>-1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>38.46</v>
+        <v>44.96</v>
       </c>
       <c r="N33" t="n">
-        <v>5383572270.12</v>
+        <v>10875189914.28</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>日振幅值达到30%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300231.SZ</t>
+          <t>003010.SZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>银信科技</t>
+          <t>若羽臣</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.08</v>
+        <v>26.23</v>
       </c>
       <c r="E34" t="n">
-        <v>19.9472</v>
+        <v>6.7997</v>
       </c>
       <c r="F34" t="n">
-        <v>11.63</v>
+        <v>10.25</v>
       </c>
       <c r="G34" t="n">
-        <v>446358624</v>
+        <v>934666393</v>
       </c>
       <c r="H34" t="n">
-        <v>53784744.61</v>
+        <v>218989873.71</v>
       </c>
       <c r="I34" t="n">
-        <v>125731415.72</v>
+        <v>165690209.57</v>
       </c>
       <c r="J34" t="n">
-        <v>179516160.33</v>
+        <v>384680083.28</v>
       </c>
       <c r="K34" t="n">
-        <v>71946671.11</v>
+        <v>-53299664.14</v>
       </c>
       <c r="L34" t="n">
-        <v>16.12</v>
+        <v>-5.7</v>
       </c>
       <c r="M34" t="n">
-        <v>40.22</v>
+        <v>41.16</v>
       </c>
       <c r="N34" t="n">
-        <v>4038091522.88</v>
+        <v>5931709433.86</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300528.SZ</t>
+          <t>003020.SZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>幸福蓝海</t>
+          <t>立方制药</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.99</v>
+        <v>19.72</v>
       </c>
       <c r="E35" t="n">
-        <v>19.9859</v>
+        <v>-9.9954</v>
       </c>
       <c r="F35" t="n">
-        <v>10.46</v>
+        <v>22.88</v>
       </c>
       <c r="G35" t="n">
-        <v>633217887</v>
+        <v>782143751</v>
       </c>
       <c r="H35" t="n">
-        <v>80367513.19</v>
+        <v>98143438.23999999</v>
       </c>
       <c r="I35" t="n">
-        <v>123944152.86</v>
+        <v>80044293.26000001</v>
       </c>
       <c r="J35" t="n">
-        <v>204311666.05</v>
+        <v>178187731.5</v>
       </c>
       <c r="K35" t="n">
-        <v>43576639.67</v>
+        <v>-18099144.98</v>
       </c>
       <c r="L35" t="n">
-        <v>6.88</v>
+        <v>-2.31</v>
       </c>
       <c r="M35" t="n">
-        <v>32.27</v>
+        <v>22.78</v>
       </c>
       <c r="N35" t="n">
-        <v>6330610837.46</v>
+        <v>3323771588.6</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日换手率达到20%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300534.SZ</t>
+          <t>110101.SH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>N宝钛转</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.8</v>
+        <v>135.046</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1519</v>
-      </c>
-      <c r="F36" t="n">
-        <v>30.1</v>
-      </c>
+        <v>35.046</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>989128857</v>
+        <v>765803340</v>
       </c>
       <c r="H36" t="n">
-        <v>95114349.95999999</v>
+        <v>97590710</v>
       </c>
       <c r="I36" t="n">
-        <v>69473498.40000001</v>
+        <v>265492150</v>
       </c>
       <c r="J36" t="n">
-        <v>164587848.36</v>
+        <v>363082860</v>
       </c>
       <c r="K36" t="n">
-        <v>-25640851.56</v>
+        <v>167901440</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.59</v>
+        <v>21.92</v>
       </c>
       <c r="M36" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3262156070.4</v>
-      </c>
+        <v>47.41</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>日换手率达到30%的前5只证券</t>
+          <t>向不特定对象发行的可转债上市首日交易公开信息</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300692.SZ</t>
+          <t>123273.SZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>中赋科技</t>
+          <t>三江转债</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9.67</v>
+        <v>277.6</v>
       </c>
       <c r="E37" t="n">
-        <v>18.2152</v>
-      </c>
-      <c r="F37" t="n">
-        <v>19.95</v>
-      </c>
+        <v>-20</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>959526177</v>
+        <v>2324501792</v>
       </c>
       <c r="H37" t="n">
-        <v>87361666.8</v>
+        <v>408099032.68</v>
       </c>
       <c r="I37" t="n">
-        <v>190580073.41</v>
+        <v>408239061.53</v>
       </c>
       <c r="J37" t="n">
-        <v>277941740.21</v>
+        <v>816338094.21</v>
       </c>
       <c r="K37" t="n">
-        <v>103218406.61</v>
+        <v>140028.85</v>
       </c>
       <c r="L37" t="n">
-        <v>10.76</v>
+        <v>0.01</v>
       </c>
       <c r="M37" t="n">
-        <v>28.97</v>
-      </c>
-      <c r="N37" t="n">
-        <v>4961503336.47</v>
-      </c>
+        <v>35.12</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>日跌幅达到15%的前5只可转债</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300821.SZ</t>
+          <t>200056.SZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>*ST皇庭B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19.51</v>
+        <v>0.53</v>
       </c>
       <c r="E38" t="n">
-        <v>-16.0138</v>
+        <v>-7.0175</v>
       </c>
       <c r="F38" t="n">
-        <v>13.82</v>
+        <v>0.05</v>
       </c>
       <c r="G38" t="n">
-        <v>3394372829</v>
+        <v>58063</v>
       </c>
       <c r="H38" t="n">
-        <v>418623965.76</v>
+        <v>50418.76</v>
       </c>
       <c r="I38" t="n">
-        <v>540987767.22</v>
+        <v>52266.68</v>
       </c>
       <c r="J38" t="n">
-        <v>959611732.98</v>
+        <v>102685.44</v>
       </c>
       <c r="K38" t="n">
-        <v>122363801.46</v>
+        <v>1847.92</v>
       </c>
       <c r="L38" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="M38" t="n">
-        <v>28.27</v>
+        <v>176.85</v>
       </c>
       <c r="N38" t="n">
-        <v>23407917532.5</v>
+        <v>1891194311.96</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>日跌幅达到15%的前5只证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300937.SZ</t>
+          <t>200521.SZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>药易购</t>
+          <t>虹美菱B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>25.36</v>
+        <v>2.41</v>
       </c>
       <c r="E39" t="n">
-        <v>9.263199999999999</v>
+        <v>-7.3077</v>
       </c>
       <c r="F39" t="n">
-        <v>29.62</v>
+        <v>0.87</v>
       </c>
       <c r="G39" t="n">
-        <v>763570310</v>
+        <v>2714350</v>
       </c>
       <c r="H39" t="n">
-        <v>152311490.08</v>
+        <v>1166021.77</v>
       </c>
       <c r="I39" t="n">
-        <v>98321155.18000001</v>
+        <v>939122.46</v>
       </c>
       <c r="J39" t="n">
-        <v>250632645.26</v>
+        <v>2105144.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-53990334.9</v>
+        <v>-226899.31</v>
       </c>
       <c r="L39" t="n">
-        <v>-7.07</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>32.82</v>
+        <v>77.56</v>
       </c>
       <c r="N39" t="n">
-        <v>1644955655.52</v>
+        <v>4855818774.74</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
+          <t>日跌幅偏离值达到7%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>301520.SZ</t>
+          <t>300149.SZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>万邦医药</t>
+          <t>睿智医药</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>58.79</v>
+        <v>11.09</v>
       </c>
       <c r="E40" t="n">
-        <v>20.0041</v>
+        <v>6.7372</v>
       </c>
       <c r="F40" t="n">
-        <v>54.06</v>
+        <v>27.21</v>
       </c>
       <c r="G40" t="n">
-        <v>964698381</v>
+        <v>2148901215</v>
       </c>
       <c r="H40" t="n">
-        <v>56026477.65</v>
+        <v>224856068.75</v>
       </c>
       <c r="I40" t="n">
-        <v>72697628.52</v>
+        <v>239745881.15</v>
       </c>
       <c r="J40" t="n">
-        <v>128724106.17</v>
+        <v>464601949.9</v>
       </c>
       <c r="K40" t="n">
-        <v>16671150.87</v>
+        <v>14889812.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>13.34</v>
+        <v>21.62</v>
       </c>
       <c r="N40" t="n">
-        <v>1922341463.97</v>
+        <v>5262908871.21</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>日涨幅达到15%的前5只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>600058.SH</t>
+          <t>300164.SZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>五矿发展</t>
+          <t>通源石油</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.880000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.6876</v>
+        <v>-8.9566</v>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>31.13</v>
       </c>
       <c r="G41" t="n">
-        <v>599713397</v>
+        <v>1839769464</v>
       </c>
       <c r="H41" t="n">
-        <v>95712397.23999999</v>
+        <v>260090776.94</v>
       </c>
       <c r="I41" t="n">
-        <v>59230802.5</v>
+        <v>173320289.96</v>
       </c>
       <c r="J41" t="n">
-        <v>154943199.74</v>
+        <v>433411066.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-36481594.74</v>
+        <v>-86770486.98</v>
       </c>
       <c r="L41" t="n">
-        <v>-6.08</v>
+        <v>-4.72</v>
       </c>
       <c r="M41" t="n">
-        <v>25.84</v>
+        <v>23.56</v>
       </c>
       <c r="N41" t="n">
-        <v>9518567113.68</v>
+        <v>5750458271.08</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>600118.SH</t>
+          <t>300231.SZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中国卫星</t>
+          <t>银信科技</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>73.92</v>
+        <v>10.06</v>
       </c>
       <c r="E42" t="n">
-        <v>-9.9963</v>
+        <v>10.793</v>
       </c>
       <c r="F42" t="n">
-        <v>7.11</v>
+        <v>18.88</v>
       </c>
       <c r="G42" t="n">
-        <v>8561449632</v>
+        <v>1258079381</v>
       </c>
       <c r="H42" t="n">
-        <v>745201508.27</v>
+        <v>163208642.62</v>
       </c>
       <c r="I42" t="n">
-        <v>468488193.56</v>
+        <v>343272484.89</v>
       </c>
       <c r="J42" t="n">
-        <v>1213689701.83</v>
+        <v>506481127.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-276713314.71</v>
+        <v>180063842.27</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.23</v>
+        <v>14.31</v>
       </c>
       <c r="M42" t="n">
-        <v>14.18</v>
+        <v>40.26</v>
       </c>
       <c r="N42" t="n">
-        <v>87409596859.2</v>
+        <v>4473920784.16</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600186.SH</t>
+          <t>300528.SZ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>莲花控股</t>
+          <t>幸福蓝海</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.25</v>
+        <v>17.99</v>
       </c>
       <c r="E43" t="n">
-        <v>3.0151</v>
+        <v>5.8858</v>
       </c>
       <c r="F43" t="n">
-        <v>15.29</v>
+        <v>14.53</v>
       </c>
       <c r="G43" t="n">
-        <v>2822522723</v>
+        <v>1563528565</v>
       </c>
       <c r="H43" t="n">
-        <v>368066675.2</v>
+        <v>184815557.4</v>
       </c>
       <c r="I43" t="n">
-        <v>688002016.64</v>
+        <v>179393201.12</v>
       </c>
       <c r="J43" t="n">
-        <v>1056068691.84</v>
+        <v>364208758.52</v>
       </c>
       <c r="K43" t="n">
-        <v>319935341.44</v>
+        <v>-5422356.28</v>
       </c>
       <c r="L43" t="n">
-        <v>11.34</v>
+        <v>-0.35</v>
       </c>
       <c r="M43" t="n">
-        <v>37.42</v>
+        <v>23.29</v>
       </c>
       <c r="N43" t="n">
-        <v>18338667482.75</v>
+        <v>6703218891.46</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>600227.SH</t>
+          <t>300534.SZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>赤天化</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.92</v>
+        <v>11.58</v>
       </c>
       <c r="E44" t="n">
-        <v>10.1887</v>
+        <v>7.2222</v>
       </c>
       <c r="F44" t="n">
-        <v>13.28</v>
+        <v>32.28</v>
       </c>
       <c r="G44" t="n">
-        <v>478566762</v>
+        <v>1037152337</v>
       </c>
       <c r="H44" t="n">
-        <v>79245379</v>
+        <v>100603420.16</v>
       </c>
       <c r="I44" t="n">
-        <v>67909384</v>
+        <v>85366474.15000001</v>
       </c>
       <c r="J44" t="n">
-        <v>147154763</v>
+        <v>185969894.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-11335995</v>
+        <v>-15236946.01</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.37</v>
+        <v>-1.47</v>
       </c>
       <c r="M44" t="n">
-        <v>30.75</v>
+        <v>17.93</v>
       </c>
       <c r="N44" t="n">
-        <v>3730591424.76</v>
+        <v>3497756231.04</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>600227.SH</t>
+          <t>300590.SZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>赤天化</t>
+          <t>移为通信</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.92</v>
+        <v>12.22</v>
       </c>
       <c r="E45" t="n">
-        <v>10.1887</v>
+        <v>-17.8763</v>
       </c>
       <c r="F45" t="n">
-        <v>13.28</v>
+        <v>17.36</v>
       </c>
       <c r="G45" t="n">
-        <v>839279692</v>
+        <v>796017626</v>
       </c>
       <c r="H45" t="n">
-        <v>133837648.1</v>
+        <v>161975395.1</v>
       </c>
       <c r="I45" t="n">
-        <v>126651965</v>
+        <v>134683545.42</v>
       </c>
       <c r="J45" t="n">
-        <v>260489613.1</v>
+        <v>296658940.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-7185683.1</v>
+        <v>-27291849.68</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.86</v>
+        <v>-3.43</v>
       </c>
       <c r="M45" t="n">
-        <v>31.04</v>
+        <v>37.27</v>
       </c>
       <c r="N45" t="n">
-        <v>3730591424.76</v>
+        <v>4372494326.46</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>600257.SH</t>
+          <t>300591.SZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>大湖股份</t>
+          <t>万里马</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.9</v>
+        <v>7.3</v>
       </c>
       <c r="E46" t="n">
-        <v>10.1124</v>
+        <v>18.8925</v>
       </c>
       <c r="F46" t="n">
-        <v>2.68</v>
+        <v>18.96</v>
       </c>
       <c r="G46" t="n">
-        <v>62644856</v>
+        <v>470686952</v>
       </c>
       <c r="H46" t="n">
-        <v>7450166</v>
+        <v>49232750.81</v>
       </c>
       <c r="I46" t="n">
-        <v>18156622.8</v>
+        <v>91979629.8</v>
       </c>
       <c r="J46" t="n">
-        <v>25606788.8</v>
+        <v>141212380.61</v>
       </c>
       <c r="K46" t="n">
-        <v>10706456.8</v>
+        <v>42746878.99</v>
       </c>
       <c r="L46" t="n">
-        <v>17.09</v>
+        <v>9.08</v>
       </c>
       <c r="M46" t="n">
-        <v>40.88</v>
+        <v>30</v>
       </c>
       <c r="N46" t="n">
-        <v>2358062221.2</v>
+        <v>2558247237.1</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>600288.SH</t>
+          <t>300596.SZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>大恒科技</t>
+          <t>利安隆</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.46</v>
+        <v>38.07</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.0116</v>
+        <v>-16.2376</v>
       </c>
       <c r="F47" t="n">
-        <v>3.3</v>
+        <v>7.92</v>
       </c>
       <c r="G47" t="n">
-        <v>226137313</v>
+        <v>719134785</v>
       </c>
       <c r="H47" t="n">
-        <v>60348868.14</v>
+        <v>261245007.91</v>
       </c>
       <c r="I47" t="n">
-        <v>30309424</v>
+        <v>184377024.32</v>
       </c>
       <c r="J47" t="n">
-        <v>90658292.14</v>
+        <v>445622032.23</v>
       </c>
       <c r="K47" t="n">
-        <v>-30039444.14</v>
+        <v>-76867983.59</v>
       </c>
       <c r="L47" t="n">
-        <v>-13.28</v>
+        <v>-10.69</v>
       </c>
       <c r="M47" t="n">
-        <v>40.09</v>
+        <v>61.97</v>
       </c>
       <c r="N47" t="n">
-        <v>6752928000</v>
+        <v>8553863023.2</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>600343.SH</t>
+          <t>300689.SZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>航天动力</t>
+          <t>澄天伟业</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20.21</v>
+        <v>54.75</v>
       </c>
       <c r="E48" t="n">
-        <v>-10.0178</v>
+        <v>-17.0455</v>
       </c>
       <c r="F48" t="n">
-        <v>7.55</v>
+        <v>7.71</v>
       </c>
       <c r="G48" t="n">
-        <v>1000237660</v>
+        <v>461467244</v>
       </c>
       <c r="H48" t="n">
-        <v>97404023.18000001</v>
+        <v>104306115.9</v>
       </c>
       <c r="I48" t="n">
-        <v>103315481.6</v>
+        <v>123107530.7</v>
       </c>
       <c r="J48" t="n">
-        <v>200719504.78</v>
+        <v>227413646.6</v>
       </c>
       <c r="K48" t="n">
-        <v>5911458.42</v>
+        <v>18801414.8</v>
       </c>
       <c r="L48" t="n">
-        <v>0.59</v>
+        <v>4.07</v>
       </c>
       <c r="M48" t="n">
-        <v>20.07</v>
+        <v>49.28</v>
       </c>
       <c r="N48" t="n">
-        <v>12898150293.08</v>
+        <v>5539724026.5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>600343.SH</t>
+          <t>300805.SZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>航天动力</t>
+          <t>电声股份</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20.21</v>
+        <v>8.83</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.0178</v>
+        <v>19.9728</v>
       </c>
       <c r="F49" t="n">
-        <v>7.55</v>
+        <v>15.04</v>
       </c>
       <c r="G49" t="n">
-        <v>1279356349</v>
+        <v>367283668</v>
       </c>
       <c r="H49" t="n">
-        <v>107505838.18</v>
+        <v>45960440.89</v>
       </c>
       <c r="I49" t="n">
-        <v>104109213.6</v>
+        <v>68392305</v>
       </c>
       <c r="J49" t="n">
-        <v>211615051.78</v>
+        <v>114352745.89</v>
       </c>
       <c r="K49" t="n">
-        <v>-3396624.58</v>
+        <v>22431864.11</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.27</v>
+        <v>6.11</v>
       </c>
       <c r="M49" t="n">
-        <v>16.54</v>
+        <v>31.13</v>
       </c>
       <c r="N49" t="n">
-        <v>12898150293.08</v>
+        <v>2546142438.16</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>600403.SH</t>
+          <t>300968.SZ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>大有能源</t>
+          <t>格林精密</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.63</v>
+        <v>10.24</v>
       </c>
       <c r="E50" t="n">
-        <v>9.960900000000001</v>
+        <v>20.0469</v>
       </c>
       <c r="F50" t="n">
-        <v>2.91</v>
+        <v>3.93</v>
       </c>
       <c r="G50" t="n">
-        <v>560509448</v>
+        <v>164026361</v>
       </c>
       <c r="H50" t="n">
-        <v>111197961.44</v>
+        <v>26388534</v>
       </c>
       <c r="I50" t="n">
-        <v>94893858.94</v>
+        <v>39845031</v>
       </c>
       <c r="J50" t="n">
-        <v>206091820.38</v>
+        <v>66233565</v>
       </c>
       <c r="K50" t="n">
-        <v>-16304102.5</v>
+        <v>13456497</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>36.77</v>
+        <v>40.38</v>
       </c>
       <c r="N50" t="n">
-        <v>13460273823.26</v>
+        <v>4233011200</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>600488.SH</t>
+          <t>301042.SZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>津药药业</t>
+          <t>安联锐视</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6.98</v>
+        <v>52.04</v>
       </c>
       <c r="E51" t="n">
-        <v>7.8825</v>
+        <v>-19.2552</v>
       </c>
       <c r="F51" t="n">
-        <v>16.86</v>
+        <v>3.83</v>
       </c>
       <c r="G51" t="n">
-        <v>1230457536</v>
+        <v>210251900</v>
       </c>
       <c r="H51" t="n">
-        <v>108405816.55</v>
+        <v>72820576.8</v>
       </c>
       <c r="I51" t="n">
-        <v>77102900</v>
+        <v>56232064</v>
       </c>
       <c r="J51" t="n">
-        <v>185508716.55</v>
+        <v>129052640.8</v>
       </c>
       <c r="K51" t="n">
-        <v>-31302916.55</v>
+        <v>-16588512.8</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.54</v>
+        <v>-7.89</v>
       </c>
       <c r="M51" t="n">
-        <v>15.08</v>
+        <v>61.38</v>
       </c>
       <c r="N51" t="n">
-        <v>7621369026.4</v>
+        <v>4800743288.96</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>日跌幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>600664.SH</t>
+          <t>301139.SZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>*ST元道</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.49</v>
+        <v>3.03</v>
       </c>
       <c r="E52" t="n">
-        <v>10.049</v>
+        <v>10.1818</v>
       </c>
       <c r="F52" t="n">
-        <v>4.43</v>
+        <v>24.1</v>
       </c>
       <c r="G52" t="n">
-        <v>494184337</v>
+        <v>53078193</v>
       </c>
       <c r="H52" t="n">
-        <v>35222688</v>
+        <v>6585860</v>
       </c>
       <c r="I52" t="n">
-        <v>147476110.77</v>
+        <v>6349203</v>
       </c>
       <c r="J52" t="n">
-        <v>182698798.77</v>
+        <v>12935063</v>
       </c>
       <c r="K52" t="n">
-        <v>112253422.77</v>
+        <v>-236657</v>
       </c>
       <c r="L52" t="n">
-        <v>22.71</v>
+        <v>-0.45</v>
       </c>
       <c r="M52" t="n">
-        <v>36.97</v>
+        <v>24.37</v>
       </c>
       <c r="N52" t="n">
-        <v>11308109343.24</v>
+        <v>230786458.44</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日振幅值达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>600721.SH</t>
+          <t>301176.SZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>百花医药</t>
+          <t>逸豪新材</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.57</v>
+        <v>58.2</v>
       </c>
       <c r="E53" t="n">
-        <v>10.0291</v>
+        <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>5.98</v>
+        <v>6.74</v>
       </c>
       <c r="G53" t="n">
-        <v>171244390</v>
+        <v>606740142</v>
       </c>
       <c r="H53" t="n">
-        <v>19906914</v>
+        <v>66921435.82</v>
       </c>
       <c r="I53" t="n">
-        <v>37592674</v>
+        <v>85510971.09999999</v>
       </c>
       <c r="J53" t="n">
-        <v>57499588</v>
+        <v>152432406.92</v>
       </c>
       <c r="K53" t="n">
-        <v>17685760</v>
+        <v>18589535.28</v>
       </c>
       <c r="L53" t="n">
-        <v>10.33</v>
+        <v>3.06</v>
       </c>
       <c r="M53" t="n">
-        <v>33.58</v>
+        <v>25.12</v>
       </c>
       <c r="N53" t="n">
-        <v>2911025596.95</v>
+        <v>9547919985.6</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>日涨幅达到15%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>600746.SH</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>江苏索普</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.31</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>9.930300000000001</v>
+        <v>13.3696</v>
       </c>
       <c r="F54" t="n">
-        <v>3.93</v>
+        <v>56.12</v>
       </c>
       <c r="G54" t="n">
-        <v>388211469</v>
+        <v>1133012888</v>
       </c>
       <c r="H54" t="n">
-        <v>72574092.68000001</v>
+        <v>98166966.79000001</v>
       </c>
       <c r="I54" t="n">
-        <v>83389806.18000001</v>
+        <v>87587568.67</v>
       </c>
       <c r="J54" t="n">
-        <v>155963898.86</v>
+        <v>185754535.46</v>
       </c>
       <c r="K54" t="n">
-        <v>10815713.5</v>
+        <v>-10579398.12</v>
       </c>
       <c r="L54" t="n">
-        <v>2.79</v>
+        <v>-0.93</v>
       </c>
       <c r="M54" t="n">
-        <v>40.17</v>
+        <v>16.39</v>
       </c>
       <c r="N54" t="n">
-        <v>7369088598.04</v>
+        <v>2179351225.95</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>日换手率达到30%的前5只证券</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>600829.SH</t>
+          <t>301520.SZ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>人民同泰</t>
+          <t>万邦医药</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9.890000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>10.0111</v>
+        <v>13.3696</v>
       </c>
       <c r="F55" t="n">
-        <v>4.24</v>
+        <v>56.12</v>
       </c>
       <c r="G55" t="n">
-        <v>394598105</v>
+        <v>2097711268</v>
       </c>
       <c r="H55" t="n">
-        <v>57693646</v>
+        <v>125997203.41</v>
       </c>
       <c r="I55" t="n">
-        <v>75987873.56</v>
+        <v>133786040.09</v>
       </c>
       <c r="J55" t="n">
-        <v>133681519.56</v>
+        <v>259783243.5</v>
       </c>
       <c r="K55" t="n">
-        <v>18294227.56</v>
+        <v>7788836.68</v>
       </c>
       <c r="L55" t="n">
-        <v>4.64</v>
+        <v>0.37</v>
       </c>
       <c r="M55" t="n">
-        <v>33.88</v>
+        <v>12.38</v>
       </c>
       <c r="N55" t="n">
-        <v>5735098224.33</v>
+        <v>2179351225.95</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>连续三个交易日内，涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>600844.SH</t>
+          <t>600162.SH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>金煤科技</t>
+          <t>香江控股</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>9.881399999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>11.29</v>
+        <v>10.56</v>
       </c>
       <c r="G56" t="n">
-        <v>337597693</v>
+        <v>1064306840</v>
       </c>
       <c r="H56" t="n">
-        <v>65931657</v>
+        <v>211285399.76</v>
       </c>
       <c r="I56" t="n">
-        <v>60403066</v>
+        <v>176884835.93</v>
       </c>
       <c r="J56" t="n">
-        <v>126334723</v>
+        <v>388170235.69</v>
       </c>
       <c r="K56" t="n">
-        <v>-5528591</v>
+        <v>-34400563.83</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.64</v>
+        <v>-3.23</v>
       </c>
       <c r="M56" t="n">
-        <v>37.42</v>
+        <v>36.47</v>
       </c>
       <c r="N56" t="n">
-        <v>2478005244.85</v>
+        <v>9086257979.16</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4844,766 +4836,766 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>600879.SH</t>
+          <t>600288.SH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>航天电子</t>
+          <t>大恒科技</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>17.38</v>
+        <v>13.91</v>
       </c>
       <c r="E57" t="n">
-        <v>-9.9948</v>
+        <v>-10.0259</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>2.14</v>
       </c>
       <c r="G57" t="n">
-        <v>14972467733</v>
+        <v>129831767</v>
       </c>
       <c r="H57" t="n">
-        <v>1042229880.97</v>
+        <v>73161036</v>
       </c>
       <c r="I57" t="n">
-        <v>907308535.8099999</v>
+        <v>43923607</v>
       </c>
       <c r="J57" t="n">
-        <v>1949538416.78</v>
+        <v>117084643</v>
       </c>
       <c r="K57" t="n">
-        <v>-134921345.16</v>
+        <v>-29237429</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.9</v>
+        <v>-22.52</v>
       </c>
       <c r="M57" t="n">
-        <v>13.02</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>57341822424.92</v>
+        <v>6075888000</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>603201.SH</t>
+          <t>600360.SH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>常润股份</t>
+          <t>华微电子</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16.9</v>
+        <v>12.88</v>
       </c>
       <c r="E58" t="n">
-        <v>7.0298</v>
+        <v>-9.993</v>
       </c>
       <c r="F58" t="n">
-        <v>6.38</v>
+        <v>13.58</v>
       </c>
       <c r="G58" t="n">
-        <v>455679610</v>
+        <v>7079348815</v>
       </c>
       <c r="H58" t="n">
-        <v>60931798.42</v>
+        <v>1039052236.85</v>
       </c>
       <c r="I58" t="n">
-        <v>91246169.70999999</v>
+        <v>897971289.1</v>
       </c>
       <c r="J58" t="n">
-        <v>152177968.13</v>
+        <v>1937023525.95</v>
       </c>
       <c r="K58" t="n">
-        <v>30314371.29</v>
+        <v>-141080947.75</v>
       </c>
       <c r="L58" t="n">
-        <v>6.65</v>
+        <v>-1.99</v>
       </c>
       <c r="M58" t="n">
-        <v>33.4</v>
+        <v>27.36</v>
       </c>
       <c r="N58" t="n">
-        <v>3183195139.8</v>
+        <v>12368603515.52</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>603272.SH</t>
+          <t>600403.SH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>*ST联翔</t>
+          <t>大有能源</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16.23</v>
+        <v>5.25</v>
       </c>
       <c r="E59" t="n">
-        <v>-9.9834</v>
+        <v>-6.7496</v>
       </c>
       <c r="F59" t="n">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="G59" t="n">
-        <v>279033238</v>
+        <v>772003004</v>
       </c>
       <c r="H59" t="n">
-        <v>55086760</v>
+        <v>87955911.08</v>
       </c>
       <c r="I59" t="n">
-        <v>98128197.8</v>
+        <v>101195033.11</v>
       </c>
       <c r="J59" t="n">
-        <v>153214957.8</v>
+        <v>189150944.19</v>
       </c>
       <c r="K59" t="n">
-        <v>43041437.8</v>
+        <v>13239122.03</v>
       </c>
       <c r="L59" t="n">
-        <v>15.43</v>
+        <v>1.71</v>
       </c>
       <c r="M59" t="n">
-        <v>54.91</v>
+        <v>24.5</v>
       </c>
       <c r="N59" t="n">
-        <v>1681866210</v>
+        <v>12551765110.5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>603339.SH</t>
+          <t>600488.SH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>四方科技</t>
+          <t>津药药业</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.94</v>
+        <v>6.45</v>
       </c>
       <c r="E60" t="n">
-        <v>-10.0139</v>
+        <v>-7.5931</v>
       </c>
       <c r="F60" t="n">
-        <v>6.54</v>
+        <v>18.69</v>
       </c>
       <c r="G60" t="n">
-        <v>264583684</v>
+        <v>1398409927</v>
       </c>
       <c r="H60" t="n">
-        <v>23983173.4</v>
+        <v>76352578.63</v>
       </c>
       <c r="I60" t="n">
-        <v>28764350</v>
+        <v>99814399.47</v>
       </c>
       <c r="J60" t="n">
-        <v>52747523.4</v>
+        <v>176166978.1</v>
       </c>
       <c r="K60" t="n">
-        <v>4781176.6</v>
+        <v>23461820.84</v>
       </c>
       <c r="L60" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="M60" t="n">
-        <v>19.94</v>
+        <v>12.6</v>
       </c>
       <c r="N60" t="n">
-        <v>4004168804.5</v>
+        <v>7042669086</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>603339.SH</t>
+          <t>600491.SH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>四方科技</t>
+          <t>ST龙元</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.94</v>
+        <v>1.42</v>
       </c>
       <c r="E61" t="n">
-        <v>-10.0139</v>
+        <v>10.0775</v>
       </c>
       <c r="F61" t="n">
-        <v>6.54</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>601688968</v>
+        <v>209323998</v>
       </c>
       <c r="H61" t="n">
-        <v>40398652.71</v>
+        <v>22604798.84</v>
       </c>
       <c r="I61" t="n">
-        <v>46952331.52</v>
+        <v>21076329</v>
       </c>
       <c r="J61" t="n">
-        <v>87350984.23</v>
+        <v>43681127.84</v>
       </c>
       <c r="K61" t="n">
-        <v>6553678.81</v>
+        <v>-1528469.84</v>
       </c>
       <c r="L61" t="n">
-        <v>1.09</v>
+        <v>-0.73</v>
       </c>
       <c r="M61" t="n">
-        <v>14.52</v>
+        <v>20.87</v>
       </c>
       <c r="N61" t="n">
-        <v>4004168804.5</v>
+        <v>2172256296.1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>603459.SH</t>
+          <t>600584.SH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>红板科技</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>85.05</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>-10</v>
+        <v>-10.0043</v>
       </c>
       <c r="F62" t="n">
-        <v>20.1</v>
+        <v>10.36</v>
       </c>
       <c r="G62" t="n">
-        <v>1410741955</v>
+        <v>15886100924</v>
       </c>
       <c r="H62" t="n">
-        <v>328754988.69</v>
+        <v>1162354763.34</v>
       </c>
       <c r="I62" t="n">
-        <v>132108808.55</v>
+        <v>1524267103.58</v>
       </c>
       <c r="J62" t="n">
-        <v>460863797.24</v>
+        <v>2686621866.92</v>
       </c>
       <c r="K62" t="n">
-        <v>-196646180.14</v>
+        <v>361912340.24</v>
       </c>
       <c r="L62" t="n">
-        <v>-13.94</v>
+        <v>2.28</v>
       </c>
       <c r="M62" t="n">
-        <v>32.67</v>
+        <v>16.91</v>
       </c>
       <c r="N62" t="n">
-        <v>6723360522.9</v>
+        <v>148897186369.7</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>603516.SH</t>
+          <t>600664.SH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>淳中科技</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>98.14</v>
+        <v>4.94</v>
       </c>
       <c r="E63" t="n">
-        <v>-9.9963</v>
+        <v>10.0223</v>
       </c>
       <c r="F63" t="n">
-        <v>5.51</v>
+        <v>11.78</v>
       </c>
       <c r="G63" t="n">
-        <v>1163871060</v>
+        <v>1959157065</v>
       </c>
       <c r="H63" t="n">
-        <v>116953920.71</v>
+        <v>130413389.62</v>
       </c>
       <c r="I63" t="n">
-        <v>139730047.49</v>
+        <v>223971859</v>
       </c>
       <c r="J63" t="n">
-        <v>256683968.2</v>
+        <v>354385248.62</v>
       </c>
       <c r="K63" t="n">
-        <v>22776126.78</v>
+        <v>93558469.38</v>
       </c>
       <c r="L63" t="n">
-        <v>1.96</v>
+        <v>4.78</v>
       </c>
       <c r="M63" t="n">
-        <v>22.05</v>
+        <v>18.09</v>
       </c>
       <c r="N63" t="n">
-        <v>19948748901.06</v>
+        <v>12441438787.44</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>603538.SH</t>
+          <t>600721.SH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>百花医药</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>39</v>
+        <v>8.31</v>
       </c>
       <c r="E64" t="n">
-        <v>10.0141</v>
+        <v>9.775399999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>30.43</v>
+        <v>18.6</v>
       </c>
       <c r="G64" t="n">
-        <v>3865780275</v>
+        <v>744962380</v>
       </c>
       <c r="H64" t="n">
-        <v>421747711.71</v>
+        <v>75257150.59999999</v>
       </c>
       <c r="I64" t="n">
-        <v>416902590.64</v>
+        <v>52378688</v>
       </c>
       <c r="J64" t="n">
-        <v>838650302.35</v>
+        <v>127635838.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-4845121.07</v>
+        <v>-22878462.6</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.13</v>
+        <v>-3.07</v>
       </c>
       <c r="M64" t="n">
-        <v>21.69</v>
+        <v>17.13</v>
       </c>
       <c r="N64" t="n">
-        <v>13139878089</v>
+        <v>3195590846.85</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>603669.SH</t>
+          <t>600759.SH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>灵康药业</t>
+          <t>ST洲际</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8.109999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="E65" t="n">
-        <v>9.5946</v>
+        <v>-10.0719</v>
       </c>
       <c r="F65" t="n">
-        <v>14.65</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>785412835</v>
+        <v>959417764</v>
       </c>
       <c r="H65" t="n">
-        <v>102552754.35</v>
+        <v>81982167.08</v>
       </c>
       <c r="I65" t="n">
-        <v>63027211.88</v>
+        <v>71623753.62</v>
       </c>
       <c r="J65" t="n">
-        <v>165579966.23</v>
+        <v>153605920.7</v>
       </c>
       <c r="K65" t="n">
-        <v>-39525542.47</v>
+        <v>-10358413.46</v>
       </c>
       <c r="L65" t="n">
-        <v>-5.03</v>
+        <v>-1.08</v>
       </c>
       <c r="M65" t="n">
-        <v>21.08</v>
+        <v>16.01</v>
       </c>
       <c r="N65" t="n">
-        <v>5777005748.15</v>
+        <v>10359214450</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>603698.SH</t>
+          <t>600785.SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>航天工程</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32.14</v>
+        <v>9.32</v>
       </c>
       <c r="E66" t="n">
-        <v>-9.997199999999999</v>
+        <v>10.0354</v>
       </c>
       <c r="F66" t="n">
-        <v>2.33</v>
+        <v>9.57</v>
       </c>
       <c r="G66" t="n">
-        <v>481945974</v>
+        <v>266701015</v>
       </c>
       <c r="H66" t="n">
-        <v>60376719</v>
+        <v>51590113.1</v>
       </c>
       <c r="I66" t="n">
-        <v>37147678.72</v>
+        <v>51001171.8</v>
       </c>
       <c r="J66" t="n">
-        <v>97524397.72</v>
+        <v>102591284.9</v>
       </c>
       <c r="K66" t="n">
-        <v>-23229040.28</v>
+        <v>-588941.3</v>
       </c>
       <c r="L66" t="n">
-        <v>-4.82</v>
+        <v>-0.22</v>
       </c>
       <c r="M66" t="n">
-        <v>20.24</v>
+        <v>38.47</v>
       </c>
       <c r="N66" t="n">
-        <v>17226718600</v>
+        <v>2944036941.44</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>603800.SH</t>
+          <t>600785.SH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>洪田股份</t>
+          <t>新华百货</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>79.20999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="E67" t="n">
-        <v>4.9695</v>
+        <v>10.0354</v>
       </c>
       <c r="F67" t="n">
-        <v>6.81</v>
+        <v>9.57</v>
       </c>
       <c r="G67" t="n">
-        <v>1127609992</v>
+        <v>491450576</v>
       </c>
       <c r="H67" t="n">
-        <v>232882456.83</v>
+        <v>82907185.56</v>
       </c>
       <c r="I67" t="n">
-        <v>309758040.48</v>
+        <v>85283994.59999999</v>
       </c>
       <c r="J67" t="n">
-        <v>542640497.3099999</v>
+        <v>168191180.16</v>
       </c>
       <c r="K67" t="n">
-        <v>76875583.65000001</v>
+        <v>2376809.04</v>
       </c>
       <c r="L67" t="n">
-        <v>6.82</v>
+        <v>0.48</v>
       </c>
       <c r="M67" t="n">
-        <v>48.12</v>
+        <v>34.22</v>
       </c>
       <c r="N67" t="n">
-        <v>16475680000</v>
+        <v>2944036941.44</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>603839.SH</t>
+          <t>603065.SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>安正时尚</t>
+          <t>宿迁联盛</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6.47</v>
+        <v>19.07</v>
       </c>
       <c r="E68" t="n">
-        <v>10.034</v>
+        <v>-10.0047</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G68" t="n">
-        <v>48893977</v>
+        <v>142058290</v>
       </c>
       <c r="H68" t="n">
-        <v>12371294.22</v>
+        <v>14519024</v>
       </c>
       <c r="I68" t="n">
-        <v>15177837</v>
+        <v>13302998</v>
       </c>
       <c r="J68" t="n">
-        <v>27549131.22</v>
+        <v>27822022</v>
       </c>
       <c r="K68" t="n">
-        <v>2806542.78</v>
+        <v>-1216026</v>
       </c>
       <c r="L68" t="n">
-        <v>5.74</v>
+        <v>-0.86</v>
       </c>
       <c r="M68" t="n">
-        <v>56.34</v>
+        <v>19.58</v>
       </c>
       <c r="N68" t="n">
-        <v>2503994814</v>
+        <v>7989711598.04</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>603928.SH</t>
+          <t>603108.SH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>兴业股份</t>
+          <t>润达医疗</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.71</v>
+        <v>10.31</v>
       </c>
       <c r="E69" t="n">
-        <v>-9.9803</v>
+        <v>10.032</v>
       </c>
       <c r="F69" t="n">
-        <v>11.45</v>
+        <v>7.38</v>
       </c>
       <c r="G69" t="n">
-        <v>1274165383</v>
+        <v>445274891</v>
       </c>
       <c r="H69" t="n">
-        <v>91024367.42</v>
+        <v>51468482</v>
       </c>
       <c r="I69" t="n">
-        <v>136781908.85</v>
+        <v>74023716.66</v>
       </c>
       <c r="J69" t="n">
-        <v>227806276.27</v>
+        <v>125492198.66</v>
       </c>
       <c r="K69" t="n">
-        <v>45757541.43</v>
+        <v>22555234.66</v>
       </c>
       <c r="L69" t="n">
-        <v>3.59</v>
+        <v>5.07</v>
       </c>
       <c r="M69" t="n">
-        <v>17.88</v>
+        <v>28.18</v>
       </c>
       <c r="N69" t="n">
-        <v>4671051840</v>
+        <v>6233465425.44</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>603949.SH</t>
+          <t>603115.SH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>海星股份</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.76</v>
+        <v>81.06</v>
       </c>
       <c r="E70" t="n">
-        <v>-10.0065</v>
+        <v>-10.0033</v>
       </c>
       <c r="F70" t="n">
-        <v>1.13</v>
+        <v>3.02</v>
       </c>
       <c r="G70" t="n">
-        <v>32737792</v>
+        <v>609579029</v>
       </c>
       <c r="H70" t="n">
-        <v>23744256</v>
+        <v>227466357</v>
       </c>
       <c r="I70" t="n">
-        <v>4697664</v>
+        <v>159831169</v>
       </c>
       <c r="J70" t="n">
-        <v>28441920</v>
+        <v>387297526</v>
       </c>
       <c r="K70" t="n">
-        <v>-19046592</v>
+        <v>-67635188</v>
       </c>
       <c r="L70" t="n">
-        <v>-58.18</v>
+        <v>-11.1</v>
       </c>
       <c r="M70" t="n">
-        <v>86.88</v>
+        <v>63.54</v>
       </c>
       <c r="N70" t="n">
-        <v>2892424570.24</v>
+        <v>19607635824</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -5614,990 +5606,1375 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>603949.SH</t>
+          <t>603120.SH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>雪龙集团</t>
+          <t>肯特催化</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.76</v>
+        <v>51.51</v>
       </c>
       <c r="E71" t="n">
-        <v>-10.0065</v>
+        <v>1.7984</v>
       </c>
       <c r="F71" t="n">
-        <v>1.13</v>
+        <v>19.34</v>
       </c>
       <c r="G71" t="n">
-        <v>50481837</v>
+        <v>373845399</v>
       </c>
       <c r="H71" t="n">
-        <v>36828348</v>
+        <v>61358185</v>
       </c>
       <c r="I71" t="n">
-        <v>6333256</v>
+        <v>71529527.34999999</v>
       </c>
       <c r="J71" t="n">
-        <v>43161604</v>
+        <v>132887712.35</v>
       </c>
       <c r="K71" t="n">
-        <v>-30495092</v>
+        <v>10171342.35</v>
       </c>
       <c r="L71" t="n">
-        <v>-60.41</v>
+        <v>2.72</v>
       </c>
       <c r="M71" t="n">
-        <v>85.5</v>
+        <v>35.55</v>
       </c>
       <c r="N71" t="n">
-        <v>2892424570.24</v>
+        <v>1952229000</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>605133.SH</t>
+          <t>603127.SH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>嵘泰股份</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>31.21</v>
+        <v>53.25</v>
       </c>
       <c r="E72" t="n">
-        <v>-10.0058</v>
+        <v>5.1956</v>
       </c>
       <c r="F72" t="n">
-        <v>4.71</v>
+        <v>19.56</v>
       </c>
       <c r="G72" t="n">
-        <v>427854069</v>
+        <v>11829856571</v>
       </c>
       <c r="H72" t="n">
-        <v>144229876.6</v>
+        <v>1219329719.41</v>
       </c>
       <c r="I72" t="n">
-        <v>62940285</v>
+        <v>647634108.9400001</v>
       </c>
       <c r="J72" t="n">
-        <v>207170161.6</v>
+        <v>1866963828.35</v>
       </c>
       <c r="K72" t="n">
-        <v>-81289591.59999999</v>
+        <v>-571695610.47</v>
       </c>
       <c r="L72" t="n">
-        <v>-19</v>
+        <v>-4.83</v>
       </c>
       <c r="M72" t="n">
-        <v>48.42</v>
+        <v>15.78</v>
       </c>
       <c r="N72" t="n">
-        <v>8804906275.52</v>
+        <v>33566297995.5</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅偏离值达到7%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>605255.SH</t>
+          <t>603459.SH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>天普股份</t>
+          <t>红板科技</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>87.19</v>
+        <v>91.45</v>
       </c>
       <c r="E73" t="n">
-        <v>10.005</v>
+        <v>7.525</v>
       </c>
       <c r="F73" t="n">
-        <v>0.89</v>
+        <v>33.64</v>
       </c>
       <c r="G73" t="n">
-        <v>245564722</v>
+        <v>2326658046</v>
       </c>
       <c r="H73" t="n">
-        <v>16708767</v>
+        <v>143692447.9</v>
       </c>
       <c r="I73" t="n">
-        <v>36459173.38</v>
+        <v>366235808.67</v>
       </c>
       <c r="J73" t="n">
-        <v>53167940.38</v>
+        <v>509928256.57</v>
       </c>
       <c r="K73" t="n">
-        <v>19750406.38</v>
+        <v>222543360.77</v>
       </c>
       <c r="L73" t="n">
-        <v>8.039999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="M73" t="n">
-        <v>21.65</v>
+        <v>21.92</v>
       </c>
       <c r="N73" t="n">
-        <v>11690435200</v>
+        <v>7229292414.1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>605598.SH</t>
+          <t>603538.SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>上海港湾</t>
+          <t>美诺华</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>29.36</v>
+        <v>38.35</v>
       </c>
       <c r="E74" t="n">
-        <v>-3.0703</v>
+        <v>-1.6667</v>
       </c>
       <c r="F74" t="n">
-        <v>4.46</v>
+        <v>35.05</v>
       </c>
       <c r="G74" t="n">
-        <v>482120915</v>
+        <v>4722823497</v>
       </c>
       <c r="H74" t="n">
-        <v>68611980</v>
+        <v>277098061.31</v>
       </c>
       <c r="I74" t="n">
-        <v>100851436</v>
+        <v>259160612.61</v>
       </c>
       <c r="J74" t="n">
-        <v>169463416</v>
+        <v>536258673.92</v>
       </c>
       <c r="K74" t="n">
-        <v>32239456</v>
+        <v>-17937448.7</v>
       </c>
       <c r="L74" t="n">
-        <v>6.69</v>
+        <v>-0.38</v>
       </c>
       <c r="M74" t="n">
-        <v>35.15</v>
+        <v>11.35</v>
       </c>
       <c r="N74" t="n">
-        <v>7134973512.24</v>
+        <v>12920880120.85</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>非S证券连续三个交易日内收盘价格跌幅偏离值累计达到20%的证券</t>
+          <t>有价格涨跌幅限制的日换手率达到20%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>688046.SH</t>
+          <t>603567.SH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>药康生物</t>
+          <t>珍宝岛</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>28.81</v>
+        <v>5.48</v>
       </c>
       <c r="E75" t="n">
-        <v>17.0187</v>
+        <v>10.0402</v>
       </c>
       <c r="F75" t="n">
-        <v>5.87</v>
+        <v>4.93</v>
       </c>
       <c r="G75" t="n">
-        <v>678745800</v>
+        <v>238262495</v>
       </c>
       <c r="H75" t="n">
-        <v>149641147.6</v>
+        <v>40700625</v>
       </c>
       <c r="I75" t="n">
-        <v>115383052.1</v>
+        <v>52153109.15</v>
       </c>
       <c r="J75" t="n">
-        <v>265024199.7</v>
+        <v>92853734.15000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-34258095.5</v>
+        <v>11452484.15</v>
       </c>
       <c r="L75" t="n">
-        <v>-5.05</v>
+        <v>4.81</v>
       </c>
       <c r="M75" t="n">
-        <v>39.05</v>
+        <v>38.97</v>
       </c>
       <c r="N75" t="n">
-        <v>11812100000</v>
+        <v>5147930040.16</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>688166.SH</t>
+          <t>603580.SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>博瑞医药</t>
+          <t>艾艾精工</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>35.44</v>
+        <v>40.84</v>
       </c>
       <c r="E76" t="n">
-        <v>20.0135</v>
+        <v>9.991899999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>2.77</v>
+        <v>0.11</v>
       </c>
       <c r="G76" t="n">
-        <v>412524800</v>
+        <v>9884900</v>
       </c>
       <c r="H76" t="n">
-        <v>87527029.31999999</v>
+        <v>3033371</v>
       </c>
       <c r="I76" t="n">
-        <v>78605231.65000001</v>
+        <v>9884900.48</v>
       </c>
       <c r="J76" t="n">
-        <v>166132260.97</v>
+        <v>12918271.48</v>
       </c>
       <c r="K76" t="n">
-        <v>-8921797.67</v>
+        <v>6851529.48</v>
       </c>
       <c r="L76" t="n">
-        <v>-2.16</v>
+        <v>69.31</v>
       </c>
       <c r="M76" t="n">
-        <v>40.27</v>
+        <v>130.69</v>
       </c>
       <c r="N76" t="n">
-        <v>15444574481.04</v>
+        <v>5336693488</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>688192.SH</t>
+          <t>603716.SH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>塞力医疗</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>67.59999999999999</v>
+        <v>16.12</v>
       </c>
       <c r="E77" t="n">
-        <v>20.0071</v>
+        <v>10.0341</v>
       </c>
       <c r="F77" t="n">
-        <v>3.43</v>
+        <v>12.13</v>
       </c>
       <c r="G77" t="n">
-        <v>1056557700</v>
+        <v>422280064</v>
       </c>
       <c r="H77" t="n">
-        <v>263185439.83</v>
+        <v>53913718.57</v>
       </c>
       <c r="I77" t="n">
-        <v>247980524.01</v>
+        <v>84941650.27</v>
       </c>
       <c r="J77" t="n">
-        <v>511165963.84</v>
+        <v>138855368.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-15204915.82</v>
+        <v>31027931.7</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.44</v>
+        <v>7.35</v>
       </c>
       <c r="M77" t="n">
-        <v>48.38</v>
+        <v>32.88</v>
       </c>
       <c r="N77" t="n">
-        <v>31178072619.2</v>
+        <v>3639747212.4</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅偏离值达到7%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>688192.SH</t>
+          <t>603725.SH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>迪哲医药</t>
+          <t>天安新材</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>67.59999999999999</v>
+        <v>14.08</v>
       </c>
       <c r="E78" t="n">
-        <v>20.0071</v>
+        <v>7.3989</v>
       </c>
       <c r="F78" t="n">
-        <v>3.43</v>
+        <v>13.58</v>
       </c>
       <c r="G78" t="n">
-        <v>1493066300</v>
+        <v>714555667</v>
       </c>
       <c r="H78" t="n">
-        <v>305030793.79</v>
+        <v>112410220</v>
       </c>
       <c r="I78" t="n">
-        <v>255528728.81</v>
+        <v>131184825.52</v>
       </c>
       <c r="J78" t="n">
-        <v>560559522.6</v>
+        <v>243595045.52</v>
       </c>
       <c r="K78" t="n">
-        <v>-49502064.98</v>
+        <v>18774605.52</v>
       </c>
       <c r="L78" t="n">
-        <v>-3.32</v>
+        <v>2.63</v>
       </c>
       <c r="M78" t="n">
-        <v>37.54</v>
+        <v>34.09</v>
       </c>
       <c r="N78" t="n">
-        <v>31178072619.2</v>
+        <v>4292396134.4</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>688333.SH</t>
+          <t>603757.SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>铂力特</t>
+          <t>大元泵业</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>116.2</v>
+        <v>79.5</v>
       </c>
       <c r="E79" t="n">
-        <v>16.7135</v>
+        <v>3.2468</v>
       </c>
       <c r="F79" t="n">
-        <v>11.82</v>
+        <v>9.51</v>
       </c>
       <c r="G79" t="n">
-        <v>3777863100</v>
+        <v>1399872466</v>
       </c>
       <c r="H79" t="n">
-        <v>527118194.25</v>
+        <v>196172510.54</v>
       </c>
       <c r="I79" t="n">
-        <v>868248332.88</v>
+        <v>262396250.68</v>
       </c>
       <c r="J79" t="n">
-        <v>1395366527.13</v>
+        <v>458568761.22</v>
       </c>
       <c r="K79" t="n">
-        <v>341130138.63</v>
+        <v>66223740.14</v>
       </c>
       <c r="L79" t="n">
-        <v>9.029999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="M79" t="n">
-        <v>36.94</v>
+        <v>32.76</v>
       </c>
       <c r="N79" t="n">
-        <v>31876236618.8</v>
+        <v>14830507090.5</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>有价格涨跌幅限制的日价格振幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>688433.SH</t>
+          <t>605028.SH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>华曙高科</t>
+          <t>世茂能源</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>96.65000000000001</v>
+        <v>24.38</v>
       </c>
       <c r="E80" t="n">
-        <v>15.0048</v>
+        <v>0.6191</v>
       </c>
       <c r="F80" t="n">
-        <v>2.55</v>
+        <v>5.11</v>
       </c>
       <c r="G80" t="n">
-        <v>1015325700</v>
+        <v>270274291</v>
       </c>
       <c r="H80" t="n">
-        <v>164570731.21</v>
+        <v>44995858.37</v>
       </c>
       <c r="I80" t="n">
-        <v>287406217.68</v>
+        <v>47145674.65</v>
       </c>
       <c r="J80" t="n">
-        <v>451976948.89</v>
+        <v>92141533.02</v>
       </c>
       <c r="K80" t="n">
-        <v>122835486.47</v>
+        <v>2149816.28</v>
       </c>
       <c r="L80" t="n">
-        <v>12.1</v>
+        <v>0.8</v>
       </c>
       <c r="M80" t="n">
-        <v>44.52</v>
+        <v>34.09</v>
       </c>
       <c r="N80" t="n">
-        <v>40165569917.55</v>
+        <v>3900800000</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>688525.SH</t>
+          <t>605189.SH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>富春染织</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>304.4</v>
+        <v>15.78</v>
       </c>
       <c r="E81" t="n">
-        <v>-15.0599</v>
+        <v>0.8951</v>
       </c>
       <c r="F81" t="n">
-        <v>11.1</v>
+        <v>16.58</v>
       </c>
       <c r="G81" t="n">
-        <v>16799676200</v>
+        <v>1489256206</v>
       </c>
       <c r="H81" t="n">
-        <v>1472525361.73</v>
+        <v>121858166.3</v>
       </c>
       <c r="I81" t="n">
-        <v>1231874526.21</v>
+        <v>94398736.31999999</v>
       </c>
       <c r="J81" t="n">
-        <v>2704399887.94</v>
+        <v>216256902.62</v>
       </c>
       <c r="K81" t="n">
-        <v>-240650835.52</v>
+        <v>-27459429.98</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.43</v>
+        <v>-1.84</v>
       </c>
       <c r="M81" t="n">
-        <v>16.1</v>
+        <v>14.52</v>
       </c>
       <c r="N81" t="n">
-        <v>143544890086.4</v>
+        <v>3759347337.42</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
+          <t>非S证券连续三个交易日内收盘价格涨幅偏离值累计达到20%的证券</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>920072.BJ</t>
+          <t>688008.SH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>科莱瑞迪</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>32.5</v>
+        <v>211.13</v>
       </c>
       <c r="E82" t="n">
-        <v>7.4025</v>
+        <v>-16.4437</v>
       </c>
       <c r="F82" t="n">
-        <v>48.55</v>
+        <v>10.13</v>
       </c>
       <c r="G82" t="n">
-        <v>229415200</v>
+        <v>25578638000</v>
       </c>
       <c r="H82" t="n">
-        <v>39041341.72</v>
+        <v>2671507594.01</v>
       </c>
       <c r="I82" t="n">
-        <v>24322273.99</v>
+        <v>3994772448.24</v>
       </c>
       <c r="J82" t="n">
-        <v>63363615.71</v>
+        <v>6666280042.25</v>
       </c>
       <c r="K82" t="n">
-        <v>-14719067.73</v>
+        <v>1323264854.23</v>
       </c>
       <c r="L82" t="n">
-        <v>-6.42</v>
+        <v>5.17</v>
       </c>
       <c r="M82" t="n">
-        <v>27.62</v>
+        <v>26.06</v>
       </c>
       <c r="N82" t="n">
-        <v>470112500</v>
+        <v>241694133318.73</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格跌幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>920088.BJ</t>
+          <t>688166.SH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>科力股份</t>
+          <t>博瑞医药</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>46.02</v>
+        <v>42.5</v>
       </c>
       <c r="E83" t="n">
-        <v>-9.4094</v>
+        <v>19.921</v>
       </c>
       <c r="F83" t="n">
-        <v>25.04</v>
+        <v>11.1</v>
       </c>
       <c r="G83" t="n">
-        <v>388516600</v>
+        <v>1945541500</v>
       </c>
       <c r="H83" t="n">
-        <v>38972059.75</v>
+        <v>310338182.44</v>
       </c>
       <c r="I83" t="n">
-        <v>59634885.58</v>
+        <v>202517283.66</v>
       </c>
       <c r="J83" t="n">
-        <v>98606945.33</v>
+        <v>512855466.1</v>
       </c>
       <c r="K83" t="n">
-        <v>20662825.83</v>
+        <v>-107820898.78</v>
       </c>
       <c r="L83" t="n">
-        <v>5.32</v>
+        <v>-5.54</v>
       </c>
       <c r="M83" t="n">
-        <v>25.38</v>
+        <v>26.36</v>
       </c>
       <c r="N83" t="n">
-        <v>1498697904.6</v>
+        <v>18521287117.5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的日收盘价格涨幅达到15%的前五只证券</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>920193.BJ</t>
+          <t>688166.SH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>吉和昌</t>
+          <t>博瑞医药</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>35.61</v>
+        <v>42.5</v>
       </c>
       <c r="E84" t="n">
-        <v>-13.9231</v>
+        <v>19.921</v>
       </c>
       <c r="F84" t="n">
-        <v>29.47</v>
+        <v>11.1</v>
       </c>
       <c r="G84" t="n">
-        <v>280802000</v>
+        <v>2358066300</v>
       </c>
       <c r="H84" t="n">
-        <v>46772603.78</v>
+        <v>330485701.08</v>
       </c>
       <c r="I84" t="n">
-        <v>23899122.6</v>
+        <v>239149333.48</v>
       </c>
       <c r="J84" t="n">
-        <v>70671726.38</v>
+        <v>569635034.5599999</v>
       </c>
       <c r="K84" t="n">
-        <v>-22873481.18</v>
+        <v>-91336367.59999999</v>
       </c>
       <c r="L84" t="n">
-        <v>-8.15</v>
+        <v>-3.87</v>
       </c>
       <c r="M84" t="n">
-        <v>25.17</v>
+        <v>24.16</v>
       </c>
       <c r="N84" t="n">
-        <v>897372000</v>
+        <v>18521287117.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>当日换手率达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>920266.BJ</t>
+          <t>688619.SH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>生物谷</t>
+          <t>罗普特</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8.75</v>
+        <v>14.83</v>
       </c>
       <c r="E85" t="n">
-        <v>26.4451</v>
+        <v>12.0937</v>
       </c>
       <c r="F85" t="n">
-        <v>19.6</v>
+        <v>4.18</v>
       </c>
       <c r="G85" t="n">
-        <v>196894800</v>
+        <v>237855100</v>
       </c>
       <c r="H85" t="n">
-        <v>32704691.72</v>
+        <v>39229304.24</v>
       </c>
       <c r="I85" t="n">
-        <v>32239550.08</v>
+        <v>59309962.49</v>
       </c>
       <c r="J85" t="n">
-        <v>64944241.8</v>
+        <v>98539266.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-465141.64</v>
+        <v>20080658.25</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.24</v>
+        <v>8.44</v>
       </c>
       <c r="M85" t="n">
-        <v>32.98</v>
+        <v>41.43</v>
       </c>
       <c r="N85" t="n">
-        <v>1036791498.75</v>
+        <v>2750046162.86</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>当日收盘价涨幅达到20%的前5只股票</t>
+          <t>有价格涨跌幅限制的连续3个交易日内收盘价格涨幅偏离值累计达到30%的证券</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>920266.BJ</t>
+          <t>920072.BJ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>生物谷</t>
+          <t>科莱瑞迪</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8.75</v>
+        <v>30.58</v>
       </c>
       <c r="E86" t="n">
-        <v>26.4451</v>
+        <v>-5.9077</v>
       </c>
       <c r="F86" t="n">
-        <v>19.6</v>
+        <v>36.59</v>
       </c>
       <c r="G86" t="n">
-        <v>334447300</v>
+        <v>164494900</v>
       </c>
       <c r="H86" t="n">
-        <v>49600297.37</v>
+        <v>26193072.39</v>
       </c>
       <c r="I86" t="n">
-        <v>39144174</v>
+        <v>19530912.89</v>
       </c>
       <c r="J86" t="n">
-        <v>88744471.37</v>
+        <v>45723985.28</v>
       </c>
       <c r="K86" t="n">
-        <v>-10456123.37</v>
+        <v>-6662159.5</v>
       </c>
       <c r="L86" t="n">
-        <v>-3.13</v>
+        <v>-4.05</v>
       </c>
       <c r="M86" t="n">
-        <v>26.53</v>
+        <v>27.8</v>
       </c>
       <c r="N86" t="n">
-        <v>1036791498.75</v>
+        <v>442339700</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>920088.BJ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>云创退</t>
+          <t>科力股份</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.2</v>
+        <v>41.8</v>
       </c>
       <c r="E87" t="n">
-        <v>29.0323</v>
+        <v>-9.1699</v>
       </c>
       <c r="F87" t="n">
-        <v>19.14</v>
+        <v>23.52</v>
       </c>
       <c r="G87" t="n">
-        <v>17665700</v>
+        <v>329853400</v>
       </c>
       <c r="H87" t="n">
-        <v>2882967.14</v>
+        <v>47067116.43</v>
       </c>
       <c r="I87" t="n">
-        <v>3855745.42</v>
+        <v>42948358.96</v>
       </c>
       <c r="J87" t="n">
-        <v>6738712.56</v>
+        <v>90015475.39</v>
       </c>
       <c r="K87" t="n">
-        <v>972778.28</v>
+        <v>-4118757.47</v>
       </c>
       <c r="L87" t="n">
-        <v>5.51</v>
+        <v>-1.25</v>
       </c>
       <c r="M87" t="n">
-        <v>38.15</v>
+        <v>27.29</v>
       </c>
       <c r="N87" t="n">
-        <v>97321050</v>
+        <v>1361268414</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>退市整理期</t>
+          <t>当日换手率达到20%的前5只股票</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>920211.BJ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>新睿电子</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>155.13</v>
+      </c>
+      <c r="E88" t="n">
+        <v>5.5306</v>
+      </c>
+      <c r="F88" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="G88" t="n">
+        <v>238205600</v>
+      </c>
+      <c r="H88" t="n">
+        <v>24108260.89</v>
+      </c>
+      <c r="I88" t="n">
+        <v>23637093.47</v>
+      </c>
+      <c r="J88" t="n">
+        <v>47745354.36</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-471167.42</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M88" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="N88" t="n">
+        <v>893548800</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>920266.BJ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>生物谷</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6.9714</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="G89" t="n">
+        <v>204746500</v>
+      </c>
+      <c r="H89" t="n">
+        <v>36239702.47</v>
+      </c>
+      <c r="I89" t="n">
+        <v>23715027.66</v>
+      </c>
+      <c r="J89" t="n">
+        <v>59954730.13</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-12524674.81</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="M89" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1109070677.52</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>当日价格振幅达到30%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E90" t="n">
+        <v>30</v>
+      </c>
+      <c r="F90" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="G90" t="n">
+        <v>46463200</v>
+      </c>
+      <c r="H90" t="n">
+        <v>6423533.15</v>
+      </c>
+      <c r="I90" t="n">
+        <v>6817321.16</v>
+      </c>
+      <c r="J90" t="n">
+        <v>13240854.31</v>
+      </c>
+      <c r="K90" t="n">
+        <v>393788.01</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M90" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>126517365</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E91" t="n">
+        <v>30</v>
+      </c>
+      <c r="F91" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="G91" t="n">
+        <v>28797500</v>
+      </c>
+      <c r="H91" t="n">
+        <v>6983260.62</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5726887.43</v>
+      </c>
+      <c r="J91" t="n">
+        <v>12710148.05</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-1256373.19</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="M91" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="N91" t="n">
+        <v>126517365</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>920305.BJ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>云创退</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E92" t="n">
+        <v>30</v>
+      </c>
+      <c r="F92" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="G92" t="n">
+        <v>74359200</v>
+      </c>
+      <c r="H92" t="n">
+        <v>74359152.04000001</v>
+      </c>
+      <c r="I92" t="n">
+        <v>74359152.04000001</v>
+      </c>
+      <c r="J92" t="n">
+        <v>148718304.08</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>200</v>
+      </c>
+      <c r="N92" t="n">
+        <v>126517365</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>北交所股票连续10个交易日内日收盘价涨跌幅偏离值累计达到+150%(-60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>920367.BJ</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>新赣江</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E88" t="n">
-        <v>12.5675</v>
-      </c>
-      <c r="F88" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="G88" t="n">
-        <v>314494700</v>
-      </c>
-      <c r="H88" t="n">
-        <v>26218412.97</v>
-      </c>
-      <c r="I88" t="n">
-        <v>21597474.46</v>
-      </c>
-      <c r="J88" t="n">
-        <v>47815887.43</v>
-      </c>
-      <c r="K88" t="n">
-        <v>-4620938.51</v>
-      </c>
-      <c r="L88" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="M88" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1226183277.6</v>
-      </c>
-      <c r="O88" t="inlineStr">
+      <c r="D93" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="E93" t="n">
+        <v>20.6164</v>
+      </c>
+      <c r="F93" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="G93" t="n">
+        <v>422583800</v>
+      </c>
+      <c r="H93" t="n">
+        <v>30824649.57</v>
+      </c>
+      <c r="I93" t="n">
+        <v>40274915.88</v>
+      </c>
+      <c r="J93" t="n">
+        <v>71099565.45</v>
+      </c>
+      <c r="K93" t="n">
+        <v>9450266.310000001</v>
+      </c>
+      <c r="L93" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M93" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1478978597.16</v>
+      </c>
+      <c r="O93" t="inlineStr">
         <is>
           <t>当日换手率达到20%的前5只股票</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>920367.BJ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>新赣江</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="E94" t="n">
+        <v>20.6164</v>
+      </c>
+      <c r="F94" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="G94" t="n">
+        <v>737078400</v>
+      </c>
+      <c r="H94" t="n">
+        <v>49306792.02</v>
+      </c>
+      <c r="I94" t="n">
+        <v>55586721.47</v>
+      </c>
+      <c r="J94" t="n">
+        <v>104893513.49</v>
+      </c>
+      <c r="K94" t="n">
+        <v>6279929.45</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M94" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1478978597.16</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>北交所股票连续3个交易日内日收盘价涨跌幅偏离值累计达到+40%(-40%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>920701.BJ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>豪声电子</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="E95" t="n">
+        <v>30</v>
+      </c>
+      <c r="F95" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="G95" t="n">
+        <v>108156000</v>
+      </c>
+      <c r="H95" t="n">
+        <v>20226305.75</v>
+      </c>
+      <c r="I95" t="n">
+        <v>25147342.74</v>
+      </c>
+      <c r="J95" t="n">
+        <v>45373648.49</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4921036.99</v>
+      </c>
+      <c r="L95" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M95" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1354801884.8</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>当日收盘价涨幅达到20%的前5只股票</t>
         </is>
       </c>
     </row>

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -916,7 +916,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920701.BJ</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -925,37 +925,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.13</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="n">
-        <v>13.52</v>
+        <v>1.56</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>1.32</v>
       </c>
       <c r="F3" t="n">
-        <v>13.52</v>
+        <v>1.56</v>
       </c>
       <c r="G3" t="n">
-        <v>10.4</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.12</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
         <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>82915.52</v>
+        <v>188379.99</v>
       </c>
       <c r="K3" t="n">
-        <v>108155.97627</v>
+        <v>28797.49011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>920701.BJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -964,31 +964,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.4</v>
+        <v>11.13</v>
       </c>
       <c r="D4" t="n">
-        <v>1.56</v>
+        <v>13.52</v>
       </c>
       <c r="E4" t="n">
-        <v>1.32</v>
+        <v>10.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>13.52</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>10.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>3.12</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>188379.99</v>
+        <v>82915.52</v>
       </c>
       <c r="K4" t="n">
-        <v>28797.49011</v>
+        <v>108155.97627</v>
       </c>
     </row>
     <row r="5">

--- a/LongAI-Daily-FIX/data/latest/daily_report.xlsx
+++ b/LongAI-Daily-FIX/data/latest/daily_report.xlsx
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5524</v>
+        <v>5522</v>
       </c>
       <c r="C2" t="n">
-        <v>2499</v>
+        <v>482</v>
       </c>
       <c r="D2" t="n">
-        <v>2861</v>
+        <v>5001</v>
       </c>
       <c r="E2" t="n">
-        <v>164</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>24189.45</v>
+        <v>26716.49</v>
       </c>
     </row>
   </sheetData>
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3882.4126</v>
+        <v>3764.1547</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.85</v>
+        <v>-3.05</v>
       </c>
       <c r="F2" t="n">
-        <v>11242.08</v>
+        <v>12464.45</v>
       </c>
     </row>
     <row r="3">
@@ -560,17 +560,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14488.6541</v>
+        <v>13706.8841</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.97</v>
+        <v>-5.4</v>
       </c>
       <c r="F3" t="n">
-        <v>7937.97</v>
+        <v>8743.379999999999</v>
       </c>
     </row>
     <row r="4">
@@ -586,17 +586,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3692.4573</v>
+        <v>3428.6298</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.95</v>
+        <v>-7.14</v>
       </c>
       <c r="F4" t="n">
-        <v>2852.36</v>
+        <v>3585.04</v>
       </c>
     </row>
     <row r="5">
@@ -612,17 +612,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4698.4344</v>
+        <v>4529.0953</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.85</v>
+        <v>-3.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7988.3</v>
+        <v>9208.219999999999</v>
       </c>
     </row>
     <row r="6">
@@ -638,17 +638,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1846.8766</v>
+        <v>1715.4044</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.02</v>
+        <v>-7.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1748.21</v>
+        <v>1914.74</v>
       </c>
     </row>
     <row r="7">
@@ -664,17 +664,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7631.7622</v>
+        <v>7167.9959</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.38</v>
+        <v>-6.08</v>
       </c>
       <c r="F7" t="n">
-        <v>4730.91</v>
+        <v>5109.07</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +706,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32052.62</v>
+        <v>31124.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31124.37</v>
+        <v>25984.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25984.66</v>
+        <v>25825.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25825.92</v>
+        <v>29322.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29322.57</v>
+        <v>34106.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34106.93</v>
+        <v>28347.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28347.13</v>
+        <v>27194.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27194.94</v>
+        <v>25874.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25874.11</v>
+        <v>24189.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24189.45</v>
+        <v>26716.49</v>
       </c>
     </row>
   </sheetData>
@@ -877,391 +877,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>920117.BJ</t>
+          <t>920305.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.5</v>
+        <v>1.82</v>
       </c>
       <c r="D2" t="n">
-        <v>40.6</v>
+        <v>2.02</v>
       </c>
       <c r="E2" t="n">
-        <v>35.2</v>
+        <v>1.78</v>
       </c>
       <c r="F2" t="n">
-        <v>35.34</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>17.83</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
-        <v>17.51</v>
+        <v>0.46</v>
       </c>
       <c r="I2" t="n">
-        <v>98.20529999999999</v>
+        <v>29.4872</v>
       </c>
       <c r="J2" t="n">
-        <v>188353.33</v>
+        <v>168756.35</v>
       </c>
       <c r="K2" t="n">
-        <v>709339.71156</v>
+        <v>33161.63562</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>920305.BJ</t>
+          <t>300795.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>9.24</v>
       </c>
       <c r="D3" t="n">
-        <v>1.56</v>
+        <v>10.48</v>
       </c>
       <c r="E3" t="n">
-        <v>1.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.56</v>
+        <v>10.48</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>8.73</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>20.0458</v>
       </c>
       <c r="J3" t="n">
-        <v>188379.99</v>
+        <v>164205.47</v>
       </c>
       <c r="K3" t="n">
-        <v>28797.49011</v>
+        <v>168320.77095</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>920701.BJ</t>
+          <t>300577.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.13</v>
+        <v>20.36</v>
       </c>
       <c r="D4" t="n">
-        <v>13.52</v>
+        <v>20.36</v>
       </c>
       <c r="E4" t="n">
-        <v>10.9</v>
+        <v>19.87</v>
       </c>
       <c r="F4" t="n">
-        <v>13.52</v>
+        <v>20.36</v>
       </c>
       <c r="G4" t="n">
-        <v>10.4</v>
+        <v>16.97</v>
       </c>
       <c r="H4" t="n">
-        <v>3.12</v>
+        <v>3.39</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>19.9764</v>
       </c>
       <c r="J4" t="n">
-        <v>82915.52</v>
+        <v>169279.96</v>
       </c>
       <c r="K4" t="n">
-        <v>108155.97627</v>
+        <v>344340.54456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>920367.BJ</t>
+          <t>300317.SZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>3.56</v>
       </c>
       <c r="D5" t="n">
-        <v>36.8</v>
+        <v>4.22</v>
       </c>
       <c r="E5" t="n">
-        <v>27.59</v>
+        <v>3.54</v>
       </c>
       <c r="F5" t="n">
-        <v>35.22</v>
+        <v>4.13</v>
       </c>
       <c r="G5" t="n">
-        <v>29.2</v>
+        <v>3.56</v>
       </c>
       <c r="H5" t="n">
-        <v>6.02</v>
+        <v>0.57</v>
       </c>
       <c r="I5" t="n">
-        <v>20.6164</v>
+        <v>16.0112</v>
       </c>
       <c r="J5" t="n">
-        <v>133155.59</v>
+        <v>1697469.68</v>
       </c>
       <c r="K5" t="n">
-        <v>422583.76016</v>
+        <v>681958.47326</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300968.SZ</t>
+          <t>301609.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.050000000000001</v>
+        <v>30.42</v>
       </c>
       <c r="D6" t="n">
-        <v>10.24</v>
+        <v>35.73</v>
       </c>
       <c r="E6" t="n">
-        <v>9.039999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="F6" t="n">
-        <v>10.24</v>
+        <v>35.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.529999999999999</v>
+        <v>30.61</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>4.49</v>
       </c>
       <c r="I6" t="n">
-        <v>20.0469</v>
+        <v>14.6684</v>
       </c>
       <c r="J6" t="n">
-        <v>162653.5</v>
+        <v>65021.31</v>
       </c>
       <c r="K6" t="n">
-        <v>164026.361</v>
+        <v>214515.71235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301176.SZ</t>
+          <t>920130.BJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>13.48</v>
       </c>
       <c r="D7" t="n">
-        <v>58.2</v>
+        <v>17.09</v>
       </c>
       <c r="E7" t="n">
-        <v>48.51</v>
+        <v>13.23</v>
       </c>
       <c r="F7" t="n">
-        <v>58.2</v>
+        <v>14.98</v>
       </c>
       <c r="G7" t="n">
-        <v>48.5</v>
+        <v>13.15</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>13.9163</v>
       </c>
       <c r="J7" t="n">
-        <v>110575.2</v>
+        <v>59758.89</v>
       </c>
       <c r="K7" t="n">
-        <v>606740.14151</v>
+        <v>93289.71008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300805.SZ</t>
+          <t>300205.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.4</v>
+        <v>4.56</v>
       </c>
       <c r="D8" t="n">
-        <v>8.83</v>
+        <v>5.25</v>
       </c>
       <c r="E8" t="n">
-        <v>7.33</v>
+        <v>4.53</v>
       </c>
       <c r="F8" t="n">
-        <v>8.83</v>
+        <v>5.17</v>
       </c>
       <c r="G8" t="n">
-        <v>7.36</v>
+        <v>4.57</v>
       </c>
       <c r="H8" t="n">
-        <v>1.47</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="n">
-        <v>19.9728</v>
+        <v>13.1291</v>
       </c>
       <c r="J8" t="n">
-        <v>433633.77</v>
+        <v>75321.17999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>367283.66845</v>
+        <v>36835.9418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>688166.SH</t>
+          <t>300157.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36.86</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>42.52</v>
+        <v>4.4</v>
       </c>
       <c r="E9" t="n">
-        <v>36.29</v>
+        <v>3.69</v>
       </c>
       <c r="F9" t="n">
-        <v>42.5</v>
+        <v>4.13</v>
       </c>
       <c r="G9" t="n">
-        <v>35.44</v>
+        <v>3.69</v>
       </c>
       <c r="H9" t="n">
-        <v>7.06</v>
+        <v>0.44</v>
       </c>
       <c r="I9" t="n">
-        <v>19.921</v>
+        <v>11.9241</v>
       </c>
       <c r="J9" t="n">
-        <v>483938.23</v>
+        <v>1562310.09</v>
       </c>
       <c r="K9" t="n">
-        <v>1945541.496</v>
+        <v>652656.16679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>300591.SZ</t>
+          <t>301092.SZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.03</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>7.37</v>
+        <v>63.2</v>
       </c>
       <c r="E10" t="n">
-        <v>6.03</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>7.3</v>
+        <v>61.82</v>
       </c>
       <c r="G10" t="n">
-        <v>6.14</v>
+        <v>55.63</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>6.19</v>
       </c>
       <c r="I10" t="n">
-        <v>18.8925</v>
+        <v>11.1271</v>
       </c>
       <c r="J10" t="n">
-        <v>664279.96</v>
+        <v>140462.45</v>
       </c>
       <c r="K10" t="n">
-        <v>470686.95204</v>
+        <v>846307.79849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>301257.SZ</t>
+          <t>920046.BJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>18.39</v>
       </c>
       <c r="D11" t="n">
-        <v>61.62</v>
+        <v>21.8</v>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>18.17</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>20.3</v>
       </c>
       <c r="G11" t="n">
-        <v>53.5</v>
+        <v>18.44</v>
       </c>
       <c r="H11" t="n">
-        <v>7.5</v>
+        <v>1.86</v>
       </c>
       <c r="I11" t="n">
-        <v>14.0187</v>
+        <v>10.0868</v>
       </c>
       <c r="J11" t="n">
-        <v>144053.43</v>
+        <v>97305.32000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>832125.34752</v>
+        <v>200187.08215</v>
       </c>
     </row>
   </sheetData>
@@ -1338,391 +1338,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301042.SZ</t>
+          <t>920117.BJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63.9</v>
+        <v>30.01</v>
       </c>
       <c r="D2" t="n">
-        <v>63.9</v>
+        <v>32.6</v>
       </c>
       <c r="E2" t="n">
-        <v>51.56</v>
+        <v>27.13</v>
       </c>
       <c r="F2" t="n">
-        <v>52.04</v>
+        <v>27.48</v>
       </c>
       <c r="G2" t="n">
-        <v>64.45</v>
+        <v>35.34</v>
       </c>
       <c r="H2" t="n">
-        <v>-12.41</v>
+        <v>-7.86</v>
       </c>
       <c r="I2" t="n">
-        <v>-19.2552</v>
+        <v>-22.2411</v>
       </c>
       <c r="J2" t="n">
-        <v>35339.96</v>
+        <v>116480.78</v>
       </c>
       <c r="K2" t="n">
-        <v>210251.8998</v>
+        <v>346945.59457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300590.SZ</t>
+          <t>300137.SZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14.15</v>
+        <v>13.09</v>
       </c>
       <c r="D3" t="n">
-        <v>14.17</v>
+        <v>13.4</v>
       </c>
       <c r="E3" t="n">
-        <v>12.1</v>
+        <v>11.46</v>
       </c>
       <c r="F3" t="n">
-        <v>12.22</v>
+        <v>11.46</v>
       </c>
       <c r="G3" t="n">
-        <v>14.88</v>
+        <v>14.33</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.66</v>
+        <v>-2.87</v>
       </c>
       <c r="I3" t="n">
-        <v>-17.8763</v>
+        <v>-20.0279</v>
       </c>
       <c r="J3" t="n">
-        <v>621321.24</v>
+        <v>126052</v>
       </c>
       <c r="K3" t="n">
-        <v>796017.62595</v>
+        <v>148890.14452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300689.SZ</t>
+          <t>300688.SZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.75</v>
+        <v>25.8</v>
       </c>
       <c r="D4" t="n">
-        <v>65.72</v>
+        <v>26.13</v>
       </c>
       <c r="E4" t="n">
-        <v>54.13</v>
+        <v>20.9</v>
       </c>
       <c r="F4" t="n">
-        <v>54.75</v>
+        <v>20.9</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>26.13</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.25</v>
+        <v>-5.23</v>
       </c>
       <c r="I4" t="n">
-        <v>-17.0455</v>
+        <v>-20.0153</v>
       </c>
       <c r="J4" t="n">
-        <v>78060.46000000001</v>
+        <v>153197.55</v>
       </c>
       <c r="K4" t="n">
-        <v>461467.2437</v>
+        <v>340601.204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>688008.SH</t>
+          <t>688371.SH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>233.03</v>
+        <v>34.11</v>
       </c>
       <c r="D5" t="n">
-        <v>241.38</v>
+        <v>34.61</v>
       </c>
       <c r="E5" t="n">
-        <v>204.12</v>
+        <v>27.34</v>
       </c>
       <c r="F5" t="n">
-        <v>211.13</v>
+        <v>27.34</v>
       </c>
       <c r="G5" t="n">
-        <v>252.68</v>
+        <v>34.18</v>
       </c>
       <c r="H5" t="n">
-        <v>-41.55</v>
+        <v>-6.84</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.4437</v>
+        <v>-20.0117</v>
       </c>
       <c r="J5" t="n">
-        <v>1160079.57</v>
+        <v>150898.22</v>
       </c>
       <c r="K5" t="n">
-        <v>25578638.046</v>
+        <v>457897.768</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300596.SZ</t>
+          <t>300005.SZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45.3</v>
+        <v>18.45</v>
       </c>
       <c r="D6" t="n">
-        <v>45.3</v>
+        <v>19.25</v>
       </c>
       <c r="E6" t="n">
-        <v>37.96</v>
+        <v>14.87</v>
       </c>
       <c r="F6" t="n">
-        <v>38.07</v>
+        <v>14.87</v>
       </c>
       <c r="G6" t="n">
-        <v>45.45</v>
+        <v>18.59</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.38</v>
+        <v>-3.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-16.2376</v>
+        <v>-20.0108</v>
       </c>
       <c r="J6" t="n">
-        <v>178059.57</v>
+        <v>967605.9</v>
       </c>
       <c r="K6" t="n">
-        <v>719134.78528</v>
+        <v>1552881.41871</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301379.SZ</t>
+          <t>688218.SH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.81</v>
+        <v>45.56</v>
       </c>
       <c r="D7" t="n">
-        <v>34.4</v>
+        <v>45.98</v>
       </c>
       <c r="E7" t="n">
-        <v>30.6</v>
+        <v>36.66</v>
       </c>
       <c r="F7" t="n">
-        <v>30.98</v>
+        <v>36.66</v>
       </c>
       <c r="G7" t="n">
-        <v>36.42</v>
+        <v>45.83</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.44</v>
+        <v>-9.17</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.9368</v>
+        <v>-20.0087</v>
       </c>
       <c r="J7" t="n">
-        <v>389859.24</v>
+        <v>84263.03999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1258433.8089</v>
+        <v>339881.763</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>300666.SZ</t>
+          <t>301228.SZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>253.75</v>
+        <v>58.93</v>
       </c>
       <c r="D8" t="n">
-        <v>264.48</v>
+        <v>58.93</v>
       </c>
       <c r="E8" t="n">
-        <v>233.42</v>
+        <v>46.3</v>
       </c>
       <c r="F8" t="n">
-        <v>240</v>
+        <v>46.3</v>
       </c>
       <c r="G8" t="n">
-        <v>282.14</v>
+        <v>57.88</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.14</v>
+        <v>-11.58</v>
       </c>
       <c r="I8" t="n">
-        <v>-14.9358</v>
+        <v>-20.0069</v>
       </c>
       <c r="J8" t="n">
-        <v>334662.16</v>
+        <v>69892.06</v>
       </c>
       <c r="K8" t="n">
-        <v>8390678.398429999</v>
+        <v>351976.21832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>301031.SZ</t>
+          <t>301042.SZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>43.25</v>
       </c>
       <c r="D9" t="n">
-        <v>91.23999999999999</v>
+        <v>51.96</v>
       </c>
       <c r="E9" t="n">
-        <v>80.8</v>
+        <v>41.63</v>
       </c>
       <c r="F9" t="n">
-        <v>81.59999999999999</v>
+        <v>41.63</v>
       </c>
       <c r="G9" t="n">
-        <v>95.09999999999999</v>
+        <v>52.04</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.5</v>
+        <v>-10.41</v>
      